--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="1717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="1718">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5495910644531</t>
+    <t xml:space="preserve">13.5495901107788</t>
   </si>
   <si>
     <t xml:space="preserve">SES.MI</t>
@@ -47,40 +47,40 @@
     <t xml:space="preserve">13.5321063995361</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2523717880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9464159011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1125059127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.858998298645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0513153076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9901237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9376735687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1037654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0250902175903</t>
+    <t xml:space="preserve">13.2523746490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9464168548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1125068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8589992523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0513143539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.990122795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9376745223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1037635803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.025089263916</t>
   </si>
   <si>
     <t xml:space="preserve">12.8502559661865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.238338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5880079269409</t>
+    <t xml:space="preserve">12.2383394241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5880060195923</t>
   </si>
   <si>
     <t xml:space="preserve">12.7890644073486</t>
@@ -89,13 +89,13 @@
     <t xml:space="preserve">12.7191314697266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6841640472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6054906845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3257579803467</t>
+    <t xml:space="preserve">12.6841650009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.605489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3257570266724</t>
   </si>
   <si>
     <t xml:space="preserve">12.0460224151611</t>
@@ -104,55 +104,55 @@
     <t xml:space="preserve">12.1771488189697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1421813964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9270896911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9795389175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3641729354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4515905380249</t>
+    <t xml:space="preserve">12.1421823501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9270877838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9795398712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3641719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4515886306763</t>
   </si>
   <si>
     <t xml:space="preserve">12.0984725952148</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1072158813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8886728286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9760904312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9323806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0110559463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0809907913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8012552261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334390640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8274803161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0635070800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5005912780762</t>
+    <t xml:space="preserve">12.1072149276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8886737823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9760875701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9323816299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0110578536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0809888839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8012571334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334400177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8274822235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0635061264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5005884170532</t>
   </si>
   <si>
     <t xml:space="preserve">12.675422668457</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">12.7978067398071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1649580001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1562156677246</t>
+    <t xml:space="preserve">13.1649570465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1562147140503</t>
   </si>
   <si>
     <t xml:space="preserve">13.0687990188599</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve">13.1212491989136</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1911811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7540979385376</t>
+    <t xml:space="preserve">13.1911821365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7540988922119</t>
   </si>
   <si>
     <t xml:space="preserve">12.8939647674561</t>
@@ -191,37 +191,37 @@
     <t xml:space="preserve">13.1999244689941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9813823699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4534330368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7069406509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4709148406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4621734619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2086658477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3223056793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.095025062561</t>
+    <t xml:space="preserve">12.9813814163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4534320831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7069396972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4709167480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4621725082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.208664894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3223066329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0950222015381</t>
   </si>
   <si>
     <t xml:space="preserve">12.9988651275635</t>
   </si>
   <si>
-    <t xml:space="preserve">12.640456199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4481382369995</t>
+    <t xml:space="preserve">12.6404590606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4481391906738</t>
   </si>
   <si>
     <t xml:space="preserve">12.3782072067261</t>
@@ -230,25 +230,25 @@
     <t xml:space="preserve">12.0285396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1509237289429</t>
+    <t xml:space="preserve">12.1509227752686</t>
   </si>
   <si>
     <t xml:space="preserve">12.4393978118896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5617828369141</t>
+    <t xml:space="preserve">12.5617818832397</t>
   </si>
   <si>
     <t xml:space="preserve">12.5268135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6317138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3694658279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7715835571289</t>
+    <t xml:space="preserve">12.6317148208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3694629669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7715826034546</t>
   </si>
   <si>
     <t xml:space="preserve">12.4306573867798</t>
@@ -257,58 +257,58 @@
     <t xml:space="preserve">12.2820472717285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1946296691895</t>
+    <t xml:space="preserve">12.1946306228638</t>
   </si>
   <si>
     <t xml:space="preserve">12.2470817565918</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4131727218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.509331703186</t>
+    <t xml:space="preserve">12.4131736755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5093326568604</t>
   </si>
   <si>
     <t xml:space="preserve">12.3869485855103</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8187408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8449649810791</t>
+    <t xml:space="preserve">11.8187398910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8449630737305</t>
   </si>
   <si>
     <t xml:space="preserve">12.2558240890503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5792646408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2208566665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1858901977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7803230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7278728485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8764810562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8065481185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7628402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8677406311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327732086182</t>
+    <t xml:space="preserve">12.5792655944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2208557128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1858882904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7803220748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7278738021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8764820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.806547164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7628412246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8677396774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327741622925</t>
   </si>
   <si>
     <t xml:space="preserve">12.5355567932129</t>
@@ -320,40 +320,40 @@
     <t xml:space="preserve">13.0338315963745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3048248291016</t>
+    <t xml:space="preserve">13.3048238754272</t>
   </si>
   <si>
     <t xml:space="preserve">13.261116027832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3747587203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6020421981812</t>
+    <t xml:space="preserve">13.3747568130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6020402908325</t>
   </si>
   <si>
     <t xml:space="preserve">13.6894569396973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.724422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7514762878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5711297988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8687019348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6252346038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6432685852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6613025665283</t>
+    <t xml:space="preserve">13.7244243621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7514753341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5711278915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8687028884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6252326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6432676315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.661301612854</t>
   </si>
   <si>
     <t xml:space="preserve">13.598180770874</t>
@@ -362,40 +362,40 @@
     <t xml:space="preserve">13.6162157058716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5260410308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5530939102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3456945419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801467895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6973724365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7785263061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6703176498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7965641021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9769105911255</t>
+    <t xml:space="preserve">13.5260419845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5530948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3456954956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801458358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6973705291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.778528213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6703205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7965631484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9769096374512</t>
   </si>
   <si>
     <t xml:space="preserve">14.0400314331055</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0129804611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9047727584839</t>
+    <t xml:space="preserve">14.0129776000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9047708511353</t>
   </si>
   <si>
     <t xml:space="preserve">14.1031532287598</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">14.2474308013916</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1572561264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3646574020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4187602996826</t>
+    <t xml:space="preserve">14.1572570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3646554946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4187593460083</t>
   </si>
   <si>
     <t xml:space="preserve">14.517951965332</t>
@@ -422,25 +422,25 @@
     <t xml:space="preserve">14.6622295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3917083740234</t>
+    <t xml:space="preserve">14.3917093276978</t>
   </si>
   <si>
     <t xml:space="preserve">14.3105525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3015356063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5450029373169</t>
+    <t xml:space="preserve">14.30153465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5450019836426</t>
   </si>
   <si>
     <t xml:space="preserve">14.6441946029663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7343692779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7163333892822</t>
+    <t xml:space="preserve">14.7343673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7163324356079</t>
   </si>
   <si>
     <t xml:space="preserve">14.6351776123047</t>
@@ -458,55 +458,55 @@
     <t xml:space="preserve">14.80650806427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7433862686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5810737609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6982975006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5089349746704</t>
+    <t xml:space="preserve">14.74338722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.581072807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.698299407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5089340209961</t>
   </si>
   <si>
     <t xml:space="preserve">14.6712474822998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6532125473022</t>
+    <t xml:space="preserve">14.6532115936279</t>
   </si>
   <si>
     <t xml:space="preserve">14.923731803894</t>
   </si>
   <si>
-    <t xml:space="preserve">15.049976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2122898101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3746004104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5549488067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9246587753296</t>
+    <t xml:space="preserve">15.0499744415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2122888565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3746013641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5549468994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9246606826782</t>
   </si>
   <si>
     <t xml:space="preserve">15.7803812026978</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8705568313599</t>
+    <t xml:space="preserve">15.8705549240112</t>
   </si>
   <si>
     <t xml:space="preserve">15.8344860076904</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7082462310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.951714515686</t>
+    <t xml:space="preserve">15.7082405090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517116546631</t>
   </si>
   <si>
     <t xml:space="preserve">16.7452392578125</t>
@@ -521,52 +521,52 @@
     <t xml:space="preserve">17.1510219573975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2231616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9796905517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9075527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3043174743652</t>
+    <t xml:space="preserve">17.2231597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9796924591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9075546264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3043193817139</t>
   </si>
   <si>
     <t xml:space="preserve">17.0337963104248</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2772617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4756469726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3223495483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.169059753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5838565826416</t>
+    <t xml:space="preserve">17.2772636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4756450653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3223476409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1690559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.583854675293</t>
   </si>
   <si>
     <t xml:space="preserve">17.574836730957</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5658168792725</t>
+    <t xml:space="preserve">17.5658206939697</t>
   </si>
   <si>
     <t xml:space="preserve">17.2411956787109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1870918273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8534469604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8444328308105</t>
+    <t xml:space="preserve">17.1870899200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8534507751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8444309234619</t>
   </si>
   <si>
     <t xml:space="preserve">16.9526386260986</t>
@@ -578,88 +578,88 @@
     <t xml:space="preserve">16.6911334991455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8624649047852</t>
+    <t xml:space="preserve">16.8624668121338</t>
   </si>
   <si>
     <t xml:space="preserve">17.0428123474121</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8173789978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9977264404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7722949981689</t>
+    <t xml:space="preserve">16.8173751831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9977245330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7722930908203</t>
   </si>
   <si>
     <t xml:space="preserve">17.006742477417</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1961078643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3584175109863</t>
+    <t xml:space="preserve">17.1961059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3584213256836</t>
   </si>
   <si>
     <t xml:space="preserve">17.6199264526367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7642021179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0076694488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9896354675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9445476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9535636901855</t>
+    <t xml:space="preserve">17.7642002105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0076713562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9896373748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9445495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9535675048828</t>
   </si>
   <si>
     <t xml:space="preserve">17.809289932251</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2601585388184</t>
+    <t xml:space="preserve">18.2601547241211</t>
   </si>
   <si>
     <t xml:space="preserve">18.7561092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.846284866333</t>
+    <t xml:space="preserve">18.8462829589844</t>
   </si>
   <si>
     <t xml:space="preserve">18.9364585876465</t>
   </si>
   <si>
-    <t xml:space="preserve">18.620849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2971534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3602752685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3512573242188</t>
+    <t xml:space="preserve">18.6208477020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.297155380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3602771759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3512554168701</t>
   </si>
   <si>
     <t xml:space="preserve">19.666862487793</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6488342285156</t>
+    <t xml:space="preserve">19.6488304138184</t>
   </si>
   <si>
     <t xml:space="preserve">19.5586566925049</t>
   </si>
   <si>
-    <t xml:space="preserve">19.252067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1709098815918</t>
+    <t xml:space="preserve">19.2520656585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1709117889404</t>
   </si>
   <si>
     <t xml:space="preserve">19.1348400115967</t>
@@ -671,76 +671,76 @@
     <t xml:space="preserve">18.9544944763184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9094085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0897560119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5757617950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1970329284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5306777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8372669219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4594669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3873252868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0185432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3612041473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8301048278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2809715270996</t>
+    <t xml:space="preserve">18.9094047546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0897579193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5757637023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1970348358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5306739807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8372707366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4594650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3873233795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0185413360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3612003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8301067352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2809734344482</t>
   </si>
   <si>
     <t xml:space="preserve">20.8751907348633</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9292964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1006240844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0104522705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5686016082764</t>
+    <t xml:space="preserve">20.9292945861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.100622177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0104484558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5685997009277</t>
   </si>
   <si>
     <t xml:space="preserve">20.7218952178955</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6046695709229</t>
+    <t xml:space="preserve">20.6046714782715</t>
   </si>
   <si>
     <t xml:space="preserve">20.1898708343506</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3792324066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6497535705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6416683197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3711490631104</t>
+    <t xml:space="preserve">20.3792381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6497592926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6416664123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3711452484131</t>
   </si>
   <si>
     <t xml:space="preserve">21.380163192749</t>
@@ -755,31 +755,31 @@
     <t xml:space="preserve">22.7147350311279</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8049068450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5984325408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0763549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0583229064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7156562805176</t>
+    <t xml:space="preserve">22.8049087524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5984344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0763530731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0583171844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7156581878662</t>
   </si>
   <si>
     <t xml:space="preserve">23.9320755004883</t>
   </si>
   <si>
-    <t xml:space="preserve">23.859935760498</t>
+    <t xml:space="preserve">23.8599395751953</t>
   </si>
   <si>
     <t xml:space="preserve">23.8058319091797</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5082626342773</t>
+    <t xml:space="preserve">23.5082607269287</t>
   </si>
   <si>
     <t xml:space="preserve">22.9942722320557</t>
@@ -788,37 +788,37 @@
     <t xml:space="preserve">22.4802799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5434055328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7057132720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4532318115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4622497558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0023612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.182710647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7237510681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3630561828613</t>
+    <t xml:space="preserve">22.5434017181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7057151794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4532299041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4622478485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0023593902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1827087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7237491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3630542755127</t>
   </si>
   <si>
     <t xml:space="preserve">22.2097587585449</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4883728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9212017059326</t>
+    <t xml:space="preserve">21.4883689880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9212074279785</t>
   </si>
   <si>
     <t xml:space="preserve">21.8761177062988</t>
@@ -827,31 +827,31 @@
     <t xml:space="preserve">21.7047882080078</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9392395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0745029449463</t>
+    <t xml:space="preserve">21.9392375946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0745010375977</t>
   </si>
   <si>
     <t xml:space="preserve">22.2999362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8139247894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3179683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1917285919189</t>
+    <t xml:space="preserve">22.8139228820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3179664611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1917247772217</t>
   </si>
   <si>
     <t xml:space="preserve">22.3540382385254</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5253658294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6065273284912</t>
+    <t xml:space="preserve">22.5253677368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6065235137939</t>
   </si>
   <si>
     <t xml:space="preserve">22.6335773468018</t>
@@ -860,19 +860,19 @@
     <t xml:space="preserve">22.2458305358887</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2277965545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1286029815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.083517074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2007446289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1376209259033</t>
+    <t xml:space="preserve">22.2277946472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1286067962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0835151672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2007465362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.137622833252</t>
   </si>
   <si>
     <t xml:space="preserve">22.1466388702393</t>
@@ -881,55 +881,55 @@
     <t xml:space="preserve">21.5965805053711</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3260593414307</t>
+    <t xml:space="preserve">21.326057434082</t>
   </si>
   <si>
     <t xml:space="preserve">21.560510635376</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0294132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6867523193359</t>
+    <t xml:space="preserve">22.0294151306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6867542266846</t>
   </si>
   <si>
     <t xml:space="preserve">22.2368144989014</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3720741271973</t>
+    <t xml:space="preserve">22.3720722198486</t>
   </si>
   <si>
     <t xml:space="preserve">22.3991260528564</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6155433654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6606254577637</t>
+    <t xml:space="preserve">22.6155452728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6606292724609</t>
   </si>
   <si>
     <t xml:space="preserve">23.0123081207275</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5193881988525</t>
+    <t xml:space="preserve">23.5193901062012</t>
   </si>
   <si>
     <t xml:space="preserve">23.2704582214355</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1739845275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7087268829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7732677459717</t>
+    <t xml:space="preserve">24.1739864349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7087249755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.773265838623</t>
   </si>
   <si>
     <t xml:space="preserve">25.243465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8150844573975</t>
+    <t xml:space="preserve">25.8150863647461</t>
   </si>
   <si>
     <t xml:space="preserve">25.7966480255127</t>
@@ -938,22 +938,22 @@
     <t xml:space="preserve">25.6860122680664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6675720214844</t>
+    <t xml:space="preserve">25.667573928833</t>
   </si>
   <si>
     <t xml:space="preserve">26.0086975097656</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8888416290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9810409545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0916748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.907283782959</t>
+    <t xml:space="preserve">25.8888454437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9810390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0916728973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9072818756104</t>
   </si>
   <si>
     <t xml:space="preserve">25.8058662414551</t>
@@ -968,34 +968,34 @@
     <t xml:space="preserve">25.6583518981934</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0775127410889</t>
+    <t xml:space="preserve">25.0775146484375</t>
   </si>
   <si>
     <t xml:space="preserve">25.4002017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">25.261905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3264465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8009243011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4186401367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6441898345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8562412261963</t>
+    <t xml:space="preserve">25.2619018554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3264427185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8009204864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4186420440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6441879272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.856237411499</t>
   </si>
   <si>
     <t xml:space="preserve">24.9576568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8931179046631</t>
+    <t xml:space="preserve">24.8931198120117</t>
   </si>
   <si>
     <t xml:space="preserve">23.187479019165</t>
@@ -1004,85 +1004,85 @@
     <t xml:space="preserve">22.9754257202148</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1229400634766</t>
+    <t xml:space="preserve">23.1229457855225</t>
   </si>
   <si>
     <t xml:space="preserve">23.2335777282715</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9938659667969</t>
+    <t xml:space="preserve">22.9938678741455</t>
   </si>
   <si>
     <t xml:space="preserve">23.0123062133789</t>
   </si>
   <si>
-    <t xml:space="preserve">22.781810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6711769104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4960041046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7264976501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5052223205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3208312988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5881977081299</t>
+    <t xml:space="preserve">22.7818145751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6711807250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4960021972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7264957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5052261352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3208274841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5881996154785</t>
   </si>
   <si>
     <t xml:space="preserve">23.1137218475342</t>
   </si>
   <si>
-    <t xml:space="preserve">22.910888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3995304107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7775382995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6208076477051</t>
+    <t xml:space="preserve">22.9108905792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3995323181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7775421142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6208038330078</t>
   </si>
   <si>
     <t xml:space="preserve">23.1413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9846496582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8740081787109</t>
+    <t xml:space="preserve">22.9846458435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8740100860596</t>
   </si>
   <si>
     <t xml:space="preserve">22.7357177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6896171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3257751464844</t>
+    <t xml:space="preserve">22.6896152496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3257732391357</t>
   </si>
   <si>
     <t xml:space="preserve">23.7406597137451</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9803733825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9711494445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.063346862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2477416992188</t>
+    <t xml:space="preserve">23.9803714752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9711513519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0633487701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2477397918701</t>
   </si>
   <si>
     <t xml:space="preserve">24.3860397338867</t>
@@ -1094,40 +1094,40 @@
     <t xml:space="preserve">24.616527557373</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8611869812012</t>
+    <t xml:space="preserve">25.8611831665039</t>
   </si>
   <si>
     <t xml:space="preserve">25.6306934356689</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2158088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1697082519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080043792725</t>
+    <t xml:space="preserve">25.2158050537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1697101593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080062866211</t>
   </si>
   <si>
     <t xml:space="preserve">25.4462985992432</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5384979248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1236133575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4321365356445</t>
+    <t xml:space="preserve">25.5384960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1236095428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4321346282959</t>
   </si>
   <si>
     <t xml:space="preserve">23.6484622955322</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0172519683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1094493865967</t>
+    <t xml:space="preserve">24.0172500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1094455718994</t>
   </si>
   <si>
     <t xml:space="preserve">24.339937210083</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">24.2016448974609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2938423156738</t>
+    <t xml:space="preserve">24.2938404083252</t>
   </si>
   <si>
     <t xml:space="preserve">24.7548236846924</t>
@@ -1145,43 +1145,43 @@
     <t xml:space="preserve">24.6626281738281</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9853172302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4923973083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7228870391846</t>
+    <t xml:space="preserve">24.9853134155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.492395401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7228889465332</t>
   </si>
   <si>
     <t xml:space="preserve">24.5704288482666</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5845966339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9994792938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.414363861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5668239593506</t>
+    <t xml:space="preserve">25.5845928192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9994812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4143657684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5668258666992</t>
   </si>
   <si>
     <t xml:space="preserve">27.7512168884277</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0739078521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5207290649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7370548248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5065631866455</t>
+    <t xml:space="preserve">28.0739059448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5207252502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7370529174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5065612792969</t>
   </si>
   <si>
     <t xml:space="preserve">25.0314140319824</t>
@@ -1190,25 +1190,25 @@
     <t xml:space="preserve">24.5243339538574</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3682670593262</t>
+    <t xml:space="preserve">26.3682651519775</t>
   </si>
   <si>
     <t xml:space="preserve">26.5987586975098</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4604663848877</t>
+    <t xml:space="preserve">26.4604644775391</t>
   </si>
   <si>
     <t xml:space="preserve">26.2299709320068</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3221683502197</t>
+    <t xml:space="preserve">26.3221664428711</t>
   </si>
   <si>
     <t xml:space="preserve">27.1980361938477</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2760696411133</t>
+    <t xml:space="preserve">26.2760734558105</t>
   </si>
   <si>
     <t xml:space="preserve">27.2902355194092</t>
@@ -1229,97 +1229,97 @@
     <t xml:space="preserve">27.1058406829834</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8753490447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8434181213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7653846740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5809860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9356117248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8114814758301</t>
+    <t xml:space="preserve">26.8753471374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8434162139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.765380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5809879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9356098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8114795684814</t>
   </si>
   <si>
     <t xml:space="preserve">28.1661033630371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7192821502686</t>
+    <t xml:space="preserve">28.7192840576172</t>
   </si>
   <si>
     <t xml:space="preserve">28.1200046539307</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0597438812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9675483703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1519393920898</t>
+    <t xml:space="preserve">27.059741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9675445556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1519374847412</t>
   </si>
   <si>
     <t xml:space="preserve">26.6909561157227</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7831535339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0455799102783</t>
+    <t xml:space="preserve">26.7831516265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0455780029297</t>
   </si>
   <si>
     <t xml:space="preserve">27.6590213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9214458465576</t>
+    <t xml:space="preserve">26.9214496612549</t>
   </si>
   <si>
     <t xml:space="preserve">26.1828804016113</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0886993408203</t>
+    <t xml:space="preserve">26.0886974334717</t>
   </si>
   <si>
     <t xml:space="preserve">26.4654293060303</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8061466217041</t>
+    <t xml:space="preserve">25.8061485290527</t>
   </si>
   <si>
     <t xml:space="preserve">25.7119636535645</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1468677520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3352336883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9114112854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4875869750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.393404006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9224853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2632083892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0277481079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0748386383057</t>
+    <t xml:space="preserve">25.1468658447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3352317810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9114074707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.487585067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3934020996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9224872589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2632064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0277500152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0748424530029</t>
   </si>
   <si>
     <t xml:space="preserve">22.7451992034912</t>
@@ -1331,34 +1331,34 @@
     <t xml:space="preserve">22.5097427368164</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4155597686768</t>
+    <t xml:space="preserve">22.4155578613281</t>
   </si>
   <si>
     <t xml:space="preserve">22.1801013946533</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0388278961182</t>
+    <t xml:space="preserve">22.0388298034668</t>
   </si>
   <si>
     <t xml:space="preserve">21.8504619598389</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4626522064209</t>
+    <t xml:space="preserve">22.4626502990723</t>
   </si>
   <si>
     <t xml:space="preserve">22.2271919250488</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4044799804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2161178588867</t>
+    <t xml:space="preserve">23.4044818878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2161121368408</t>
   </si>
   <si>
     <t xml:space="preserve">22.886474609375</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4986610412598</t>
+    <t xml:space="preserve">23.498664855957</t>
   </si>
   <si>
     <t xml:space="preserve">22.5568332672119</t>
@@ -1367,46 +1367,46 @@
     <t xml:space="preserve">22.1330089569092</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6620979309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1911792755127</t>
+    <t xml:space="preserve">21.6620941162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1911811828613</t>
   </si>
   <si>
     <t xml:space="preserve">21.0028133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0969982147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8615379333496</t>
+    <t xml:space="preserve">21.096996307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8615398406982</t>
   </si>
   <si>
     <t xml:space="preserve">21.379545211792</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4737300872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2742824554443</t>
+    <t xml:space="preserve">21.4737281799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.274284362793</t>
   </si>
   <si>
     <t xml:space="preserve">21.7562770843506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9446449279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5679111480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5208225250244</t>
+    <t xml:space="preserve">21.9446468353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5679130554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5208187103271</t>
   </si>
   <si>
     <t xml:space="preserve">21.3324546813965</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2382698059082</t>
+    <t xml:space="preserve">21.2382717132568</t>
   </si>
   <si>
     <t xml:space="preserve">22.8393840789795</t>
@@ -1415,34 +1415,34 @@
     <t xml:space="preserve">22.7922916412354</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5457534790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6399421691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7341213226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6870307922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.781213760376</t>
+    <t xml:space="preserve">23.5457553863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6399402618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7341232299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6870288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7812118530273</t>
   </si>
   <si>
     <t xml:space="preserve">24.0166721343994</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2992172241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1579456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.252124786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7230434417725</t>
+    <t xml:space="preserve">24.2992191314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1579418182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2521286010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7230453491211</t>
   </si>
   <si>
     <t xml:space="preserve">24.6288604736328</t>
@@ -1454,10 +1454,10 @@
     <t xml:space="preserve">24.5817680358887</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7701320648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9584999084473</t>
+    <t xml:space="preserve">24.7701358795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9585018157959</t>
   </si>
   <si>
     <t xml:space="preserve">25.900333404541</t>
@@ -1466,13 +1466,13 @@
     <t xml:space="preserve">25.7590579986572</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9474220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.277063369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9363460540771</t>
+    <t xml:space="preserve">25.9474201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2770614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9363422393799</t>
   </si>
   <si>
     <t xml:space="preserve">26.983434677124</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">26.7479782104492</t>
   </si>
   <si>
-    <t xml:space="preserve">27.265983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4543514251709</t>
+    <t xml:space="preserve">27.2659854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4543495178223</t>
   </si>
   <si>
     <t xml:space="preserve">27.501443862915</t>
@@ -1496,22 +1496,22 @@
     <t xml:space="preserve">27.3130760192871</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0776195526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7008857727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6537971496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6067047119141</t>
+    <t xml:space="preserve">27.0776176452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7008876800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6537952423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6067028045654</t>
   </si>
   <si>
     <t xml:space="preserve">25.9945125579834</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1357898712158</t>
+    <t xml:space="preserve">26.1357917785645</t>
   </si>
   <si>
     <t xml:space="preserve">26.0416030883789</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">25.6177825927734</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4294166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0055904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0997714996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8643188476562</t>
+    <t xml:space="preserve">25.4294185638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0055923461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0997753143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8643169403076</t>
   </si>
   <si>
     <t xml:space="preserve">24.4404964447021</t>
@@ -1538,52 +1538,52 @@
     <t xml:space="preserve">25.5235977172852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.371244430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3241577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7950687408447</t>
+    <t xml:space="preserve">26.3712463378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3241558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.795072555542</t>
   </si>
   <si>
     <t xml:space="preserve">26.8892517089844</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0305309295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1718044281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5485363006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6898059844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1136302947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.396183013916</t>
+    <t xml:space="preserve">27.0305290222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1718006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5485343933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6898078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1136322021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3961811065674</t>
   </si>
   <si>
     <t xml:space="preserve">28.7258224487305</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9141864776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9501991271973</t>
+    <t xml:space="preserve">28.9141902923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9502010345459</t>
   </si>
   <si>
     <t xml:space="preserve">29.761833190918</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3269348144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3740253448486</t>
+    <t xml:space="preserve">30.3269329071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3740272521973</t>
   </si>
   <si>
     <t xml:space="preserve">31.5042247772217</t>
@@ -1592,82 +1592,82 @@
     <t xml:space="preserve">31.692590713501</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4460563659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4931411743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.482063293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6704254150391</t>
+    <t xml:space="preserve">32.446044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4931449890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4820671081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6704330444336</t>
   </si>
   <si>
     <t xml:space="preserve">33.2936973571777</t>
   </si>
   <si>
-    <t xml:space="preserve">33.576244354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9058876037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2466049194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.869873046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1524276733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0582389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5873222351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3047790527344</t>
+    <t xml:space="preserve">33.5762481689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9058837890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2466087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8698768615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1524200439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.058235168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5873260498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3047752380371</t>
   </si>
   <si>
     <t xml:space="preserve">31.9280490875244</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4571304321289</t>
+    <t xml:space="preserve">31.4571342468262</t>
   </si>
   <si>
     <t xml:space="preserve">31.3629474639893</t>
   </si>
   <si>
-    <t xml:space="preserve">30.892032623291</t>
+    <t xml:space="preserve">30.8920269012451</t>
   </si>
   <si>
     <t xml:space="preserve">31.0803966522217</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0333080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6565723419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6094818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2687664031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9862174987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4100360870361</t>
+    <t xml:space="preserve">31.0333042144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6565742492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6094837188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2687644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9862194061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4100379943848</t>
   </si>
   <si>
     <t xml:space="preserve">30.8449401855469</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1745758056641</t>
+    <t xml:space="preserve">31.1745777130127</t>
   </si>
   <si>
     <t xml:space="preserve">31.8809509277344</t>
@@ -1679,22 +1679,22 @@
     <t xml:space="preserve">31.7396755218506</t>
   </si>
   <si>
-    <t xml:space="preserve">34.000072479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4709854125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.78955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5901031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7784652709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1552047729492</t>
+    <t xml:space="preserve">34.0000686645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4709815979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7895469665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5900993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7784690856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.155200958252</t>
   </si>
   <si>
     <t xml:space="preserve">37.6732063293457</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">38.1803665161133</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3717498779297</t>
+    <t xml:space="preserve">38.3717422485352</t>
   </si>
   <si>
     <t xml:space="preserve">37.9411430358887</t>
@@ -1724,25 +1724,25 @@
     <t xml:space="preserve">37.9889907836914</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8454513549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3191604614258</t>
+    <t xml:space="preserve">37.8454551696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3191566467285</t>
   </si>
   <si>
     <t xml:space="preserve">38.8501968383789</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7545051574707</t>
+    <t xml:space="preserve">38.754508972168</t>
   </si>
   <si>
     <t xml:space="preserve">39.3286437988281</t>
   </si>
   <si>
-    <t xml:space="preserve">39.041576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8023529052734</t>
+    <t xml:space="preserve">39.0415802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8023490905762</t>
   </si>
   <si>
     <t xml:space="preserve">38.4674377441406</t>
@@ -1751,10 +1751,10 @@
     <t xml:space="preserve">38.1325149536133</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8980484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7066612243652</t>
+    <t xml:space="preserve">38.8980445861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7066650390625</t>
   </si>
   <si>
     <t xml:space="preserve">38.2760543823242</t>
@@ -1763,31 +1763,31 @@
     <t xml:space="preserve">38.5631256103516</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4195938110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3764953613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1372680664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1851081848145</t>
+    <t xml:space="preserve">38.4195899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3764915466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1372718811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.185115814209</t>
   </si>
   <si>
     <t xml:space="preserve">39.2808036804199</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9027938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1946067810059</t>
+    <t xml:space="preserve">39.9027900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1946029663086</t>
   </si>
   <si>
     <t xml:space="preserve">42.1036643981934</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5342712402344</t>
+    <t xml:space="preserve">42.5342750549316</t>
   </si>
   <si>
     <t xml:space="preserve">41.6730537414551</t>
@@ -1796,52 +1796,52 @@
     <t xml:space="preserve">40.8118476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7161560058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9122848510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0605621337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4911689758301</t>
+    <t xml:space="preserve">40.7161521911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9122772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0605659484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4911727905273</t>
   </si>
   <si>
     <t xml:space="preserve">44.2566909790039</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7829856872559</t>
+    <t xml:space="preserve">44.7829895019531</t>
   </si>
   <si>
     <t xml:space="preserve">43.4433250427246</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0174674987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6347007751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2041015625</t>
+    <t xml:space="preserve">44.017463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6347045898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2041053771973</t>
   </si>
   <si>
     <t xml:space="preserve">42.9170303344727</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9265174865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.404972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2614364624023</t>
+    <t xml:space="preserve">44.9265213012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4049682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2614326477051</t>
   </si>
   <si>
     <t xml:space="preserve">45.5963554382324</t>
   </si>
   <si>
-    <t xml:space="preserve">47.653694152832</t>
+    <t xml:space="preserve">47.6536865234375</t>
   </si>
   <si>
     <t xml:space="preserve">48.8976631164551</t>
@@ -1850,43 +1850,43 @@
     <t xml:space="preserve">48.6105918884277</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1847381591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9933547973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7588768005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2804183959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6631851196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3761100769043</t>
+    <t xml:space="preserve">49.1847343444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.993350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7588729858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2804260253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6631813049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3761138916016</t>
   </si>
   <si>
     <t xml:space="preserve">49.5674934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6200866699219</t>
+    <t xml:space="preserve">50.6200828552246</t>
   </si>
   <si>
     <t xml:space="preserve">51.0028457641602</t>
   </si>
   <si>
-    <t xml:space="preserve">52.7252655029297</t>
+    <t xml:space="preserve">52.725269317627</t>
   </si>
   <si>
     <t xml:space="preserve">52.6295776367188</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9597473144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8640518188477</t>
+    <t xml:space="preserve">51.9597396850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8640556335449</t>
   </si>
   <si>
     <t xml:space="preserve">51.6726760864258</t>
@@ -1895,49 +1895,49 @@
     <t xml:space="preserve">48.4192085266113</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3235206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0459403991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3856048583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9071578979492</t>
+    <t xml:space="preserve">48.3235244750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0459480285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3856086730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.907154083252</t>
   </si>
   <si>
     <t xml:space="preserve">49.8545608520508</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4287033081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5338859558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0649337768555</t>
+    <t xml:space="preserve">50.4287071228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5338897705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0649299621582</t>
   </si>
   <si>
     <t xml:space="preserve">53.2994079589844</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4381942749023</t>
+    <t xml:space="preserve">52.4381980895996</t>
   </si>
   <si>
     <t xml:space="preserve">47.3666191101074</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9838600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3618774414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7398834228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.974365234375</t>
+    <t xml:space="preserve">46.9838562011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.361873626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7398872375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9743614196777</t>
   </si>
   <si>
     <t xml:space="preserve">43.5868606567383</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">41.7687454223633</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6493225097656</t>
+    <t xml:space="preserve">36.6493263244629</t>
   </si>
   <si>
     <t xml:space="preserve">35.5967330932617</t>
@@ -1964,22 +1964,22 @@
     <t xml:space="preserve">31.5299053192139</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0992965698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3816204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9269027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.410099029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5010452270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3096618652344</t>
+    <t xml:space="preserve">31.0992946624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3816223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9268989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4100952148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5010414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3096656799316</t>
   </si>
   <si>
     <t xml:space="preserve">34.5441398620605</t>
@@ -1988,16 +1988,16 @@
     <t xml:space="preserve">35.0704345703125</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0799331665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2234649658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1277694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2329559326172</t>
+    <t xml:space="preserve">37.0799255371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.223461151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1277770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2329597473145</t>
   </si>
   <si>
     <t xml:space="preserve">40.429084777832</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">44.7351379394531</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9791107177734</t>
+    <t xml:space="preserve">45.9791145324707</t>
   </si>
   <si>
     <t xml:space="preserve">45.4528160095215</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">45.0700569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3571281433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1179046630859</t>
+    <t xml:space="preserve">45.3571319580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1179008483887</t>
   </si>
   <si>
     <t xml:space="preserve">46.4575614929199</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">44.8786773681641</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3092842102051</t>
+    <t xml:space="preserve">45.3092803955078</t>
   </si>
   <si>
     <t xml:space="preserve">45.1657447814941</t>
@@ -2045,31 +2045,31 @@
     <t xml:space="preserve">43.15625</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9217720031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8644371032715</t>
+    <t xml:space="preserve">43.9217758178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8644409179688</t>
   </si>
   <si>
     <t xml:space="preserve">42.5821113586426</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0222129821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5485076904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5101585388184</t>
+    <t xml:space="preserve">45.0222053527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5485038757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5101509094238</t>
   </si>
   <si>
     <t xml:space="preserve">47.7015342712402</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7062873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9407577514648</t>
+    <t xml:space="preserve">48.7062797546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9407615661621</t>
   </si>
   <si>
     <t xml:space="preserve">48.5149002075195</t>
@@ -2078,19 +2078,19 @@
     <t xml:space="preserve">51.4812965393066</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1942291259766</t>
+    <t xml:space="preserve">51.1942253112793</t>
   </si>
   <si>
     <t xml:space="preserve">51.7683639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2899169921875</t>
+    <t xml:space="preserve">51.2899131774902</t>
   </si>
   <si>
     <t xml:space="preserve">53.1080322265625</t>
   </si>
   <si>
-    <t xml:space="preserve">53.96923828125</t>
+    <t xml:space="preserve">53.9692420959473</t>
   </si>
   <si>
     <t xml:space="preserve">53.4907913208008</t>
@@ -2099,25 +2099,25 @@
     <t xml:space="preserve">55.1175231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6916656494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5002822875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3519973754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6390686035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8304481506348</t>
+    <t xml:space="preserve">55.6916618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5002784729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.351993560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6390647888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.830451965332</t>
   </si>
   <si>
     <t xml:space="preserve">55.4045944213867</t>
   </si>
   <si>
-    <t xml:space="preserve">56.744255065918</t>
+    <t xml:space="preserve">56.7442512512207</t>
   </si>
   <si>
     <t xml:space="preserve">56.9356346130371</t>
@@ -2126,34 +2126,34 @@
     <t xml:space="preserve">57.1270141601562</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2658004760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9787368774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3183937072754</t>
+    <t xml:space="preserve">56.2658042907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9787330627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3183975219727</t>
   </si>
   <si>
     <t xml:space="preserve">58.6580543518066</t>
   </si>
   <si>
-    <t xml:space="preserve">57.2227020263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7011604309082</t>
+    <t xml:space="preserve">57.2227058410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7011528015137</t>
   </si>
   <si>
     <t xml:space="preserve">56.3614921569824</t>
   </si>
   <si>
-    <t xml:space="preserve">57.9882278442383</t>
+    <t xml:space="preserve">57.988224029541</t>
   </si>
   <si>
     <t xml:space="preserve">58.8494338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">61.3373756408691</t>
+    <t xml:space="preserve">61.3373794555664</t>
   </si>
   <si>
     <t xml:space="preserve">63.4425659179688</t>
@@ -2162,13 +2162,13 @@
     <t xml:space="preserve">62.2942810058594</t>
   </si>
   <si>
-    <t xml:space="preserve">63.346866607666</t>
+    <t xml:space="preserve">63.3468704223633</t>
   </si>
   <si>
     <t xml:space="preserve">63.7296295166016</t>
   </si>
   <si>
-    <t xml:space="preserve">63.6339454650879</t>
+    <t xml:space="preserve">63.6339416503906</t>
   </si>
   <si>
     <t xml:space="preserve">64.3037719726562</t>
@@ -2177,10 +2177,10 @@
     <t xml:space="preserve">64.5908432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">65.9305114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6960220336914</t>
+    <t xml:space="preserve">65.9305038452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6960296630859</t>
   </si>
   <si>
     <t xml:space="preserve">65.3563690185547</t>
@@ -2189,37 +2189,37 @@
     <t xml:space="preserve">66.9831008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">67.1744689941406</t>
+    <t xml:space="preserve">67.1744766235352</t>
   </si>
   <si>
     <t xml:space="preserve">66.5046463012695</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8443222045898</t>
+    <t xml:space="preserve">67.8443069458008</t>
   </si>
   <si>
     <t xml:space="preserve">70.0451889038086</t>
   </si>
   <si>
-    <t xml:space="preserve">69.1839752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.2891464233398</t>
+    <t xml:space="preserve">69.1839828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.2891540527344</t>
   </si>
   <si>
     <t xml:space="preserve">70.8107070922852</t>
   </si>
   <si>
-    <t xml:space="preserve">70.6193237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7676086425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.0546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0020904541016</t>
+    <t xml:space="preserve">70.6193313598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7676010131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.0546722412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.002082824707</t>
   </si>
   <si>
     <t xml:space="preserve">69.4710388183594</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">68.9925994873047</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9495010375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8012161254883</t>
+    <t xml:space="preserve">69.9494857788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8012084960938</t>
   </si>
   <si>
     <t xml:space="preserve">69.6624221801758</t>
@@ -2258,13 +2258,13 @@
     <t xml:space="preserve">77.8917694091797</t>
   </si>
   <si>
-    <t xml:space="preserve">78.2745361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.7960968017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.4228134155273</t>
+    <t xml:space="preserve">78.274543762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.7960891723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.4228210449219</t>
   </si>
   <si>
     <t xml:space="preserve">80.7624816894531</t>
@@ -2276,19 +2276,19 @@
     <t xml:space="preserve">81.5279922485352</t>
   </si>
   <si>
-    <t xml:space="preserve">81.9107666015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.3892135620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4323120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.1452484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4753952026367</t>
+    <t xml:space="preserve">81.910758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.3892059326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4323043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1452407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4754104614258</t>
   </si>
   <si>
     <t xml:space="preserve">81.7193832397461</t>
@@ -2300,34 +2300,34 @@
     <t xml:space="preserve">83.3461074829102</t>
   </si>
   <si>
-    <t xml:space="preserve">80.953857421875</t>
+    <t xml:space="preserve">80.9538497924805</t>
   </si>
   <si>
     <t xml:space="preserve">82.7719802856445</t>
   </si>
   <si>
-    <t xml:space="preserve">82.2935104370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.0305709838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3271331787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.728874206543</t>
+    <t xml:space="preserve">82.2935256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.0305633544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3271255493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7288818359375</t>
   </si>
   <si>
     <t xml:space="preserve">82.1021423339844</t>
   </si>
   <si>
-    <t xml:space="preserve">76.7434997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.5185012817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8055877685547</t>
+    <t xml:space="preserve">76.7434844970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.5185089111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8055801391602</t>
   </si>
   <si>
     <t xml:space="preserve">82.4849014282227</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">78.6572875976562</t>
   </si>
   <si>
-    <t xml:space="preserve">78.4659118652344</t>
+    <t xml:space="preserve">78.4659194946289</t>
   </si>
   <si>
     <t xml:space="preserve">84.6857681274414</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">85.3556060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">83.0590362548828</t>
+    <t xml:space="preserve">83.0590438842773</t>
   </si>
   <si>
     <t xml:space="preserve">85.9297485351562</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">87.1737213134766</t>
   </si>
   <si>
-    <t xml:space="preserve">87.269401550293</t>
+    <t xml:space="preserve">87.2694091796875</t>
   </si>
   <si>
     <t xml:space="preserve">88.3219985961914</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">93.1065139770508</t>
   </si>
   <si>
-    <t xml:space="preserve">95.8815155029297</t>
+    <t xml:space="preserve">95.8815231323242</t>
   </si>
   <si>
     <t xml:space="preserve">97.2211837768555</t>
@@ -2384,16 +2384,16 @@
     <t xml:space="preserve">100.474647521973</t>
   </si>
   <si>
-    <t xml:space="preserve">101.622932434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.240173339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.9867095947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5608367919922</t>
+    <t xml:space="preserve">101.622917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.240165710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.986701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5608520507812</t>
   </si>
   <si>
     <t xml:space="preserve">99.900505065918</t>
@@ -2405,37 +2405,37 @@
     <t xml:space="preserve">95.6901397705078</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8289337158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3073883056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2547912597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.446159362793</t>
+    <t xml:space="preserve">94.8289260864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.307373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2547836303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4461669921875</t>
   </si>
   <si>
     <t xml:space="preserve">97.0298004150391</t>
   </si>
   <si>
-    <t xml:space="preserve">94.541862487793</t>
+    <t xml:space="preserve">94.5418548583984</t>
   </si>
   <si>
     <t xml:space="preserve">94.1591033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8720169067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0634078979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3935699462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6806488037109</t>
+    <t xml:space="preserve">93.8720321655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0634155273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3935775756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6806411743164</t>
   </si>
   <si>
     <t xml:space="preserve">92.9151229858398</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">93.2978897094727</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7237548828125</t>
+    <t xml:space="preserve">92.723747253418</t>
   </si>
   <si>
     <t xml:space="preserve">94.3504867553711</t>
@@ -2453,52 +2453,52 @@
     <t xml:space="preserve">97.6039428710938</t>
   </si>
   <si>
-    <t xml:space="preserve">101.431541442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.876388549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.493629455566</t>
+    <t xml:space="preserve">101.43155670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.876396179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.493621826172</t>
   </si>
   <si>
     <t xml:space="preserve">106.598815917969</t>
   </si>
   <si>
-    <t xml:space="preserve">107.36434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.66089630127</t>
+    <t xml:space="preserve">107.364334106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.660903930664</t>
   </si>
   <si>
     <t xml:space="preserve">110.235046386719</t>
   </si>
   <si>
-    <t xml:space="preserve">105.641914367676</t>
+    <t xml:space="preserve">105.641929626465</t>
   </si>
   <si>
     <t xml:space="preserve">106.216064453125</t>
   </si>
   <si>
-    <t xml:space="preserve">107.9384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.555717468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.469520568848</t>
+    <t xml:space="preserve">107.938484191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.555725097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.469528198242</t>
   </si>
   <si>
     <t xml:space="preserve">107.747100830078</t>
   </si>
   <si>
-    <t xml:space="preserve">108.703994750977</t>
+    <t xml:space="preserve">108.703987121582</t>
   </si>
   <si>
     <t xml:space="preserve">102.197074890137</t>
   </si>
   <si>
-    <t xml:space="preserve">99.5177536010742</t>
+    <t xml:space="preserve">99.5177459716797</t>
   </si>
   <si>
     <t xml:space="preserve">99.7091217041016</t>
@@ -2510,13 +2510,13 @@
     <t xml:space="preserve">103.536727905273</t>
   </si>
   <si>
-    <t xml:space="preserve">106.024681091309</t>
+    <t xml:space="preserve">106.024673461914</t>
   </si>
   <si>
     <t xml:space="preserve">106.981582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">108.51261138916</t>
+    <t xml:space="preserve">108.512626647949</t>
   </si>
   <si>
     <t xml:space="preserve">105.833282470703</t>
@@ -2525,25 +2525,25 @@
     <t xml:space="preserve">101.048789978027</t>
   </si>
   <si>
-    <t xml:space="preserve">102.388458251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.153984069824</t>
+    <t xml:space="preserve">102.388450622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.15397644043</t>
   </si>
   <si>
     <t xml:space="preserve">102.962593078613</t>
   </si>
   <si>
-    <t xml:space="preserve">105.450531005859</t>
+    <t xml:space="preserve">105.450538635254</t>
   </si>
   <si>
     <t xml:space="preserve">102.00569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">103.919494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.407440185547</t>
+    <t xml:space="preserve">103.919479370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.407432556152</t>
   </si>
   <si>
     <t xml:space="preserve">109.086761474609</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">110.809188842773</t>
   </si>
   <si>
-    <t xml:space="preserve">113.679885864258</t>
+    <t xml:space="preserve">113.679893493652</t>
   </si>
   <si>
     <t xml:space="preserve">110.043655395508</t>
@@ -2561,10 +2561,10 @@
     <t xml:space="preserve">107.172958374023</t>
   </si>
   <si>
-    <t xml:space="preserve">111.000564575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.914367675781</t>
+    <t xml:space="preserve">111.000556945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.914360046387</t>
   </si>
   <si>
     <t xml:space="preserve">109.85228729248</t>
@@ -2573,16 +2573,16 @@
     <t xml:space="preserve">110.426422119141</t>
   </si>
   <si>
-    <t xml:space="preserve">111.383331298828</t>
+    <t xml:space="preserve">111.383323669434</t>
   </si>
   <si>
     <t xml:space="preserve">112.340232849121</t>
   </si>
   <si>
-    <t xml:space="preserve">114.445404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.297134399414</t>
+    <t xml:space="preserve">114.445411682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.29712677002</t>
   </si>
   <si>
     <t xml:space="preserve">112.722984313965</t>
@@ -2591,16 +2591,16 @@
     <t xml:space="preserve">115.019546508789</t>
   </si>
   <si>
-    <t xml:space="preserve">115.593688964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.2109375</t>
+    <t xml:space="preserve">115.593696594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.210922241211</t>
   </si>
   <si>
     <t xml:space="preserve">116.741973876953</t>
   </si>
   <si>
-    <t xml:space="preserve">116.167831420898</t>
+    <t xml:space="preserve">116.167839050293</t>
   </si>
   <si>
     <t xml:space="preserve">115.785064697266</t>
@@ -2612,31 +2612,31 @@
     <t xml:space="preserve">119.804054260254</t>
   </si>
   <si>
-    <t xml:space="preserve">120.186828613281</t>
+    <t xml:space="preserve">120.186820983887</t>
   </si>
   <si>
     <t xml:space="preserve">122.100616455078</t>
   </si>
   <si>
-    <t xml:space="preserve">122.86612701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.631652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.478256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.267890930176</t>
+    <t xml:space="preserve">122.866134643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.631660461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.478240966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.267883300781</t>
   </si>
   <si>
     <t xml:space="preserve">127.459259033203</t>
   </si>
   <si>
-    <t xml:space="preserve">128.990295410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.05241394043</t>
+    <t xml:space="preserve">128.990325927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.052383422852</t>
   </si>
   <si>
     <t xml:space="preserve">134.157577514648</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">133.774826049805</t>
   </si>
   <si>
-    <t xml:space="preserve">132.626525878906</t>
+    <t xml:space="preserve">132.626541137695</t>
   </si>
   <si>
     <t xml:space="preserve">132.435150146484</t>
@@ -2657,16 +2657,16 @@
     <t xml:space="preserve">136.645523071289</t>
   </si>
   <si>
-    <t xml:space="preserve">137.411041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.305847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.861022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.731719970703</t>
+    <t xml:space="preserve">137.411071777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.305862426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.86100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.731704711914</t>
   </si>
   <si>
     <t xml:space="preserve">136.262756347656</t>
@@ -2681,10 +2681,10 @@
     <t xml:space="preserve">137.028274536133</t>
   </si>
   <si>
-    <t xml:space="preserve">138.559310913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.899002075195</t>
+    <t xml:space="preserve">138.559341430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.898971557617</t>
   </si>
   <si>
     <t xml:space="preserve">136.454147338867</t>
@@ -2702,40 +2702,40 @@
     <t xml:space="preserve">135.497253417969</t>
   </si>
   <si>
-    <t xml:space="preserve">144.492111206055</t>
+    <t xml:space="preserve">144.492095947266</t>
   </si>
   <si>
     <t xml:space="preserve">144.874877929688</t>
   </si>
   <si>
-    <t xml:space="preserve">144.109375</t>
+    <t xml:space="preserve">144.109344482422</t>
   </si>
   <si>
     <t xml:space="preserve">142.195556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">143.726577758789</t>
+    <t xml:space="preserve">143.726593017578</t>
   </si>
   <si>
     <t xml:space="preserve">143.91796875</t>
   </si>
   <si>
-    <t xml:space="preserve">144.683471679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.25764465332</t>
+    <t xml:space="preserve">144.683486938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.257629394531</t>
   </si>
   <si>
     <t xml:space="preserve">147.936965942383</t>
   </si>
   <si>
-    <t xml:space="preserve">145.640396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.788665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.276641845703</t>
+    <t xml:space="preserve">145.640380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.788681030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.276626586914</t>
   </si>
   <si>
     <t xml:space="preserve">150.999038696289</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">150.424896240234</t>
   </si>
   <si>
-    <t xml:space="preserve">153.486999511719</t>
+    <t xml:space="preserve">153.486968994141</t>
   </si>
   <si>
     <t xml:space="preserve">152.338714599609</t>
@@ -2756,16 +2756,16 @@
     <t xml:space="preserve">151.1904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">157.888732910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.037002563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.654266357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.611175537109</t>
+    <t xml:space="preserve">157.888717651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.037017822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.654251098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.61116027832</t>
   </si>
   <si>
     <t xml:space="preserve">161.333587646484</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">163.438766479492</t>
   </si>
   <si>
-    <t xml:space="preserve">163.821533203125</t>
+    <t xml:space="preserve">163.821517944336</t>
   </si>
   <si>
     <t xml:space="preserve">168.606018066406</t>
@@ -2789,13 +2789,13 @@
     <t xml:space="preserve">170.32844543457</t>
   </si>
   <si>
-    <t xml:space="preserve">165.161178588867</t>
+    <t xml:space="preserve">165.161193847656</t>
   </si>
   <si>
     <t xml:space="preserve">168.03190612793</t>
   </si>
   <si>
-    <t xml:space="preserve">165.352554321289</t>
+    <t xml:space="preserve">165.352584838867</t>
   </si>
   <si>
     <t xml:space="preserve">160.75944519043</t>
@@ -2810,7 +2810,7 @@
     <t xml:space="preserve">167.074981689453</t>
   </si>
   <si>
-    <t xml:space="preserve">161.93049621582</t>
+    <t xml:space="preserve">161.930511474609</t>
   </si>
   <si>
     <t xml:space="preserve">161.353576660156</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">160.58430480957</t>
   </si>
   <si>
-    <t xml:space="preserve">159.045761108398</t>
+    <t xml:space="preserve">159.045776367188</t>
   </si>
   <si>
     <t xml:space="preserve">152.122375488281</t>
@@ -2831,13 +2831,13 @@
     <t xml:space="preserve">147.314468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">150.391525268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.19921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.083709716797</t>
+    <t xml:space="preserve">150.391540527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.199203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.083740234375</t>
   </si>
   <si>
     <t xml:space="preserve">151.737747192383</t>
@@ -2846,34 +2846,34 @@
     <t xml:space="preserve">149.622268676758</t>
   </si>
   <si>
-    <t xml:space="preserve">155.199447631836</t>
+    <t xml:space="preserve">155.199417114258</t>
   </si>
   <si>
     <t xml:space="preserve">156.545654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">155.968719482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.430191040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.776611328125</t>
+    <t xml:space="preserve">155.968688964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.43017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.776626586914</t>
   </si>
   <si>
     <t xml:space="preserve">166.353805541992</t>
   </si>
   <si>
-    <t xml:space="preserve">170.200119018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.469284057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.430618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.007583618164</t>
+    <t xml:space="preserve">170.200134277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.469268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.430648803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.007598876953</t>
   </si>
   <si>
     <t xml:space="preserve">162.507461547852</t>
@@ -2885,22 +2885,22 @@
     <t xml:space="preserve">165.584533691406</t>
   </si>
   <si>
-    <t xml:space="preserve">161.161270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.084426879883</t>
+    <t xml:space="preserve">161.161254882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.084411621094</t>
   </si>
   <si>
     <t xml:space="preserve">161.738189697266</t>
   </si>
   <si>
-    <t xml:space="preserve">168.853912353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.508178710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.584976196289</t>
+    <t xml:space="preserve">168.853927612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.508163452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.584991455078</t>
   </si>
   <si>
     <t xml:space="preserve">180.392913818359</t>
@@ -2909,19 +2909,19 @@
     <t xml:space="preserve">180.777526855469</t>
   </si>
   <si>
-    <t xml:space="preserve">178.469757080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.815948486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.739120483398</t>
+    <t xml:space="preserve">178.469741821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.815963745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.739135742188</t>
   </si>
   <si>
     <t xml:space="preserve">185.008499145508</t>
   </si>
   <si>
-    <t xml:space="preserve">183.085327148438</t>
+    <t xml:space="preserve">183.085311889648</t>
   </si>
   <si>
     <t xml:space="preserve">182.508392333984</t>
@@ -2933,7 +2933,7 @@
     <t xml:space="preserve">169.046234130859</t>
   </si>
   <si>
-    <t xml:space="preserve">170.584762573242</t>
+    <t xml:space="preserve">170.584747314453</t>
   </si>
   <si>
     <t xml:space="preserve">167.507705688477</t>
@@ -2954,16 +2954,16 @@
     <t xml:space="preserve">175.008041381836</t>
   </si>
   <si>
-    <t xml:space="preserve">172.700256347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.123306274414</t>
+    <t xml:space="preserve">172.700241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.123291015625</t>
   </si>
   <si>
     <t xml:space="preserve">171.93098449707</t>
   </si>
   <si>
-    <t xml:space="preserve">167.315399169922</t>
+    <t xml:space="preserve">167.315383911133</t>
   </si>
   <si>
     <t xml:space="preserve">163.85368347168</t>
@@ -2972,22 +2972,22 @@
     <t xml:space="preserve">166.738418579102</t>
   </si>
   <si>
-    <t xml:space="preserve">164.238311767578</t>
+    <t xml:space="preserve">164.238327026367</t>
   </si>
   <si>
     <t xml:space="preserve">166.546112060547</t>
   </si>
   <si>
-    <t xml:space="preserve">167.700012207031</t>
+    <t xml:space="preserve">167.699996948242</t>
   </si>
   <si>
     <t xml:space="preserve">165.392211914062</t>
   </si>
   <si>
-    <t xml:space="preserve">151.160797119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.853454589844</t>
+    <t xml:space="preserve">151.160781860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.853439331055</t>
   </si>
   <si>
     <t xml:space="preserve">158.468826293945</t>
@@ -2999,16 +2999,16 @@
     <t xml:space="preserve">159.815048217773</t>
   </si>
   <si>
-    <t xml:space="preserve">156.930282592773</t>
+    <t xml:space="preserve">156.930297851562</t>
   </si>
   <si>
     <t xml:space="preserve">156.161026000977</t>
   </si>
   <si>
-    <t xml:space="preserve">152.314682006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.96826171875</t>
+    <t xml:space="preserve">152.314666748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.968246459961</t>
   </si>
   <si>
     <t xml:space="preserve">146.929824829102</t>
@@ -3020,28 +3020,28 @@
     <t xml:space="preserve">153.468597412109</t>
   </si>
   <si>
-    <t xml:space="preserve">153.276245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.122604370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.930053710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.545196533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.968017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.92936706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.660232543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.698425292969</t>
+    <t xml:space="preserve">153.276275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.122589111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.930068969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.545181274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.968032836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.929351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.660217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.69841003418</t>
   </si>
   <si>
     <t xml:space="preserve">132.506088256836</t>
@@ -3056,16 +3056,16 @@
     <t xml:space="preserve">130.005981445312</t>
   </si>
   <si>
-    <t xml:space="preserve">130.77522277832</t>
+    <t xml:space="preserve">130.775238037109</t>
   </si>
   <si>
     <t xml:space="preserve">128.852081298828</t>
   </si>
   <si>
-    <t xml:space="preserve">129.621353149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.890731811523</t>
+    <t xml:space="preserve">129.621337890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.890716552734</t>
   </si>
   <si>
     <t xml:space="preserve">137.506317138672</t>
@@ -3074,19 +3074,19 @@
     <t xml:space="preserve">136.160110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">138.467910766602</t>
+    <t xml:space="preserve">138.467895507812</t>
   </si>
   <si>
     <t xml:space="preserve">135.583145141602</t>
   </si>
   <si>
-    <t xml:space="preserve">124.813438415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.659309387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.582695007324</t>
+    <t xml:space="preserve">124.813423156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.659301757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.582710266113</t>
   </si>
   <si>
     <t xml:space="preserve">125.198059082031</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">137.314010620117</t>
   </si>
   <si>
-    <t xml:space="preserve">138.8525390625</t>
+    <t xml:space="preserve">138.852523803711</t>
   </si>
   <si>
     <t xml:space="preserve">142.891174316406</t>
@@ -3110,40 +3110,40 @@
     <t xml:space="preserve">145.00666809082</t>
   </si>
   <si>
-    <t xml:space="preserve">145.775939941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.814361572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.276031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.275802612305</t>
+    <t xml:space="preserve">145.775924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.814346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.27604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.275817871094</t>
   </si>
   <si>
     <t xml:space="preserve">142.602722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">142.698852539062</t>
+    <t xml:space="preserve">142.698867797852</t>
   </si>
   <si>
     <t xml:space="preserve">143.08349609375</t>
   </si>
   <si>
-    <t xml:space="preserve">139.525634765625</t>
+    <t xml:space="preserve">139.525650024414</t>
   </si>
   <si>
     <t xml:space="preserve">141.160339355469</t>
   </si>
   <si>
-    <t xml:space="preserve">140.198745727539</t>
+    <t xml:space="preserve">140.198760986328</t>
   </si>
   <si>
     <t xml:space="preserve">139.910263061523</t>
   </si>
   <si>
-    <t xml:space="preserve">139.429473876953</t>
+    <t xml:space="preserve">139.429489135742</t>
   </si>
   <si>
     <t xml:space="preserve">139.237167358398</t>
@@ -3164,55 +3164,55 @@
     <t xml:space="preserve">130.87141418457</t>
   </si>
   <si>
-    <t xml:space="preserve">129.525161743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.90983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.371520996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.275131225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.294448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.236473083496</t>
+    <t xml:space="preserve">129.525192260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.909820556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.371505737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.275115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.294464111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.236480712891</t>
   </si>
   <si>
     <t xml:space="preserve">122.890266418457</t>
   </si>
   <si>
-    <t xml:space="preserve">118.563148498535</t>
+    <t xml:space="preserve">118.563140869141</t>
   </si>
   <si>
     <t xml:space="preserve">109.81273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">113.56290435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.389915466309</t>
+    <t xml:space="preserve">113.562911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.389930725098</t>
   </si>
   <si>
     <t xml:space="preserve">115.774551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">118.755462646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.08235168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.313301086426</t>
+    <t xml:space="preserve">118.75545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.082359313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.313316345215</t>
   </si>
   <si>
     <t xml:space="preserve">120.293983459473</t>
   </si>
   <si>
-    <t xml:space="preserve">120.101669311523</t>
+    <t xml:space="preserve">120.101676940918</t>
   </si>
   <si>
     <t xml:space="preserve">119.236251831055</t>
@@ -3230,52 +3230,52 @@
     <t xml:space="preserve">119.043937683105</t>
   </si>
   <si>
-    <t xml:space="preserve">121.736366271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.621109008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.274894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.544044494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.044158935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.332641601562</t>
+    <t xml:space="preserve">121.736358642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.621124267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.274887084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.544052124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.044151306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.332633972168</t>
   </si>
   <si>
     <t xml:space="preserve">127.986656188965</t>
   </si>
   <si>
-    <t xml:space="preserve">128.659774780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.698188781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.178749084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.524490356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.889801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.236030578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.062789916992</t>
+    <t xml:space="preserve">128.659759521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.698173522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.178741455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.52449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.889808654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.236022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.062797546387</t>
   </si>
   <si>
     <t xml:space="preserve">112.216690063477</t>
   </si>
   <si>
-    <t xml:space="preserve">112.505180358887</t>
+    <t xml:space="preserve">112.505165100098</t>
   </si>
   <si>
     <t xml:space="preserve">113.947547912598</t>
@@ -3284,10 +3284,10 @@
     <t xml:space="preserve">116.447662353516</t>
   </si>
   <si>
-    <t xml:space="preserve">115.197608947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.140090942383</t>
+    <t xml:space="preserve">115.197601318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.140098571777</t>
   </si>
   <si>
     <t xml:space="preserve">119.909355163574</t>
@@ -3305,13 +3305,13 @@
     <t xml:space="preserve">113.178276062012</t>
   </si>
   <si>
-    <t xml:space="preserve">119.332405090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.082580566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.390365600586</t>
+    <t xml:space="preserve">119.332397460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.082588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.39037322998</t>
   </si>
   <si>
     <t xml:space="preserve">122.986419677734</t>
@@ -3320,10 +3320,10 @@
     <t xml:space="preserve">118.274673461914</t>
   </si>
   <si>
-    <t xml:space="preserve">119.71703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.774787902832</t>
+    <t xml:space="preserve">119.717041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.774780273438</t>
   </si>
   <si>
     <t xml:space="preserve">123.659538269043</t>
@@ -3335,16 +3335,16 @@
     <t xml:space="preserve">131.73681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">130.679077148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.832740783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.794319152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.467468261719</t>
+    <t xml:space="preserve">130.679061889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.832748413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.794334411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.46745300293</t>
   </si>
   <si>
     <t xml:space="preserve">132.602249145508</t>
@@ -3359,58 +3359,58 @@
     <t xml:space="preserve">125.967323303223</t>
   </si>
   <si>
-    <t xml:space="preserve">126.351943969727</t>
+    <t xml:space="preserve">126.351951599121</t>
   </si>
   <si>
     <t xml:space="preserve">123.563369750977</t>
   </si>
   <si>
-    <t xml:space="preserve">127.313545227051</t>
+    <t xml:space="preserve">127.313552856445</t>
   </si>
   <si>
     <t xml:space="preserve">128.371292114258</t>
   </si>
   <si>
-    <t xml:space="preserve">126.736587524414</t>
+    <t xml:space="preserve">126.736610412598</t>
   </si>
   <si>
     <t xml:space="preserve">121.447891235352</t>
   </si>
   <si>
-    <t xml:space="preserve">117.601554870605</t>
+    <t xml:space="preserve">117.6015625</t>
   </si>
   <si>
     <t xml:space="preserve">118.947769165039</t>
   </si>
   <si>
-    <t xml:space="preserve">120.197822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.063255310059</t>
+    <t xml:space="preserve">120.197830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.063247680664</t>
   </si>
   <si>
     <t xml:space="preserve">117.505393981934</t>
   </si>
   <si>
-    <t xml:space="preserve">115.870704650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.255348205566</t>
+    <t xml:space="preserve">115.870712280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.255340576172</t>
   </si>
   <si>
     <t xml:space="preserve">112.312858581543</t>
   </si>
   <si>
-    <t xml:space="preserve">115.582237243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.678398132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.178512573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.909126281738</t>
+    <t xml:space="preserve">115.582229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.67839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.178504943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.909118652344</t>
   </si>
   <si>
     <t xml:space="preserve">106.596168518066</t>
@@ -3434,37 +3434,37 @@
     <t xml:space="preserve">102.816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">106.014739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.041603088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.437377929688</t>
+    <t xml:space="preserve">106.01473236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.041610717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.437370300293</t>
   </si>
   <si>
     <t xml:space="preserve">109.212615966797</t>
   </si>
   <si>
-    <t xml:space="preserve">113.185752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.441452026367</t>
+    <t xml:space="preserve">113.185760498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.441444396973</t>
   </si>
   <si>
     <t xml:space="preserve">111.829071044922</t>
   </si>
   <si>
-    <t xml:space="preserve">107.27449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.851860046387</t>
+    <t xml:space="preserve">107.274505615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.851867675781</t>
   </si>
   <si>
     <t xml:space="preserve">104.658050537109</t>
   </si>
   <si>
-    <t xml:space="preserve">101.847785949707</t>
+    <t xml:space="preserve">101.847801208496</t>
   </si>
   <si>
     <t xml:space="preserve">102.429222106934</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">103.495193481445</t>
   </si>
   <si>
-    <t xml:space="preserve">104.076622009277</t>
+    <t xml:space="preserve">104.076629638672</t>
   </si>
   <si>
     <t xml:space="preserve">106.402359008789</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">102.332321166992</t>
   </si>
   <si>
-    <t xml:space="preserve">100.87873840332</t>
+    <t xml:space="preserve">100.878730773926</t>
   </si>
   <si>
     <t xml:space="preserve">103.979721069336</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">108.340476989746</t>
   </si>
   <si>
-    <t xml:space="preserve">117.643409729004</t>
+    <t xml:space="preserve">117.643417358398</t>
   </si>
   <si>
     <t xml:space="preserve">118.515556335449</t>
@@ -3524,10 +3524,10 @@
     <t xml:space="preserve">116.771255493164</t>
   </si>
   <si>
-    <t xml:space="preserve">114.445518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.73624420166</t>
+    <t xml:space="preserve">114.445526123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.736236572266</t>
   </si>
   <si>
     <t xml:space="preserve">115.026947021484</t>
@@ -3539,16 +3539,16 @@
     <t xml:space="preserve">115.511474609375</t>
   </si>
   <si>
-    <t xml:space="preserve">115.220771789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.965065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.476470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.25171661377</t>
+    <t xml:space="preserve">115.220764160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.965072631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.476463317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.251708984375</t>
   </si>
   <si>
     <t xml:space="preserve">114.833145141602</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">117.449592590332</t>
   </si>
   <si>
-    <t xml:space="preserve">118.61247253418</t>
+    <t xml:space="preserve">118.612464904785</t>
   </si>
   <si>
     <t xml:space="preserve">112.99193572998</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">112.604316711426</t>
   </si>
   <si>
-    <t xml:space="preserve">115.996017456055</t>
+    <t xml:space="preserve">115.99600982666</t>
   </si>
   <si>
     <t xml:space="preserve">112.216697692871</t>
   </si>
   <si>
-    <t xml:space="preserve">108.24356842041</t>
+    <t xml:space="preserve">108.243560791016</t>
   </si>
   <si>
     <t xml:space="preserve">107.080696105957</t>
@@ -3593,19 +3593,19 @@
     <t xml:space="preserve">110.181671142578</t>
   </si>
   <si>
-    <t xml:space="preserve">109.890953063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.24764251709</t>
+    <t xml:space="preserve">109.890960693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.247634887695</t>
   </si>
   <si>
     <t xml:space="preserve">113.282661437988</t>
   </si>
   <si>
-    <t xml:space="preserve">112.410499572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.639335632324</t>
+    <t xml:space="preserve">112.410507202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.639343261719</t>
   </si>
   <si>
     <t xml:space="preserve">117.934120178223</t>
@@ -3620,10 +3620,10 @@
     <t xml:space="preserve">118.031028747559</t>
   </si>
   <si>
-    <t xml:space="preserve">121.13200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.10107421875</t>
+    <t xml:space="preserve">121.132011413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.101066589355</t>
   </si>
   <si>
     <t xml:space="preserve">122.876312255859</t>
@@ -3641,16 +3641,16 @@
     <t xml:space="preserve">122.779403686523</t>
   </si>
   <si>
-    <t xml:space="preserve">123.26392364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.810348510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.74437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.74845123291</t>
+    <t xml:space="preserve">123.263931274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.810340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.74439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.748458862305</t>
   </si>
   <si>
     <t xml:space="preserve">131.985443115234</t>
@@ -3659,10 +3659,10 @@
     <t xml:space="preserve">131.888549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">132.179244995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.531829833984</t>
+    <t xml:space="preserve">132.179260253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.531860351562</t>
   </si>
   <si>
     <t xml:space="preserve">128.593734741211</t>
@@ -3671,10 +3671,10 @@
     <t xml:space="preserve">127.043251037598</t>
   </si>
   <si>
-    <t xml:space="preserve">124.814430236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.686569213867</t>
+    <t xml:space="preserve">124.814422607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.686561584473</t>
   </si>
   <si>
     <t xml:space="preserve">126.849433898926</t>
@@ -3692,10 +3692,10 @@
     <t xml:space="preserve">123.845367431641</t>
   </si>
   <si>
-    <t xml:space="preserve">121.422729492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.325820922852</t>
+    <t xml:space="preserve">121.422737121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.325813293457</t>
   </si>
   <si>
     <t xml:space="preserve">120.259857177734</t>
@@ -3707,28 +3707,28 @@
     <t xml:space="preserve">118.321746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">116.8681640625</t>
+    <t xml:space="preserve">116.868156433105</t>
   </si>
   <si>
     <t xml:space="preserve">115.802200317383</t>
   </si>
   <si>
-    <t xml:space="preserve">113.864097595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.960998535156</t>
+    <t xml:space="preserve">113.86408996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.960990905762</t>
   </si>
   <si>
     <t xml:space="preserve">113.088836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">110.472396850586</t>
+    <t xml:space="preserve">110.472389221191</t>
   </si>
   <si>
     <t xml:space="preserve">108.825004577637</t>
   </si>
   <si>
-    <t xml:space="preserve">115.414573669434</t>
+    <t xml:space="preserve">115.414581298828</t>
   </si>
   <si>
     <t xml:space="preserve">109.987861633301</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">113.670280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">118.1279296875</t>
+    <t xml:space="preserve">118.127937316895</t>
   </si>
   <si>
     <t xml:space="preserve">114.154808044434</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">119.193901062012</t>
   </si>
   <si>
-    <t xml:space="preserve">119.09700012207</t>
+    <t xml:space="preserve">119.096992492676</t>
   </si>
   <si>
     <t xml:space="preserve">119.678428649902</t>
@@ -3770,16 +3770,16 @@
     <t xml:space="preserve">110.569297790527</t>
   </si>
   <si>
-    <t xml:space="preserve">110.956924438477</t>
+    <t xml:space="preserve">110.956916809082</t>
   </si>
   <si>
     <t xml:space="preserve">108.921905517578</t>
   </si>
   <si>
-    <t xml:space="preserve">107.952850341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.565223693848</t>
+    <t xml:space="preserve">107.952842712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.565231323242</t>
   </si>
   <si>
     <t xml:space="preserve">105.045684814453</t>
@@ -3788,19 +3788,19 @@
     <t xml:space="preserve">104.754959106445</t>
   </si>
   <si>
-    <t xml:space="preserve">105.724021911621</t>
+    <t xml:space="preserve">105.724014282227</t>
   </si>
   <si>
     <t xml:space="preserve">103.592094421387</t>
   </si>
   <si>
-    <t xml:space="preserve">106.88688659668</t>
+    <t xml:space="preserve">106.886894226074</t>
   </si>
   <si>
     <t xml:space="preserve">103.204475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">100.588020324707</t>
+    <t xml:space="preserve">100.588027954102</t>
   </si>
   <si>
     <t xml:space="preserve">100.297302246094</t>
@@ -3809,10 +3809,10 @@
     <t xml:space="preserve">102.719947814941</t>
   </si>
   <si>
-    <t xml:space="preserve">103.107566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.561149597168</t>
+    <t xml:space="preserve">103.107574462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.561157226562</t>
   </si>
   <si>
     <t xml:space="preserve">107.37141418457</t>
@@ -3827,13 +3827,13 @@
     <t xml:space="preserve">110.084770202637</t>
   </si>
   <si>
-    <t xml:space="preserve">116.480545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.705291748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.379570007324</t>
+    <t xml:space="preserve">116.480537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.705307006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.37956237793</t>
   </si>
   <si>
     <t xml:space="preserve">112.798126220703</t>
@@ -3851,16 +3851,16 @@
     <t xml:space="preserve">109.115715026855</t>
   </si>
   <si>
-    <t xml:space="preserve">110.278579711914</t>
+    <t xml:space="preserve">110.278587341309</t>
   </si>
   <si>
     <t xml:space="preserve">109.697143554688</t>
   </si>
   <si>
-    <t xml:space="preserve">102.235420227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.623046875</t>
+    <t xml:space="preserve">102.235412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.623039245605</t>
   </si>
   <si>
     <t xml:space="preserve">104.173522949219</t>
@@ -3881,22 +3881,22 @@
     <t xml:space="preserve">100.006591796875</t>
   </si>
   <si>
-    <t xml:space="preserve">99.4251480102539</t>
+    <t xml:space="preserve">99.4251556396484</t>
   </si>
   <si>
     <t xml:space="preserve">101.26636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">101.653984069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.39421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.328239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6189727783203</t>
+    <t xml:space="preserve">101.65397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.394203186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.328254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6189651489258</t>
   </si>
   <si>
     <t xml:space="preserve">99.2313385009766</t>
@@ -3926,16 +3926,16 @@
     <t xml:space="preserve">99.0078277587891</t>
   </si>
   <si>
-    <t xml:space="preserve">98.6164932250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.573173522949</t>
+    <t xml:space="preserve">98.6165008544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.573181152344</t>
   </si>
   <si>
     <t xml:space="preserve">97.051155090332</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0672302246094</t>
+    <t xml:space="preserve">94.0672225952148</t>
   </si>
   <si>
     <t xml:space="preserve">95.8771438598633</t>
@@ -3956,7 +3956,7 @@
     <t xml:space="preserve">95.7793197631836</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5780487060547</t>
+    <t xml:space="preserve">93.5780563354492</t>
   </si>
   <si>
     <t xml:space="preserve">92.5997161865234</t>
@@ -3983,7 +3983,7 @@
     <t xml:space="preserve">90.0071182250977</t>
   </si>
   <si>
-    <t xml:space="preserve">90.4962844848633</t>
+    <t xml:space="preserve">90.4962921142578</t>
   </si>
   <si>
     <t xml:space="preserve">90.8386993408203</t>
@@ -3992,13 +3992,13 @@
     <t xml:space="preserve">92.3062133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">92.942138671875</t>
+    <t xml:space="preserve">92.9421310424805</t>
   </si>
   <si>
     <t xml:space="preserve">91.2789611816406</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6213760375977</t>
+    <t xml:space="preserve">91.6213836669922</t>
   </si>
   <si>
     <t xml:space="preserve">90.6430435180664</t>
@@ -4049,28 +4049,28 @@
     <t xml:space="preserve">103.508193969727</t>
   </si>
   <si>
-    <t xml:space="preserve">103.703857421875</t>
+    <t xml:space="preserve">103.70384979248</t>
   </si>
   <si>
     <t xml:space="preserve">106.051864624023</t>
   </si>
   <si>
-    <t xml:space="preserve">104.975700378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.171356201172</t>
+    <t xml:space="preserve">104.975692749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.171363830566</t>
   </si>
   <si>
     <t xml:space="preserve">102.627685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">101.747184753418</t>
+    <t xml:space="preserve">101.747177124023</t>
   </si>
   <si>
     <t xml:space="preserve">103.997360229492</t>
   </si>
   <si>
-    <t xml:space="preserve">102.529846191406</t>
+    <t xml:space="preserve">102.529853820801</t>
   </si>
   <si>
     <t xml:space="preserve">100.377502441406</t>
@@ -4082,10 +4082,10 @@
     <t xml:space="preserve">104.193023681641</t>
   </si>
   <si>
-    <t xml:space="preserve">106.541030883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.617210388184</t>
+    <t xml:space="preserve">106.541038513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.617202758789</t>
   </si>
   <si>
     <t xml:space="preserve">106.834533691406</t>
@@ -4094,13 +4094,13 @@
     <t xml:space="preserve">105.85619354248</t>
   </si>
   <si>
-    <t xml:space="preserve">111.530563354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.367736816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.291572570801</t>
+    <t xml:space="preserve">111.530555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.367744445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.291564941406</t>
   </si>
   <si>
     <t xml:space="preserve">117.694091796875</t>
@@ -4109,22 +4109,22 @@
     <t xml:space="preserve">118.672431945801</t>
   </si>
   <si>
-    <t xml:space="preserve">118.378921508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.259429931641</t>
+    <t xml:space="preserve">118.378929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.259437561035</t>
   </si>
   <si>
     <t xml:space="preserve">120.335601806641</t>
   </si>
   <si>
-    <t xml:space="preserve">118.085426330566</t>
+    <t xml:space="preserve">118.085418701172</t>
   </si>
   <si>
     <t xml:space="preserve">115.346084594727</t>
   </si>
   <si>
-    <t xml:space="preserve">115.737411499023</t>
+    <t xml:space="preserve">115.737419128418</t>
   </si>
   <si>
     <t xml:space="preserve">113.682907104492</t>
@@ -4139,19 +4139,19 @@
     <t xml:space="preserve">111.921897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">111.824058532715</t>
+    <t xml:space="preserve">111.824066162109</t>
   </si>
   <si>
     <t xml:space="preserve">114.074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">113.976402282715</t>
+    <t xml:space="preserve">113.976409912109</t>
   </si>
   <si>
     <t xml:space="preserve">112.802406311035</t>
   </si>
   <si>
-    <t xml:space="preserve">112.31324005127</t>
+    <t xml:space="preserve">112.313232421875</t>
   </si>
   <si>
     <t xml:space="preserve">114.856910705566</t>
@@ -4172,10 +4172,10 @@
     <t xml:space="preserve">122.585784912109</t>
   </si>
   <si>
-    <t xml:space="preserve">122.781448364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.368453979492</t>
+    <t xml:space="preserve">122.781455993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.368446350098</t>
   </si>
   <si>
     <t xml:space="preserve">120.433433532715</t>
@@ -4190,13 +4190,13 @@
     <t xml:space="preserve">122.194450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">121.803108215332</t>
+    <t xml:space="preserve">121.803115844727</t>
   </si>
   <si>
     <t xml:space="preserve">120.042098999023</t>
   </si>
   <si>
-    <t xml:space="preserve">119.455101013184</t>
+    <t xml:space="preserve">119.455093383789</t>
   </si>
   <si>
     <t xml:space="preserve">118.574592590332</t>
@@ -4232,31 +4232,31 @@
     <t xml:space="preserve">112.019729614258</t>
   </si>
   <si>
-    <t xml:space="preserve">112.900238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.095893859863</t>
+    <t xml:space="preserve">112.900230407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.095901489258</t>
   </si>
   <si>
     <t xml:space="preserve">110.943557739258</t>
   </si>
   <si>
-    <t xml:space="preserve">111.334892272949</t>
+    <t xml:space="preserve">111.334899902344</t>
   </si>
   <si>
     <t xml:space="preserve">110.747886657715</t>
   </si>
   <si>
-    <t xml:space="preserve">110.063049316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.671722412109</t>
+    <t xml:space="preserve">110.063056945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.671714782715</t>
   </si>
   <si>
     <t xml:space="preserve">102.725517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">100.181838989258</t>
+    <t xml:space="preserve">100.181831359863</t>
   </si>
   <si>
     <t xml:space="preserve">96.8554840087891</t>
@@ -4289,10 +4289,10 @@
     <t xml:space="preserve">98.322998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">96.8065643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2195587158203</t>
+    <t xml:space="preserve">96.8065719604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2195663452148</t>
   </si>
   <si>
     <t xml:space="preserve">94.9966430664062</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">95.7303924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">97.9316558837891</t>
+    <t xml:space="preserve">97.9316635131836</t>
   </si>
   <si>
     <t xml:space="preserve">95.8282318115234</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">106.638870239258</t>
   </si>
   <si>
-    <t xml:space="preserve">107.128036499023</t>
+    <t xml:space="preserve">107.128044128418</t>
   </si>
   <si>
     <t xml:space="preserve">105.954032897949</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">104.682189941406</t>
   </si>
   <si>
-    <t xml:space="preserve">103.899513244629</t>
+    <t xml:space="preserve">103.899520874023</t>
   </si>
   <si>
     <t xml:space="preserve">104.78002166748</t>
@@ -4364,10 +4364,10 @@
     <t xml:space="preserve">105.660530090332</t>
   </si>
   <si>
-    <t xml:space="preserve">106.345367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.443199157715</t>
+    <t xml:space="preserve">106.345359802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.443206787109</t>
   </si>
   <si>
     <t xml:space="preserve">103.801681518555</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">112.704566955566</t>
   </si>
   <si>
-    <t xml:space="preserve">114.172073364258</t>
+    <t xml:space="preserve">114.172065734863</t>
   </si>
   <si>
     <t xml:space="preserve">117.107086181641</t>
@@ -4391,10 +4391,10 @@
     <t xml:space="preserve">115.150405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">116.813591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.204925537109</t>
+    <t xml:space="preserve">116.813583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.204917907715</t>
   </si>
   <si>
     <t xml:space="preserve">116.128746032715</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">96.5619812011719</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2628860473633</t>
+    <t xml:space="preserve">94.2628936767578</t>
   </si>
   <si>
     <t xml:space="preserve">91.3767929077148</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">95.3390579223633</t>
   </si>
   <si>
-    <t xml:space="preserve">94.3118133544922</t>
+    <t xml:space="preserve">94.3118057250977</t>
   </si>
   <si>
     <t xml:space="preserve">93.4802169799805</t>
@@ -4451,28 +4451,28 @@
     <t xml:space="preserve">94.7031478881836</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8498840332031</t>
+    <t xml:space="preserve">94.8498916625977</t>
   </si>
   <si>
     <t xml:space="preserve">94.2139739990234</t>
   </si>
   <si>
-    <t xml:space="preserve">91.8659591674805</t>
+    <t xml:space="preserve">91.865966796875</t>
   </si>
   <si>
     <t xml:space="preserve">90.6919479370117</t>
   </si>
   <si>
-    <t xml:space="preserve">89.2244415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7080230712891</t>
+    <t xml:space="preserve">89.2244491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7080307006836</t>
   </si>
   <si>
     <t xml:space="preserve">85.751350402832</t>
   </si>
   <si>
-    <t xml:space="preserve">84.5284194946289</t>
+    <t xml:space="preserve">84.5284271240234</t>
   </si>
   <si>
     <t xml:space="preserve">84.3327560424805</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">86.2894287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2517013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.441780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0287857055664</t>
+    <t xml:space="preserve">90.251708984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4417724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0287780761719</t>
   </si>
   <si>
     <t xml:space="preserve">88.4906921386719</t>
@@ -5163,6 +5163,9 @@
   </si>
   <si>
     <t xml:space="preserve">82.6999969482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.6500015258789</t>
   </si>
 </sst>
 </file>
@@ -70189,7 +70192,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6495949074</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>23651</v>
@@ -70210,6 +70213,32 @@
         <v>1716</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6496180556</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>22647</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>84.4499969482422</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>81.9499969482422</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>83.9000015258789</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>82.6500015258789</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1717</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1716" uniqueCount="1716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="1717">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5495910644531</t>
+    <t xml:space="preserve">13.5495891571045</t>
   </si>
   <si>
     <t xml:space="preserve">SES.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5321054458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2523727416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9464168548584</t>
+    <t xml:space="preserve">13.5321063995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2523736953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9464149475098</t>
   </si>
   <si>
     <t xml:space="preserve">13.1125068664551</t>
@@ -59,91 +59,91 @@
     <t xml:space="preserve">12.8589992523193</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0513153076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9901237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9376745223999</t>
+    <t xml:space="preserve">13.0513143539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9901218414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9376735687256</t>
   </si>
   <si>
     <t xml:space="preserve">13.1037654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">13.025089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8502559661865</t>
+    <t xml:space="preserve">13.0250902175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8502569198608</t>
   </si>
   <si>
     <t xml:space="preserve">12.2383394241333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.588005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7890653610229</t>
+    <t xml:space="preserve">12.5880069732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7890663146973</t>
   </si>
   <si>
     <t xml:space="preserve">12.7191305160522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6841669082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.605489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.325756072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0460214614868</t>
+    <t xml:space="preserve">12.6841650009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6054906845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3257579803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0460243225098</t>
   </si>
   <si>
     <t xml:space="preserve">12.1771478652954</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1421823501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9270887374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9795389175415</t>
+    <t xml:space="preserve">12.142183303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9270877838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9795379638672</t>
   </si>
   <si>
     <t xml:space="preserve">11.3641719818115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4515886306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0984725952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.107216835022</t>
+    <t xml:space="preserve">11.4515895843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0984735488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1072158813477</t>
   </si>
   <si>
     <t xml:space="preserve">11.8886737823486</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760894775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9323816299438</t>
+    <t xml:space="preserve">11.9760885238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9323797225952</t>
   </si>
   <si>
     <t xml:space="preserve">12.0110559463501</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0809907913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8012571334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334409713745</t>
+    <t xml:space="preserve">12.0809879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8012552261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334390640259</t>
   </si>
   <si>
     <t xml:space="preserve">11.8274812698364</t>
@@ -155,22 +155,22 @@
     <t xml:space="preserve">12.5005903244019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6754236221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7978067398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1649560928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1562147140503</t>
+    <t xml:space="preserve">12.675422668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7978048324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1649570465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1562166213989</t>
   </si>
   <si>
     <t xml:space="preserve">13.0687990188599</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1212482452393</t>
+    <t xml:space="preserve">13.1212501525879</t>
   </si>
   <si>
     <t xml:space="preserve">13.1911821365356</t>
@@ -179,61 +179,61 @@
     <t xml:space="preserve">12.7540988922119</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8939647674561</t>
+    <t xml:space="preserve">12.8939666748047</t>
   </si>
   <si>
     <t xml:space="preserve">12.9027070999146</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0600566864014</t>
+    <t xml:space="preserve">13.0600576400757</t>
   </si>
   <si>
     <t xml:space="preserve">13.1999244689941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9813823699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4534320831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7069406509399</t>
+    <t xml:space="preserve">12.9813814163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4534330368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7069416046143</t>
   </si>
   <si>
     <t xml:space="preserve">13.4709157943726</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4621715545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.208664894104</t>
+    <t xml:space="preserve">13.4621734619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2086639404297</t>
   </si>
   <si>
     <t xml:space="preserve">13.3223066329956</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0950231552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9988651275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6404581069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4481391906738</t>
+    <t xml:space="preserve">13.0950222015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9988641738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.640456199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4481382369995</t>
   </si>
   <si>
     <t xml:space="preserve">12.3782072067261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0285396575928</t>
+    <t xml:space="preserve">12.0285406112671</t>
   </si>
   <si>
     <t xml:space="preserve">12.1509237289429</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4393968582153</t>
+    <t xml:space="preserve">12.4393978118896</t>
   </si>
   <si>
     <t xml:space="preserve">12.5617818832397</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">12.5268144607544</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6317138671875</t>
+    <t xml:space="preserve">12.6317157745361</t>
   </si>
   <si>
     <t xml:space="preserve">12.3694648742676</t>
@@ -251,37 +251,37 @@
     <t xml:space="preserve">12.7715816497803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4306564331055</t>
+    <t xml:space="preserve">12.4306573867798</t>
   </si>
   <si>
     <t xml:space="preserve">12.2820482254028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1946296691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2470808029175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4131736755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5093326568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3869485855103</t>
+    <t xml:space="preserve">12.1946306228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2470817565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4131717681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.509331703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3869476318359</t>
   </si>
   <si>
     <t xml:space="preserve">11.8187398910522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8449640274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2558250427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5792646408081</t>
+    <t xml:space="preserve">11.8449649810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.255823135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5792655944824</t>
   </si>
   <si>
     <t xml:space="preserve">12.2208557128906</t>
@@ -290,16 +290,16 @@
     <t xml:space="preserve">12.1858892440796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7803220748901</t>
+    <t xml:space="preserve">12.7803239822388</t>
   </si>
   <si>
     <t xml:space="preserve">12.7278738021851</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8764810562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8065481185913</t>
+    <t xml:space="preserve">12.8764820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.806547164917</t>
   </si>
   <si>
     <t xml:space="preserve">12.7628402709961</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">12.8677406311035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8327741622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5355577468872</t>
+    <t xml:space="preserve">12.8327732086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5355567932129</t>
   </si>
   <si>
     <t xml:space="preserve">13.1824398040771</t>
@@ -320,55 +320,55 @@
     <t xml:space="preserve">13.0338306427002</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3048238754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.261116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3747587203979</t>
+    <t xml:space="preserve">13.3048248291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2611150741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3747577667236</t>
   </si>
   <si>
     <t xml:space="preserve">13.6020402908325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6894569396973</t>
+    <t xml:space="preserve">13.6894588470459</t>
   </si>
   <si>
     <t xml:space="preserve">13.7244234085083</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7514753341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5711278915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8687028884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6252326965332</t>
+    <t xml:space="preserve">13.7514762878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5711307525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8687009811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6252317428589</t>
   </si>
   <si>
     <t xml:space="preserve">13.6432676315308</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6613025665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5981817245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6162147521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5260410308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5530939102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3456954956055</t>
+    <t xml:space="preserve">13.6613006591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.598180770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6162157058716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5260419845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5530948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3456945419312</t>
   </si>
   <si>
     <t xml:space="preserve">13.5801458358765</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">13.6703195571899</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7965641021729</t>
+    <t xml:space="preserve">13.7965621948242</t>
   </si>
   <si>
     <t xml:space="preserve">13.9769096374512</t>
@@ -392,16 +392,16 @@
     <t xml:space="preserve">14.0400314331055</t>
   </si>
   <si>
-    <t xml:space="preserve">14.012978553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9047708511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1031551361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2474317550659</t>
+    <t xml:space="preserve">14.0129795074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9047718048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1031532287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2474298477173</t>
   </si>
   <si>
     <t xml:space="preserve">14.1572570800781</t>
@@ -410,61 +410,61 @@
     <t xml:space="preserve">14.3646564483643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4187602996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.517951965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6081256866455</t>
+    <t xml:space="preserve">14.4187612533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5179529190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6081266403198</t>
   </si>
   <si>
     <t xml:space="preserve">14.6622295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3917093276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3105516433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3015365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5450029373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6441946029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7343683242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7163333892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6351776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6261596679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6892833709717</t>
+    <t xml:space="preserve">14.3917083740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3105535507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3015356063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5450038909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.644193649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7343692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7163314819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6351766586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6261587142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6892824172974</t>
   </si>
   <si>
     <t xml:space="preserve">14.8245420455933</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8065071105957</t>
+    <t xml:space="preserve">14.80650806427</t>
   </si>
   <si>
     <t xml:space="preserve">14.74338722229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5810747146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.698299407959</t>
+    <t xml:space="preserve">14.581072807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.698296546936</t>
   </si>
   <si>
     <t xml:space="preserve">14.5089349746704</t>
@@ -473,79 +473,79 @@
     <t xml:space="preserve">14.6712465286255</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6532115936279</t>
+    <t xml:space="preserve">14.6532125473022</t>
   </si>
   <si>
     <t xml:space="preserve">14.923731803894</t>
   </si>
   <si>
-    <t xml:space="preserve">15.049976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2122898101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3746013641357</t>
+    <t xml:space="preserve">15.0499773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2122888565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3746023178101</t>
   </si>
   <si>
     <t xml:space="preserve">15.5549478530884</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9246587753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7803831100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8705549240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344860076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7082443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517116546631</t>
+    <t xml:space="preserve">15.9246616363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7803802490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8705539703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344850540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7082433700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517126083374</t>
   </si>
   <si>
     <t xml:space="preserve">16.7452392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8714847564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0878982543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1510200500488</t>
+    <t xml:space="preserve">16.8714828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0879001617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1510181427002</t>
   </si>
   <si>
     <t xml:space="preserve">17.2231597900391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9796905517578</t>
+    <t xml:space="preserve">16.9796924591064</t>
   </si>
   <si>
     <t xml:space="preserve">16.9075527191162</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3043193817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0337944030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2772655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4756469726562</t>
+    <t xml:space="preserve">17.3043155670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0337963104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2772636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4756450653076</t>
   </si>
   <si>
     <t xml:space="preserve">17.3223476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1690578460693</t>
+    <t xml:space="preserve">17.1690559387207</t>
   </si>
   <si>
     <t xml:space="preserve">17.583854675293</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">17.574836730957</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5658226013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2411975860596</t>
+    <t xml:space="preserve">17.5658187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2411956787109</t>
   </si>
   <si>
     <t xml:space="preserve">17.1870899200439</t>
@@ -566,16 +566,16 @@
     <t xml:space="preserve">16.8534469604492</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8444309234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9526386260986</t>
+    <t xml:space="preserve">16.8444328308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.95263671875</t>
   </si>
   <si>
     <t xml:space="preserve">16.7272033691406</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6911354064941</t>
+    <t xml:space="preserve">16.6911373138428</t>
   </si>
   <si>
     <t xml:space="preserve">16.8624668121338</t>
@@ -587,16 +587,16 @@
     <t xml:space="preserve">16.8173770904541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9977264404297</t>
+    <t xml:space="preserve">16.9977283477783</t>
   </si>
   <si>
     <t xml:space="preserve">16.7722930908203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0067462921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1961059570312</t>
+    <t xml:space="preserve">17.0067443847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1961078643799</t>
   </si>
   <si>
     <t xml:space="preserve">17.358419418335</t>
@@ -605,52 +605,52 @@
     <t xml:space="preserve">17.6199264526367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7642021179199</t>
+    <t xml:space="preserve">17.7642002105713</t>
   </si>
   <si>
     <t xml:space="preserve">18.0076694488525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9896354675293</t>
+    <t xml:space="preserve">17.9896373748779</t>
   </si>
   <si>
     <t xml:space="preserve">17.9445495605469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9535694122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8092861175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2601566314697</t>
+    <t xml:space="preserve">17.9535655975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8092918395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2601547241211</t>
   </si>
   <si>
     <t xml:space="preserve">18.7561111450195</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8462867736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9364566802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.620849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2971534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3602752685547</t>
+    <t xml:space="preserve">18.8462829589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9364585876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6208477020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.297155380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3602771759033</t>
   </si>
   <si>
     <t xml:space="preserve">19.3512573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6668643951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6488285064697</t>
+    <t xml:space="preserve">19.6668663024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.648832321167</t>
   </si>
   <si>
     <t xml:space="preserve">19.5586585998535</t>
@@ -662,43 +662,43 @@
     <t xml:space="preserve">19.1709098815918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1348400115967</t>
+    <t xml:space="preserve">19.1348419189453</t>
   </si>
   <si>
     <t xml:space="preserve">19.197961807251</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9544944763184</t>
+    <t xml:space="preserve">18.9544925689697</t>
   </si>
   <si>
     <t xml:space="preserve">18.9094066619873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0897560119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5757656097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1970386505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5306739807129</t>
+    <t xml:space="preserve">19.0897541046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5757675170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1970367431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5306777954102</t>
   </si>
   <si>
     <t xml:space="preserve">18.8372688293457</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4594631195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3873291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0185432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3612003326416</t>
+    <t xml:space="preserve">19.4594688415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3873271942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0185394287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3612022399902</t>
   </si>
   <si>
     <t xml:space="preserve">20.8301048278809</t>
@@ -710,22 +710,22 @@
     <t xml:space="preserve">20.8751926422119</t>
   </si>
   <si>
-    <t xml:space="preserve">20.929292678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1006240844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0104503631592</t>
+    <t xml:space="preserve">20.9292964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.100622177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0104541778564</t>
   </si>
   <si>
     <t xml:space="preserve">20.5685997009277</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7218933105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6046695709229</t>
+    <t xml:space="preserve">20.7218952178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6046714782715</t>
   </si>
   <si>
     <t xml:space="preserve">20.189868927002</t>
@@ -737,49 +737,49 @@
     <t xml:space="preserve">20.6497573852539</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6416683197021</t>
+    <t xml:space="preserve">21.6416645050049</t>
   </si>
   <si>
     <t xml:space="preserve">21.3711471557617</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3801593780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0925331115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6245594024658</t>
+    <t xml:space="preserve">21.380163192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0925369262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6245632171631</t>
   </si>
   <si>
     <t xml:space="preserve">22.7147331237793</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8049087524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5984344482422</t>
+    <t xml:space="preserve">22.8049068450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5984325408936</t>
   </si>
   <si>
     <t xml:space="preserve">24.0763568878174</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0583171844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7156600952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9320755004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8599395751953</t>
+    <t xml:space="preserve">24.0583209991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7156581878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9320774078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8599376678467</t>
   </si>
   <si>
     <t xml:space="preserve">23.8058338165283</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5082588195801</t>
+    <t xml:space="preserve">23.5082626342773</t>
   </si>
   <si>
     <t xml:space="preserve">22.994270324707</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">22.480281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5434036254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7057151794434</t>
+    <t xml:space="preserve">22.5434017181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.705717086792</t>
   </si>
   <si>
     <t xml:space="preserve">22.4532299041748</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">22.182710647583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7237510681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3630599975586</t>
+    <t xml:space="preserve">22.7237529754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3630561828613</t>
   </si>
   <si>
     <t xml:space="preserve">22.2097587585449</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">21.9212055206299</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8761157989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7047863006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9392414093018</t>
+    <t xml:space="preserve">21.8761196136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7047901153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9392433166504</t>
   </si>
   <si>
     <t xml:space="preserve">22.0745010375977</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2999362945557</t>
+    <t xml:space="preserve">22.299934387207</t>
   </si>
   <si>
     <t xml:space="preserve">22.8139228820801</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3179664611816</t>
+    <t xml:space="preserve">22.3179702758789</t>
   </si>
   <si>
     <t xml:space="preserve">22.1917266845703</t>
@@ -851,61 +851,61 @@
     <t xml:space="preserve">22.5253677368164</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6065235137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6335792541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2458324432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2277946472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.128604888916</t>
+    <t xml:space="preserve">22.6065254211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6335735321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2458305358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2277965545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1286067962646</t>
   </si>
   <si>
     <t xml:space="preserve">22.0835151672363</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2007427215576</t>
+    <t xml:space="preserve">22.2007446289062</t>
   </si>
   <si>
     <t xml:space="preserve">22.1376209259033</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1466369628906</t>
+    <t xml:space="preserve">22.1466388702393</t>
   </si>
   <si>
     <t xml:space="preserve">21.5965805053711</t>
   </si>
   <si>
-    <t xml:space="preserve">21.326057434082</t>
+    <t xml:space="preserve">21.3260593414307</t>
   </si>
   <si>
     <t xml:space="preserve">21.560510635376</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0294151306152</t>
+    <t xml:space="preserve">22.0294132232666</t>
   </si>
   <si>
     <t xml:space="preserve">21.6867523193359</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2368144989014</t>
+    <t xml:space="preserve">22.2368125915527</t>
   </si>
   <si>
     <t xml:space="preserve">22.3720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3991222381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6155414581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6606292724609</t>
+    <t xml:space="preserve">22.3991279602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6155395507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6606311798096</t>
   </si>
   <si>
     <t xml:space="preserve">23.0123062133789</t>
@@ -914,85 +914,85 @@
     <t xml:space="preserve">23.5193881988525</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2704563140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1739864349365</t>
+    <t xml:space="preserve">23.2704582214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1739826202393</t>
   </si>
   <si>
     <t xml:space="preserve">24.7087249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7732639312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2434673309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8150863647461</t>
+    <t xml:space="preserve">24.773265838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.243465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8150882720947</t>
   </si>
   <si>
     <t xml:space="preserve">25.7966480255127</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6860122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6675701141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0086994171143</t>
+    <t xml:space="preserve">25.6860103607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6675720214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0086975097656</t>
   </si>
   <si>
     <t xml:space="preserve">25.8888454437256</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9810428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0916767120361</t>
+    <t xml:space="preserve">25.9810409545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0916748046875</t>
   </si>
   <si>
     <t xml:space="preserve">25.907283782959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8058681488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9533824920654</t>
+    <t xml:space="preserve">25.8058662414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9533843994141</t>
   </si>
   <si>
     <t xml:space="preserve">25.676794052124</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6583557128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0775146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4002017974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.261905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3264408111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8009223937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4186420440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6441898345947</t>
+    <t xml:space="preserve">25.6583499908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0775108337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4001998901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2619075775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3264446258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8009204864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4186401367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6441879272461</t>
   </si>
   <si>
     <t xml:space="preserve">24.8562412261963</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9576549530029</t>
+    <t xml:space="preserve">24.9576568603516</t>
   </si>
   <si>
     <t xml:space="preserve">24.8931198120117</t>
@@ -1007,31 +1007,31 @@
     <t xml:space="preserve">23.1229419708252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2335796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9938659667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.781810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.671178817749</t>
+    <t xml:space="preserve">23.2335777282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9938678741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7818145751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6711769104004</t>
   </si>
   <si>
     <t xml:space="preserve">22.4960041046143</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7264957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5052242279053</t>
+    <t xml:space="preserve">22.7264976501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5052223205566</t>
   </si>
   <si>
     <t xml:space="preserve">22.3208293914795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5881996154785</t>
+    <t xml:space="preserve">22.5882015228271</t>
   </si>
   <si>
     <t xml:space="preserve">23.1137218475342</t>
@@ -1040,121 +1040,121 @@
     <t xml:space="preserve">22.9108905792236</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3995323181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7775421142578</t>
+    <t xml:space="preserve">23.3995304107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7775382995605</t>
   </si>
   <si>
     <t xml:space="preserve">23.6208038330078</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1413841247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9846477508545</t>
+    <t xml:space="preserve">23.1413803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9846496582031</t>
   </si>
   <si>
     <t xml:space="preserve">22.8740081787109</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7357177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6896171569824</t>
+    <t xml:space="preserve">22.7357158660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6896190643311</t>
   </si>
   <si>
     <t xml:space="preserve">23.3257732391357</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7406578063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9803714752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9711532592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0633506774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2477416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3860397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1555480957031</t>
+    <t xml:space="preserve">23.7406597137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9803733825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9711494445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.063346862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2477436065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3860378265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1555461883545</t>
   </si>
   <si>
     <t xml:space="preserve">24.6165313720703</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8611850738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6306915283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2158050537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1697101593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080043792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4463005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5384998321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1236133575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4321365356445</t>
+    <t xml:space="preserve">25.8611831665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6306953430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2158107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1697082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4462966918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5384979248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1236095428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4321346282959</t>
   </si>
   <si>
     <t xml:space="preserve">23.6484622955322</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0172481536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.109447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3399391174316</t>
+    <t xml:space="preserve">24.0172500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1094455718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.339937210083</t>
   </si>
   <si>
     <t xml:space="preserve">24.2016448974609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2938365936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.754825592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6626262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9853172302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4923973083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7228889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5704307556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5845947265625</t>
+    <t xml:space="preserve">24.2938404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7548236846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6626281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9853191375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4923992156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7228870391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5704326629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5845966339111</t>
   </si>
   <si>
     <t xml:space="preserve">25.9994812011719</t>
@@ -1166,25 +1166,25 @@
     <t xml:space="preserve">27.5668239593506</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7512168884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0739059448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5207290649414</t>
+    <t xml:space="preserve">27.751220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0739097595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5207252502441</t>
   </si>
   <si>
     <t xml:space="preserve">26.7370529174805</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5065631866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0314159393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5243320465088</t>
+    <t xml:space="preserve">26.5065612792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0314121246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5243358612061</t>
   </si>
   <si>
     <t xml:space="preserve">26.3682670593262</t>
@@ -1193,16 +1193,16 @@
     <t xml:space="preserve">26.5987606048584</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4604644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2299690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3221683502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1980381011963</t>
+    <t xml:space="preserve">26.4604663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2299709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3221702575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1980361938477</t>
   </si>
   <si>
     <t xml:space="preserve">26.2760715484619</t>
@@ -1214,52 +1214,52 @@
     <t xml:space="preserve">27.3824329376221</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4746246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5526580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8292484283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1058406829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8753509521484</t>
+    <t xml:space="preserve">27.4746284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5526599884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8292503356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.105842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8753471374512</t>
   </si>
   <si>
     <t xml:space="preserve">27.8434143066406</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7653827667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5809879302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9356117248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8114795684814</t>
+    <t xml:space="preserve">28.7653846740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5809860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9356098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8114814758301</t>
   </si>
   <si>
     <t xml:space="preserve">28.1661033630371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7192859649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1200046539307</t>
+    <t xml:space="preserve">28.7192840576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1200084686279</t>
   </si>
   <si>
     <t xml:space="preserve">27.059741973877</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9675483703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1519374847412</t>
+    <t xml:space="preserve">26.9675464630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1519412994385</t>
   </si>
   <si>
     <t xml:space="preserve">26.6909561157227</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">26.7831516265869</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0455799102783</t>
+    <t xml:space="preserve">26.0455780029297</t>
   </si>
   <si>
     <t xml:space="preserve">27.6590194702148</t>
@@ -1277,19 +1277,19 @@
     <t xml:space="preserve">26.9214477539062</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1828784942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0886993408203</t>
+    <t xml:space="preserve">26.1828804016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0886974334717</t>
   </si>
   <si>
     <t xml:space="preserve">26.4654273986816</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8061485290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7119636535645</t>
+    <t xml:space="preserve">25.8061466217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7119617462158</t>
   </si>
   <si>
     <t xml:space="preserve">25.1468677520752</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">25.3352336883545</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9114112854004</t>
+    <t xml:space="preserve">24.9114093780518</t>
   </si>
   <si>
     <t xml:space="preserve">24.487585067749</t>
@@ -1310,31 +1310,31 @@
     <t xml:space="preserve">23.9224872589111</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2632083892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0277481079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0748386383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7451992034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6039257049561</t>
+    <t xml:space="preserve">23.2632064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0277500152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0748405456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7451972961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6039237976074</t>
   </si>
   <si>
     <t xml:space="preserve">22.5097427368164</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4155616760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1801013946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0388259887695</t>
+    <t xml:space="preserve">22.4155578613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.180103302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0388278961182</t>
   </si>
   <si>
     <t xml:space="preserve">21.8504619598389</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">22.4626522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2271938323975</t>
+    <t xml:space="preserve">22.2271919250488</t>
   </si>
   <si>
     <t xml:space="preserve">23.4044799804688</t>
@@ -1361,22 +1361,22 @@
     <t xml:space="preserve">22.5568351745605</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1330127716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6620960235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1911773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.002815246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.096996307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8615398406982</t>
+    <t xml:space="preserve">22.1330089569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6620922088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.19118309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0028133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0969982147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8615379333496</t>
   </si>
   <si>
     <t xml:space="preserve">21.379545211792</t>
@@ -1388,25 +1388,25 @@
     <t xml:space="preserve">22.274284362793</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7562789916992</t>
+    <t xml:space="preserve">21.7562770843506</t>
   </si>
   <si>
     <t xml:space="preserve">21.9446449279785</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5679111480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5208187103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3324527740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2382698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8393802642822</t>
+    <t xml:space="preserve">21.5679130554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5208206176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3324565887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2382717132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8393821716309</t>
   </si>
   <si>
     <t xml:space="preserve">22.792293548584</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">23.6870288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7812099456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0166702270508</t>
+    <t xml:space="preserve">23.781213760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0166683197021</t>
   </si>
   <si>
     <t xml:space="preserve">24.2992191314697</t>
@@ -1436,40 +1436,40 @@
     <t xml:space="preserve">24.1579456329346</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2521286010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7230415344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6288604736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.675952911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5817680358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7701320648193</t>
+    <t xml:space="preserve">24.2521266937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7230434417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6288585662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6759510040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5817699432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.770133972168</t>
   </si>
   <si>
     <t xml:space="preserve">24.9584999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9003295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7590579986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9474239349365</t>
+    <t xml:space="preserve">25.9003314971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7590560913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9474201202393</t>
   </si>
   <si>
     <t xml:space="preserve">26.2770614624023</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9363441467285</t>
+    <t xml:space="preserve">26.9363460540771</t>
   </si>
   <si>
     <t xml:space="preserve">26.9834365844727</t>
@@ -1478,13 +1478,13 @@
     <t xml:space="preserve">26.8421611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7479801177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.265983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4543514251709</t>
+    <t xml:space="preserve">26.7479782104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2659873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4543495178223</t>
   </si>
   <si>
     <t xml:space="preserve">27.501443862915</t>
@@ -1496,40 +1496,40 @@
     <t xml:space="preserve">27.0776195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7008857727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6537952423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6067028045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.994514465332</t>
+    <t xml:space="preserve">26.7008838653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6537933349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6067008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9945125579834</t>
   </si>
   <si>
     <t xml:space="preserve">26.1357898712158</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0416069030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6177845001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4294147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0055923461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0997753143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8643169403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4404964447021</t>
+    <t xml:space="preserve">26.0416049957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6177806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4294166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0055904388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0997734069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.864315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4404945373535</t>
   </si>
   <si>
     <t xml:space="preserve">25.5235977172852</t>
@@ -1538,46 +1538,46 @@
     <t xml:space="preserve">26.3712463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3241558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7950706481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8892517089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0305290222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1718006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5485343933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6898097991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1136302947998</t>
+    <t xml:space="preserve">26.3241539001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7950687408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.889253616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0305309295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1718044281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5485324859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6898078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1136341094971</t>
   </si>
   <si>
     <t xml:space="preserve">28.3961791992188</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7258205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9141883850098</t>
+    <t xml:space="preserve">28.7258243560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9141902923584</t>
   </si>
   <si>
     <t xml:space="preserve">29.9502010345459</t>
   </si>
   <si>
-    <t xml:space="preserve">29.761833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3269309997559</t>
+    <t xml:space="preserve">29.7618370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3269348144531</t>
   </si>
   <si>
     <t xml:space="preserve">30.3740253448486</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">32.4460487365723</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4931373596191</t>
+    <t xml:space="preserve">32.4931449890137</t>
   </si>
   <si>
     <t xml:space="preserve">33.4820671081543</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">33.5762481689453</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9058876037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2466049194336</t>
+    <t xml:space="preserve">33.905891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2466125488281</t>
   </si>
   <si>
     <t xml:space="preserve">32.8698768615723</t>
@@ -1619,76 +1619,76 @@
     <t xml:space="preserve">33.1524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0582389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5873184204102</t>
+    <t xml:space="preserve">33.0582427978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5873222351074</t>
   </si>
   <si>
     <t xml:space="preserve">32.3047752380371</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9280471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4571342468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3629474639893</t>
+    <t xml:space="preserve">31.9280452728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4571285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.362943649292</t>
   </si>
   <si>
     <t xml:space="preserve">30.8920288085938</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0803966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0333042144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6565742492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6094818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2687683105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9862155914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4100360870361</t>
+    <t xml:space="preserve">31.0803985595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0333080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6565723419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6094837188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.268762588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.986213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4100341796875</t>
   </si>
   <si>
     <t xml:space="preserve">30.8449401855469</t>
   </si>
   <si>
-    <t xml:space="preserve">31.17458152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8809547424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0222244262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7396850585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0000686645508</t>
+    <t xml:space="preserve">31.1745758056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8809509277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0222320556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7396755218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.000072479248</t>
   </si>
   <si>
     <t xml:space="preserve">34.4709854125977</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7895469665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5900993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7784729003906</t>
+    <t xml:space="preserve">35.78955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5901031494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7784652709961</t>
   </si>
   <si>
     <t xml:space="preserve">37.155200958252</t>
@@ -1703,10 +1703,10 @@
     <t xml:space="preserve">38.2282104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">37.367000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.797607421875</t>
+    <t xml:space="preserve">37.3669967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7976112365723</t>
   </si>
   <si>
     <t xml:space="preserve">38.1803665161133</t>
@@ -1718,31 +1718,31 @@
     <t xml:space="preserve">37.9411430358887</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9889869689941</t>
+    <t xml:space="preserve">37.9889907836914</t>
   </si>
   <si>
     <t xml:space="preserve">37.8454513549805</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3191528320312</t>
+    <t xml:space="preserve">37.3191566467285</t>
   </si>
   <si>
     <t xml:space="preserve">38.8501968383789</t>
   </si>
   <si>
-    <t xml:space="preserve">38.754508972168</t>
+    <t xml:space="preserve">38.7545051574707</t>
   </si>
   <si>
     <t xml:space="preserve">39.3286476135254</t>
   </si>
   <si>
-    <t xml:space="preserve">39.041576385498</t>
+    <t xml:space="preserve">39.0415802001953</t>
   </si>
   <si>
     <t xml:space="preserve">38.8023529052734</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4674415588379</t>
+    <t xml:space="preserve">38.4674339294434</t>
   </si>
   <si>
     <t xml:space="preserve">38.1325187683105</t>
@@ -1757,40 +1757,40 @@
     <t xml:space="preserve">38.2760543823242</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5631217956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4195938110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3764953613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1372756958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.185115814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2808036804199</t>
+    <t xml:space="preserve">38.5631256103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4195899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3764915466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1372718811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1851119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2807998657227</t>
   </si>
   <si>
     <t xml:space="preserve">39.9027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1946067810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1036605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5342712402344</t>
+    <t xml:space="preserve">41.1946029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1036643981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5342636108398</t>
   </si>
   <si>
     <t xml:space="preserve">41.6730537414551</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8118476867676</t>
+    <t xml:space="preserve">40.8118438720703</t>
   </si>
   <si>
     <t xml:space="preserve">40.7161521911621</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">41.912281036377</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0605583190918</t>
+    <t xml:space="preserve">43.0605659484863</t>
   </si>
   <si>
     <t xml:space="preserve">43.4911689758301</t>
@@ -1811,10 +1811,10 @@
     <t xml:space="preserve">44.7829856872559</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4433212280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0174674987793</t>
+    <t xml:space="preserve">43.4433250427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0174598693848</t>
   </si>
   <si>
     <t xml:space="preserve">43.6347045898438</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">43.2040977478027</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9170265197754</t>
+    <t xml:space="preserve">42.9170227050781</t>
   </si>
   <si>
     <t xml:space="preserve">44.9265213012695</t>
@@ -1832,55 +1832,55 @@
     <t xml:space="preserve">45.4049758911133</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2614364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5963516235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6536865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8976669311523</t>
+    <t xml:space="preserve">45.2614326477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5963592529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6536903381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8976593017578</t>
   </si>
   <si>
     <t xml:space="preserve">48.6105918884277</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1847381591797</t>
+    <t xml:space="preserve">49.1847343444824</t>
   </si>
   <si>
     <t xml:space="preserve">48.993350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7588729858398</t>
+    <t xml:space="preserve">49.7588691711426</t>
   </si>
   <si>
     <t xml:space="preserve">49.2804222106934</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6631889343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3761100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5674934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6200866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0028457641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.725269317627</t>
+    <t xml:space="preserve">49.6631813049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3761138916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5674896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6200828552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0028419494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7252655029297</t>
   </si>
   <si>
     <t xml:space="preserve">52.6295776367188</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9597473144531</t>
+    <t xml:space="preserve">51.9597434997559</t>
   </si>
   <si>
     <t xml:space="preserve">51.8640556335449</t>
@@ -1889,10 +1889,10 @@
     <t xml:space="preserve">51.6726760864258</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4192123413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3235168457031</t>
+    <t xml:space="preserve">48.4192085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3235244750977</t>
   </si>
   <si>
     <t xml:space="preserve">50.0459403991699</t>
@@ -1907,67 +1907,67 @@
     <t xml:space="preserve">49.8545608520508</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4287033081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5338897705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0649299621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2994041442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4382019042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3666152954102</t>
+    <t xml:space="preserve">50.4287071228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5338859558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0649223327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2994079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4381942749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3666191101074</t>
   </si>
   <si>
     <t xml:space="preserve">46.9838562011719</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3618774414062</t>
+    <t xml:space="preserve">46.361873626709</t>
   </si>
   <si>
     <t xml:space="preserve">45.7398872375488</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9743690490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.586856842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7687492370605</t>
+    <t xml:space="preserve">44.974365234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5868606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7687454223633</t>
   </si>
   <si>
     <t xml:space="preserve">36.6493225097656</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5967330932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0945491790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4820575714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1854934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.529899597168</t>
+    <t xml:space="preserve">35.596736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0945510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4820556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1854953765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5299053192139</t>
   </si>
   <si>
     <t xml:space="preserve">31.0992965698242</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3816204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9269027709961</t>
+    <t xml:space="preserve">30.3816223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9268989562988</t>
   </si>
   <si>
     <t xml:space="preserve">36.410099029541</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">35.3096656799316</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5441398620605</t>
+    <t xml:space="preserve">34.5441436767578</t>
   </si>
   <si>
     <t xml:space="preserve">35.0704383850098</t>
@@ -1994,22 +1994,22 @@
     <t xml:space="preserve">37.1277732849121</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2329559326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.429084777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9984741210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7351455688477</t>
+    <t xml:space="preserve">39.2329597473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4290809631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.998477935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7351417541504</t>
   </si>
   <si>
     <t xml:space="preserve">45.9791145324707</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4528198242188</t>
+    <t xml:space="preserve">45.4528160095215</t>
   </si>
   <si>
     <t xml:space="preserve">45.0700569152832</t>
@@ -2021,16 +2021,16 @@
     <t xml:space="preserve">45.1179046630859</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4575653076172</t>
+    <t xml:space="preserve">46.4575614929199</t>
   </si>
   <si>
     <t xml:space="preserve">45.6441993713379</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8786773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3092803955078</t>
+    <t xml:space="preserve">44.8786811828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3092842102051</t>
   </si>
   <si>
     <t xml:space="preserve">45.1657447814941</t>
@@ -2039,91 +2039,91 @@
     <t xml:space="preserve">44.2088432312012</t>
   </si>
   <si>
-    <t xml:space="preserve">43.15625</t>
+    <t xml:space="preserve">43.1562538146973</t>
   </si>
   <si>
     <t xml:space="preserve">43.9217758178711</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8644409179688</t>
+    <t xml:space="preserve">41.8644371032715</t>
   </si>
   <si>
     <t xml:space="preserve">42.5821151733398</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0222129821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5485076904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5101547241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7015342712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7062835693359</t>
+    <t xml:space="preserve">45.0222091674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5485038757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5101585388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7015380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7062797546387</t>
   </si>
   <si>
     <t xml:space="preserve">47.9407577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5149040222168</t>
+    <t xml:space="preserve">48.5149002075195</t>
   </si>
   <si>
     <t xml:space="preserve">51.4812965393066</t>
   </si>
   <si>
-    <t xml:space="preserve">51.194221496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.768367767334</t>
+    <t xml:space="preserve">51.1942253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7683601379395</t>
   </si>
   <si>
     <t xml:space="preserve">51.2899131774902</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1080322265625</t>
+    <t xml:space="preserve">53.1080284118652</t>
   </si>
   <si>
     <t xml:space="preserve">53.9692420959473</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4907913208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1175193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6916618347168</t>
+    <t xml:space="preserve">53.4907875061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1175270080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6916656494141</t>
   </si>
   <si>
     <t xml:space="preserve">55.5002822875977</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3520011901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6390686035156</t>
+    <t xml:space="preserve">54.3519973754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6390724182129</t>
   </si>
   <si>
     <t xml:space="preserve">54.830451965332</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4045906066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7442474365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9356346130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.127010345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2658081054688</t>
+    <t xml:space="preserve">55.4045944213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.744255065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9356384277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1270179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2658042907715</t>
   </si>
   <si>
     <t xml:space="preserve">55.9787330627441</t>
@@ -2132,58 +2132,58 @@
     <t xml:space="preserve">57.3183975219727</t>
   </si>
   <si>
-    <t xml:space="preserve">58.6580543518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2227020263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7011489868164</t>
+    <t xml:space="preserve">58.6580581665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2227058410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7011528015137</t>
   </si>
   <si>
     <t xml:space="preserve">56.3614959716797</t>
   </si>
   <si>
-    <t xml:space="preserve">57.9882278442383</t>
+    <t xml:space="preserve">57.988224029541</t>
   </si>
   <si>
     <t xml:space="preserve">58.849437713623</t>
   </si>
   <si>
-    <t xml:space="preserve">61.3373794555664</t>
+    <t xml:space="preserve">61.3373756408691</t>
   </si>
   <si>
     <t xml:space="preserve">63.4425659179688</t>
   </si>
   <si>
-    <t xml:space="preserve">62.2942810058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3468742370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7296333312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6339454650879</t>
+    <t xml:space="preserve">62.2942771911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3468627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7296295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6339492797852</t>
   </si>
   <si>
     <t xml:space="preserve">64.3037719726562</t>
   </si>
   <si>
-    <t xml:space="preserve">64.5908432006836</t>
+    <t xml:space="preserve">64.5908508300781</t>
   </si>
   <si>
     <t xml:space="preserve">65.9305038452148</t>
   </si>
   <si>
-    <t xml:space="preserve">66.6960220336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3563613891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.9830932617188</t>
+    <t xml:space="preserve">66.6960296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3563690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9831008911133</t>
   </si>
   <si>
     <t xml:space="preserve">67.1744766235352</t>
@@ -2192,19 +2192,19 @@
     <t xml:space="preserve">66.5046463012695</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8443145751953</t>
+    <t xml:space="preserve">67.8443069458008</t>
   </si>
   <si>
     <t xml:space="preserve">70.0451812744141</t>
   </si>
   <si>
-    <t xml:space="preserve">69.1839752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.2891616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8106994628906</t>
+    <t xml:space="preserve">69.1839828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.2891540527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8107070922852</t>
   </si>
   <si>
     <t xml:space="preserve">70.6193313598633</t>
@@ -2213,25 +2213,25 @@
     <t xml:space="preserve">71.7676086425781</t>
   </si>
   <si>
-    <t xml:space="preserve">72.0546875</t>
+    <t xml:space="preserve">72.0546798706055</t>
   </si>
   <si>
     <t xml:space="preserve">71.002082824707</t>
   </si>
   <si>
-    <t xml:space="preserve">69.4710388183594</t>
+    <t xml:space="preserve">69.4710311889648</t>
   </si>
   <si>
     <t xml:space="preserve">68.9925918579102</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9495010375977</t>
+    <t xml:space="preserve">69.9494857788086</t>
   </si>
   <si>
     <t xml:space="preserve">68.8012161254883</t>
   </si>
   <si>
-    <t xml:space="preserve">69.6624298095703</t>
+    <t xml:space="preserve">69.6624221801758</t>
   </si>
   <si>
     <t xml:space="preserve">76.5521087646484</t>
@@ -2243,10 +2243,10 @@
     <t xml:space="preserve">75.8822860717773</t>
   </si>
   <si>
-    <t xml:space="preserve">74.734001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.8727798461914</t>
+    <t xml:space="preserve">74.7339935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.8727874755859</t>
   </si>
   <si>
     <t xml:space="preserve">74.8296890258789</t>
@@ -2255,34 +2255,34 @@
     <t xml:space="preserve">77.8917770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">78.2745513916016</t>
+    <t xml:space="preserve">78.274543762207</t>
   </si>
   <si>
     <t xml:space="preserve">77.7960891723633</t>
   </si>
   <si>
-    <t xml:space="preserve">79.4228134155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.7624816894531</t>
+    <t xml:space="preserve">79.4228210449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.7624740600586</t>
   </si>
   <si>
     <t xml:space="preserve">82.0064392089844</t>
   </si>
   <si>
-    <t xml:space="preserve">81.5279998779297</t>
+    <t xml:space="preserve">81.5279922485352</t>
   </si>
   <si>
     <t xml:space="preserve">81.910758972168</t>
   </si>
   <si>
-    <t xml:space="preserve">82.3892135620117</t>
+    <t xml:space="preserve">82.3892059326172</t>
   </si>
   <si>
     <t xml:space="preserve">81.4323043823242</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1452484130859</t>
+    <t xml:space="preserve">81.1452407836914</t>
   </si>
   <si>
     <t xml:space="preserve">80.4754104614258</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">81.7193832397461</t>
   </si>
   <si>
-    <t xml:space="preserve">81.8150787353516</t>
+    <t xml:space="preserve">81.8150634765625</t>
   </si>
   <si>
     <t xml:space="preserve">83.3461074829102</t>
@@ -2303,16 +2303,16 @@
     <t xml:space="preserve">82.77197265625</t>
   </si>
   <si>
-    <t xml:space="preserve">82.2935180664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.0305709838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3271179199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7288818359375</t>
+    <t xml:space="preserve">82.2935256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.0305557250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3271255493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.728874206543</t>
   </si>
   <si>
     <t xml:space="preserve">82.1021499633789</t>
@@ -2330,46 +2330,46 @@
     <t xml:space="preserve">82.4849014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3797149658203</t>
+    <t xml:space="preserve">80.3797225952148</t>
   </si>
   <si>
     <t xml:space="preserve">78.6572952270508</t>
   </si>
   <si>
-    <t xml:space="preserve">78.4659118652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6857833862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3556137084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0590515136719</t>
+    <t xml:space="preserve">78.4659194946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6857757568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.355598449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0590438842773</t>
   </si>
   <si>
     <t xml:space="preserve">85.9297485351562</t>
   </si>
   <si>
-    <t xml:space="preserve">87.173713684082</t>
+    <t xml:space="preserve">87.1737213134766</t>
   </si>
   <si>
     <t xml:space="preserve">87.2694091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">88.3219985961914</t>
+    <t xml:space="preserve">88.3220062255859</t>
   </si>
   <si>
     <t xml:space="preserve">86.7909545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">90.9056396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3840866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1064987182617</t>
+    <t xml:space="preserve">90.905632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3840942382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1065063476562</t>
   </si>
   <si>
     <t xml:space="preserve">95.8815155029297</t>
@@ -2378,13 +2378,13 @@
     <t xml:space="preserve">97.2211837768555</t>
   </si>
   <si>
-    <t xml:space="preserve">100.474639892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.622924804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.240173339844</t>
+    <t xml:space="preserve">100.474647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.622917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.240165710449</t>
   </si>
   <si>
     <t xml:space="preserve">97.986701965332</t>
@@ -2405,61 +2405,61 @@
     <t xml:space="preserve">94.8289337158203</t>
   </si>
   <si>
-    <t xml:space="preserve">95.307373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2547836303711</t>
+    <t xml:space="preserve">95.3073806762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2547988891602</t>
   </si>
   <si>
     <t xml:space="preserve">94.4461669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">97.0298080444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.541862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1590957641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8720245361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0634078979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3935699462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6806488037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9151306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.2978820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7237548828125</t>
+    <t xml:space="preserve">97.0298004150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5418548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1591033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8720321655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0634155273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3935775756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6806564331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9151229858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.2978897094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.723747253418</t>
   </si>
   <si>
     <t xml:space="preserve">94.3504791259766</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6039428710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.431549072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.876403808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.493629455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.598808288574</t>
+    <t xml:space="preserve">97.6039352416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.431541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.876388549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.493621826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.598815917969</t>
   </si>
   <si>
     <t xml:space="preserve">107.364334106445</t>
@@ -2468,34 +2468,34 @@
     <t xml:space="preserve">109.660903930664</t>
   </si>
   <si>
-    <t xml:space="preserve">110.235038757324</t>
+    <t xml:space="preserve">110.235054016113</t>
   </si>
   <si>
     <t xml:space="preserve">105.641914367676</t>
   </si>
   <si>
-    <t xml:space="preserve">106.216064453125</t>
+    <t xml:space="preserve">106.21605682373</t>
   </si>
   <si>
     <t xml:space="preserve">107.938484191895</t>
   </si>
   <si>
-    <t xml:space="preserve">107.555709838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.469520568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.747093200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.704002380371</t>
+    <t xml:space="preserve">107.555717468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.469528198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.747100830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.703994750977</t>
   </si>
   <si>
     <t xml:space="preserve">102.197074890137</t>
   </si>
   <si>
-    <t xml:space="preserve">99.5177459716797</t>
+    <t xml:space="preserve">99.5177383422852</t>
   </si>
   <si>
     <t xml:space="preserve">99.7091217041016</t>
@@ -2504,40 +2504,40 @@
     <t xml:space="preserve">103.345352172852</t>
   </si>
   <si>
-    <t xml:space="preserve">103.536735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.024688720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.981582641602</t>
+    <t xml:space="preserve">103.536720275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.024673461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.981575012207</t>
   </si>
   <si>
     <t xml:space="preserve">108.51261138916</t>
   </si>
   <si>
-    <t xml:space="preserve">105.833297729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.048789978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.388442993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.15397644043</t>
+    <t xml:space="preserve">105.833290100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.048782348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.388450622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.153968811035</t>
   </si>
   <si>
     <t xml:space="preserve">102.962593078613</t>
   </si>
   <si>
-    <t xml:space="preserve">105.450538635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.00569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.919494628906</t>
+    <t xml:space="preserve">105.450531005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.005683898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.919486999512</t>
   </si>
   <si>
     <t xml:space="preserve">106.407432556152</t>
@@ -2546,16 +2546,16 @@
     <t xml:space="preserve">109.086761474609</t>
   </si>
   <si>
-    <t xml:space="preserve">110.809181213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.679885864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.043663024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.172950744629</t>
+    <t xml:space="preserve">110.809188842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.679893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.043670654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.172958374023</t>
   </si>
   <si>
     <t xml:space="preserve">111.000564575195</t>
@@ -2564,22 +2564,22 @@
     <t xml:space="preserve">112.914367675781</t>
   </si>
   <si>
-    <t xml:space="preserve">109.852279663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.426422119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.383323669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.340225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.445404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.29712677002</t>
+    <t xml:space="preserve">109.852294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.426429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.383331298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.340232849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.445411682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.297134399414</t>
   </si>
   <si>
     <t xml:space="preserve">112.722991943359</t>
@@ -2594,10 +2594,10 @@
     <t xml:space="preserve">115.210929870605</t>
   </si>
   <si>
-    <t xml:space="preserve">116.741973876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.167823791504</t>
+    <t xml:space="preserve">116.741981506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.167831420898</t>
   </si>
   <si>
     <t xml:space="preserve">115.78507232666</t>
@@ -2606,10 +2606,10 @@
     <t xml:space="preserve">116.550598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">119.804061889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.186820983887</t>
+    <t xml:space="preserve">119.804054260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.186813354492</t>
   </si>
   <si>
     <t xml:space="preserve">122.100616455078</t>
@@ -2618,43 +2618,43 @@
     <t xml:space="preserve">122.866134643555</t>
   </si>
   <si>
-    <t xml:space="preserve">123.63166809082</t>
+    <t xml:space="preserve">123.631660461426</t>
   </si>
   <si>
     <t xml:space="preserve">131.478240966797</t>
   </si>
   <si>
-    <t xml:space="preserve">127.267890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.459266662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.990325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.052368164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.157577514648</t>
+    <t xml:space="preserve">127.26789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.459259033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.990310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.052398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.157592773438</t>
   </si>
   <si>
     <t xml:space="preserve">133.774826049805</t>
   </si>
   <si>
-    <t xml:space="preserve">132.626525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.435134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.923095703125</t>
+    <t xml:space="preserve">132.626541137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.435150146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.923080444336</t>
   </si>
   <si>
     <t xml:space="preserve">136.645538330078</t>
   </si>
   <si>
-    <t xml:space="preserve">137.411041259766</t>
+    <t xml:space="preserve">137.411071777344</t>
   </si>
   <si>
     <t xml:space="preserve">135.305847167969</t>
@@ -2666,22 +2666,22 @@
     <t xml:space="preserve">134.731719970703</t>
   </si>
   <si>
-    <t xml:space="preserve">136.262741088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.793792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.176559448242</t>
+    <t xml:space="preserve">136.262771606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.793823242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.176574707031</t>
   </si>
   <si>
     <t xml:space="preserve">137.028289794922</t>
   </si>
   <si>
-    <t xml:space="preserve">138.559326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.899002075195</t>
+    <t xml:space="preserve">138.559341430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.898971557617</t>
   </si>
   <si>
     <t xml:space="preserve">136.454147338867</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">138.750701904297</t>
   </si>
   <si>
-    <t xml:space="preserve">139.324859619141</t>
+    <t xml:space="preserve">139.324844360352</t>
   </si>
   <si>
     <t xml:space="preserve">137.98518371582</t>
@@ -2699,46 +2699,46 @@
     <t xml:space="preserve">135.497253417969</t>
   </si>
   <si>
-    <t xml:space="preserve">144.492095947266</t>
+    <t xml:space="preserve">144.492111206055</t>
   </si>
   <si>
     <t xml:space="preserve">144.874862670898</t>
   </si>
   <si>
-    <t xml:space="preserve">144.109375</t>
+    <t xml:space="preserve">144.109359741211</t>
   </si>
   <si>
     <t xml:space="preserve">142.195556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">143.726608276367</t>
+    <t xml:space="preserve">143.726577758789</t>
   </si>
   <si>
     <t xml:space="preserve">143.91796875</t>
   </si>
   <si>
-    <t xml:space="preserve">144.683486938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.257629394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.936965942383</t>
+    <t xml:space="preserve">144.683502197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.25764465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.936950683594</t>
   </si>
   <si>
     <t xml:space="preserve">145.640396118164</t>
   </si>
   <si>
-    <t xml:space="preserve">146.788681030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.276611328125</t>
+    <t xml:space="preserve">146.788665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.276626586914</t>
   </si>
   <si>
     <t xml:space="preserve">150.999038696289</t>
   </si>
   <si>
-    <t xml:space="preserve">150.424896240234</t>
+    <t xml:space="preserve">150.424911499023</t>
   </si>
   <si>
     <t xml:space="preserve">153.48698425293</t>
@@ -2750,25 +2750,25 @@
     <t xml:space="preserve">155.400787353516</t>
   </si>
   <si>
-    <t xml:space="preserve">151.1904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.888748168945</t>
+    <t xml:space="preserve">151.190444946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.888717651367</t>
   </si>
   <si>
     <t xml:space="preserve">159.037002563477</t>
   </si>
   <si>
-    <t xml:space="preserve">158.654235839844</t>
+    <t xml:space="preserve">158.654251098633</t>
   </si>
   <si>
     <t xml:space="preserve">159.61116027832</t>
   </si>
   <si>
-    <t xml:space="preserve">161.333572387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.524963378906</t>
+    <t xml:space="preserve">161.333587646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.524948120117</t>
   </si>
   <si>
     <t xml:space="preserve">163.438766479492</t>
@@ -2777,10 +2777,10 @@
     <t xml:space="preserve">163.821517944336</t>
   </si>
   <si>
-    <t xml:space="preserve">168.606033325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.773284912109</t>
+    <t xml:space="preserve">168.606018066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">170.328460693359</t>
@@ -2792,19 +2792,19 @@
     <t xml:space="preserve">168.031890869141</t>
   </si>
   <si>
-    <t xml:space="preserve">165.352569580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.759429931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.099090576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.668106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.074996948242</t>
+    <t xml:space="preserve">165.352584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.75944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.099075317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.668090820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.074981689453</t>
   </si>
   <si>
     <t xml:space="preserve">161.930511474609</t>
@@ -2816,10 +2816,10 @@
     <t xml:space="preserve">160.58430480957</t>
   </si>
   <si>
-    <t xml:space="preserve">159.045745849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.12239074707</t>
+    <t xml:space="preserve">159.045761108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.122375488281</t>
   </si>
   <si>
     <t xml:space="preserve">145.583602905273</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">150.391525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">150.19921875</t>
+    <t xml:space="preserve">150.199203491211</t>
   </si>
   <si>
     <t xml:space="preserve">148.083724975586</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">156.545669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">155.968719482422</t>
+    <t xml:space="preserve">155.968704223633</t>
   </si>
   <si>
     <t xml:space="preserve">154.43017578125</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">170.200134277344</t>
   </si>
   <si>
-    <t xml:space="preserve">168.469284057617</t>
+    <t xml:space="preserve">168.469268798828</t>
   </si>
   <si>
     <t xml:space="preserve">164.430633544922</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">162.507461547852</t>
   </si>
   <si>
-    <t xml:space="preserve">163.469039916992</t>
+    <t xml:space="preserve">163.469055175781</t>
   </si>
   <si>
     <t xml:space="preserve">165.584533691406</t>
@@ -2900,10 +2900,10 @@
     <t xml:space="preserve">175.584991455078</t>
   </si>
   <si>
-    <t xml:space="preserve">180.392913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.777542114258</t>
+    <t xml:space="preserve">180.392929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.777526855469</t>
   </si>
   <si>
     <t xml:space="preserve">178.469741821289</t>
@@ -2915,22 +2915,22 @@
     <t xml:space="preserve">181.739135742188</t>
   </si>
   <si>
-    <t xml:space="preserve">185.008514404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.085342407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.508392333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.276977539062</t>
+    <t xml:space="preserve">185.008499145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.085327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.508407592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.276962280273</t>
   </si>
   <si>
     <t xml:space="preserve">169.046234130859</t>
   </si>
   <si>
-    <t xml:space="preserve">170.584762573242</t>
+    <t xml:space="preserve">170.584747314453</t>
   </si>
   <si>
     <t xml:space="preserve">167.507705688477</t>
@@ -2954,13 +2954,13 @@
     <t xml:space="preserve">172.700241088867</t>
   </si>
   <si>
-    <t xml:space="preserve">172.123306274414</t>
+    <t xml:space="preserve">172.123291015625</t>
   </si>
   <si>
     <t xml:space="preserve">171.93098449707</t>
   </si>
   <si>
-    <t xml:space="preserve">167.315368652344</t>
+    <t xml:space="preserve">167.315383911133</t>
   </si>
   <si>
     <t xml:space="preserve">163.853668212891</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">165.392211914062</t>
   </si>
   <si>
-    <t xml:space="preserve">151.160781860352</t>
+    <t xml:space="preserve">151.160797119141</t>
   </si>
   <si>
     <t xml:space="preserve">158.853454589844</t>
@@ -2996,19 +2996,19 @@
     <t xml:space="preserve">159.815032958984</t>
   </si>
   <si>
-    <t xml:space="preserve">156.930282592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.161010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.314697265625</t>
+    <t xml:space="preserve">156.930297851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.161026000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.314682006836</t>
   </si>
   <si>
     <t xml:space="preserve">145.968246459961</t>
   </si>
   <si>
-    <t xml:space="preserve">146.929824829102</t>
+    <t xml:space="preserve">146.929840087891</t>
   </si>
   <si>
     <t xml:space="preserve">151.353088378906</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">153.468597412109</t>
   </si>
   <si>
-    <t xml:space="preserve">153.276260375977</t>
+    <t xml:space="preserve">153.276275634766</t>
   </si>
   <si>
     <t xml:space="preserve">157.122604370117</t>
@@ -3026,28 +3026,28 @@
     <t xml:space="preserve">151.930053710938</t>
   </si>
   <si>
-    <t xml:space="preserve">146.545196533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.968032836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.92936706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.660217285156</t>
+    <t xml:space="preserve">146.545181274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.968017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.929351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.660232543945</t>
   </si>
   <si>
     <t xml:space="preserve">132.698394775391</t>
   </si>
   <si>
-    <t xml:space="preserve">132.506088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.198287963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.813888549805</t>
+    <t xml:space="preserve">132.506072998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.198303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.813873291016</t>
   </si>
   <si>
     <t xml:space="preserve">130.005981445312</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">132.890716552734</t>
   </si>
   <si>
-    <t xml:space="preserve">137.506332397461</t>
+    <t xml:space="preserve">137.506317138672</t>
   </si>
   <si>
     <t xml:space="preserve">136.160110473633</t>
@@ -3074,16 +3074,16 @@
     <t xml:space="preserve">138.467895507812</t>
   </si>
   <si>
-    <t xml:space="preserve">135.583160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.813430786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.659294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.582695007324</t>
+    <t xml:space="preserve">135.583145141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.813423156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.659301757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.582702636719</t>
   </si>
   <si>
     <t xml:space="preserve">125.198059082031</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">137.314010620117</t>
   </si>
   <si>
-    <t xml:space="preserve">138.8525390625</t>
+    <t xml:space="preserve">138.852523803711</t>
   </si>
   <si>
     <t xml:space="preserve">142.891189575195</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">143.275817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">142.60270690918</t>
+    <t xml:space="preserve">142.602722167969</t>
   </si>
   <si>
     <t xml:space="preserve">142.698867797852</t>
@@ -3131,19 +3131,19 @@
     <t xml:space="preserve">139.525650024414</t>
   </si>
   <si>
-    <t xml:space="preserve">141.160354614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.198745727539</t>
+    <t xml:space="preserve">141.160339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.198760986328</t>
   </si>
   <si>
     <t xml:space="preserve">139.910278320312</t>
   </si>
   <si>
-    <t xml:space="preserve">139.429473876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.237182617188</t>
+    <t xml:space="preserve">139.429489135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.237167358398</t>
   </si>
   <si>
     <t xml:space="preserve">140.006439208984</t>
@@ -3173,16 +3173,16 @@
     <t xml:space="preserve">128.275131225586</t>
   </si>
   <si>
-    <t xml:space="preserve">130.294448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.236473083496</t>
+    <t xml:space="preserve">130.294464111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.236480712891</t>
   </si>
   <si>
     <t xml:space="preserve">122.890258789062</t>
   </si>
   <si>
-    <t xml:space="preserve">118.563148498535</t>
+    <t xml:space="preserve">118.563140869141</t>
   </si>
   <si>
     <t xml:space="preserve">109.81273651123</t>
@@ -3218,19 +3218,19 @@
     <t xml:space="preserve">120.486312866211</t>
   </si>
   <si>
-    <t xml:space="preserve">116.736137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.832290649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.043930053711</t>
+    <t xml:space="preserve">116.736129760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.832298278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.043937683105</t>
   </si>
   <si>
     <t xml:space="preserve">121.736358642578</t>
   </si>
   <si>
-    <t xml:space="preserve">124.621116638184</t>
+    <t xml:space="preserve">124.621124267578</t>
   </si>
   <si>
     <t xml:space="preserve">123.274894714355</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">121.544044494629</t>
   </si>
   <si>
-    <t xml:space="preserve">124.044166564941</t>
+    <t xml:space="preserve">124.044158935547</t>
   </si>
   <si>
     <t xml:space="preserve">124.332641601562</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">123.178741455078</t>
   </si>
   <si>
-    <t xml:space="preserve">114.524490356445</t>
+    <t xml:space="preserve">114.524482727051</t>
   </si>
   <si>
     <t xml:space="preserve">112.889808654785</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">116.447654724121</t>
   </si>
   <si>
-    <t xml:space="preserve">115.197593688965</t>
+    <t xml:space="preserve">115.197601318359</t>
   </si>
   <si>
     <t xml:space="preserve">119.140098571777</t>
@@ -3293,13 +3293,13 @@
     <t xml:space="preserve">119.428573608398</t>
   </si>
   <si>
-    <t xml:space="preserve">117.890029907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.293762207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.178276062012</t>
+    <t xml:space="preserve">117.890037536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.293754577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.178283691406</t>
   </si>
   <si>
     <t xml:space="preserve">119.332405090332</t>
@@ -3311,10 +3311,10 @@
     <t xml:space="preserve">125.39037322998</t>
   </si>
   <si>
-    <t xml:space="preserve">122.986427307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.27466583252</t>
+    <t xml:space="preserve">122.986419677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.274673461914</t>
   </si>
   <si>
     <t xml:space="preserve">119.717041015625</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">120.774780273438</t>
   </si>
   <si>
-    <t xml:space="preserve">123.659538269043</t>
+    <t xml:space="preserve">123.659530639648</t>
   </si>
   <si>
     <t xml:space="preserve">128.9482421875</t>
@@ -3350,16 +3350,16 @@
     <t xml:space="preserve">129.044403076172</t>
   </si>
   <si>
-    <t xml:space="preserve">131.159881591797</t>
+    <t xml:space="preserve">131.159866333008</t>
   </si>
   <si>
     <t xml:space="preserve">125.967330932617</t>
   </si>
   <si>
-    <t xml:space="preserve">126.351959228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.563362121582</t>
+    <t xml:space="preserve">126.35196685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.563369750977</t>
   </si>
   <si>
     <t xml:space="preserve">127.313537597656</t>
@@ -3371,7 +3371,7 @@
     <t xml:space="preserve">126.736595153809</t>
   </si>
   <si>
-    <t xml:space="preserve">121.447883605957</t>
+    <t xml:space="preserve">121.447891235352</t>
   </si>
   <si>
     <t xml:space="preserve">117.6015625</t>
@@ -3386,10 +3386,10 @@
     <t xml:space="preserve">121.063255310059</t>
   </si>
   <si>
-    <t xml:space="preserve">117.505401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.870704650879</t>
+    <t xml:space="preserve">117.505393981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.870712280273</t>
   </si>
   <si>
     <t xml:space="preserve">116.255348205566</t>
@@ -3398,19 +3398,19 @@
     <t xml:space="preserve">112.312850952148</t>
   </si>
   <si>
-    <t xml:space="preserve">115.582237243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.678398132324</t>
+    <t xml:space="preserve">115.582229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.67839050293</t>
   </si>
   <si>
     <t xml:space="preserve">118.178512573242</t>
   </si>
   <si>
-    <t xml:space="preserve">114.909133911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.596160888672</t>
+    <t xml:space="preserve">114.909126281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.596168518066</t>
   </si>
   <si>
     <t xml:space="preserve">105.336387634277</t>
@@ -3443,10 +3443,10 @@
     <t xml:space="preserve">109.212615966797</t>
   </si>
   <si>
-    <t xml:space="preserve">113.185745239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.441444396973</t>
+    <t xml:space="preserve">113.185752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.441452026367</t>
   </si>
   <si>
     <t xml:space="preserve">111.829071044922</t>
@@ -3455,19 +3455,19 @@
     <t xml:space="preserve">107.274505615234</t>
   </si>
   <si>
-    <t xml:space="preserve">104.851860046387</t>
+    <t xml:space="preserve">104.851867675781</t>
   </si>
   <si>
     <t xml:space="preserve">104.658058166504</t>
   </si>
   <si>
-    <t xml:space="preserve">101.847785949707</t>
+    <t xml:space="preserve">101.847793579102</t>
   </si>
   <si>
     <t xml:space="preserve">102.429222106934</t>
   </si>
   <si>
-    <t xml:space="preserve">103.49520111084</t>
+    <t xml:space="preserve">103.495193481445</t>
   </si>
   <si>
     <t xml:space="preserve">104.076622009277</t>
@@ -3488,25 +3488,25 @@
     <t xml:space="preserve">114.348617553711</t>
   </si>
   <si>
-    <t xml:space="preserve">109.794059753418</t>
+    <t xml:space="preserve">109.794052124023</t>
   </si>
   <si>
     <t xml:space="preserve">107.468315124512</t>
   </si>
   <si>
-    <t xml:space="preserve">106.305442810059</t>
+    <t xml:space="preserve">106.305450439453</t>
   </si>
   <si>
     <t xml:space="preserve">102.332321166992</t>
   </si>
   <si>
-    <t xml:space="preserve">100.87873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.979713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.340469360352</t>
+    <t xml:space="preserve">100.878730773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.979721069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.340476989746</t>
   </si>
   <si>
     <t xml:space="preserve">117.643409729004</t>
@@ -3518,16 +3518,16 @@
     <t xml:space="preserve">117.837219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">116.771263122559</t>
+    <t xml:space="preserve">116.771255493164</t>
   </si>
   <si>
     <t xml:space="preserve">114.445518493652</t>
   </si>
   <si>
-    <t xml:space="preserve">114.73624420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.026954650879</t>
+    <t xml:space="preserve">114.736236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.026947021484</t>
   </si>
   <si>
     <t xml:space="preserve">115.317672729492</t>
@@ -3536,10 +3536,10 @@
     <t xml:space="preserve">115.51148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">115.220764160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.965057373047</t>
+    <t xml:space="preserve">115.220771789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.965065002441</t>
   </si>
   <si>
     <t xml:space="preserve">113.476463317871</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">118.612464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">112.991943359375</t>
+    <t xml:space="preserve">112.99193572998</t>
   </si>
   <si>
     <t xml:space="preserve">111.053825378418</t>
@@ -3575,10 +3575,10 @@
     <t xml:space="preserve">108.243560791016</t>
   </si>
   <si>
-    <t xml:space="preserve">107.080696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.375495910645</t>
+    <t xml:space="preserve">107.080703735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.37548828125</t>
   </si>
   <si>
     <t xml:space="preserve">108.534278869629</t>
@@ -3587,16 +3587,16 @@
     <t xml:space="preserve">110.181671142578</t>
   </si>
   <si>
-    <t xml:space="preserve">109.890960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.24764251709</t>
+    <t xml:space="preserve">109.890953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.247634887695</t>
   </si>
   <si>
     <t xml:space="preserve">113.282661437988</t>
   </si>
   <si>
-    <t xml:space="preserve">112.410507202148</t>
+    <t xml:space="preserve">112.410499572754</t>
   </si>
   <si>
     <t xml:space="preserve">114.639335632324</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">117.255783081055</t>
   </si>
   <si>
-    <t xml:space="preserve">117.352691650391</t>
+    <t xml:space="preserve">117.352684020996</t>
   </si>
   <si>
     <t xml:space="preserve">118.031028747559</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">120.162956237793</t>
   </si>
   <si>
-    <t xml:space="preserve">121.907257080078</t>
+    <t xml:space="preserve">121.907249450684</t>
   </si>
   <si>
     <t xml:space="preserve">120.550575256348</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">122.779403686523</t>
   </si>
   <si>
-    <t xml:space="preserve">123.263931274414</t>
+    <t xml:space="preserve">123.263938903809</t>
   </si>
   <si>
     <t xml:space="preserve">121.810340881348</t>
@@ -3647,10 +3647,10 @@
     <t xml:space="preserve">123.748458862305</t>
   </si>
   <si>
-    <t xml:space="preserve">131.985427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.888534545898</t>
+    <t xml:space="preserve">131.985443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.888549804688</t>
   </si>
   <si>
     <t xml:space="preserve">132.179244995117</t>
@@ -3683,10 +3683,10 @@
     <t xml:space="preserve">124.136085510254</t>
   </si>
   <si>
-    <t xml:space="preserve">123.845367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.422729492188</t>
+    <t xml:space="preserve">123.845359802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.422737121582</t>
   </si>
   <si>
     <t xml:space="preserve">121.325820922852</t>
@@ -3698,19 +3698,19 @@
     <t xml:space="preserve">120.35676574707</t>
   </si>
   <si>
-    <t xml:space="preserve">118.321739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.8681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.802200317383</t>
+    <t xml:space="preserve">118.321746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.868156433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.802207946777</t>
   </si>
   <si>
     <t xml:space="preserve">113.864097595215</t>
   </si>
   <si>
-    <t xml:space="preserve">113.960990905762</t>
+    <t xml:space="preserve">113.960998535156</t>
   </si>
   <si>
     <t xml:space="preserve">113.088836669922</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">110.472389221191</t>
   </si>
   <si>
-    <t xml:space="preserve">108.824996948242</t>
+    <t xml:space="preserve">108.825004577637</t>
   </si>
   <si>
     <t xml:space="preserve">115.414573669434</t>
   </si>
   <si>
-    <t xml:space="preserve">109.987869262695</t>
+    <t xml:space="preserve">109.987861633301</t>
   </si>
   <si>
     <t xml:space="preserve">111.538352966309</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">113.670280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">118.127944946289</t>
+    <t xml:space="preserve">118.127937316895</t>
   </si>
   <si>
     <t xml:space="preserve">114.154808044434</t>
@@ -3752,13 +3752,13 @@
     <t xml:space="preserve">119.678428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">116.383628845215</t>
+    <t xml:space="preserve">116.383636474609</t>
   </si>
   <si>
     <t xml:space="preserve">115.123863220215</t>
   </si>
   <si>
-    <t xml:space="preserve">112.119789123535</t>
+    <t xml:space="preserve">112.119781494141</t>
   </si>
   <si>
     <t xml:space="preserve">110.569290161133</t>
@@ -3782,13 +3782,13 @@
     <t xml:space="preserve">104.754959106445</t>
   </si>
   <si>
-    <t xml:space="preserve">105.724006652832</t>
+    <t xml:space="preserve">105.724014282227</t>
   </si>
   <si>
     <t xml:space="preserve">103.592094421387</t>
   </si>
   <si>
-    <t xml:space="preserve">106.88688659668</t>
+    <t xml:space="preserve">106.886894226074</t>
   </si>
   <si>
     <t xml:space="preserve">103.204475402832</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">100.588027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">100.297309875488</t>
+    <t xml:space="preserve">100.297302246094</t>
   </si>
   <si>
     <t xml:space="preserve">102.719940185547</t>
@@ -3806,13 +3806,13 @@
     <t xml:space="preserve">103.107566833496</t>
   </si>
   <si>
-    <t xml:space="preserve">104.561149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.371421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.855949401855</t>
+    <t xml:space="preserve">104.561157226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.37141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.855941772461</t>
   </si>
   <si>
     <t xml:space="preserve">109.018814086914</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">116.480545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">115.705291748047</t>
+    <t xml:space="preserve">115.705299377441</t>
   </si>
   <si>
     <t xml:space="preserve">113.37956237793</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">102.235420227051</t>
   </si>
   <si>
-    <t xml:space="preserve">102.623046875</t>
+    <t xml:space="preserve">102.623039245605</t>
   </si>
   <si>
     <t xml:space="preserve">104.173530578613</t>
@@ -3866,10 +3866,10 @@
     <t xml:space="preserve">100.975639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">100.200393676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.491111755371</t>
+    <t xml:space="preserve">100.200401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.491104125977</t>
   </si>
   <si>
     <t xml:space="preserve">100.006591796875</t>
@@ -3884,10 +3884,10 @@
     <t xml:space="preserve">101.653984069824</t>
   </si>
   <si>
-    <t xml:space="preserve">100.39421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3282470703125</t>
+    <t xml:space="preserve">100.394203186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.328254699707</t>
   </si>
   <si>
     <t xml:space="preserve">99.6189727783203</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">102.138511657715</t>
   </si>
   <si>
-    <t xml:space="preserve">101.75089263916</t>
+    <t xml:space="preserve">101.750885009766</t>
   </si>
   <si>
     <t xml:space="preserve">99.8127746582031</t>
@@ -3914,7 +3914,7 @@
     <t xml:space="preserve">97.1963272094727</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6808547973633</t>
+    <t xml:space="preserve">97.6808624267578</t>
   </si>
   <si>
     <t xml:space="preserve">99.0078277587891</t>
@@ -5160,6 +5160,9 @@
   </si>
   <si>
     <t xml:space="preserve">82.6500015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8000030517578</t>
   </si>
 </sst>
 </file>
@@ -70238,7 +70241,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6495717593</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>27518</v>
@@ -70259,6 +70262,32 @@
         <v>1715</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6496527778</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>46124</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>82.9000015258789</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>79.3000030517578</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>81.8000030517578</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1716</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="1726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1727" uniqueCount="1727">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5495910644531</t>
+    <t xml:space="preserve">13.5495901107788</t>
   </si>
   <si>
     <t xml:space="preserve">SES.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5321063995361</t>
+    <t xml:space="preserve">13.5321083068848</t>
   </si>
   <si>
     <t xml:space="preserve">13.2523727416992</t>
@@ -56,28 +56,28 @@
     <t xml:space="preserve">13.1125078201294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8589992523193</t>
+    <t xml:space="preserve">12.858998298645</t>
   </si>
   <si>
     <t xml:space="preserve">13.0513153076172</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9901237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9376735687256</t>
+    <t xml:space="preserve">12.990122795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9376726150513</t>
   </si>
   <si>
     <t xml:space="preserve">13.1037654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">13.025089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8502559661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2383394241333</t>
+    <t xml:space="preserve">13.0250902175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8502550125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.238338470459</t>
   </si>
   <si>
     <t xml:space="preserve">12.5880069732666</t>
@@ -89,13 +89,13 @@
     <t xml:space="preserve">12.7191324234009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6841650009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6054906845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3257570266724</t>
+    <t xml:space="preserve">12.6841659545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.605489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3257579803467</t>
   </si>
   <si>
     <t xml:space="preserve">12.0460224151611</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">12.1421823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9270906448364</t>
+    <t xml:space="preserve">10.9270887374878</t>
   </si>
   <si>
     <t xml:space="preserve">10.9795398712158</t>
@@ -116,52 +116,52 @@
     <t xml:space="preserve">11.3641729354858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4515905380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0984745025635</t>
+    <t xml:space="preserve">11.4515914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0984735488892</t>
   </si>
   <si>
     <t xml:space="preserve">12.1072149276733</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8886737823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9760894775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9323797225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0110549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0809888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8012561798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334400177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8274803161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0635080337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5005903244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6754217147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7978067398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1649560928345</t>
+    <t xml:space="preserve">11.8886747360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9760885238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9323806762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0110540390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0809907913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8012571334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334390640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8274812698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0635061264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5005893707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6754236221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7978076934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1649580001831</t>
   </si>
   <si>
     <t xml:space="preserve">13.1562156677246</t>
@@ -170,40 +170,40 @@
     <t xml:space="preserve">13.0687980651855</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1212482452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.19118309021</t>
+    <t xml:space="preserve">13.1212491989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1911821365356</t>
   </si>
   <si>
     <t xml:space="preserve">12.7540979385376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8939657211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9027080535889</t>
+    <t xml:space="preserve">12.8939647674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9027070999146</t>
   </si>
   <si>
     <t xml:space="preserve">13.0600566864014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1999235153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9813814163208</t>
+    <t xml:space="preserve">13.1999244689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9813833236694</t>
   </si>
   <si>
     <t xml:space="preserve">13.4534320831299</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7069406509399</t>
+    <t xml:space="preserve">13.7069416046143</t>
   </si>
   <si>
     <t xml:space="preserve">13.4709157943726</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4621744155884</t>
+    <t xml:space="preserve">13.4621734619141</t>
   </si>
   <si>
     <t xml:space="preserve">13.2086639404297</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">13.3223066329956</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0950241088867</t>
+    <t xml:space="preserve">13.0950231552124</t>
   </si>
   <si>
     <t xml:space="preserve">12.9988651275635</t>
@@ -224,70 +224,70 @@
     <t xml:space="preserve">12.4481391906738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3782072067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0285396575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1509227752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4393968582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5617809295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5268154144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6317157745361</t>
+    <t xml:space="preserve">12.3782062530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0285387039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1509237289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4393978118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5617799758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5268144607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6317148208618</t>
   </si>
   <si>
     <t xml:space="preserve">12.3694648742676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.771580696106</t>
+    <t xml:space="preserve">12.7715816497803</t>
   </si>
   <si>
     <t xml:space="preserve">12.4306573867798</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2820482254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1946296691895</t>
+    <t xml:space="preserve">12.2820491790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1946306228638</t>
   </si>
   <si>
     <t xml:space="preserve">12.2470817565918</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4131736755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5093326568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3869495391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8187389373779</t>
+    <t xml:space="preserve">12.4131717681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5093307495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3869476318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8187398910522</t>
   </si>
   <si>
     <t xml:space="preserve">11.8449649810791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2558221817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5792646408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2208547592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1858892440796</t>
+    <t xml:space="preserve">12.2558250427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5792665481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2208557128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1858901977539</t>
   </si>
   <si>
     <t xml:space="preserve">12.7803230285645</t>
@@ -299,10 +299,10 @@
     <t xml:space="preserve">12.8764810562134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8065481185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7628393173218</t>
+    <t xml:space="preserve">12.8065500259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7628412246704</t>
   </si>
   <si>
     <t xml:space="preserve">12.8677406311035</t>
@@ -311,37 +311,37 @@
     <t xml:space="preserve">12.8327741622925</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5355577468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1824407577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0338325500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3048229217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.261116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3747587203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6020402908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6894550323486</t>
+    <t xml:space="preserve">12.5355558395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1824417114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0338296890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3048248291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2611150741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3747577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6020412445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6894569396973</t>
   </si>
   <si>
     <t xml:space="preserve">13.724422454834</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7514753341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5711288452148</t>
+    <t xml:space="preserve">13.7514772415161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5711297988892</t>
   </si>
   <si>
     <t xml:space="preserve">13.8687019348145</t>
@@ -353,25 +353,25 @@
     <t xml:space="preserve">13.6432676315308</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6613006591797</t>
+    <t xml:space="preserve">13.6613025665283</t>
   </si>
   <si>
     <t xml:space="preserve">13.5981817245483</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6162166595459</t>
+    <t xml:space="preserve">13.6162147521973</t>
   </si>
   <si>
     <t xml:space="preserve">13.5260429382324</t>
   </si>
   <si>
-    <t xml:space="preserve">13.553092956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3456954956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801458358765</t>
+    <t xml:space="preserve">13.5530939102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3456945419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801467895508</t>
   </si>
   <si>
     <t xml:space="preserve">13.6973714828491</t>
@@ -386,16 +386,16 @@
     <t xml:space="preserve">13.7965631484985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9769115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0400304794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0129795074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9047718048096</t>
+    <t xml:space="preserve">13.9769105911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0400314331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.012978553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9047727584839</t>
   </si>
   <si>
     <t xml:space="preserve">14.1031532287598</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">14.2474317550659</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1572561264038</t>
+    <t xml:space="preserve">14.1572570800781</t>
   </si>
   <si>
     <t xml:space="preserve">14.3646564483643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4187593460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.517951965332</t>
+    <t xml:space="preserve">14.4187602996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5179510116577</t>
   </si>
   <si>
     <t xml:space="preserve">14.6081266403198</t>
@@ -422,49 +422,49 @@
     <t xml:space="preserve">14.6622295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3917093276978</t>
+    <t xml:space="preserve">14.3917074203491</t>
   </si>
   <si>
     <t xml:space="preserve">14.3105525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3015336990356</t>
+    <t xml:space="preserve">14.3015356063843</t>
   </si>
   <si>
     <t xml:space="preserve">14.5450029373169</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6441946029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7343702316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7163324356079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6351766586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6261577606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.689284324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8245420455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8065071105957</t>
+    <t xml:space="preserve">14.6441955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7343692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7163333892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6351776123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6261596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.689281463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8245439529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.80650806427</t>
   </si>
   <si>
     <t xml:space="preserve">14.7433862686157</t>
   </si>
   <si>
-    <t xml:space="preserve">14.581072807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.698296546936</t>
+    <t xml:space="preserve">14.5810737609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6982984542847</t>
   </si>
   <si>
     <t xml:space="preserve">14.5089340209961</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">14.6712474822998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6532135009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.923731803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0499753952026</t>
+    <t xml:space="preserve">14.6532125473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9237308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0499773025513</t>
   </si>
   <si>
     <t xml:space="preserve">15.2122888565063</t>
@@ -488,34 +488,34 @@
     <t xml:space="preserve">15.3746004104614</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5549488067627</t>
+    <t xml:space="preserve">15.554949760437</t>
   </si>
   <si>
     <t xml:space="preserve">15.9246587753296</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7803821563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8705558776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344879150391</t>
+    <t xml:space="preserve">15.7803831100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8705549240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344869613647</t>
   </si>
   <si>
     <t xml:space="preserve">15.7082433700562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9517135620117</t>
+    <t xml:space="preserve">15.9517107009888</t>
   </si>
   <si>
     <t xml:space="preserve">16.7452392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8714809417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0879001617432</t>
+    <t xml:space="preserve">16.8714847564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0879020690918</t>
   </si>
   <si>
     <t xml:space="preserve">17.1510219573975</t>
@@ -524,70 +524,70 @@
     <t xml:space="preserve">17.2231597900391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9796924591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9075508117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3043174743652</t>
+    <t xml:space="preserve">16.9796943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9075527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3043155670166</t>
   </si>
   <si>
     <t xml:space="preserve">17.0337944030762</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2772655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4756450653076</t>
+    <t xml:space="preserve">17.2772617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4756469726562</t>
   </si>
   <si>
     <t xml:space="preserve">17.3223514556885</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1690559387207</t>
+    <t xml:space="preserve">17.1690578460693</t>
   </si>
   <si>
     <t xml:space="preserve">17.583854675293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5748348236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5658187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2411956787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1870918273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8534488677979</t>
+    <t xml:space="preserve">17.5748386383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5658168792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2411975860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1870899200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8534469604492</t>
   </si>
   <si>
     <t xml:space="preserve">16.8444290161133</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9526386260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7272052764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6911354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8624668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0428142547607</t>
+    <t xml:space="preserve">16.9526405334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7272071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6911334991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8624687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0428104400635</t>
   </si>
   <si>
     <t xml:space="preserve">16.8173770904541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9977245330811</t>
+    <t xml:space="preserve">16.9977226257324</t>
   </si>
   <si>
     <t xml:space="preserve">16.7722930908203</t>
@@ -599,13 +599,13 @@
     <t xml:space="preserve">17.1961078643799</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3584232330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6199264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7642002105713</t>
+    <t xml:space="preserve">17.358419418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6199245452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7642021179199</t>
   </si>
   <si>
     <t xml:space="preserve">18.0076675415039</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">17.9445476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9535655975342</t>
+    <t xml:space="preserve">17.9535636901855</t>
   </si>
   <si>
     <t xml:space="preserve">17.8092880249023</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">18.2601566314697</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7561111450195</t>
+    <t xml:space="preserve">18.7561092376709</t>
   </si>
   <si>
     <t xml:space="preserve">18.846284866333</t>
@@ -635,19 +635,19 @@
     <t xml:space="preserve">18.9364585876465</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6208515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2971534729004</t>
+    <t xml:space="preserve">18.620849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.297155380249</t>
   </si>
   <si>
     <t xml:space="preserve">19.3602733612061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3512554168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6668643951416</t>
+    <t xml:space="preserve">19.3512573242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6668663024902</t>
   </si>
   <si>
     <t xml:space="preserve">19.648832321167</t>
@@ -659,25 +659,25 @@
     <t xml:space="preserve">19.252067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1709117889404</t>
+    <t xml:space="preserve">19.1709079742432</t>
   </si>
   <si>
     <t xml:space="preserve">19.134838104248</t>
   </si>
   <si>
-    <t xml:space="preserve">19.197961807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9544925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9094066619873</t>
+    <t xml:space="preserve">19.1979637145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9544944763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9094047546387</t>
   </si>
   <si>
     <t xml:space="preserve">19.0897541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5757656097412</t>
+    <t xml:space="preserve">18.5757637023926</t>
   </si>
   <si>
     <t xml:space="preserve">18.1970367431641</t>
@@ -686,43 +686,43 @@
     <t xml:space="preserve">18.5306777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8372669219971</t>
+    <t xml:space="preserve">18.8372650146484</t>
   </si>
   <si>
     <t xml:space="preserve">19.4594650268555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3873271942139</t>
+    <t xml:space="preserve">19.3873291015625</t>
   </si>
   <si>
     <t xml:space="preserve">20.0185432434082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3612041473389</t>
+    <t xml:space="preserve">20.3612022399902</t>
   </si>
   <si>
     <t xml:space="preserve">20.8301029205322</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2809734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8751907348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9292945861816</t>
+    <t xml:space="preserve">21.2809715270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8751888275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.929292678833</t>
   </si>
   <si>
     <t xml:space="preserve">21.1006259918213</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0104484558105</t>
+    <t xml:space="preserve">21.0104503631592</t>
   </si>
   <si>
     <t xml:space="preserve">20.5686016082764</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7218971252441</t>
+    <t xml:space="preserve">20.7218952178955</t>
   </si>
   <si>
     <t xml:space="preserve">20.6046695709229</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">20.1898727416992</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3792381286621</t>
+    <t xml:space="preserve">20.3792362213135</t>
   </si>
   <si>
     <t xml:space="preserve">20.6497573852539</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">21.3711471557617</t>
   </si>
   <si>
-    <t xml:space="preserve">21.380163192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0925369262695</t>
+    <t xml:space="preserve">21.3801612854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0925350189209</t>
   </si>
   <si>
     <t xml:space="preserve">22.6245594024658</t>
@@ -755,70 +755,70 @@
     <t xml:space="preserve">22.7147331237793</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8049087524414</t>
+    <t xml:space="preserve">22.8049068450928</t>
   </si>
   <si>
     <t xml:space="preserve">23.5984363555908</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0763549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0583209991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7156600952148</t>
+    <t xml:space="preserve">24.0763530731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0583190917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7156581878662</t>
   </si>
   <si>
     <t xml:space="preserve">23.9320774078369</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8599376678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8058338165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5082607269287</t>
+    <t xml:space="preserve">23.859935760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.805835723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5082626342773</t>
   </si>
   <si>
     <t xml:space="preserve">22.994270324707</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4802837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5434055328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.705717086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4532299041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4622459411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0023612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1827087402344</t>
+    <t xml:space="preserve">22.480281829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5434017181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7057132720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4532279968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4622497558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0023593902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1827125549316</t>
   </si>
   <si>
     <t xml:space="preserve">22.7237529754639</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3630523681641</t>
+    <t xml:space="preserve">22.3630542755127</t>
   </si>
   <si>
     <t xml:space="preserve">22.2097606658936</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4883708953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9212055206299</t>
+    <t xml:space="preserve">21.4883728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9212036132812</t>
   </si>
   <si>
     <t xml:space="preserve">21.8761196136475</t>
@@ -827,28 +827,28 @@
     <t xml:space="preserve">21.7047882080078</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9392395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.074499130249</t>
+    <t xml:space="preserve">21.9392375946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0745029449463</t>
   </si>
   <si>
     <t xml:space="preserve">22.299934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8139247894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3179702758789</t>
+    <t xml:space="preserve">22.8139228820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3179664611816</t>
   </si>
   <si>
     <t xml:space="preserve">22.1917285919189</t>
   </si>
   <si>
-    <t xml:space="preserve">22.354040145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5253658294678</t>
+    <t xml:space="preserve">22.3540363311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5253677368164</t>
   </si>
   <si>
     <t xml:space="preserve">22.6065254211426</t>
@@ -857,37 +857,37 @@
     <t xml:space="preserve">22.6335773468018</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2458305358887</t>
+    <t xml:space="preserve">22.24582862854</t>
   </si>
   <si>
     <t xml:space="preserve">22.2277965545654</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1286067962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.083517074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.200740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1376209259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1466388702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5965824127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.326057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5605087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0294151306152</t>
+    <t xml:space="preserve">22.128604888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0835189819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2007465362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1376190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1466369628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5965805053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3260593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.560510635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0294132232666</t>
   </si>
   <si>
     <t xml:space="preserve">21.6867523193359</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">22.2368144989014</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3720741271973</t>
+    <t xml:space="preserve">22.3720703125</t>
   </si>
   <si>
     <t xml:space="preserve">22.3991260528564</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6155433654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6606292724609</t>
+    <t xml:space="preserve">22.6155414581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6606273651123</t>
   </si>
   <si>
     <t xml:space="preserve">23.0123062133789</t>
@@ -917,34 +917,34 @@
     <t xml:space="preserve">23.2704563140869</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1739864349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7087230682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7732620239258</t>
+    <t xml:space="preserve">24.1739826202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7087268829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.773265838623</t>
   </si>
   <si>
     <t xml:space="preserve">25.2434692382812</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8150844573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7966461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6860084533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6675720214844</t>
+    <t xml:space="preserve">25.8150882720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7966480255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6860103607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.667573928833</t>
   </si>
   <si>
     <t xml:space="preserve">26.0087013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8888454437256</t>
+    <t xml:space="preserve">25.888843536377</t>
   </si>
   <si>
     <t xml:space="preserve">25.9810409545898</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">26.0916748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">25.907283782959</t>
+    <t xml:space="preserve">25.9072856903076</t>
   </si>
   <si>
     <t xml:space="preserve">25.8058681488037</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">25.0775146484375</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4001998901367</t>
+    <t xml:space="preserve">25.4002017974854</t>
   </si>
   <si>
     <t xml:space="preserve">25.261905670166</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">24.8009223937988</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4186401367188</t>
+    <t xml:space="preserve">25.4186420440674</t>
   </si>
   <si>
     <t xml:space="preserve">24.6441879272461</t>
@@ -992,16 +992,16 @@
     <t xml:space="preserve">24.8562412261963</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9576568603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8931198120117</t>
+    <t xml:space="preserve">24.9576549530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8931179046631</t>
   </si>
   <si>
     <t xml:space="preserve">23.1874809265137</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9754276275635</t>
+    <t xml:space="preserve">22.9754257202148</t>
   </si>
   <si>
     <t xml:space="preserve">23.1229419708252</t>
@@ -1016,22 +1016,22 @@
     <t xml:space="preserve">23.0123043060303</t>
   </si>
   <si>
-    <t xml:space="preserve">22.781810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.671178817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4960060119629</t>
+    <t xml:space="preserve">22.7818145751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6711769104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4960041046143</t>
   </si>
   <si>
     <t xml:space="preserve">22.7264957427979</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5052242279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3208312988281</t>
+    <t xml:space="preserve">22.5052223205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3208293914795</t>
   </si>
   <si>
     <t xml:space="preserve">22.5882015228271</t>
@@ -1040,19 +1040,19 @@
     <t xml:space="preserve">23.1137218475342</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9108905792236</t>
+    <t xml:space="preserve">22.9108867645264</t>
   </si>
   <si>
     <t xml:space="preserve">23.3995304107666</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7775421142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6208038330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1413822174072</t>
+    <t xml:space="preserve">23.7775382995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6208076477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1413841247559</t>
   </si>
   <si>
     <t xml:space="preserve">22.9846477508545</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">22.8740100860596</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7357158660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6896190643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3257732391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7406578063965</t>
+    <t xml:space="preserve">22.7357120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6896152496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.325777053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7406597137451</t>
   </si>
   <si>
     <t xml:space="preserve">23.9803733825684</t>
@@ -1079,28 +1079,28 @@
     <t xml:space="preserve">23.9711513519287</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0633525848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2477397918701</t>
+    <t xml:space="preserve">24.063346862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2477416992188</t>
   </si>
   <si>
     <t xml:space="preserve">24.3860378265381</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1555442810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6165313720703</t>
+    <t xml:space="preserve">24.1555480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6165294647217</t>
   </si>
   <si>
     <t xml:space="preserve">25.8611831665039</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6306915283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2158107757568</t>
+    <t xml:space="preserve">25.6306934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2158069610596</t>
   </si>
   <si>
     <t xml:space="preserve">25.1697063446045</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">25.4463005065918</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5384960174561</t>
+    <t xml:space="preserve">25.5384979248047</t>
   </si>
   <si>
     <t xml:space="preserve">25.1236114501953</t>
@@ -1127,37 +1127,37 @@
     <t xml:space="preserve">24.0172481536865</t>
   </si>
   <si>
-    <t xml:space="preserve">24.109447479248</t>
+    <t xml:space="preserve">24.1094493865967</t>
   </si>
   <si>
     <t xml:space="preserve">24.3399391174316</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2016429901123</t>
+    <t xml:space="preserve">24.2016448974609</t>
   </si>
   <si>
     <t xml:space="preserve">24.2938423156738</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7548236846924</t>
+    <t xml:space="preserve">24.754825592041</t>
   </si>
   <si>
     <t xml:space="preserve">24.6626281738281</t>
   </si>
   <si>
-    <t xml:space="preserve">24.985315322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4924011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7228927612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5704326629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5845947265625</t>
+    <t xml:space="preserve">24.9853172302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4923973083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7228908538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5704288482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5845966339111</t>
   </si>
   <si>
     <t xml:space="preserve">25.9994812011719</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">26.4143657684326</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5668239593506</t>
+    <t xml:space="preserve">27.5668258666992</t>
   </si>
   <si>
     <t xml:space="preserve">27.7512187957764</t>
@@ -1178,10 +1178,10 @@
     <t xml:space="preserve">27.5207271575928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7370548248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5065631866455</t>
+    <t xml:space="preserve">26.7370567321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5065612792969</t>
   </si>
   <si>
     <t xml:space="preserve">25.0314159393311</t>
@@ -1190,19 +1190,19 @@
     <t xml:space="preserve">24.5243339538574</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3682670593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5987606048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4604625701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2299747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3221702575684</t>
+    <t xml:space="preserve">26.3682689666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5987567901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4604644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2299728393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3221664428711</t>
   </si>
   <si>
     <t xml:space="preserve">27.1980381011963</t>
@@ -1214,19 +1214,19 @@
     <t xml:space="preserve">27.2902355194092</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3824348449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4746265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5526599884033</t>
+    <t xml:space="preserve">27.3824310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4746246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.552661895752</t>
   </si>
   <si>
     <t xml:space="preserve">26.8292503356934</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1058406829834</t>
+    <t xml:space="preserve">27.105842590332</t>
   </si>
   <si>
     <t xml:space="preserve">26.8753490447998</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">28.7653827667236</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5809898376465</t>
+    <t xml:space="preserve">28.5809879302979</t>
   </si>
   <si>
     <t xml:space="preserve">27.9356136322021</t>
@@ -1250,28 +1250,28 @@
     <t xml:space="preserve">28.1661033630371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7192821502686</t>
+    <t xml:space="preserve">28.7192859649658</t>
   </si>
   <si>
     <t xml:space="preserve">28.1200046539307</t>
   </si>
   <si>
-    <t xml:space="preserve">27.059741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9675445556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1519432067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6909561157227</t>
+    <t xml:space="preserve">27.0597438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9675464630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1519412994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6909580230713</t>
   </si>
   <si>
     <t xml:space="preserve">26.7831535339355</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0455799102783</t>
+    <t xml:space="preserve">26.0455780029297</t>
   </si>
   <si>
     <t xml:space="preserve">27.6590213775635</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">26.9214496612549</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1828784942627</t>
+    <t xml:space="preserve">26.1828804016113</t>
   </si>
   <si>
     <t xml:space="preserve">26.0886974334717</t>
@@ -1289,16 +1289,16 @@
     <t xml:space="preserve">26.4654312133789</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2299728393555</t>
+    <t xml:space="preserve">26.2299709320068</t>
   </si>
   <si>
     <t xml:space="preserve">25.8061466217041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7119636535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1468677520752</t>
+    <t xml:space="preserve">25.7119655609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1468658447266</t>
   </si>
   <si>
     <t xml:space="preserve">25.3352336883545</t>
@@ -1307,19 +1307,19 @@
     <t xml:space="preserve">24.9114112854004</t>
   </si>
   <si>
-    <t xml:space="preserve">24.487585067749</t>
+    <t xml:space="preserve">24.4875888824463</t>
   </si>
   <si>
     <t xml:space="preserve">24.3934020996094</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9224891662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2632064819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0277481079102</t>
+    <t xml:space="preserve">23.9224853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2632083892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0277500152588</t>
   </si>
   <si>
     <t xml:space="preserve">23.0748405456543</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">22.7451992034912</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6039237976074</t>
+    <t xml:space="preserve">22.6039257049561</t>
   </si>
   <si>
     <t xml:space="preserve">22.5097427368164</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">22.4155578613281</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1801013946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0388259887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8504600524902</t>
+    <t xml:space="preserve">22.180103302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0388298034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8504619598389</t>
   </si>
   <si>
     <t xml:space="preserve">22.4626522064209</t>
@@ -1364,64 +1364,64 @@
     <t xml:space="preserve">23.498664855957</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5568351745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1330089569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6620979309082</t>
+    <t xml:space="preserve">22.5568332672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1330070495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6620960235596</t>
   </si>
   <si>
     <t xml:space="preserve">21.1911811828613</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0028114318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0969944000244</t>
+    <t xml:space="preserve">21.0028133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0969982147217</t>
   </si>
   <si>
     <t xml:space="preserve">20.8615379333496</t>
   </si>
   <si>
-    <t xml:space="preserve">21.379545211792</t>
+    <t xml:space="preserve">21.3795471191406</t>
   </si>
   <si>
     <t xml:space="preserve">21.4737281799316</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2742862701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7562808990479</t>
+    <t xml:space="preserve">22.2742824554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7562770843506</t>
   </si>
   <si>
     <t xml:space="preserve">21.9446430206299</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5679092407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5208225250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3324527740479</t>
+    <t xml:space="preserve">21.5679130554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5208206176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3324546813965</t>
   </si>
   <si>
     <t xml:space="preserve">21.2382717132568</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8393821716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7922916412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5457534790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6399383544922</t>
+    <t xml:space="preserve">22.8393840789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.792293548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5457553863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6399402618408</t>
   </si>
   <si>
     <t xml:space="preserve">23.7341213226318</t>
@@ -1430,58 +1430,58 @@
     <t xml:space="preserve">23.6870307922363</t>
   </si>
   <si>
-    <t xml:space="preserve">23.781213760376</t>
+    <t xml:space="preserve">23.7812118530273</t>
   </si>
   <si>
     <t xml:space="preserve">24.0166721343994</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2992172241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1579437255859</t>
+    <t xml:space="preserve">24.2992191314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1579456329346</t>
   </si>
   <si>
     <t xml:space="preserve">24.2521266937256</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7230434417725</t>
+    <t xml:space="preserve">24.7230415344238</t>
   </si>
   <si>
     <t xml:space="preserve">24.6288623809814</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6759510040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5817718505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7701320648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9584999084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9003295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7590579986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9474201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2770652770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9363441467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9834365844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8421611785889</t>
+    <t xml:space="preserve">24.675952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.58176612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.770133972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9585018157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9003314971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7590560913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9474220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.277063369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9363479614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.983434677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8421592712402</t>
   </si>
   <si>
     <t xml:space="preserve">26.7479782104492</t>
@@ -1490,10 +1490,10 @@
     <t xml:space="preserve">27.2659854888916</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4543495178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5014419555664</t>
+    <t xml:space="preserve">27.4543514251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.501443862915</t>
   </si>
   <si>
     <t xml:space="preserve">27.3130779266357</t>
@@ -1502,37 +1502,37 @@
     <t xml:space="preserve">27.0776195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7008876800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6537914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6067047119141</t>
+    <t xml:space="preserve">26.7008857727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6537952423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6067066192627</t>
   </si>
   <si>
     <t xml:space="preserve">25.994514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1357879638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0416069030762</t>
+    <t xml:space="preserve">26.1357898712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0416049957275</t>
   </si>
   <si>
     <t xml:space="preserve">25.6177825927734</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4294166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0055885314941</t>
+    <t xml:space="preserve">25.4294147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0055904388428</t>
   </si>
   <si>
     <t xml:space="preserve">25.0997753143311</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8643188476562</t>
+    <t xml:space="preserve">24.8643169403076</t>
   </si>
   <si>
     <t xml:space="preserve">24.4404945373535</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">25.5235996246338</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3712463378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3241558074951</t>
+    <t xml:space="preserve">26.371244430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3241577148438</t>
   </si>
   <si>
     <t xml:space="preserve">26.7950706481934</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">27.0305271148682</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1718044281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5485324859619</t>
+    <t xml:space="preserve">27.171802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5485343933105</t>
   </si>
   <si>
     <t xml:space="preserve">27.6898078918457</t>
@@ -1571,10 +1571,10 @@
     <t xml:space="preserve">28.3961791992188</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7258224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9141864776611</t>
+    <t xml:space="preserve">28.7258205413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9141883850098</t>
   </si>
   <si>
     <t xml:space="preserve">29.9502010345459</t>
@@ -1583,25 +1583,25 @@
     <t xml:space="preserve">29.7618350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3269309997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3740272521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5042190551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6925888061523</t>
+    <t xml:space="preserve">30.3269348144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.504222869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6925868988037</t>
   </si>
   <si>
     <t xml:space="preserve">32.4460525512695</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4931373596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4820671081543</t>
+    <t xml:space="preserve">32.4931449890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4820594787598</t>
   </si>
   <si>
     <t xml:space="preserve">33.6704292297363</t>
@@ -1610,10 +1610,10 @@
     <t xml:space="preserve">33.293701171875</t>
   </si>
   <si>
-    <t xml:space="preserve">33.576244354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9058876037598</t>
+    <t xml:space="preserve">33.5762519836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.905891418457</t>
   </si>
   <si>
     <t xml:space="preserve">33.2466049194336</t>
@@ -1625,100 +1625,100 @@
     <t xml:space="preserve">33.1524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">33.058235168457</t>
+    <t xml:space="preserve">33.0582389831543</t>
   </si>
   <si>
     <t xml:space="preserve">32.5873222351074</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3047790527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9280433654785</t>
+    <t xml:space="preserve">32.3047752380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9280452728271</t>
   </si>
   <si>
     <t xml:space="preserve">31.4571285247803</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3629455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8920307159424</t>
+    <t xml:space="preserve">31.362943649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8920345306396</t>
   </si>
   <si>
     <t xml:space="preserve">31.0803966522217</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0333061218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6565742492676</t>
+    <t xml:space="preserve">31.0333042144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6565761566162</t>
   </si>
   <si>
     <t xml:space="preserve">30.6094837188721</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2687644958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9862155914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4100379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8449363708496</t>
+    <t xml:space="preserve">31.2687683105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.986213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4100322723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8449382781982</t>
   </si>
   <si>
     <t xml:space="preserve">31.17458152771</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8809547424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0222244262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7396850585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.000072479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4709854125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7895469665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5901069641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7784729003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1552047729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.673210144043</t>
+    <t xml:space="preserve">31.8809509277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0222206115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7396793365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0000686645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4709815979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.78955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5901031494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7784690856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.155200958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6732063293457</t>
   </si>
   <si>
     <t xml:space="preserve">38.0846748352051</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2282104492188</t>
+    <t xml:space="preserve">38.228214263916</t>
   </si>
   <si>
     <t xml:space="preserve">37.367000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">37.797607421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.180362701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3717460632324</t>
+    <t xml:space="preserve">37.7976036071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1803703308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3717422485352</t>
   </si>
   <si>
     <t xml:space="preserve">37.9411430358887</t>
@@ -1727,16 +1727,16 @@
     <t xml:space="preserve">37.9889869689941</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8454475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3191566467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8501930236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.754508972168</t>
+    <t xml:space="preserve">37.8454551696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3191604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8501968383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7545051574707</t>
   </si>
   <si>
     <t xml:space="preserve">39.3286476135254</t>
@@ -1745,22 +1745,22 @@
     <t xml:space="preserve">39.041576385498</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8023490905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4674377441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1325187683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8980407714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7066612243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2760581970215</t>
+    <t xml:space="preserve">38.8023529052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4674415588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1325149536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8980445861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7066650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2760543823242</t>
   </si>
   <si>
     <t xml:space="preserve">38.5631256103516</t>
@@ -1775,34 +1775,34 @@
     <t xml:space="preserve">39.1372680664062</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1851119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2807998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9027862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1946029663086</t>
+    <t xml:space="preserve">39.185115814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2808036804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9027900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1946067810059</t>
   </si>
   <si>
     <t xml:space="preserve">42.1036605834961</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5342674255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6730537414551</t>
+    <t xml:space="preserve">42.5342712402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6730575561523</t>
   </si>
   <si>
     <t xml:space="preserve">40.8118476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7161521911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9122772216797</t>
+    <t xml:space="preserve">40.7161598205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9122848510742</t>
   </si>
   <si>
     <t xml:space="preserve">43.0605659484863</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">44.2566909790039</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7829856872559</t>
+    <t xml:space="preserve">44.7829895019531</t>
   </si>
   <si>
     <t xml:space="preserve">43.4433250427246</t>
@@ -1823,31 +1823,31 @@
     <t xml:space="preserve">44.0174674987793</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6347045898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9170265197754</t>
+    <t xml:space="preserve">43.6347007751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2041053771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9170303344727</t>
   </si>
   <si>
     <t xml:space="preserve">44.9265213012695</t>
   </si>
   <si>
-    <t xml:space="preserve">45.404972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2614364624023</t>
+    <t xml:space="preserve">45.4049758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2614326477051</t>
   </si>
   <si>
     <t xml:space="preserve">45.5963516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6536903381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8976593017578</t>
+    <t xml:space="preserve">47.6536865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8976631164551</t>
   </si>
   <si>
     <t xml:space="preserve">48.6105918884277</t>
@@ -1856,10 +1856,10 @@
     <t xml:space="preserve">49.1847343444824</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9933471679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7588729858398</t>
+    <t xml:space="preserve">48.993350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7588768005371</t>
   </si>
   <si>
     <t xml:space="preserve">49.2804222106934</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">49.3761138916016</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5674934387207</t>
+    <t xml:space="preserve">49.5674896240234</t>
   </si>
   <si>
     <t xml:space="preserve">50.6200866699219</t>
@@ -1892,19 +1892,19 @@
     <t xml:space="preserve">51.8640594482422</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6726760864258</t>
+    <t xml:space="preserve">51.6726722717285</t>
   </si>
   <si>
     <t xml:space="preserve">48.4192085266113</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3235206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0459442138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3856048583984</t>
+    <t xml:space="preserve">48.3235168457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0459480285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3856086730957</t>
   </si>
   <si>
     <t xml:space="preserve">50.9071578979492</t>
@@ -1913,19 +1913,19 @@
     <t xml:space="preserve">49.8545608520508</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4287071228027</t>
+    <t xml:space="preserve">50.4287033081055</t>
   </si>
   <si>
     <t xml:space="preserve">52.5338897705078</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0649299621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2994117736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4381980895996</t>
+    <t xml:space="preserve">54.0649337768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2994079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4381942749023</t>
   </si>
   <si>
     <t xml:space="preserve">47.3666191101074</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">43.586856842041</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7687492370605</t>
+    <t xml:space="preserve">41.7687454223633</t>
   </si>
   <si>
     <t xml:space="preserve">36.6493225097656</t>
@@ -1964,10 +1964,10 @@
     <t xml:space="preserve">29.1854915618896</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5299034118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0992965698242</t>
+    <t xml:space="preserve">31.5299015045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0992984771729</t>
   </si>
   <si>
     <t xml:space="preserve">30.3816204071045</t>
@@ -1979,19 +1979,19 @@
     <t xml:space="preserve">36.410099029541</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5010414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3096618652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5441436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.070442199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0799331665039</t>
+    <t xml:space="preserve">35.5010452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3096656799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5441360473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0704383850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0799293518066</t>
   </si>
   <si>
     <t xml:space="preserve">37.2234649658203</t>
@@ -2000,40 +2000,40 @@
     <t xml:space="preserve">37.1277694702148</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2329559326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4290885925293</t>
+    <t xml:space="preserve">39.2329521179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.429084777832</t>
   </si>
   <si>
     <t xml:space="preserve">39.998477935791</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7351417541504</t>
+    <t xml:space="preserve">44.7351379394531</t>
   </si>
   <si>
     <t xml:space="preserve">45.9791145324707</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4528198242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0700531005859</t>
+    <t xml:space="preserve">45.4528160095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0700607299805</t>
   </si>
   <si>
     <t xml:space="preserve">45.3571319580078</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1179046630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4575653076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6441955566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8786811828613</t>
+    <t xml:space="preserve">45.1179008483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4575576782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6441993713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8786773681641</t>
   </si>
   <si>
     <t xml:space="preserve">45.3092803955078</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">45.1657485961914</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2088432312012</t>
+    <t xml:space="preserve">44.2088470458984</t>
   </si>
   <si>
     <t xml:space="preserve">43.1562538146973</t>
@@ -2051,13 +2051,13 @@
     <t xml:space="preserve">43.9217758178711</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8644371032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5821113586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0222129821777</t>
+    <t xml:space="preserve">41.8644332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5821151733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0222091674805</t>
   </si>
   <si>
     <t xml:space="preserve">45.5485038757324</t>
@@ -2069,10 +2069,10 @@
     <t xml:space="preserve">47.7015342712402</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7062873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9407577514648</t>
+    <t xml:space="preserve">48.7062835693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9407539367676</t>
   </si>
   <si>
     <t xml:space="preserve">48.5149002075195</t>
@@ -2087,58 +2087,58 @@
     <t xml:space="preserve">51.768367767334</t>
   </si>
   <si>
-    <t xml:space="preserve">51.289909362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1080284118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9692420959473</t>
+    <t xml:space="preserve">51.2899169921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1080322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.96923828125</t>
   </si>
   <si>
     <t xml:space="preserve">53.490795135498</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1175231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6916656494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5002822875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3519973754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6390724182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.830451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4045906066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7442512512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9356307983398</t>
+    <t xml:space="preserve">55.1175193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6916618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5002861022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3520011901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6390686035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8304481506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4045944213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.744255065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9356346130371</t>
   </si>
   <si>
     <t xml:space="preserve">57.1270141601562</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2658004760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9787292480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3183975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6580581665039</t>
+    <t xml:space="preserve">56.2658042907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9787330627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3183937072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6580505371094</t>
   </si>
   <si>
     <t xml:space="preserve">57.2227058410645</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">56.3614959716797</t>
   </si>
   <si>
-    <t xml:space="preserve">57.9882278442383</t>
+    <t xml:space="preserve">57.988224029541</t>
   </si>
   <si>
     <t xml:space="preserve">58.849437713623</t>
@@ -2159,10 +2159,10 @@
     <t xml:space="preserve">61.3373794555664</t>
   </si>
   <si>
-    <t xml:space="preserve">63.442569732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2942810058594</t>
+    <t xml:space="preserve">63.4425659179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2942848205566</t>
   </si>
   <si>
     <t xml:space="preserve">63.3468742370605</t>
@@ -2174,28 +2174,28 @@
     <t xml:space="preserve">63.6339454650879</t>
   </si>
   <si>
-    <t xml:space="preserve">64.3037719726562</t>
+    <t xml:space="preserve">64.3037643432617</t>
   </si>
   <si>
     <t xml:space="preserve">64.5908432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">65.9305038452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6960372924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3563766479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.9830856323242</t>
+    <t xml:space="preserve">65.9305114746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6960220336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3563690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9831085205078</t>
   </si>
   <si>
     <t xml:space="preserve">67.1744766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5046463012695</t>
+    <t xml:space="preserve">66.5046539306641</t>
   </si>
   <si>
     <t xml:space="preserve">67.8443145751953</t>
@@ -2207,43 +2207,43 @@
     <t xml:space="preserve">69.1839752197266</t>
   </si>
   <si>
-    <t xml:space="preserve">71.2891616821289</t>
+    <t xml:space="preserve">71.2891464233398</t>
   </si>
   <si>
     <t xml:space="preserve">70.8107070922852</t>
   </si>
   <si>
-    <t xml:space="preserve">70.6193237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7676086425781</t>
+    <t xml:space="preserve">70.6193313598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7676010131836</t>
   </si>
   <si>
     <t xml:space="preserve">72.0546722412109</t>
   </si>
   <si>
-    <t xml:space="preserve">71.002082824707</t>
+    <t xml:space="preserve">71.0020904541016</t>
   </si>
   <si>
     <t xml:space="preserve">69.4710464477539</t>
   </si>
   <si>
-    <t xml:space="preserve">68.9925842285156</t>
+    <t xml:space="preserve">68.9925994873047</t>
   </si>
   <si>
     <t xml:space="preserve">69.9494934082031</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8012161254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.6624145507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.552116394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.7003860473633</t>
+    <t xml:space="preserve">68.8012084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.6624221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.5521087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.7003936767578</t>
   </si>
   <si>
     <t xml:space="preserve">75.8822860717773</t>
@@ -2252,40 +2252,40 @@
     <t xml:space="preserve">74.734001159668</t>
   </si>
   <si>
-    <t xml:space="preserve">73.8727874755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8296966552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.8917770385742</t>
+    <t xml:space="preserve">73.8727798461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8296890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.8917694091797</t>
   </si>
   <si>
     <t xml:space="preserve">78.2745361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7960815429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.4228210449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.7624740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0064468383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5280075073242</t>
+    <t xml:space="preserve">77.7960891723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.4228286743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.7624816894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0064544677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.5279998779297</t>
   </si>
   <si>
     <t xml:space="preserve">81.910758972168</t>
   </si>
   <si>
-    <t xml:space="preserve">82.3892059326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4323043823242</t>
+    <t xml:space="preserve">82.3892135620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4323196411133</t>
   </si>
   <si>
     <t xml:space="preserve">81.1452407836914</t>
@@ -2294,46 +2294,46 @@
     <t xml:space="preserve">80.4754028320312</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7193832397461</t>
+    <t xml:space="preserve">81.7193756103516</t>
   </si>
   <si>
     <t xml:space="preserve">81.815071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">83.3461074829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.9538497924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7719802856445</t>
+    <t xml:space="preserve">83.3461151123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.953857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.77197265625</t>
   </si>
   <si>
     <t xml:space="preserve">82.2935180664062</t>
   </si>
   <si>
-    <t xml:space="preserve">77.0305633544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3271331787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.728874206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.1021423339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.7434921264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.5185165405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8055725097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4848937988281</t>
+    <t xml:space="preserve">77.0305709838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3271255493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7288665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.1021499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.7434844970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.5185012817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8055801391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4848861694336</t>
   </si>
   <si>
     <t xml:space="preserve">80.3797225952148</t>
@@ -2342,49 +2342,49 @@
     <t xml:space="preserve">78.6572952270508</t>
   </si>
   <si>
-    <t xml:space="preserve">78.4659118652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6857757568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.355598449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0590438842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.9297561645508</t>
+    <t xml:space="preserve">78.4659042358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6857681274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3556060791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0590362548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.9297409057617</t>
   </si>
   <si>
     <t xml:space="preserve">87.173713684082</t>
   </si>
   <si>
-    <t xml:space="preserve">87.2694091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3220062255859</t>
+    <t xml:space="preserve">87.269401550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3219985961914</t>
   </si>
   <si>
     <t xml:space="preserve">86.7909545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">90.9056396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3840866088867</t>
+    <t xml:space="preserve">90.905632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3840942382812</t>
   </si>
   <si>
     <t xml:space="preserve">93.1065139770508</t>
   </si>
   <si>
-    <t xml:space="preserve">95.8815155029297</t>
+    <t xml:space="preserve">95.8815078735352</t>
   </si>
   <si>
     <t xml:space="preserve">97.2211837768555</t>
   </si>
   <si>
-    <t xml:space="preserve">100.474647521973</t>
+    <t xml:space="preserve">100.474639892578</t>
   </si>
   <si>
     <t xml:space="preserve">101.622924804688</t>
@@ -2393,13 +2393,13 @@
     <t xml:space="preserve">101.240173339844</t>
   </si>
   <si>
-    <t xml:space="preserve">97.9866943359375</t>
+    <t xml:space="preserve">97.986701965332</t>
   </si>
   <si>
     <t xml:space="preserve">98.5608444213867</t>
   </si>
   <si>
-    <t xml:space="preserve">99.9005126953125</t>
+    <t xml:space="preserve">99.9004974365234</t>
   </si>
   <si>
     <t xml:space="preserve">96.2642822265625</t>
@@ -2411,103 +2411,103 @@
     <t xml:space="preserve">94.8289337158203</t>
   </si>
   <si>
-    <t xml:space="preserve">95.3073806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2547912597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.446159362793</t>
+    <t xml:space="preserve">95.307373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2547836303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4461669921875</t>
   </si>
   <si>
     <t xml:space="preserve">97.0298004150391</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5418548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1591033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8720245361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0634155273438</t>
+    <t xml:space="preserve">94.541862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1590957641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8720321655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0634078979492</t>
   </si>
   <si>
     <t xml:space="preserve">93.3935775756836</t>
   </si>
   <si>
-    <t xml:space="preserve">93.6806564331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9151306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.2978820800781</t>
+    <t xml:space="preserve">93.6806411743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9151153564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.2978897094727</t>
   </si>
   <si>
     <t xml:space="preserve">92.723747253418</t>
   </si>
   <si>
-    <t xml:space="preserve">94.3504867553711</t>
+    <t xml:space="preserve">94.3504791259766</t>
   </si>
   <si>
     <t xml:space="preserve">97.6039505004883</t>
   </si>
   <si>
-    <t xml:space="preserve">101.431541442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.876396179199</t>
+    <t xml:space="preserve">101.431549072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.876388549805</t>
   </si>
   <si>
     <t xml:space="preserve">104.493629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">106.598823547363</t>
+    <t xml:space="preserve">106.598815917969</t>
   </si>
   <si>
     <t xml:space="preserve">107.364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">109.660903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.235046386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.64192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.21605682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.938484191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.555725097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.469520568848</t>
+    <t xml:space="preserve">109.66089630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.235038757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.641914367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.216064453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.9384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.555732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.469528198242</t>
   </si>
   <si>
     <t xml:space="preserve">107.747100830078</t>
   </si>
   <si>
-    <t xml:space="preserve">108.703994750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.197082519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5177459716797</t>
+    <t xml:space="preserve">108.704002380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.197074890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5177536010742</t>
   </si>
   <si>
     <t xml:space="preserve">99.7091217041016</t>
   </si>
   <si>
-    <t xml:space="preserve">103.345352172852</t>
+    <t xml:space="preserve">103.345344543457</t>
   </si>
   <si>
     <t xml:space="preserve">103.536735534668</t>
@@ -2522,10 +2522,10 @@
     <t xml:space="preserve">108.512619018555</t>
   </si>
   <si>
-    <t xml:space="preserve">105.833297729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.048789978027</t>
+    <t xml:space="preserve">105.833290100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.048782348633</t>
   </si>
   <si>
     <t xml:space="preserve">102.388450622559</t>
@@ -2546,13 +2546,13 @@
     <t xml:space="preserve">103.919486999512</t>
   </si>
   <si>
-    <t xml:space="preserve">106.407432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.086761474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.809181213379</t>
+    <t xml:space="preserve">106.407440185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.086753845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.809188842773</t>
   </si>
   <si>
     <t xml:space="preserve">113.679893493652</t>
@@ -2561,25 +2561,25 @@
     <t xml:space="preserve">110.043663024902</t>
   </si>
   <si>
-    <t xml:space="preserve">107.172943115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.000564575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.914360046387</t>
+    <t xml:space="preserve">107.172958374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.00057220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.914367675781</t>
   </si>
   <si>
     <t xml:space="preserve">109.852279663086</t>
   </si>
   <si>
-    <t xml:space="preserve">110.426429748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.383331298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.340232849121</t>
+    <t xml:space="preserve">110.426422119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.383323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.340225219727</t>
   </si>
   <si>
     <t xml:space="preserve">114.445411682129</t>
@@ -2591,13 +2591,13 @@
     <t xml:space="preserve">112.722991943359</t>
   </si>
   <si>
-    <t xml:space="preserve">115.019554138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.593688964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.210922241211</t>
+    <t xml:space="preserve">115.019546508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.593696594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.2109375</t>
   </si>
   <si>
     <t xml:space="preserve">116.741966247559</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">115.78507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">116.550582885742</t>
+    <t xml:space="preserve">116.550590515137</t>
   </si>
   <si>
     <t xml:space="preserve">119.804054260254</t>
   </si>
   <si>
-    <t xml:space="preserve">120.186813354492</t>
+    <t xml:space="preserve">120.186820983887</t>
   </si>
   <si>
     <t xml:space="preserve">122.100616455078</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">122.866134643555</t>
   </si>
   <si>
-    <t xml:space="preserve">123.631660461426</t>
+    <t xml:space="preserve">123.631652832031</t>
   </si>
   <si>
     <t xml:space="preserve">131.478256225586</t>
@@ -2636,16 +2636,16 @@
     <t xml:space="preserve">127.459259033203</t>
   </si>
   <si>
-    <t xml:space="preserve">128.990325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.052398681641</t>
+    <t xml:space="preserve">128.990310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.05241394043</t>
   </si>
   <si>
     <t xml:space="preserve">134.157577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">133.774826049805</t>
+    <t xml:space="preserve">133.774795532227</t>
   </si>
   <si>
     <t xml:space="preserve">132.626525878906</t>
@@ -2654,31 +2654,31 @@
     <t xml:space="preserve">132.435150146484</t>
   </si>
   <si>
-    <t xml:space="preserve">134.923095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.6455078125</t>
+    <t xml:space="preserve">134.923080444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.645523071289</t>
   </si>
   <si>
     <t xml:space="preserve">137.411056518555</t>
   </si>
   <si>
-    <t xml:space="preserve">135.305847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.86100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.731735229492</t>
+    <t xml:space="preserve">135.305862426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.861022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.731719970703</t>
   </si>
   <si>
     <t xml:space="preserve">136.262756347656</t>
   </si>
   <si>
-    <t xml:space="preserve">137.793792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.176574707031</t>
+    <t xml:space="preserve">137.793807983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.176544189453</t>
   </si>
   <si>
     <t xml:space="preserve">137.028274536133</t>
@@ -2690,22 +2690,22 @@
     <t xml:space="preserve">139.898986816406</t>
   </si>
   <si>
-    <t xml:space="preserve">136.454132080078</t>
+    <t xml:space="preserve">136.454162597656</t>
   </si>
   <si>
     <t xml:space="preserve">138.750701904297</t>
   </si>
   <si>
-    <t xml:space="preserve">139.324829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.985168457031</t>
+    <t xml:space="preserve">139.324844360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.985198974609</t>
   </si>
   <si>
     <t xml:space="preserve">135.497253417969</t>
   </si>
   <si>
-    <t xml:space="preserve">144.492111206055</t>
+    <t xml:space="preserve">144.492126464844</t>
   </si>
   <si>
     <t xml:space="preserve">144.874877929688</t>
@@ -2717,10 +2717,10 @@
     <t xml:space="preserve">142.195556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">143.726593017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.91796875</t>
+    <t xml:space="preserve">143.726577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.917984008789</t>
   </si>
   <si>
     <t xml:space="preserve">144.683486938477</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">145.25764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">147.936950683594</t>
+    <t xml:space="preserve">147.936981201172</t>
   </si>
   <si>
     <t xml:space="preserve">145.640396118164</t>
@@ -2738,58 +2738,58 @@
     <t xml:space="preserve">146.788681030273</t>
   </si>
   <si>
-    <t xml:space="preserve">149.276626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.999053955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.424896240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.48698425293</t>
+    <t xml:space="preserve">149.276641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.9990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.424911499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.486968994141</t>
   </si>
   <si>
     <t xml:space="preserve">152.33869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">155.400772094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.1904296875</t>
+    <t xml:space="preserve">155.400787353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.190414428711</t>
   </si>
   <si>
     <t xml:space="preserve">157.888732910156</t>
   </si>
   <si>
-    <t xml:space="preserve">159.037033081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.654266357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.611145019531</t>
+    <t xml:space="preserve">159.037002563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.654251098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.61116027832</t>
   </si>
   <si>
     <t xml:space="preserve">161.333587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">161.524948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.438766479492</t>
+    <t xml:space="preserve">161.524963378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.438751220703</t>
   </si>
   <si>
     <t xml:space="preserve">163.821517944336</t>
   </si>
   <si>
-    <t xml:space="preserve">168.606018066406</t>
+    <t xml:space="preserve">168.606002807617</t>
   </si>
   <si>
     <t xml:space="preserve">173.773300170898</t>
   </si>
   <si>
-    <t xml:space="preserve">170.32844543457</t>
+    <t xml:space="preserve">170.328460693359</t>
   </si>
   <si>
     <t xml:space="preserve">165.161209106445</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">168.03190612793</t>
   </si>
   <si>
-    <t xml:space="preserve">165.352569580078</t>
+    <t xml:space="preserve">165.352584838867</t>
   </si>
   <si>
     <t xml:space="preserve">160.75944519043</t>
@@ -2807,43 +2807,43 @@
     <t xml:space="preserve">162.099090576172</t>
   </si>
   <si>
-    <t xml:space="preserve">171.668106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.074996948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.930511474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.353576660156</t>
+    <t xml:space="preserve">171.668121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.074981689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.93049621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.353561401367</t>
   </si>
   <si>
     <t xml:space="preserve">160.58430480957</t>
   </si>
   <si>
-    <t xml:space="preserve">159.045761108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.122375488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.583602905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.314453125</t>
+    <t xml:space="preserve">159.045776367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.12239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.583618164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.314468383789</t>
   </si>
   <si>
     <t xml:space="preserve">150.391525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">150.199203491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.083740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.737747192383</t>
+    <t xml:space="preserve">150.19921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.083724975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.737731933594</t>
   </si>
   <si>
     <t xml:space="preserve">149.622268676758</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">156.545654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">155.968688964844</t>
+    <t xml:space="preserve">155.968704223633</t>
   </si>
   <si>
     <t xml:space="preserve">154.43017578125</t>
@@ -2864,16 +2864,16 @@
     <t xml:space="preserve">160.776611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">166.353805541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.200134277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.469268798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.430648803711</t>
+    <t xml:space="preserve">166.353790283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.200119018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.469284057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.430633544922</t>
   </si>
   <si>
     <t xml:space="preserve">165.007598876953</t>
@@ -2882,46 +2882,46 @@
     <t xml:space="preserve">162.507461547852</t>
   </si>
   <si>
-    <t xml:space="preserve">163.469055175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.584518432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.161254882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.084442138672</t>
+    <t xml:space="preserve">163.46907043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.584533691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.161270141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.084426879883</t>
   </si>
   <si>
     <t xml:space="preserve">161.738189697266</t>
   </si>
   <si>
-    <t xml:space="preserve">168.853942871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.508178710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.585006713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.392929077148</t>
+    <t xml:space="preserve">168.853927612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.508163452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.584991455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.392913818359</t>
   </si>
   <si>
     <t xml:space="preserve">180.777526855469</t>
   </si>
   <si>
-    <t xml:space="preserve">178.469741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.815963745117</t>
+    <t xml:space="preserve">178.469757080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.815948486328</t>
   </si>
   <si>
     <t xml:space="preserve">181.739120483398</t>
   </si>
   <si>
-    <t xml:space="preserve">185.008499145508</t>
+    <t xml:space="preserve">185.008514404297</t>
   </si>
   <si>
     <t xml:space="preserve">183.085327148438</t>
@@ -2936,13 +2936,13 @@
     <t xml:space="preserve">169.046234130859</t>
   </si>
   <si>
-    <t xml:space="preserve">170.584762573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.507675170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.046447753906</t>
+    <t xml:space="preserve">170.584747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.507705688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.046463012695</t>
   </si>
   <si>
     <t xml:space="preserve">170.96940612793</t>
@@ -2957,13 +2957,13 @@
     <t xml:space="preserve">175.008041381836</t>
   </si>
   <si>
-    <t xml:space="preserve">172.700256347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.123291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.930969238281</t>
+    <t xml:space="preserve">172.700241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.123306274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.93098449707</t>
   </si>
   <si>
     <t xml:space="preserve">167.315383911133</t>
@@ -2972,10 +2972,10 @@
     <t xml:space="preserve">163.85368347168</t>
   </si>
   <si>
-    <t xml:space="preserve">166.73844909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.238327026367</t>
+    <t xml:space="preserve">166.738403320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.238311767578</t>
   </si>
   <si>
     <t xml:space="preserve">166.546112060547</t>
@@ -2987,13 +2987,13 @@
     <t xml:space="preserve">165.392211914062</t>
   </si>
   <si>
-    <t xml:space="preserve">151.160781860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.853439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.468826293945</t>
+    <t xml:space="preserve">151.160797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.853454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.468841552734</t>
   </si>
   <si>
     <t xml:space="preserve">157.314926147461</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">156.930282592773</t>
   </si>
   <si>
-    <t xml:space="preserve">156.161010742188</t>
+    <t xml:space="preserve">156.161026000977</t>
   </si>
   <si>
     <t xml:space="preserve">152.314682006836</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">145.96826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">146.929840087891</t>
+    <t xml:space="preserve">146.929824829102</t>
   </si>
   <si>
     <t xml:space="preserve">151.353103637695</t>
@@ -3023,46 +3023,46 @@
     <t xml:space="preserve">153.468597412109</t>
   </si>
   <si>
-    <t xml:space="preserve">153.276260375977</t>
+    <t xml:space="preserve">153.276245117188</t>
   </si>
   <si>
     <t xml:space="preserve">157.122604370117</t>
   </si>
   <si>
-    <t xml:space="preserve">151.930068969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.545181274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.968032836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.929351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.660217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.698394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.506088256836</t>
+    <t xml:space="preserve">151.930053710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.545196533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.968017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.92936706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.660232543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.698425292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.506103515625</t>
   </si>
   <si>
     <t xml:space="preserve">130.198287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">134.813873291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.005966186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.775238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.852066040039</t>
+    <t xml:space="preserve">134.813888549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.005981445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.77522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.852081298828</t>
   </si>
   <si>
     <t xml:space="preserve">129.621353149414</t>
@@ -3071,13 +3071,13 @@
     <t xml:space="preserve">132.890716552734</t>
   </si>
   <si>
-    <t xml:space="preserve">137.506317138672</t>
+    <t xml:space="preserve">137.506332397461</t>
   </si>
   <si>
     <t xml:space="preserve">136.160110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">138.467895507812</t>
+    <t xml:space="preserve">138.467910766602</t>
   </si>
   <si>
     <t xml:space="preserve">135.583145141602</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">118.659301757812</t>
   </si>
   <si>
-    <t xml:space="preserve">125.582695007324</t>
+    <t xml:space="preserve">125.582702636719</t>
   </si>
   <si>
     <t xml:space="preserve">125.198066711426</t>
@@ -3098,13 +3098,13 @@
     <t xml:space="preserve">137.314010620117</t>
   </si>
   <si>
-    <t xml:space="preserve">138.8525390625</t>
+    <t xml:space="preserve">138.852523803711</t>
   </si>
   <si>
     <t xml:space="preserve">142.891189575195</t>
   </si>
   <si>
-    <t xml:space="preserve">140.391067504883</t>
+    <t xml:space="preserve">140.391052246094</t>
   </si>
   <si>
     <t xml:space="preserve">145.391296386719</t>
@@ -3113,28 +3113,28 @@
     <t xml:space="preserve">145.00666809082</t>
   </si>
   <si>
-    <t xml:space="preserve">145.775939941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.814361572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.27604675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.275833129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.602722167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.698852539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.083511352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.525665283203</t>
+    <t xml:space="preserve">145.775924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.814346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.276031494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.275802612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.60270690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.698867797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.08349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.525634765625</t>
   </si>
   <si>
     <t xml:space="preserve">141.160354614258</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">143.179641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">142.314224243164</t>
+    <t xml:space="preserve">142.314239501953</t>
   </si>
   <si>
     <t xml:space="preserve">130.87141418457</t>
@@ -3170,10 +3170,10 @@
     <t xml:space="preserve">129.525177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">129.909820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.371505737305</t>
+    <t xml:space="preserve">129.90983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.371520996094</t>
   </si>
   <si>
     <t xml:space="preserve">128.275115966797</t>
@@ -3185,19 +3185,19 @@
     <t xml:space="preserve">124.236473083496</t>
   </si>
   <si>
-    <t xml:space="preserve">122.890258789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.563140869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.812744140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.562911987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.389923095703</t>
+    <t xml:space="preserve">122.890266418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.563148498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.81273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.56290435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.389915466309</t>
   </si>
   <si>
     <t xml:space="preserve">115.774551391602</t>
@@ -3206,34 +3206,34 @@
     <t xml:space="preserve">118.755462646484</t>
   </si>
   <si>
-    <t xml:space="preserve">118.082344055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.313316345215</t>
+    <t xml:space="preserve">118.08235168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.31330871582</t>
   </si>
   <si>
     <t xml:space="preserve">120.293983459473</t>
   </si>
   <si>
-    <t xml:space="preserve">120.101676940918</t>
+    <t xml:space="preserve">120.101669311523</t>
   </si>
   <si>
     <t xml:space="preserve">119.236251831055</t>
   </si>
   <si>
-    <t xml:space="preserve">120.486305236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.736137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.832290649414</t>
+    <t xml:space="preserve">120.486312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.736145019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.832298278809</t>
   </si>
   <si>
     <t xml:space="preserve">119.043937683105</t>
   </si>
   <si>
-    <t xml:space="preserve">121.736358642578</t>
+    <t xml:space="preserve">121.736366271973</t>
   </si>
   <si>
     <t xml:space="preserve">124.621116638184</t>
@@ -3242,37 +3242,37 @@
     <t xml:space="preserve">123.274894714355</t>
   </si>
   <si>
-    <t xml:space="preserve">121.544044494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.044166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.332626342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.986671447754</t>
+    <t xml:space="preserve">121.544052124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.044158935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.332633972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.986640930176</t>
   </si>
   <si>
     <t xml:space="preserve">128.659774780273</t>
   </si>
   <si>
-    <t xml:space="preserve">127.698173522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.178741455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.524490356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.889808654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.236022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.062789916992</t>
+    <t xml:space="preserve">127.698188781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.178749084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.52449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.889801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.236030578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.062797546387</t>
   </si>
   <si>
     <t xml:space="preserve">112.216690063477</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">115.197601318359</t>
   </si>
   <si>
-    <t xml:space="preserve">119.140083312988</t>
+    <t xml:space="preserve">119.140090942383</t>
   </si>
   <si>
     <t xml:space="preserve">119.909355163574</t>
@@ -3299,19 +3299,19 @@
     <t xml:space="preserve">119.428565979004</t>
   </si>
   <si>
-    <t xml:space="preserve">117.890037536621</t>
+    <t xml:space="preserve">117.890022277832</t>
   </si>
   <si>
     <t xml:space="preserve">115.293762207031</t>
   </si>
   <si>
-    <t xml:space="preserve">113.178283691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.332405090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.082588195801</t>
+    <t xml:space="preserve">113.178276062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.332412719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.082580566406</t>
   </si>
   <si>
     <t xml:space="preserve">125.390365600586</t>
@@ -3320,73 +3320,73 @@
     <t xml:space="preserve">122.986419677734</t>
   </si>
   <si>
-    <t xml:space="preserve">118.27466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.71704864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.774780273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.659530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.948226928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.73681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.679077148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.832740783691</t>
+    <t xml:space="preserve">118.274673461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.71703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.774787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.659538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.948257446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.736801147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.679061889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.83275604248</t>
   </si>
   <si>
     <t xml:space="preserve">127.794334411621</t>
   </si>
   <si>
-    <t xml:space="preserve">128.467437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.602233886719</t>
+    <t xml:space="preserve">128.46745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.602249145508</t>
   </si>
   <si>
     <t xml:space="preserve">129.044387817383</t>
   </si>
   <si>
-    <t xml:space="preserve">131.159866333008</t>
+    <t xml:space="preserve">131.159881591797</t>
   </si>
   <si>
     <t xml:space="preserve">125.967323303223</t>
   </si>
   <si>
-    <t xml:space="preserve">126.351959228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.563377380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.313552856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.371292114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.736595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.447883605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.6015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.947776794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.197845458984</t>
+    <t xml:space="preserve">126.351943969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.563369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.313545227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.371307373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.736587524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.447891235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.601554870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.947769165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.197830200195</t>
   </si>
   <si>
     <t xml:space="preserve">121.063255310059</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">115.870704650879</t>
   </si>
   <si>
-    <t xml:space="preserve">116.255340576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.312850952148</t>
+    <t xml:space="preserve">116.255348205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.312858581543</t>
   </si>
   <si>
     <t xml:space="preserve">115.582237243652</t>
@@ -5190,6 +5190,9 @@
   </si>
   <si>
     <t xml:space="preserve">80.9499969482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1999969482422</t>
   </si>
 </sst>
 </file>
@@ -70502,7 +70505,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6909837963</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>21399</v>
@@ -70523,6 +70526,32 @@
         <v>1725</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6910532407</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>22524</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>81.8000030517578</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>80.5999984741211</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>81.1999969482422</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>81.1999969482422</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1726</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1727" uniqueCount="1727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="1728">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">SES.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5321083068848</t>
+    <t xml:space="preserve">13.5321063995361</t>
   </si>
   <si>
     <t xml:space="preserve">13.2523727416992</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9464149475098</t>
+    <t xml:space="preserve">12.9464159011841</t>
   </si>
   <si>
     <t xml:space="preserve">13.1125078201294</t>
@@ -59,43 +59,43 @@
     <t xml:space="preserve">12.858998298645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0513153076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.990122795105</t>
+    <t xml:space="preserve">13.0513172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9901218414307</t>
   </si>
   <si>
     <t xml:space="preserve">12.9376726150513</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1037654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0250902175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8502550125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.238338470459</t>
+    <t xml:space="preserve">13.1037645339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.025089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8502569198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2383394241333</t>
   </si>
   <si>
     <t xml:space="preserve">12.5880069732666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7890653610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7191324234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6841659545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.605489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3257579803467</t>
+    <t xml:space="preserve">12.7890644073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7191305160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6841640472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6054916381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3257570266724</t>
   </si>
   <si>
     <t xml:space="preserve">12.0460224151611</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">12.1771488189697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1421823501587</t>
+    <t xml:space="preserve">12.1421813964844</t>
   </si>
   <si>
     <t xml:space="preserve">10.9270887374878</t>
@@ -113,19 +113,19 @@
     <t xml:space="preserve">10.9795398712158</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3641729354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4515914916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0984735488892</t>
+    <t xml:space="preserve">11.3641719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4515905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0984745025635</t>
   </si>
   <si>
     <t xml:space="preserve">12.1072149276733</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8886747360229</t>
+    <t xml:space="preserve">11.8886737823486</t>
   </si>
   <si>
     <t xml:space="preserve">11.9760885238647</t>
@@ -134,28 +134,28 @@
     <t xml:space="preserve">11.9323806762695</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0110540390015</t>
+    <t xml:space="preserve">12.0110559463501</t>
   </si>
   <si>
     <t xml:space="preserve">12.0809907913208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8012571334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334390640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8274812698364</t>
+    <t xml:space="preserve">11.8012552261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334400177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8274803161621</t>
   </si>
   <si>
     <t xml:space="preserve">12.0635061264038</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5005893707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6754236221313</t>
+    <t xml:space="preserve">12.5005912780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6754245758057</t>
   </si>
   <si>
     <t xml:space="preserve">12.7978076934814</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve">13.1212491989136</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1911821365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7540979385376</t>
+    <t xml:space="preserve">13.1911811828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7540969848633</t>
   </si>
   <si>
     <t xml:space="preserve">12.8939647674561</t>
@@ -185,22 +185,22 @@
     <t xml:space="preserve">12.9027070999146</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0600566864014</t>
+    <t xml:space="preserve">13.06005859375</t>
   </si>
   <si>
     <t xml:space="preserve">13.1999244689941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9813833236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4534320831299</t>
+    <t xml:space="preserve">12.9813823699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4534330368042</t>
   </si>
   <si>
     <t xml:space="preserve">13.7069416046143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4709157943726</t>
+    <t xml:space="preserve">13.4709148406982</t>
   </si>
   <si>
     <t xml:space="preserve">13.4621734619141</t>
@@ -212,19 +212,19 @@
     <t xml:space="preserve">13.3223066329956</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0950231552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9988651275635</t>
+    <t xml:space="preserve">13.095025062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9988641738892</t>
   </si>
   <si>
     <t xml:space="preserve">12.6404571533203</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4481391906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3782062530518</t>
+    <t xml:space="preserve">12.4481382369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3782052993774</t>
   </si>
   <si>
     <t xml:space="preserve">12.0285387039185</t>
@@ -233,31 +233,31 @@
     <t xml:space="preserve">12.1509237289429</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4393978118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5617799758911</t>
+    <t xml:space="preserve">12.439398765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5617818832397</t>
   </si>
   <si>
     <t xml:space="preserve">12.5268144607544</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6317148208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3694648742676</t>
+    <t xml:space="preserve">12.6317157745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3694658279419</t>
   </si>
   <si>
     <t xml:space="preserve">12.7715816497803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4306573867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2820491790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1946306228638</t>
+    <t xml:space="preserve">12.4306554794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2820472717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1946315765381</t>
   </si>
   <si>
     <t xml:space="preserve">12.2470817565918</t>
@@ -266,25 +266,25 @@
     <t xml:space="preserve">12.4131717681885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5093307495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3869476318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8187398910522</t>
+    <t xml:space="preserve">12.509331703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3869485855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8187389373779</t>
   </si>
   <si>
     <t xml:space="preserve">11.8449649810791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2558250427246</t>
+    <t xml:space="preserve">12.255823135376</t>
   </si>
   <si>
     <t xml:space="preserve">12.5792665481567</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2208557128906</t>
+    <t xml:space="preserve">12.2208566665649</t>
   </si>
   <si>
     <t xml:space="preserve">12.1858901977539</t>
@@ -293,31 +293,31 @@
     <t xml:space="preserve">12.7803230285645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7278738021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8764810562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8065500259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7628412246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8677406311035</t>
+    <t xml:space="preserve">12.7278747558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8764820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8065490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7628393173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8677396774292</t>
   </si>
   <si>
     <t xml:space="preserve">12.8327741622925</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5355558395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1824417114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0338296890259</t>
+    <t xml:space="preserve">12.5355567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1824407577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0338325500488</t>
   </si>
   <si>
     <t xml:space="preserve">13.3048248291016</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">13.2611150741577</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3747577667236</t>
+    <t xml:space="preserve">13.3747568130493</t>
   </si>
   <si>
     <t xml:space="preserve">13.6020412445068</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">13.6894569396973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.724422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7514772415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5711297988892</t>
+    <t xml:space="preserve">13.7244234085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7514753341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5711288452148</t>
   </si>
   <si>
     <t xml:space="preserve">13.8687019348145</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">13.6432676315308</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6613025665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5981817245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6162147521973</t>
+    <t xml:space="preserve">13.661301612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.598180770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6162157058716</t>
   </si>
   <si>
     <t xml:space="preserve">13.5260429382324</t>
@@ -368,34 +368,34 @@
     <t xml:space="preserve">13.5530939102173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3456945419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801467895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6973714828491</t>
+    <t xml:space="preserve">13.3456954956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801477432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6973705291748</t>
   </si>
   <si>
     <t xml:space="preserve">13.778528213501</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6703186035156</t>
+    <t xml:space="preserve">13.6703195571899</t>
   </si>
   <si>
     <t xml:space="preserve">13.7965631484985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9769105911255</t>
+    <t xml:space="preserve">13.9769096374512</t>
   </si>
   <si>
     <t xml:space="preserve">14.0400314331055</t>
   </si>
   <si>
-    <t xml:space="preserve">14.012978553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9047727584839</t>
+    <t xml:space="preserve">14.0129804611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9047718048096</t>
   </si>
   <si>
     <t xml:space="preserve">14.1031532287598</t>
@@ -404,61 +404,61 @@
     <t xml:space="preserve">14.2474317550659</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1572570800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3646564483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4187602996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5179510116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6081266403198</t>
+    <t xml:space="preserve">14.1572580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3646574020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4187622070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.517951965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6081275939941</t>
   </si>
   <si>
     <t xml:space="preserve">14.6622295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3917074203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3105525970459</t>
+    <t xml:space="preserve">14.3917093276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3105535507202</t>
   </si>
   <si>
     <t xml:space="preserve">14.3015356063843</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5450029373169</t>
+    <t xml:space="preserve">14.5450038909912</t>
   </si>
   <si>
     <t xml:space="preserve">14.6441955566406</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7343692779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7163333892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6351776123047</t>
+    <t xml:space="preserve">14.7343683242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7163343429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6351766586304</t>
   </si>
   <si>
     <t xml:space="preserve">14.6261596679688</t>
   </si>
   <si>
-    <t xml:space="preserve">14.689281463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8245439529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.80650806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7433862686157</t>
+    <t xml:space="preserve">14.6892824172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8245420455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8065061569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7433853149414</t>
   </si>
   <si>
     <t xml:space="preserve">14.5810737609863</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">14.6982984542847</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5089340209961</t>
+    <t xml:space="preserve">14.5089359283447</t>
   </si>
   <si>
     <t xml:space="preserve">14.6712474822998</t>
@@ -476,40 +476,40 @@
     <t xml:space="preserve">14.6532125473022</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9237308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0499773025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2122888565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3746004104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.554949760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9246587753296</t>
+    <t xml:space="preserve">14.923731803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.049976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2122898101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3746023178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5549488067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.924656867981</t>
   </si>
   <si>
     <t xml:space="preserve">15.7803831100464</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8705549240112</t>
+    <t xml:space="preserve">15.8705577850342</t>
   </si>
   <si>
     <t xml:space="preserve">15.8344869613647</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7082433700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517107009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7452392578125</t>
+    <t xml:space="preserve">15.7082414627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517126083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7452411651611</t>
   </si>
   <si>
     <t xml:space="preserve">16.8714847564697</t>
@@ -518,46 +518,46 @@
     <t xml:space="preserve">17.0879020690918</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1510219573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2231597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9796943664551</t>
+    <t xml:space="preserve">17.1510238647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2231616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9796924591064</t>
   </si>
   <si>
     <t xml:space="preserve">16.9075527191162</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3043155670166</t>
+    <t xml:space="preserve">17.3043193817139</t>
   </si>
   <si>
     <t xml:space="preserve">17.0337944030762</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2772617340088</t>
+    <t xml:space="preserve">17.2772636413574</t>
   </si>
   <si>
     <t xml:space="preserve">17.4756469726562</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3223514556885</t>
+    <t xml:space="preserve">17.3223495483398</t>
   </si>
   <si>
     <t xml:space="preserve">17.1690578460693</t>
   </si>
   <si>
-    <t xml:space="preserve">17.583854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5748386383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5658168792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2411975860596</t>
+    <t xml:space="preserve">17.5838584899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5748348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5658206939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2411956787109</t>
   </si>
   <si>
     <t xml:space="preserve">17.1870899200439</t>
@@ -569,28 +569,28 @@
     <t xml:space="preserve">16.8444290161133</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9526405334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7272071838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6911334991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8624687194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0428104400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8173770904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9977226257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7722930908203</t>
+    <t xml:space="preserve">16.9526386260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7272052764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6911354064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8624649047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0428123474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8173789978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9977245330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7722911834717</t>
   </si>
   <si>
     <t xml:space="preserve">17.006742477417</t>
@@ -602,52 +602,52 @@
     <t xml:space="preserve">17.358419418335</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6199245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7642021179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0076675415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9896354675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9445476531982</t>
+    <t xml:space="preserve">17.6199264526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7642040252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0076694488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9896373748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9445514678955</t>
   </si>
   <si>
     <t xml:space="preserve">17.9535636901855</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8092880249023</t>
+    <t xml:space="preserve">17.809289932251</t>
   </si>
   <si>
     <t xml:space="preserve">18.2601566314697</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7561092376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.846284866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9364585876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.620849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.297155380249</t>
+    <t xml:space="preserve">18.7561111450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8462886810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9364566802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6208515167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2971534729004</t>
   </si>
   <si>
     <t xml:space="preserve">19.3602733612061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3512573242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6668663024902</t>
+    <t xml:space="preserve">19.3512554168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.666862487793</t>
   </si>
   <si>
     <t xml:space="preserve">19.648832321167</t>
@@ -656,25 +656,25 @@
     <t xml:space="preserve">19.5586566925049</t>
   </si>
   <si>
-    <t xml:space="preserve">19.252067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1709079742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.134838104248</t>
+    <t xml:space="preserve">19.2520637512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1709098815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1348400115967</t>
   </si>
   <si>
     <t xml:space="preserve">19.1979637145996</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9544944763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9094047546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0897541046143</t>
+    <t xml:space="preserve">18.954496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9094066619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0897560119629</t>
   </si>
   <si>
     <t xml:space="preserve">18.5757637023926</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">18.1970367431641</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5306777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8372650146484</t>
+    <t xml:space="preserve">18.5306797027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8372688293457</t>
   </si>
   <si>
     <t xml:space="preserve">19.4594650268555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3873291015625</t>
+    <t xml:space="preserve">19.3873271942139</t>
   </si>
   <si>
     <t xml:space="preserve">20.0185432434082</t>
@@ -701,67 +701,67 @@
     <t xml:space="preserve">20.3612022399902</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8301029205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2809715270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8751888275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.929292678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1006259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0104503631592</t>
+    <t xml:space="preserve">20.8301048278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2809734344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.875186920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9292945861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1006278991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0104465484619</t>
   </si>
   <si>
     <t xml:space="preserve">20.5686016082764</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7218952178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6046695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1898727416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792362213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6497573852539</t>
+    <t xml:space="preserve">20.7218971252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6046714782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1898708343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6497554779053</t>
   </si>
   <si>
     <t xml:space="preserve">21.6416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3711471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3801612854004</t>
+    <t xml:space="preserve">21.3711490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3801651000977</t>
   </si>
   <si>
     <t xml:space="preserve">22.0925350189209</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6245594024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7147331237793</t>
+    <t xml:space="preserve">22.6245574951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7147350311279</t>
   </si>
   <si>
     <t xml:space="preserve">22.8049068450928</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5984363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0763530731201</t>
+    <t xml:space="preserve">23.5984325408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0763549804688</t>
   </si>
   <si>
     <t xml:space="preserve">24.0583190917969</t>
@@ -770,82 +770,82 @@
     <t xml:space="preserve">23.7156581878662</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9320774078369</t>
+    <t xml:space="preserve">23.9320793151855</t>
   </si>
   <si>
     <t xml:space="preserve">23.859935760498</t>
   </si>
   <si>
-    <t xml:space="preserve">23.805835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5082626342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.994270324707</t>
+    <t xml:space="preserve">23.8058338165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5082588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9942722320557</t>
   </si>
   <si>
     <t xml:space="preserve">22.480281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5434017181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7057132720947</t>
+    <t xml:space="preserve">22.5434036254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.705717086792</t>
   </si>
   <si>
     <t xml:space="preserve">22.4532279968262</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4622497558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0023593902588</t>
+    <t xml:space="preserve">22.4622478485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0023632049561</t>
   </si>
   <si>
     <t xml:space="preserve">22.1827125549316</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7237529754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3630542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2097606658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4883728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9212036132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8761196136475</t>
+    <t xml:space="preserve">22.7237510681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3630561828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2097587585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.488374710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9212055206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8761157989502</t>
   </si>
   <si>
     <t xml:space="preserve">21.7047882080078</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9392375946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0745029449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.299934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8139228820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3179664611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1917285919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3540363311768</t>
+    <t xml:space="preserve">21.9392414093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0745010375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2999324798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8139247894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3179683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1917266845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.354040145874</t>
   </si>
   <si>
     <t xml:space="preserve">22.5253677368164</t>
@@ -854,31 +854,31 @@
     <t xml:space="preserve">22.6065254211426</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6335773468018</t>
+    <t xml:space="preserve">22.6335754394531</t>
   </si>
   <si>
     <t xml:space="preserve">22.24582862854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2277965545654</t>
+    <t xml:space="preserve">22.2277946472168</t>
   </si>
   <si>
     <t xml:space="preserve">22.128604888916</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0835189819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2007465362549</t>
+    <t xml:space="preserve">22.083517074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2007427215576</t>
   </si>
   <si>
     <t xml:space="preserve">22.1376190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1466369628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5965805053711</t>
+    <t xml:space="preserve">22.1466407775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5965843200684</t>
   </si>
   <si>
     <t xml:space="preserve">21.3260593414307</t>
@@ -890,151 +890,151 @@
     <t xml:space="preserve">22.0294132232666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6867523193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2368144989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3720703125</t>
+    <t xml:space="preserve">21.6867542266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2368125915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3720722198486</t>
   </si>
   <si>
     <t xml:space="preserve">22.3991260528564</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6155414581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6606273651123</t>
+    <t xml:space="preserve">22.6155452728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6606254577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0123043060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5193881988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2704563140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1739845275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7087249755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7732639312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2434673309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8150844573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7966499328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.686014175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6675720214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0087032318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.888843536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9810409545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0916748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.907283782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8058681488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9533824920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6767921447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6583518981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0775127410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4002017974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2619094848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3264427185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8009243011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4186420440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6441898345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8562412261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9576549530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8931179046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.187479019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9754276275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1229438781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2335796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9938640594482</t>
   </si>
   <si>
     <t xml:space="preserve">23.0123062133789</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5193881988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2704563140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1739826202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7087268829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.773265838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2434692382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8150882720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7966480255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6860103607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.667573928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0087013244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.888843536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9810409545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0916748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9072856903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8058681488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9533805847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6767921447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.658353805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0775146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4002017974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.261905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3264427185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8009223937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4186420440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6441879272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8562412261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9576549530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8931179046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1874809265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9754257202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1229419708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2335796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9938659667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0123043060303</t>
-  </si>
-  <si>
     <t xml:space="preserve">22.7818145751953</t>
   </si>
   <si>
     <t xml:space="preserve">22.6711769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4960041046143</t>
+    <t xml:space="preserve">22.4960060119629</t>
   </si>
   <si>
     <t xml:space="preserve">22.7264957427979</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5052223205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3208293914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5882015228271</t>
+    <t xml:space="preserve">22.5052242279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3208312988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5881996154785</t>
   </si>
   <si>
     <t xml:space="preserve">23.1137218475342</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">23.3995304107666</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7775382995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6208076477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1413841247559</t>
+    <t xml:space="preserve">23.7775421142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6208057403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1413803100586</t>
   </si>
   <si>
     <t xml:space="preserve">22.9846477508545</t>
@@ -1061,46 +1061,46 @@
     <t xml:space="preserve">22.8740100860596</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7357120513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6896152496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.325777053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7406597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9803733825684</t>
+    <t xml:space="preserve">22.7357158660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6896171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3257751464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7406578063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9803714752197</t>
   </si>
   <si>
     <t xml:space="preserve">23.9711513519287</t>
   </si>
   <si>
-    <t xml:space="preserve">24.063346862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2477416992188</t>
+    <t xml:space="preserve">24.0633487701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2477397918701</t>
   </si>
   <si>
     <t xml:space="preserve">24.3860378265381</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1555480957031</t>
+    <t xml:space="preserve">24.1555461883545</t>
   </si>
   <si>
     <t xml:space="preserve">24.6165294647217</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8611831665039</t>
+    <t xml:space="preserve">25.8611869812012</t>
   </si>
   <si>
     <t xml:space="preserve">25.6306934356689</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2158069610596</t>
+    <t xml:space="preserve">25.2158050537109</t>
   </si>
   <si>
     <t xml:space="preserve">25.1697063446045</t>
@@ -1109,16 +1109,16 @@
     <t xml:space="preserve">25.3080062866211</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4463005065918</t>
+    <t xml:space="preserve">25.4462985992432</t>
   </si>
   <si>
     <t xml:space="preserve">25.5384979248047</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1236114501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4321365356445</t>
+    <t xml:space="preserve">25.1236133575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4321403503418</t>
   </si>
   <si>
     <t xml:space="preserve">23.6484622955322</t>
@@ -1130,13 +1130,13 @@
     <t xml:space="preserve">24.1094493865967</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3399391174316</t>
+    <t xml:space="preserve">24.339937210083</t>
   </si>
   <si>
     <t xml:space="preserve">24.2016448974609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2938423156738</t>
+    <t xml:space="preserve">24.2938404083252</t>
   </si>
   <si>
     <t xml:space="preserve">24.754825592041</t>
@@ -1154,22 +1154,22 @@
     <t xml:space="preserve">25.7228908538818</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5704288482666</t>
+    <t xml:space="preserve">24.570426940918</t>
   </si>
   <si>
     <t xml:space="preserve">25.5845966339111</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9994812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4143657684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5668258666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7512187957764</t>
+    <t xml:space="preserve">25.9994792938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4143676757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5668239593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7512168884277</t>
   </si>
   <si>
     <t xml:space="preserve">28.0739059448242</t>
@@ -1178,127 +1178,127 @@
     <t xml:space="preserve">27.5207271575928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7370567321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5065612792969</t>
+    <t xml:space="preserve">26.7370548248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5065593719482</t>
   </si>
   <si>
     <t xml:space="preserve">25.0314159393311</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5243339538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3682689666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5987567901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4604644775391</t>
+    <t xml:space="preserve">24.5243320465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3682670593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5987606048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4604663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2299747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3221664428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1980381011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2760696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2902374267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3824329376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4746265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.552661895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8292503356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.105842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8753490447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8434162139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7653827667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5809879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9356098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8114814758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1661052703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7192859649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.120002746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0597438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9675426483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1519393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6909580230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7831535339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0455780029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6590232849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9214477539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1828804016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0886974334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4654293060303</t>
   </si>
   <si>
     <t xml:space="preserve">26.2299728393555</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3221664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1980381011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2760696411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2902355194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3824310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4746246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.552661895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8292503356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.105842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8753490447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8434162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7653827667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5809879302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9356136322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8114833831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1661033630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7192859649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1200046539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0597438812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9675464630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1519412994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6909580230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7831535339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0455780029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6590213775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9214496612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1828804016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0886974334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4654312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2299709320068</t>
-  </si>
-  <si>
     <t xml:space="preserve">25.8061466217041</t>
   </si>
   <si>
     <t xml:space="preserve">25.7119655609131</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1468658447266</t>
+    <t xml:space="preserve">25.1468677520752</t>
   </si>
   <si>
     <t xml:space="preserve">25.3352336883545</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">24.9114112854004</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4875888824463</t>
+    <t xml:space="preserve">24.4875869750977</t>
   </si>
   <si>
     <t xml:space="preserve">24.3934020996094</t>
@@ -1316,19 +1316,19 @@
     <t xml:space="preserve">23.9224853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2632083892822</t>
+    <t xml:space="preserve">23.2632064819336</t>
   </si>
   <si>
     <t xml:space="preserve">23.0277500152588</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0748405456543</t>
+    <t xml:space="preserve">23.0748386383057</t>
   </si>
   <si>
     <t xml:space="preserve">22.7451992034912</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6039257049561</t>
+    <t xml:space="preserve">22.6039237976074</t>
   </si>
   <si>
     <t xml:space="preserve">22.5097427368164</t>
@@ -1337,19 +1337,19 @@
     <t xml:space="preserve">22.4155578613281</t>
   </si>
   <si>
-    <t xml:space="preserve">22.180103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0388298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8504619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4626522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2271938323975</t>
+    <t xml:space="preserve">22.1801013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0388278961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8504638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4626502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2271919250488</t>
   </si>
   <si>
     <t xml:space="preserve">23.4044818878174</t>
@@ -1358,16 +1358,16 @@
     <t xml:space="preserve">23.2161159515381</t>
   </si>
   <si>
-    <t xml:space="preserve">22.886474609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.498664855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5568332672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1330070495605</t>
+    <t xml:space="preserve">22.8864727020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4986629486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5568351745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1330089569092</t>
   </si>
   <si>
     <t xml:space="preserve">21.6620960235596</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">21.0028133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0969982147217</t>
+    <t xml:space="preserve">21.096996307373</t>
   </si>
   <si>
     <t xml:space="preserve">20.8615379333496</t>
@@ -1391,31 +1391,31 @@
     <t xml:space="preserve">21.4737281799316</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2742824554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7562770843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9446430206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5679130554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5208206176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3324546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2382717132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8393840789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.792293548584</t>
+    <t xml:space="preserve">22.274284362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7562789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9446449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5679111480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5208225250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3324527740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2382698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8393821716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7922916412354</t>
   </si>
   <si>
     <t xml:space="preserve">23.5457553863525</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">23.6870307922363</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7812118530273</t>
+    <t xml:space="preserve">23.781213760376</t>
   </si>
   <si>
     <t xml:space="preserve">24.0166721343994</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">24.2521266937256</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7230415344238</t>
+    <t xml:space="preserve">24.7230434417725</t>
   </si>
   <si>
     <t xml:space="preserve">24.6288623809814</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">24.675952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">24.58176612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.770133972168</t>
+    <t xml:space="preserve">24.5817680358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7701320648193</t>
   </si>
   <si>
     <t xml:space="preserve">24.9585018157959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9003314971924</t>
+    <t xml:space="preserve">25.9003295898438</t>
   </si>
   <si>
     <t xml:space="preserve">25.7590560913086</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">26.277063369751</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9363479614258</t>
+    <t xml:space="preserve">26.9363460540771</t>
   </si>
   <si>
     <t xml:space="preserve">26.983434677124</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">26.8421592712402</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7479782104492</t>
+    <t xml:space="preserve">26.7479763031006</t>
   </si>
   <si>
     <t xml:space="preserve">27.2659854888916</t>
@@ -1496,13 +1496,13 @@
     <t xml:space="preserve">27.501443862915</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3130779266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0776195526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7008857727051</t>
+    <t xml:space="preserve">27.3130760192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0776176452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7008876800537</t>
   </si>
   <si>
     <t xml:space="preserve">26.6537952423096</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">26.1357898712158</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0416049957275</t>
+    <t xml:space="preserve">26.0416030883789</t>
   </si>
   <si>
     <t xml:space="preserve">25.6177825927734</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">25.0997753143311</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8643169403076</t>
+    <t xml:space="preserve">24.8643207550049</t>
   </si>
   <si>
     <t xml:space="preserve">24.4404945373535</t>
@@ -1541,25 +1541,25 @@
     <t xml:space="preserve">25.5235996246338</t>
   </si>
   <si>
-    <t xml:space="preserve">26.371244430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3241577148438</t>
+    <t xml:space="preserve">26.3712482452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3241558074951</t>
   </si>
   <si>
     <t xml:space="preserve">26.7950706481934</t>
   </si>
   <si>
-    <t xml:space="preserve">26.889253616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0305271148682</t>
+    <t xml:space="preserve">26.8892517089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0305290222168</t>
   </si>
   <si>
     <t xml:space="preserve">27.171802520752</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5485343933105</t>
+    <t xml:space="preserve">27.5485324859619</t>
   </si>
   <si>
     <t xml:space="preserve">27.6898078918457</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">28.3961791992188</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7258205413818</t>
+    <t xml:space="preserve">28.7258186340332</t>
   </si>
   <si>
     <t xml:space="preserve">28.9141883850098</t>
@@ -1583,43 +1583,43 @@
     <t xml:space="preserve">29.7618350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3269348144531</t>
+    <t xml:space="preserve">30.3269329071045</t>
   </si>
   <si>
     <t xml:space="preserve">30.3740234375</t>
   </si>
   <si>
-    <t xml:space="preserve">31.504222869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6925868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4460525512695</t>
+    <t xml:space="preserve">31.5042247772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6925888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4460487365723</t>
   </si>
   <si>
     <t xml:space="preserve">32.4931449890137</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4820594787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6704292297363</t>
+    <t xml:space="preserve">33.482063293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6704330444336</t>
   </si>
   <si>
     <t xml:space="preserve">33.293701171875</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5762519836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.905891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2466049194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.869873046875</t>
+    <t xml:space="preserve">33.5762481689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9058876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2466087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8698768615723</t>
   </si>
   <si>
     <t xml:space="preserve">33.1524238586426</t>
@@ -1628,127 +1628,127 @@
     <t xml:space="preserve">33.0582389831543</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5873222351074</t>
+    <t xml:space="preserve">32.5873260498047</t>
   </si>
   <si>
     <t xml:space="preserve">32.3047752380371</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9280452728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4571285247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.362943649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8920345306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0803966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0333042144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6565761566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6094837188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2687683105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.986213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4100322723389</t>
+    <t xml:space="preserve">31.9280490875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4571304321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3629455566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8920307159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0803928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0333080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6565742492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6094799041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2687644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9862155914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4100379943848</t>
   </si>
   <si>
     <t xml:space="preserve">30.8449382781982</t>
   </si>
   <si>
-    <t xml:space="preserve">31.17458152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8809509277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0222206115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7396793365479</t>
+    <t xml:space="preserve">31.1745796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8809490203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0222244262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7396812438965</t>
   </si>
   <si>
     <t xml:space="preserve">34.0000686645508</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4709815979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.78955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5901031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7784690856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.155200958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6732063293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0846748352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.228214263916</t>
+    <t xml:space="preserve">34.4709854125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7895469665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5901069641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7784729003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1552047729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.673210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0846786499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2282104492188</t>
   </si>
   <si>
     <t xml:space="preserve">37.367000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7976036071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1803703308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3717422485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9411430358887</t>
+    <t xml:space="preserve">37.797607421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1803665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3717460632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9411392211914</t>
   </si>
   <si>
     <t xml:space="preserve">37.9889869689941</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8454551696777</t>
+    <t xml:space="preserve">37.8454513549805</t>
   </si>
   <si>
     <t xml:space="preserve">37.3191604614258</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8501968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7545051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3286476135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.041576385498</t>
+    <t xml:space="preserve">38.8501930236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.754508972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3286437988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0415802001953</t>
   </si>
   <si>
     <t xml:space="preserve">38.8023529052734</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4674415588379</t>
+    <t xml:space="preserve">38.4674377441406</t>
   </si>
   <si>
     <t xml:space="preserve">38.1325149536133</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">38.4195938110352</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3764915466309</t>
+    <t xml:space="preserve">39.3764953613281</t>
   </si>
   <si>
     <t xml:space="preserve">39.1372680664062</t>
@@ -1787,22 +1787,22 @@
     <t xml:space="preserve">41.1946067810059</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1036605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5342712402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6730575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8118476867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7161598205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9122848510742</t>
+    <t xml:space="preserve">42.1036643981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5342674255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6730537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8118438720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7161560058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.912281036377</t>
   </si>
   <si>
     <t xml:space="preserve">43.0605659484863</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">44.2566909790039</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7829895019531</t>
+    <t xml:space="preserve">44.7829856872559</t>
   </si>
   <si>
     <t xml:space="preserve">43.4433250427246</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">43.6347007751465</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2041053771973</t>
+    <t xml:space="preserve">43.2041015625</t>
   </si>
   <si>
     <t xml:space="preserve">42.9170303344727</t>
@@ -1835,22 +1835,22 @@
     <t xml:space="preserve">44.9265213012695</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4049758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2614326477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5963516235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6536865234375</t>
+    <t xml:space="preserve">45.404972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2614364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5963592529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6536903381348</t>
   </si>
   <si>
     <t xml:space="preserve">48.8976631164551</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6105918884277</t>
+    <t xml:space="preserve">48.610595703125</t>
   </si>
   <si>
     <t xml:space="preserve">49.1847343444824</t>
@@ -1859,10 +1859,10 @@
     <t xml:space="preserve">48.993350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7588768005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2804222106934</t>
+    <t xml:space="preserve">49.7588729858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2804260253906</t>
   </si>
   <si>
     <t xml:space="preserve">49.6631813049316</t>
@@ -1871,10 +1871,10 @@
     <t xml:space="preserve">49.3761138916016</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5674896240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6200866699219</t>
+    <t xml:space="preserve">49.5674934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6200828552246</t>
   </si>
   <si>
     <t xml:space="preserve">51.0028457641602</t>
@@ -1883,25 +1883,25 @@
     <t xml:space="preserve">52.7252655029297</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6295776367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.9597434997559</t>
+    <t xml:space="preserve">52.6295738220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9597396850586</t>
   </si>
   <si>
     <t xml:space="preserve">51.8640594482422</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6726722717285</t>
+    <t xml:space="preserve">51.6726760864258</t>
   </si>
   <si>
     <t xml:space="preserve">48.4192085266113</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3235168457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0459480285645</t>
+    <t xml:space="preserve">48.3235206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0459442138672</t>
   </si>
   <si>
     <t xml:space="preserve">51.3856086730957</t>
@@ -1931,49 +1931,49 @@
     <t xml:space="preserve">47.3666191101074</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9838562011719</t>
+    <t xml:space="preserve">46.9838600158691</t>
   </si>
   <si>
     <t xml:space="preserve">46.361873626709</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7398872375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9743614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.586856842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7687454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6493225097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5967330932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0945510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4820575714111</t>
+    <t xml:space="preserve">45.7398834228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.974365234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5868606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7687492370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6493263244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5967292785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0945491790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4820594787598</t>
   </si>
   <si>
     <t xml:space="preserve">29.1854915618896</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5299015045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0992984771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3816204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9268989562988</t>
+    <t xml:space="preserve">31.5299053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0992946624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3816223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9268951416016</t>
   </si>
   <si>
     <t xml:space="preserve">36.410099029541</t>
@@ -1985,10 +1985,10 @@
     <t xml:space="preserve">35.3096656799316</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5441360473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0704383850098</t>
+    <t xml:space="preserve">34.5441398620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0704345703125</t>
   </si>
   <si>
     <t xml:space="preserve">37.0799293518066</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">37.2234649658203</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1277694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2329521179199</t>
+    <t xml:space="preserve">37.1277732849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2329559326172</t>
   </si>
   <si>
     <t xml:space="preserve">40.429084777832</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">45.4528160095215</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0700607299805</t>
+    <t xml:space="preserve">45.0700569152832</t>
   </si>
   <si>
     <t xml:space="preserve">45.3571319580078</t>
@@ -2027,34 +2027,34 @@
     <t xml:space="preserve">45.1179008483887</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4575576782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6441993713379</t>
+    <t xml:space="preserve">46.4575614929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6441955566406</t>
   </si>
   <si>
     <t xml:space="preserve">44.8786773681641</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3092803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1657485961914</t>
+    <t xml:space="preserve">45.3092842102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1657447814941</t>
   </si>
   <si>
     <t xml:space="preserve">44.2088470458984</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1562538146973</t>
+    <t xml:space="preserve">43.15625</t>
   </si>
   <si>
     <t xml:space="preserve">43.9217758178711</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8644332885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5821151733398</t>
+    <t xml:space="preserve">41.8644371032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5821113586426</t>
   </si>
   <si>
     <t xml:space="preserve">45.0222091674805</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">45.5485038757324</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5101585388184</t>
+    <t xml:space="preserve">47.5101547241211</t>
   </si>
   <si>
     <t xml:space="preserve">47.7015342712402</t>
@@ -2072,22 +2072,22 @@
     <t xml:space="preserve">48.7062835693359</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9407539367676</t>
+    <t xml:space="preserve">47.9407615661621</t>
   </si>
   <si>
     <t xml:space="preserve">48.5149002075195</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4812965393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1942253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.768367767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2899169921875</t>
+    <t xml:space="preserve">51.4813003540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1942291259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7683639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.289909362793</t>
   </si>
   <si>
     <t xml:space="preserve">53.1080322265625</t>
@@ -2096,55 +2096,55 @@
     <t xml:space="preserve">53.96923828125</t>
   </si>
   <si>
-    <t xml:space="preserve">53.490795135498</t>
+    <t xml:space="preserve">53.4907913208008</t>
   </si>
   <si>
     <t xml:space="preserve">55.1175193786621</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6916618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5002861022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3520011901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6390686035156</t>
+    <t xml:space="preserve">55.6916656494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5002822875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3519973754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6390647888184</t>
   </si>
   <si>
     <t xml:space="preserve">54.8304481506348</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4045944213867</t>
+    <t xml:space="preserve">55.404598236084</t>
   </si>
   <si>
     <t xml:space="preserve">56.744255065918</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9356346130371</t>
+    <t xml:space="preserve">56.9356307983398</t>
   </si>
   <si>
     <t xml:space="preserve">57.1270141601562</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2658042907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9787330627441</t>
+    <t xml:space="preserve">56.2658004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9787292480469</t>
   </si>
   <si>
     <t xml:space="preserve">57.3183937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">58.6580505371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2227058410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7011528015137</t>
+    <t xml:space="preserve">58.6580543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2227020263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7011566162109</t>
   </si>
   <si>
     <t xml:space="preserve">56.3614959716797</t>
@@ -2153,13 +2153,13 @@
     <t xml:space="preserve">57.988224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">58.849437713623</t>
+    <t xml:space="preserve">58.8494338989258</t>
   </si>
   <si>
     <t xml:space="preserve">61.3373794555664</t>
   </si>
   <si>
-    <t xml:space="preserve">63.4425659179688</t>
+    <t xml:space="preserve">63.4425621032715</t>
   </si>
   <si>
     <t xml:space="preserve">62.2942848205566</t>
@@ -2174,13 +2174,13 @@
     <t xml:space="preserve">63.6339454650879</t>
   </si>
   <si>
-    <t xml:space="preserve">64.3037643432617</t>
+    <t xml:space="preserve">64.3037719726562</t>
   </si>
   <si>
     <t xml:space="preserve">64.5908432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">65.9305114746094</t>
+    <t xml:space="preserve">65.9305038452148</t>
   </si>
   <si>
     <t xml:space="preserve">66.6960220336914</t>
@@ -2189,25 +2189,25 @@
     <t xml:space="preserve">65.3563690185547</t>
   </si>
   <si>
-    <t xml:space="preserve">66.9831085205078</t>
+    <t xml:space="preserve">66.9831008911133</t>
   </si>
   <si>
     <t xml:space="preserve">67.1744766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5046539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8443145751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.0451812744141</t>
+    <t xml:space="preserve">66.5046463012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8443069458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.0451889038086</t>
   </si>
   <si>
     <t xml:space="preserve">69.1839752197266</t>
   </si>
   <si>
-    <t xml:space="preserve">71.2891464233398</t>
+    <t xml:space="preserve">71.2891540527344</t>
   </si>
   <si>
     <t xml:space="preserve">70.8107070922852</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">71.0020904541016</t>
   </si>
   <si>
-    <t xml:space="preserve">69.4710464477539</t>
+    <t xml:space="preserve">69.4710388183594</t>
   </si>
   <si>
     <t xml:space="preserve">68.9925994873047</t>
@@ -2237,16 +2237,16 @@
     <t xml:space="preserve">68.8012084960938</t>
   </si>
   <si>
-    <t xml:space="preserve">69.6624221801758</t>
+    <t xml:space="preserve">69.6624298095703</t>
   </si>
   <si>
     <t xml:space="preserve">76.5521087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7003936767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8822860717773</t>
+    <t xml:space="preserve">77.7003860473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8822784423828</t>
   </si>
   <si>
     <t xml:space="preserve">74.734001159668</t>
@@ -2270,22 +2270,22 @@
     <t xml:space="preserve">79.4228286743164</t>
   </si>
   <si>
-    <t xml:space="preserve">80.7624816894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0064544677734</t>
+    <t xml:space="preserve">80.7624893188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0064468383789</t>
   </si>
   <si>
     <t xml:space="preserve">81.5279998779297</t>
   </si>
   <si>
-    <t xml:space="preserve">81.910758972168</t>
+    <t xml:space="preserve">81.9107513427734</t>
   </si>
   <si>
     <t xml:space="preserve">82.3892135620117</t>
   </si>
   <si>
-    <t xml:space="preserve">81.4323196411133</t>
+    <t xml:space="preserve">81.4323120117188</t>
   </si>
   <si>
     <t xml:space="preserve">81.1452407836914</t>
@@ -2294,19 +2294,19 @@
     <t xml:space="preserve">80.4754028320312</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7193756103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.815071105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.3461151123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.953857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.77197265625</t>
+    <t xml:space="preserve">81.7193832397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8150787353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.3461074829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.9538497924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7719802856445</t>
   </si>
   <si>
     <t xml:space="preserve">82.2935180664062</t>
@@ -2318,31 +2318,31 @@
     <t xml:space="preserve">79.3271255493164</t>
   </si>
   <si>
-    <t xml:space="preserve">83.7288665771484</t>
+    <t xml:space="preserve">83.728874206543</t>
   </si>
   <si>
     <t xml:space="preserve">82.1021499633789</t>
   </si>
   <si>
-    <t xml:space="preserve">76.7434844970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.5185012817383</t>
+    <t xml:space="preserve">76.7434921264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.5185089111328</t>
   </si>
   <si>
     <t xml:space="preserve">79.8055801391602</t>
   </si>
   <si>
-    <t xml:space="preserve">82.4848861694336</t>
+    <t xml:space="preserve">82.4848937988281</t>
   </si>
   <si>
     <t xml:space="preserve">80.3797225952148</t>
   </si>
   <si>
-    <t xml:space="preserve">78.6572952270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.4659042358398</t>
+    <t xml:space="preserve">78.6572875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.4659118652344</t>
   </si>
   <si>
     <t xml:space="preserve">84.6857681274414</t>
@@ -2351,13 +2351,13 @@
     <t xml:space="preserve">85.3556060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">83.0590362548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.9297409057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.173713684082</t>
+    <t xml:space="preserve">83.0590438842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.9297485351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.1737213134766</t>
   </si>
   <si>
     <t xml:space="preserve">87.269401550293</t>
@@ -2366,40 +2366,40 @@
     <t xml:space="preserve">88.3219985961914</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7909545898438</t>
+    <t xml:space="preserve">86.7909622192383</t>
   </si>
   <si>
     <t xml:space="preserve">90.905632019043</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3840942382812</t>
+    <t xml:space="preserve">91.3840866088867</t>
   </si>
   <si>
     <t xml:space="preserve">93.1065139770508</t>
   </si>
   <si>
-    <t xml:space="preserve">95.8815078735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.2211837768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.474639892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.622924804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.240173339844</t>
+    <t xml:space="preserve">95.8815231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.22119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.474647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.622932434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.240165710449</t>
   </si>
   <si>
     <t xml:space="preserve">97.986701965332</t>
   </si>
   <si>
-    <t xml:space="preserve">98.5608444213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.9004974365234</t>
+    <t xml:space="preserve">98.5608520507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.900505065918</t>
   </si>
   <si>
     <t xml:space="preserve">96.2642822265625</t>
@@ -2408,10 +2408,10 @@
     <t xml:space="preserve">95.6901397705078</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8289337158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.307373046875</t>
+    <t xml:space="preserve">94.8289260864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3073806762695</t>
   </si>
   <si>
     <t xml:space="preserve">94.2547836303711</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">93.8720321655273</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0634078979492</t>
+    <t xml:space="preserve">94.0634002685547</t>
   </si>
   <si>
     <t xml:space="preserve">93.3935775756836</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">93.6806411743164</t>
   </si>
   <si>
-    <t xml:space="preserve">92.9151153564453</t>
+    <t xml:space="preserve">92.9151229858398</t>
   </si>
   <si>
     <t xml:space="preserve">93.2978897094727</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">106.598815917969</t>
   </si>
   <si>
-    <t xml:space="preserve">107.364326477051</t>
+    <t xml:space="preserve">107.364334106445</t>
   </si>
   <si>
     <t xml:space="preserve">109.66089630127</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">110.235038757324</t>
   </si>
   <si>
-    <t xml:space="preserve">105.641914367676</t>
+    <t xml:space="preserve">105.64192199707</t>
   </si>
   <si>
     <t xml:space="preserve">106.216064453125</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">107.9384765625</t>
   </si>
   <si>
-    <t xml:space="preserve">107.555732727051</t>
+    <t xml:space="preserve">107.555725097656</t>
   </si>
   <si>
     <t xml:space="preserve">109.469528198242</t>
@@ -2495,28 +2495,28 @@
     <t xml:space="preserve">107.747100830078</t>
   </si>
   <si>
-    <t xml:space="preserve">108.704002380371</t>
+    <t xml:space="preserve">108.703994750977</t>
   </si>
   <si>
     <t xml:space="preserve">102.197074890137</t>
   </si>
   <si>
-    <t xml:space="preserve">99.5177536010742</t>
+    <t xml:space="preserve">99.5177459716797</t>
   </si>
   <si>
     <t xml:space="preserve">99.7091217041016</t>
   </si>
   <si>
-    <t xml:space="preserve">103.345344543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.536735534668</t>
+    <t xml:space="preserve">103.345352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.536727905273</t>
   </si>
   <si>
     <t xml:space="preserve">106.024673461914</t>
   </si>
   <si>
-    <t xml:space="preserve">106.981590270996</t>
+    <t xml:space="preserve">106.981582641602</t>
   </si>
   <si>
     <t xml:space="preserve">108.512619018555</t>
@@ -2525,16 +2525,16 @@
     <t xml:space="preserve">105.833290100098</t>
   </si>
   <si>
-    <t xml:space="preserve">101.048782348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.388450622559</t>
+    <t xml:space="preserve">101.048789978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.388458251953</t>
   </si>
   <si>
     <t xml:space="preserve">103.15397644043</t>
   </si>
   <si>
-    <t xml:space="preserve">102.962593078613</t>
+    <t xml:space="preserve">102.962600708008</t>
   </si>
   <si>
     <t xml:space="preserve">105.450531005859</t>
@@ -2543,28 +2543,28 @@
     <t xml:space="preserve">102.00569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">103.919486999512</t>
+    <t xml:space="preserve">103.919479370117</t>
   </si>
   <si>
     <t xml:space="preserve">106.407440185547</t>
   </si>
   <si>
-    <t xml:space="preserve">109.086753845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.809188842773</t>
+    <t xml:space="preserve">109.086761474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.809196472168</t>
   </si>
   <si>
     <t xml:space="preserve">113.679893493652</t>
   </si>
   <si>
-    <t xml:space="preserve">110.043663024902</t>
+    <t xml:space="preserve">110.043655395508</t>
   </si>
   <si>
     <t xml:space="preserve">107.172958374023</t>
   </si>
   <si>
-    <t xml:space="preserve">111.00057220459</t>
+    <t xml:space="preserve">111.000564575195</t>
   </si>
   <si>
     <t xml:space="preserve">112.914367675781</t>
@@ -2576,28 +2576,28 @@
     <t xml:space="preserve">110.426422119141</t>
   </si>
   <si>
-    <t xml:space="preserve">111.383323669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.340225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.445411682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.29712677002</t>
+    <t xml:space="preserve">111.383331298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.340232849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.445404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.297119140625</t>
   </si>
   <si>
     <t xml:space="preserve">112.722991943359</t>
   </si>
   <si>
-    <t xml:space="preserve">115.019546508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.593696594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.2109375</t>
+    <t xml:space="preserve">115.019538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.593704223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.210929870605</t>
   </si>
   <si>
     <t xml:space="preserve">116.741966247559</t>
@@ -2609,19 +2609,19 @@
     <t xml:space="preserve">115.78507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">116.550590515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.804054260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.186820983887</t>
+    <t xml:space="preserve">116.550598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.804061889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.186828613281</t>
   </si>
   <si>
     <t xml:space="preserve">122.100616455078</t>
   </si>
   <si>
-    <t xml:space="preserve">122.866134643555</t>
+    <t xml:space="preserve">122.866142272949</t>
   </si>
   <si>
     <t xml:space="preserve">123.631652832031</t>
@@ -2639,19 +2639,19 @@
     <t xml:space="preserve">128.990310668945</t>
   </si>
   <si>
-    <t xml:space="preserve">132.05241394043</t>
+    <t xml:space="preserve">132.052398681641</t>
   </si>
   <si>
     <t xml:space="preserve">134.157577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">133.774795532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.626525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.435150146484</t>
+    <t xml:space="preserve">133.774810791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.626556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.435165405273</t>
   </si>
   <si>
     <t xml:space="preserve">134.923080444336</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">135.305862426758</t>
   </si>
   <si>
-    <t xml:space="preserve">131.861022949219</t>
+    <t xml:space="preserve">131.86100769043</t>
   </si>
   <si>
     <t xml:space="preserve">134.731719970703</t>
@@ -2675,13 +2675,13 @@
     <t xml:space="preserve">136.262756347656</t>
   </si>
   <si>
-    <t xml:space="preserve">137.793807983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.176544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.028274536133</t>
+    <t xml:space="preserve">137.793792724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.176559448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.028259277344</t>
   </si>
   <si>
     <t xml:space="preserve">138.559326171875</t>
@@ -2690,13 +2690,13 @@
     <t xml:space="preserve">139.898986816406</t>
   </si>
   <si>
-    <t xml:space="preserve">136.454162597656</t>
+    <t xml:space="preserve">136.454147338867</t>
   </si>
   <si>
     <t xml:space="preserve">138.750701904297</t>
   </si>
   <si>
-    <t xml:space="preserve">139.324844360352</t>
+    <t xml:space="preserve">139.324859619141</t>
   </si>
   <si>
     <t xml:space="preserve">137.985198974609</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">135.497253417969</t>
   </si>
   <si>
-    <t xml:space="preserve">144.492126464844</t>
+    <t xml:space="preserve">144.492111206055</t>
   </si>
   <si>
     <t xml:space="preserve">144.874877929688</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">143.917984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">144.683486938477</t>
+    <t xml:space="preserve">144.683502197266</t>
   </si>
   <si>
     <t xml:space="preserve">145.25764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">147.936981201172</t>
+    <t xml:space="preserve">147.936965942383</t>
   </si>
   <si>
     <t xml:space="preserve">145.640396118164</t>
@@ -2741,28 +2741,28 @@
     <t xml:space="preserve">149.276641845703</t>
   </si>
   <si>
-    <t xml:space="preserve">150.9990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.424911499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.486968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.33869934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.400787353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.190414428711</t>
+    <t xml:space="preserve">150.999038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.424896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.48698425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.338714599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.400772094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.1904296875</t>
   </si>
   <si>
     <t xml:space="preserve">157.888732910156</t>
   </si>
   <si>
-    <t xml:space="preserve">159.037002563477</t>
+    <t xml:space="preserve">159.037017822266</t>
   </si>
   <si>
     <t xml:space="preserve">158.654251098633</t>
@@ -2771,16 +2771,16 @@
     <t xml:space="preserve">159.61116027832</t>
   </si>
   <si>
-    <t xml:space="preserve">161.333587646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.524963378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.438751220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.821517944336</t>
+    <t xml:space="preserve">161.333572387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.524978637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.438766479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.821502685547</t>
   </si>
   <si>
     <t xml:space="preserve">168.606002807617</t>
@@ -2789,16 +2789,16 @@
     <t xml:space="preserve">173.773300170898</t>
   </si>
   <si>
-    <t xml:space="preserve">170.328460693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.161209106445</t>
+    <t xml:space="preserve">170.32844543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.161193847656</t>
   </si>
   <si>
     <t xml:space="preserve">168.03190612793</t>
   </si>
   <si>
-    <t xml:space="preserve">165.352584838867</t>
+    <t xml:space="preserve">165.352569580078</t>
   </si>
   <si>
     <t xml:space="preserve">160.75944519043</t>
@@ -2810,7 +2810,7 @@
     <t xml:space="preserve">171.668121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">167.074981689453</t>
+    <t xml:space="preserve">167.074996948242</t>
   </si>
   <si>
     <t xml:space="preserve">161.93049621582</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">150.391525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">150.19921875</t>
+    <t xml:space="preserve">150.199203491211</t>
   </si>
   <si>
     <t xml:space="preserve">148.083724975586</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">153.468597412109</t>
   </si>
   <si>
-    <t xml:space="preserve">153.276245117188</t>
+    <t xml:space="preserve">153.276260375977</t>
   </si>
   <si>
     <t xml:space="preserve">157.122604370117</t>
@@ -3044,13 +3044,13 @@
     <t xml:space="preserve">138.660232543945</t>
   </si>
   <si>
-    <t xml:space="preserve">132.698425292969</t>
+    <t xml:space="preserve">132.69841003418</t>
   </si>
   <si>
     <t xml:space="preserve">132.506103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">130.198287963867</t>
+    <t xml:space="preserve">130.198272705078</t>
   </si>
   <si>
     <t xml:space="preserve">134.813888549805</t>
@@ -3059,7 +3059,7 @@
     <t xml:space="preserve">130.005981445312</t>
   </si>
   <si>
-    <t xml:space="preserve">130.77522277832</t>
+    <t xml:space="preserve">130.775238037109</t>
   </si>
   <si>
     <t xml:space="preserve">128.852081298828</t>
@@ -3113,34 +3113,34 @@
     <t xml:space="preserve">145.00666809082</t>
   </si>
   <si>
-    <t xml:space="preserve">145.775924682617</t>
+    <t xml:space="preserve">145.775939941406</t>
   </si>
   <si>
     <t xml:space="preserve">144.814346313477</t>
   </si>
   <si>
-    <t xml:space="preserve">148.276031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.275802612305</t>
+    <t xml:space="preserve">148.27604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.275817871094</t>
   </si>
   <si>
     <t xml:space="preserve">142.60270690918</t>
   </si>
   <si>
-    <t xml:space="preserve">142.698867797852</t>
+    <t xml:space="preserve">142.698852539062</t>
   </si>
   <si>
     <t xml:space="preserve">143.08349609375</t>
   </si>
   <si>
-    <t xml:space="preserve">139.525634765625</t>
+    <t xml:space="preserve">139.525650024414</t>
   </si>
   <si>
     <t xml:space="preserve">141.160354614258</t>
   </si>
   <si>
-    <t xml:space="preserve">140.198760986328</t>
+    <t xml:space="preserve">140.198745727539</t>
   </si>
   <si>
     <t xml:space="preserve">139.910278320312</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">130.87141418457</t>
   </si>
   <si>
-    <t xml:space="preserve">129.525177001953</t>
+    <t xml:space="preserve">129.525192260742</t>
   </si>
   <si>
     <t xml:space="preserve">129.90983581543</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">133.371520996094</t>
   </si>
   <si>
-    <t xml:space="preserve">128.275115966797</t>
+    <t xml:space="preserve">128.275131225586</t>
   </si>
   <si>
     <t xml:space="preserve">130.294448852539</t>
   </si>
   <si>
-    <t xml:space="preserve">124.236473083496</t>
+    <t xml:space="preserve">124.236480712891</t>
   </si>
   <si>
     <t xml:space="preserve">122.890266418457</t>
@@ -3191,10 +3191,10 @@
     <t xml:space="preserve">118.563148498535</t>
   </si>
   <si>
-    <t xml:space="preserve">109.81273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.56290435791</t>
+    <t xml:space="preserve">109.812744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.562911987305</t>
   </si>
   <si>
     <t xml:space="preserve">115.389915466309</t>
@@ -3221,13 +3221,13 @@
     <t xml:space="preserve">119.236251831055</t>
   </si>
   <si>
-    <t xml:space="preserve">120.486312866211</t>
+    <t xml:space="preserve">120.486320495605</t>
   </si>
   <si>
     <t xml:space="preserve">116.736145019531</t>
   </si>
   <si>
-    <t xml:space="preserve">116.832298278809</t>
+    <t xml:space="preserve">116.832290649414</t>
   </si>
   <si>
     <t xml:space="preserve">119.043937683105</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">128.659774780273</t>
   </si>
   <si>
-    <t xml:space="preserve">127.698188781738</t>
+    <t xml:space="preserve">127.698173522949</t>
   </si>
   <si>
     <t xml:space="preserve">123.178749084473</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">114.236030578613</t>
   </si>
   <si>
-    <t xml:space="preserve">111.062797546387</t>
+    <t xml:space="preserve">111.062805175781</t>
   </si>
   <si>
     <t xml:space="preserve">112.216690063477</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">113.178276062012</t>
   </si>
   <si>
-    <t xml:space="preserve">119.332412719727</t>
+    <t xml:space="preserve">119.332405090332</t>
   </si>
   <si>
     <t xml:space="preserve">123.082580566406</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">125.390365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">122.986419677734</t>
+    <t xml:space="preserve">122.986427307129</t>
   </si>
   <si>
     <t xml:space="preserve">118.274673461914</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">123.659538269043</t>
   </si>
   <si>
-    <t xml:space="preserve">128.948257446289</t>
+    <t xml:space="preserve">128.9482421875</t>
   </si>
   <si>
     <t xml:space="preserve">131.736801147461</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">128.371307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">126.736587524414</t>
+    <t xml:space="preserve">126.736595153809</t>
   </si>
   <si>
     <t xml:space="preserve">121.447891235352</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">120.197830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">121.063255310059</t>
+    <t xml:space="preserve">121.063262939453</t>
   </si>
   <si>
     <t xml:space="preserve">117.505401611328</t>
@@ -3401,10 +3401,10 @@
     <t xml:space="preserve">116.255348205566</t>
   </si>
   <si>
-    <t xml:space="preserve">112.312858581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.582237243652</t>
+    <t xml:space="preserve">112.312866210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.582229614258</t>
   </si>
   <si>
     <t xml:space="preserve">115.67839050293</t>
@@ -3449,10 +3449,10 @@
     <t xml:space="preserve">109.212615966797</t>
   </si>
   <si>
-    <t xml:space="preserve">113.185752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.441452026367</t>
+    <t xml:space="preserve">113.185760498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.441444396973</t>
   </si>
   <si>
     <t xml:space="preserve">111.829071044922</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">104.658050537109</t>
   </si>
   <si>
-    <t xml:space="preserve">101.847793579102</t>
+    <t xml:space="preserve">101.847801208496</t>
   </si>
   <si>
     <t xml:space="preserve">102.429222106934</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">104.076629638672</t>
   </si>
   <si>
-    <t xml:space="preserve">106.402366638184</t>
+    <t xml:space="preserve">106.402359008789</t>
   </si>
   <si>
     <t xml:space="preserve">106.693069458008</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">116.771255493164</t>
   </si>
   <si>
-    <t xml:space="preserve">114.445518493652</t>
+    <t xml:space="preserve">114.445526123047</t>
   </si>
   <si>
     <t xml:space="preserve">114.736236572266</t>
@@ -3542,10 +3542,10 @@
     <t xml:space="preserve">115.511474609375</t>
   </si>
   <si>
-    <t xml:space="preserve">115.220771789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.965065002441</t>
+    <t xml:space="preserve">115.220764160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.965072631836</t>
   </si>
   <si>
     <t xml:space="preserve">113.476463317871</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">111.053825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">112.701232910156</t>
+    <t xml:space="preserve">112.701225280762</t>
   </si>
   <si>
     <t xml:space="preserve">112.604316711426</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">108.534278869629</t>
   </si>
   <si>
-    <t xml:space="preserve">110.181678771973</t>
+    <t xml:space="preserve">110.181671142578</t>
   </si>
   <si>
     <t xml:space="preserve">109.890960693359</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">120.550575256348</t>
   </si>
   <si>
-    <t xml:space="preserve">122.779411315918</t>
+    <t xml:space="preserve">122.779403686523</t>
   </si>
   <si>
     <t xml:space="preserve">123.263931274414</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">121.810340881348</t>
   </si>
   <si>
-    <t xml:space="preserve">120.744384765625</t>
+    <t xml:space="preserve">120.74439239502</t>
   </si>
   <si>
     <t xml:space="preserve">123.748458862305</t>
@@ -3665,7 +3665,7 @@
     <t xml:space="preserve">132.179260253906</t>
   </si>
   <si>
-    <t xml:space="preserve">130.531845092773</t>
+    <t xml:space="preserve">130.531860351562</t>
   </si>
   <si>
     <t xml:space="preserve">128.593734741211</t>
@@ -3695,13 +3695,13 @@
     <t xml:space="preserve">123.845367431641</t>
   </si>
   <si>
-    <t xml:space="preserve">121.422729492188</t>
+    <t xml:space="preserve">121.422737121582</t>
   </si>
   <si>
     <t xml:space="preserve">121.325813293457</t>
   </si>
   <si>
-    <t xml:space="preserve">120.259864807129</t>
+    <t xml:space="preserve">120.259857177734</t>
   </si>
   <si>
     <t xml:space="preserve">120.35676574707</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">113.86408996582</t>
   </si>
   <si>
-    <t xml:space="preserve">113.960998535156</t>
+    <t xml:space="preserve">113.960990905762</t>
   </si>
   <si>
     <t xml:space="preserve">113.088836669922</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">110.956916809082</t>
   </si>
   <si>
-    <t xml:space="preserve">108.921913146973</t>
+    <t xml:space="preserve">108.921905517578</t>
   </si>
   <si>
     <t xml:space="preserve">107.952842712402</t>
@@ -3797,13 +3797,13 @@
     <t xml:space="preserve">103.592094421387</t>
   </si>
   <si>
-    <t xml:space="preserve">106.88688659668</t>
+    <t xml:space="preserve">106.886894226074</t>
   </si>
   <si>
     <t xml:space="preserve">103.204475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">100.588020324707</t>
+    <t xml:space="preserve">100.588027954102</t>
   </si>
   <si>
     <t xml:space="preserve">100.297302246094</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">102.719947814941</t>
   </si>
   <si>
-    <t xml:space="preserve">103.107566833496</t>
+    <t xml:space="preserve">103.107574462891</t>
   </si>
   <si>
     <t xml:space="preserve">104.561157226562</t>
@@ -3830,10 +3830,10 @@
     <t xml:space="preserve">110.084770202637</t>
   </si>
   <si>
-    <t xml:space="preserve">116.480545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.705299377441</t>
+    <t xml:space="preserve">116.480537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.705307006836</t>
   </si>
   <si>
     <t xml:space="preserve">113.37956237793</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">102.235412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">102.623046875</t>
+    <t xml:space="preserve">102.623039245605</t>
   </si>
   <si>
     <t xml:space="preserve">104.173522949219</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">100.394203186035</t>
   </si>
   <si>
-    <t xml:space="preserve">99.3282470703125</t>
+    <t xml:space="preserve">99.328254699707</t>
   </si>
   <si>
     <t xml:space="preserve">99.6189651489258</t>
@@ -3929,16 +3929,16 @@
     <t xml:space="preserve">99.0078277587891</t>
   </si>
   <si>
-    <t xml:space="preserve">98.6164932250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.573173522949</t>
+    <t xml:space="preserve">98.6165008544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.573181152344</t>
   </si>
   <si>
     <t xml:space="preserve">97.051155090332</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0672302246094</t>
+    <t xml:space="preserve">94.0672225952148</t>
   </si>
   <si>
     <t xml:space="preserve">95.8771438598633</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">95.7793197631836</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5780487060547</t>
+    <t xml:space="preserve">93.5780563354492</t>
   </si>
   <si>
     <t xml:space="preserve">92.5997161865234</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">90.0071182250977</t>
   </si>
   <si>
-    <t xml:space="preserve">90.4962844848633</t>
+    <t xml:space="preserve">90.4962921142578</t>
   </si>
   <si>
     <t xml:space="preserve">90.8386993408203</t>
@@ -3995,13 +3995,13 @@
     <t xml:space="preserve">92.3062133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">92.942138671875</t>
+    <t xml:space="preserve">92.9421310424805</t>
   </si>
   <si>
     <t xml:space="preserve">91.2789611816406</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6213760375977</t>
+    <t xml:space="preserve">91.6213836669922</t>
   </si>
   <si>
     <t xml:space="preserve">90.6430435180664</t>
@@ -4052,28 +4052,28 @@
     <t xml:space="preserve">103.508193969727</t>
   </si>
   <si>
-    <t xml:space="preserve">103.703857421875</t>
+    <t xml:space="preserve">103.70384979248</t>
   </si>
   <si>
     <t xml:space="preserve">106.051864624023</t>
   </si>
   <si>
-    <t xml:space="preserve">104.975700378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.171356201172</t>
+    <t xml:space="preserve">104.975692749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.171363830566</t>
   </si>
   <si>
     <t xml:space="preserve">102.627685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">101.747184753418</t>
+    <t xml:space="preserve">101.747177124023</t>
   </si>
   <si>
     <t xml:space="preserve">103.997360229492</t>
   </si>
   <si>
-    <t xml:space="preserve">102.529846191406</t>
+    <t xml:space="preserve">102.529853820801</t>
   </si>
   <si>
     <t xml:space="preserve">100.377502441406</t>
@@ -4085,10 +4085,10 @@
     <t xml:space="preserve">104.193023681641</t>
   </si>
   <si>
-    <t xml:space="preserve">106.541030883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.617210388184</t>
+    <t xml:space="preserve">106.541038513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.617202758789</t>
   </si>
   <si>
     <t xml:space="preserve">106.834533691406</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">105.85619354248</t>
   </si>
   <si>
-    <t xml:space="preserve">111.530563354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.367736816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.291572570801</t>
+    <t xml:space="preserve">111.530555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.367744445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.291564941406</t>
   </si>
   <si>
     <t xml:space="preserve">117.694091796875</t>
@@ -4112,22 +4112,22 @@
     <t xml:space="preserve">118.672431945801</t>
   </si>
   <si>
-    <t xml:space="preserve">118.378921508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.259429931641</t>
+    <t xml:space="preserve">118.378929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.259437561035</t>
   </si>
   <si>
     <t xml:space="preserve">120.335601806641</t>
   </si>
   <si>
-    <t xml:space="preserve">118.085426330566</t>
+    <t xml:space="preserve">118.085418701172</t>
   </si>
   <si>
     <t xml:space="preserve">115.346084594727</t>
   </si>
   <si>
-    <t xml:space="preserve">115.737411499023</t>
+    <t xml:space="preserve">115.737419128418</t>
   </si>
   <si>
     <t xml:space="preserve">113.682907104492</t>
@@ -4142,19 +4142,19 @@
     <t xml:space="preserve">111.921897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">111.824058532715</t>
+    <t xml:space="preserve">111.824066162109</t>
   </si>
   <si>
     <t xml:space="preserve">114.074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">113.976402282715</t>
+    <t xml:space="preserve">113.976409912109</t>
   </si>
   <si>
     <t xml:space="preserve">112.802406311035</t>
   </si>
   <si>
-    <t xml:space="preserve">112.31324005127</t>
+    <t xml:space="preserve">112.313232421875</t>
   </si>
   <si>
     <t xml:space="preserve">114.856910705566</t>
@@ -4175,10 +4175,10 @@
     <t xml:space="preserve">122.585784912109</t>
   </si>
   <si>
-    <t xml:space="preserve">122.781448364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.368453979492</t>
+    <t xml:space="preserve">122.781455993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.368446350098</t>
   </si>
   <si>
     <t xml:space="preserve">120.433433532715</t>
@@ -4193,13 +4193,13 @@
     <t xml:space="preserve">122.194450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">121.803108215332</t>
+    <t xml:space="preserve">121.803115844727</t>
   </si>
   <si>
     <t xml:space="preserve">120.042098999023</t>
   </si>
   <si>
-    <t xml:space="preserve">119.455101013184</t>
+    <t xml:space="preserve">119.455093383789</t>
   </si>
   <si>
     <t xml:space="preserve">118.574592590332</t>
@@ -4235,31 +4235,31 @@
     <t xml:space="preserve">112.019729614258</t>
   </si>
   <si>
-    <t xml:space="preserve">112.900238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.095893859863</t>
+    <t xml:space="preserve">112.900230407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.095901489258</t>
   </si>
   <si>
     <t xml:space="preserve">110.943557739258</t>
   </si>
   <si>
-    <t xml:space="preserve">111.334892272949</t>
+    <t xml:space="preserve">111.334899902344</t>
   </si>
   <si>
     <t xml:space="preserve">110.747886657715</t>
   </si>
   <si>
-    <t xml:space="preserve">110.063049316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.671722412109</t>
+    <t xml:space="preserve">110.063056945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.671714782715</t>
   </si>
   <si>
     <t xml:space="preserve">102.725517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">100.181838989258</t>
+    <t xml:space="preserve">100.181831359863</t>
   </si>
   <si>
     <t xml:space="preserve">96.8554840087891</t>
@@ -4292,10 +4292,10 @@
     <t xml:space="preserve">98.322998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">96.8065643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2195587158203</t>
+    <t xml:space="preserve">96.8065719604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2195663452148</t>
   </si>
   <si>
     <t xml:space="preserve">94.9966430664062</t>
@@ -4313,7 +4313,7 @@
     <t xml:space="preserve">95.7303924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">97.9316558837891</t>
+    <t xml:space="preserve">97.9316635131836</t>
   </si>
   <si>
     <t xml:space="preserve">95.8282318115234</t>
@@ -4346,7 +4346,7 @@
     <t xml:space="preserve">106.638870239258</t>
   </si>
   <si>
-    <t xml:space="preserve">107.128036499023</t>
+    <t xml:space="preserve">107.128044128418</t>
   </si>
   <si>
     <t xml:space="preserve">105.954032897949</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">104.682189941406</t>
   </si>
   <si>
-    <t xml:space="preserve">103.899513244629</t>
+    <t xml:space="preserve">103.899520874023</t>
   </si>
   <si>
     <t xml:space="preserve">104.78002166748</t>
@@ -4367,10 +4367,10 @@
     <t xml:space="preserve">105.660530090332</t>
   </si>
   <si>
-    <t xml:space="preserve">106.345367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.443199157715</t>
+    <t xml:space="preserve">106.345359802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.443206787109</t>
   </si>
   <si>
     <t xml:space="preserve">103.801681518555</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">112.704566955566</t>
   </si>
   <si>
-    <t xml:space="preserve">114.172073364258</t>
+    <t xml:space="preserve">114.172065734863</t>
   </si>
   <si>
     <t xml:space="preserve">117.107086181641</t>
@@ -4394,10 +4394,10 @@
     <t xml:space="preserve">115.150405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">116.813591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.204925537109</t>
+    <t xml:space="preserve">116.813583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.204917907715</t>
   </si>
   <si>
     <t xml:space="preserve">116.128746032715</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">96.5619812011719</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2628860473633</t>
+    <t xml:space="preserve">94.2628936767578</t>
   </si>
   <si>
     <t xml:space="preserve">91.3767929077148</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">95.3390579223633</t>
   </si>
   <si>
-    <t xml:space="preserve">94.3118133544922</t>
+    <t xml:space="preserve">94.3118057250977</t>
   </si>
   <si>
     <t xml:space="preserve">93.4802169799805</t>
@@ -4454,28 +4454,28 @@
     <t xml:space="preserve">94.7031478881836</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8498840332031</t>
+    <t xml:space="preserve">94.8498916625977</t>
   </si>
   <si>
     <t xml:space="preserve">94.2139739990234</t>
   </si>
   <si>
-    <t xml:space="preserve">91.8659591674805</t>
+    <t xml:space="preserve">91.865966796875</t>
   </si>
   <si>
     <t xml:space="preserve">90.6919479370117</t>
   </si>
   <si>
-    <t xml:space="preserve">89.2244415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7080230712891</t>
+    <t xml:space="preserve">89.2244491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7080307006836</t>
   </si>
   <si>
     <t xml:space="preserve">85.751350402832</t>
   </si>
   <si>
-    <t xml:space="preserve">84.5284194946289</t>
+    <t xml:space="preserve">84.5284271240234</t>
   </si>
   <si>
     <t xml:space="preserve">84.3327560424805</t>
@@ -4484,13 +4484,13 @@
     <t xml:space="preserve">86.2894287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2517013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.441780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0287857055664</t>
+    <t xml:space="preserve">90.251708984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4417724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0287780761719</t>
   </si>
   <si>
     <t xml:space="preserve">88.4906921386719</t>
@@ -5193,6 +5193,9 @@
   </si>
   <si>
     <t xml:space="preserve">81.1999969482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.5999984741211</t>
   </si>
 </sst>
 </file>
@@ -70531,7 +70534,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6910532407</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>22524</v>
@@ -70552,6 +70555,32 @@
         <v>1726</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6911805556</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>37417</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>81.5500030517578</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>79.8000030517578</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>81.1999969482422</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>80.5999984741211</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1727</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -50,37 +50,37 @@
     <t xml:space="preserve">13.2523736953735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9464139938354</t>
+    <t xml:space="preserve">12.9464149475098</t>
   </si>
   <si>
     <t xml:space="preserve">13.1125068664551</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8589992523193</t>
+    <t xml:space="preserve">12.858998298645</t>
   </si>
   <si>
     <t xml:space="preserve">13.0513143539429</t>
   </si>
   <si>
-    <t xml:space="preserve">12.990122795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9376726150513</t>
+    <t xml:space="preserve">12.9901237487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9376745223999</t>
   </si>
   <si>
     <t xml:space="preserve">13.1037654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">13.025089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8502569198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2383403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5880069732666</t>
+    <t xml:space="preserve">13.0250911712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8502559661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2383394241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5880060195923</t>
   </si>
   <si>
     <t xml:space="preserve">12.7890663146973</t>
@@ -89,25 +89,25 @@
     <t xml:space="preserve">12.7191314697266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6841659545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.605489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.325756072998</t>
+    <t xml:space="preserve">12.6841640472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6054887771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.325758934021</t>
   </si>
   <si>
     <t xml:space="preserve">12.0460224151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.177149772644</t>
+    <t xml:space="preserve">12.1771488189697</t>
   </si>
   <si>
     <t xml:space="preserve">12.1421823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9270896911621</t>
+    <t xml:space="preserve">10.9270877838135</t>
   </si>
   <si>
     <t xml:space="preserve">10.9795398712158</t>
@@ -116,76 +116,76 @@
     <t xml:space="preserve">11.3641719818115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4515895843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0984735488892</t>
+    <t xml:space="preserve">11.451587677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0984725952148</t>
   </si>
   <si>
     <t xml:space="preserve">12.1072149276733</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8886737823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9760894775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9323806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0110549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0809898376465</t>
+    <t xml:space="preserve">11.8886728286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9760885238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9323816299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0110569000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0809888839722</t>
   </si>
   <si>
     <t xml:space="preserve">11.8012571334839</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1334409713745</t>
+    <t xml:space="preserve">12.1334390640259</t>
   </si>
   <si>
     <t xml:space="preserve">11.8274812698364</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0635080337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5005893707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6754245758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7978076934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1649570465088</t>
+    <t xml:space="preserve">12.0635061264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5005903244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6754217147827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7978057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1649580001831</t>
   </si>
   <si>
     <t xml:space="preserve">13.1562156677246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0687971115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1212472915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.19118309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7540988922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8939647674561</t>
+    <t xml:space="preserve">13.0687980651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1212491989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1911821365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7540979385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8939657211304</t>
   </si>
   <si>
     <t xml:space="preserve">12.9027070999146</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0600557327271</t>
+    <t xml:space="preserve">13.0600576400757</t>
   </si>
   <si>
     <t xml:space="preserve">13.1999244689941</t>
@@ -194,31 +194,31 @@
     <t xml:space="preserve">12.9813823699951</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4534311294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7069416046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4709167480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4621725082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2086639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3223075866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0950231552124</t>
+    <t xml:space="preserve">13.4534320831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7069425582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4709157943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4621734619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2086658477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.322304725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0950241088867</t>
   </si>
   <si>
     <t xml:space="preserve">12.9988641738892</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6404581069946</t>
+    <t xml:space="preserve">12.6404552459717</t>
   </si>
   <si>
     <t xml:space="preserve">12.4481401443481</t>
@@ -236,76 +236,76 @@
     <t xml:space="preserve">12.4393978118896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5617818832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5268154144287</t>
+    <t xml:space="preserve">12.5617809295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5268135070801</t>
   </si>
   <si>
     <t xml:space="preserve">12.6317157745361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3694658279419</t>
+    <t xml:space="preserve">12.3694648742676</t>
   </si>
   <si>
     <t xml:space="preserve">12.771580696106</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4306583404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2820491790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1946315765381</t>
+    <t xml:space="preserve">12.4306573867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2820482254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1946325302124</t>
   </si>
   <si>
     <t xml:space="preserve">12.2470817565918</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4131736755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5093326568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3869476318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8187398910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8449649810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2558240890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5792655944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2208557128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1858911514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7803230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7278738021851</t>
+    <t xml:space="preserve">12.4131727218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5093336105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3869495391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8187408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8449640274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.255823135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5792646408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2208547592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1858892440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7803239822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7278728485107</t>
   </si>
   <si>
     <t xml:space="preserve">12.8764810562134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8065490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7628412246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8677406311035</t>
+    <t xml:space="preserve">12.806547164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7628402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8677387237549</t>
   </si>
   <si>
     <t xml:space="preserve">12.8327732086182</t>
@@ -314,151 +314,151 @@
     <t xml:space="preserve">12.5355577468872</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1824398040771</t>
+    <t xml:space="preserve">13.1824407577515</t>
   </si>
   <si>
     <t xml:space="preserve">13.0338315963745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3048238754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2611150741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3747577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6020412445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6894559860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7244234085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7514753341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5711288452148</t>
+    <t xml:space="preserve">13.3048248291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2611141204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3747568130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6020402908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6894569396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7244243621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7514762878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5711307525635</t>
   </si>
   <si>
     <t xml:space="preserve">13.8687019348145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6252326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6432666778564</t>
+    <t xml:space="preserve">13.6252317428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6432676315308</t>
   </si>
   <si>
     <t xml:space="preserve">13.661301612854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5981817245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6162166595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5260419845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5530939102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3456945419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801458358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6973705291748</t>
+    <t xml:space="preserve">13.5981798171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6162157058716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5260429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5530948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3456964492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801448822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6973714828491</t>
   </si>
   <si>
     <t xml:space="preserve">13.778528213501</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6703195571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7965641021729</t>
+    <t xml:space="preserve">13.6703205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7965621948242</t>
   </si>
   <si>
     <t xml:space="preserve">13.9769105911255</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0400314331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0129795074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9047718048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1031522750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2474317550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1572580337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3646583557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4187612533569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5179510116577</t>
+    <t xml:space="preserve">14.0400304794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0129804611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9047708511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1031541824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2474308013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1572570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3646554946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4187602996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.517951965332</t>
   </si>
   <si>
     <t xml:space="preserve">14.6081266403198</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6622304916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3917093276978</t>
+    <t xml:space="preserve">14.6622295379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3917083740234</t>
   </si>
   <si>
     <t xml:space="preserve">14.3105516433716</t>
   </si>
   <si>
-    <t xml:space="preserve">14.30153465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5450029373169</t>
+    <t xml:space="preserve">14.3015365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5450019836426</t>
   </si>
   <si>
     <t xml:space="preserve">14.6441946029663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7343692779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7163343429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6351766586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6261596679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6892824172974</t>
+    <t xml:space="preserve">14.7343664169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7163333892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6351776123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6261568069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6892833709717</t>
   </si>
   <si>
     <t xml:space="preserve">14.8245420455933</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8065071105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7433862686157</t>
+    <t xml:space="preserve">14.80650806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.74338722229</t>
   </si>
   <si>
     <t xml:space="preserve">14.581072807312</t>
@@ -470,70 +470,70 @@
     <t xml:space="preserve">14.5089340209961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6712474822998</t>
+    <t xml:space="preserve">14.6712465286255</t>
   </si>
   <si>
     <t xml:space="preserve">14.6532135009766</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9237327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0499773025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2122917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3745985031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5549459457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9246606826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7803821563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8705568313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344860076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7082433700562</t>
+    <t xml:space="preserve">14.9237308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.049976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2122898101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3746004104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5549516677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9246597290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7803812026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8705558776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344869613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7082443237305</t>
   </si>
   <si>
     <t xml:space="preserve">15.9517107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7452392578125</t>
+    <t xml:space="preserve">16.7452373504639</t>
   </si>
   <si>
     <t xml:space="preserve">16.8714809417725</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0878982543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1510238647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2231597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9796905517578</t>
+    <t xml:space="preserve">17.0879001617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1510200500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2231616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9796924591064</t>
   </si>
   <si>
     <t xml:space="preserve">16.9075508117676</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3043174743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0337924957275</t>
+    <t xml:space="preserve">17.3043155670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0337944030762</t>
   </si>
   <si>
     <t xml:space="preserve">17.2772636413574</t>
@@ -542,22 +542,22 @@
     <t xml:space="preserve">17.4756450653076</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3223495483398</t>
+    <t xml:space="preserve">17.3223514556885</t>
   </si>
   <si>
     <t xml:space="preserve">17.1690559387207</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5838527679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5748348236084</t>
+    <t xml:space="preserve">17.583854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.574836730957</t>
   </si>
   <si>
     <t xml:space="preserve">17.5658206939697</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2411937713623</t>
+    <t xml:space="preserve">17.2411956787109</t>
   </si>
   <si>
     <t xml:space="preserve">17.1870899200439</t>
@@ -566,10 +566,10 @@
     <t xml:space="preserve">16.8534469604492</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8444309234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9526386260986</t>
+    <t xml:space="preserve">16.8444328308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.95263671875</t>
   </si>
   <si>
     <t xml:space="preserve">16.7272033691406</t>
@@ -578,22 +578,22 @@
     <t xml:space="preserve">16.6911354064941</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8624668121338</t>
+    <t xml:space="preserve">16.8624687194824</t>
   </si>
   <si>
     <t xml:space="preserve">17.0428123474121</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8173770904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9977245330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7722911834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.006742477417</t>
+    <t xml:space="preserve">16.8173789978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9977283477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7722930908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0067443847656</t>
   </si>
   <si>
     <t xml:space="preserve">17.1961059570312</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">17.6199264526367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7642002105713</t>
+    <t xml:space="preserve">17.7642040252686</t>
   </si>
   <si>
     <t xml:space="preserve">18.0076694488525</t>
@@ -614,28 +614,28 @@
     <t xml:space="preserve">17.9896354675293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9445476531982</t>
+    <t xml:space="preserve">17.9445495605469</t>
   </si>
   <si>
     <t xml:space="preserve">17.9535655975342</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8092880249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2601566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7561092376709</t>
+    <t xml:space="preserve">17.8092918395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2601585388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7561111450195</t>
   </si>
   <si>
     <t xml:space="preserve">18.8462867736816</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9364566802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.620849609375</t>
+    <t xml:space="preserve">18.9364604949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6208477020264</t>
   </si>
   <si>
     <t xml:space="preserve">19.2971515655518</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">19.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6668643951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6488285064697</t>
+    <t xml:space="preserve">19.666862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6488304138184</t>
   </si>
   <si>
     <t xml:space="preserve">19.5586566925049</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">19.252067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1709098815918</t>
+    <t xml:space="preserve">19.1709117889404</t>
   </si>
   <si>
     <t xml:space="preserve">19.1348400115967</t>
@@ -668,61 +668,61 @@
     <t xml:space="preserve">19.197961807251</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9544925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9094047546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0897521972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5757637023926</t>
+    <t xml:space="preserve">18.9544944763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9094085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0897541046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5757656097412</t>
   </si>
   <si>
     <t xml:space="preserve">18.1970367431641</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5306777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8372688293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4594631195068</t>
+    <t xml:space="preserve">18.5306797027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8372650146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4594650268555</t>
   </si>
   <si>
     <t xml:space="preserve">19.3873252868652</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0185413360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3612003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8301029205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2809753417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8751926422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9292945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1006240844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0104484558105</t>
+    <t xml:space="preserve">20.0185432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3612041473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8301048278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2809734344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8751907348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.929292678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.100622177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0104503631592</t>
   </si>
   <si>
     <t xml:space="preserve">20.5685997009277</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7218952178955</t>
+    <t xml:space="preserve">20.7218914031982</t>
   </si>
   <si>
     <t xml:space="preserve">20.6046714782715</t>
@@ -740,55 +740,55 @@
     <t xml:space="preserve">21.6416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3711452484131</t>
+    <t xml:space="preserve">21.3711471557617</t>
   </si>
   <si>
     <t xml:space="preserve">21.3801612854004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0925369262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6245613098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7147331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8049049377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5984344482422</t>
+    <t xml:space="preserve">22.0925350189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6245594024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7147350311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8049087524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5984325408936</t>
   </si>
   <si>
     <t xml:space="preserve">24.0763568878174</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0583209991455</t>
+    <t xml:space="preserve">24.0583229064941</t>
   </si>
   <si>
     <t xml:space="preserve">23.7156600952148</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9320793151855</t>
+    <t xml:space="preserve">23.9320774078369</t>
   </si>
   <si>
     <t xml:space="preserve">23.8599376678467</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8058338165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5082588195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9942722320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4802837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5434017181396</t>
+    <t xml:space="preserve">23.8058319091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5082607269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9942741394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4802799224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5434055328369</t>
   </si>
   <si>
     <t xml:space="preserve">22.7057151794434</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">22.0023593902588</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1827068328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7237491607666</t>
+    <t xml:space="preserve">22.1827087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7237510681152</t>
   </si>
   <si>
     <t xml:space="preserve">22.3630542755127</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">22.2097587585449</t>
   </si>
   <si>
-    <t xml:space="preserve">21.488374710083</t>
+    <t xml:space="preserve">21.4883728027344</t>
   </si>
   <si>
     <t xml:space="preserve">21.9212055206299</t>
@@ -830,73 +830,73 @@
     <t xml:space="preserve">21.9392395019531</t>
   </si>
   <si>
-    <t xml:space="preserve">22.074499130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2999362945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8139247894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3179683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1917266845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.354040145874</t>
+    <t xml:space="preserve">22.0745010375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2999324798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8139209747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3179702758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1917285919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3540382385254</t>
   </si>
   <si>
     <t xml:space="preserve">22.5253677368164</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6065273284912</t>
+    <t xml:space="preserve">22.6065254211426</t>
   </si>
   <si>
     <t xml:space="preserve">22.6335754394531</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2458324432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2277965545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1286029815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0835189819336</t>
+    <t xml:space="preserve">22.2458305358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2277946472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1286067962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.083517074585</t>
   </si>
   <si>
     <t xml:space="preserve">22.2007446289062</t>
   </si>
   <si>
-    <t xml:space="preserve">22.137622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1466369628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5965824127197</t>
+    <t xml:space="preserve">22.1376190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1466388702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5965805053711</t>
   </si>
   <si>
     <t xml:space="preserve">21.3260593414307</t>
   </si>
   <si>
-    <t xml:space="preserve">21.560510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0294170379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6867542266846</t>
+    <t xml:space="preserve">21.5605125427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0294132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6867523193359</t>
   </si>
   <si>
     <t xml:space="preserve">22.2368144989014</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3720741271973</t>
+    <t xml:space="preserve">22.3720760345459</t>
   </si>
   <si>
     <t xml:space="preserve">22.3991241455078</t>
@@ -917,10 +917,10 @@
     <t xml:space="preserve">23.2704582214355</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1739845275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7087268829346</t>
+    <t xml:space="preserve">24.1739864349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7087249755859</t>
   </si>
   <si>
     <t xml:space="preserve">24.7732639312744</t>
@@ -929,7 +929,7 @@
     <t xml:space="preserve">25.2434673309326</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8150863647461</t>
+    <t xml:space="preserve">25.8150882720947</t>
   </si>
   <si>
     <t xml:space="preserve">25.7966480255127</t>
@@ -941,13 +941,13 @@
     <t xml:space="preserve">25.6675720214844</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0086975097656</t>
+    <t xml:space="preserve">26.0086994171143</t>
   </si>
   <si>
     <t xml:space="preserve">25.8888454437256</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9810409545898</t>
+    <t xml:space="preserve">25.9810390472412</t>
   </si>
   <si>
     <t xml:space="preserve">26.0916748046875</t>
@@ -965,22 +965,22 @@
     <t xml:space="preserve">25.6767902374268</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6583499908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0775127410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4001998901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2619075775146</t>
+    <t xml:space="preserve">25.6583518981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0775108337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4001979827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.261905670166</t>
   </si>
   <si>
     <t xml:space="preserve">25.3264427185059</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8009204864502</t>
+    <t xml:space="preserve">24.8009223937988</t>
   </si>
   <si>
     <t xml:space="preserve">25.4186420440674</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">24.8562393188477</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9576568603516</t>
+    <t xml:space="preserve">24.9576587677002</t>
   </si>
   <si>
     <t xml:space="preserve">24.8931198120117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1874809265137</t>
+    <t xml:space="preserve">23.187479019165</t>
   </si>
   <si>
     <t xml:space="preserve">22.9754257202148</t>
@@ -1007,55 +1007,55 @@
     <t xml:space="preserve">23.1229419708252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2335777282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9938697814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.781810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.671178817749</t>
+    <t xml:space="preserve">23.2335796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9938678741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7818145751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6711769104004</t>
   </si>
   <si>
     <t xml:space="preserve">22.4960021972656</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7264957427979</t>
+    <t xml:space="preserve">22.7264976501465</t>
   </si>
   <si>
     <t xml:space="preserve">22.5052242279053</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3208293914795</t>
+    <t xml:space="preserve">22.3208312988281</t>
   </si>
   <si>
     <t xml:space="preserve">22.5881996154785</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1137218475342</t>
+    <t xml:space="preserve">23.1137199401855</t>
   </si>
   <si>
     <t xml:space="preserve">22.910888671875</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3995342254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7775382995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6208057403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1413822174072</t>
+    <t xml:space="preserve">23.3995304107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7775402069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6208038330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1413803100586</t>
   </si>
   <si>
     <t xml:space="preserve">22.9846458435059</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8740100860596</t>
+    <t xml:space="preserve">22.8740119934082</t>
   </si>
   <si>
     <t xml:space="preserve">22.7357177734375</t>
@@ -1064,31 +1064,31 @@
     <t xml:space="preserve">22.6896190643311</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3257751464844</t>
+    <t xml:space="preserve">23.3257713317871</t>
   </si>
   <si>
     <t xml:space="preserve">23.7406597137451</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9803733825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9711532592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.063346862793</t>
+    <t xml:space="preserve">23.980375289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9711513519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0633487701416</t>
   </si>
   <si>
     <t xml:space="preserve">24.2477416992188</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3860397338867</t>
+    <t xml:space="preserve">24.3860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">24.1555442810059</t>
   </si>
   <si>
-    <t xml:space="preserve">24.616527557373</t>
+    <t xml:space="preserve">24.6165294647217</t>
   </si>
   <si>
     <t xml:space="preserve">25.8611831665039</t>
@@ -1097,52 +1097,52 @@
     <t xml:space="preserve">25.6306915283203</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2158126831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1697101593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080043792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4463005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5384960174561</t>
+    <t xml:space="preserve">25.2158107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1697082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4462985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5384979248047</t>
   </si>
   <si>
     <t xml:space="preserve">25.1236095428467</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4321365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6484622955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0172481536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.109447479248</t>
+    <t xml:space="preserve">24.4321346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6484642028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0172519683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1094455718994</t>
   </si>
   <si>
     <t xml:space="preserve">24.339937210083</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2016429901123</t>
+    <t xml:space="preserve">24.2016448974609</t>
   </si>
   <si>
     <t xml:space="preserve">24.2938404083252</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7548236846924</t>
+    <t xml:space="preserve">24.754825592041</t>
   </si>
   <si>
     <t xml:space="preserve">24.6626281738281</t>
   </si>
   <si>
-    <t xml:space="preserve">24.985315322876</t>
+    <t xml:space="preserve">24.9853172302246</t>
   </si>
   <si>
     <t xml:space="preserve">25.4923973083496</t>
@@ -1151,10 +1151,10 @@
     <t xml:space="preserve">25.7228870391846</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5704307556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5845947265625</t>
+    <t xml:space="preserve">24.570426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5845928192139</t>
   </si>
   <si>
     <t xml:space="preserve">25.9994812011719</t>
@@ -1163,43 +1163,43 @@
     <t xml:space="preserve">26.414363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5668239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7512168884277</t>
+    <t xml:space="preserve">27.5668277740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.751220703125</t>
   </si>
   <si>
     <t xml:space="preserve">28.0739078521729</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5207252502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7370548248291</t>
+    <t xml:space="preserve">27.5207271575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7370529174805</t>
   </si>
   <si>
     <t xml:space="preserve">26.5065631866455</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0314159393311</t>
+    <t xml:space="preserve">25.0314140319824</t>
   </si>
   <si>
     <t xml:space="preserve">24.5243339538574</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3682670593262</t>
+    <t xml:space="preserve">26.3682689666748</t>
   </si>
   <si>
     <t xml:space="preserve">26.5987606048584</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4604644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2299728393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3221664428711</t>
+    <t xml:space="preserve">26.4604682922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2299709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3221702575684</t>
   </si>
   <si>
     <t xml:space="preserve">27.1980381011963</t>
@@ -1208,40 +1208,40 @@
     <t xml:space="preserve">26.2760715484619</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2902355194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3824329376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4746246337891</t>
+    <t xml:space="preserve">27.2902374267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3824310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4746265411377</t>
   </si>
   <si>
     <t xml:space="preserve">26.552661895752</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8292503356934</t>
+    <t xml:space="preserve">26.829252243042</t>
   </si>
   <si>
     <t xml:space="preserve">27.105842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8753509521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8434162139893</t>
+    <t xml:space="preserve">26.8753490447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8434143066406</t>
   </si>
   <si>
     <t xml:space="preserve">28.7653846740723</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5809879302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9356098175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8114795684814</t>
+    <t xml:space="preserve">28.5809898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9356117248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8114814758301</t>
   </si>
   <si>
     <t xml:space="preserve">28.1661033630371</t>
@@ -1253,16 +1253,16 @@
     <t xml:space="preserve">28.1200065612793</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0597457885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9675445556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1519393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6909561157227</t>
+    <t xml:space="preserve">27.0597438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9675464630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1519412994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6909580230713</t>
   </si>
   <si>
     <t xml:space="preserve">26.7831554412842</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">26.0455780029297</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6590194702148</t>
+    <t xml:space="preserve">27.6590213775635</t>
   </si>
   <si>
     <t xml:space="preserve">26.9214496612549</t>
@@ -1283,67 +1283,67 @@
     <t xml:space="preserve">26.0886974334717</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4654293060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2299709320068</t>
+    <t xml:space="preserve">26.4654273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2299690246582</t>
   </si>
   <si>
     <t xml:space="preserve">25.8061485290527</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7119655609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1468658447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3352317810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.911413192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4875869750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3934020996094</t>
+    <t xml:space="preserve">25.7119636535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1468677520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3352336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9114093780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.487585067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3934001922607</t>
   </si>
   <si>
     <t xml:space="preserve">23.9224872589111</t>
   </si>
   <si>
-    <t xml:space="preserve">23.263204574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0277519226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0748405456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7451972961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6039257049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.509744644165</t>
+    <t xml:space="preserve">23.2632064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0277500152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0748386383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7451992034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6039237976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5097427368164</t>
   </si>
   <si>
     <t xml:space="preserve">22.4155578613281</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1801013946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0388278961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8504638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4626483917236</t>
+    <t xml:space="preserve">22.180103302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0388259887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8504619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4626522064209</t>
   </si>
   <si>
     <t xml:space="preserve">22.2271938323975</t>
@@ -1361,25 +1361,25 @@
     <t xml:space="preserve">23.498664855957</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5568370819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1330070495605</t>
+    <t xml:space="preserve">22.5568332672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1330089569092</t>
   </si>
   <si>
     <t xml:space="preserve">21.6620941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1911792755127</t>
+    <t xml:space="preserve">21.19118309021</t>
   </si>
   <si>
     <t xml:space="preserve">21.0028133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.096996307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8615398406982</t>
+    <t xml:space="preserve">21.0969982147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8615379333496</t>
   </si>
   <si>
     <t xml:space="preserve">21.379545211792</t>
@@ -1391,46 +1391,46 @@
     <t xml:space="preserve">22.274284362793</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7562789916992</t>
+    <t xml:space="preserve">21.7562770843506</t>
   </si>
   <si>
     <t xml:space="preserve">21.9446449279785</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5679111480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5208225250244</t>
+    <t xml:space="preserve">21.5679130554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5208206176758</t>
   </si>
   <si>
     <t xml:space="preserve">21.3324546813965</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2382717132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8393840789795</t>
+    <t xml:space="preserve">21.2382698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8393821716309</t>
   </si>
   <si>
     <t xml:space="preserve">22.792293548584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5457553863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6399402618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7341213226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6870307922363</t>
+    <t xml:space="preserve">23.5457572937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6399383544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7341232299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6870288848877</t>
   </si>
   <si>
     <t xml:space="preserve">23.781213760376</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0166683197021</t>
+    <t xml:space="preserve">24.0166702270508</t>
   </si>
   <si>
     <t xml:space="preserve">24.2992191314697</t>
@@ -1439,31 +1439,31 @@
     <t xml:space="preserve">24.1579456329346</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2521286010742</t>
+    <t xml:space="preserve">24.2521266937256</t>
   </si>
   <si>
     <t xml:space="preserve">24.7230434417725</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6288604736328</t>
+    <t xml:space="preserve">24.6288585662842</t>
   </si>
   <si>
     <t xml:space="preserve">24.6759510040283</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5817680358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7701358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9585018157959</t>
+    <t xml:space="preserve">24.5817699432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.770133972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9584999084473</t>
   </si>
   <si>
     <t xml:space="preserve">25.9003314971924</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7590599060059</t>
+    <t xml:space="preserve">25.7590579986572</t>
   </si>
   <si>
     <t xml:space="preserve">25.9474201202393</t>
@@ -1472,22 +1472,22 @@
     <t xml:space="preserve">26.2770614624023</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9363441467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.983434677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8421630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7479763031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.265983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4543514251709</t>
+    <t xml:space="preserve">26.9363460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9834365844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8421611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7479782104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2659873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4543495178223</t>
   </si>
   <si>
     <t xml:space="preserve">27.501443862915</t>
@@ -1499,82 +1499,82 @@
     <t xml:space="preserve">27.0776195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7008857727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6537952423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6067047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.994514465332</t>
+    <t xml:space="preserve">26.7008838653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6537933349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6067028045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9945125579834</t>
   </si>
   <si>
     <t xml:space="preserve">26.1357879638672</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0416069030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6177806854248</t>
+    <t xml:space="preserve">26.0416049957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6177787780762</t>
   </si>
   <si>
     <t xml:space="preserve">25.4294166564941</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0055885314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0997753143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8643169403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4404964447021</t>
+    <t xml:space="preserve">25.0055904388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0997714996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.864315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4404945373535</t>
   </si>
   <si>
     <t xml:space="preserve">25.5235977172852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3712463378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3241558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7950706481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8892498016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0305290222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1718044281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5485324859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6898097991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1136322021484</t>
+    <t xml:space="preserve">26.3712482452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3241539001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7950687408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.889253616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0305309295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.171802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5485343933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6898078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1136341094971</t>
   </si>
   <si>
     <t xml:space="preserve">28.3961811065674</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7258243560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9141864776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9501991271973</t>
+    <t xml:space="preserve">28.7258224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9141902923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9502010345459</t>
   </si>
   <si>
     <t xml:space="preserve">29.7618350982666</t>
@@ -1586,43 +1586,43 @@
     <t xml:space="preserve">30.3740253448486</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5042190551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6925926208496</t>
+    <t xml:space="preserve">31.504222869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6925868988037</t>
   </si>
   <si>
     <t xml:space="preserve">32.4460487365723</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4931411743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4820594787598</t>
+    <t xml:space="preserve">32.4931488037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4820671081543</t>
   </si>
   <si>
     <t xml:space="preserve">33.6704292297363</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2936935424805</t>
+    <t xml:space="preserve">33.293701171875</t>
   </si>
   <si>
     <t xml:space="preserve">33.5762481689453</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9058837890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2466049194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.869873046875</t>
+    <t xml:space="preserve">33.9058876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2466087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8698768615723</t>
   </si>
   <si>
     <t xml:space="preserve">33.1524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">33.058235168457</t>
+    <t xml:space="preserve">33.0582427978516</t>
   </si>
   <si>
     <t xml:space="preserve">32.5873260498047</t>
@@ -1631,22 +1631,22 @@
     <t xml:space="preserve">32.3047790527344</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9280433654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4571304321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3629455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8920307159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0803985595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0333099365234</t>
+    <t xml:space="preserve">31.9280414581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4571285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.362943649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.892032623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0804023742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0333080291748</t>
   </si>
   <si>
     <t xml:space="preserve">30.6565742492676</t>
@@ -1661,25 +1661,25 @@
     <t xml:space="preserve">30.9862174987793</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4100399017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8449382781982</t>
+    <t xml:space="preserve">31.4100341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8449420928955</t>
   </si>
   <si>
     <t xml:space="preserve">31.1745758056641</t>
   </si>
   <si>
-    <t xml:space="preserve">31.880952835083</t>
+    <t xml:space="preserve">31.8809509277344</t>
   </si>
   <si>
     <t xml:space="preserve">32.0222282409668</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7396793365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0000686645508</t>
+    <t xml:space="preserve">31.7396717071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.000072479248</t>
   </si>
   <si>
     <t xml:space="preserve">34.4709854125977</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">36.5900993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7784690856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1552085876465</t>
+    <t xml:space="preserve">36.7784652709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.155200958252</t>
   </si>
   <si>
     <t xml:space="preserve">37.6732063293457</t>
@@ -1703,13 +1703,13 @@
     <t xml:space="preserve">38.0846786499023</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2282104492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.367000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.797607421875</t>
+    <t xml:space="preserve">38.2282066345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3669967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7976112365723</t>
   </si>
   <si>
     <t xml:space="preserve">38.1803665161133</t>
@@ -1724,28 +1724,28 @@
     <t xml:space="preserve">37.9889869689941</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8454475402832</t>
+    <t xml:space="preserve">37.8454513549805</t>
   </si>
   <si>
     <t xml:space="preserve">37.3191566467285</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8501968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7545051574707</t>
+    <t xml:space="preserve">38.8502006530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.754508972168</t>
   </si>
   <si>
     <t xml:space="preserve">39.3286476135254</t>
   </si>
   <si>
-    <t xml:space="preserve">39.041576385498</t>
+    <t xml:space="preserve">39.0415802001953</t>
   </si>
   <si>
     <t xml:space="preserve">38.8023529052734</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4674377441406</t>
+    <t xml:space="preserve">38.4674339294434</t>
   </si>
   <si>
     <t xml:space="preserve">38.1325187683105</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">38.8980445861816</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7066612243652</t>
+    <t xml:space="preserve">38.706657409668</t>
   </si>
   <si>
     <t xml:space="preserve">38.2760543823242</t>
@@ -1763,22 +1763,22 @@
     <t xml:space="preserve">38.5631256103516</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4195938110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3764953613281</t>
+    <t xml:space="preserve">38.4195899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3764915466309</t>
   </si>
   <si>
     <t xml:space="preserve">39.1372718811035</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1851119995117</t>
+    <t xml:space="preserve">39.185115814209</t>
   </si>
   <si>
     <t xml:space="preserve">39.2807998657227</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9027938842773</t>
+    <t xml:space="preserve">39.9027900695801</t>
   </si>
   <si>
     <t xml:space="preserve">41.1946067810059</t>
@@ -1793,52 +1793,52 @@
     <t xml:space="preserve">41.6730537414551</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8118476867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7161483764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9122848510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0605621337891</t>
+    <t xml:space="preserve">40.8118438720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7161521911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.912281036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0605659484863</t>
   </si>
   <si>
     <t xml:space="preserve">43.4911689758301</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2566871643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7829856872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4433212280273</t>
+    <t xml:space="preserve">44.2566909790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7829818725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4433250427246</t>
   </si>
   <si>
     <t xml:space="preserve">44.017463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6347007751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9170303344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9265213012695</t>
+    <t xml:space="preserve">43.6347045898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2040977478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9170227050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9265251159668</t>
   </si>
   <si>
     <t xml:space="preserve">45.4049758911133</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2614364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5963516235352</t>
+    <t xml:space="preserve">45.2614326477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5963554382324</t>
   </si>
   <si>
     <t xml:space="preserve">47.6536903381348</t>
@@ -1853,37 +1853,37 @@
     <t xml:space="preserve">49.1847343444824</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9933547973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7588768005371</t>
+    <t xml:space="preserve">48.993350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7588691711426</t>
   </si>
   <si>
     <t xml:space="preserve">49.2804222106934</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6631889343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3761100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5674934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6200904846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0028457641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.7252616882324</t>
+    <t xml:space="preserve">49.6631813049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3761138916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5674858093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6200828552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0028381347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7252655029297</t>
   </si>
   <si>
     <t xml:space="preserve">52.6295776367188</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9597473144531</t>
+    <t xml:space="preserve">51.9597434997559</t>
   </si>
   <si>
     <t xml:space="preserve">51.8640556335449</t>
@@ -1892,34 +1892,34 @@
     <t xml:space="preserve">51.6726760864258</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4192123413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3235206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0459442138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3856048583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9071578979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8545608520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4287033081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5338859558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0649299621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2994079589844</t>
+    <t xml:space="preserve">48.4192047119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3235244750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0459403991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3856086730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.907154083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.854564666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4287071228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5338897705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0649261474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2994041442871</t>
   </si>
   <si>
     <t xml:space="preserve">52.4381980895996</t>
@@ -1928,16 +1928,16 @@
     <t xml:space="preserve">47.3666191101074</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9838600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.361873626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7398910522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9743614196777</t>
+    <t xml:space="preserve">46.9838562011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3618774414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7398872375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.974365234375</t>
   </si>
   <si>
     <t xml:space="preserve">43.5868606567383</t>
@@ -1949,16 +1949,16 @@
     <t xml:space="preserve">36.6493263244629</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5967330932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0945491790771</t>
+    <t xml:space="preserve">35.596736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0945510864258</t>
   </si>
   <si>
     <t xml:space="preserve">31.4820594787598</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1854953765869</t>
+    <t xml:space="preserve">29.1854934692383</t>
   </si>
   <si>
     <t xml:space="preserve">31.5299053192139</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">31.0992984771729</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3816223144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9269027709961</t>
+    <t xml:space="preserve">30.3816204071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9268989562988</t>
   </si>
   <si>
     <t xml:space="preserve">36.410099029541</t>
@@ -1982,13 +1982,13 @@
     <t xml:space="preserve">35.3096656799316</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5441398620605</t>
+    <t xml:space="preserve">34.5441436767578</t>
   </si>
   <si>
     <t xml:space="preserve">35.0704383850098</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0799331665039</t>
+    <t xml:space="preserve">37.0799293518066</t>
   </si>
   <si>
     <t xml:space="preserve">37.2234649658203</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">40.4290809631348</t>
   </si>
   <si>
-    <t xml:space="preserve">39.998477935791</t>
+    <t xml:space="preserve">39.9984817504883</t>
   </si>
   <si>
     <t xml:space="preserve">44.7351417541504</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">45.9791145324707</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4528198242188</t>
+    <t xml:space="preserve">45.4528160095215</t>
   </si>
   <si>
     <t xml:space="preserve">45.0700569152832</t>
@@ -2024,43 +2024,43 @@
     <t xml:space="preserve">45.1179046630859</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4575614929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6441917419434</t>
+    <t xml:space="preserve">46.4575653076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6441993713379</t>
   </si>
   <si>
     <t xml:space="preserve">44.8786773681641</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3092765808105</t>
+    <t xml:space="preserve">45.3092842102051</t>
   </si>
   <si>
     <t xml:space="preserve">45.1657485961914</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2088470458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1562538146973</t>
+    <t xml:space="preserve">44.2088432312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.15625</t>
   </si>
   <si>
     <t xml:space="preserve">43.9217758178711</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8644371032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5821151733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0222129821777</t>
+    <t xml:space="preserve">41.8644332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5821189880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0222091674805</t>
   </si>
   <si>
     <t xml:space="preserve">45.5485038757324</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5101547241211</t>
+    <t xml:space="preserve">47.5101585388184</t>
   </si>
   <si>
     <t xml:space="preserve">47.7015342712402</t>
@@ -2072,34 +2072,34 @@
     <t xml:space="preserve">47.9407577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5149040222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4812927246094</t>
+    <t xml:space="preserve">48.5148963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4812965393066</t>
   </si>
   <si>
     <t xml:space="preserve">51.1942253112793</t>
   </si>
   <si>
-    <t xml:space="preserve">51.768367767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2899169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1080284118652</t>
+    <t xml:space="preserve">51.7683601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2899131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.108024597168</t>
   </si>
   <si>
     <t xml:space="preserve">53.9692420959473</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4907913208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1175231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6916618347168</t>
+    <t xml:space="preserve">53.4907875061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1175270080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6916656494141</t>
   </si>
   <si>
     <t xml:space="preserve">55.5002822875977</t>
@@ -2108,13 +2108,13 @@
     <t xml:space="preserve">54.3519973754883</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6390647888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8304481506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4045906066895</t>
+    <t xml:space="preserve">54.6390724182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.830451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4045944213867</t>
   </si>
   <si>
     <t xml:space="preserve">56.7442512512207</t>
@@ -2123,40 +2123,40 @@
     <t xml:space="preserve">56.9356346130371</t>
   </si>
   <si>
-    <t xml:space="preserve">57.1270141601562</t>
+    <t xml:space="preserve">57.1270179748535</t>
   </si>
   <si>
     <t xml:space="preserve">56.2658042907715</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9787292480469</t>
+    <t xml:space="preserve">55.9787368774414</t>
   </si>
   <si>
     <t xml:space="preserve">57.3183975219727</t>
   </si>
   <si>
-    <t xml:space="preserve">58.6580543518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2227058410645</t>
+    <t xml:space="preserve">58.6580581665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2227096557617</t>
   </si>
   <si>
     <t xml:space="preserve">57.7011566162109</t>
   </si>
   <si>
-    <t xml:space="preserve">56.3614921569824</t>
+    <t xml:space="preserve">56.3614959716797</t>
   </si>
   <si>
     <t xml:space="preserve">57.988224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">58.849437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.3373756408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4425735473633</t>
+    <t xml:space="preserve">58.8494338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.3373794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4425659179688</t>
   </si>
   <si>
     <t xml:space="preserve">62.2942810058594</t>
@@ -2165,31 +2165,31 @@
     <t xml:space="preserve">63.3468627929688</t>
   </si>
   <si>
-    <t xml:space="preserve">63.7296333312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6339454650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3037796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5908432006836</t>
+    <t xml:space="preserve">63.7296295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6339492797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3037719726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5908508300781</t>
   </si>
   <si>
     <t xml:space="preserve">65.9305038452148</t>
   </si>
   <si>
-    <t xml:space="preserve">66.6960144042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3563613891602</t>
+    <t xml:space="preserve">66.6960296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3563690185547</t>
   </si>
   <si>
     <t xml:space="preserve">66.9831008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">67.1744689941406</t>
+    <t xml:space="preserve">67.1744766235352</t>
   </si>
   <si>
     <t xml:space="preserve">66.5046463012695</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">69.1839752197266</t>
   </si>
   <si>
-    <t xml:space="preserve">71.2891616821289</t>
+    <t xml:space="preserve">71.2891540527344</t>
   </si>
   <si>
     <t xml:space="preserve">70.8107070922852</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">70.6193313598633</t>
   </si>
   <si>
-    <t xml:space="preserve">71.7676086425781</t>
+    <t xml:space="preserve">71.7676010131836</t>
   </si>
   <si>
     <t xml:space="preserve">72.0546798706055</t>
@@ -2222,40 +2222,40 @@
     <t xml:space="preserve">71.002082824707</t>
   </si>
   <si>
-    <t xml:space="preserve">69.4710464477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.9925994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9494934082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8012084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.6624298095703</t>
+    <t xml:space="preserve">69.4710388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.9925918579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9494857788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8012161254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.6624221801758</t>
   </si>
   <si>
     <t xml:space="preserve">76.5521087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7003936767578</t>
+    <t xml:space="preserve">77.7004013061523</t>
   </si>
   <si>
     <t xml:space="preserve">75.8822860717773</t>
   </si>
   <si>
-    <t xml:space="preserve">74.734001159668</t>
+    <t xml:space="preserve">74.7339935302734</t>
   </si>
   <si>
     <t xml:space="preserve">73.8727874755859</t>
   </si>
   <si>
-    <t xml:space="preserve">74.8296890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.8917694091797</t>
+    <t xml:space="preserve">74.8296813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.8917846679688</t>
   </si>
   <si>
     <t xml:space="preserve">78.274543762207</t>
@@ -2264,28 +2264,28 @@
     <t xml:space="preserve">77.7960891723633</t>
   </si>
   <si>
-    <t xml:space="preserve">79.4228210449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.7624740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0064468383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5279998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9107666015625</t>
+    <t xml:space="preserve">79.4228134155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.7624816894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0064392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.5279922485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.910758972168</t>
   </si>
   <si>
     <t xml:space="preserve">82.3892135620117</t>
   </si>
   <si>
-    <t xml:space="preserve">81.4322967529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.1452484130859</t>
+    <t xml:space="preserve">81.4323043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1452407836914</t>
   </si>
   <si>
     <t xml:space="preserve">80.4754104614258</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">81.7193832397461</t>
   </si>
   <si>
-    <t xml:space="preserve">81.815071105957</t>
+    <t xml:space="preserve">81.8150634765625</t>
   </si>
   <si>
     <t xml:space="preserve">83.3461074829102</t>
@@ -2309,13 +2309,13 @@
     <t xml:space="preserve">82.2935180664062</t>
   </si>
   <si>
-    <t xml:space="preserve">77.0305633544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3271331787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.728874206543</t>
+    <t xml:space="preserve">77.0305557250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3271255493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7288665771484</t>
   </si>
   <si>
     <t xml:space="preserve">82.1021423339844</t>
@@ -2324,16 +2324,16 @@
     <t xml:space="preserve">76.7434921264648</t>
   </si>
   <si>
-    <t xml:space="preserve">79.5185012817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8055877685547</t>
+    <t xml:space="preserve">79.5184936523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8055801391602</t>
   </si>
   <si>
     <t xml:space="preserve">82.4849014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3797149658203</t>
+    <t xml:space="preserve">80.3797225952148</t>
   </si>
   <si>
     <t xml:space="preserve">78.6572952270508</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">84.6857757568359</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3556060791016</t>
+    <t xml:space="preserve">85.355598449707</t>
   </si>
   <si>
     <t xml:space="preserve">83.0590438842773</t>
@@ -2357,16 +2357,16 @@
     <t xml:space="preserve">87.1737213134766</t>
   </si>
   <si>
-    <t xml:space="preserve">87.269401550293</t>
+    <t xml:space="preserve">87.2694091796875</t>
   </si>
   <si>
     <t xml:space="preserve">88.3220062255859</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7909622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.9056396484375</t>
+    <t xml:space="preserve">86.7909545898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.905632019043</t>
   </si>
   <si>
     <t xml:space="preserve">91.3840866088867</t>
@@ -2387,10 +2387,10 @@
     <t xml:space="preserve">101.622917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">101.240180969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.9867095947266</t>
+    <t xml:space="preserve">101.240165710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.986701965332</t>
   </si>
   <si>
     <t xml:space="preserve">98.5608444213867</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">96.2642822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">95.6901397705078</t>
+    <t xml:space="preserve">95.6901473999023</t>
   </si>
   <si>
     <t xml:space="preserve">94.8289337158203</t>
@@ -2414,10 +2414,10 @@
     <t xml:space="preserve">94.2547912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">94.4461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0298080444336</t>
+    <t xml:space="preserve">94.446159362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0297927856445</t>
   </si>
   <si>
     <t xml:space="preserve">94.5418548583984</t>
@@ -2426,58 +2426,58 @@
     <t xml:space="preserve">94.1591033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8720169067383</t>
+    <t xml:space="preserve">93.8720321655273</t>
   </si>
   <si>
     <t xml:space="preserve">94.0634155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">93.3935699462891</t>
+    <t xml:space="preserve">93.3935775756836</t>
   </si>
   <si>
     <t xml:space="preserve">93.6806564331055</t>
   </si>
   <si>
-    <t xml:space="preserve">92.9151229858398</t>
+    <t xml:space="preserve">92.9151306152344</t>
   </si>
   <si>
     <t xml:space="preserve">93.2978897094727</t>
   </si>
   <si>
-    <t xml:space="preserve">92.723747253418</t>
+    <t xml:space="preserve">92.7237548828125</t>
   </si>
   <si>
     <t xml:space="preserve">94.3504791259766</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6039352416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.43155670166</t>
+    <t xml:space="preserve">97.6039428710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.431541442871</t>
   </si>
   <si>
     <t xml:space="preserve">104.876396179199</t>
   </si>
   <si>
-    <t xml:space="preserve">104.493637084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.598815917969</t>
+    <t xml:space="preserve">104.493629455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.598808288574</t>
   </si>
   <si>
     <t xml:space="preserve">107.364334106445</t>
   </si>
   <si>
-    <t xml:space="preserve">109.66089630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.235046386719</t>
+    <t xml:space="preserve">109.660903930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.235054016113</t>
   </si>
   <si>
     <t xml:space="preserve">105.641914367676</t>
   </si>
   <si>
-    <t xml:space="preserve">106.21605682373</t>
+    <t xml:space="preserve">106.216049194336</t>
   </si>
   <si>
     <t xml:space="preserve">107.938484191895</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">107.555717468262</t>
   </si>
   <si>
-    <t xml:space="preserve">109.469520568848</t>
+    <t xml:space="preserve">109.469528198242</t>
   </si>
   <si>
     <t xml:space="preserve">107.747100830078</t>
@@ -2495,31 +2495,31 @@
     <t xml:space="preserve">108.703994750977</t>
   </si>
   <si>
-    <t xml:space="preserve">102.197067260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5177536010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.7091217041016</t>
+    <t xml:space="preserve">102.197074890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5177383422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.7091293334961</t>
   </si>
   <si>
     <t xml:space="preserve">103.345352172852</t>
   </si>
   <si>
-    <t xml:space="preserve">103.536735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.024681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.981582641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.512619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.833297729492</t>
+    <t xml:space="preserve">103.536720275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.024673461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.981575012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.51261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.833290100098</t>
   </si>
   <si>
     <t xml:space="preserve">101.048782348633</t>
@@ -2528,37 +2528,37 @@
     <t xml:space="preserve">102.388450622559</t>
   </si>
   <si>
-    <t xml:space="preserve">103.15397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.962585449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.450523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.00569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.919494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.407432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.086769104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.809181213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.679901123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.043663024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.172958374023</t>
+    <t xml:space="preserve">103.153968811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.962593078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.450531005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.005676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.919486999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.407424926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.086761474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.809188842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.679885864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.043670654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.172966003418</t>
   </si>
   <si>
     <t xml:space="preserve">111.000564575195</t>
@@ -2567,43 +2567,43 @@
     <t xml:space="preserve">112.914367675781</t>
   </si>
   <si>
-    <t xml:space="preserve">109.85228729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.426429748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.383323669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.340232849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.445411682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.29712677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.722984313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.019554138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.593696594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.210929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.741981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.167823791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.785064697266</t>
+    <t xml:space="preserve">109.852294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.426422119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.383331298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.340240478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.445419311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.297134399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.722991943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.019546508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.593688964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.2109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.741973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.167831420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.78507232666</t>
   </si>
   <si>
     <t xml:space="preserve">116.550598144531</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">119.804054260254</t>
   </si>
   <si>
-    <t xml:space="preserve">120.186820983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.100624084473</t>
+    <t xml:space="preserve">120.186813354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.100616455078</t>
   </si>
   <si>
     <t xml:space="preserve">122.866142272949</t>
@@ -2624,22 +2624,22 @@
     <t xml:space="preserve">123.631660461426</t>
   </si>
   <si>
-    <t xml:space="preserve">131.478271484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.267890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.459266662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.990310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.052383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.157592773438</t>
+    <t xml:space="preserve">131.478256225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.26789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.459259033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.990295410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.05241394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.157577514648</t>
   </si>
   <si>
     <t xml:space="preserve">133.774826049805</t>
@@ -2648,19 +2648,19 @@
     <t xml:space="preserve">132.626541137695</t>
   </si>
   <si>
-    <t xml:space="preserve">132.435150146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.923095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.645523071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.411041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.305847167969</t>
+    <t xml:space="preserve">132.435165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.923080444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.645538330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.411056518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.305862426758</t>
   </si>
   <si>
     <t xml:space="preserve">131.86100769043</t>
@@ -2669,22 +2669,22 @@
     <t xml:space="preserve">134.731719970703</t>
   </si>
   <si>
-    <t xml:space="preserve">136.262756347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.793792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.176559448242</t>
+    <t xml:space="preserve">136.262771606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.793807983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.176574707031</t>
   </si>
   <si>
     <t xml:space="preserve">137.028274536133</t>
   </si>
   <si>
-    <t xml:space="preserve">138.559326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.898986816406</t>
+    <t xml:space="preserve">138.559341430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.898971557617</t>
   </si>
   <si>
     <t xml:space="preserve">136.454147338867</t>
@@ -2693,55 +2693,55 @@
     <t xml:space="preserve">138.750701904297</t>
   </si>
   <si>
-    <t xml:space="preserve">139.324859619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.985198974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.497268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.492111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.874877929688</t>
+    <t xml:space="preserve">139.324844360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.98518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.497253417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.492095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.874847412109</t>
   </si>
   <si>
     <t xml:space="preserve">144.109359741211</t>
   </si>
   <si>
-    <t xml:space="preserve">142.195556640625</t>
+    <t xml:space="preserve">142.195571899414</t>
   </si>
   <si>
     <t xml:space="preserve">143.726577758789</t>
   </si>
   <si>
-    <t xml:space="preserve">143.91796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.683471679688</t>
+    <t xml:space="preserve">143.917953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.683486938477</t>
   </si>
   <si>
     <t xml:space="preserve">145.25764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">147.936965942383</t>
+    <t xml:space="preserve">147.936950683594</t>
   </si>
   <si>
     <t xml:space="preserve">145.640396118164</t>
   </si>
   <si>
-    <t xml:space="preserve">146.788681030273</t>
+    <t xml:space="preserve">146.788665771484</t>
   </si>
   <si>
     <t xml:space="preserve">149.276626586914</t>
   </si>
   <si>
-    <t xml:space="preserve">150.999069213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.424896240234</t>
+    <t xml:space="preserve">150.999038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.424911499023</t>
   </si>
   <si>
     <t xml:space="preserve">153.48698425293</t>
@@ -2750,61 +2750,61 @@
     <t xml:space="preserve">152.338714599609</t>
   </si>
   <si>
-    <t xml:space="preserve">155.400787353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.1904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.888748168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.037002563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.654266357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.611175537109</t>
+    <t xml:space="preserve">155.400802612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.190444946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.888717651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.036987304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.654251098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.61116027832</t>
   </si>
   <si>
     <t xml:space="preserve">161.333587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">161.524948120117</t>
+    <t xml:space="preserve">161.524963378906</t>
   </si>
   <si>
     <t xml:space="preserve">163.438766479492</t>
   </si>
   <si>
-    <t xml:space="preserve">163.821533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.606033325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.773284912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.328460693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.161193847656</t>
+    <t xml:space="preserve">163.821517944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.606018066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.773300170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.328475952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.161209106445</t>
   </si>
   <si>
     <t xml:space="preserve">168.031890869141</t>
   </si>
   <si>
-    <t xml:space="preserve">165.352554321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.759429931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.099105834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.668121337891</t>
+    <t xml:space="preserve">165.352584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.75944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.099075317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.668090820312</t>
   </si>
   <si>
     <t xml:space="preserve">167.074981689453</t>
@@ -2816,10 +2816,10 @@
     <t xml:space="preserve">161.353576660156</t>
   </si>
   <si>
-    <t xml:space="preserve">160.584320068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.045761108398</t>
+    <t xml:space="preserve">160.58430480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.045776367188</t>
   </si>
   <si>
     <t xml:space="preserve">152.122375488281</t>
@@ -2828,19 +2828,19 @@
     <t xml:space="preserve">145.583602905273</t>
   </si>
   <si>
-    <t xml:space="preserve">147.314468383789</t>
+    <t xml:space="preserve">147.314453125</t>
   </si>
   <si>
     <t xml:space="preserve">150.391525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">150.19921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.083724975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.737762451172</t>
+    <t xml:space="preserve">150.199203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.083740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.737747192383</t>
   </si>
   <si>
     <t xml:space="preserve">149.622268676758</t>
@@ -2852,13 +2852,13 @@
     <t xml:space="preserve">156.545654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">155.968704223633</t>
+    <t xml:space="preserve">155.968688964844</t>
   </si>
   <si>
     <t xml:space="preserve">154.43017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">160.776626586914</t>
+    <t xml:space="preserve">160.776611328125</t>
   </si>
   <si>
     <t xml:space="preserve">166.353805541992</t>
@@ -2867,19 +2867,19 @@
     <t xml:space="preserve">170.200119018555</t>
   </si>
   <si>
-    <t xml:space="preserve">168.469284057617</t>
+    <t xml:space="preserve">168.469268798828</t>
   </si>
   <si>
     <t xml:space="preserve">164.430633544922</t>
   </si>
   <si>
-    <t xml:space="preserve">165.007583618164</t>
+    <t xml:space="preserve">165.007598876953</t>
   </si>
   <si>
     <t xml:space="preserve">162.507461547852</t>
   </si>
   <si>
-    <t xml:space="preserve">163.469055175781</t>
+    <t xml:space="preserve">163.46907043457</t>
   </si>
   <si>
     <t xml:space="preserve">165.584533691406</t>
@@ -2894,46 +2894,46 @@
     <t xml:space="preserve">161.738189697266</t>
   </si>
   <si>
-    <t xml:space="preserve">168.853897094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.508178710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.584991455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.392913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.777542114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.469741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.815948486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.739120483398</t>
+    <t xml:space="preserve">168.853927612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.508163452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.585006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.392929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.777526855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.4697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.815963745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.739135742188</t>
   </si>
   <si>
     <t xml:space="preserve">185.008499145508</t>
   </si>
   <si>
-    <t xml:space="preserve">183.085342407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.508392333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.276977539062</t>
+    <t xml:space="preserve">183.085311889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.508407592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.276962280273</t>
   </si>
   <si>
     <t xml:space="preserve">169.046234130859</t>
   </si>
   <si>
-    <t xml:space="preserve">170.584762573242</t>
+    <t xml:space="preserve">170.584747314453</t>
   </si>
   <si>
     <t xml:space="preserve">167.507690429688</t>
@@ -2945,13 +2945,13 @@
     <t xml:space="preserve">170.96940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">169.623184204102</t>
+    <t xml:space="preserve">169.623168945312</t>
   </si>
   <si>
     <t xml:space="preserve">169.238540649414</t>
   </si>
   <si>
-    <t xml:space="preserve">175.008056640625</t>
+    <t xml:space="preserve">175.008041381836</t>
   </si>
   <si>
     <t xml:space="preserve">172.700241088867</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">163.853668212891</t>
   </si>
   <si>
-    <t xml:space="preserve">166.738418579102</t>
+    <t xml:space="preserve">166.738433837891</t>
   </si>
   <si>
     <t xml:space="preserve">164.238327026367</t>
@@ -2978,49 +2978,49 @@
     <t xml:space="preserve">166.546112060547</t>
   </si>
   <si>
-    <t xml:space="preserve">167.699996948242</t>
+    <t xml:space="preserve">167.700012207031</t>
   </si>
   <si>
     <t xml:space="preserve">165.392211914062</t>
   </si>
   <si>
-    <t xml:space="preserve">151.160781860352</t>
+    <t xml:space="preserve">151.160797119141</t>
   </si>
   <si>
     <t xml:space="preserve">158.853454589844</t>
   </si>
   <si>
-    <t xml:space="preserve">158.468811035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.314926147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.815032958984</t>
+    <t xml:space="preserve">158.468826293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.31494140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.815048217773</t>
   </si>
   <si>
     <t xml:space="preserve">156.930297851562</t>
   </si>
   <si>
-    <t xml:space="preserve">156.161010742188</t>
+    <t xml:space="preserve">156.161026000977</t>
   </si>
   <si>
     <t xml:space="preserve">152.314682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">145.968246459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.929824829102</t>
+    <t xml:space="preserve">145.96826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.929840087891</t>
   </si>
   <si>
     <t xml:space="preserve">151.353088378906</t>
   </si>
   <si>
-    <t xml:space="preserve">153.468597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.276260375977</t>
+    <t xml:space="preserve">153.46858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.276275634766</t>
   </si>
   <si>
     <t xml:space="preserve">157.122604370117</t>
@@ -3029,31 +3029,31 @@
     <t xml:space="preserve">151.930053710938</t>
   </si>
   <si>
-    <t xml:space="preserve">146.545211791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.968032836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.929382324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.660217285156</t>
+    <t xml:space="preserve">146.545181274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.968017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.929351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.660232543945</t>
   </si>
   <si>
     <t xml:space="preserve">132.69841003418</t>
   </si>
   <si>
-    <t xml:space="preserve">132.506088256836</t>
+    <t xml:space="preserve">132.506072998047</t>
   </si>
   <si>
     <t xml:space="preserve">130.198287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">134.813888549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.005981445312</t>
+    <t xml:space="preserve">134.813873291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.005966186523</t>
   </si>
   <si>
     <t xml:space="preserve">130.775238037109</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">128.852066040039</t>
   </si>
   <si>
-    <t xml:space="preserve">129.621337890625</t>
+    <t xml:space="preserve">129.621353149414</t>
   </si>
   <si>
     <t xml:space="preserve">132.890716552734</t>
@@ -3071,46 +3071,46 @@
     <t xml:space="preserve">137.506317138672</t>
   </si>
   <si>
-    <t xml:space="preserve">136.160125732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.467895507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.583160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.813438415527</t>
+    <t xml:space="preserve">136.160110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.467910766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.583145141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.813430786133</t>
   </si>
   <si>
     <t xml:space="preserve">118.659301757812</t>
   </si>
   <si>
-    <t xml:space="preserve">125.582695007324</t>
+    <t xml:space="preserve">125.582702636719</t>
   </si>
   <si>
     <t xml:space="preserve">125.198059082031</t>
   </si>
   <si>
-    <t xml:space="preserve">137.314010620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.8525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.891174316406</t>
+    <t xml:space="preserve">137.313995361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.852523803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.891189575195</t>
   </si>
   <si>
     <t xml:space="preserve">140.391067504883</t>
   </si>
   <si>
-    <t xml:space="preserve">145.39128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.00666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.775924682617</t>
+    <t xml:space="preserve">145.391296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.006652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.775939941406</t>
   </si>
   <si>
     <t xml:space="preserve">144.814361572266</t>
@@ -3122,22 +3122,22 @@
     <t xml:space="preserve">143.275817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">142.60270690918</t>
+    <t xml:space="preserve">142.602737426758</t>
   </si>
   <si>
     <t xml:space="preserve">142.698867797852</t>
   </si>
   <si>
-    <t xml:space="preserve">143.083511352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.525634765625</t>
+    <t xml:space="preserve">143.08349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.525650024414</t>
   </si>
   <si>
     <t xml:space="preserve">141.160339355469</t>
   </si>
   <si>
-    <t xml:space="preserve">140.198745727539</t>
+    <t xml:space="preserve">140.198760986328</t>
   </si>
   <si>
     <t xml:space="preserve">139.910278320312</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">139.429473876953</t>
   </si>
   <si>
-    <t xml:space="preserve">139.237167358398</t>
+    <t xml:space="preserve">139.237152099609</t>
   </si>
   <si>
     <t xml:space="preserve">140.006439208984</t>
@@ -3170,31 +3170,31 @@
     <t xml:space="preserve">129.909820556641</t>
   </si>
   <si>
-    <t xml:space="preserve">133.371505737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.275131225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.294448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.236473083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.890266418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.563148498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.812728881836</t>
+    <t xml:space="preserve">133.371520996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.275115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.294464111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.236480712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.890258789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.563140869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.81273651123</t>
   </si>
   <si>
     <t xml:space="preserve">113.562911987305</t>
   </si>
   <si>
-    <t xml:space="preserve">115.389915466309</t>
+    <t xml:space="preserve">115.389923095703</t>
   </si>
   <si>
     <t xml:space="preserve">115.774551391602</t>
@@ -3206,34 +3206,34 @@
     <t xml:space="preserve">118.08235168457</t>
   </si>
   <si>
-    <t xml:space="preserve">122.31330871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.293991088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.101676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.236251831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.486312866211</t>
+    <t xml:space="preserve">122.313316345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.293983459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.101684570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.23624420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.486305236816</t>
   </si>
   <si>
     <t xml:space="preserve">116.736137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">116.832298278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.043930053711</t>
+    <t xml:space="preserve">116.832290649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.0439453125</t>
   </si>
   <si>
     <t xml:space="preserve">121.736358642578</t>
   </si>
   <si>
-    <t xml:space="preserve">124.621109008789</t>
+    <t xml:space="preserve">124.621124267578</t>
   </si>
   <si>
     <t xml:space="preserve">123.274894714355</t>
@@ -3242,10 +3242,10 @@
     <t xml:space="preserve">121.544044494629</t>
   </si>
   <si>
-    <t xml:space="preserve">124.044166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.332641601562</t>
+    <t xml:space="preserve">124.044158935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.332633972168</t>
   </si>
   <si>
     <t xml:space="preserve">127.986656188965</t>
@@ -3257,22 +3257,22 @@
     <t xml:space="preserve">127.698173522949</t>
   </si>
   <si>
-    <t xml:space="preserve">123.178741455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.524490356445</t>
+    <t xml:space="preserve">123.178749084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.524482727051</t>
   </si>
   <si>
     <t xml:space="preserve">112.889808654785</t>
   </si>
   <si>
-    <t xml:space="preserve">114.236030578613</t>
+    <t xml:space="preserve">114.236022949219</t>
   </si>
   <si>
     <t xml:space="preserve">111.062797546387</t>
   </si>
   <si>
-    <t xml:space="preserve">112.216697692871</t>
+    <t xml:space="preserve">112.216690063477</t>
   </si>
   <si>
     <t xml:space="preserve">112.505172729492</t>
@@ -3281,10 +3281,10 @@
     <t xml:space="preserve">113.947547912598</t>
   </si>
   <si>
-    <t xml:space="preserve">116.447654724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.197601318359</t>
+    <t xml:space="preserve">116.447662353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.197608947754</t>
   </si>
   <si>
     <t xml:space="preserve">119.140090942383</t>
@@ -3293,16 +3293,16 @@
     <t xml:space="preserve">119.909355163574</t>
   </si>
   <si>
-    <t xml:space="preserve">119.428573608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.890029907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.293762207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.178276062012</t>
+    <t xml:space="preserve">119.428565979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.890037536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.293754577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.178283691406</t>
   </si>
   <si>
     <t xml:space="preserve">119.332405090332</t>
@@ -3314,22 +3314,22 @@
     <t xml:space="preserve">125.39037322998</t>
   </si>
   <si>
-    <t xml:space="preserve">122.986427307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.274658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.71703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.774780273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.659530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.948257446289</t>
+    <t xml:space="preserve">122.986419677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.274673461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.717041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.774772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.659523010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.948226928711</t>
   </si>
   <si>
     <t xml:space="preserve">131.736831665039</t>
@@ -3341,37 +3341,37 @@
     <t xml:space="preserve">126.832733154297</t>
   </si>
   <si>
-    <t xml:space="preserve">127.794319152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.46745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.602249145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.044387817383</t>
+    <t xml:space="preserve">127.794334411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.467437744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.602233886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.044403076172</t>
   </si>
   <si>
     <t xml:space="preserve">131.159866333008</t>
   </si>
   <si>
-    <t xml:space="preserve">125.967323303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.351943969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.563362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.313522338867</t>
+    <t xml:space="preserve">125.967330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.351951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.563377380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.313537597656</t>
   </si>
   <si>
     <t xml:space="preserve">128.371276855469</t>
   </si>
   <si>
-    <t xml:space="preserve">126.736602783203</t>
+    <t xml:space="preserve">126.736595153809</t>
   </si>
   <si>
     <t xml:space="preserve">121.447891235352</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">117.6015625</t>
   </si>
   <si>
-    <t xml:space="preserve">118.947761535645</t>
+    <t xml:space="preserve">118.947769165039</t>
   </si>
   <si>
     <t xml:space="preserve">120.19783782959</t>
@@ -3389,34 +3389,34 @@
     <t xml:space="preserve">121.063255310059</t>
   </si>
   <si>
-    <t xml:space="preserve">117.505401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.870704650879</t>
+    <t xml:space="preserve">117.505393981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.870712280273</t>
   </si>
   <si>
     <t xml:space="preserve">116.255348205566</t>
   </si>
   <si>
-    <t xml:space="preserve">112.312858581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.582237243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.678398132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.178512573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.909133911133</t>
+    <t xml:space="preserve">112.312850952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.582229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.67839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.178504943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.909126281738</t>
   </si>
   <si>
     <t xml:space="preserve">106.596168518066</t>
   </si>
   <si>
-    <t xml:space="preserve">105.336395263672</t>
+    <t xml:space="preserve">105.336387634277</t>
   </si>
   <si>
     <t xml:space="preserve">106.983795166016</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">102.816841125488</t>
   </si>
   <si>
-    <t xml:space="preserve">106.014739990234</t>
+    <t xml:space="preserve">106.01473236084</t>
   </si>
   <si>
     <t xml:space="preserve">102.041610717773</t>
@@ -3443,22 +3443,22 @@
     <t xml:space="preserve">108.437377929688</t>
   </si>
   <si>
-    <t xml:space="preserve">109.212623596191</t>
+    <t xml:space="preserve">109.212615966797</t>
   </si>
   <si>
     <t xml:space="preserve">113.185752868652</t>
   </si>
   <si>
-    <t xml:space="preserve">111.441444396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.829078674316</t>
+    <t xml:space="preserve">111.441452026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.829071044922</t>
   </si>
   <si>
     <t xml:space="preserve">107.274505615234</t>
   </si>
   <si>
-    <t xml:space="preserve">104.851860046387</t>
+    <t xml:space="preserve">104.851867675781</t>
   </si>
   <si>
     <t xml:space="preserve">104.658058166504</t>
@@ -3476,10 +3476,10 @@
     <t xml:space="preserve">104.076622009277</t>
   </si>
   <si>
-    <t xml:space="preserve">106.402359008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.693077087402</t>
+    <t xml:space="preserve">106.402366638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.693069458008</t>
   </si>
   <si>
     <t xml:space="preserve">110.860015869141</t>
@@ -3491,25 +3491,25 @@
     <t xml:space="preserve">114.348617553711</t>
   </si>
   <si>
-    <t xml:space="preserve">109.794059753418</t>
+    <t xml:space="preserve">109.794052124023</t>
   </si>
   <si>
     <t xml:space="preserve">107.468315124512</t>
   </si>
   <si>
-    <t xml:space="preserve">106.305442810059</t>
+    <t xml:space="preserve">106.305450439453</t>
   </si>
   <si>
     <t xml:space="preserve">102.332321166992</t>
   </si>
   <si>
-    <t xml:space="preserve">100.87873840332</t>
+    <t xml:space="preserve">100.878730773926</t>
   </si>
   <si>
     <t xml:space="preserve">103.979721069336</t>
   </si>
   <si>
-    <t xml:space="preserve">108.340469360352</t>
+    <t xml:space="preserve">108.340476989746</t>
   </si>
   <si>
     <t xml:space="preserve">117.643409729004</t>
@@ -3524,19 +3524,19 @@
     <t xml:space="preserve">116.771255493164</t>
   </si>
   <si>
-    <t xml:space="preserve">114.445526123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.73624420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.026954650879</t>
+    <t xml:space="preserve">114.445518493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.736236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.026947021484</t>
   </si>
   <si>
     <t xml:space="preserve">115.317672729492</t>
   </si>
   <si>
-    <t xml:space="preserve">115.511474609375</t>
+    <t xml:space="preserve">115.51148223877</t>
   </si>
   <si>
     <t xml:space="preserve">115.220771789551</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">118.612464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">112.991943359375</t>
+    <t xml:space="preserve">112.99193572998</t>
   </si>
   <si>
     <t xml:space="preserve">111.053825378418</t>
@@ -3578,10 +3578,10 @@
     <t xml:space="preserve">108.243560791016</t>
   </si>
   <si>
-    <t xml:space="preserve">107.080696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.375495910645</t>
+    <t xml:space="preserve">107.080703735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.37548828125</t>
   </si>
   <si>
     <t xml:space="preserve">108.534278869629</t>
@@ -3590,28 +3590,28 @@
     <t xml:space="preserve">110.181671142578</t>
   </si>
   <si>
-    <t xml:space="preserve">109.890960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.247650146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.282653808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.410507202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.63932800293</t>
+    <t xml:space="preserve">109.890953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.247634887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.282661437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.410499572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.639335632324</t>
   </si>
   <si>
     <t xml:space="preserve">117.934120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">117.25577545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.352691650391</t>
+    <t xml:space="preserve">117.255783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.352684020996</t>
   </si>
   <si>
     <t xml:space="preserve">118.031028747559</t>
@@ -3629,7 +3629,7 @@
     <t xml:space="preserve">120.162956237793</t>
   </si>
   <si>
-    <t xml:space="preserve">121.907257080078</t>
+    <t xml:space="preserve">121.907249450684</t>
   </si>
   <si>
     <t xml:space="preserve">120.550575256348</t>
@@ -3638,37 +3638,37 @@
     <t xml:space="preserve">122.779403686523</t>
   </si>
   <si>
-    <t xml:space="preserve">123.26392364502</t>
+    <t xml:space="preserve">123.263938903809</t>
   </si>
   <si>
     <t xml:space="preserve">121.810340881348</t>
   </si>
   <si>
-    <t xml:space="preserve">120.744384765625</t>
+    <t xml:space="preserve">120.74439239502</t>
   </si>
   <si>
     <t xml:space="preserve">123.748458862305</t>
   </si>
   <si>
-    <t xml:space="preserve">131.985427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.888534545898</t>
+    <t xml:space="preserve">131.985443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.888549804688</t>
   </si>
   <si>
     <t xml:space="preserve">132.179244995117</t>
   </si>
   <si>
-    <t xml:space="preserve">130.531845092773</t>
+    <t xml:space="preserve">130.531860351562</t>
   </si>
   <si>
     <t xml:space="preserve">128.593734741211</t>
   </si>
   <si>
-    <t xml:space="preserve">127.043251037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.814430236816</t>
+    <t xml:space="preserve">127.043266296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.814422607422</t>
   </si>
   <si>
     <t xml:space="preserve">125.686576843262</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">126.849433898926</t>
   </si>
   <si>
-    <t xml:space="preserve">127.333961486816</t>
+    <t xml:space="preserve">127.333969116211</t>
   </si>
   <si>
     <t xml:space="preserve">126.946342468262</t>
@@ -3686,10 +3686,10 @@
     <t xml:space="preserve">124.136085510254</t>
   </si>
   <si>
-    <t xml:space="preserve">123.845367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.422729492188</t>
+    <t xml:space="preserve">123.845359802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.422737121582</t>
   </si>
   <si>
     <t xml:space="preserve">121.325820922852</t>
@@ -3704,25 +3704,25 @@
     <t xml:space="preserve">118.321746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">116.8681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.802200317383</t>
+    <t xml:space="preserve">116.868156433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.802207946777</t>
   </si>
   <si>
     <t xml:space="preserve">113.864097595215</t>
   </si>
   <si>
-    <t xml:space="preserve">113.960990905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.088844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.472396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.824996948242</t>
+    <t xml:space="preserve">113.960998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.088836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.472389221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.825004577637</t>
   </si>
   <si>
     <t xml:space="preserve">115.414573669434</t>
@@ -3755,16 +3755,16 @@
     <t xml:space="preserve">119.678428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">116.383628845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.123870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.119789123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.569297790527</t>
+    <t xml:space="preserve">116.383636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.123863220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.119781494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.569290161133</t>
   </si>
   <si>
     <t xml:space="preserve">110.956924438477</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">108.921905517578</t>
   </si>
   <si>
-    <t xml:space="preserve">107.952850341797</t>
+    <t xml:space="preserve">107.952842712402</t>
   </si>
   <si>
     <t xml:space="preserve">107.565223693848</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">103.592094421387</t>
   </si>
   <si>
-    <t xml:space="preserve">106.88688659668</t>
+    <t xml:space="preserve">106.886894226074</t>
   </si>
   <si>
     <t xml:space="preserve">103.204475402832</t>
@@ -3803,22 +3803,22 @@
     <t xml:space="preserve">100.297302246094</t>
   </si>
   <si>
-    <t xml:space="preserve">102.719947814941</t>
+    <t xml:space="preserve">102.719940185547</t>
   </si>
   <si>
     <t xml:space="preserve">103.107566833496</t>
   </si>
   <si>
-    <t xml:space="preserve">104.561149597168</t>
+    <t xml:space="preserve">104.561157226562</t>
   </si>
   <si>
     <t xml:space="preserve">107.37141418457</t>
   </si>
   <si>
-    <t xml:space="preserve">107.855949401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.01880645752</t>
+    <t xml:space="preserve">107.855941772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.018814086914</t>
   </si>
   <si>
     <t xml:space="preserve">110.084770202637</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">111.150726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">110.763107299805</t>
+    <t xml:space="preserve">110.763114929199</t>
   </si>
   <si>
     <t xml:space="preserve">109.503341674805</t>
@@ -3848,31 +3848,31 @@
     <t xml:space="preserve">109.115715026855</t>
   </si>
   <si>
-    <t xml:space="preserve">110.278579711914</t>
+    <t xml:space="preserve">110.278587341309</t>
   </si>
   <si>
     <t xml:space="preserve">109.697143554688</t>
   </si>
   <si>
-    <t xml:space="preserve">102.235412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.623046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.173522949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.781837463379</t>
+    <t xml:space="preserve">102.235420227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.623039245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.173530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.781829833984</t>
   </si>
   <si>
     <t xml:space="preserve">100.975639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">100.200393676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.491111755371</t>
+    <t xml:space="preserve">100.200401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.491104125977</t>
   </si>
   <si>
     <t xml:space="preserve">100.006591796875</t>
@@ -3887,22 +3887,22 @@
     <t xml:space="preserve">101.653984069824</t>
   </si>
   <si>
-    <t xml:space="preserve">100.39421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3282470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6189651489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2313461303711</t>
+    <t xml:space="preserve">100.394203186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.328254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6189727783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2313385009766</t>
   </si>
   <si>
     <t xml:space="preserve">102.138511657715</t>
   </si>
   <si>
-    <t xml:space="preserve">101.75089263916</t>
+    <t xml:space="preserve">101.750885009766</t>
   </si>
   <si>
     <t xml:space="preserve">99.8127746582031</t>
@@ -3917,22 +3917,22 @@
     <t xml:space="preserve">97.1963272094727</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6808471679688</t>
+    <t xml:space="preserve">97.6808624267578</t>
   </si>
   <si>
     <t xml:space="preserve">99.0078277587891</t>
   </si>
   <si>
-    <t xml:space="preserve">98.6164932250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.573173522949</t>
+    <t xml:space="preserve">98.6165008544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.573181152344</t>
   </si>
   <si>
     <t xml:space="preserve">97.051155090332</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0672302246094</t>
+    <t xml:space="preserve">94.0672225952148</t>
   </si>
   <si>
     <t xml:space="preserve">95.8771438598633</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">95.7793197631836</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5780487060547</t>
+    <t xml:space="preserve">93.5780563354492</t>
   </si>
   <si>
     <t xml:space="preserve">92.5997161865234</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">90.0071182250977</t>
   </si>
   <si>
-    <t xml:space="preserve">90.4962844848633</t>
+    <t xml:space="preserve">90.4962921142578</t>
   </si>
   <si>
     <t xml:space="preserve">90.8386993408203</t>
@@ -3989,13 +3989,13 @@
     <t xml:space="preserve">92.3062133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">92.942138671875</t>
+    <t xml:space="preserve">92.9421310424805</t>
   </si>
   <si>
     <t xml:space="preserve">91.2789611816406</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6213760375977</t>
+    <t xml:space="preserve">91.6213836669922</t>
   </si>
   <si>
     <t xml:space="preserve">90.6430435180664</t>
@@ -4046,28 +4046,28 @@
     <t xml:space="preserve">103.508193969727</t>
   </si>
   <si>
-    <t xml:space="preserve">103.703857421875</t>
+    <t xml:space="preserve">103.70384979248</t>
   </si>
   <si>
     <t xml:space="preserve">106.051864624023</t>
   </si>
   <si>
-    <t xml:space="preserve">104.975700378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.171356201172</t>
+    <t xml:space="preserve">104.975692749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.171363830566</t>
   </si>
   <si>
     <t xml:space="preserve">102.627685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">101.747184753418</t>
+    <t xml:space="preserve">101.747177124023</t>
   </si>
   <si>
     <t xml:space="preserve">103.997360229492</t>
   </si>
   <si>
-    <t xml:space="preserve">102.529846191406</t>
+    <t xml:space="preserve">102.529853820801</t>
   </si>
   <si>
     <t xml:space="preserve">100.377502441406</t>
@@ -4079,10 +4079,10 @@
     <t xml:space="preserve">104.193023681641</t>
   </si>
   <si>
-    <t xml:space="preserve">106.541030883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.617210388184</t>
+    <t xml:space="preserve">106.541038513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.617202758789</t>
   </si>
   <si>
     <t xml:space="preserve">106.834533691406</t>
@@ -4091,13 +4091,13 @@
     <t xml:space="preserve">105.85619354248</t>
   </si>
   <si>
-    <t xml:space="preserve">111.530563354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.367736816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.291572570801</t>
+    <t xml:space="preserve">111.530555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.367744445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.291564941406</t>
   </si>
   <si>
     <t xml:space="preserve">117.694091796875</t>
@@ -4106,22 +4106,22 @@
     <t xml:space="preserve">118.672431945801</t>
   </si>
   <si>
-    <t xml:space="preserve">118.378921508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.259429931641</t>
+    <t xml:space="preserve">118.378929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.259437561035</t>
   </si>
   <si>
     <t xml:space="preserve">120.335601806641</t>
   </si>
   <si>
-    <t xml:space="preserve">118.085426330566</t>
+    <t xml:space="preserve">118.085418701172</t>
   </si>
   <si>
     <t xml:space="preserve">115.346084594727</t>
   </si>
   <si>
-    <t xml:space="preserve">115.737411499023</t>
+    <t xml:space="preserve">115.737419128418</t>
   </si>
   <si>
     <t xml:space="preserve">113.682907104492</t>
@@ -4136,19 +4136,19 @@
     <t xml:space="preserve">111.921897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">111.824058532715</t>
+    <t xml:space="preserve">111.824066162109</t>
   </si>
   <si>
     <t xml:space="preserve">114.074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">113.976402282715</t>
+    <t xml:space="preserve">113.976409912109</t>
   </si>
   <si>
     <t xml:space="preserve">112.802406311035</t>
   </si>
   <si>
-    <t xml:space="preserve">112.31324005127</t>
+    <t xml:space="preserve">112.313232421875</t>
   </si>
   <si>
     <t xml:space="preserve">114.856910705566</t>
@@ -4169,10 +4169,10 @@
     <t xml:space="preserve">122.585784912109</t>
   </si>
   <si>
-    <t xml:space="preserve">122.781448364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.368453979492</t>
+    <t xml:space="preserve">122.781455993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.368446350098</t>
   </si>
   <si>
     <t xml:space="preserve">120.433433532715</t>
@@ -4187,13 +4187,13 @@
     <t xml:space="preserve">122.194450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">121.803108215332</t>
+    <t xml:space="preserve">121.803115844727</t>
   </si>
   <si>
     <t xml:space="preserve">120.042098999023</t>
   </si>
   <si>
-    <t xml:space="preserve">119.455101013184</t>
+    <t xml:space="preserve">119.455093383789</t>
   </si>
   <si>
     <t xml:space="preserve">118.574592590332</t>
@@ -4229,31 +4229,31 @@
     <t xml:space="preserve">112.019729614258</t>
   </si>
   <si>
-    <t xml:space="preserve">112.900238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.095893859863</t>
+    <t xml:space="preserve">112.900230407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.095901489258</t>
   </si>
   <si>
     <t xml:space="preserve">110.943557739258</t>
   </si>
   <si>
-    <t xml:space="preserve">111.334892272949</t>
+    <t xml:space="preserve">111.334899902344</t>
   </si>
   <si>
     <t xml:space="preserve">110.747886657715</t>
   </si>
   <si>
-    <t xml:space="preserve">110.063049316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.671722412109</t>
+    <t xml:space="preserve">110.063056945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.671714782715</t>
   </si>
   <si>
     <t xml:space="preserve">102.725517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">100.181838989258</t>
+    <t xml:space="preserve">100.181831359863</t>
   </si>
   <si>
     <t xml:space="preserve">96.8554840087891</t>
@@ -4286,10 +4286,10 @@
     <t xml:space="preserve">98.322998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">96.8065643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2195587158203</t>
+    <t xml:space="preserve">96.8065719604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2195663452148</t>
   </si>
   <si>
     <t xml:space="preserve">94.9966430664062</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">95.7303924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">97.9316558837891</t>
+    <t xml:space="preserve">97.9316635131836</t>
   </si>
   <si>
     <t xml:space="preserve">95.8282318115234</t>
@@ -4340,7 +4340,7 @@
     <t xml:space="preserve">106.638870239258</t>
   </si>
   <si>
-    <t xml:space="preserve">107.128036499023</t>
+    <t xml:space="preserve">107.128044128418</t>
   </si>
   <si>
     <t xml:space="preserve">105.954032897949</t>
@@ -4349,7 +4349,7 @@
     <t xml:space="preserve">104.682189941406</t>
   </si>
   <si>
-    <t xml:space="preserve">103.899513244629</t>
+    <t xml:space="preserve">103.899520874023</t>
   </si>
   <si>
     <t xml:space="preserve">104.78002166748</t>
@@ -4361,10 +4361,10 @@
     <t xml:space="preserve">105.660530090332</t>
   </si>
   <si>
-    <t xml:space="preserve">106.345367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.443199157715</t>
+    <t xml:space="preserve">106.345359802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.443206787109</t>
   </si>
   <si>
     <t xml:space="preserve">103.801681518555</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">112.704566955566</t>
   </si>
   <si>
-    <t xml:space="preserve">114.172073364258</t>
+    <t xml:space="preserve">114.172065734863</t>
   </si>
   <si>
     <t xml:space="preserve">117.107086181641</t>
@@ -4388,10 +4388,10 @@
     <t xml:space="preserve">115.150405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">116.813591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.204925537109</t>
+    <t xml:space="preserve">116.813583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.204917907715</t>
   </si>
   <si>
     <t xml:space="preserve">116.128746032715</t>
@@ -4412,7 +4412,7 @@
     <t xml:space="preserve">96.5619812011719</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2628860473633</t>
+    <t xml:space="preserve">94.2628936767578</t>
   </si>
   <si>
     <t xml:space="preserve">91.3767929077148</t>
@@ -4439,7 +4439,7 @@
     <t xml:space="preserve">95.3390579223633</t>
   </si>
   <si>
-    <t xml:space="preserve">94.3118133544922</t>
+    <t xml:space="preserve">94.3118057250977</t>
   </si>
   <si>
     <t xml:space="preserve">93.4802169799805</t>
@@ -4448,28 +4448,28 @@
     <t xml:space="preserve">94.7031478881836</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8498840332031</t>
+    <t xml:space="preserve">94.8498916625977</t>
   </si>
   <si>
     <t xml:space="preserve">94.2139739990234</t>
   </si>
   <si>
-    <t xml:space="preserve">91.8659591674805</t>
+    <t xml:space="preserve">91.865966796875</t>
   </si>
   <si>
     <t xml:space="preserve">90.6919479370117</t>
   </si>
   <si>
-    <t xml:space="preserve">89.2244415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7080230712891</t>
+    <t xml:space="preserve">89.2244491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7080307006836</t>
   </si>
   <si>
     <t xml:space="preserve">85.751350402832</t>
   </si>
   <si>
-    <t xml:space="preserve">84.5284194946289</t>
+    <t xml:space="preserve">84.5284271240234</t>
   </si>
   <si>
     <t xml:space="preserve">84.3327560424805</t>
@@ -4478,13 +4478,13 @@
     <t xml:space="preserve">86.2894287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2517013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.441780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0287857055664</t>
+    <t xml:space="preserve">90.251708984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4417724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0287780761719</t>
   </si>
   <si>
     <t xml:space="preserve">88.4906921386719</t>
@@ -70728,7 +70728,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.691087963</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>25847</v>
@@ -70749,6 +70749,32 @@
         <v>1731</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.691099537</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>48707</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>81.4000015258789</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>77.0999984741211</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>79.4000015258789</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>81.1999969482422</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>1724</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="1737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="1738">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5495901107788</t>
+    <t xml:space="preserve">13.5495910644531</t>
   </si>
   <si>
     <t xml:space="preserve">SES.MI</t>
@@ -50,79 +50,79 @@
     <t xml:space="preserve">13.2523736953735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9464149475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1125059127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.858998298645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0513134002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9901247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9376735687256</t>
+    <t xml:space="preserve">12.9464139938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1125068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8589992523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0513162612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9901218414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.937671661377</t>
   </si>
   <si>
     <t xml:space="preserve">13.1037654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">13.025089263916</t>
+    <t xml:space="preserve">13.0250902175903</t>
   </si>
   <si>
     <t xml:space="preserve">12.8502569198608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2383394241333</t>
+    <t xml:space="preserve">12.2383403778076</t>
   </si>
   <si>
     <t xml:space="preserve">12.5880069732666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7890663146973</t>
+    <t xml:space="preserve">12.7890644073486</t>
   </si>
   <si>
     <t xml:space="preserve">12.7191314697266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6841640472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.605489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.325756072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0460224151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.177149772644</t>
+    <t xml:space="preserve">12.6841659545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6054906845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3257570266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0460243225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1771469116211</t>
   </si>
   <si>
     <t xml:space="preserve">12.1421813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9270887374878</t>
+    <t xml:space="preserve">10.9270896911621</t>
   </si>
   <si>
     <t xml:space="preserve">10.9795398712158</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3641719818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4515886306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0984725952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1072158813477</t>
+    <t xml:space="preserve">11.3641729354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4515905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0984735488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.107213973999</t>
   </si>
   <si>
     <t xml:space="preserve">11.8886728286743</t>
@@ -134,22 +134,22 @@
     <t xml:space="preserve">11.9323806762695</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0110569000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0809888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8012552261353</t>
+    <t xml:space="preserve">12.0110549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0809879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8012561798096</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334390640259</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8274812698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0635070800781</t>
+    <t xml:space="preserve">11.8274803161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0635061264038</t>
   </si>
   <si>
     <t xml:space="preserve">12.5005893707275</t>
@@ -161,40 +161,40 @@
     <t xml:space="preserve">12.7978067398071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1649570465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1562147140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0687971115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1212491989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1911821365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7540979385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8939657211304</t>
+    <t xml:space="preserve">13.1649580001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1562156677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0687990188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1212501525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.19118309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7540988922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8939647674561</t>
   </si>
   <si>
     <t xml:space="preserve">12.9027070999146</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0600566864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1999244689941</t>
+    <t xml:space="preserve">13.0600576400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1999254226685</t>
   </si>
   <si>
     <t xml:space="preserve">12.9813814163208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4534330368042</t>
+    <t xml:space="preserve">13.4534320831299</t>
   </si>
   <si>
     <t xml:space="preserve">13.7069416046143</t>
@@ -215,22 +215,22 @@
     <t xml:space="preserve">13.0950241088867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9988641738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6404581069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4481382369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3782043457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0285406112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1509218215942</t>
+    <t xml:space="preserve">12.9988651275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6404571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4481391906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3782062530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0285396575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1509237289429</t>
   </si>
   <si>
     <t xml:space="preserve">12.4393968582153</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">12.5617818832397</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5268144607544</t>
+    <t xml:space="preserve">12.526816368103</t>
   </si>
   <si>
     <t xml:space="preserve">12.6317148208618</t>
@@ -251,19 +251,19 @@
     <t xml:space="preserve">12.771580696106</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4306554794312</t>
+    <t xml:space="preserve">12.4306573867798</t>
   </si>
   <si>
     <t xml:space="preserve">12.2820482254028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1946325302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2470817565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4131717681885</t>
+    <t xml:space="preserve">12.1946315765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2470827102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4131727218628</t>
   </si>
   <si>
     <t xml:space="preserve">12.5093326568604</t>
@@ -272,28 +272,28 @@
     <t xml:space="preserve">12.3869485855103</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8187389373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8449649810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2558240890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5792646408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2208557128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1858892440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7803230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7278747558594</t>
+    <t xml:space="preserve">11.8187408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8449640274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.255823135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5792665481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2208566665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1858882904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7803239822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7278738021851</t>
   </si>
   <si>
     <t xml:space="preserve">12.8764810562134</t>
@@ -302,31 +302,31 @@
     <t xml:space="preserve">12.8065490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7628412246704</t>
+    <t xml:space="preserve">12.7628402709961</t>
   </si>
   <si>
     <t xml:space="preserve">12.8677396774292</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8327732086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5355567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1824417114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0338315963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3048248291016</t>
+    <t xml:space="preserve">12.8327741622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5355577468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1824407577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0338325500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3048238754272</t>
   </si>
   <si>
     <t xml:space="preserve">13.2611141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3747577667236</t>
+    <t xml:space="preserve">13.3747568130493</t>
   </si>
   <si>
     <t xml:space="preserve">13.6020402908325</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">13.6894578933716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7244253158569</t>
+    <t xml:space="preserve">13.7244234085083</t>
   </si>
   <si>
     <t xml:space="preserve">13.7514753341675</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">13.5711288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8687009811401</t>
+    <t xml:space="preserve">13.8687019348145</t>
   </si>
   <si>
     <t xml:space="preserve">13.6252326965332</t>
@@ -362,25 +362,25 @@
     <t xml:space="preserve">13.6162166595459</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5260410308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5530939102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3456945419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801467895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6973705291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.778528213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6703195571899</t>
+    <t xml:space="preserve">13.5260429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.553092956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3456954956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801477432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6973714828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7785272598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6703205108643</t>
   </si>
   <si>
     <t xml:space="preserve">13.7965631484985</t>
@@ -389,10 +389,10 @@
     <t xml:space="preserve">13.9769096374512</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0400323867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.012978553772</t>
+    <t xml:space="preserve">14.0400304794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0129795074463</t>
   </si>
   <si>
     <t xml:space="preserve">13.9047708511353</t>
@@ -401,19 +401,19 @@
     <t xml:space="preserve">14.1031532287598</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2474317550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1572580337524</t>
+    <t xml:space="preserve">14.2474327087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1572570800781</t>
   </si>
   <si>
     <t xml:space="preserve">14.3646564483643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4187612533569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5179529190063</t>
+    <t xml:space="preserve">14.4187602996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.517951965332</t>
   </si>
   <si>
     <t xml:space="preserve">14.6081266403198</t>
@@ -422,19 +422,19 @@
     <t xml:space="preserve">14.6622295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3917074203491</t>
+    <t xml:space="preserve">14.3917093276978</t>
   </si>
   <si>
     <t xml:space="preserve">14.3105525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3015336990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5450019836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6441946029663</t>
+    <t xml:space="preserve">14.3015356063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5450029373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6441955566406</t>
   </si>
   <si>
     <t xml:space="preserve">14.7343683242798</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">14.7163333892822</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6351776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6261587142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6892824172974</t>
+    <t xml:space="preserve">14.6351766586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6261606216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6892833709717</t>
   </si>
   <si>
     <t xml:space="preserve">14.8245429992676</t>
@@ -458,25 +458,25 @@
     <t xml:space="preserve">14.8065071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7433853149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.581072807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6982984542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5089349746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6712474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6532115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.923731803894</t>
+    <t xml:space="preserve">14.7433862686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5810737609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.698296546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5089359283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6712455749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6532125473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9237337112427</t>
   </si>
   <si>
     <t xml:space="preserve">15.0499753952026</t>
@@ -488,28 +488,28 @@
     <t xml:space="preserve">15.3746004104614</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5549488067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9246606826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7803840637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8705549240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344850540161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7082433700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517135620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7452411651611</t>
+    <t xml:space="preserve">15.554949760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9246587753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7803821563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8705568313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344860076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7082424163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517126083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7452392578125</t>
   </si>
   <si>
     <t xml:space="preserve">16.8714828491211</t>
@@ -518,100 +518,100 @@
     <t xml:space="preserve">17.0879001617432</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1510200500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2231616973877</t>
+    <t xml:space="preserve">17.1510238647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2231597900391</t>
   </si>
   <si>
     <t xml:space="preserve">16.9796905517578</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9075508117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3043155670166</t>
+    <t xml:space="preserve">16.9075527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3043193817139</t>
   </si>
   <si>
     <t xml:space="preserve">17.0337944030762</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2772655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.475643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3223514556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1690578460693</t>
+    <t xml:space="preserve">17.2772636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4756450653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3223495483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.169059753418</t>
   </si>
   <si>
     <t xml:space="preserve">17.5838565826416</t>
   </si>
   <si>
-    <t xml:space="preserve">17.574836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5658168792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2411975860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1870880126953</t>
+    <t xml:space="preserve">17.5748348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5658206939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2411956787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1870899200439</t>
   </si>
   <si>
     <t xml:space="preserve">16.8534488677979</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8444290161133</t>
+    <t xml:space="preserve">16.8444309234619</t>
   </si>
   <si>
     <t xml:space="preserve">16.9526386260986</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7272052764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6911354064941</t>
+    <t xml:space="preserve">16.7272033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6911373138428</t>
   </si>
   <si>
     <t xml:space="preserve">16.8624668121338</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0428123474121</t>
+    <t xml:space="preserve">17.0428142547607</t>
   </si>
   <si>
     <t xml:space="preserve">16.8173789978027</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9977245330811</t>
+    <t xml:space="preserve">16.9977264404297</t>
   </si>
   <si>
     <t xml:space="preserve">16.7722911834717</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0067443847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1961040496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.358419418335</t>
+    <t xml:space="preserve">17.006742477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1961078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3584213256836</t>
   </si>
   <si>
     <t xml:space="preserve">17.6199264526367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7642002105713</t>
+    <t xml:space="preserve">17.7642040252686</t>
   </si>
   <si>
     <t xml:space="preserve">18.0076713562012</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9896373748779</t>
+    <t xml:space="preserve">17.9896354675293</t>
   </si>
   <si>
     <t xml:space="preserve">17.9445476531982</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">17.9535655975342</t>
   </si>
   <si>
-    <t xml:space="preserve">17.809289932251</t>
+    <t xml:space="preserve">17.8092880249023</t>
   </si>
   <si>
     <t xml:space="preserve">18.2601547241211</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7561111450195</t>
+    <t xml:space="preserve">18.7561092376709</t>
   </si>
   <si>
     <t xml:space="preserve">18.8462867736816</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">18.9364585876465</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6208515167236</t>
+    <t xml:space="preserve">18.620849609375</t>
   </si>
   <si>
     <t xml:space="preserve">19.2971515655518</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3602752685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3512573242188</t>
+    <t xml:space="preserve">19.3602733612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3512554168701</t>
   </si>
   <si>
     <t xml:space="preserve">19.6668643951416</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">19.6488304138184</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5586585998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.252067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1709079742432</t>
+    <t xml:space="preserve">19.5586566925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2520656585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1709117889404</t>
   </si>
   <si>
     <t xml:space="preserve">19.1348419189453</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">18.9544944763184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9094066619873</t>
+    <t xml:space="preserve">18.9094047546387</t>
   </si>
   <si>
     <t xml:space="preserve">19.0897541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5757656097412</t>
+    <t xml:space="preserve">18.5757637023926</t>
   </si>
   <si>
     <t xml:space="preserve">18.1970348358154</t>
@@ -692,16 +692,16 @@
     <t xml:space="preserve">19.4594650268555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3873233795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0185451507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3612041473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8301067352295</t>
+    <t xml:space="preserve">19.3873252868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0185432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3612022399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8301029205322</t>
   </si>
   <si>
     <t xml:space="preserve">21.2809734344482</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">20.5686016082764</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7218952178955</t>
+    <t xml:space="preserve">20.7218971252441</t>
   </si>
   <si>
     <t xml:space="preserve">20.6046714782715</t>
@@ -731,55 +731,55 @@
     <t xml:space="preserve">20.1898727416992</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3792343139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6497573852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6416702270508</t>
+    <t xml:space="preserve">20.3792400360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6497554779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6416683197021</t>
   </si>
   <si>
     <t xml:space="preserve">21.3711471557617</t>
   </si>
   <si>
-    <t xml:space="preserve">21.380163192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0925369262695</t>
+    <t xml:space="preserve">21.3801651000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0925350189209</t>
   </si>
   <si>
     <t xml:space="preserve">22.6245594024658</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7147331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8049087524414</t>
+    <t xml:space="preserve">22.7147350311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8049049377441</t>
   </si>
   <si>
     <t xml:space="preserve">23.5984344482422</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0763568878174</t>
+    <t xml:space="preserve">24.0763549804688</t>
   </si>
   <si>
     <t xml:space="preserve">24.0583209991455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7156600952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9320774078369</t>
+    <t xml:space="preserve">23.7156581878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9320812225342</t>
   </si>
   <si>
     <t xml:space="preserve">23.8599395751953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8058319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5082626342773</t>
+    <t xml:space="preserve">23.8058338165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5082588195801</t>
   </si>
   <si>
     <t xml:space="preserve">22.9942722320557</t>
@@ -788,22 +788,22 @@
     <t xml:space="preserve">22.480281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5434017181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7057151794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4532299041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4622440338135</t>
+    <t xml:space="preserve">22.5434036254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7057189941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4532279968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4622459411621</t>
   </si>
   <si>
     <t xml:space="preserve">22.0023612976074</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1827087402344</t>
+    <t xml:space="preserve">22.182710647583</t>
   </si>
   <si>
     <t xml:space="preserve">22.7237491607666</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">22.3630542755127</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2097606658936</t>
+    <t xml:space="preserve">22.2097587585449</t>
   </si>
   <si>
     <t xml:space="preserve">21.4883728027344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9212036132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8761215209961</t>
+    <t xml:space="preserve">21.9212055206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8761157989502</t>
   </si>
   <si>
     <t xml:space="preserve">21.7047882080078</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9392395019531</t>
+    <t xml:space="preserve">21.9392414093018</t>
   </si>
   <si>
     <t xml:space="preserve">22.0745010375977</t>
@@ -836,16 +836,16 @@
     <t xml:space="preserve">22.299934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8139228820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3179702758789</t>
+    <t xml:space="preserve">22.8139266967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3179740905762</t>
   </si>
   <si>
     <t xml:space="preserve">22.1917266845703</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3540382385254</t>
+    <t xml:space="preserve">22.3540420532227</t>
   </si>
   <si>
     <t xml:space="preserve">22.5253677368164</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">22.128604888916</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0835189819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2007427215576</t>
+    <t xml:space="preserve">22.083517074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2007446289062</t>
   </si>
   <si>
     <t xml:space="preserve">22.1376209259033</t>
@@ -878,25 +878,25 @@
     <t xml:space="preserve">22.1466407775879</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5965785980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3260593414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.560510635376</t>
+    <t xml:space="preserve">21.5965843200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3260555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5605125427246</t>
   </si>
   <si>
     <t xml:space="preserve">22.0294151306152</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6867561340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2368125915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3720741271973</t>
+    <t xml:space="preserve">21.6867523193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2368144989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3720722198486</t>
   </si>
   <si>
     <t xml:space="preserve">22.3991260528564</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">22.6155414581299</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6606273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0123062133789</t>
+    <t xml:space="preserve">22.6606292724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0123043060303</t>
   </si>
   <si>
     <t xml:space="preserve">23.5193881988525</t>
@@ -917,49 +917,49 @@
     <t xml:space="preserve">23.2704563140869</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1739826202393</t>
+    <t xml:space="preserve">24.1739807128906</t>
   </si>
   <si>
     <t xml:space="preserve">24.7087249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">24.773265838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.243465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8150863647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7966480255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.686014175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6675701141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0086994171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8888454437256</t>
+    <t xml:space="preserve">24.7732639312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2434673309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8150844573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7966499328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6860122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6675720214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0087032318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.888843536377</t>
   </si>
   <si>
     <t xml:space="preserve">25.9810428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0916786193848</t>
+    <t xml:space="preserve">26.0916748046875</t>
   </si>
   <si>
     <t xml:space="preserve">25.907283782959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8058700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9533805847168</t>
+    <t xml:space="preserve">25.8058662414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9533824920654</t>
   </si>
   <si>
     <t xml:space="preserve">25.6767921447754</t>
@@ -968,13 +968,13 @@
     <t xml:space="preserve">25.6583518981934</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0775146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4001998901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2619075775146</t>
+    <t xml:space="preserve">25.0775127410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.400203704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.261905670166</t>
   </si>
   <si>
     <t xml:space="preserve">25.3264446258545</t>
@@ -983,10 +983,10 @@
     <t xml:space="preserve">24.8009223937988</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4186420440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6441860198975</t>
+    <t xml:space="preserve">25.418643951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6441879272461</t>
   </si>
   <si>
     <t xml:space="preserve">24.8562393188477</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">24.8931179046631</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1874771118164</t>
+    <t xml:space="preserve">23.1874809265137</t>
   </si>
   <si>
     <t xml:space="preserve">22.9754276275635</t>
@@ -1007,13 +1007,13 @@
     <t xml:space="preserve">23.1229419708252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2335758209229</t>
+    <t xml:space="preserve">23.2335777282715</t>
   </si>
   <si>
     <t xml:space="preserve">22.9938659667969</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7818145751953</t>
+    <t xml:space="preserve">22.7818164825439</t>
   </si>
   <si>
     <t xml:space="preserve">22.6711769104004</t>
@@ -1025,70 +1025,70 @@
     <t xml:space="preserve">22.7264957427979</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5052242279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3208312988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5882015228271</t>
+    <t xml:space="preserve">22.5052261352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3208293914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5881996154785</t>
   </si>
   <si>
     <t xml:space="preserve">23.1137237548828</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9108905792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3995304107666</t>
+    <t xml:space="preserve">22.910888671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3995342254639</t>
   </si>
   <si>
     <t xml:space="preserve">23.7775402069092</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6208038330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9846477508545</t>
+    <t xml:space="preserve">23.6208057403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1413803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9846458435059</t>
   </si>
   <si>
     <t xml:space="preserve">22.8740100860596</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7357139587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6896171569824</t>
+    <t xml:space="preserve">22.7357158660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6896190643311</t>
   </si>
   <si>
     <t xml:space="preserve">23.3257751464844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7406578063965</t>
+    <t xml:space="preserve">23.7406597137451</t>
   </si>
   <si>
     <t xml:space="preserve">23.9803714752197</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9711494445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0633487701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2477416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3860397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1555423736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6165332794189</t>
+    <t xml:space="preserve">23.9711532592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0633506774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2477397918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3860340118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1555442810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6165294647217</t>
   </si>
   <si>
     <t xml:space="preserve">25.8611831665039</t>
@@ -1103,31 +1103,31 @@
     <t xml:space="preserve">25.1697082519531</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3080043792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4463005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5384979248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1236095428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4321384429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6484661102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0172500610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.109447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.339937210083</t>
+    <t xml:space="preserve">25.3080062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4462985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5384960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1236114501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4321365356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6484622955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0172481536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1094493865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3399391174316</t>
   </si>
   <si>
     <t xml:space="preserve">24.2016429901123</t>
@@ -1139,28 +1139,28 @@
     <t xml:space="preserve">24.754825592041</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6626281738281</t>
+    <t xml:space="preserve">24.6626300811768</t>
   </si>
   <si>
     <t xml:space="preserve">24.985315322876</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4923992156982</t>
+    <t xml:space="preserve">25.4923973083496</t>
   </si>
   <si>
     <t xml:space="preserve">25.7228908538818</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5704307556152</t>
+    <t xml:space="preserve">24.5704288482666</t>
   </si>
   <si>
     <t xml:space="preserve">25.5845966339111</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9994812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.414363861084</t>
+    <t xml:space="preserve">25.9994792938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4143676757812</t>
   </si>
   <si>
     <t xml:space="preserve">27.566822052002</t>
@@ -1175,25 +1175,25 @@
     <t xml:space="preserve">27.5207271575928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7370548248291</t>
+    <t xml:space="preserve">26.7370529174805</t>
   </si>
   <si>
     <t xml:space="preserve">26.5065612792969</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0314140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5243320465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3682670593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5987567901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4604644775391</t>
+    <t xml:space="preserve">25.0314159393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5243301391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3682689666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5987586975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4604625701904</t>
   </si>
   <si>
     <t xml:space="preserve">26.2299728393555</t>
@@ -1202,31 +1202,31 @@
     <t xml:space="preserve">26.3221683502197</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1980381011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2760734558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2902336120605</t>
+    <t xml:space="preserve">27.1980361938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2760696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2902355194092</t>
   </si>
   <si>
     <t xml:space="preserve">27.3824310302734</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4746246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5526599884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.829252243042</t>
+    <t xml:space="preserve">27.4746265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.552661895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8292484283447</t>
   </si>
   <si>
     <t xml:space="preserve">27.1058406829834</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8753490447998</t>
+    <t xml:space="preserve">26.8753509521484</t>
   </si>
   <si>
     <t xml:space="preserve">27.8434162139893</t>
@@ -1235,28 +1235,28 @@
     <t xml:space="preserve">28.7653827667236</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5809898376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9356117248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8114814758301</t>
+    <t xml:space="preserve">28.5809879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9356098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8114795684814</t>
   </si>
   <si>
     <t xml:space="preserve">28.1661052703857</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7192840576172</t>
+    <t xml:space="preserve">28.7192821502686</t>
   </si>
   <si>
     <t xml:space="preserve">28.120002746582</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0597457885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9675464630127</t>
+    <t xml:space="preserve">27.0597438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9675445556641</t>
   </si>
   <si>
     <t xml:space="preserve">27.1519393920898</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">26.0455799102783</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6590194702148</t>
+    <t xml:space="preserve">27.6590232849121</t>
   </si>
   <si>
     <t xml:space="preserve">26.9214496612549</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">26.1828804016113</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0886974334717</t>
+    <t xml:space="preserve">26.088695526123</t>
   </si>
   <si>
     <t xml:space="preserve">26.4654312133789</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">25.3352336883545</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9114112854004</t>
+    <t xml:space="preserve">24.9114093780518</t>
   </si>
   <si>
     <t xml:space="preserve">24.487585067749</t>
@@ -1310,13 +1310,13 @@
     <t xml:space="preserve">24.3934020996094</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9224891662598</t>
+    <t xml:space="preserve">23.9224872589111</t>
   </si>
   <si>
     <t xml:space="preserve">23.263204574585</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0277500152588</t>
+    <t xml:space="preserve">23.0277519226074</t>
   </si>
   <si>
     <t xml:space="preserve">23.0748405456543</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">22.7451992034912</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6039257049561</t>
+    <t xml:space="preserve">22.6039237976074</t>
   </si>
   <si>
     <t xml:space="preserve">22.5097427368164</t>
@@ -1334,37 +1334,37 @@
     <t xml:space="preserve">22.4155578613281</t>
   </si>
   <si>
-    <t xml:space="preserve">22.180103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0388259887695</t>
+    <t xml:space="preserve">22.1801013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0388298034668</t>
   </si>
   <si>
     <t xml:space="preserve">21.8504638671875</t>
   </si>
   <si>
-    <t xml:space="preserve">22.462646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2271919250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4044818878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2161140441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8864727020264</t>
+    <t xml:space="preserve">22.4626502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2271938323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4044799804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2161159515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.886474609375</t>
   </si>
   <si>
     <t xml:space="preserve">23.498664855957</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5568351745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1330108642578</t>
+    <t xml:space="preserve">22.5568370819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1330070495605</t>
   </si>
   <si>
     <t xml:space="preserve">21.6620960235596</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">21.0028133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.096996307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8615398406982</t>
+    <t xml:space="preserve">21.0969944000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8615417480469</t>
   </si>
   <si>
     <t xml:space="preserve">21.3795471191406</t>
@@ -1388,10 +1388,10 @@
     <t xml:space="preserve">21.4737281799316</t>
   </si>
   <si>
-    <t xml:space="preserve">22.274284362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7562789916992</t>
+    <t xml:space="preserve">22.2742824554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7562770843506</t>
   </si>
   <si>
     <t xml:space="preserve">21.9446430206299</t>
@@ -1400,10 +1400,10 @@
     <t xml:space="preserve">21.5679111480713</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5208206176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3324546813965</t>
+    <t xml:space="preserve">21.5208225250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3324565887451</t>
   </si>
   <si>
     <t xml:space="preserve">21.2382698059082</t>
@@ -1415,16 +1415,16 @@
     <t xml:space="preserve">22.7922916412354</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5457534790039</t>
+    <t xml:space="preserve">23.5457572937012</t>
   </si>
   <si>
     <t xml:space="preserve">23.6399402618408</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7341194152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6870269775391</t>
+    <t xml:space="preserve">23.7341213226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6870307922363</t>
   </si>
   <si>
     <t xml:space="preserve">23.781213760376</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">24.7230434417725</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6288604736328</t>
+    <t xml:space="preserve">24.6288623809814</t>
   </si>
   <si>
     <t xml:space="preserve">24.675952911377</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">24.5817680358887</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7701320648193</t>
+    <t xml:space="preserve">24.770133972168</t>
   </si>
   <si>
     <t xml:space="preserve">24.9585018157959</t>
@@ -1466,79 +1466,79 @@
     <t xml:space="preserve">25.7590560913086</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9474201202393</t>
+    <t xml:space="preserve">25.9474239349365</t>
   </si>
   <si>
     <t xml:space="preserve">26.277063369751</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9363441467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.983434677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8421630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7479763031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2659893035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4543495178223</t>
+    <t xml:space="preserve">26.9363460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9834365844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8421611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.747974395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2659854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4543514251709</t>
   </si>
   <si>
     <t xml:space="preserve">27.501443862915</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3130779266357</t>
+    <t xml:space="preserve">27.3130760192871</t>
   </si>
   <si>
     <t xml:space="preserve">27.0776176452637</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7008857727051</t>
+    <t xml:space="preserve">26.7008876800537</t>
   </si>
   <si>
     <t xml:space="preserve">26.6537952423096</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6067047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.994514465332</t>
+    <t xml:space="preserve">26.6067066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9945163726807</t>
   </si>
   <si>
     <t xml:space="preserve">26.1357898712158</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0416069030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6177845001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4294128417969</t>
+    <t xml:space="preserve">26.0416030883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6177825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4294166564941</t>
   </si>
   <si>
     <t xml:space="preserve">25.0055904388428</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0997772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8643169403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4404945373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5236015319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3712463378906</t>
+    <t xml:space="preserve">25.0997753143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8643188476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4404926300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5235996246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.371244430542</t>
   </si>
   <si>
     <t xml:space="preserve">26.3241577148438</t>
@@ -1547,52 +1547,52 @@
     <t xml:space="preserve">26.7950706481934</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8892517089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0305252075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1718006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5485343933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6898059844971</t>
+    <t xml:space="preserve">26.8892498016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0305290222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1718044281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5485324859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6898078918457</t>
   </si>
   <si>
     <t xml:space="preserve">28.1136322021484</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3961811065674</t>
+    <t xml:space="preserve">28.3961791992188</t>
   </si>
   <si>
     <t xml:space="preserve">28.7258205413818</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9141883850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9502010345459</t>
+    <t xml:space="preserve">28.914192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9502029418945</t>
   </si>
   <si>
     <t xml:space="preserve">29.7618370056152</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3269348144531</t>
+    <t xml:space="preserve">30.3269329071045</t>
   </si>
   <si>
     <t xml:space="preserve">30.3740234375</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5042190551758</t>
+    <t xml:space="preserve">31.5042266845703</t>
   </si>
   <si>
     <t xml:space="preserve">31.6925888061523</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4460525512695</t>
+    <t xml:space="preserve">32.4460487365723</t>
   </si>
   <si>
     <t xml:space="preserve">32.4931449890137</t>
@@ -1601,121 +1601,121 @@
     <t xml:space="preserve">33.482063293457</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6704330444336</t>
+    <t xml:space="preserve">33.6704292297363</t>
   </si>
   <si>
     <t xml:space="preserve">33.2936973571777</t>
   </si>
   <si>
-    <t xml:space="preserve">33.576244354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.905891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2466087341309</t>
+    <t xml:space="preserve">33.5762481689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9058837890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2466049194336</t>
   </si>
   <si>
     <t xml:space="preserve">32.8698768615723</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1524200439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.058235168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5873222351074</t>
+    <t xml:space="preserve">33.1524238586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0582389831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5873260498047</t>
   </si>
   <si>
     <t xml:space="preserve">32.3047752380371</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9280490875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4571323394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3629474639893</t>
+    <t xml:space="preserve">31.9280433654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4571285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.362943649292</t>
   </si>
   <si>
     <t xml:space="preserve">30.8920307159424</t>
   </si>
   <si>
-    <t xml:space="preserve">31.080394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0333099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6565723419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6094837188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2687664031982</t>
+    <t xml:space="preserve">31.0803966522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0333080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6565742492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6094818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2687644958496</t>
   </si>
   <si>
     <t xml:space="preserve">30.9862155914307</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4100399017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8449401855469</t>
+    <t xml:space="preserve">31.4100379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8449382781982</t>
   </si>
   <si>
     <t xml:space="preserve">31.1745777130127</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8809509277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0222282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7396793365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0000648498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4709815979004</t>
+    <t xml:space="preserve">31.880952835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0222244262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7396831512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0000686645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4709892272949</t>
   </si>
   <si>
     <t xml:space="preserve">35.78955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5901031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7784652709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1552047729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.673210144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0846748352051</t>
+    <t xml:space="preserve">36.5901069641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7784690856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.155200958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6732063293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0846786499023</t>
   </si>
   <si>
     <t xml:space="preserve">38.228214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3669967651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7976036071777</t>
+    <t xml:space="preserve">37.367000579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.797607421875</t>
   </si>
   <si>
     <t xml:space="preserve">38.1803665161133</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3717422485352</t>
+    <t xml:space="preserve">38.3717460632324</t>
   </si>
   <si>
     <t xml:space="preserve">37.9411430358887</t>
@@ -1733,13 +1733,13 @@
     <t xml:space="preserve">38.8501930236816</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7545051574707</t>
+    <t xml:space="preserve">38.754508972168</t>
   </si>
   <si>
     <t xml:space="preserve">39.3286476135254</t>
   </si>
   <si>
-    <t xml:space="preserve">39.041576385498</t>
+    <t xml:space="preserve">39.0415802001953</t>
   </si>
   <si>
     <t xml:space="preserve">38.8023490905762</t>
@@ -1754,37 +1754,37 @@
     <t xml:space="preserve">38.8980445861816</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7066612243652</t>
+    <t xml:space="preserve">38.7066650390625</t>
   </si>
   <si>
     <t xml:space="preserve">38.2760543823242</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5631217956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4195938110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3764915466309</t>
+    <t xml:space="preserve">38.5631256103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4195899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3764953613281</t>
   </si>
   <si>
     <t xml:space="preserve">39.1372680664062</t>
   </si>
   <si>
-    <t xml:space="preserve">39.185115814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2807998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9027862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1946067810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1036605834961</t>
+    <t xml:space="preserve">39.1851119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2808036804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9027900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1946029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1036643981934</t>
   </si>
   <si>
     <t xml:space="preserve">42.5342712402344</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">41.6730537414551</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8118476867676</t>
+    <t xml:space="preserve">40.8118438720703</t>
   </si>
   <si>
     <t xml:space="preserve">40.7161521911621</t>
@@ -1811,28 +1811,28 @@
     <t xml:space="preserve">44.2566909790039</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7829856872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4433288574219</t>
+    <t xml:space="preserve">44.7829895019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4433250427246</t>
   </si>
   <si>
     <t xml:space="preserve">44.0174674987793</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6347045898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2041053771973</t>
+    <t xml:space="preserve">43.6347007751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2041015625</t>
   </si>
   <si>
     <t xml:space="preserve">42.9170303344727</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9265251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.404972076416</t>
+    <t xml:space="preserve">44.9265213012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4049682617188</t>
   </si>
   <si>
     <t xml:space="preserve">45.2614326477051</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">47.6536865234375</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8976631164551</t>
+    <t xml:space="preserve">48.8976593017578</t>
   </si>
   <si>
     <t xml:space="preserve">48.6105918884277</t>
@@ -1856,16 +1856,16 @@
     <t xml:space="preserve">48.993350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7588768005371</t>
+    <t xml:space="preserve">49.7588729858398</t>
   </si>
   <si>
     <t xml:space="preserve">49.2804222106934</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6631851196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3761177062988</t>
+    <t xml:space="preserve">49.6631813049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3761138916016</t>
   </si>
   <si>
     <t xml:space="preserve">49.5674934387207</t>
@@ -1874,31 +1874,31 @@
     <t xml:space="preserve">50.6200828552246</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0028419494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.7252655029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6295738220215</t>
+    <t xml:space="preserve">51.0028457641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.725269317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6295776367188</t>
   </si>
   <si>
     <t xml:space="preserve">51.9597434997559</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8640556335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6726684570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4192161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3235168457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0459518432617</t>
+    <t xml:space="preserve">51.8640594482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6726760864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4192123413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3235206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0459480285645</t>
   </si>
   <si>
     <t xml:space="preserve">51.3856086730957</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">50.907154083252</t>
   </si>
   <si>
-    <t xml:space="preserve">49.854564666748</t>
+    <t xml:space="preserve">49.8545608520508</t>
   </si>
   <si>
     <t xml:space="preserve">50.4287033081055</t>
@@ -1916,16 +1916,16 @@
     <t xml:space="preserve">52.5338897705078</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0649261474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2994041442871</t>
+    <t xml:space="preserve">54.0649337768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2994079589844</t>
   </si>
   <si>
     <t xml:space="preserve">52.4381980895996</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3666229248047</t>
+    <t xml:space="preserve">47.3666191101074</t>
   </si>
   <si>
     <t xml:space="preserve">46.9838562011719</t>
@@ -1940,67 +1940,67 @@
     <t xml:space="preserve">44.9743614196777</t>
   </si>
   <si>
-    <t xml:space="preserve">43.586856842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7687454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6493225097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.596736907959</t>
+    <t xml:space="preserve">43.5868606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7687492370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6493263244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5967292785645</t>
   </si>
   <si>
     <t xml:space="preserve">30.0945510864258</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4820594787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1854934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5299015045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0992984771729</t>
+    <t xml:space="preserve">31.4820575714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1854915618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5299034118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0992946624756</t>
   </si>
   <si>
     <t xml:space="preserve">30.3816204071045</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9269027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4100952148438</t>
+    <t xml:space="preserve">34.9268989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.410099029541</t>
   </si>
   <si>
     <t xml:space="preserve">35.5010414123535</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3096694946289</t>
+    <t xml:space="preserve">35.3096656799316</t>
   </si>
   <si>
     <t xml:space="preserve">34.5441398620605</t>
   </si>
   <si>
-    <t xml:space="preserve">35.070442199707</t>
+    <t xml:space="preserve">35.0704383850098</t>
   </si>
   <si>
     <t xml:space="preserve">37.0799293518066</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2234649658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1277694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2329521179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.429084777832</t>
+    <t xml:space="preserve">37.223461151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1277732849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2329597473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4290885925293</t>
   </si>
   <si>
     <t xml:space="preserve">39.998477935791</t>
@@ -2009,22 +2009,22 @@
     <t xml:space="preserve">44.7351379394531</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9791107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4528160095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0700607299805</t>
+    <t xml:space="preserve">45.9791145324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4528198242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0700569152832</t>
   </si>
   <si>
     <t xml:space="preserve">45.3571319580078</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1179008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4575576782227</t>
+    <t xml:space="preserve">45.1179046630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4575614929199</t>
   </si>
   <si>
     <t xml:space="preserve">45.6441955566406</t>
@@ -2042,13 +2042,13 @@
     <t xml:space="preserve">44.2088432312012</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1562538146973</t>
+    <t xml:space="preserve">43.15625</t>
   </si>
   <si>
     <t xml:space="preserve">43.9217758178711</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8644371032715</t>
+    <t xml:space="preserve">41.8644409179688</t>
   </si>
   <si>
     <t xml:space="preserve">42.5821113586426</t>
@@ -2057,19 +2057,19 @@
     <t xml:space="preserve">45.0222091674805</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5485076904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5101585388184</t>
+    <t xml:space="preserve">45.5485038757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5101547241211</t>
   </si>
   <si>
     <t xml:space="preserve">47.7015342712402</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7062873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9407577514648</t>
+    <t xml:space="preserve">48.7062835693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9407615661621</t>
   </si>
   <si>
     <t xml:space="preserve">48.5149040222168</t>
@@ -2078,61 +2078,61 @@
     <t xml:space="preserve">51.4812965393066</t>
   </si>
   <si>
-    <t xml:space="preserve">51.194221496582</t>
+    <t xml:space="preserve">51.1942253112793</t>
   </si>
   <si>
     <t xml:space="preserve">51.768367767334</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2899131774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1080284118652</t>
+    <t xml:space="preserve">51.289909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1080322265625</t>
   </si>
   <si>
     <t xml:space="preserve">53.96923828125</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4907913208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1175231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6916580200195</t>
+    <t xml:space="preserve">53.490795135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1175193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6916618347168</t>
   </si>
   <si>
     <t xml:space="preserve">55.5002822875977</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3519973754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6390686035156</t>
+    <t xml:space="preserve">54.351993560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6390647888184</t>
   </si>
   <si>
     <t xml:space="preserve">54.830451965332</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4045906066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.744255065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9356346130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1270179748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2658042907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9787330627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3183937072754</t>
+    <t xml:space="preserve">55.4045944213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7442512512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9356307983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1270141601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2658004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9787292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3183975219727</t>
   </si>
   <si>
     <t xml:space="preserve">58.6580543518066</t>
@@ -2150,70 +2150,70 @@
     <t xml:space="preserve">57.988224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">58.8494415283203</t>
+    <t xml:space="preserve">58.849437713623</t>
   </si>
   <si>
     <t xml:space="preserve">61.3373794555664</t>
   </si>
   <si>
-    <t xml:space="preserve">63.4425659179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2942848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3468742370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7296333312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6339492797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3037643432617</t>
+    <t xml:space="preserve">63.442569732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2942810058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.346866607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7296295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6339454650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3037719726562</t>
   </si>
   <si>
     <t xml:space="preserve">64.5908432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">65.9305114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6960220336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3563613891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.9831008911133</t>
+    <t xml:space="preserve">65.9305038452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6960296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3563766479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9830932617188</t>
   </si>
   <si>
     <t xml:space="preserve">67.1744766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5046539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8443145751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.0451812744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1839828491211</t>
+    <t xml:space="preserve">66.5046463012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8443069458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.0451889038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1839752197266</t>
   </si>
   <si>
     <t xml:space="preserve">71.2891540527344</t>
   </si>
   <si>
-    <t xml:space="preserve">70.8107070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6193389892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7676086425781</t>
+    <t xml:space="preserve">70.8107147216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6193313598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7676010131836</t>
   </si>
   <si>
     <t xml:space="preserve">72.0546722412109</t>
@@ -2225,16 +2225,16 @@
     <t xml:space="preserve">69.4710464477539</t>
   </si>
   <si>
-    <t xml:space="preserve">68.9925994873047</t>
+    <t xml:space="preserve">68.9925918579102</t>
   </si>
   <si>
     <t xml:space="preserve">69.9494934082031</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8012161254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.6624298095703</t>
+    <t xml:space="preserve">68.8012084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.6624221801758</t>
   </si>
   <si>
     <t xml:space="preserve">76.5521087646484</t>
@@ -2246,16 +2246,16 @@
     <t xml:space="preserve">75.8822860717773</t>
   </si>
   <si>
-    <t xml:space="preserve">74.7339935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.8727798461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8296813964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.8917770385742</t>
+    <t xml:space="preserve">74.734001159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.8727874755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8296890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.8917694091797</t>
   </si>
   <si>
     <t xml:space="preserve">78.2745361328125</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">81.910758972168</t>
   </si>
   <si>
-    <t xml:space="preserve">82.3892135620117</t>
+    <t xml:space="preserve">82.3892059326172</t>
   </si>
   <si>
     <t xml:space="preserve">81.4323043823242</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">80.4754028320312</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7193756103516</t>
+    <t xml:space="preserve">81.7193832397461</t>
   </si>
   <si>
     <t xml:space="preserve">81.815071105957</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">80.9538497924805</t>
   </si>
   <si>
-    <t xml:space="preserve">82.7719650268555</t>
+    <t xml:space="preserve">82.7719802856445</t>
   </si>
   <si>
     <t xml:space="preserve">82.2935180664062</t>
@@ -2312,40 +2312,40 @@
     <t xml:space="preserve">77.0305633544922</t>
   </si>
   <si>
-    <t xml:space="preserve">79.3271255493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.728874206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.1021499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.7434844970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.5185012817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8055725097656</t>
+    <t xml:space="preserve">79.3271331787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7288818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.1021423339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.7434921264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.5185165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8055801391602</t>
   </si>
   <si>
     <t xml:space="preserve">82.4848937988281</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3797149658203</t>
+    <t xml:space="preserve">80.3797225952148</t>
   </si>
   <si>
     <t xml:space="preserve">78.6572952270508</t>
   </si>
   <si>
-    <t xml:space="preserve">78.4659042358398</t>
+    <t xml:space="preserve">78.4659194946289</t>
   </si>
   <si>
     <t xml:space="preserve">84.6857681274414</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3556137084961</t>
+    <t xml:space="preserve">85.3556060791016</t>
   </si>
   <si>
     <t xml:space="preserve">83.0590438842773</t>
@@ -2354,28 +2354,28 @@
     <t xml:space="preserve">85.9297485351562</t>
   </si>
   <si>
-    <t xml:space="preserve">87.173713684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2694091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3220062255859</t>
+    <t xml:space="preserve">87.1737213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.269401550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3219985961914</t>
   </si>
   <si>
     <t xml:space="preserve">86.7909545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">90.905632019043</t>
+    <t xml:space="preserve">90.9056396484375</t>
   </si>
   <si>
     <t xml:space="preserve">91.3840866088867</t>
   </si>
   <si>
-    <t xml:space="preserve">93.1065216064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.8815155029297</t>
+    <t xml:space="preserve">93.1065139770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.8815231323242</t>
   </si>
   <si>
     <t xml:space="preserve">97.2211837768555</t>
@@ -2402,10 +2402,10 @@
     <t xml:space="preserve">96.2642822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">95.6901397705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8289260864258</t>
+    <t xml:space="preserve">95.6901473999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8289337158203</t>
   </si>
   <si>
     <t xml:space="preserve">95.307373046875</t>
@@ -2414,22 +2414,22 @@
     <t xml:space="preserve">94.2547836303711</t>
   </si>
   <si>
-    <t xml:space="preserve">94.446174621582</t>
+    <t xml:space="preserve">94.4461669921875</t>
   </si>
   <si>
     <t xml:space="preserve">97.0298080444336</t>
   </si>
   <si>
-    <t xml:space="preserve">94.541862487793</t>
+    <t xml:space="preserve">94.5418548583984</t>
   </si>
   <si>
     <t xml:space="preserve">94.1591033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8720321655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0634155273438</t>
+    <t xml:space="preserve">93.8720245361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0634078979492</t>
   </si>
   <si>
     <t xml:space="preserve">93.3935775756836</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">93.6806488037109</t>
   </si>
   <si>
-    <t xml:space="preserve">92.9151153564453</t>
+    <t xml:space="preserve">92.9151229858398</t>
   </si>
   <si>
     <t xml:space="preserve">93.2978897094727</t>
@@ -2447,22 +2447,22 @@
     <t xml:space="preserve">92.723747253418</t>
   </si>
   <si>
-    <t xml:space="preserve">94.3504791259766</t>
+    <t xml:space="preserve">94.3504867553711</t>
   </si>
   <si>
     <t xml:space="preserve">97.6039505004883</t>
   </si>
   <si>
-    <t xml:space="preserve">101.431549072266</t>
+    <t xml:space="preserve">101.43155670166</t>
   </si>
   <si>
     <t xml:space="preserve">104.876396179199</t>
   </si>
   <si>
-    <t xml:space="preserve">104.493629455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.598808288574</t>
+    <t xml:space="preserve">104.493621826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.598815917969</t>
   </si>
   <si>
     <t xml:space="preserve">107.364326477051</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">109.660903930664</t>
   </si>
   <si>
-    <t xml:space="preserve">110.235046386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.641914367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.21605682373</t>
+    <t xml:space="preserve">110.235038757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.64192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.216064453125</t>
   </si>
   <si>
     <t xml:space="preserve">107.9384765625</t>
@@ -2486,25 +2486,25 @@
     <t xml:space="preserve">107.555725097656</t>
   </si>
   <si>
-    <t xml:space="preserve">109.469520568848</t>
+    <t xml:space="preserve">109.469528198242</t>
   </si>
   <si>
     <t xml:space="preserve">107.747100830078</t>
   </si>
   <si>
-    <t xml:space="preserve">108.703994750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.197074890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5177536010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.7091293334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.345336914062</t>
+    <t xml:space="preserve">108.703987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.197082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5177459716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.7091217041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.345352172852</t>
   </si>
   <si>
     <t xml:space="preserve">103.536735534668</t>
@@ -2513,19 +2513,19 @@
     <t xml:space="preserve">106.024673461914</t>
   </si>
   <si>
-    <t xml:space="preserve">106.981582641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.512619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.833290100098</t>
+    <t xml:space="preserve">106.981590270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.512626647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.833282470703</t>
   </si>
   <si>
     <t xml:space="preserve">101.048789978027</t>
   </si>
   <si>
-    <t xml:space="preserve">102.388442993164</t>
+    <t xml:space="preserve">102.388450622559</t>
   </si>
   <si>
     <t xml:space="preserve">103.153968811035</t>
@@ -2534,22 +2534,22 @@
     <t xml:space="preserve">102.962593078613</t>
   </si>
   <si>
-    <t xml:space="preserve">105.450531005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.005683898926</t>
+    <t xml:space="preserve">105.450538635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.00569152832</t>
   </si>
   <si>
     <t xml:space="preserve">103.919486999512</t>
   </si>
   <si>
-    <t xml:space="preserve">106.407432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.086753845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.809181213379</t>
+    <t xml:space="preserve">106.407440185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.086761474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.809188842773</t>
   </si>
   <si>
     <t xml:space="preserve">113.679893493652</t>
@@ -2564,19 +2564,19 @@
     <t xml:space="preserve">111.000564575195</t>
   </si>
   <si>
-    <t xml:space="preserve">112.914375305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.852279663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.426422119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.383316040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.340225219727</t>
+    <t xml:space="preserve">112.914367675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.85228729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.426429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.383323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.340232849121</t>
   </si>
   <si>
     <t xml:space="preserve">114.445411682129</t>
@@ -2588,19 +2588,19 @@
     <t xml:space="preserve">112.722984313965</t>
   </si>
   <si>
-    <t xml:space="preserve">115.019554138184</t>
+    <t xml:space="preserve">115.019546508789</t>
   </si>
   <si>
     <t xml:space="preserve">115.593696594238</t>
   </si>
   <si>
-    <t xml:space="preserve">115.210929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.741973876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.167831420898</t>
+    <t xml:space="preserve">115.210922241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.741966247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.167839050293</t>
   </si>
   <si>
     <t xml:space="preserve">115.78507232666</t>
@@ -2624,25 +2624,25 @@
     <t xml:space="preserve">123.631660461426</t>
   </si>
   <si>
-    <t xml:space="preserve">131.478256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.26789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.459266662598</t>
+    <t xml:space="preserve">131.478240966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.267890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.459259033203</t>
   </si>
   <si>
     <t xml:space="preserve">128.990325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">132.05241394043</t>
+    <t xml:space="preserve">132.052398681641</t>
   </si>
   <si>
     <t xml:space="preserve">134.157577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">133.774826049805</t>
+    <t xml:space="preserve">133.774810791016</t>
   </si>
   <si>
     <t xml:space="preserve">132.626541137695</t>
@@ -2651,10 +2651,10 @@
     <t xml:space="preserve">132.435150146484</t>
   </si>
   <si>
-    <t xml:space="preserve">134.923110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.645523071289</t>
+    <t xml:space="preserve">134.923095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.6455078125</t>
   </si>
   <si>
     <t xml:space="preserve">137.411071777344</t>
@@ -2663,22 +2663,22 @@
     <t xml:space="preserve">135.305862426758</t>
   </si>
   <si>
-    <t xml:space="preserve">131.861022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.731735229492</t>
+    <t xml:space="preserve">131.86100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.731719970703</t>
   </si>
   <si>
     <t xml:space="preserve">136.262756347656</t>
   </si>
   <si>
-    <t xml:space="preserve">137.793807983398</t>
+    <t xml:space="preserve">137.793792724609</t>
   </si>
   <si>
     <t xml:space="preserve">138.176559448242</t>
   </si>
   <si>
-    <t xml:space="preserve">137.028289794922</t>
+    <t xml:space="preserve">137.028274536133</t>
   </si>
   <si>
     <t xml:space="preserve">138.559341430664</t>
@@ -2687,40 +2687,40 @@
     <t xml:space="preserve">139.898986816406</t>
   </si>
   <si>
-    <t xml:space="preserve">136.454162597656</t>
+    <t xml:space="preserve">136.454147338867</t>
   </si>
   <si>
     <t xml:space="preserve">138.750701904297</t>
   </si>
   <si>
-    <t xml:space="preserve">139.324859619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.985198974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.497268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.492111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.874862670898</t>
+    <t xml:space="preserve">139.324844360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.98518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.497253417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.492095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.874877929688</t>
   </si>
   <si>
     <t xml:space="preserve">144.109344482422</t>
   </si>
   <si>
-    <t xml:space="preserve">142.195571899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.726593017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.91796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.683471679688</t>
+    <t xml:space="preserve">142.195556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.726608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.917984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.683486938477</t>
   </si>
   <si>
     <t xml:space="preserve">145.257629394531</t>
@@ -2729,10 +2729,10 @@
     <t xml:space="preserve">147.936965942383</t>
   </si>
   <si>
-    <t xml:space="preserve">145.640380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.788650512695</t>
+    <t xml:space="preserve">145.640396118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.788681030273</t>
   </si>
   <si>
     <t xml:space="preserve">149.276626586914</t>
@@ -2744,28 +2744,28 @@
     <t xml:space="preserve">150.424896240234</t>
   </si>
   <si>
-    <t xml:space="preserve">153.486968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.33869934082</t>
+    <t xml:space="preserve">153.48698425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.338714599609</t>
   </si>
   <si>
     <t xml:space="preserve">155.400772094727</t>
   </si>
   <si>
-    <t xml:space="preserve">151.190414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.888732910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.037002563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.654251098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.611145019531</t>
+    <t xml:space="preserve">151.1904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.888717651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.037033081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.654266357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.61116027832</t>
   </si>
   <si>
     <t xml:space="preserve">161.333587646484</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">161.524963378906</t>
   </si>
   <si>
-    <t xml:space="preserve">163.438751220703</t>
+    <t xml:space="preserve">163.438766479492</t>
   </si>
   <si>
     <t xml:space="preserve">163.821517944336</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">168.606018066406</t>
   </si>
   <si>
-    <t xml:space="preserve">173.773315429688</t>
+    <t xml:space="preserve">173.773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">170.32844543457</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">165.352584838867</t>
   </si>
   <si>
-    <t xml:space="preserve">160.759429931641</t>
+    <t xml:space="preserve">160.75944519043</t>
   </si>
   <si>
     <t xml:space="preserve">162.099090576172</t>
@@ -2807,13 +2807,13 @@
     <t xml:space="preserve">171.668121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">167.074981689453</t>
+    <t xml:space="preserve">167.074996948242</t>
   </si>
   <si>
     <t xml:space="preserve">161.93049621582</t>
   </si>
   <si>
-    <t xml:space="preserve">161.353561401367</t>
+    <t xml:space="preserve">161.353576660156</t>
   </si>
   <si>
     <t xml:space="preserve">160.58430480957</t>
@@ -2828,10 +2828,10 @@
     <t xml:space="preserve">145.583602905273</t>
   </si>
   <si>
-    <t xml:space="preserve">147.314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.391510009766</t>
+    <t xml:space="preserve">147.314468383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.391525268555</t>
   </si>
   <si>
     <t xml:space="preserve">150.199203491211</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">148.083724975586</t>
   </si>
   <si>
-    <t xml:space="preserve">151.737731933594</t>
+    <t xml:space="preserve">151.737747192383</t>
   </si>
   <si>
     <t xml:space="preserve">149.622268676758</t>
@@ -2858,19 +2858,19 @@
     <t xml:space="preserve">154.43017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">160.776611328125</t>
+    <t xml:space="preserve">160.776626586914</t>
   </si>
   <si>
     <t xml:space="preserve">166.353790283203</t>
   </si>
   <si>
-    <t xml:space="preserve">170.200119018555</t>
+    <t xml:space="preserve">170.200134277344</t>
   </si>
   <si>
     <t xml:space="preserve">168.469268798828</t>
   </si>
   <si>
-    <t xml:space="preserve">164.430633544922</t>
+    <t xml:space="preserve">164.430648803711</t>
   </si>
   <si>
     <t xml:space="preserve">165.007598876953</t>
@@ -2894,13 +2894,13 @@
     <t xml:space="preserve">161.738189697266</t>
   </si>
   <si>
-    <t xml:space="preserve">168.853927612305</t>
+    <t xml:space="preserve">168.853942871094</t>
   </si>
   <si>
     <t xml:space="preserve">177.508163452148</t>
   </si>
   <si>
-    <t xml:space="preserve">175.585006713867</t>
+    <t xml:space="preserve">175.584991455078</t>
   </si>
   <si>
     <t xml:space="preserve">180.392913818359</t>
@@ -2909,19 +2909,19 @@
     <t xml:space="preserve">180.777526855469</t>
   </si>
   <si>
-    <t xml:space="preserve">178.469757080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.815948486328</t>
+    <t xml:space="preserve">178.469741821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.815963745117</t>
   </si>
   <si>
     <t xml:space="preserve">181.739120483398</t>
   </si>
   <si>
-    <t xml:space="preserve">185.008514404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.085342407227</t>
+    <t xml:space="preserve">185.008499145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.085327148438</t>
   </si>
   <si>
     <t xml:space="preserve">182.508392333984</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">167.507690429688</t>
   </si>
   <si>
-    <t xml:space="preserve">174.046463012695</t>
+    <t xml:space="preserve">174.046447753906</t>
   </si>
   <si>
     <t xml:space="preserve">170.96940612793</t>
@@ -2963,16 +2963,16 @@
     <t xml:space="preserve">171.93098449707</t>
   </si>
   <si>
-    <t xml:space="preserve">167.315368652344</t>
+    <t xml:space="preserve">167.315383911133</t>
   </si>
   <si>
     <t xml:space="preserve">163.85368347168</t>
   </si>
   <si>
-    <t xml:space="preserve">166.738418579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.238311767578</t>
+    <t xml:space="preserve">166.738433837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.238327026367</t>
   </si>
   <si>
     <t xml:space="preserve">166.546112060547</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">157.314926147461</t>
   </si>
   <si>
-    <t xml:space="preserve">159.815017700195</t>
+    <t xml:space="preserve">159.815032958984</t>
   </si>
   <si>
     <t xml:space="preserve">156.930282592773</t>
@@ -3011,22 +3011,22 @@
     <t xml:space="preserve">145.968246459961</t>
   </si>
   <si>
-    <t xml:space="preserve">146.929824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.353088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.468597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.276245117188</t>
+    <t xml:space="preserve">146.929840087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.353103637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.468612670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.276260375977</t>
   </si>
   <si>
     <t xml:space="preserve">157.122589111328</t>
   </si>
   <si>
-    <t xml:space="preserve">151.930053710938</t>
+    <t xml:space="preserve">151.930068969727</t>
   </si>
   <si>
     <t xml:space="preserve">146.545181274414</t>
@@ -3035,16 +3035,16 @@
     <t xml:space="preserve">140.968032836914</t>
   </si>
   <si>
-    <t xml:space="preserve">136.92936706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.660232543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.698425292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.506103515625</t>
+    <t xml:space="preserve">136.929351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.660217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.69841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.506088256836</t>
   </si>
   <si>
     <t xml:space="preserve">130.198287963867</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">128.852081298828</t>
   </si>
   <si>
-    <t xml:space="preserve">129.621353149414</t>
+    <t xml:space="preserve">129.621337890625</t>
   </si>
   <si>
     <t xml:space="preserve">132.890716552734</t>
@@ -3071,22 +3071,22 @@
     <t xml:space="preserve">137.506332397461</t>
   </si>
   <si>
-    <t xml:space="preserve">136.160125732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.467910766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.583160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.813430786133</t>
+    <t xml:space="preserve">136.160110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.467895507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.583145141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.813423156738</t>
   </si>
   <si>
     <t xml:space="preserve">118.659294128418</t>
   </si>
   <si>
-    <t xml:space="preserve">125.582702636719</t>
+    <t xml:space="preserve">125.582710266113</t>
   </si>
   <si>
     <t xml:space="preserve">125.198066711426</t>
@@ -3098,49 +3098,49 @@
     <t xml:space="preserve">138.852523803711</t>
   </si>
   <si>
-    <t xml:space="preserve">142.891204833984</t>
+    <t xml:space="preserve">142.891189575195</t>
   </si>
   <si>
     <t xml:space="preserve">140.391067504883</t>
   </si>
   <si>
-    <t xml:space="preserve">145.39128112793</t>
+    <t xml:space="preserve">145.391296386719</t>
   </si>
   <si>
     <t xml:space="preserve">145.00666809082</t>
   </si>
   <si>
-    <t xml:space="preserve">145.775924682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.814346313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.276031494141</t>
+    <t xml:space="preserve">145.775939941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.814361572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.27604675293</t>
   </si>
   <si>
     <t xml:space="preserve">143.275817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">142.60270690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.698867797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.083511352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.525650024414</t>
+    <t xml:space="preserve">142.602722167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.698852539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.08349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.525665283203</t>
   </si>
   <si>
     <t xml:space="preserve">141.160354614258</t>
   </si>
   <si>
-    <t xml:space="preserve">140.198776245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.910278320312</t>
+    <t xml:space="preserve">140.198760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.910263061523</t>
   </si>
   <si>
     <t xml:space="preserve">139.429489135742</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">139.237182617188</t>
   </si>
   <si>
-    <t xml:space="preserve">140.006454467773</t>
+    <t xml:space="preserve">140.006439208984</t>
   </si>
   <si>
     <t xml:space="preserve">138.564071655273</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">130.294448852539</t>
   </si>
   <si>
-    <t xml:space="preserve">124.236480712891</t>
+    <t xml:space="preserve">124.236473083496</t>
   </si>
   <si>
     <t xml:space="preserve">122.890266418457</t>
   </si>
   <si>
-    <t xml:space="preserve">118.563148498535</t>
+    <t xml:space="preserve">118.563140869141</t>
   </si>
   <si>
     <t xml:space="preserve">109.81273651123</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">113.562911987305</t>
   </si>
   <si>
-    <t xml:space="preserve">115.389923095703</t>
+    <t xml:space="preserve">115.389930725098</t>
   </si>
   <si>
     <t xml:space="preserve">115.774551391602</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">122.313316345215</t>
   </si>
   <si>
-    <t xml:space="preserve">120.293991088867</t>
+    <t xml:space="preserve">120.293983459473</t>
   </si>
   <si>
     <t xml:space="preserve">120.101669311523</t>
@@ -3230,40 +3230,40 @@
     <t xml:space="preserve">119.043937683105</t>
   </si>
   <si>
-    <t xml:space="preserve">121.736366271973</t>
+    <t xml:space="preserve">121.736358642578</t>
   </si>
   <si>
     <t xml:space="preserve">124.621124267578</t>
   </si>
   <si>
-    <t xml:space="preserve">123.274894714355</t>
+    <t xml:space="preserve">123.274887084961</t>
   </si>
   <si>
     <t xml:space="preserve">121.544052124023</t>
   </si>
   <si>
-    <t xml:space="preserve">124.044166564941</t>
+    <t xml:space="preserve">124.044158935547</t>
   </si>
   <si>
     <t xml:space="preserve">124.332633972168</t>
   </si>
   <si>
-    <t xml:space="preserve">127.986640930176</t>
+    <t xml:space="preserve">127.986656188965</t>
   </si>
   <si>
     <t xml:space="preserve">128.659774780273</t>
   </si>
   <si>
-    <t xml:space="preserve">127.698188781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.178749084473</t>
+    <t xml:space="preserve">127.698173522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.178741455078</t>
   </si>
   <si>
     <t xml:space="preserve">114.52449798584</t>
   </si>
   <si>
-    <t xml:space="preserve">112.889801025391</t>
+    <t xml:space="preserve">112.889808654785</t>
   </si>
   <si>
     <t xml:space="preserve">114.236022949219</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">113.178276062012</t>
   </si>
   <si>
-    <t xml:space="preserve">119.332412719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.082580566406</t>
+    <t xml:space="preserve">119.332405090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.082588195801</t>
   </si>
   <si>
     <t xml:space="preserve">125.390365600586</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">123.659538269043</t>
   </si>
   <si>
-    <t xml:space="preserve">128.9482421875</t>
+    <t xml:space="preserve">128.948226928711</t>
   </si>
   <si>
     <t xml:space="preserve">131.73681640625</t>
@@ -3350,22 +3350,22 @@
     <t xml:space="preserve">132.602233886719</t>
   </si>
   <si>
-    <t xml:space="preserve">129.044387817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.159881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.967330932617</t>
+    <t xml:space="preserve">129.044372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.159866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.967323303223</t>
   </si>
   <si>
     <t xml:space="preserve">126.351951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">123.563377380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.313545227051</t>
+    <t xml:space="preserve">123.563369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.313552856445</t>
   </si>
   <si>
     <t xml:space="preserve">128.371292114258</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">121.447891235352</t>
   </si>
   <si>
-    <t xml:space="preserve">117.601554870605</t>
+    <t xml:space="preserve">117.6015625</t>
   </si>
   <si>
     <t xml:space="preserve">118.947769165039</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">120.19783782959</t>
   </si>
   <si>
-    <t xml:space="preserve">121.063255310059</t>
+    <t xml:space="preserve">121.063247680664</t>
   </si>
   <si>
     <t xml:space="preserve">117.505401611328</t>
@@ -3395,13 +3395,13 @@
     <t xml:space="preserve">115.870712280273</t>
   </si>
   <si>
-    <t xml:space="preserve">116.255340576172</t>
+    <t xml:space="preserve">116.255332946777</t>
   </si>
   <si>
     <t xml:space="preserve">112.312858581543</t>
   </si>
   <si>
-    <t xml:space="preserve">115.582237243652</t>
+    <t xml:space="preserve">115.582229614258</t>
   </si>
   <si>
     <t xml:space="preserve">115.67839050293</t>
@@ -5223,6 +5223,9 @@
   </si>
   <si>
     <t xml:space="preserve">82.0999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.75</t>
   </si>
 </sst>
 </file>
@@ -70925,7 +70928,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6911805556</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>27821</v>
@@ -70946,6 +70949,32 @@
         <v>1720</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6912384259</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>28633</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>84.4499969482422</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>81.3000030517578</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>84.1500015258789</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>1737</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="1743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="1744">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5495910644531</t>
+    <t xml:space="preserve">13.5495901107788</t>
   </si>
   <si>
     <t xml:space="preserve">SES.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5321073532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2523727416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9464159011841</t>
+    <t xml:space="preserve">13.5321063995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2523736953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9464139938354</t>
   </si>
   <si>
     <t xml:space="preserve">13.1125078201294</t>
@@ -59,37 +59,37 @@
     <t xml:space="preserve">12.8589992523193</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0513153076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9901237487793</t>
+    <t xml:space="preserve">13.0513143539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9901218414307</t>
   </si>
   <si>
     <t xml:space="preserve">12.9376726150513</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1037645339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.025089263916</t>
+    <t xml:space="preserve">13.1037654876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0250902175903</t>
   </si>
   <si>
     <t xml:space="preserve">12.8502559661865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2383403778076</t>
+    <t xml:space="preserve">12.2383394241333</t>
   </si>
   <si>
     <t xml:space="preserve">12.5880060195923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7890644073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7191314697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6841650009155</t>
+    <t xml:space="preserve">12.7890663146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7191324234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6841659545898</t>
   </si>
   <si>
     <t xml:space="preserve">12.6054906845093</t>
@@ -101,25 +101,25 @@
     <t xml:space="preserve">12.0460224151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1771488189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1421813964844</t>
+    <t xml:space="preserve">12.1771478652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1421823501587</t>
   </si>
   <si>
     <t xml:space="preserve">10.9270896911621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9795398712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3641729354858</t>
+    <t xml:space="preserve">10.9795389175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3641719818115</t>
   </si>
   <si>
     <t xml:space="preserve">11.4515895843506</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0984735488892</t>
+    <t xml:space="preserve">12.0984745025635</t>
   </si>
   <si>
     <t xml:space="preserve">12.1072149276733</t>
@@ -128,28 +128,28 @@
     <t xml:space="preserve">11.8886737823486</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760904312134</t>
+    <t xml:space="preserve">11.9760875701904</t>
   </si>
   <si>
     <t xml:space="preserve">11.9323816299438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0110559463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0809879302979</t>
+    <t xml:space="preserve">12.0110549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0809898376465</t>
   </si>
   <si>
     <t xml:space="preserve">11.8012561798096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1334390640259</t>
+    <t xml:space="preserve">12.1334400177002</t>
   </si>
   <si>
     <t xml:space="preserve">11.8274803161621</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0635070800781</t>
+    <t xml:space="preserve">12.0635061264038</t>
   </si>
   <si>
     <t xml:space="preserve">12.5005903244019</t>
@@ -161,25 +161,25 @@
     <t xml:space="preserve">12.7978067398071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1649580001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1562147140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0687980651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1212482452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1911821365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7540979385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8939647674561</t>
+    <t xml:space="preserve">13.1649570465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1562156677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0687990188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1212501525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1911811828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7540988922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8939657211304</t>
   </si>
   <si>
     <t xml:space="preserve">12.9027070999146</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">13.0600566864014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1999254226685</t>
+    <t xml:space="preserve">13.1999235153198</t>
   </si>
   <si>
     <t xml:space="preserve">12.9813814163208</t>
@@ -197,46 +197,46 @@
     <t xml:space="preserve">13.4534320831299</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7069396972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4709157943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4621725082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2086639404297</t>
+    <t xml:space="preserve">13.7069406509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4709148406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4621734619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.208664894104</t>
   </si>
   <si>
     <t xml:space="preserve">13.3223075866699</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0950231552124</t>
+    <t xml:space="preserve">13.0950241088867</t>
   </si>
   <si>
     <t xml:space="preserve">12.9988651275635</t>
   </si>
   <si>
-    <t xml:space="preserve">12.640456199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4481391906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3782072067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0285396575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1509237289429</t>
+    <t xml:space="preserve">12.6404571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4481382369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3782062530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0285406112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1509227752686</t>
   </si>
   <si>
     <t xml:space="preserve">12.4393968582153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5617828369141</t>
+    <t xml:space="preserve">12.5617818832397</t>
   </si>
   <si>
     <t xml:space="preserve">12.5268144607544</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">12.3694658279419</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7715826034546</t>
+    <t xml:space="preserve">12.7715816497803</t>
   </si>
   <si>
     <t xml:space="preserve">12.4306564331055</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">12.2820491790771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1946315765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2470836639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4131736755371</t>
+    <t xml:space="preserve">12.1946306228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2470817565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4131727218628</t>
   </si>
   <si>
     <t xml:space="preserve">12.509331703186</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">12.3869485855103</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8187389373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8449659347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.255823135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5792665481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2208547592163</t>
+    <t xml:space="preserve">11.8187417984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8449640274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2558240890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5792655944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2208557128906</t>
   </si>
   <si>
     <t xml:space="preserve">12.1858892440796</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">12.7803230285645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7278728485107</t>
+    <t xml:space="preserve">12.7278738021851</t>
   </si>
   <si>
     <t xml:space="preserve">12.8764810562134</t>
@@ -302,22 +302,22 @@
     <t xml:space="preserve">12.8065481185913</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7628412246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8677406311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327732086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5355567932129</t>
+    <t xml:space="preserve">12.7628402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8677396774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327741622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5355577468872</t>
   </si>
   <si>
     <t xml:space="preserve">13.1824407577515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0338296890259</t>
+    <t xml:space="preserve">13.0338315963745</t>
   </si>
   <si>
     <t xml:space="preserve">13.3048238754272</t>
@@ -329,13 +329,13 @@
     <t xml:space="preserve">13.3747577667236</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6020412445068</t>
+    <t xml:space="preserve">13.6020421981812</t>
   </si>
   <si>
     <t xml:space="preserve">13.6894578933716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7244243621826</t>
+    <t xml:space="preserve">13.7244234085083</t>
   </si>
   <si>
     <t xml:space="preserve">13.7514753341675</t>
@@ -347,16 +347,16 @@
     <t xml:space="preserve">13.8687019348145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6252317428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6432685852051</t>
+    <t xml:space="preserve">13.6252326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6432666778564</t>
   </si>
   <si>
     <t xml:space="preserve">13.661301612854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.598180770874</t>
+    <t xml:space="preserve">13.5981817245483</t>
   </si>
   <si>
     <t xml:space="preserve">13.6162166595459</t>
@@ -365,55 +365,55 @@
     <t xml:space="preserve">13.5260419845581</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5530948638916</t>
+    <t xml:space="preserve">13.5530939102173</t>
   </si>
   <si>
     <t xml:space="preserve">13.3456945419312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5801477432251</t>
+    <t xml:space="preserve">13.5801458358765</t>
   </si>
   <si>
     <t xml:space="preserve">13.6973724365234</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7785272598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6703186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7965631484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9769105911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0400304794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0129804611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9047718048096</t>
+    <t xml:space="preserve">13.7785263061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6703205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7965612411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9769115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0400314331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.012978553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9047727584839</t>
   </si>
   <si>
     <t xml:space="preserve">14.1031532287598</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2474317550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1572580337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3646554946899</t>
+    <t xml:space="preserve">14.2474308013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1572561264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3646564483643</t>
   </si>
   <si>
     <t xml:space="preserve">14.4187602996826</t>
   </si>
   <si>
-    <t xml:space="preserve">14.517951965332</t>
+    <t xml:space="preserve">14.5179510116577</t>
   </si>
   <si>
     <t xml:space="preserve">14.6081266403198</t>
@@ -422,28 +422,28 @@
     <t xml:space="preserve">14.6622314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3917083740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3105516433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3015336990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5450019836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6441946029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7343673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7163324356079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.635178565979</t>
+    <t xml:space="preserve">14.3917093276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3105525970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.30153465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5450038909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6441955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7343692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7163333892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6351766586304</t>
   </si>
   <si>
     <t xml:space="preserve">14.6261596679688</t>
@@ -452,16 +452,16 @@
     <t xml:space="preserve">14.6892833709717</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8245410919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8065061569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.74338722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5810737609863</t>
+    <t xml:space="preserve">14.8245429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8065071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7433862686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.581072807312</t>
   </si>
   <si>
     <t xml:space="preserve">14.6982984542847</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">14.6532115936279</t>
   </si>
   <si>
-    <t xml:space="preserve">14.923731803894</t>
+    <t xml:space="preserve">14.9237308502197</t>
   </si>
   <si>
     <t xml:space="preserve">15.0499773025513</t>
@@ -485,97 +485,97 @@
     <t xml:space="preserve">15.2122888565063</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3746013641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.554949760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9246606826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7803831100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8705558776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344888687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7082414627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517126083374</t>
+    <t xml:space="preserve">15.3746004104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5549468994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9246587753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7803821563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8705577850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344860076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7082433700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517135620117</t>
   </si>
   <si>
     <t xml:space="preserve">16.7452411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8714828491211</t>
+    <t xml:space="preserve">16.8714790344238</t>
   </si>
   <si>
     <t xml:space="preserve">17.0879020690918</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1510219573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2231636047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9796886444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9075527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3043155670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0337944030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2772655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4756450653076</t>
+    <t xml:space="preserve">17.1510238647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2231578826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9796924591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9075508117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3043174743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0337924957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2772636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4756469726562</t>
   </si>
   <si>
     <t xml:space="preserve">17.3223514556885</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1690559387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.583854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.574836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5658168792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2411937713623</t>
+    <t xml:space="preserve">17.1690578460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5838565826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5748329162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5658187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2411956787109</t>
   </si>
   <si>
     <t xml:space="preserve">17.1870899200439</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8534488677979</t>
+    <t xml:space="preserve">16.8534469604492</t>
   </si>
   <si>
     <t xml:space="preserve">16.8444309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9526386260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7272033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6911354064941</t>
+    <t xml:space="preserve">16.9526405334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7272052764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6911373138428</t>
   </si>
   <si>
     <t xml:space="preserve">16.8624668121338</t>
@@ -587,46 +587,46 @@
     <t xml:space="preserve">16.8173789978027</t>
   </si>
   <si>
-    <t xml:space="preserve">16.997730255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7722911834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.006742477417</t>
+    <t xml:space="preserve">16.9977245330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7722930908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0067443847656</t>
   </si>
   <si>
     <t xml:space="preserve">17.1961059570312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.358419418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6199226379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7642002105713</t>
+    <t xml:space="preserve">17.3584232330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6199245452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7642021179199</t>
   </si>
   <si>
     <t xml:space="preserve">18.0076713562012</t>
   </si>
   <si>
-    <t xml:space="preserve">17.989631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9445495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9535675048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8092861175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2601566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7561092376709</t>
+    <t xml:space="preserve">17.9896354675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9445476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9535636901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8092880249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2601585388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7561111450195</t>
   </si>
   <si>
     <t xml:space="preserve">18.846284866333</t>
@@ -635,43 +635,43 @@
     <t xml:space="preserve">18.9364566802979</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6208477020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2971515655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3602752685547</t>
+    <t xml:space="preserve">18.620849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.297155380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3602733612061</t>
   </si>
   <si>
     <t xml:space="preserve">19.3512554168701</t>
   </si>
   <si>
-    <t xml:space="preserve">19.666862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6488304138184</t>
+    <t xml:space="preserve">19.6668643951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6488342285156</t>
   </si>
   <si>
     <t xml:space="preserve">19.5586566925049</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2520656585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1709117889404</t>
+    <t xml:space="preserve">19.252067565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1709098815918</t>
   </si>
   <si>
     <t xml:space="preserve">19.134838104248</t>
   </si>
   <si>
-    <t xml:space="preserve">19.197961807251</t>
+    <t xml:space="preserve">19.1979637145996</t>
   </si>
   <si>
     <t xml:space="preserve">18.9544944763184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9094085693359</t>
+    <t xml:space="preserve">18.9094047546387</t>
   </si>
   <si>
     <t xml:space="preserve">19.0897541046143</t>
@@ -680,25 +680,25 @@
     <t xml:space="preserve">18.5757656097412</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1970329284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5306777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8372688293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4594631195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3873252868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0185432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3612041473389</t>
+    <t xml:space="preserve">18.1970348358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5306758880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8372669219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4594669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3873271942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0185451507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3612003326416</t>
   </si>
   <si>
     <t xml:space="preserve">20.8301048278809</t>
@@ -710,109 +710,109 @@
     <t xml:space="preserve">20.8751907348633</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9292945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1006278991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0104541778564</t>
+    <t xml:space="preserve">20.929292678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1006240844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0104522705078</t>
   </si>
   <si>
     <t xml:space="preserve">20.5685997009277</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7218952178955</t>
+    <t xml:space="preserve">20.7218971252441</t>
   </si>
   <si>
     <t xml:space="preserve">20.6046695709229</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1898708343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792381286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6497573852539</t>
+    <t xml:space="preserve">20.1898746490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792362213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6497554779053</t>
   </si>
   <si>
     <t xml:space="preserve">21.6416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3711490631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.380163192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0925331115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6245594024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7147350311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8049068450928</t>
+    <t xml:space="preserve">21.3711471557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3801612854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0925350189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6245613098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7147331237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8049087524414</t>
   </si>
   <si>
     <t xml:space="preserve">23.5984344482422</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0763549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0583209991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7156600952148</t>
+    <t xml:space="preserve">24.0763530731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0583171844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7156581878662</t>
   </si>
   <si>
     <t xml:space="preserve">23.9320774078369</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8599395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.805835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5082588195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.994270324707</t>
+    <t xml:space="preserve">23.8599376678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8058338165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5082607269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9942722320557</t>
   </si>
   <si>
     <t xml:space="preserve">22.480281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5434055328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7057132720947</t>
+    <t xml:space="preserve">22.5434017181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7057151794434</t>
   </si>
   <si>
     <t xml:space="preserve">22.4532299041748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4622459411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0023593902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1827068328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7237510681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3630561828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2097606658936</t>
+    <t xml:space="preserve">22.4622497558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0023632049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1827087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7237491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3630542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2097587585449</t>
   </si>
   <si>
     <t xml:space="preserve">21.4883708953857</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">21.9212036132812</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8761177062988</t>
+    <t xml:space="preserve">21.8761196136475</t>
   </si>
   <si>
     <t xml:space="preserve">21.7047901153564</t>
@@ -833,28 +833,28 @@
     <t xml:space="preserve">22.074499130249</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2999324798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8139209747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3179702758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1917247772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3540420532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.525369644165</t>
+    <t xml:space="preserve">22.299934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8139247894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3179683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1917266845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.354040145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5253658294678</t>
   </si>
   <si>
     <t xml:space="preserve">22.6065235137939</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6335773468018</t>
+    <t xml:space="preserve">22.6335754394531</t>
   </si>
   <si>
     <t xml:space="preserve">22.2458305358887</t>
@@ -863,16 +863,16 @@
     <t xml:space="preserve">22.2277965545654</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1286067962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0835189819336</t>
+    <t xml:space="preserve">22.128604888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0835208892822</t>
   </si>
   <si>
     <t xml:space="preserve">22.2007446289062</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1376209259033</t>
+    <t xml:space="preserve">22.1376190185547</t>
   </si>
   <si>
     <t xml:space="preserve">22.1466388702393</t>
@@ -881,19 +881,19 @@
     <t xml:space="preserve">21.5965824127197</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3260612487793</t>
+    <t xml:space="preserve">21.3260593414307</t>
   </si>
   <si>
     <t xml:space="preserve">21.5605087280273</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0294151306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6867523193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2368106842041</t>
+    <t xml:space="preserve">22.0294132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6867542266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2368144989014</t>
   </si>
   <si>
     <t xml:space="preserve">22.3720741271973</t>
@@ -902,37 +902,37 @@
     <t xml:space="preserve">22.3991260528564</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6155395507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6606273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0123062133789</t>
+    <t xml:space="preserve">22.6155414581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6606292724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0123081207275</t>
   </si>
   <si>
     <t xml:space="preserve">23.5193881988525</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2704563140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1739845275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7087249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7732639312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2434692382812</t>
+    <t xml:space="preserve">23.2704582214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1739864349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7087230682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7732620239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2434673309326</t>
   </si>
   <si>
     <t xml:space="preserve">25.8150863647461</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7966442108154</t>
+    <t xml:space="preserve">25.7966480255127</t>
   </si>
   <si>
     <t xml:space="preserve">25.6860122680664</t>
@@ -941,13 +941,13 @@
     <t xml:space="preserve">25.6675720214844</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0086975097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8888454437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9810390472412</t>
+    <t xml:space="preserve">26.0086994171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8888473510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9810409545898</t>
   </si>
   <si>
     <t xml:space="preserve">26.0916767120361</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">25.907283782959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8058662414551</t>
+    <t xml:space="preserve">25.8058681488037</t>
   </si>
   <si>
     <t xml:space="preserve">25.9533824920654</t>
@@ -968,37 +968,37 @@
     <t xml:space="preserve">25.6583518981934</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0775146484375</t>
+    <t xml:space="preserve">25.0775127410889</t>
   </si>
   <si>
     <t xml:space="preserve">25.4002017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2619075775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3264427185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8009223937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4186401367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6441879272461</t>
+    <t xml:space="preserve">25.261905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3264446258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8009204864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4186382293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6441860198975</t>
   </si>
   <si>
     <t xml:space="preserve">24.8562393188477</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9576568603516</t>
+    <t xml:space="preserve">24.9576587677002</t>
   </si>
   <si>
     <t xml:space="preserve">24.8931198120117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1874771118164</t>
+    <t xml:space="preserve">23.187479019165</t>
   </si>
   <si>
     <t xml:space="preserve">22.9754257202148</t>
@@ -1007,49 +1007,49 @@
     <t xml:space="preserve">23.1229400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2335796356201</t>
+    <t xml:space="preserve">23.2335815429688</t>
   </si>
   <si>
     <t xml:space="preserve">22.9938659667969</t>
   </si>
   <si>
-    <t xml:space="preserve">22.781810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.671178817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4960021972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7264957427979</t>
+    <t xml:space="preserve">22.7818126678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6711769104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4960041046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7264976501465</t>
   </si>
   <si>
     <t xml:space="preserve">22.5052242279053</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3208274841309</t>
+    <t xml:space="preserve">22.3208312988281</t>
   </si>
   <si>
     <t xml:space="preserve">22.5881996154785</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1137218475342</t>
+    <t xml:space="preserve">23.1137237548828</t>
   </si>
   <si>
     <t xml:space="preserve">22.910888671875</t>
   </si>
   <si>
-    <t xml:space="preserve">23.399528503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7775363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6208057403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1413822174072</t>
+    <t xml:space="preserve">23.3995323181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7775402069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6208038330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1413841247559</t>
   </si>
   <si>
     <t xml:space="preserve">22.9846477508545</t>
@@ -1058,22 +1058,22 @@
     <t xml:space="preserve">22.8740100860596</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7357139587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6896152496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3257732391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7406616210938</t>
+    <t xml:space="preserve">22.7357158660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6896171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3257751464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7406597137451</t>
   </si>
   <si>
     <t xml:space="preserve">23.9803714752197</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9711513519287</t>
+    <t xml:space="preserve">23.9711532592773</t>
   </si>
   <si>
     <t xml:space="preserve">24.0633487701416</t>
@@ -1085,25 +1085,25 @@
     <t xml:space="preserve">24.3860378265381</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1555480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6165313720703</t>
+    <t xml:space="preserve">24.1555461883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6165294647217</t>
   </si>
   <si>
     <t xml:space="preserve">25.8611850738525</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6306953430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2158088684082</t>
+    <t xml:space="preserve">25.6306915283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2158107757568</t>
   </si>
   <si>
     <t xml:space="preserve">25.1697101593018</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3080062866211</t>
+    <t xml:space="preserve">25.3080081939697</t>
   </si>
   <si>
     <t xml:space="preserve">25.4463005065918</t>
@@ -1112,28 +1112,28 @@
     <t xml:space="preserve">25.5384979248047</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1236095428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4321365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6484603881836</t>
+    <t xml:space="preserve">25.1236114501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4321327209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6484622955322</t>
   </si>
   <si>
     <t xml:space="preserve">24.0172481536865</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1094493865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3399410247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2016448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2938404083252</t>
+    <t xml:space="preserve">24.109447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3399353027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2016429901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2938385009766</t>
   </si>
   <si>
     <t xml:space="preserve">24.754825592041</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">24.6626281738281</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9853191375732</t>
+    <t xml:space="preserve">24.9853172302246</t>
   </si>
   <si>
     <t xml:space="preserve">25.4923992156982</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7228908538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5704307556152</t>
+    <t xml:space="preserve">25.7228889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5704326629639</t>
   </si>
   <si>
     <t xml:space="preserve">25.5845966339111</t>
@@ -1160,13 +1160,13 @@
     <t xml:space="preserve">25.9994812011719</t>
   </si>
   <si>
-    <t xml:space="preserve">26.414363861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5668239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7512149810791</t>
+    <t xml:space="preserve">26.4143657684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5668258666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7512187957764</t>
   </si>
   <si>
     <t xml:space="preserve">28.0739059448242</t>
@@ -1178,58 +1178,58 @@
     <t xml:space="preserve">26.7370529174805</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5065612792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0314140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5243358612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3682670593262</t>
+    <t xml:space="preserve">26.5065631866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0314159393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5243339538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3682651519775</t>
   </si>
   <si>
     <t xml:space="preserve">26.5987586975098</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4604625701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2299709320068</t>
+    <t xml:space="preserve">26.4604644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2299728393555</t>
   </si>
   <si>
     <t xml:space="preserve">26.3221664428711</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1980381011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2760696411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2902336120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3824310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4746265411377</t>
+    <t xml:space="preserve">27.1980400085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2760677337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2902355194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3824348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.474630355835</t>
   </si>
   <si>
     <t xml:space="preserve">26.5526580810547</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8292484283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1058387756348</t>
+    <t xml:space="preserve">26.8292503356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.105842590332</t>
   </si>
   <si>
     <t xml:space="preserve">26.8753490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8434162139893</t>
+    <t xml:space="preserve">27.8434181213379</t>
   </si>
   <si>
     <t xml:space="preserve">28.7653827667236</t>
@@ -1238,10 +1238,10 @@
     <t xml:space="preserve">28.5809898376465</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9356098175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8114814758301</t>
+    <t xml:space="preserve">27.9356136322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8114795684814</t>
   </si>
   <si>
     <t xml:space="preserve">28.1661014556885</t>
@@ -1250,58 +1250,58 @@
     <t xml:space="preserve">28.7192840576172</t>
   </si>
   <si>
-    <t xml:space="preserve">28.120002746582</t>
+    <t xml:space="preserve">28.1200046539307</t>
   </si>
   <si>
     <t xml:space="preserve">27.059741973877</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9675464630127</t>
+    <t xml:space="preserve">26.9675445556641</t>
   </si>
   <si>
     <t xml:space="preserve">27.1519412994385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6909561157227</t>
+    <t xml:space="preserve">26.690954208374</t>
   </si>
   <si>
     <t xml:space="preserve">26.7831497192383</t>
   </si>
   <si>
-    <t xml:space="preserve">26.045581817627</t>
+    <t xml:space="preserve">26.0455799102783</t>
   </si>
   <si>
     <t xml:space="preserve">27.6590213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9214496612549</t>
+    <t xml:space="preserve">26.9214477539062</t>
   </si>
   <si>
     <t xml:space="preserve">26.1828784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">26.088695526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4654293060303</t>
+    <t xml:space="preserve">26.0886974334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4654312133789</t>
   </si>
   <si>
     <t xml:space="preserve">25.8061466217041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7119636535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1468677520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3352317810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9114093780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.487585067749</t>
+    <t xml:space="preserve">25.7119655609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1468696594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3352336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9114112854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4875869750977</t>
   </si>
   <si>
     <t xml:space="preserve">24.3934020996094</t>
@@ -1313,13 +1313,13 @@
     <t xml:space="preserve">23.2632064819336</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0277481079102</t>
+    <t xml:space="preserve">23.0277500152588</t>
   </si>
   <si>
     <t xml:space="preserve">23.0748386383057</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7452011108398</t>
+    <t xml:space="preserve">22.7451992034912</t>
   </si>
   <si>
     <t xml:space="preserve">22.6039257049561</t>
@@ -1328,58 +1328,58 @@
     <t xml:space="preserve">22.5097427368164</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4155597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1801013946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0388259887695</t>
+    <t xml:space="preserve">22.4155616760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1800994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0388278961182</t>
   </si>
   <si>
     <t xml:space="preserve">21.8504619598389</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4626502990723</t>
+    <t xml:space="preserve">22.4626522064209</t>
   </si>
   <si>
     <t xml:space="preserve">22.2271938323975</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4044780731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2161140441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.886474609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.498664855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5568332672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1330108642578</t>
+    <t xml:space="preserve">23.4044799804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2161159515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8864727020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4986629486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5568351745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1330089569092</t>
   </si>
   <si>
     <t xml:space="preserve">21.6620979309082</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1911811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0028133392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0969944000244</t>
+    <t xml:space="preserve">21.1911792755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0028114318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.096996307373</t>
   </si>
   <si>
     <t xml:space="preserve">20.8615398406982</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3795471191406</t>
+    <t xml:space="preserve">21.379545211792</t>
   </si>
   <si>
     <t xml:space="preserve">21.4737281799316</t>
@@ -1391,34 +1391,34 @@
     <t xml:space="preserve">21.7562789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9446468353271</t>
+    <t xml:space="preserve">21.9446430206299</t>
   </si>
   <si>
     <t xml:space="preserve">21.5679130554199</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5208206176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3324546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2382698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8393821716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7922916412354</t>
+    <t xml:space="preserve">21.5208187103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3324527740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2382717132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8393840789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.792293548584</t>
   </si>
   <si>
     <t xml:space="preserve">23.5457553863525</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6399402618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7341213226318</t>
+    <t xml:space="preserve">23.6399383544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7341232299805</t>
   </si>
   <si>
     <t xml:space="preserve">23.6870288848877</t>
@@ -1427,16 +1427,16 @@
     <t xml:space="preserve">23.781213760376</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0166721343994</t>
+    <t xml:space="preserve">24.0166702270508</t>
   </si>
   <si>
     <t xml:space="preserve">24.2992191314697</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1579456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2521305084229</t>
+    <t xml:space="preserve">24.1579437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2521266937256</t>
   </si>
   <si>
     <t xml:space="preserve">24.7230453491211</t>
@@ -1448,28 +1448,28 @@
     <t xml:space="preserve">24.675952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5817699432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7701320648193</t>
+    <t xml:space="preserve">24.5817680358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.770133972168</t>
   </si>
   <si>
     <t xml:space="preserve">24.9584999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9003295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7590579986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9474220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2770614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9363460540771</t>
+    <t xml:space="preserve">25.9003314971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7590560913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9474201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.277063369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9363441467285</t>
   </si>
   <si>
     <t xml:space="preserve">26.9834365844727</t>
@@ -1478,43 +1478,43 @@
     <t xml:space="preserve">26.8421611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7479801177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.265983581543</t>
+    <t xml:space="preserve">26.7479763031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2659873962402</t>
   </si>
   <si>
     <t xml:space="preserve">27.4543514251709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.501443862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3130798339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0776176452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7008876800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6537971496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6067028045654</t>
+    <t xml:space="preserve">27.5014419555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3130779266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0776214599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7008857727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6537952423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6067047119141</t>
   </si>
   <si>
     <t xml:space="preserve">25.9945125579834</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1357898712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0416030883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6177825927734</t>
+    <t xml:space="preserve">26.1357879638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0416049957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6177806854248</t>
   </si>
   <si>
     <t xml:space="preserve">25.4294147491455</t>
@@ -1523,16 +1523,16 @@
     <t xml:space="preserve">25.0055923461914</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0997753143311</t>
+    <t xml:space="preserve">25.0997772216797</t>
   </si>
   <si>
     <t xml:space="preserve">24.8643169403076</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4404964447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5235977172852</t>
+    <t xml:space="preserve">24.4404945373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5235996246338</t>
   </si>
   <si>
     <t xml:space="preserve">26.3712463378906</t>
@@ -1544,19 +1544,19 @@
     <t xml:space="preserve">26.7950706481934</t>
   </si>
   <si>
-    <t xml:space="preserve">26.889253616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0305309295654</t>
+    <t xml:space="preserve">26.8892517089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0305290222168</t>
   </si>
   <si>
     <t xml:space="preserve">27.171802520752</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5485343933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6898097991943</t>
+    <t xml:space="preserve">27.5485324859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6898078918457</t>
   </si>
   <si>
     <t xml:space="preserve">28.1136322021484</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">28.7258224487305</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9141864776611</t>
+    <t xml:space="preserve">28.9141883850098</t>
   </si>
   <si>
     <t xml:space="preserve">29.9502029418945</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">30.3269329071045</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3740253448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.504222869873</t>
+    <t xml:space="preserve">30.3740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5042266845703</t>
   </si>
   <si>
     <t xml:space="preserve">31.6925888061523</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">32.4931449890137</t>
   </si>
   <si>
-    <t xml:space="preserve">33.482063293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6704368591309</t>
+    <t xml:space="preserve">33.4820671081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6704330444336</t>
   </si>
   <si>
     <t xml:space="preserve">33.2936973571777</t>
@@ -1613,34 +1613,34 @@
     <t xml:space="preserve">33.2466087341309</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8698806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1524238586426</t>
+    <t xml:space="preserve">32.8698768615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1524200439453</t>
   </si>
   <si>
     <t xml:space="preserve">33.058235168457</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5873260498047</t>
+    <t xml:space="preserve">32.5873222351074</t>
   </si>
   <si>
     <t xml:space="preserve">32.3047752380371</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9280471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4571304321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3629493713379</t>
+    <t xml:space="preserve">31.9280433654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4571285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3629474639893</t>
   </si>
   <si>
     <t xml:space="preserve">30.8920288085938</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0803985595703</t>
+    <t xml:space="preserve">31.0804004669189</t>
   </si>
   <si>
     <t xml:space="preserve">31.0333061218262</t>
@@ -1655,40 +1655,40 @@
     <t xml:space="preserve">31.2687644958496</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9862194061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4100379943848</t>
+    <t xml:space="preserve">30.9862174987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4100341796875</t>
   </si>
   <si>
     <t xml:space="preserve">30.8449401855469</t>
   </si>
   <si>
-    <t xml:space="preserve">31.17458152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8809509277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0222282409668</t>
+    <t xml:space="preserve">31.1745796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8809547424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0222244262695</t>
   </si>
   <si>
     <t xml:space="preserve">31.7396812438965</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0000686645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4709892272949</t>
+    <t xml:space="preserve">34.0000762939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4709854125977</t>
   </si>
   <si>
     <t xml:space="preserve">35.7895469665527</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5900993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7784729003906</t>
+    <t xml:space="preserve">36.5901031494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7784690856934</t>
   </si>
   <si>
     <t xml:space="preserve">37.1552047729492</t>
@@ -1697,10 +1697,10 @@
     <t xml:space="preserve">37.6732063293457</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0846748352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2282104492188</t>
+    <t xml:space="preserve">38.0846786499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.228214263916</t>
   </si>
   <si>
     <t xml:space="preserve">37.367000579834</t>
@@ -1709,16 +1709,16 @@
     <t xml:space="preserve">37.7976036071777</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1803665161133</t>
+    <t xml:space="preserve">38.1803703308105</t>
   </si>
   <si>
     <t xml:space="preserve">38.3717460632324</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9411392211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9889907836914</t>
+    <t xml:space="preserve">37.9411430358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9889869689941</t>
   </si>
   <si>
     <t xml:space="preserve">37.8454475402832</t>
@@ -1727,16 +1727,16 @@
     <t xml:space="preserve">37.3191604614258</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8501968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.754508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3286437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.041576385498</t>
+    <t xml:space="preserve">38.8501930236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7545051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3286476135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0415802001953</t>
   </si>
   <si>
     <t xml:space="preserve">38.8023529052734</t>
@@ -1760,19 +1760,19 @@
     <t xml:space="preserve">38.5631256103516</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4195938110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3764915466309</t>
+    <t xml:space="preserve">38.4195976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3764953613281</t>
   </si>
   <si>
     <t xml:space="preserve">39.1372680664062</t>
   </si>
   <si>
-    <t xml:space="preserve">39.185115814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2807998657227</t>
+    <t xml:space="preserve">39.1851119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2808036804199</t>
   </si>
   <si>
     <t xml:space="preserve">39.9027900695801</t>
@@ -1781,10 +1781,10 @@
     <t xml:space="preserve">41.1946067810059</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1036605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5342712402344</t>
+    <t xml:space="preserve">42.1036682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5342674255371</t>
   </si>
   <si>
     <t xml:space="preserve">41.6730537414551</t>
@@ -1796,79 +1796,79 @@
     <t xml:space="preserve">40.7161521911621</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9122848510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0605583190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4911727905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2566947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7829895019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4433250427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0174674987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6347045898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2040977478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9170265197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9265251159668</t>
+    <t xml:space="preserve">41.9122772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0605659484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4911651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2566909790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7829856872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4433288574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.017463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6347007751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9170227050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9265213012695</t>
   </si>
   <si>
     <t xml:space="preserve">45.404972076416</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2614364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5963554382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6536865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8976631164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.610595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1847343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9933471679688</t>
+    <t xml:space="preserve">45.2614402770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5963516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6536903381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8976593017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6105880737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1847381591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9933547973633</t>
   </si>
   <si>
     <t xml:space="preserve">49.7588729858398</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2804260253906</t>
+    <t xml:space="preserve">49.2804222106934</t>
   </si>
   <si>
     <t xml:space="preserve">49.6631851196289</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3761138916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5674896240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6200866699219</t>
+    <t xml:space="preserve">49.3761100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5674934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6200828552246</t>
   </si>
   <si>
     <t xml:space="preserve">51.0028457641602</t>
@@ -1880,25 +1880,25 @@
     <t xml:space="preserve">52.6295776367188</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9597434997559</t>
+    <t xml:space="preserve">51.9597473144531</t>
   </si>
   <si>
     <t xml:space="preserve">51.8640556335449</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6726760864258</t>
+    <t xml:space="preserve">51.6726722717285</t>
   </si>
   <si>
     <t xml:space="preserve">48.4192085266113</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3235206604004</t>
+    <t xml:space="preserve">48.3235244750977</t>
   </si>
   <si>
     <t xml:space="preserve">50.0459442138672</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3856048583984</t>
+    <t xml:space="preserve">51.3856086730957</t>
   </si>
   <si>
     <t xml:space="preserve">50.907154083252</t>
@@ -1910,16 +1910,16 @@
     <t xml:space="preserve">50.4287071228027</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5338897705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0649299621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2994117736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4381980895996</t>
+    <t xml:space="preserve">52.5338859558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0649337768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2994079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4381942749023</t>
   </si>
   <si>
     <t xml:space="preserve">47.3666191101074</t>
@@ -1934,13 +1934,13 @@
     <t xml:space="preserve">45.7398872375488</t>
   </si>
   <si>
-    <t xml:space="preserve">44.974365234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5868606567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7687492370605</t>
+    <t xml:space="preserve">44.9743614196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.586856842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7687454223633</t>
   </si>
   <si>
     <t xml:space="preserve">36.6493263244629</t>
@@ -1949,25 +1949,25 @@
     <t xml:space="preserve">35.5967330932617</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0945491790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4820575714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1854953765869</t>
+    <t xml:space="preserve">30.0945510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4820594787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1854934692383</t>
   </si>
   <si>
     <t xml:space="preserve">31.5299034118652</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0992984771729</t>
+    <t xml:space="preserve">31.0992965698242</t>
   </si>
   <si>
     <t xml:space="preserve">30.3816204071045</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9268989562988</t>
+    <t xml:space="preserve">34.9269027709961</t>
   </si>
   <si>
     <t xml:space="preserve">36.410099029541</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">35.5010414123535</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3096656799316</t>
+    <t xml:space="preserve">35.3096618652344</t>
   </si>
   <si>
     <t xml:space="preserve">34.5441398620605</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">35.0704383850098</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0799293518066</t>
+    <t xml:space="preserve">37.0799331665039</t>
   </si>
   <si>
     <t xml:space="preserve">37.2234687805176</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">37.1277732849121</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2329559326172</t>
+    <t xml:space="preserve">39.2329597473145</t>
   </si>
   <si>
     <t xml:space="preserve">40.429084777832</t>
@@ -2003,16 +2003,16 @@
     <t xml:space="preserve">39.998477935791</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7351417541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9791107177734</t>
+    <t xml:space="preserve">44.7351379394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9791069030762</t>
   </si>
   <si>
     <t xml:space="preserve">45.4528198242188</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0700531005859</t>
+    <t xml:space="preserve">45.0700569152832</t>
   </si>
   <si>
     <t xml:space="preserve">45.3571281433105</t>
@@ -2021,37 +2021,37 @@
     <t xml:space="preserve">45.1179046630859</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4575653076172</t>
+    <t xml:space="preserve">46.4575614929199</t>
   </si>
   <si>
     <t xml:space="preserve">45.6441955566406</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8786773681641</t>
+    <t xml:space="preserve">44.8786735534668</t>
   </si>
   <si>
     <t xml:space="preserve">45.3092803955078</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1657447814941</t>
+    <t xml:space="preserve">45.1657485961914</t>
   </si>
   <si>
     <t xml:space="preserve">44.2088470458984</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1562538146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9217758178711</t>
+    <t xml:space="preserve">43.15625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9217720031738</t>
   </si>
   <si>
     <t xml:space="preserve">41.8644371032715</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5821189880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0222091674805</t>
+    <t xml:space="preserve">42.5821113586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.022216796875</t>
   </si>
   <si>
     <t xml:space="preserve">45.5485038757324</t>
@@ -2072,19 +2072,19 @@
     <t xml:space="preserve">48.5149040222168</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4812927246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1942291259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.768367767334</t>
+    <t xml:space="preserve">51.4813003540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1942253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7683639526367</t>
   </si>
   <si>
     <t xml:space="preserve">51.2899131774902</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1080322265625</t>
+    <t xml:space="preserve">53.1080284118652</t>
   </si>
   <si>
     <t xml:space="preserve">53.9692420959473</t>
@@ -2096,16 +2096,16 @@
     <t xml:space="preserve">55.1175231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6916656494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5002822875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3520011901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6390724182129</t>
+    <t xml:space="preserve">55.6916618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5002784729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3519973754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6390647888184</t>
   </si>
   <si>
     <t xml:space="preserve">54.8304481506348</t>
@@ -2120,19 +2120,19 @@
     <t xml:space="preserve">56.9356346130371</t>
   </si>
   <si>
-    <t xml:space="preserve">57.1270141601562</t>
+    <t xml:space="preserve">57.1270179748535</t>
   </si>
   <si>
     <t xml:space="preserve">56.2658042907715</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9787292480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3183975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6580581665039</t>
+    <t xml:space="preserve">55.9787330627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3183937072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6580505371094</t>
   </si>
   <si>
     <t xml:space="preserve">57.2227058410645</t>
@@ -2147,40 +2147,40 @@
     <t xml:space="preserve">57.988224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">58.8494338989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.3373794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4425735473633</t>
+    <t xml:space="preserve">58.849437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.3373756408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.442569732666</t>
   </si>
   <si>
     <t xml:space="preserve">62.2942810058594</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3468704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7296257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6339378356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3037796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5908508300781</t>
+    <t xml:space="preserve">63.346866607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7296295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6339454650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3037719726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5908432006836</t>
   </si>
   <si>
     <t xml:space="preserve">65.9305038452148</t>
   </si>
   <si>
-    <t xml:space="preserve">66.6960220336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3563613891602</t>
+    <t xml:space="preserve">66.6960296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3563766479492</t>
   </si>
   <si>
     <t xml:space="preserve">66.9831008911133</t>
@@ -2189,25 +2189,25 @@
     <t xml:space="preserve">67.1744766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5046463012695</t>
+    <t xml:space="preserve">66.5046539306641</t>
   </si>
   <si>
     <t xml:space="preserve">67.8443145751953</t>
   </si>
   <si>
-    <t xml:space="preserve">70.0451889038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1839828491211</t>
+    <t xml:space="preserve">70.0451812744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1839752197266</t>
   </si>
   <si>
     <t xml:space="preserve">71.2891616821289</t>
   </si>
   <si>
-    <t xml:space="preserve">70.8106994628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6193313598633</t>
+    <t xml:space="preserve">70.8107147216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6193237304688</t>
   </si>
   <si>
     <t xml:space="preserve">71.7676010131836</t>
@@ -2219,13 +2219,13 @@
     <t xml:space="preserve">71.002082824707</t>
   </si>
   <si>
-    <t xml:space="preserve">69.4710388183594</t>
+    <t xml:space="preserve">69.4710464477539</t>
   </si>
   <si>
     <t xml:space="preserve">68.9925918579102</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9495010375977</t>
+    <t xml:space="preserve">69.9494857788086</t>
   </si>
   <si>
     <t xml:space="preserve">68.8012161254883</t>
@@ -2237,10 +2237,10 @@
     <t xml:space="preserve">76.5521087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7003936767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8822784423828</t>
+    <t xml:space="preserve">77.7003860473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8822860717773</t>
   </si>
   <si>
     <t xml:space="preserve">74.734001159668</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">73.8727798461914</t>
   </si>
   <si>
-    <t xml:space="preserve">74.8296966552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.8917770385742</t>
+    <t xml:space="preserve">74.8296890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.8917694091797</t>
   </si>
   <si>
     <t xml:space="preserve">78.2745361328125</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">79.4228210449219</t>
   </si>
   <si>
-    <t xml:space="preserve">80.7624740600586</t>
+    <t xml:space="preserve">80.7624893188477</t>
   </si>
   <si>
     <t xml:space="preserve">82.0064468383789</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">81.5279998779297</t>
   </si>
   <si>
-    <t xml:space="preserve">81.9107513427734</t>
+    <t xml:space="preserve">81.910758972168</t>
   </si>
   <si>
     <t xml:space="preserve">82.3892135620117</t>
@@ -2282,31 +2282,31 @@
     <t xml:space="preserve">81.4323043823242</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1452484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4754180908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7193832397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8150787353516</t>
+    <t xml:space="preserve">81.1452407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4754028320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7193756103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8150634765625</t>
   </si>
   <si>
     <t xml:space="preserve">83.3461074829102</t>
   </si>
   <si>
-    <t xml:space="preserve">80.953857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.77197265625</t>
+    <t xml:space="preserve">80.9538497924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7719802856445</t>
   </si>
   <si>
     <t xml:space="preserve">82.2935180664062</t>
   </si>
   <si>
-    <t xml:space="preserve">77.0305709838867</t>
+    <t xml:space="preserve">77.0305557250977</t>
   </si>
   <si>
     <t xml:space="preserve">79.3271331787109</t>
@@ -2327,22 +2327,22 @@
     <t xml:space="preserve">79.8055801391602</t>
   </si>
   <si>
-    <t xml:space="preserve">82.4849090576172</t>
+    <t xml:space="preserve">82.4849014282227</t>
   </si>
   <si>
     <t xml:space="preserve">80.3797149658203</t>
   </si>
   <si>
-    <t xml:space="preserve">78.6572875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.4659118652344</t>
+    <t xml:space="preserve">78.6572952270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.4659194946289</t>
   </si>
   <si>
     <t xml:space="preserve">84.6857757568359</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3556060791016</t>
+    <t xml:space="preserve">85.355598449707</t>
   </si>
   <si>
     <t xml:space="preserve">83.0590438842773</t>
@@ -2351,10 +2351,10 @@
     <t xml:space="preserve">85.9297485351562</t>
   </si>
   <si>
-    <t xml:space="preserve">87.1737213134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2694091796875</t>
+    <t xml:space="preserve">87.173713684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.269401550293</t>
   </si>
   <si>
     <t xml:space="preserve">88.3220062255859</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">95.8815155029297</t>
   </si>
   <si>
-    <t xml:space="preserve">97.22119140625</t>
+    <t xml:space="preserve">97.2211761474609</t>
   </si>
   <si>
     <t xml:space="preserve">100.474647521973</t>
@@ -2384,16 +2384,16 @@
     <t xml:space="preserve">101.622924804688</t>
   </si>
   <si>
-    <t xml:space="preserve">101.240173339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.9866943359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5608520507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.9005126953125</t>
+    <t xml:space="preserve">101.240165710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.9867095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5608444213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.9004974365234</t>
   </si>
   <si>
     <t xml:space="preserve">96.2642822265625</t>
@@ -2402,10 +2402,10 @@
     <t xml:space="preserve">95.6901473999023</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8289260864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.307373046875</t>
+    <t xml:space="preserve">94.8289337158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3073806762695</t>
   </si>
   <si>
     <t xml:space="preserve">94.2547912597656</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">94.1591033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8720245361328</t>
+    <t xml:space="preserve">93.8720169067383</t>
   </si>
   <si>
     <t xml:space="preserve">94.0634155273438</t>
@@ -2432,10 +2432,10 @@
     <t xml:space="preserve">93.3935699462891</t>
   </si>
   <si>
-    <t xml:space="preserve">93.6806488037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9151306152344</t>
+    <t xml:space="preserve">93.6806564331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9151229858398</t>
   </si>
   <si>
     <t xml:space="preserve">93.2978820800781</t>
@@ -2453,13 +2453,13 @@
     <t xml:space="preserve">101.431549072266</t>
   </si>
   <si>
-    <t xml:space="preserve">104.876396179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.493637084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.598823547363</t>
+    <t xml:space="preserve">104.876388549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.493629455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.598815917969</t>
   </si>
   <si>
     <t xml:space="preserve">107.364334106445</t>
@@ -2471,16 +2471,16 @@
     <t xml:space="preserve">110.235046386719</t>
   </si>
   <si>
-    <t xml:space="preserve">105.641914367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.216064453125</t>
+    <t xml:space="preserve">105.64192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.21605682373</t>
   </si>
   <si>
     <t xml:space="preserve">107.938484191895</t>
   </si>
   <si>
-    <t xml:space="preserve">107.555725097656</t>
+    <t xml:space="preserve">107.555717468262</t>
   </si>
   <si>
     <t xml:space="preserve">109.469520568848</t>
@@ -2489,7 +2489,7 @@
     <t xml:space="preserve">107.747100830078</t>
   </si>
   <si>
-    <t xml:space="preserve">108.704002380371</t>
+    <t xml:space="preserve">108.703994750977</t>
   </si>
   <si>
     <t xml:space="preserve">102.197074890137</t>
@@ -2501,13 +2501,13 @@
     <t xml:space="preserve">99.7091217041016</t>
   </si>
   <si>
-    <t xml:space="preserve">103.345352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.536735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.024673461914</t>
+    <t xml:space="preserve">103.345344543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.536727905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.024681091309</t>
   </si>
   <si>
     <t xml:space="preserve">106.981582641602</t>
@@ -2516,19 +2516,19 @@
     <t xml:space="preserve">108.51261138916</t>
   </si>
   <si>
-    <t xml:space="preserve">105.833290100098</t>
+    <t xml:space="preserve">105.833282470703</t>
   </si>
   <si>
     <t xml:space="preserve">101.048789978027</t>
   </si>
   <si>
-    <t xml:space="preserve">102.388458251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.15397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.962585449219</t>
+    <t xml:space="preserve">102.388450622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.153968811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.962600708008</t>
   </si>
   <si>
     <t xml:space="preserve">105.450531005859</t>
@@ -2537,10 +2537,10 @@
     <t xml:space="preserve">102.00569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">103.919486999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.407432556152</t>
+    <t xml:space="preserve">103.919494628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.407447814941</t>
   </si>
   <si>
     <t xml:space="preserve">109.086769104004</t>
@@ -2552,28 +2552,28 @@
     <t xml:space="preserve">113.679893493652</t>
   </si>
   <si>
-    <t xml:space="preserve">110.043663024902</t>
+    <t xml:space="preserve">110.043670654297</t>
   </si>
   <si>
     <t xml:space="preserve">107.172950744629</t>
   </si>
   <si>
-    <t xml:space="preserve">111.000564575195</t>
+    <t xml:space="preserve">111.000556945801</t>
   </si>
   <si>
     <t xml:space="preserve">112.914367675781</t>
   </si>
   <si>
-    <t xml:space="preserve">109.852279663086</t>
+    <t xml:space="preserve">109.85228729248</t>
   </si>
   <si>
     <t xml:space="preserve">110.426429748535</t>
   </si>
   <si>
-    <t xml:space="preserve">111.383331298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.340232849121</t>
+    <t xml:space="preserve">111.383323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.340225219727</t>
   </si>
   <si>
     <t xml:space="preserve">114.445411682129</t>
@@ -2588,22 +2588,22 @@
     <t xml:space="preserve">115.019554138184</t>
   </si>
   <si>
-    <t xml:space="preserve">115.593696594238</t>
+    <t xml:space="preserve">115.593688964844</t>
   </si>
   <si>
     <t xml:space="preserve">115.210929870605</t>
   </si>
   <si>
-    <t xml:space="preserve">116.741981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.167831420898</t>
+    <t xml:space="preserve">116.741973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.167839050293</t>
   </si>
   <si>
     <t xml:space="preserve">115.78507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">116.550598144531</t>
+    <t xml:space="preserve">116.550590515137</t>
   </si>
   <si>
     <t xml:space="preserve">119.804054260254</t>
@@ -2615,34 +2615,34 @@
     <t xml:space="preserve">122.100616455078</t>
   </si>
   <si>
-    <t xml:space="preserve">122.866142272949</t>
+    <t xml:space="preserve">122.866134643555</t>
   </si>
   <si>
     <t xml:space="preserve">123.631660461426</t>
   </si>
   <si>
-    <t xml:space="preserve">131.478256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.267875671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.459251403809</t>
+    <t xml:space="preserve">131.478240966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.267890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.459259033203</t>
   </si>
   <si>
     <t xml:space="preserve">128.990310668945</t>
   </si>
   <si>
-    <t xml:space="preserve">132.052383422852</t>
+    <t xml:space="preserve">132.052398681641</t>
   </si>
   <si>
     <t xml:space="preserve">134.157577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">133.774810791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.626541137695</t>
+    <t xml:space="preserve">133.774826049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.626525878906</t>
   </si>
   <si>
     <t xml:space="preserve">132.435134887695</t>
@@ -2651,25 +2651,25 @@
     <t xml:space="preserve">134.923095703125</t>
   </si>
   <si>
-    <t xml:space="preserve">136.6455078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.411041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.305862426758</t>
+    <t xml:space="preserve">136.645538330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.411056518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.305847167969</t>
   </si>
   <si>
     <t xml:space="preserve">131.86100769043</t>
   </si>
   <si>
-    <t xml:space="preserve">134.731719970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.262741088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.793807983398</t>
+    <t xml:space="preserve">134.731735229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.262756347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.793792724609</t>
   </si>
   <si>
     <t xml:space="preserve">138.176559448242</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">138.559326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">139.899002075195</t>
+    <t xml:space="preserve">139.898971557617</t>
   </si>
   <si>
     <t xml:space="preserve">136.454132080078</t>
@@ -2699,10 +2699,10 @@
     <t xml:space="preserve">135.49723815918</t>
   </si>
   <si>
-    <t xml:space="preserve">144.492095947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.874862670898</t>
+    <t xml:space="preserve">144.492111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.874877929688</t>
   </si>
   <si>
     <t xml:space="preserve">144.109359741211</t>
@@ -2711,7 +2711,7 @@
     <t xml:space="preserve">142.195541381836</t>
   </si>
   <si>
-    <t xml:space="preserve">143.726593017578</t>
+    <t xml:space="preserve">143.726577758789</t>
   </si>
   <si>
     <t xml:space="preserve">143.91796875</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">145.640396118164</t>
   </si>
   <si>
-    <t xml:space="preserve">146.788681030273</t>
+    <t xml:space="preserve">146.788665771484</t>
   </si>
   <si>
     <t xml:space="preserve">149.276641845703</t>
@@ -2744,10 +2744,10 @@
     <t xml:space="preserve">153.48698425293</t>
   </si>
   <si>
-    <t xml:space="preserve">152.33869934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.400787353516</t>
+    <t xml:space="preserve">152.338714599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.400772094727</t>
   </si>
   <si>
     <t xml:space="preserve">151.190414428711</t>
@@ -2765,34 +2765,34 @@
     <t xml:space="preserve">159.61116027832</t>
   </si>
   <si>
-    <t xml:space="preserve">161.333602905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.524948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.438766479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.821502685547</t>
+    <t xml:space="preserve">161.333587646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.524978637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.438751220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.821517944336</t>
   </si>
   <si>
     <t xml:space="preserve">168.606018066406</t>
   </si>
   <si>
-    <t xml:space="preserve">173.773300170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.328475952148</t>
+    <t xml:space="preserve">173.773315429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.32844543457</t>
   </si>
   <si>
     <t xml:space="preserve">165.161193847656</t>
   </si>
   <si>
-    <t xml:space="preserve">168.031890869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.352569580078</t>
+    <t xml:space="preserve">168.031875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.352554321289</t>
   </si>
   <si>
     <t xml:space="preserve">160.759429931641</t>
@@ -2801,16 +2801,16 @@
     <t xml:space="preserve">162.099090576172</t>
   </si>
   <si>
-    <t xml:space="preserve">171.668106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.074996948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.930526733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.353591918945</t>
+    <t xml:space="preserve">171.668090820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.074981689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.93049621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.353576660156</t>
   </si>
   <si>
     <t xml:space="preserve">160.58430480957</t>
@@ -2819,22 +2819,22 @@
     <t xml:space="preserve">159.045761108398</t>
   </si>
   <si>
-    <t xml:space="preserve">152.122375488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.583602905273</t>
+    <t xml:space="preserve">152.122360229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.583618164062</t>
   </si>
   <si>
     <t xml:space="preserve">147.314468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">150.391525268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.19921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.083740234375</t>
+    <t xml:space="preserve">150.391510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.199203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.083724975586</t>
   </si>
   <si>
     <t xml:space="preserve">151.737747192383</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">155.199432373047</t>
   </si>
   <si>
-    <t xml:space="preserve">156.545669555664</t>
+    <t xml:space="preserve">156.545654296875</t>
   </si>
   <si>
     <t xml:space="preserve">155.968704223633</t>
@@ -2861,13 +2861,13 @@
     <t xml:space="preserve">166.353805541992</t>
   </si>
   <si>
-    <t xml:space="preserve">170.200119018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.469284057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.430633544922</t>
+    <t xml:space="preserve">170.200134277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.469268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.430618286133</t>
   </si>
   <si>
     <t xml:space="preserve">165.007583618164</t>
@@ -2876,13 +2876,13 @@
     <t xml:space="preserve">162.507461547852</t>
   </si>
   <si>
-    <t xml:space="preserve">163.469055175781</t>
+    <t xml:space="preserve">163.469039916992</t>
   </si>
   <si>
     <t xml:space="preserve">165.584533691406</t>
   </si>
   <si>
-    <t xml:space="preserve">161.161254882812</t>
+    <t xml:space="preserve">161.161270141602</t>
   </si>
   <si>
     <t xml:space="preserve">163.084426879883</t>
@@ -2894,34 +2894,34 @@
     <t xml:space="preserve">168.853912353516</t>
   </si>
   <si>
-    <t xml:space="preserve">177.508163452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.585006713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.392929077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.777542114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.469741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.815963745117</t>
+    <t xml:space="preserve">177.508178710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.584991455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.392913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.777526855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.469757080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.815948486328</t>
   </si>
   <si>
     <t xml:space="preserve">181.739120483398</t>
   </si>
   <si>
-    <t xml:space="preserve">185.008514404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.085327148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.508407592773</t>
+    <t xml:space="preserve">185.008499145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.085342407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.508392333984</t>
   </si>
   <si>
     <t xml:space="preserve">168.276962280273</t>
@@ -2930,10 +2930,10 @@
     <t xml:space="preserve">169.046249389648</t>
   </si>
   <si>
-    <t xml:space="preserve">170.584762573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.507705688477</t>
+    <t xml:space="preserve">170.584777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.507690429688</t>
   </si>
   <si>
     <t xml:space="preserve">174.046463012695</t>
@@ -2945,13 +2945,13 @@
     <t xml:space="preserve">169.623184204102</t>
   </si>
   <si>
-    <t xml:space="preserve">169.238540649414</t>
+    <t xml:space="preserve">169.238555908203</t>
   </si>
   <si>
     <t xml:space="preserve">175.008041381836</t>
   </si>
   <si>
-    <t xml:space="preserve">172.700241088867</t>
+    <t xml:space="preserve">172.700256347656</t>
   </si>
   <si>
     <t xml:space="preserve">172.123291015625</t>
@@ -2963,13 +2963,13 @@
     <t xml:space="preserve">167.315383911133</t>
   </si>
   <si>
-    <t xml:space="preserve">163.853668212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.738418579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.238327026367</t>
+    <t xml:space="preserve">163.85368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.738433837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.238311767578</t>
   </si>
   <si>
     <t xml:space="preserve">166.546112060547</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">167.700012207031</t>
   </si>
   <si>
-    <t xml:space="preserve">165.392227172852</t>
+    <t xml:space="preserve">165.392211914062</t>
   </si>
   <si>
     <t xml:space="preserve">151.160781860352</t>
@@ -2990,10 +2990,10 @@
     <t xml:space="preserve">158.468826293945</t>
   </si>
   <si>
-    <t xml:space="preserve">157.314926147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.815048217773</t>
+    <t xml:space="preserve">157.31494140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.815032958984</t>
   </si>
   <si>
     <t xml:space="preserve">156.930282592773</t>
@@ -3002,25 +3002,25 @@
     <t xml:space="preserve">156.161010742188</t>
   </si>
   <si>
-    <t xml:space="preserve">152.314697265625</t>
+    <t xml:space="preserve">152.314666748047</t>
   </si>
   <si>
     <t xml:space="preserve">145.96826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">146.929824829102</t>
+    <t xml:space="preserve">146.929840087891</t>
   </si>
   <si>
     <t xml:space="preserve">151.353088378906</t>
   </si>
   <si>
-    <t xml:space="preserve">153.46858215332</t>
+    <t xml:space="preserve">153.468612670898</t>
   </si>
   <si>
     <t xml:space="preserve">153.276260375977</t>
   </si>
   <si>
-    <t xml:space="preserve">157.122619628906</t>
+    <t xml:space="preserve">157.122604370117</t>
   </si>
   <si>
     <t xml:space="preserve">151.930053710938</t>
@@ -3029,10 +3029,10 @@
     <t xml:space="preserve">146.545196533203</t>
   </si>
   <si>
-    <t xml:space="preserve">140.968032836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.929351806641</t>
+    <t xml:space="preserve">140.968017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.92936706543</t>
   </si>
   <si>
     <t xml:space="preserve">138.660217285156</t>
@@ -3044,31 +3044,31 @@
     <t xml:space="preserve">132.506088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">130.198272705078</t>
+    <t xml:space="preserve">130.198287963867</t>
   </si>
   <si>
     <t xml:space="preserve">134.813888549805</t>
   </si>
   <si>
-    <t xml:space="preserve">130.005966186523</t>
+    <t xml:space="preserve">130.005981445312</t>
   </si>
   <si>
     <t xml:space="preserve">130.775238037109</t>
   </si>
   <si>
-    <t xml:space="preserve">128.852081298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.621337890625</t>
+    <t xml:space="preserve">128.852066040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.621353149414</t>
   </si>
   <si>
     <t xml:space="preserve">132.890716552734</t>
   </si>
   <si>
-    <t xml:space="preserve">137.506332397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.160110473633</t>
+    <t xml:space="preserve">137.506317138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.160125732422</t>
   </si>
   <si>
     <t xml:space="preserve">138.467895507812</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">135.583160400391</t>
   </si>
   <si>
-    <t xml:space="preserve">124.813430786133</t>
+    <t xml:space="preserve">124.813438415527</t>
   </si>
   <si>
     <t xml:space="preserve">118.659301757812</t>
@@ -3086,16 +3086,16 @@
     <t xml:space="preserve">125.582702636719</t>
   </si>
   <si>
-    <t xml:space="preserve">125.198066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.313995361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.8525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.891174316406</t>
+    <t xml:space="preserve">125.198059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.314010620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.852523803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.891189575195</t>
   </si>
   <si>
     <t xml:space="preserve">140.391067504883</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">145.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">145.006652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.775939941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.814346313477</t>
+    <t xml:space="preserve">145.00666809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.775955200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.814361572266</t>
   </si>
   <si>
     <t xml:space="preserve">148.27604675293</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">143.275817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">142.60270690918</t>
+    <t xml:space="preserve">142.602722167969</t>
   </si>
   <si>
     <t xml:space="preserve">142.698852539062</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">140.198745727539</t>
   </si>
   <si>
-    <t xml:space="preserve">139.910293579102</t>
+    <t xml:space="preserve">139.910263061523</t>
   </si>
   <si>
     <t xml:space="preserve">139.429473876953</t>
@@ -3149,16 +3149,16 @@
     <t xml:space="preserve">140.006439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">138.564056396484</t>
+    <t xml:space="preserve">138.564071655273</t>
   </si>
   <si>
     <t xml:space="preserve">143.179641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">142.314224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.87141418457</t>
+    <t xml:space="preserve">142.314239501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.871398925781</t>
   </si>
   <si>
     <t xml:space="preserve">129.525177001953</t>
@@ -3179,10 +3179,10 @@
     <t xml:space="preserve">124.236473083496</t>
   </si>
   <si>
-    <t xml:space="preserve">122.890258789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.563140869141</t>
+    <t xml:space="preserve">122.890266418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.563148498535</t>
   </si>
   <si>
     <t xml:space="preserve">109.81273651123</t>
@@ -3200,40 +3200,40 @@
     <t xml:space="preserve">118.755462646484</t>
   </si>
   <si>
-    <t xml:space="preserve">118.08235168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.313316345215</t>
+    <t xml:space="preserve">118.082344055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.31330871582</t>
   </si>
   <si>
     <t xml:space="preserve">120.293991088867</t>
   </si>
   <si>
-    <t xml:space="preserve">120.101684570312</t>
+    <t xml:space="preserve">120.101669311523</t>
   </si>
   <si>
     <t xml:space="preserve">119.236251831055</t>
   </si>
   <si>
-    <t xml:space="preserve">120.486305236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.736137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.832290649414</t>
+    <t xml:space="preserve">120.486312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.736129760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.832298278809</t>
   </si>
   <si>
     <t xml:space="preserve">119.043937683105</t>
   </si>
   <si>
-    <t xml:space="preserve">121.736358642578</t>
+    <t xml:space="preserve">121.736366271973</t>
   </si>
   <si>
     <t xml:space="preserve">124.621116638184</t>
   </si>
   <si>
-    <t xml:space="preserve">123.27490234375</t>
+    <t xml:space="preserve">123.274887084961</t>
   </si>
   <si>
     <t xml:space="preserve">121.544044494629</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">128.659759521484</t>
   </si>
   <si>
-    <t xml:space="preserve">127.69815826416</t>
+    <t xml:space="preserve">127.698173522949</t>
   </si>
   <si>
     <t xml:space="preserve">123.178741455078</t>
   </si>
   <si>
-    <t xml:space="preserve">114.524490356445</t>
+    <t xml:space="preserve">114.52449798584</t>
   </si>
   <si>
     <t xml:space="preserve">112.889801025391</t>
@@ -3266,22 +3266,22 @@
     <t xml:space="preserve">114.236022949219</t>
   </si>
   <si>
-    <t xml:space="preserve">111.062797546387</t>
+    <t xml:space="preserve">111.062789916992</t>
   </si>
   <si>
     <t xml:space="preserve">112.216690063477</t>
   </si>
   <si>
-    <t xml:space="preserve">112.505172729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.947540283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.447654724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.197601318359</t>
+    <t xml:space="preserve">112.505180358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.947547912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.447662353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.197608947754</t>
   </si>
   <si>
     <t xml:space="preserve">119.140090942383</t>
@@ -3290,10 +3290,10 @@
     <t xml:space="preserve">119.909355163574</t>
   </si>
   <si>
-    <t xml:space="preserve">119.428558349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.890037536621</t>
+    <t xml:space="preserve">119.428565979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.890029907227</t>
   </si>
   <si>
     <t xml:space="preserve">115.293762207031</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">113.178276062012</t>
   </si>
   <si>
-    <t xml:space="preserve">119.332397460938</t>
+    <t xml:space="preserve">119.332405090332</t>
   </si>
   <si>
     <t xml:space="preserve">123.082580566406</t>
@@ -3311,76 +3311,76 @@
     <t xml:space="preserve">125.390365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">122.986427307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.274658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.71703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.774772644043</t>
+    <t xml:space="preserve">122.986419677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.27466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.717041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.774787902832</t>
   </si>
   <si>
     <t xml:space="preserve">123.659530639648</t>
   </si>
   <si>
-    <t xml:space="preserve">128.9482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.73681640625</t>
+    <t xml:space="preserve">128.948226928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.736831665039</t>
   </si>
   <si>
     <t xml:space="preserve">130.679077148438</t>
   </si>
   <si>
-    <t xml:space="preserve">126.832748413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.794334411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.46745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.602249145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.044403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.159881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.967315673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.351951599121</t>
+    <t xml:space="preserve">126.832740783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.794319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.467437744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.602233886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.044372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.159866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.967338562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.351959228516</t>
   </si>
   <si>
     <t xml:space="preserve">123.563369750977</t>
   </si>
   <si>
-    <t xml:space="preserve">127.313537597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.371292114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.736602783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.447883605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.6015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.947776794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.19783782959</t>
+    <t xml:space="preserve">127.313529968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.371276855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.736595153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.447891235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.601554870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.947769165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.197830200195</t>
   </si>
   <si>
     <t xml:space="preserve">121.063255310059</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">117.505393981934</t>
   </si>
   <si>
-    <t xml:space="preserve">115.870704650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.255348205566</t>
+    <t xml:space="preserve">115.870712280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.255332946777</t>
   </si>
   <si>
     <t xml:space="preserve">112.312850952148</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">115.678398132324</t>
   </si>
   <si>
-    <t xml:space="preserve">118.178512573242</t>
+    <t xml:space="preserve">118.178504943848</t>
   </si>
   <si>
     <t xml:space="preserve">114.909133911133</t>
@@ -3428,40 +3428,40 @@
     <t xml:space="preserve">105.917831420898</t>
   </si>
   <si>
-    <t xml:space="preserve">102.816841125488</t>
+    <t xml:space="preserve">102.816848754883</t>
   </si>
   <si>
     <t xml:space="preserve">106.014739990234</t>
   </si>
   <si>
-    <t xml:space="preserve">102.041610717773</t>
+    <t xml:space="preserve">102.041603088379</t>
   </si>
   <si>
     <t xml:space="preserve">108.437377929688</t>
   </si>
   <si>
-    <t xml:space="preserve">109.212623596191</t>
+    <t xml:space="preserve">109.212615966797</t>
   </si>
   <si>
     <t xml:space="preserve">113.185752868652</t>
   </si>
   <si>
-    <t xml:space="preserve">111.441444396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.829078674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.274505615234</t>
+    <t xml:space="preserve">111.441452026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.829071044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.27449798584</t>
   </si>
   <si>
     <t xml:space="preserve">104.851860046387</t>
   </si>
   <si>
-    <t xml:space="preserve">104.658058166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.847793579102</t>
+    <t xml:space="preserve">104.658050537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.847785949707</t>
   </si>
   <si>
     <t xml:space="preserve">102.429222106934</t>
@@ -3476,10 +3476,10 @@
     <t xml:space="preserve">106.402359008789</t>
   </si>
   <si>
-    <t xml:space="preserve">106.693077087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.860015869141</t>
+    <t xml:space="preserve">106.693069458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.860023498535</t>
   </si>
   <si>
     <t xml:space="preserve">116.189826965332</t>
@@ -3488,13 +3488,13 @@
     <t xml:space="preserve">114.348617553711</t>
   </si>
   <si>
-    <t xml:space="preserve">109.794059753418</t>
+    <t xml:space="preserve">109.794052124023</t>
   </si>
   <si>
     <t xml:space="preserve">107.468315124512</t>
   </si>
   <si>
-    <t xml:space="preserve">106.305442810059</t>
+    <t xml:space="preserve">106.305450439453</t>
   </si>
   <si>
     <t xml:space="preserve">102.332321166992</t>
@@ -3506,13 +3506,13 @@
     <t xml:space="preserve">103.979721069336</t>
   </si>
   <si>
-    <t xml:space="preserve">108.340469360352</t>
+    <t xml:space="preserve">108.340476989746</t>
   </si>
   <si>
     <t xml:space="preserve">117.643409729004</t>
   </si>
   <si>
-    <t xml:space="preserve">118.515563964844</t>
+    <t xml:space="preserve">118.515556335449</t>
   </si>
   <si>
     <t xml:space="preserve">117.837219238281</t>
@@ -3521,13 +3521,13 @@
     <t xml:space="preserve">116.771255493164</t>
   </si>
   <si>
-    <t xml:space="preserve">114.445526123047</t>
+    <t xml:space="preserve">114.445518493652</t>
   </si>
   <si>
     <t xml:space="preserve">114.73624420166</t>
   </si>
   <si>
-    <t xml:space="preserve">115.026954650879</t>
+    <t xml:space="preserve">115.026947021484</t>
   </si>
   <si>
     <t xml:space="preserve">115.317672729492</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">116.965065002441</t>
   </si>
   <si>
-    <t xml:space="preserve">113.476463317871</t>
+    <t xml:space="preserve">113.476470947266</t>
   </si>
   <si>
     <t xml:space="preserve">114.25171661377</t>
@@ -3554,10 +3554,10 @@
     <t xml:space="preserve">117.449592590332</t>
   </si>
   <si>
-    <t xml:space="preserve">118.612464904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.991943359375</t>
+    <t xml:space="preserve">118.61247253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.99193572998</t>
   </si>
   <si>
     <t xml:space="preserve">111.053825378418</t>
@@ -3569,19 +3569,19 @@
     <t xml:space="preserve">112.604316711426</t>
   </si>
   <si>
-    <t xml:space="preserve">115.99600982666</t>
+    <t xml:space="preserve">115.996017456055</t>
   </si>
   <si>
     <t xml:space="preserve">112.216697692871</t>
   </si>
   <si>
-    <t xml:space="preserve">108.243560791016</t>
+    <t xml:space="preserve">108.24356842041</t>
   </si>
   <si>
     <t xml:space="preserve">107.080696105957</t>
   </si>
   <si>
-    <t xml:space="preserve">110.375495910645</t>
+    <t xml:space="preserve">110.37548828125</t>
   </si>
   <si>
     <t xml:space="preserve">108.534278869629</t>
@@ -3590,25 +3590,25 @@
     <t xml:space="preserve">110.181671142578</t>
   </si>
   <si>
-    <t xml:space="preserve">109.890960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.247650146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.282653808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.410507202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.63932800293</t>
+    <t xml:space="preserve">109.890953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.24764251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.282661437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.410499572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.639335632324</t>
   </si>
   <si>
     <t xml:space="preserve">117.934120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">117.25577545166</t>
+    <t xml:space="preserve">117.255783081055</t>
   </si>
   <si>
     <t xml:space="preserve">117.352691650391</t>
@@ -3617,10 +3617,10 @@
     <t xml:space="preserve">118.031028747559</t>
   </si>
   <si>
-    <t xml:space="preserve">121.132011413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.101066589355</t>
+    <t xml:space="preserve">121.13200378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.10107421875</t>
   </si>
   <si>
     <t xml:space="preserve">122.876312255859</t>
@@ -3641,25 +3641,25 @@
     <t xml:space="preserve">123.26392364502</t>
   </si>
   <si>
-    <t xml:space="preserve">121.810340881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.744384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.748458862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.985427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.888534545898</t>
+    <t xml:space="preserve">121.810348510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.74437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.74845123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.985443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.888549804688</t>
   </si>
   <si>
     <t xml:space="preserve">132.179244995117</t>
   </si>
   <si>
-    <t xml:space="preserve">130.531845092773</t>
+    <t xml:space="preserve">130.531829833984</t>
   </si>
   <si>
     <t xml:space="preserve">128.593734741211</t>
@@ -3671,19 +3671,19 @@
     <t xml:space="preserve">124.814430236816</t>
   </si>
   <si>
-    <t xml:space="preserve">125.686576843262</t>
+    <t xml:space="preserve">125.686569213867</t>
   </si>
   <si>
     <t xml:space="preserve">126.849433898926</t>
   </si>
   <si>
-    <t xml:space="preserve">127.333961486816</t>
+    <t xml:space="preserve">127.333953857422</t>
   </si>
   <si>
     <t xml:space="preserve">126.946342468262</t>
   </si>
   <si>
-    <t xml:space="preserve">124.136085510254</t>
+    <t xml:space="preserve">124.136093139648</t>
   </si>
   <si>
     <t xml:space="preserve">123.845367431641</t>
@@ -3713,16 +3713,16 @@
     <t xml:space="preserve">113.864097595215</t>
   </si>
   <si>
-    <t xml:space="preserve">113.960990905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.088844299316</t>
+    <t xml:space="preserve">113.960998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.088836669922</t>
   </si>
   <si>
     <t xml:space="preserve">110.472396850586</t>
   </si>
   <si>
-    <t xml:space="preserve">108.824996948242</t>
+    <t xml:space="preserve">108.825004577637</t>
   </si>
   <si>
     <t xml:space="preserve">115.414573669434</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">113.670280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">118.127937316895</t>
+    <t xml:space="preserve">118.1279296875</t>
   </si>
   <si>
     <t xml:space="preserve">114.154808044434</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">116.286727905273</t>
   </si>
   <si>
-    <t xml:space="preserve">119.193893432617</t>
+    <t xml:space="preserve">119.193901062012</t>
   </si>
   <si>
     <t xml:space="preserve">119.09700012207</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">119.678428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">116.383628845215</t>
+    <t xml:space="preserve">116.383636474609</t>
   </si>
   <si>
     <t xml:space="preserve">115.123870849609</t>
@@ -3779,13 +3779,13 @@
     <t xml:space="preserve">107.565223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">105.045677185059</t>
+    <t xml:space="preserve">105.045684814453</t>
   </si>
   <si>
     <t xml:space="preserve">104.754959106445</t>
   </si>
   <si>
-    <t xml:space="preserve">105.724014282227</t>
+    <t xml:space="preserve">105.724021911621</t>
   </si>
   <si>
     <t xml:space="preserve">103.592094421387</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">103.204475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">100.588027954102</t>
+    <t xml:space="preserve">100.588020324707</t>
   </si>
   <si>
     <t xml:space="preserve">100.297302246094</t>
@@ -3827,10 +3827,10 @@
     <t xml:space="preserve">116.480545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">115.705299377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.37956237793</t>
+    <t xml:space="preserve">115.705291748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.379570007324</t>
   </si>
   <si>
     <t xml:space="preserve">112.798126220703</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">111.150726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">110.763107299805</t>
+    <t xml:space="preserve">110.763114929199</t>
   </si>
   <si>
     <t xml:space="preserve">109.503341674805</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">109.697143554688</t>
   </si>
   <si>
-    <t xml:space="preserve">102.235412597656</t>
+    <t xml:space="preserve">102.235420227051</t>
   </si>
   <si>
     <t xml:space="preserve">102.623046875</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">100.975639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">100.200393676758</t>
+    <t xml:space="preserve">100.200401306152</t>
   </si>
   <si>
     <t xml:space="preserve">100.491111755371</t>
@@ -3878,7 +3878,7 @@
     <t xml:space="preserve">100.006591796875</t>
   </si>
   <si>
-    <t xml:space="preserve">99.4251556396484</t>
+    <t xml:space="preserve">99.4251480102539</t>
   </si>
   <si>
     <t xml:space="preserve">101.26636505127</t>
@@ -3890,19 +3890,19 @@
     <t xml:space="preserve">100.39421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">99.3282470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6189651489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2313461303711</t>
+    <t xml:space="preserve">99.328239440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6189727783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2313385009766</t>
   </si>
   <si>
     <t xml:space="preserve">102.138511657715</t>
   </si>
   <si>
-    <t xml:space="preserve">101.75089263916</t>
+    <t xml:space="preserve">101.750885009766</t>
   </si>
   <si>
     <t xml:space="preserve">99.8127746582031</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">97.1963272094727</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6808471679688</t>
+    <t xml:space="preserve">97.6808547973633</t>
   </si>
   <si>
     <t xml:space="preserve">99.0078277587891</t>
@@ -5241,6 +5241,9 @@
   </si>
   <si>
     <t xml:space="preserve">84.3000030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3499984741211</t>
   </si>
 </sst>
 </file>
@@ -71125,7 +71128,7 @@
     </row>
     <row r="2522">
       <c r="A2522" s="1" t="n">
-        <v>45989.6911574074</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2522" t="n">
         <v>26637</v>
@@ -71146,6 +71149,32 @@
         <v>1742</v>
       </c>
       <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.6912962963</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>35062</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>85.3499984741211</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>83</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>84.3000030517578</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>85.3499984741211</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>1743</v>
+      </c>
+      <c r="H2523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1754" uniqueCount="1754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="1755">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5495910644531</t>
+    <t xml:space="preserve">13.5495891571045</t>
   </si>
   <si>
     <t xml:space="preserve">SES.MI</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">13.5321063995361</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2523736953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9464149475098</t>
+    <t xml:space="preserve">13.2523746490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9464159011841</t>
   </si>
   <si>
     <t xml:space="preserve">13.1125068664551</t>
@@ -65,28 +65,28 @@
     <t xml:space="preserve">12.9901237487793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9376726150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1037654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.025089263916</t>
+    <t xml:space="preserve">12.9376735687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1037635803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0250902175903</t>
   </si>
   <si>
     <t xml:space="preserve">12.8502559661865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.238338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5880069732666</t>
+    <t xml:space="preserve">12.2383413314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5880060195923</t>
   </si>
   <si>
     <t xml:space="preserve">12.7890653610229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7191324234009</t>
+    <t xml:space="preserve">12.7191295623779</t>
   </si>
   <si>
     <t xml:space="preserve">12.6841650009155</t>
@@ -95,31 +95,31 @@
     <t xml:space="preserve">12.6054906845093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3257570266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0460214614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1771478652954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1421813964844</t>
+    <t xml:space="preserve">12.325756072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0460224151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1771488189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1421823501587</t>
   </si>
   <si>
     <t xml:space="preserve">10.9270896911621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9795408248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3641729354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4515895843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0984716415405</t>
+    <t xml:space="preserve">10.9795379638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3641719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4515905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0984735488892</t>
   </si>
   <si>
     <t xml:space="preserve">12.1072149276733</t>
@@ -131,82 +131,82 @@
     <t xml:space="preserve">11.9760894775391</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9323816299438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0110578536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0809898376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8012580871582</t>
+    <t xml:space="preserve">11.9323806762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0110559463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0809879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8012552261353</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334400177002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8274793624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0635061264038</t>
+    <t xml:space="preserve">11.8274812698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0635051727295</t>
   </si>
   <si>
     <t xml:space="preserve">12.5005903244019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.675422668457</t>
+    <t xml:space="preserve">12.6754236221313</t>
   </si>
   <si>
     <t xml:space="preserve">12.7978067398071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1649560928345</t>
+    <t xml:space="preserve">13.1649570465088</t>
   </si>
   <si>
     <t xml:space="preserve">13.1562156677246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0687980651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1212501525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.19118309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7540998458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8939647674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9027080535889</t>
+    <t xml:space="preserve">13.0687999725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1212491989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1911821365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7540988922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8939657211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9027061462402</t>
   </si>
   <si>
     <t xml:space="preserve">13.0600566864014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1999225616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9813833236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4534320831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7069406509399</t>
+    <t xml:space="preserve">13.1999244689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9813814163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4534311294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7069425582886</t>
   </si>
   <si>
     <t xml:space="preserve">13.4709138870239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4621753692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2086658477783</t>
+    <t xml:space="preserve">13.4621725082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2086639404297</t>
   </si>
   <si>
     <t xml:space="preserve">13.3223075866699</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">13.0950231552124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9988641738892</t>
+    <t xml:space="preserve">12.9988651275635</t>
   </si>
   <si>
     <t xml:space="preserve">12.640456199646</t>
@@ -230,91 +230,91 @@
     <t xml:space="preserve">12.0285396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1509227752686</t>
+    <t xml:space="preserve">12.1509237289429</t>
   </si>
   <si>
     <t xml:space="preserve">12.4393978118896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5617809295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5268135070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6317148208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3694639205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7715816497803</t>
+    <t xml:space="preserve">12.5617828369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.526816368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6317157745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3694648742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.771580696106</t>
   </si>
   <si>
     <t xml:space="preserve">12.4306564331055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2820501327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1946325302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2470817565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4131727218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5093307495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3869485855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8187389373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8449640274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.255823135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5792655944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2208566665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1858892440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7803249359131</t>
+    <t xml:space="preserve">12.2820491790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1946315765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2470808029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4131717681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5093326568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3869476318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8187398910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8449659347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2558221817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5792665481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2208557128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1858901977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7803230285645</t>
   </si>
   <si>
     <t xml:space="preserve">12.7278738021851</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8764801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8065490722656</t>
+    <t xml:space="preserve">12.8764810562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8065481185913</t>
   </si>
   <si>
     <t xml:space="preserve">12.7628402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8677406311035</t>
+    <t xml:space="preserve">12.8677396774292</t>
   </si>
   <si>
     <t xml:space="preserve">12.8327741622925</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5355577468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1824407577515</t>
+    <t xml:space="preserve">12.5355567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1824388504028</t>
   </si>
   <si>
     <t xml:space="preserve">13.0338315963745</t>
@@ -323,37 +323,37 @@
     <t xml:space="preserve">13.3048238754272</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2611169815063</t>
+    <t xml:space="preserve">13.2611141204834</t>
   </si>
   <si>
     <t xml:space="preserve">13.3747577667236</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6020421981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6894569396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7244243621826</t>
+    <t xml:space="preserve">13.6020393371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6894578933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7244234085083</t>
   </si>
   <si>
     <t xml:space="preserve">13.7514762878418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5711288452148</t>
+    <t xml:space="preserve">13.5711307525635</t>
   </si>
   <si>
     <t xml:space="preserve">13.8687019348145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6252326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6432685852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6613035202026</t>
+    <t xml:space="preserve">13.6252317428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6432676315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6613025665283</t>
   </si>
   <si>
     <t xml:space="preserve">13.598180770874</t>
@@ -362,40 +362,40 @@
     <t xml:space="preserve">13.6162147521973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5260419845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5530939102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3456935882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801458358765</t>
+    <t xml:space="preserve">13.5260429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5530948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3456954956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801467895508</t>
   </si>
   <si>
     <t xml:space="preserve">13.6973714828491</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7785263061523</t>
+    <t xml:space="preserve">13.7785272598267</t>
   </si>
   <si>
     <t xml:space="preserve">13.6703205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7965631484985</t>
+    <t xml:space="preserve">13.7965621948242</t>
   </si>
   <si>
     <t xml:space="preserve">13.9769105911255</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0400314331055</t>
+    <t xml:space="preserve">14.0400304794312</t>
   </si>
   <si>
     <t xml:space="preserve">14.0129795074463</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9047698974609</t>
+    <t xml:space="preserve">13.9047718048096</t>
   </si>
   <si>
     <t xml:space="preserve">14.1031532287598</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">14.2474308013916</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1572580337524</t>
+    <t xml:space="preserve">14.1572561264038</t>
   </si>
   <si>
     <t xml:space="preserve">14.3646564483643</t>
@@ -413,46 +413,46 @@
     <t xml:space="preserve">14.4187602996826</t>
   </si>
   <si>
-    <t xml:space="preserve">14.517951965332</t>
+    <t xml:space="preserve">14.5179529190063</t>
   </si>
   <si>
     <t xml:space="preserve">14.6081266403198</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6622285842896</t>
+    <t xml:space="preserve">14.6622295379639</t>
   </si>
   <si>
     <t xml:space="preserve">14.3917083740234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3105535507202</t>
+    <t xml:space="preserve">14.3105525970459</t>
   </si>
   <si>
     <t xml:space="preserve">14.30153465271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5450029373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6441946029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7343692779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7163352966309</t>
+    <t xml:space="preserve">14.5450038909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.644193649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7343673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7163314819336</t>
   </si>
   <si>
     <t xml:space="preserve">14.6351776123047</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6261596679688</t>
+    <t xml:space="preserve">14.6261577606201</t>
   </si>
   <si>
     <t xml:space="preserve">14.6892824172974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8245429992676</t>
+    <t xml:space="preserve">14.8245410919189</t>
   </si>
   <si>
     <t xml:space="preserve">14.8065071105957</t>
@@ -464,34 +464,34 @@
     <t xml:space="preserve">14.581072807312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.698296546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5089349746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6712484359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6532135009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9237337112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.049976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2122888565063</t>
+    <t xml:space="preserve">14.6982975006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5089340209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6712474822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6532125473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.923731803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0499782562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2122898101807</t>
   </si>
   <si>
     <t xml:space="preserve">15.3746004104614</t>
   </si>
   <si>
-    <t xml:space="preserve">15.554949760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9246616363525</t>
+    <t xml:space="preserve">15.5549478530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9246578216553</t>
   </si>
   <si>
     <t xml:space="preserve">15.7803802490234</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">15.7082433700562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9517126083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7452373504639</t>
+    <t xml:space="preserve">15.9517107009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7452392578125</t>
   </si>
   <si>
     <t xml:space="preserve">16.8714828491211</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">17.0879001617432</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1510219573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2231616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9796924591064</t>
+    <t xml:space="preserve">17.1510200500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2231636047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9796943664551</t>
   </si>
   <si>
     <t xml:space="preserve">16.9075527191162</t>
@@ -533,64 +533,64 @@
     <t xml:space="preserve">17.3043174743652</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0337905883789</t>
+    <t xml:space="preserve">17.0337963104248</t>
   </si>
   <si>
     <t xml:space="preserve">17.2772655487061</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4756450653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3223514556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1690578460693</t>
+    <t xml:space="preserve">17.4756469726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3223476409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1690559387207</t>
   </si>
   <si>
     <t xml:space="preserve">17.5838565826416</t>
   </si>
   <si>
-    <t xml:space="preserve">17.574836730957</t>
+    <t xml:space="preserve">17.5748386383057</t>
   </si>
   <si>
     <t xml:space="preserve">17.5658187866211</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2411937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1870899200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8534507751465</t>
+    <t xml:space="preserve">17.2411975860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1870918273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8534469604492</t>
   </si>
   <si>
     <t xml:space="preserve">16.8444309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9526386260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7272052764893</t>
+    <t xml:space="preserve">16.9526348114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7272033691406</t>
   </si>
   <si>
     <t xml:space="preserve">16.6911373138428</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8624649047852</t>
+    <t xml:space="preserve">16.8624668121338</t>
   </si>
   <si>
     <t xml:space="preserve">17.0428123474121</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8173809051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9977283477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7722930908203</t>
+    <t xml:space="preserve">16.8173770904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.997730255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.772289276123</t>
   </si>
   <si>
     <t xml:space="preserve">17.0067443847656</t>
@@ -599,31 +599,31 @@
     <t xml:space="preserve">17.1961078643799</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3584213256836</t>
+    <t xml:space="preserve">17.358419418335</t>
   </si>
   <si>
     <t xml:space="preserve">17.6199264526367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7642040252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0076675415039</t>
+    <t xml:space="preserve">17.7642021179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0076694488525</t>
   </si>
   <si>
     <t xml:space="preserve">17.9896373748779</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9445476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9535655975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8092880249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2601566314697</t>
+    <t xml:space="preserve">17.9445495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9535636901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8092918395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2601547241211</t>
   </si>
   <si>
     <t xml:space="preserve">18.7561092376709</t>
@@ -632,10 +632,10 @@
     <t xml:space="preserve">18.8462829589844</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9364604949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6208515167236</t>
+    <t xml:space="preserve">18.9364585876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.620849609375</t>
   </si>
   <si>
     <t xml:space="preserve">19.2971534729004</t>
@@ -644,31 +644,31 @@
     <t xml:space="preserve">19.3602733612061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3512592315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6668663024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6488304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5586605072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.252067565918</t>
+    <t xml:space="preserve">19.3512554168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6668643951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.648832321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5586566925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2520656585693</t>
   </si>
   <si>
     <t xml:space="preserve">19.1709136962891</t>
   </si>
   <si>
-    <t xml:space="preserve">19.134838104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.197961807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9544906616211</t>
+    <t xml:space="preserve">19.1348400115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1979637145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9544925689697</t>
   </si>
   <si>
     <t xml:space="preserve">18.9094066619873</t>
@@ -677,100 +677,100 @@
     <t xml:space="preserve">19.0897541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5757637023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1970367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5306758880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8372688293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4594688415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3873252868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0185451507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3612022399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8301067352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2809734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8751907348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9292945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1006259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0104503631592</t>
+    <t xml:space="preserve">18.5757656097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1970348358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5306777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8372669219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4594669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3873271942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0185413360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3612041473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8301048278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2809715270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8751945495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9292964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.100622177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0104522705078</t>
   </si>
   <si>
     <t xml:space="preserve">20.5685997009277</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7218952178955</t>
+    <t xml:space="preserve">20.7218933105469</t>
   </si>
   <si>
     <t xml:space="preserve">20.6046695709229</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1898708343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792381286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6497573852539</t>
+    <t xml:space="preserve">20.189868927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792400360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6497554779053</t>
   </si>
   <si>
     <t xml:space="preserve">21.6416683197021</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3711452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.380163192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0925331115723</t>
+    <t xml:space="preserve">21.3711490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3801612854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0925369262695</t>
   </si>
   <si>
     <t xml:space="preserve">22.6245613098145</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7147350311279</t>
+    <t xml:space="preserve">22.7147331237793</t>
   </si>
   <si>
     <t xml:space="preserve">22.8049087524414</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5984325408936</t>
+    <t xml:space="preserve">23.5984344482422</t>
   </si>
   <si>
     <t xml:space="preserve">24.0763568878174</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0583209991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7156600952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9320774078369</t>
+    <t xml:space="preserve">24.0583229064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7156581878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9320793151855</t>
   </si>
   <si>
     <t xml:space="preserve">23.8599376678467</t>
@@ -779,13 +779,13 @@
     <t xml:space="preserve">23.8058319091797</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5082588195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9942722320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4802799224854</t>
+    <t xml:space="preserve">23.5082626342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.994270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4802780151367</t>
   </si>
   <si>
     <t xml:space="preserve">22.5434036254883</t>
@@ -803,16 +803,16 @@
     <t xml:space="preserve">22.0023612976074</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1827125549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7237510681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.36305809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2097587585449</t>
+    <t xml:space="preserve">22.182710647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7237491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3630542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2097606658936</t>
   </si>
   <si>
     <t xml:space="preserve">21.4883728027344</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">21.9212055206299</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8761196136475</t>
+    <t xml:space="preserve">21.8761177062988</t>
   </si>
   <si>
     <t xml:space="preserve">21.7047901153564</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9392375946045</t>
+    <t xml:space="preserve">21.9392414093018</t>
   </si>
   <si>
     <t xml:space="preserve">22.0745010375977</t>
@@ -836,10 +836,10 @@
     <t xml:space="preserve">22.299934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8139209747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3179683685303</t>
+    <t xml:space="preserve">22.8139247894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3179702758789</t>
   </si>
   <si>
     <t xml:space="preserve">22.1917266845703</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">22.354040145874</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5253658294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6065235137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6335754394531</t>
+    <t xml:space="preserve">22.5253677368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6065254211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6335773468018</t>
   </si>
   <si>
     <t xml:space="preserve">22.2458305358887</t>
@@ -866,25 +866,25 @@
     <t xml:space="preserve">22.128604888916</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0835189819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2007427215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.137622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1466369628906</t>
+    <t xml:space="preserve">22.083517074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2007465362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1376190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1466388702393</t>
   </si>
   <si>
     <t xml:space="preserve">21.5965805053711</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3260593414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5605144500732</t>
+    <t xml:space="preserve">21.326057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5605125427246</t>
   </si>
   <si>
     <t xml:space="preserve">22.0294132232666</t>
@@ -893,28 +893,28 @@
     <t xml:space="preserve">21.6867542266846</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2368106842041</t>
+    <t xml:space="preserve">22.2368125915527</t>
   </si>
   <si>
     <t xml:space="preserve">22.3720741271973</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3991241455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6155452728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6606273651123</t>
+    <t xml:space="preserve">22.3991260528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6155414581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6606292724609</t>
   </si>
   <si>
     <t xml:space="preserve">23.0123062133789</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5193881988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2704563140869</t>
+    <t xml:space="preserve">23.5193862915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2704582214355</t>
   </si>
   <si>
     <t xml:space="preserve">24.1739845275879</t>
@@ -923,67 +923,67 @@
     <t xml:space="preserve">24.7087249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7732639312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.243465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8150844573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7966461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6860103607178</t>
+    <t xml:space="preserve">24.7732677459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2434673309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8150863647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7966480255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6860122680664</t>
   </si>
   <si>
     <t xml:space="preserve">25.667573928833</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0086994171143</t>
+    <t xml:space="preserve">26.0087013244629</t>
   </si>
   <si>
     <t xml:space="preserve">25.888843536377</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9810447692871</t>
+    <t xml:space="preserve">25.9810409545898</t>
   </si>
   <si>
     <t xml:space="preserve">26.0916748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9072856903076</t>
+    <t xml:space="preserve">25.907283782959</t>
   </si>
   <si>
     <t xml:space="preserve">25.8058662414551</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9533805847168</t>
+    <t xml:space="preserve">25.9533843994141</t>
   </si>
   <si>
     <t xml:space="preserve">25.6767921447754</t>
   </si>
   <si>
-    <t xml:space="preserve">25.658353805542</t>
+    <t xml:space="preserve">25.6583499908447</t>
   </si>
   <si>
     <t xml:space="preserve">25.0775127410889</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4001998901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.261905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3264465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8009262084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4186401367188</t>
+    <t xml:space="preserve">25.4002017974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2619075775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3264427185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8009204864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.418643951416</t>
   </si>
   <si>
     <t xml:space="preserve">24.6441879272461</t>
@@ -1001,58 +1001,55 @@
     <t xml:space="preserve">23.187479019165</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9754295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1229457855225</t>
+    <t xml:space="preserve">22.9754257202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1229419708252</t>
   </si>
   <si>
     <t xml:space="preserve">23.2335777282715</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9938678741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0123043060303</t>
+    <t xml:space="preserve">22.9938659667969</t>
   </si>
   <si>
     <t xml:space="preserve">22.7818145751953</t>
   </si>
   <si>
-    <t xml:space="preserve">22.671178817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4960021972656</t>
+    <t xml:space="preserve">22.6711769104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4960060119629</t>
   </si>
   <si>
     <t xml:space="preserve">22.7264976501465</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5052242279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3208293914795</t>
+    <t xml:space="preserve">22.5052223205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3208274841309</t>
   </si>
   <si>
     <t xml:space="preserve">22.5882015228271</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1137237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.910888671875</t>
+    <t xml:space="preserve">23.1137218475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9108867645264</t>
   </si>
   <si>
     <t xml:space="preserve">23.3995323181152</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7775402069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6208057403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.14137840271</t>
+    <t xml:space="preserve">23.7775382995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6208038330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1413822174072</t>
   </si>
   <si>
     <t xml:space="preserve">22.9846458435059</t>
@@ -1064,31 +1061,31 @@
     <t xml:space="preserve">22.7357158660889</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6896190643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3257732391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7406578063965</t>
+    <t xml:space="preserve">22.6896171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3257751464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7406597137451</t>
   </si>
   <si>
     <t xml:space="preserve">23.9803733825684</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9711532592773</t>
+    <t xml:space="preserve">23.9711513519287</t>
   </si>
   <si>
     <t xml:space="preserve">24.0633487701416</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2477416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3860416412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1555461883545</t>
+    <t xml:space="preserve">24.2477436065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3860378265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1555442810059</t>
   </si>
   <si>
     <t xml:space="preserve">24.6165313720703</t>
@@ -1097,16 +1094,16 @@
     <t xml:space="preserve">25.8611850738525</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6306915283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2158069610596</t>
+    <t xml:space="preserve">25.6306934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2158088684082</t>
   </si>
   <si>
     <t xml:space="preserve">25.1697101593018</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3080043792725</t>
+    <t xml:space="preserve">25.3080062866211</t>
   </si>
   <si>
     <t xml:space="preserve">25.4462985992432</t>
@@ -1115,88 +1112,88 @@
     <t xml:space="preserve">25.5384960174561</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1236133575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4321365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6484622955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0172500610352</t>
+    <t xml:space="preserve">25.1236095428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4321346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6484642028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0172519683838</t>
   </si>
   <si>
     <t xml:space="preserve">24.109447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3399391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2016448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2938423156738</t>
+    <t xml:space="preserve">24.339937210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2016429901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2938404083252</t>
   </si>
   <si>
     <t xml:space="preserve">24.754825592041</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6626281738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.985315322876</t>
+    <t xml:space="preserve">24.6626262664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9853172302246</t>
   </si>
   <si>
     <t xml:space="preserve">25.4923973083496</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7228927612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5704307556152</t>
+    <t xml:space="preserve">25.7228908538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5704326629639</t>
   </si>
   <si>
     <t xml:space="preserve">25.5845947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9994812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.414363861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.566822052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7512168884277</t>
+    <t xml:space="preserve">25.9994831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4143657684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5668239593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.751220703125</t>
   </si>
   <si>
     <t xml:space="preserve">28.0739059448242</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5207271575928</t>
+    <t xml:space="preserve">27.5207252502441</t>
   </si>
   <si>
     <t xml:space="preserve">26.7370529174805</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5065650939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0314121246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5243320465088</t>
+    <t xml:space="preserve">26.5065612792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0314140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5243339538574</t>
   </si>
   <si>
     <t xml:space="preserve">26.3682670593262</t>
   </si>
   <si>
-    <t xml:space="preserve">26.598762512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4604663848877</t>
+    <t xml:space="preserve">26.5987606048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4604644775391</t>
   </si>
   <si>
     <t xml:space="preserve">26.2299728393555</t>
@@ -1211,22 +1208,22 @@
     <t xml:space="preserve">26.2760696411133</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2902336120605</t>
+    <t xml:space="preserve">27.2902355194092</t>
   </si>
   <si>
     <t xml:space="preserve">27.3824329376221</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4746265411377</t>
+    <t xml:space="preserve">27.4746284484863</t>
   </si>
   <si>
     <t xml:space="preserve">26.552661895752</t>
   </si>
   <si>
-    <t xml:space="preserve">26.829252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1058406829834</t>
+    <t xml:space="preserve">26.8292503356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.105842590332</t>
   </si>
   <si>
     <t xml:space="preserve">26.8753490447998</t>
@@ -1235,31 +1232,31 @@
     <t xml:space="preserve">27.8434143066406</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7653865814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5809898376465</t>
+    <t xml:space="preserve">28.7653827667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5809879302979</t>
   </si>
   <si>
     <t xml:space="preserve">27.9356117248535</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8114814758301</t>
+    <t xml:space="preserve">28.8114795684814</t>
   </si>
   <si>
     <t xml:space="preserve">28.1661033630371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7192859649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1200065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0597457885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9675464630127</t>
+    <t xml:space="preserve">28.7192821502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1200046539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0597438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9675445556641</t>
   </si>
   <si>
     <t xml:space="preserve">27.1519412994385</t>
@@ -1280,40 +1277,43 @@
     <t xml:space="preserve">26.9214477539062</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1828784942627</t>
+    <t xml:space="preserve">26.1828804016113</t>
   </si>
   <si>
     <t xml:space="preserve">26.0886974334717</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4654312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8061466217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7119655609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1468696594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3352355957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.911413192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4875869750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3934001922607</t>
+    <t xml:space="preserve">26.4654273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2299709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8061485290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7119617462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1468677520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3352317810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9114112854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.487585067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3934020996094</t>
   </si>
   <si>
     <t xml:space="preserve">23.9224872589111</t>
   </si>
   <si>
-    <t xml:space="preserve">23.263204574585</t>
+    <t xml:space="preserve">23.2632064819336</t>
   </si>
   <si>
     <t xml:space="preserve">23.0277500152588</t>
@@ -1325,28 +1325,28 @@
     <t xml:space="preserve">22.7451992034912</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6039257049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5097427368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4155597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1801013946533</t>
+    <t xml:space="preserve">22.6039237976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5097408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4155559539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.180103302002</t>
   </si>
   <si>
     <t xml:space="preserve">22.0388278961182</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8504600524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4626502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2271957397461</t>
+    <t xml:space="preserve">21.8504619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4626522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2271919250488</t>
   </si>
   <si>
     <t xml:space="preserve">23.4044799804688</t>
@@ -1361,85 +1361,85 @@
     <t xml:space="preserve">23.498664855957</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5568370819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1330089569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6620960235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1911792755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0028114318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.096996307373</t>
+    <t xml:space="preserve">22.5568351745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1330070495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6620941162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1911849975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.002815246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0969982147217</t>
   </si>
   <si>
     <t xml:space="preserve">20.8615398406982</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3795471191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4737281799316</t>
+    <t xml:space="preserve">21.379545211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4737300872803</t>
   </si>
   <si>
     <t xml:space="preserve">22.274284362793</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7562808990479</t>
+    <t xml:space="preserve">21.7562770843506</t>
   </si>
   <si>
     <t xml:space="preserve">21.9446430206299</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5679111480713</t>
+    <t xml:space="preserve">21.5679130554199</t>
   </si>
   <si>
     <t xml:space="preserve">21.5208206176758</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3324527740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2382717132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8393840789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7922916412354</t>
+    <t xml:space="preserve">21.3324565887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2382698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8393821716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.792293548584</t>
   </si>
   <si>
     <t xml:space="preserve">23.5457553863525</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6399364471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7341213226318</t>
+    <t xml:space="preserve">23.6399383544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7341232299805</t>
   </si>
   <si>
     <t xml:space="preserve">23.6870288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">23.781213760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0166721343994</t>
+    <t xml:space="preserve">23.7812156677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0166683197021</t>
   </si>
   <si>
     <t xml:space="preserve">24.2992191314697</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1579437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2521266937256</t>
+    <t xml:space="preserve">24.1579456329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2521286010742</t>
   </si>
   <si>
     <t xml:space="preserve">24.7230434417725</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">24.6288604736328</t>
   </si>
   <si>
-    <t xml:space="preserve">24.675952911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5817680358887</t>
+    <t xml:space="preserve">24.6759510040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5817699432373</t>
   </si>
   <si>
     <t xml:space="preserve">24.770133972168</t>
@@ -1460,22 +1460,22 @@
     <t xml:space="preserve">24.9585018157959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9003295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7590560913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9474201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2770652770996</t>
+    <t xml:space="preserve">25.9003314971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7590579986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9474220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.277063369751</t>
   </si>
   <si>
     <t xml:space="preserve">26.9363441467285</t>
   </si>
   <si>
-    <t xml:space="preserve">26.983434677124</t>
+    <t xml:space="preserve">26.9834365844727</t>
   </si>
   <si>
     <t xml:space="preserve">26.8421611785889</t>
@@ -1490,34 +1490,34 @@
     <t xml:space="preserve">27.4543514251709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5014419555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3130760192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0776214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7008857727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6537933349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6067047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9945125579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1357879638672</t>
+    <t xml:space="preserve">27.501443862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3130741119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0776176452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7008876800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6537952423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6067028045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.994514465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1357917785645</t>
   </si>
   <si>
     <t xml:space="preserve">26.0416049957275</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6177825927734</t>
+    <t xml:space="preserve">25.6177806854248</t>
   </si>
   <si>
     <t xml:space="preserve">25.4294166564941</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">25.0997753143311</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8643188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4404945373535</t>
+    <t xml:space="preserve">24.864315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4404964447021</t>
   </si>
   <si>
     <t xml:space="preserve">25.5235977172852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.371244430542</t>
+    <t xml:space="preserve">26.3712463378906</t>
   </si>
   <si>
     <t xml:space="preserve">26.3241558074951</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">26.7950706481934</t>
   </si>
   <si>
-    <t xml:space="preserve">26.889253616333</t>
+    <t xml:space="preserve">26.8892517089844</t>
   </si>
   <si>
     <t xml:space="preserve">27.0305290222168</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1718044281006</t>
+    <t xml:space="preserve">27.171802520752</t>
   </si>
   <si>
     <t xml:space="preserve">27.5485343933105</t>
@@ -1562,22 +1562,22 @@
     <t xml:space="preserve">27.6898078918457</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1136322021484</t>
+    <t xml:space="preserve">28.1136341094971</t>
   </si>
   <si>
     <t xml:space="preserve">28.3961811065674</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7258224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9141864776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9502010345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7618350982666</t>
+    <t xml:space="preserve">28.7258243560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9141883850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9501991271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7618370056152</t>
   </si>
   <si>
     <t xml:space="preserve">30.3269348144531</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">31.504222869873</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6925888061523</t>
+    <t xml:space="preserve">31.6925868988037</t>
   </si>
   <si>
     <t xml:space="preserve">32.4460487365723</t>
@@ -1598,10 +1598,10 @@
     <t xml:space="preserve">32.4931411743164</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4820671081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6704330444336</t>
+    <t xml:space="preserve">33.4820709228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6704292297363</t>
   </si>
   <si>
     <t xml:space="preserve">33.293701171875</t>
@@ -1613,25 +1613,25 @@
     <t xml:space="preserve">33.9058876037598</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2466049194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8698768615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1524238586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.058235168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5873184204102</t>
+    <t xml:space="preserve">33.2466087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.869873046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1524200439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0582427978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5873222351074</t>
   </si>
   <si>
     <t xml:space="preserve">32.3047752380371</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9280433654785</t>
+    <t xml:space="preserve">31.9280414581299</t>
   </si>
   <si>
     <t xml:space="preserve">31.4571285247803</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">30.8920307159424</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0803985595703</t>
+    <t xml:space="preserve">31.0804023742676</t>
   </si>
   <si>
     <t xml:space="preserve">31.0333080291748</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">30.6094818115234</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2687606811523</t>
+    <t xml:space="preserve">31.2687664031982</t>
   </si>
   <si>
     <t xml:space="preserve">30.986213684082</t>
@@ -1664,52 +1664,52 @@
     <t xml:space="preserve">31.4100379943848</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8449382781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.17458152771</t>
+    <t xml:space="preserve">30.8449420928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1745758056641</t>
   </si>
   <si>
     <t xml:space="preserve">31.8809509277344</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0222244262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7396812438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.000072479248</t>
+    <t xml:space="preserve">32.0222320556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7396755218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0000686645508</t>
   </si>
   <si>
     <t xml:space="preserve">34.4709892272949</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7895469665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5901069641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7784729003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1552047729492</t>
+    <t xml:space="preserve">35.78955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5901031494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7784652709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.155200958252</t>
   </si>
   <si>
     <t xml:space="preserve">37.6732063293457</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0846748352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2282104492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.367000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7976036071777</t>
+    <t xml:space="preserve">38.0846786499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2282066345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3669967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.797607421875</t>
   </si>
   <si>
     <t xml:space="preserve">38.1803665161133</t>
@@ -1721,16 +1721,16 @@
     <t xml:space="preserve">37.9411430358887</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9889907836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8454475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3191604614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8501930236816</t>
+    <t xml:space="preserve">37.9889869689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8454513549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3191566467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8502006530762</t>
   </si>
   <si>
     <t xml:space="preserve">38.7545051574707</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">39.0415802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8023529052734</t>
+    <t xml:space="preserve">38.8023490905762</t>
   </si>
   <si>
     <t xml:space="preserve">38.4674377441406</t>
@@ -1754,28 +1754,28 @@
     <t xml:space="preserve">38.8980445861816</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7066612243652</t>
+    <t xml:space="preserve">38.7066650390625</t>
   </si>
   <si>
     <t xml:space="preserve">38.2760543823242</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5631294250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4195976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3764953613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1372680664062</t>
+    <t xml:space="preserve">38.5631256103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4195899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3764915466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1372718811035</t>
   </si>
   <si>
     <t xml:space="preserve">39.1851119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2807998657227</t>
+    <t xml:space="preserve">39.2808036804199</t>
   </si>
   <si>
     <t xml:space="preserve">39.9027900695801</t>
@@ -1787,91 +1787,91 @@
     <t xml:space="preserve">42.1036643981934</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5342674255371</t>
+    <t xml:space="preserve">42.5342712402344</t>
   </si>
   <si>
     <t xml:space="preserve">41.6730537414551</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8118438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7161560058594</t>
+    <t xml:space="preserve">40.8118515014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7161521911621</t>
   </si>
   <si>
     <t xml:space="preserve">41.912281036377</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0605659484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4911651611328</t>
+    <t xml:space="preserve">43.0605697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4911727905273</t>
   </si>
   <si>
     <t xml:space="preserve">44.2566909790039</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7829895019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4433288574219</t>
+    <t xml:space="preserve">44.7829856872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4433250427246</t>
   </si>
   <si>
     <t xml:space="preserve">44.017463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6347007751465</t>
+    <t xml:space="preserve">43.634708404541</t>
   </si>
   <si>
     <t xml:space="preserve">43.2041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9170227050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9265251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4049758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2614364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5963516235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6536903381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8976593017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6105880737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1847381591797</t>
+    <t xml:space="preserve">42.9170303344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9265213012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.404972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2614326477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5963554382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6536865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8976631164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6105918884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1847343444824</t>
   </si>
   <si>
     <t xml:space="preserve">48.993350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7588729858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2804222106934</t>
+    <t xml:space="preserve">49.7588691711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2804260253906</t>
   </si>
   <si>
     <t xml:space="preserve">49.6631851196289</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3761100769043</t>
+    <t xml:space="preserve">49.3761138916016</t>
   </si>
   <si>
     <t xml:space="preserve">49.5674896240234</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6200828552246</t>
+    <t xml:space="preserve">50.6200866699219</t>
   </si>
   <si>
     <t xml:space="preserve">51.0028457641602</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">51.6726760864258</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4192085266113</t>
+    <t xml:space="preserve">48.4192047119141</t>
   </si>
   <si>
     <t xml:space="preserve">48.3235244750977</t>
@@ -1913,16 +1913,16 @@
     <t xml:space="preserve">50.4287071228027</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5338859558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0649337768555</t>
+    <t xml:space="preserve">52.5338897705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0649261474609</t>
   </si>
   <si>
     <t xml:space="preserve">53.2994079589844</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4381942749023</t>
+    <t xml:space="preserve">52.4381980895996</t>
   </si>
   <si>
     <t xml:space="preserve">47.3666191101074</t>
@@ -1934,70 +1934,70 @@
     <t xml:space="preserve">46.3618774414062</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7398872375488</t>
+    <t xml:space="preserve">45.7398834228516</t>
   </si>
   <si>
     <t xml:space="preserve">44.9743614196777</t>
   </si>
   <si>
-    <t xml:space="preserve">43.586856842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7687492370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6493263244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5967330932617</t>
+    <t xml:space="preserve">43.5868606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7687454223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6493225097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.596736907959</t>
   </si>
   <si>
     <t xml:space="preserve">30.0945510864258</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4820575714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1854934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5299034118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0992965698242</t>
+    <t xml:space="preserve">31.4820556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1854953765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5299053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0992946624756</t>
   </si>
   <si>
     <t xml:space="preserve">30.3816204071045</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9269027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.410099029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5010414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3096618652344</t>
+    <t xml:space="preserve">34.9268989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4100952148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5010375976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3096656799316</t>
   </si>
   <si>
     <t xml:space="preserve">34.5441398620605</t>
   </si>
   <si>
-    <t xml:space="preserve">35.070442199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0799331665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2234687805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1277694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2329559326172</t>
+    <t xml:space="preserve">35.0704383850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0799255371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.223461151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1277770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2329597473145</t>
   </si>
   <si>
     <t xml:space="preserve">40.429084777832</t>
@@ -2006,16 +2006,16 @@
     <t xml:space="preserve">39.998477935791</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7351417541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9791107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4528198242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0700531005859</t>
+    <t xml:space="preserve">44.7351379394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9791145324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4528160095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0700569152832</t>
   </si>
   <si>
     <t xml:space="preserve">45.3571281433105</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">46.4575614929199</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6441955566406</t>
+    <t xml:space="preserve">45.6441993713379</t>
   </si>
   <si>
     <t xml:space="preserve">44.8786773681641</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">45.3092803955078</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1657485961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2088470458984</t>
+    <t xml:space="preserve">45.1657447814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2088432312012</t>
   </si>
   <si>
     <t xml:space="preserve">43.15625</t>
@@ -2054,40 +2054,40 @@
     <t xml:space="preserve">42.5821151733398</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0222129821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5485038757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5101585388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7015380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7062835693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9407577514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5149040222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4813003540039</t>
+    <t xml:space="preserve">45.0222053527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5485000610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5101547241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7015342712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7062797546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9407615661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5149002075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4812927246094</t>
   </si>
   <si>
     <t xml:space="preserve">51.1942253112793</t>
   </si>
   <si>
-    <t xml:space="preserve">51.768367767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.289909362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1080284118652</t>
+    <t xml:space="preserve">51.7683639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2899131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1080322265625</t>
   </si>
   <si>
     <t xml:space="preserve">53.9692420959473</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">55.1175231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6916656494141</t>
+    <t xml:space="preserve">55.6916618347168</t>
   </si>
   <si>
     <t xml:space="preserve">55.5002784729004</t>
@@ -2111,37 +2111,37 @@
     <t xml:space="preserve">54.6390686035156</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8304481506348</t>
+    <t xml:space="preserve">54.830451965332</t>
   </si>
   <si>
     <t xml:space="preserve">55.4045944213867</t>
   </si>
   <si>
-    <t xml:space="preserve">56.744255065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9356346130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1270141601562</t>
+    <t xml:space="preserve">56.7442512512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9356384277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1270179748535</t>
   </si>
   <si>
     <t xml:space="preserve">56.2658042907715</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9787292480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3183937072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6580543518066</t>
+    <t xml:space="preserve">55.9787368774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3183975219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6580581665039</t>
   </si>
   <si>
     <t xml:space="preserve">57.2227058410645</t>
   </si>
   <si>
-    <t xml:space="preserve">57.7011528015137</t>
+    <t xml:space="preserve">57.7011566162109</t>
   </si>
   <si>
     <t xml:space="preserve">56.3614959716797</t>
@@ -2150,31 +2150,31 @@
     <t xml:space="preserve">57.988224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">58.849437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.3373794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.442569732666</t>
+    <t xml:space="preserve">58.8494338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.3373756408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4425659179688</t>
   </si>
   <si>
     <t xml:space="preserve">62.2942810058594</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3468742370605</t>
+    <t xml:space="preserve">63.3468627929688</t>
   </si>
   <si>
     <t xml:space="preserve">63.7296295166016</t>
   </si>
   <si>
-    <t xml:space="preserve">63.6339454650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3037643432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5908432006836</t>
+    <t xml:space="preserve">63.6339416503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3037719726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5908508300781</t>
   </si>
   <si>
     <t xml:space="preserve">65.9305038452148</t>
@@ -2183,10 +2183,10 @@
     <t xml:space="preserve">66.6960296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">65.3563766479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.9830932617188</t>
+    <t xml:space="preserve">65.3563690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9831008911133</t>
   </si>
   <si>
     <t xml:space="preserve">67.1744766235352</t>
@@ -2195,22 +2195,22 @@
     <t xml:space="preserve">66.5046463012695</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8443145751953</t>
+    <t xml:space="preserve">67.8443069458008</t>
   </si>
   <si>
     <t xml:space="preserve">70.0451889038086</t>
   </si>
   <si>
-    <t xml:space="preserve">69.1839752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.2891616821289</t>
+    <t xml:space="preserve">69.1839828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.2891540527344</t>
   </si>
   <si>
     <t xml:space="preserve">70.8107070922852</t>
   </si>
   <si>
-    <t xml:space="preserve">70.6193237304688</t>
+    <t xml:space="preserve">70.6193313598633</t>
   </si>
   <si>
     <t xml:space="preserve">71.7676010131836</t>
@@ -2219,10 +2219,10 @@
     <t xml:space="preserve">72.0546798706055</t>
   </si>
   <si>
-    <t xml:space="preserve">71.002082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.4710388183594</t>
+    <t xml:space="preserve">71.0020751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.4710311889648</t>
   </si>
   <si>
     <t xml:space="preserve">68.9925918579102</t>
@@ -2240,31 +2240,31 @@
     <t xml:space="preserve">76.5521087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7003860473633</t>
+    <t xml:space="preserve">77.7004013061523</t>
   </si>
   <si>
     <t xml:space="preserve">75.8822860717773</t>
   </si>
   <si>
-    <t xml:space="preserve">74.734001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.8727798461914</t>
+    <t xml:space="preserve">74.7339935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.8727874755859</t>
   </si>
   <si>
     <t xml:space="preserve">74.8296890258789</t>
   </si>
   <si>
-    <t xml:space="preserve">77.8917770385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.2745361328125</t>
+    <t xml:space="preserve">77.8917694091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.274543762207</t>
   </si>
   <si>
     <t xml:space="preserve">77.7960891723633</t>
   </si>
   <si>
-    <t xml:space="preserve">79.4228210449219</t>
+    <t xml:space="preserve">79.4228134155273</t>
   </si>
   <si>
     <t xml:space="preserve">80.7624816894531</t>
@@ -2273,28 +2273,28 @@
     <t xml:space="preserve">82.0064468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">81.5279998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.910758972168</t>
+    <t xml:space="preserve">81.5279922485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9107666015625</t>
   </si>
   <si>
     <t xml:space="preserve">82.3892059326172</t>
   </si>
   <si>
-    <t xml:space="preserve">81.4323120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.1452407836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4754028320312</t>
+    <t xml:space="preserve">81.4323043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1452484130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4754104614258</t>
   </si>
   <si>
     <t xml:space="preserve">81.7193832397461</t>
   </si>
   <si>
-    <t xml:space="preserve">81.815071105957</t>
+    <t xml:space="preserve">81.8150634765625</t>
   </si>
   <si>
     <t xml:space="preserve">83.3461074829102</t>
@@ -2306,13 +2306,13 @@
     <t xml:space="preserve">82.7719802856445</t>
   </si>
   <si>
-    <t xml:space="preserve">82.2935180664062</t>
+    <t xml:space="preserve">82.2935256958008</t>
   </si>
   <si>
     <t xml:space="preserve">77.0305557250977</t>
   </si>
   <si>
-    <t xml:space="preserve">79.3271331787109</t>
+    <t xml:space="preserve">79.3271255493164</t>
   </si>
   <si>
     <t xml:space="preserve">83.728874206543</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">76.7434844970703</t>
   </si>
   <si>
-    <t xml:space="preserve">79.5185165405273</t>
+    <t xml:space="preserve">79.5185012817383</t>
   </si>
   <si>
     <t xml:space="preserve">79.8055801391602</t>
@@ -2333,19 +2333,19 @@
     <t xml:space="preserve">82.4849014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3797149658203</t>
+    <t xml:space="preserve">80.3797225952148</t>
   </si>
   <si>
     <t xml:space="preserve">78.6572875976562</t>
   </si>
   <si>
-    <t xml:space="preserve">78.4659118652344</t>
+    <t xml:space="preserve">78.4659194946289</t>
   </si>
   <si>
     <t xml:space="preserve">84.6857757568359</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3555908203125</t>
+    <t xml:space="preserve">85.3556060791016</t>
   </si>
   <si>
     <t xml:space="preserve">83.0590438842773</t>
@@ -2354,10 +2354,10 @@
     <t xml:space="preserve">85.9297485351562</t>
   </si>
   <si>
-    <t xml:space="preserve">87.173713684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.269401550293</t>
+    <t xml:space="preserve">87.1737213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.269416809082</t>
   </si>
   <si>
     <t xml:space="preserve">88.3219985961914</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">86.7909545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">90.9056396484375</t>
+    <t xml:space="preserve">90.905632019043</t>
   </si>
   <si>
     <t xml:space="preserve">91.3840866088867</t>
@@ -2375,25 +2375,25 @@
     <t xml:space="preserve">93.1065063476562</t>
   </si>
   <si>
-    <t xml:space="preserve">95.8815155029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.2211761474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.474639892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.622932434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.240165710449</t>
+    <t xml:space="preserve">95.8815231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.2211837768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.474647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.622917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.240173339844</t>
   </si>
   <si>
     <t xml:space="preserve">97.986701965332</t>
   </si>
   <si>
-    <t xml:space="preserve">98.5608444213867</t>
+    <t xml:space="preserve">98.5608520507812</t>
   </si>
   <si>
     <t xml:space="preserve">99.900505065918</t>
@@ -2402,13 +2402,13 @@
     <t xml:space="preserve">96.2642822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">95.6901473999023</t>
+    <t xml:space="preserve">95.6901397705078</t>
   </si>
   <si>
     <t xml:space="preserve">94.8289260864258</t>
   </si>
   <si>
-    <t xml:space="preserve">95.3073806762695</t>
+    <t xml:space="preserve">95.307373046875</t>
   </si>
   <si>
     <t xml:space="preserve">94.2547912597656</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">94.446159362793</t>
   </si>
   <si>
-    <t xml:space="preserve">97.0298080444336</t>
+    <t xml:space="preserve">97.0298004150391</t>
   </si>
   <si>
     <t xml:space="preserve">94.5418548583984</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">94.1591033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8720245361328</t>
+    <t xml:space="preserve">93.8720321655273</t>
   </si>
   <si>
     <t xml:space="preserve">94.0634155273438</t>
@@ -2435,13 +2435,13 @@
     <t xml:space="preserve">93.3935699462891</t>
   </si>
   <si>
-    <t xml:space="preserve">93.6806564331055</t>
+    <t xml:space="preserve">93.6806488037109</t>
   </si>
   <si>
     <t xml:space="preserve">92.9151229858398</t>
   </si>
   <si>
-    <t xml:space="preserve">93.2978820800781</t>
+    <t xml:space="preserve">93.2978897094727</t>
   </si>
   <si>
     <t xml:space="preserve">92.7237548828125</t>
@@ -2450,25 +2450,25 @@
     <t xml:space="preserve">94.3504867553711</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6039505004883</t>
+    <t xml:space="preserve">97.6039352416992</t>
   </si>
   <si>
     <t xml:space="preserve">101.431549072266</t>
   </si>
   <si>
-    <t xml:space="preserve">104.876388549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.493629455566</t>
+    <t xml:space="preserve">104.876396179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.493621826172</t>
   </si>
   <si>
     <t xml:space="preserve">106.598815917969</t>
   </si>
   <si>
-    <t xml:space="preserve">107.364334106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.66089630127</t>
+    <t xml:space="preserve">107.36434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.660903930664</t>
   </si>
   <si>
     <t xml:space="preserve">110.235046386719</t>
@@ -2477,19 +2477,19 @@
     <t xml:space="preserve">105.64192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">106.21605682373</t>
+    <t xml:space="preserve">106.216064453125</t>
   </si>
   <si>
     <t xml:space="preserve">107.938484191895</t>
   </si>
   <si>
-    <t xml:space="preserve">107.555725097656</t>
+    <t xml:space="preserve">107.555717468262</t>
   </si>
   <si>
     <t xml:space="preserve">109.469520568848</t>
   </si>
   <si>
-    <t xml:space="preserve">107.747100830078</t>
+    <t xml:space="preserve">107.747108459473</t>
   </si>
   <si>
     <t xml:space="preserve">108.703994750977</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">102.197074890137</t>
   </si>
   <si>
-    <t xml:space="preserve">99.5177459716797</t>
+    <t xml:space="preserve">99.5177383422852</t>
   </si>
   <si>
     <t xml:space="preserve">99.7091293334961</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">103.345352172852</t>
   </si>
   <si>
-    <t xml:space="preserve">103.536735534668</t>
+    <t xml:space="preserve">103.536727905273</t>
   </si>
   <si>
     <t xml:space="preserve">106.024673461914</t>
@@ -2516,22 +2516,22 @@
     <t xml:space="preserve">106.981582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">108.51261138916</t>
+    <t xml:space="preserve">108.512626647949</t>
   </si>
   <si>
     <t xml:space="preserve">105.833290100098</t>
   </si>
   <si>
-    <t xml:space="preserve">101.048789978027</t>
+    <t xml:space="preserve">101.048782348633</t>
   </si>
   <si>
     <t xml:space="preserve">102.388450622559</t>
   </si>
   <si>
-    <t xml:space="preserve">103.153968811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.962600708008</t>
+    <t xml:space="preserve">103.15397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.962585449219</t>
   </si>
   <si>
     <t xml:space="preserve">105.450538635254</t>
@@ -2543,22 +2543,22 @@
     <t xml:space="preserve">103.919486999512</t>
   </si>
   <si>
-    <t xml:space="preserve">106.407440185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.086769104004</t>
+    <t xml:space="preserve">106.407432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.086761474609</t>
   </si>
   <si>
     <t xml:space="preserve">110.809188842773</t>
   </si>
   <si>
-    <t xml:space="preserve">113.679893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.043670654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.172950744629</t>
+    <t xml:space="preserve">113.679885864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.043663024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.172958374023</t>
   </si>
   <si>
     <t xml:space="preserve">111.000556945801</t>
@@ -2567,28 +2567,28 @@
     <t xml:space="preserve">112.914360046387</t>
   </si>
   <si>
-    <t xml:space="preserve">109.852279663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.426429748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.383331298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.340225219727</t>
+    <t xml:space="preserve">109.85228729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.426422119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.383323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.340232849121</t>
   </si>
   <si>
     <t xml:space="preserve">114.445411682129</t>
   </si>
   <si>
-    <t xml:space="preserve">113.29712677002</t>
+    <t xml:space="preserve">113.297134399414</t>
   </si>
   <si>
     <t xml:space="preserve">112.722991943359</t>
   </si>
   <si>
-    <t xml:space="preserve">115.019554138184</t>
+    <t xml:space="preserve">115.019546508789</t>
   </si>
   <si>
     <t xml:space="preserve">115.593688964844</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">115.210929870605</t>
   </si>
   <si>
-    <t xml:space="preserve">116.741973876953</t>
+    <t xml:space="preserve">116.741981506348</t>
   </si>
   <si>
     <t xml:space="preserve">116.167839050293</t>
@@ -2606,16 +2606,16 @@
     <t xml:space="preserve">115.78507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">116.550590515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.804046630859</t>
+    <t xml:space="preserve">116.550598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.804054260254</t>
   </si>
   <si>
     <t xml:space="preserve">120.186813354492</t>
   </si>
   <si>
-    <t xml:space="preserve">122.100608825684</t>
+    <t xml:space="preserve">122.100616455078</t>
   </si>
   <si>
     <t xml:space="preserve">122.866134643555</t>
@@ -2624,10 +2624,10 @@
     <t xml:space="preserve">123.631660461426</t>
   </si>
   <si>
-    <t xml:space="preserve">131.478256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.267890930176</t>
+    <t xml:space="preserve">131.478240966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.267883300781</t>
   </si>
   <si>
     <t xml:space="preserve">127.459259033203</t>
@@ -2636,19 +2636,19 @@
     <t xml:space="preserve">128.990310668945</t>
   </si>
   <si>
-    <t xml:space="preserve">132.052398681641</t>
+    <t xml:space="preserve">132.052383422852</t>
   </si>
   <si>
     <t xml:space="preserve">134.157577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">133.774826049805</t>
+    <t xml:space="preserve">133.774841308594</t>
   </si>
   <si>
     <t xml:space="preserve">132.626525878906</t>
   </si>
   <si>
-    <t xml:space="preserve">132.435134887695</t>
+    <t xml:space="preserve">132.435150146484</t>
   </si>
   <si>
     <t xml:space="preserve">134.923095703125</t>
@@ -2666,28 +2666,28 @@
     <t xml:space="preserve">131.86100769043</t>
   </si>
   <si>
-    <t xml:space="preserve">134.731735229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.262741088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.793792724609</t>
+    <t xml:space="preserve">134.731704711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.262756347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.793807983398</t>
   </si>
   <si>
     <t xml:space="preserve">138.176559448242</t>
   </si>
   <si>
-    <t xml:space="preserve">137.028289794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.559326171875</t>
+    <t xml:space="preserve">137.028274536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.559341430664</t>
   </si>
   <si>
     <t xml:space="preserve">139.898971557617</t>
   </si>
   <si>
-    <t xml:space="preserve">136.454132080078</t>
+    <t xml:space="preserve">136.454147338867</t>
   </si>
   <si>
     <t xml:space="preserve">138.750701904297</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">137.98518371582</t>
   </si>
   <si>
-    <t xml:space="preserve">135.49723815918</t>
+    <t xml:space="preserve">135.497253417969</t>
   </si>
   <si>
     <t xml:space="preserve">144.492111206055</t>
@@ -2711,13 +2711,13 @@
     <t xml:space="preserve">144.109359741211</t>
   </si>
   <si>
-    <t xml:space="preserve">142.195541381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.726577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.917984008789</t>
+    <t xml:space="preserve">142.195571899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.726593017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.917953491211</t>
   </si>
   <si>
     <t xml:space="preserve">144.683486938477</t>
@@ -2729,16 +2729,16 @@
     <t xml:space="preserve">147.936965942383</t>
   </si>
   <si>
-    <t xml:space="preserve">145.640396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.788665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.276641845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.999053955078</t>
+    <t xml:space="preserve">145.640380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.788681030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.276626586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.999038696289</t>
   </si>
   <si>
     <t xml:space="preserve">150.424896240234</t>
@@ -2747,22 +2747,22 @@
     <t xml:space="preserve">153.486968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">152.33869934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.400772094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.190414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.888732910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.037033081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.654266357422</t>
+    <t xml:space="preserve">152.338714599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.400802612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.1904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.888717651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.037002563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.654251098633</t>
   </si>
   <si>
     <t xml:space="preserve">159.61116027832</t>
@@ -2777,13 +2777,13 @@
     <t xml:space="preserve">163.438766479492</t>
   </si>
   <si>
-    <t xml:space="preserve">163.821517944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.606002807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.773315429688</t>
+    <t xml:space="preserve">163.821533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.606033325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">170.328460693359</t>
@@ -2795,19 +2795,19 @@
     <t xml:space="preserve">168.031890869141</t>
   </si>
   <si>
-    <t xml:space="preserve">165.352554321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.759429931641</t>
+    <t xml:space="preserve">165.352584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.75944519043</t>
   </si>
   <si>
     <t xml:space="preserve">162.099075317383</t>
   </si>
   <si>
-    <t xml:space="preserve">171.668090820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.074996948242</t>
+    <t xml:space="preserve">171.668121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.074981689453</t>
   </si>
   <si>
     <t xml:space="preserve">161.930511474609</t>
@@ -2819,19 +2819,19 @@
     <t xml:space="preserve">160.58430480957</t>
   </si>
   <si>
-    <t xml:space="preserve">159.045761108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.122360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.583602905273</t>
+    <t xml:space="preserve">159.045776367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.122375488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.583618164062</t>
   </si>
   <si>
     <t xml:space="preserve">147.314468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">150.391510009766</t>
+    <t xml:space="preserve">150.391540527344</t>
   </si>
   <si>
     <t xml:space="preserve">150.199203491211</t>
@@ -2846,19 +2846,19 @@
     <t xml:space="preserve">149.622268676758</t>
   </si>
   <si>
-    <t xml:space="preserve">155.199432373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.545669555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.968704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.430191040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.776611328125</t>
+    <t xml:space="preserve">155.199417114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.545654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.968688964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.43017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.776626586914</t>
   </si>
   <si>
     <t xml:space="preserve">166.353805541992</t>
@@ -2867,28 +2867,28 @@
     <t xml:space="preserve">170.200134277344</t>
   </si>
   <si>
-    <t xml:space="preserve">168.469284057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.430633544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.007583618164</t>
+    <t xml:space="preserve">168.469268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.430648803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.007598876953</t>
   </si>
   <si>
     <t xml:space="preserve">162.507461547852</t>
   </si>
   <si>
-    <t xml:space="preserve">163.469039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.584518432617</t>
+    <t xml:space="preserve">163.469055175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.584533691406</t>
   </si>
   <si>
     <t xml:space="preserve">161.161254882812</t>
   </si>
   <si>
-    <t xml:space="preserve">163.084426879883</t>
+    <t xml:space="preserve">163.084411621094</t>
   </si>
   <si>
     <t xml:space="preserve">161.738189697266</t>
@@ -2900,10 +2900,10 @@
     <t xml:space="preserve">177.508163452148</t>
   </si>
   <si>
-    <t xml:space="preserve">175.585006713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.392929077148</t>
+    <t xml:space="preserve">175.584991455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.392913818359</t>
   </si>
   <si>
     <t xml:space="preserve">180.777526855469</t>
@@ -2915,37 +2915,37 @@
     <t xml:space="preserve">179.815963745117</t>
   </si>
   <si>
-    <t xml:space="preserve">181.739120483398</t>
+    <t xml:space="preserve">181.739135742188</t>
   </si>
   <si>
     <t xml:space="preserve">185.008499145508</t>
   </si>
   <si>
-    <t xml:space="preserve">183.085342407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.508407592773</t>
+    <t xml:space="preserve">183.085311889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.508392333984</t>
   </si>
   <si>
     <t xml:space="preserve">168.276962280273</t>
   </si>
   <si>
-    <t xml:space="preserve">169.046249389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.584777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.507690429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.046447753906</t>
+    <t xml:space="preserve">169.046234130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.584747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.507705688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.046463012695</t>
   </si>
   <si>
     <t xml:space="preserve">170.96940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">169.623184204102</t>
+    <t xml:space="preserve">169.623168945312</t>
   </si>
   <si>
     <t xml:space="preserve">169.238540649414</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">175.008041381836</t>
   </si>
   <si>
-    <t xml:space="preserve">172.700256347656</t>
+    <t xml:space="preserve">172.700241088867</t>
   </si>
   <si>
     <t xml:space="preserve">172.123291015625</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">163.85368347168</t>
   </si>
   <si>
-    <t xml:space="preserve">166.738433837891</t>
+    <t xml:space="preserve">166.738418579102</t>
   </si>
   <si>
     <t xml:space="preserve">164.238327026367</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">166.546112060547</t>
   </si>
   <si>
-    <t xml:space="preserve">167.700012207031</t>
+    <t xml:space="preserve">167.699996948242</t>
   </si>
   <si>
     <t xml:space="preserve">165.392211914062</t>
@@ -2987,46 +2987,46 @@
     <t xml:space="preserve">151.160781860352</t>
   </si>
   <si>
-    <t xml:space="preserve">158.853454589844</t>
+    <t xml:space="preserve">158.853439331055</t>
   </si>
   <si>
     <t xml:space="preserve">158.468826293945</t>
   </si>
   <si>
-    <t xml:space="preserve">157.31494140625</t>
+    <t xml:space="preserve">157.314926147461</t>
   </si>
   <si>
     <t xml:space="preserve">159.815048217773</t>
   </si>
   <si>
-    <t xml:space="preserve">156.930282592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.161010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.314682006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.96826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.929840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.353088378906</t>
+    <t xml:space="preserve">156.930297851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.161026000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.314666748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.968246459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.929824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.353103637695</t>
   </si>
   <si>
     <t xml:space="preserve">153.468597412109</t>
   </si>
   <si>
-    <t xml:space="preserve">153.276260375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.122604370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.930053710938</t>
+    <t xml:space="preserve">153.276275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.122589111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.930068969727</t>
   </si>
   <si>
     <t xml:space="preserve">146.545181274414</t>
@@ -3047,13 +3047,13 @@
     <t xml:space="preserve">132.506088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">130.198272705078</t>
+    <t xml:space="preserve">130.198287963867</t>
   </si>
   <si>
     <t xml:space="preserve">134.813888549805</t>
   </si>
   <si>
-    <t xml:space="preserve">130.005966186523</t>
+    <t xml:space="preserve">130.005981445312</t>
   </si>
   <si>
     <t xml:space="preserve">130.775238037109</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">128.852081298828</t>
   </si>
   <si>
-    <t xml:space="preserve">129.621353149414</t>
+    <t xml:space="preserve">129.621337890625</t>
   </si>
   <si>
     <t xml:space="preserve">132.890716552734</t>
@@ -3071,34 +3071,34 @@
     <t xml:space="preserve">137.506317138672</t>
   </si>
   <si>
-    <t xml:space="preserve">136.160125732422</t>
+    <t xml:space="preserve">136.160110473633</t>
   </si>
   <si>
     <t xml:space="preserve">138.467895507812</t>
   </si>
   <si>
-    <t xml:space="preserve">135.583160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.813430786133</t>
+    <t xml:space="preserve">135.583145141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.813423156738</t>
   </si>
   <si>
     <t xml:space="preserve">118.659301757812</t>
   </si>
   <si>
-    <t xml:space="preserve">125.582702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.198066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.313995361328</t>
+    <t xml:space="preserve">125.582710266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.198059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.314010620117</t>
   </si>
   <si>
     <t xml:space="preserve">138.852523803711</t>
   </si>
   <si>
-    <t xml:space="preserve">142.891189575195</t>
+    <t xml:space="preserve">142.891174316406</t>
   </si>
   <si>
     <t xml:space="preserve">140.391067504883</t>
@@ -3110,10 +3110,10 @@
     <t xml:space="preserve">145.00666809082</t>
   </si>
   <si>
-    <t xml:space="preserve">145.775955200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.814361572266</t>
+    <t xml:space="preserve">145.775924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.814346313477</t>
   </si>
   <si>
     <t xml:space="preserve">148.27604675293</t>
@@ -3125,10 +3125,10 @@
     <t xml:space="preserve">142.602722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">142.698852539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.083511352539</t>
+    <t xml:space="preserve">142.698867797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.08349609375</t>
   </si>
   <si>
     <t xml:space="preserve">139.525650024414</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">140.198760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">139.910278320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.429473876953</t>
+    <t xml:space="preserve">139.910263061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.429489135742</t>
   </si>
   <si>
     <t xml:space="preserve">139.237167358398</t>
@@ -3152,43 +3152,43 @@
     <t xml:space="preserve">140.006439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">138.564056396484</t>
+    <t xml:space="preserve">138.564071655273</t>
   </si>
   <si>
     <t xml:space="preserve">143.179641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">142.314224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.871398925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.525177001953</t>
+    <t xml:space="preserve">142.314239501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.87141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.525192260742</t>
   </si>
   <si>
     <t xml:space="preserve">129.909820556641</t>
   </si>
   <si>
-    <t xml:space="preserve">133.371520996094</t>
+    <t xml:space="preserve">133.371505737305</t>
   </si>
   <si>
     <t xml:space="preserve">128.275115966797</t>
   </si>
   <si>
-    <t xml:space="preserve">130.294448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.236473083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.890258789062</t>
+    <t xml:space="preserve">130.294464111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.236480712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.890266418457</t>
   </si>
   <si>
     <t xml:space="preserve">118.563140869141</t>
   </si>
   <si>
-    <t xml:space="preserve">109.812744140625</t>
+    <t xml:space="preserve">109.81273651123</t>
   </si>
   <si>
     <t xml:space="preserve">113.562911987305</t>
@@ -3200,16 +3200,16 @@
     <t xml:space="preserve">115.774551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">118.755462646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.082344055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.31330871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.293991088867</t>
+    <t xml:space="preserve">118.75545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.082359313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.313316345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.293983459473</t>
   </si>
   <si>
     <t xml:space="preserve">120.101676940918</t>
@@ -3218,31 +3218,31 @@
     <t xml:space="preserve">119.236251831055</t>
   </si>
   <si>
-    <t xml:space="preserve">120.486305236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.736129760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.832290649414</t>
+    <t xml:space="preserve">120.486312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.736137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.832298278809</t>
   </si>
   <si>
     <t xml:space="preserve">119.043937683105</t>
   </si>
   <si>
-    <t xml:space="preserve">121.736366271973</t>
+    <t xml:space="preserve">121.736358642578</t>
   </si>
   <si>
     <t xml:space="preserve">124.621124267578</t>
   </si>
   <si>
-    <t xml:space="preserve">123.274894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.544044494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.044158935547</t>
+    <t xml:space="preserve">123.274887084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.544052124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.044151306152</t>
   </si>
   <si>
     <t xml:space="preserve">124.332633972168</t>
@@ -3254,49 +3254,49 @@
     <t xml:space="preserve">128.659759521484</t>
   </si>
   <si>
-    <t xml:space="preserve">127.69815826416</t>
+    <t xml:space="preserve">127.698173522949</t>
   </si>
   <si>
     <t xml:space="preserve">123.178741455078</t>
   </si>
   <si>
-    <t xml:space="preserve">114.524490356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.889801025391</t>
+    <t xml:space="preserve">114.52449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.889808654785</t>
   </si>
   <si>
     <t xml:space="preserve">114.236022949219</t>
   </si>
   <si>
-    <t xml:space="preserve">111.062789916992</t>
+    <t xml:space="preserve">111.062797546387</t>
   </si>
   <si>
     <t xml:space="preserve">112.216690063477</t>
   </si>
   <si>
-    <t xml:space="preserve">112.505172729492</t>
+    <t xml:space="preserve">112.505165100098</t>
   </si>
   <si>
     <t xml:space="preserve">113.947547912598</t>
   </si>
   <si>
-    <t xml:space="preserve">116.447654724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.197608947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.140083312988</t>
+    <t xml:space="preserve">116.447662353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.197601318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.140098571777</t>
   </si>
   <si>
     <t xml:space="preserve">119.909355163574</t>
   </si>
   <si>
-    <t xml:space="preserve">119.428558349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.890037536621</t>
+    <t xml:space="preserve">119.428565979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.890029907227</t>
   </si>
   <si>
     <t xml:space="preserve">115.293762207031</t>
@@ -3305,19 +3305,19 @@
     <t xml:space="preserve">113.178276062012</t>
   </si>
   <si>
-    <t xml:space="preserve">119.332405090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.082580566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.390365600586</t>
+    <t xml:space="preserve">119.332397460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.082588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.39037322998</t>
   </si>
   <si>
     <t xml:space="preserve">122.986419677734</t>
   </si>
   <si>
-    <t xml:space="preserve">118.27466583252</t>
+    <t xml:space="preserve">118.274673461914</t>
   </si>
   <si>
     <t xml:space="preserve">119.717041015625</t>
@@ -3326,25 +3326,25 @@
     <t xml:space="preserve">120.774780273438</t>
   </si>
   <si>
-    <t xml:space="preserve">123.659530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.948226928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.736831665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.679077148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.832740783691</t>
+    <t xml:space="preserve">123.659538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.9482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.73681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.679061889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.832748413086</t>
   </si>
   <si>
     <t xml:space="preserve">127.794334411621</t>
   </si>
   <si>
-    <t xml:space="preserve">128.467437744141</t>
+    <t xml:space="preserve">128.46745300293</t>
   </si>
   <si>
     <t xml:space="preserve">132.602249145508</t>
@@ -3359,19 +3359,19 @@
     <t xml:space="preserve">125.967323303223</t>
   </si>
   <si>
-    <t xml:space="preserve">126.351959228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.563377380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.313545227051</t>
+    <t xml:space="preserve">126.351951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.563369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.313552856445</t>
   </si>
   <si>
     <t xml:space="preserve">128.371292114258</t>
   </si>
   <si>
-    <t xml:space="preserve">126.736595153809</t>
+    <t xml:space="preserve">126.736610412598</t>
   </si>
   <si>
     <t xml:space="preserve">121.447891235352</t>
@@ -3380,13 +3380,13 @@
     <t xml:space="preserve">117.6015625</t>
   </si>
   <si>
-    <t xml:space="preserve">118.947776794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.19783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.063255310059</t>
+    <t xml:space="preserve">118.947769165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.197830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.063247680664</t>
   </si>
   <si>
     <t xml:space="preserve">117.505393981934</t>
@@ -3398,19 +3398,19 @@
     <t xml:space="preserve">116.255340576172</t>
   </si>
   <si>
-    <t xml:space="preserve">112.312850952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.582237243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.678398132324</t>
+    <t xml:space="preserve">112.312858581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.582229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.67839050293</t>
   </si>
   <si>
     <t xml:space="preserve">118.178504943848</t>
   </si>
   <si>
-    <t xml:space="preserve">114.909133911133</t>
+    <t xml:space="preserve">114.909118652344</t>
   </si>
   <si>
     <t xml:space="preserve">106.596168518066</t>
@@ -3434,37 +3434,37 @@
     <t xml:space="preserve">102.816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">106.014739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.041603088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.437377929688</t>
+    <t xml:space="preserve">106.01473236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.041610717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.437370300293</t>
   </si>
   <si>
     <t xml:space="preserve">109.212615966797</t>
   </si>
   <si>
-    <t xml:space="preserve">113.185752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.441452026367</t>
+    <t xml:space="preserve">113.185760498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.441444396973</t>
   </si>
   <si>
     <t xml:space="preserve">111.829071044922</t>
   </si>
   <si>
-    <t xml:space="preserve">107.27449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.851860046387</t>
+    <t xml:space="preserve">107.274505615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.851867675781</t>
   </si>
   <si>
     <t xml:space="preserve">104.658050537109</t>
   </si>
   <si>
-    <t xml:space="preserve">101.847785949707</t>
+    <t xml:space="preserve">101.847801208496</t>
   </si>
   <si>
     <t xml:space="preserve">102.429222106934</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">103.495193481445</t>
   </si>
   <si>
-    <t xml:space="preserve">104.076622009277</t>
+    <t xml:space="preserve">104.076629638672</t>
   </si>
   <si>
     <t xml:space="preserve">106.402359008789</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">102.332321166992</t>
   </si>
   <si>
-    <t xml:space="preserve">100.87873840332</t>
+    <t xml:space="preserve">100.878730773926</t>
   </si>
   <si>
     <t xml:space="preserve">103.979721069336</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">108.340476989746</t>
   </si>
   <si>
-    <t xml:space="preserve">117.643409729004</t>
+    <t xml:space="preserve">117.643417358398</t>
   </si>
   <si>
     <t xml:space="preserve">118.515556335449</t>
@@ -3524,10 +3524,10 @@
     <t xml:space="preserve">116.771255493164</t>
   </si>
   <si>
-    <t xml:space="preserve">114.445518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.73624420166</t>
+    <t xml:space="preserve">114.445526123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.736236572266</t>
   </si>
   <si>
     <t xml:space="preserve">115.026947021484</t>
@@ -3539,16 +3539,16 @@
     <t xml:space="preserve">115.511474609375</t>
   </si>
   <si>
-    <t xml:space="preserve">115.220771789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.965065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.476470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.25171661377</t>
+    <t xml:space="preserve">115.220764160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.965072631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.476463317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.251708984375</t>
   </si>
   <si>
     <t xml:space="preserve">114.833145141602</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">117.449592590332</t>
   </si>
   <si>
-    <t xml:space="preserve">118.61247253418</t>
+    <t xml:space="preserve">118.612464904785</t>
   </si>
   <si>
     <t xml:space="preserve">112.99193572998</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">112.604316711426</t>
   </si>
   <si>
-    <t xml:space="preserve">115.996017456055</t>
+    <t xml:space="preserve">115.99600982666</t>
   </si>
   <si>
     <t xml:space="preserve">112.216697692871</t>
   </si>
   <si>
-    <t xml:space="preserve">108.24356842041</t>
+    <t xml:space="preserve">108.243560791016</t>
   </si>
   <si>
     <t xml:space="preserve">107.080696105957</t>
@@ -3593,19 +3593,19 @@
     <t xml:space="preserve">110.181671142578</t>
   </si>
   <si>
-    <t xml:space="preserve">109.890953063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.24764251709</t>
+    <t xml:space="preserve">109.890960693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.247634887695</t>
   </si>
   <si>
     <t xml:space="preserve">113.282661437988</t>
   </si>
   <si>
-    <t xml:space="preserve">112.410499572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.639335632324</t>
+    <t xml:space="preserve">112.410507202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.639343261719</t>
   </si>
   <si>
     <t xml:space="preserve">117.934120178223</t>
@@ -3620,10 +3620,10 @@
     <t xml:space="preserve">118.031028747559</t>
   </si>
   <si>
-    <t xml:space="preserve">121.13200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.10107421875</t>
+    <t xml:space="preserve">121.132011413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.101066589355</t>
   </si>
   <si>
     <t xml:space="preserve">122.876312255859</t>
@@ -3641,16 +3641,16 @@
     <t xml:space="preserve">122.779403686523</t>
   </si>
   <si>
-    <t xml:space="preserve">123.26392364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.810348510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.74437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.74845123291</t>
+    <t xml:space="preserve">123.263931274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.810340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.74439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.748458862305</t>
   </si>
   <si>
     <t xml:space="preserve">131.985443115234</t>
@@ -3659,10 +3659,10 @@
     <t xml:space="preserve">131.888549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">132.179244995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.531829833984</t>
+    <t xml:space="preserve">132.179260253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.531860351562</t>
   </si>
   <si>
     <t xml:space="preserve">128.593734741211</t>
@@ -3671,10 +3671,10 @@
     <t xml:space="preserve">127.043251037598</t>
   </si>
   <si>
-    <t xml:space="preserve">124.814430236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.686569213867</t>
+    <t xml:space="preserve">124.814422607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.686561584473</t>
   </si>
   <si>
     <t xml:space="preserve">126.849433898926</t>
@@ -3692,10 +3692,10 @@
     <t xml:space="preserve">123.845367431641</t>
   </si>
   <si>
-    <t xml:space="preserve">121.422729492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.325820922852</t>
+    <t xml:space="preserve">121.422737121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.325813293457</t>
   </si>
   <si>
     <t xml:space="preserve">120.259857177734</t>
@@ -3707,28 +3707,28 @@
     <t xml:space="preserve">118.321746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">116.8681640625</t>
+    <t xml:space="preserve">116.868156433105</t>
   </si>
   <si>
     <t xml:space="preserve">115.802200317383</t>
   </si>
   <si>
-    <t xml:space="preserve">113.864097595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.960998535156</t>
+    <t xml:space="preserve">113.86408996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.960990905762</t>
   </si>
   <si>
     <t xml:space="preserve">113.088836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">110.472396850586</t>
+    <t xml:space="preserve">110.472389221191</t>
   </si>
   <si>
     <t xml:space="preserve">108.825004577637</t>
   </si>
   <si>
-    <t xml:space="preserve">115.414573669434</t>
+    <t xml:space="preserve">115.414581298828</t>
   </si>
   <si>
     <t xml:space="preserve">109.987861633301</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">113.670280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">118.1279296875</t>
+    <t xml:space="preserve">118.127937316895</t>
   </si>
   <si>
     <t xml:space="preserve">114.154808044434</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">119.193901062012</t>
   </si>
   <si>
-    <t xml:space="preserve">119.09700012207</t>
+    <t xml:space="preserve">119.096992492676</t>
   </si>
   <si>
     <t xml:space="preserve">119.678428649902</t>
@@ -3770,16 +3770,16 @@
     <t xml:space="preserve">110.569297790527</t>
   </si>
   <si>
-    <t xml:space="preserve">110.956924438477</t>
+    <t xml:space="preserve">110.956916809082</t>
   </si>
   <si>
     <t xml:space="preserve">108.921905517578</t>
   </si>
   <si>
-    <t xml:space="preserve">107.952850341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.565223693848</t>
+    <t xml:space="preserve">107.952842712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.565231323242</t>
   </si>
   <si>
     <t xml:space="preserve">105.045684814453</t>
@@ -3788,19 +3788,19 @@
     <t xml:space="preserve">104.754959106445</t>
   </si>
   <si>
-    <t xml:space="preserve">105.724021911621</t>
+    <t xml:space="preserve">105.724014282227</t>
   </si>
   <si>
     <t xml:space="preserve">103.592094421387</t>
   </si>
   <si>
-    <t xml:space="preserve">106.88688659668</t>
+    <t xml:space="preserve">106.886894226074</t>
   </si>
   <si>
     <t xml:space="preserve">103.204475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">100.588020324707</t>
+    <t xml:space="preserve">100.588027954102</t>
   </si>
   <si>
     <t xml:space="preserve">100.297302246094</t>
@@ -3809,10 +3809,10 @@
     <t xml:space="preserve">102.719947814941</t>
   </si>
   <si>
-    <t xml:space="preserve">103.107566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.561149597168</t>
+    <t xml:space="preserve">103.107574462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.561157226562</t>
   </si>
   <si>
     <t xml:space="preserve">107.37141418457</t>
@@ -3827,13 +3827,13 @@
     <t xml:space="preserve">110.084770202637</t>
   </si>
   <si>
-    <t xml:space="preserve">116.480545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.705291748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.379570007324</t>
+    <t xml:space="preserve">116.480537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.705307006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.37956237793</t>
   </si>
   <si>
     <t xml:space="preserve">112.798126220703</t>
@@ -3851,16 +3851,16 @@
     <t xml:space="preserve">109.115715026855</t>
   </si>
   <si>
-    <t xml:space="preserve">110.278579711914</t>
+    <t xml:space="preserve">110.278587341309</t>
   </si>
   <si>
     <t xml:space="preserve">109.697143554688</t>
   </si>
   <si>
-    <t xml:space="preserve">102.235420227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.623046875</t>
+    <t xml:space="preserve">102.235412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.623039245605</t>
   </si>
   <si>
     <t xml:space="preserve">104.173522949219</t>
@@ -3881,22 +3881,22 @@
     <t xml:space="preserve">100.006591796875</t>
   </si>
   <si>
-    <t xml:space="preserve">99.4251480102539</t>
+    <t xml:space="preserve">99.4251556396484</t>
   </si>
   <si>
     <t xml:space="preserve">101.26636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">101.653984069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.39421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.328239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6189727783203</t>
+    <t xml:space="preserve">101.65397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.394203186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.328254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6189651489258</t>
   </si>
   <si>
     <t xml:space="preserve">99.2313385009766</t>
@@ -3926,16 +3926,16 @@
     <t xml:space="preserve">99.0078277587891</t>
   </si>
   <si>
-    <t xml:space="preserve">98.6164932250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.573173522949</t>
+    <t xml:space="preserve">98.6165008544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.573181152344</t>
   </si>
   <si>
     <t xml:space="preserve">97.051155090332</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0672302246094</t>
+    <t xml:space="preserve">94.0672225952148</t>
   </si>
   <si>
     <t xml:space="preserve">95.8771438598633</t>
@@ -3956,7 +3956,7 @@
     <t xml:space="preserve">95.7793197631836</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5780487060547</t>
+    <t xml:space="preserve">93.5780563354492</t>
   </si>
   <si>
     <t xml:space="preserve">92.5997161865234</t>
@@ -3983,7 +3983,7 @@
     <t xml:space="preserve">90.0071182250977</t>
   </si>
   <si>
-    <t xml:space="preserve">90.4962844848633</t>
+    <t xml:space="preserve">90.4962921142578</t>
   </si>
   <si>
     <t xml:space="preserve">90.8386993408203</t>
@@ -3992,13 +3992,13 @@
     <t xml:space="preserve">92.3062133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">92.942138671875</t>
+    <t xml:space="preserve">92.9421310424805</t>
   </si>
   <si>
     <t xml:space="preserve">91.2789611816406</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6213760375977</t>
+    <t xml:space="preserve">91.6213836669922</t>
   </si>
   <si>
     <t xml:space="preserve">90.6430435180664</t>
@@ -4049,28 +4049,28 @@
     <t xml:space="preserve">103.508193969727</t>
   </si>
   <si>
-    <t xml:space="preserve">103.703857421875</t>
+    <t xml:space="preserve">103.70384979248</t>
   </si>
   <si>
     <t xml:space="preserve">106.051864624023</t>
   </si>
   <si>
-    <t xml:space="preserve">104.975700378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.171356201172</t>
+    <t xml:space="preserve">104.975692749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.171363830566</t>
   </si>
   <si>
     <t xml:space="preserve">102.627685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">101.747184753418</t>
+    <t xml:space="preserve">101.747177124023</t>
   </si>
   <si>
     <t xml:space="preserve">103.997360229492</t>
   </si>
   <si>
-    <t xml:space="preserve">102.529846191406</t>
+    <t xml:space="preserve">102.529853820801</t>
   </si>
   <si>
     <t xml:space="preserve">100.377502441406</t>
@@ -4082,10 +4082,10 @@
     <t xml:space="preserve">104.193023681641</t>
   </si>
   <si>
-    <t xml:space="preserve">106.541030883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.617210388184</t>
+    <t xml:space="preserve">106.541038513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.617202758789</t>
   </si>
   <si>
     <t xml:space="preserve">106.834533691406</t>
@@ -4094,13 +4094,13 @@
     <t xml:space="preserve">105.85619354248</t>
   </si>
   <si>
-    <t xml:space="preserve">111.530563354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.367736816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.291572570801</t>
+    <t xml:space="preserve">111.530555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.367744445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.291564941406</t>
   </si>
   <si>
     <t xml:space="preserve">117.694091796875</t>
@@ -4109,22 +4109,22 @@
     <t xml:space="preserve">118.672431945801</t>
   </si>
   <si>
-    <t xml:space="preserve">118.378921508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.259429931641</t>
+    <t xml:space="preserve">118.378929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.259437561035</t>
   </si>
   <si>
     <t xml:space="preserve">120.335601806641</t>
   </si>
   <si>
-    <t xml:space="preserve">118.085426330566</t>
+    <t xml:space="preserve">118.085418701172</t>
   </si>
   <si>
     <t xml:space="preserve">115.346084594727</t>
   </si>
   <si>
-    <t xml:space="preserve">115.737411499023</t>
+    <t xml:space="preserve">115.737419128418</t>
   </si>
   <si>
     <t xml:space="preserve">113.682907104492</t>
@@ -4139,19 +4139,19 @@
     <t xml:space="preserve">111.921897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">111.824058532715</t>
+    <t xml:space="preserve">111.824066162109</t>
   </si>
   <si>
     <t xml:space="preserve">114.074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">113.976402282715</t>
+    <t xml:space="preserve">113.976409912109</t>
   </si>
   <si>
     <t xml:space="preserve">112.802406311035</t>
   </si>
   <si>
-    <t xml:space="preserve">112.31324005127</t>
+    <t xml:space="preserve">112.313232421875</t>
   </si>
   <si>
     <t xml:space="preserve">114.856910705566</t>
@@ -4172,10 +4172,10 @@
     <t xml:space="preserve">122.585784912109</t>
   </si>
   <si>
-    <t xml:space="preserve">122.781448364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.368453979492</t>
+    <t xml:space="preserve">122.781455993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.368446350098</t>
   </si>
   <si>
     <t xml:space="preserve">120.433433532715</t>
@@ -4190,13 +4190,13 @@
     <t xml:space="preserve">122.194450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">121.803108215332</t>
+    <t xml:space="preserve">121.803115844727</t>
   </si>
   <si>
     <t xml:space="preserve">120.042098999023</t>
   </si>
   <si>
-    <t xml:space="preserve">119.455101013184</t>
+    <t xml:space="preserve">119.455093383789</t>
   </si>
   <si>
     <t xml:space="preserve">118.574592590332</t>
@@ -4232,31 +4232,31 @@
     <t xml:space="preserve">112.019729614258</t>
   </si>
   <si>
-    <t xml:space="preserve">112.900238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.095893859863</t>
+    <t xml:space="preserve">112.900230407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.095901489258</t>
   </si>
   <si>
     <t xml:space="preserve">110.943557739258</t>
   </si>
   <si>
-    <t xml:space="preserve">111.334892272949</t>
+    <t xml:space="preserve">111.334899902344</t>
   </si>
   <si>
     <t xml:space="preserve">110.747886657715</t>
   </si>
   <si>
-    <t xml:space="preserve">110.063049316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.671722412109</t>
+    <t xml:space="preserve">110.063056945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.671714782715</t>
   </si>
   <si>
     <t xml:space="preserve">102.725517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">100.181838989258</t>
+    <t xml:space="preserve">100.181831359863</t>
   </si>
   <si>
     <t xml:space="preserve">96.8554840087891</t>
@@ -4289,10 +4289,10 @@
     <t xml:space="preserve">98.322998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">96.8065643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2195587158203</t>
+    <t xml:space="preserve">96.8065719604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2195663452148</t>
   </si>
   <si>
     <t xml:space="preserve">94.9966430664062</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">95.7303924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">97.9316558837891</t>
+    <t xml:space="preserve">97.9316635131836</t>
   </si>
   <si>
     <t xml:space="preserve">95.8282318115234</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">106.638870239258</t>
   </si>
   <si>
-    <t xml:space="preserve">107.128036499023</t>
+    <t xml:space="preserve">107.128044128418</t>
   </si>
   <si>
     <t xml:space="preserve">105.954032897949</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">104.682189941406</t>
   </si>
   <si>
-    <t xml:space="preserve">103.899513244629</t>
+    <t xml:space="preserve">103.899520874023</t>
   </si>
   <si>
     <t xml:space="preserve">104.78002166748</t>
@@ -4364,10 +4364,10 @@
     <t xml:space="preserve">105.660530090332</t>
   </si>
   <si>
-    <t xml:space="preserve">106.345367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.443199157715</t>
+    <t xml:space="preserve">106.345359802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.443206787109</t>
   </si>
   <si>
     <t xml:space="preserve">103.801681518555</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">112.704566955566</t>
   </si>
   <si>
-    <t xml:space="preserve">114.172073364258</t>
+    <t xml:space="preserve">114.172065734863</t>
   </si>
   <si>
     <t xml:space="preserve">117.107086181641</t>
@@ -4391,10 +4391,10 @@
     <t xml:space="preserve">115.150405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">116.813591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.204925537109</t>
+    <t xml:space="preserve">116.813583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.204917907715</t>
   </si>
   <si>
     <t xml:space="preserve">116.128746032715</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">96.5619812011719</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2628860473633</t>
+    <t xml:space="preserve">94.2628936767578</t>
   </si>
   <si>
     <t xml:space="preserve">91.3767929077148</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">95.3390579223633</t>
   </si>
   <si>
-    <t xml:space="preserve">94.3118133544922</t>
+    <t xml:space="preserve">94.3118057250977</t>
   </si>
   <si>
     <t xml:space="preserve">93.4802169799805</t>
@@ -4451,28 +4451,28 @@
     <t xml:space="preserve">94.7031478881836</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8498840332031</t>
+    <t xml:space="preserve">94.8498916625977</t>
   </si>
   <si>
     <t xml:space="preserve">94.2139739990234</t>
   </si>
   <si>
-    <t xml:space="preserve">91.8659591674805</t>
+    <t xml:space="preserve">91.865966796875</t>
   </si>
   <si>
     <t xml:space="preserve">90.6919479370117</t>
   </si>
   <si>
-    <t xml:space="preserve">89.2244415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7080230712891</t>
+    <t xml:space="preserve">89.2244491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7080307006836</t>
   </si>
   <si>
     <t xml:space="preserve">85.751350402832</t>
   </si>
   <si>
-    <t xml:space="preserve">84.5284194946289</t>
+    <t xml:space="preserve">84.5284271240234</t>
   </si>
   <si>
     <t xml:space="preserve">84.3327560424805</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">86.2894287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2517013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.441780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0287857055664</t>
+    <t xml:space="preserve">90.251708984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4417724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0287780761719</t>
   </si>
   <si>
     <t xml:space="preserve">88.4906921386719</t>
@@ -5274,6 +5274,9 @@
   </si>
   <si>
     <t xml:space="preserve">83.9000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4499969482422</t>
   </si>
 </sst>
 </file>
@@ -18240,7 +18243,7 @@
         <v>24.9599990844727</v>
       </c>
       <c r="G486" t="s">
-        <v>333</v>
+        <v>298</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -18292,7 +18295,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G488" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -18318,7 +18321,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G489" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -18344,7 +18347,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G490" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -18370,7 +18373,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G491" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -18396,7 +18399,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G492" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -18422,7 +18425,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G493" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -18448,7 +18451,7 @@
         <v>24.5</v>
       </c>
       <c r="G494" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -18474,7 +18477,7 @@
         <v>25.0699996948242</v>
       </c>
       <c r="G495" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -18500,7 +18503,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G496" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -18526,7 +18529,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G497" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -18552,7 +18555,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G498" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -18578,7 +18581,7 @@
         <v>25.7900009155273</v>
       </c>
       <c r="G499" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -18604,7 +18607,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G500" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -18630,7 +18633,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G501" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -18656,7 +18659,7 @@
         <v>24.9300003051758</v>
       </c>
       <c r="G502" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -18682,7 +18685,7 @@
         <v>24.5</v>
       </c>
       <c r="G503" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -18708,7 +18711,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G504" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -18734,7 +18737,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G505" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -18760,7 +18763,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G506" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -18786,7 +18789,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G507" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18812,7 +18815,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G508" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18838,7 +18841,7 @@
         <v>25.75</v>
       </c>
       <c r="G509" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18864,7 +18867,7 @@
         <v>26.0100002288818</v>
       </c>
       <c r="G510" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18890,7 +18893,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G511" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18916,7 +18919,7 @@
         <v>26</v>
       </c>
       <c r="G512" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18942,7 +18945,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G513" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18968,7 +18971,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G514" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18994,7 +18997,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G515" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -19020,7 +19023,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G516" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -19046,7 +19049,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G517" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -19124,7 +19127,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G520" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -19202,7 +19205,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G523" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -19228,7 +19231,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G524" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -19254,7 +19257,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G525" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -19280,7 +19283,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G526" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -19306,7 +19309,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G527" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -19384,7 +19387,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G530" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -19410,7 +19413,7 @@
         <v>27.25</v>
       </c>
       <c r="G531" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -19488,7 +19491,7 @@
         <v>26.5</v>
       </c>
       <c r="G534" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -19514,7 +19517,7 @@
         <v>26.5</v>
       </c>
       <c r="G535" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -19540,7 +19543,7 @@
         <v>26</v>
       </c>
       <c r="G536" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -19566,7 +19569,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G537" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -19592,7 +19595,7 @@
         <v>26</v>
       </c>
       <c r="G538" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -19618,7 +19621,7 @@
         <v>26.0499992370605</v>
       </c>
       <c r="G539" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -19644,7 +19647,7 @@
         <v>26</v>
       </c>
       <c r="G540" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -19670,7 +19673,7 @@
         <v>26.5</v>
       </c>
       <c r="G541" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -19696,7 +19699,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G542" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -19722,7 +19725,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G543" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -19748,7 +19751,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G544" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -19774,7 +19777,7 @@
         <v>26.5</v>
       </c>
       <c r="G545" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -19826,7 +19829,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G547" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19852,7 +19855,7 @@
         <v>26.25</v>
       </c>
       <c r="G548" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19878,7 +19881,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G549" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19904,7 +19907,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G550" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19930,7 +19933,7 @@
         <v>26.8500003814697</v>
       </c>
       <c r="G551" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19956,7 +19959,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G552" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -20034,7 +20037,7 @@
         <v>25.75</v>
       </c>
       <c r="G555" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -20060,7 +20063,7 @@
         <v>26</v>
       </c>
       <c r="G556" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -20086,7 +20089,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G557" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -20138,7 +20141,7 @@
         <v>26.75</v>
       </c>
       <c r="G559" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -20164,7 +20167,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G560" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -20190,7 +20193,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G561" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -20216,7 +20219,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G562" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -20242,7 +20245,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G563" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -20294,7 +20297,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G565" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -20320,7 +20323,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G566" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -20346,7 +20349,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G567" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -20398,7 +20401,7 @@
         <v>26.5</v>
       </c>
       <c r="G569" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -20424,7 +20427,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G570" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -20450,7 +20453,7 @@
         <v>26.0499992370605</v>
       </c>
       <c r="G571" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -20502,7 +20505,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G573" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -20554,7 +20557,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G575" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -20580,7 +20583,7 @@
         <v>26</v>
       </c>
       <c r="G576" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -20606,7 +20609,7 @@
         <v>26</v>
       </c>
       <c r="G577" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -20632,7 +20635,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G578" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -20658,7 +20661,7 @@
         <v>26.0499992370605</v>
       </c>
       <c r="G579" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -20684,7 +20687,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G580" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -20710,7 +20713,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G581" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -20736,7 +20739,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G582" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -20762,7 +20765,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G583" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -20788,7 +20791,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G584" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20814,7 +20817,7 @@
         <v>26.75</v>
       </c>
       <c r="G585" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20840,7 +20843,7 @@
         <v>27.25</v>
       </c>
       <c r="G586" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20892,7 +20895,7 @@
         <v>26.75</v>
       </c>
       <c r="G588" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20944,7 +20947,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G590" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20996,7 +20999,7 @@
         <v>26.6499996185303</v>
       </c>
       <c r="G592" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -21022,7 +21025,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G593" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -21048,7 +21051,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G594" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -21074,7 +21077,7 @@
         <v>27.75</v>
       </c>
       <c r="G595" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -21100,7 +21103,7 @@
         <v>27.75</v>
       </c>
       <c r="G596" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -21126,7 +21129,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G597" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -21152,7 +21155,7 @@
         <v>27.75</v>
       </c>
       <c r="G598" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -21204,7 +21207,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G600" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -21230,7 +21233,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G601" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -21256,7 +21259,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G602" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -21282,7 +21285,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G603" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -21308,7 +21311,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G604" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -21334,7 +21337,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G605" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -21360,7 +21363,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G606" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -21386,7 +21389,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G607" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -21412,7 +21415,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G608" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -21438,7 +21441,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G609" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -21464,7 +21467,7 @@
         <v>29</v>
       </c>
       <c r="G610" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -21490,7 +21493,7 @@
         <v>28.75</v>
       </c>
       <c r="G611" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -21542,7 +21545,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G613" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -21568,7 +21571,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G614" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -21620,7 +21623,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G616" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -21646,7 +21649,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G617" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -21698,7 +21701,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G619" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21724,7 +21727,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G620" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21750,7 +21753,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G621" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21828,7 +21831,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G624" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21854,7 +21857,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21880,7 +21883,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G626" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21906,7 +21909,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G627" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21932,7 +21935,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G628" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21958,7 +21961,7 @@
         <v>28.75</v>
       </c>
       <c r="G629" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21984,7 +21987,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G630" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -22010,7 +22013,7 @@
         <v>28.75</v>
       </c>
       <c r="G631" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -22036,7 +22039,7 @@
         <v>29.5</v>
       </c>
       <c r="G632" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -22062,7 +22065,7 @@
         <v>28.75</v>
       </c>
       <c r="G633" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -22088,7 +22091,7 @@
         <v>28.5</v>
       </c>
       <c r="G634" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -22114,7 +22117,7 @@
         <v>28.5</v>
       </c>
       <c r="G635" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -22192,7 +22195,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G638" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -22218,7 +22221,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -22244,7 +22247,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G640" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -22270,7 +22273,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G641" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -22296,7 +22299,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G642" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -22322,7 +22325,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -22348,7 +22351,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G644" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -22374,7 +22377,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -22452,7 +22455,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G648" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -22478,7 +22481,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G649" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -22504,7 +22507,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G650" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -22530,7 +22533,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G651" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -22556,7 +22559,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G652" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -22582,7 +22585,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G653" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -22608,7 +22611,7 @@
         <v>28.5</v>
       </c>
       <c r="G654" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -22634,7 +22637,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G655" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -22660,7 +22663,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G656" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -22686,7 +22689,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G657" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22712,7 +22715,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G658" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22738,7 +22741,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G659" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22764,7 +22767,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G660" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22790,7 +22793,7 @@
         <v>31</v>
       </c>
       <c r="G661" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22816,7 +22819,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G662" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22842,7 +22845,7 @@
         <v>31.25</v>
       </c>
       <c r="G663" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22868,7 +22871,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G664" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22894,7 +22897,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G665" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22920,7 +22923,7 @@
         <v>30.5</v>
       </c>
       <c r="G666" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22946,7 +22949,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G667" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22972,7 +22975,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G668" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22998,7 +23001,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G669" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -23024,7 +23027,7 @@
         <v>29.25</v>
       </c>
       <c r="G670" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -23050,7 +23053,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G671" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -23076,7 +23079,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G672" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -23102,7 +23105,7 @@
         <v>29.25</v>
       </c>
       <c r="G673" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -23128,7 +23131,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G674" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -23154,7 +23157,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G675" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -23206,7 +23209,7 @@
         <v>28.5</v>
       </c>
       <c r="G677" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -23232,7 +23235,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G678" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -23258,7 +23261,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G679" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -23284,7 +23287,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G680" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -23310,7 +23313,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G681" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -23336,7 +23339,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G682" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -23362,7 +23365,7 @@
         <v>28.25</v>
       </c>
       <c r="G683" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -23414,7 +23417,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G685" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -23440,7 +23443,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G686" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -23466,7 +23469,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G687" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -23518,7 +23521,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G689" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -23544,7 +23547,7 @@
         <v>30</v>
       </c>
       <c r="G690" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -23570,7 +23573,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G691" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -23596,7 +23599,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G692" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -23622,7 +23625,7 @@
         <v>29</v>
       </c>
       <c r="G693" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -23648,7 +23651,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G694" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -23674,7 +23677,7 @@
         <v>28.5</v>
       </c>
       <c r="G695" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -23700,7 +23703,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G696" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23726,7 +23729,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G697" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23752,7 +23755,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G698" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23778,7 +23781,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G699" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23804,7 +23807,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -26430,7 +26433,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G801" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -27262,7 +27265,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G833" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -71444,7 +71447,7 @@
     </row>
     <row r="2533">
       <c r="A2533" s="1" t="n">
-        <v>46006.6909953704</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B2533" t="n">
         <v>32013</v>
@@ -71465,6 +71468,32 @@
         <v>1753</v>
       </c>
       <c r="H2533" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" s="1" t="n">
+        <v>46007.6911574074</v>
+      </c>
+      <c r="B2534" t="n">
+        <v>15640</v>
+      </c>
+      <c r="C2534" t="n">
+        <v>84.8000030517578</v>
+      </c>
+      <c r="D2534" t="n">
+        <v>83.6500015258789</v>
+      </c>
+      <c r="E2534" t="n">
+        <v>84.0999984741211</v>
+      </c>
+      <c r="F2534" t="n">
+        <v>84.4499969482422</v>
+      </c>
+      <c r="G2534" t="s">
+        <v>1754</v>
+      </c>
+      <c r="H2534" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="1757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="1758">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,46 +50,46 @@
     <t xml:space="preserve">13.2523736953735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9464139938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1125078201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8589992523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0513143539429</t>
+    <t xml:space="preserve">12.9464149475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1125059127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.858998298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0513162612915</t>
   </si>
   <si>
     <t xml:space="preserve">12.9901237487793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9376726150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1037645339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0250873565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8502559661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2383394241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5880069732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7890644073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7191324234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6841669082642</t>
+    <t xml:space="preserve">12.9376735687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1037635803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0250902175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8502569198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2383403778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5880079269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7890653610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7191314697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6841659545898</t>
   </si>
   <si>
     <t xml:space="preserve">12.605489730835</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">12.0460224151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1771488189697</t>
+    <t xml:space="preserve">12.177149772644</t>
   </si>
   <si>
     <t xml:space="preserve">12.1421813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9270896911621</t>
+    <t xml:space="preserve">10.9270877838135</t>
   </si>
   <si>
     <t xml:space="preserve">10.9795398712158</t>
@@ -116,52 +116,52 @@
     <t xml:space="preserve">11.3641719818115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4515905380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0984745025635</t>
+    <t xml:space="preserve">11.4515886306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0984735488892</t>
   </si>
   <si>
     <t xml:space="preserve">12.107213973999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9760894775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9323797225952</t>
+    <t xml:space="preserve">11.8886737823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9760885238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9323816299438</t>
   </si>
   <si>
     <t xml:space="preserve">12.0110559463501</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0809888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8012571334839</t>
+    <t xml:space="preserve">12.0809898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8012552261353</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334400177002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8274793624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0635070800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5005893707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6754236221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7978076934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1649570465088</t>
+    <t xml:space="preserve">11.8274812698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0635051727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5005903244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6754245758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7978067398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1649580001831</t>
   </si>
   <si>
     <t xml:space="preserve">13.1562156677246</t>
@@ -173,16 +173,16 @@
     <t xml:space="preserve">13.1212482452393</t>
   </si>
   <si>
-    <t xml:space="preserve">13.19118309021</t>
+    <t xml:space="preserve">13.1911821365356</t>
   </si>
   <si>
     <t xml:space="preserve">12.7540979385376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8939666748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9027080535889</t>
+    <t xml:space="preserve">12.8939647674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9027061462402</t>
   </si>
   <si>
     <t xml:space="preserve">13.0600576400757</t>
@@ -197,34 +197,34 @@
     <t xml:space="preserve">13.4534330368042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7069396972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4709157943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4621734619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.208664894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3223056793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0950241088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9988651275635</t>
+    <t xml:space="preserve">13.7069416046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4709148406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4621744155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2086639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3223066329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0950231552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9988641738892</t>
   </si>
   <si>
     <t xml:space="preserve">12.6404571533203</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4481391906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3782043457031</t>
+    <t xml:space="preserve">12.4481382369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3782062530518</t>
   </si>
   <si>
     <t xml:space="preserve">12.0285396575928</t>
@@ -233,34 +233,34 @@
     <t xml:space="preserve">12.1509237289429</t>
   </si>
   <si>
-    <t xml:space="preserve">12.439398765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5617818832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5268154144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6317148208618</t>
+    <t xml:space="preserve">12.4393968582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5617809295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5268144607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6317138671875</t>
   </si>
   <si>
     <t xml:space="preserve">12.3694648742676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.771580696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4306573867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2820472717285</t>
+    <t xml:space="preserve">12.7715826034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4306564331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2820491790771</t>
   </si>
   <si>
     <t xml:space="preserve">12.1946315765381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2470836639404</t>
+    <t xml:space="preserve">12.2470817565918</t>
   </si>
   <si>
     <t xml:space="preserve">12.4131736755371</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">12.3869485855103</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8187417984009</t>
+    <t xml:space="preserve">11.8187398910522</t>
   </si>
   <si>
     <t xml:space="preserve">11.8449649810791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2558240890503</t>
+    <t xml:space="preserve">12.2558250427246</t>
   </si>
   <si>
     <t xml:space="preserve">12.5792655944824</t>
@@ -287,43 +287,43 @@
     <t xml:space="preserve">12.2208557128906</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1858882904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7803230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7278747558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8764820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8065481185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7628402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8677406311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327732086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5355577468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1824407577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0338306427002</t>
+    <t xml:space="preserve">12.1858892440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7803239822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7278738021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8764810562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8065490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7628421783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8677415847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327741622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5355567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1824398040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0338325500488</t>
   </si>
   <si>
     <t xml:space="preserve">13.3048248291016</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2611141204834</t>
+    <t xml:space="preserve">13.2611150741577</t>
   </si>
   <si>
     <t xml:space="preserve">13.3747577667236</t>
@@ -332,67 +332,67 @@
     <t xml:space="preserve">13.6020402908325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6894569396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7244253158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7514772415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5711288452148</t>
+    <t xml:space="preserve">13.6894559860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7244243621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7514753341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5711278915405</t>
   </si>
   <si>
     <t xml:space="preserve">13.8687019348145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6252317428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6432666778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6613025665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5981817245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6162176132202</t>
+    <t xml:space="preserve">13.6252326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6432676315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6613035202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.598180770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6162166595459</t>
   </si>
   <si>
     <t xml:space="preserve">13.5260419845581</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5530920028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3456935882568</t>
+    <t xml:space="preserve">13.5530948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3456945419312</t>
   </si>
   <si>
     <t xml:space="preserve">13.5801467895508</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6973714828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.778528213501</t>
+    <t xml:space="preserve">13.6973724365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7785263061523</t>
   </si>
   <si>
     <t xml:space="preserve">13.6703195571899</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7965631484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9769096374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0400314331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0129776000977</t>
+    <t xml:space="preserve">13.7965641021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9769105911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0400304794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0129795074463</t>
   </si>
   <si>
     <t xml:space="preserve">13.9047718048096</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">14.1031532287598</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2474317550659</t>
+    <t xml:space="preserve">14.2474308013916</t>
   </si>
   <si>
     <t xml:space="preserve">14.1572580337524</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3646564483643</t>
+    <t xml:space="preserve">14.3646574020386</t>
   </si>
   <si>
     <t xml:space="preserve">14.4187612533569</t>
@@ -416,31 +416,31 @@
     <t xml:space="preserve">14.517951965332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6081266403198</t>
+    <t xml:space="preserve">14.6081256866455</t>
   </si>
   <si>
     <t xml:space="preserve">14.6622314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3917093276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3105516433716</t>
+    <t xml:space="preserve">14.3917074203491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3105535507202</t>
   </si>
   <si>
     <t xml:space="preserve">14.30153465271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5450019836426</t>
+    <t xml:space="preserve">14.5450029373169</t>
   </si>
   <si>
     <t xml:space="preserve">14.6441946029663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7343683242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7163324356079</t>
+    <t xml:space="preserve">14.7343692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7163333892822</t>
   </si>
   <si>
     <t xml:space="preserve">14.635178565979</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">14.6261606216431</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6892833709717</t>
+    <t xml:space="preserve">14.6892824172974</t>
   </si>
   <si>
     <t xml:space="preserve">14.8245429992676</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">14.8065071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7433862686157</t>
+    <t xml:space="preserve">14.7433853149414</t>
   </si>
   <si>
     <t xml:space="preserve">14.5810718536377</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">14.6982975006104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5089330673218</t>
+    <t xml:space="preserve">14.5089349746704</t>
   </si>
   <si>
     <t xml:space="preserve">14.6712484359741</t>
@@ -476,49 +476,49 @@
     <t xml:space="preserve">14.6532125473022</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9237308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.049976348877</t>
+    <t xml:space="preserve">14.923731803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0499782562256</t>
   </si>
   <si>
     <t xml:space="preserve">15.2122898101807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3746023178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5549478530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9246606826782</t>
+    <t xml:space="preserve">15.3745975494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.554949760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9246587753296</t>
   </si>
   <si>
     <t xml:space="preserve">15.7803812026978</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8705558776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344879150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7082424163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517135620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7452411651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8714809417725</t>
+    <t xml:space="preserve">15.8705549240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7082443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.951714515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7452392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8714828491211</t>
   </si>
   <si>
     <t xml:space="preserve">17.0879001617432</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1510200500488</t>
+    <t xml:space="preserve">17.1510219573975</t>
   </si>
   <si>
     <t xml:space="preserve">17.2231597900391</t>
@@ -527,43 +527,43 @@
     <t xml:space="preserve">16.9796924591064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9075527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3043174743652</t>
+    <t xml:space="preserve">16.9075508117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3043155670166</t>
   </si>
   <si>
     <t xml:space="preserve">17.0337944030762</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2772655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4756450653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3223514556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1690616607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5838527679443</t>
+    <t xml:space="preserve">17.2772636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4756469726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3223495483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.169059753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.583854675293</t>
   </si>
   <si>
     <t xml:space="preserve">17.574836730957</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5658168792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2411975860596</t>
+    <t xml:space="preserve">17.5658149719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2411956787109</t>
   </si>
   <si>
     <t xml:space="preserve">17.1870899200439</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8534469604492</t>
+    <t xml:space="preserve">16.8534507751465</t>
   </si>
   <si>
     <t xml:space="preserve">16.8444290161133</t>
@@ -572,46 +572,46 @@
     <t xml:space="preserve">16.9526386260986</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7272071838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6911373138428</t>
+    <t xml:space="preserve">16.7272052764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6911334991455</t>
   </si>
   <si>
     <t xml:space="preserve">16.8624668121338</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0428142547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8173770904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9977245330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7722911834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0067443847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1961059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3584213256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6199245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7642002105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0076675415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9896354675293</t>
+    <t xml:space="preserve">17.0428123474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8173809051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9977264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7722930908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.006742477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1961097717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3584175109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6199283599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7642021179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0076694488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9896335601807</t>
   </si>
   <si>
     <t xml:space="preserve">17.9445476531982</t>
@@ -620,28 +620,28 @@
     <t xml:space="preserve">17.9535675048828</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8092880249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2601566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7561092376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8462829589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9364604949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6208515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2971515655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3602714538574</t>
+    <t xml:space="preserve">17.809289932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2601585388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7561111450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8462886810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9364585876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.620849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2971534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3602752685547</t>
   </si>
   <si>
     <t xml:space="preserve">19.3512573242188</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">19.6668643951416</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6488285064697</t>
+    <t xml:space="preserve">19.6488304138184</t>
   </si>
   <si>
     <t xml:space="preserve">19.5586585998535</t>
@@ -659,31 +659,31 @@
     <t xml:space="preserve">19.2520656585693</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1709098815918</t>
+    <t xml:space="preserve">19.1709079742432</t>
   </si>
   <si>
     <t xml:space="preserve">19.1348400115967</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1979637145996</t>
+    <t xml:space="preserve">19.197961807251</t>
   </si>
   <si>
     <t xml:space="preserve">18.9544925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9094066619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0897541046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5757656097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1970367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5306797027588</t>
+    <t xml:space="preserve">18.9094085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0897560119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5757637023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1970348358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5306777954102</t>
   </si>
   <si>
     <t xml:space="preserve">18.8372688293457</t>
@@ -692,10 +692,10 @@
     <t xml:space="preserve">19.4594650268555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3873291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0185432434082</t>
+    <t xml:space="preserve">19.3873271942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0185413360596</t>
   </si>
   <si>
     <t xml:space="preserve">20.3612022399902</t>
@@ -704,52 +704,52 @@
     <t xml:space="preserve">20.8301048278809</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2809734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8751907348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9292945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1006259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0104503631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5685997009277</t>
+    <t xml:space="preserve">21.2809715270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8751888275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9292984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1006240844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0104522705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5686016082764</t>
   </si>
   <si>
     <t xml:space="preserve">20.7218971252441</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6046695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1898708343506</t>
+    <t xml:space="preserve">20.6046676635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1898727416992</t>
   </si>
   <si>
     <t xml:space="preserve">20.3792381286621</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6497554779053</t>
+    <t xml:space="preserve">20.6497592926025</t>
   </si>
   <si>
     <t xml:space="preserve">21.6416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3711471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3801612854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0925388336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6245632171631</t>
+    <t xml:space="preserve">21.371150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3801651000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0925350189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6245594024658</t>
   </si>
   <si>
     <t xml:space="preserve">22.7147331237793</t>
@@ -758,85 +758,85 @@
     <t xml:space="preserve">22.8049087524414</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5984363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0763530731201</t>
+    <t xml:space="preserve">23.5984325408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0763549804688</t>
   </si>
   <si>
     <t xml:space="preserve">24.0583209991455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7156600952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9320774078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8599395751953</t>
+    <t xml:space="preserve">23.7156581878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9320755004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8599376678467</t>
   </si>
   <si>
     <t xml:space="preserve">23.8058319091797</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5082607269287</t>
+    <t xml:space="preserve">23.5082588195801</t>
   </si>
   <si>
     <t xml:space="preserve">22.9942722320557</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4802799224854</t>
+    <t xml:space="preserve">22.480281829834</t>
   </si>
   <si>
     <t xml:space="preserve">22.5434036254883</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7057151794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4532318115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4622440338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0023574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1827087402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7237529754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3630542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2097606658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4883689880371</t>
+    <t xml:space="preserve">22.7057132720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4532279968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4622478485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0023593902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.182710647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7237510681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.36305809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2097587585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4883708953857</t>
   </si>
   <si>
     <t xml:space="preserve">21.9212036132812</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8761196136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7047901153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9392395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0745029449463</t>
+    <t xml:space="preserve">21.8761177062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7047863006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9392375946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0745010375977</t>
   </si>
   <si>
     <t xml:space="preserve">22.299934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8139228820801</t>
+    <t xml:space="preserve">22.8139247894287</t>
   </si>
   <si>
     <t xml:space="preserve">22.3179683685303</t>
@@ -848,19 +848,19 @@
     <t xml:space="preserve">22.3540382385254</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5253715515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6065254211426</t>
+    <t xml:space="preserve">22.5253658294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6065292358398</t>
   </si>
   <si>
     <t xml:space="preserve">22.6335792541504</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2458343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2277946472168</t>
+    <t xml:space="preserve">22.24582862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2277965545654</t>
   </si>
   <si>
     <t xml:space="preserve">22.128604888916</t>
@@ -869,22 +869,22 @@
     <t xml:space="preserve">22.0835189819336</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2007427215576</t>
+    <t xml:space="preserve">22.2007446289062</t>
   </si>
   <si>
     <t xml:space="preserve">22.1376209259033</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1466426849365</t>
+    <t xml:space="preserve">22.1466388702393</t>
   </si>
   <si>
     <t xml:space="preserve">21.5965824127197</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3260612487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5605087280273</t>
+    <t xml:space="preserve">21.3260593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.560510635376</t>
   </si>
   <si>
     <t xml:space="preserve">22.0294132232666</t>
@@ -893,25 +893,25 @@
     <t xml:space="preserve">21.6867523193359</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2368144989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3720722198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3991241455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6155414581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6606311798096</t>
+    <t xml:space="preserve">22.2368125915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3720741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3991279602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6155433654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6606273651123</t>
   </si>
   <si>
     <t xml:space="preserve">23.0123081207275</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5193881988525</t>
+    <t xml:space="preserve">23.5193862915039</t>
   </si>
   <si>
     <t xml:space="preserve">23.2704582214355</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">24.7087268829346</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7732620239258</t>
+    <t xml:space="preserve">24.773265838623</t>
   </si>
   <si>
     <t xml:space="preserve">25.243465423584</t>
@@ -935,58 +935,58 @@
     <t xml:space="preserve">25.7966461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6860103607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6675701141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0086975097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8888454437256</t>
+    <t xml:space="preserve">25.686014175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6675720214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0086994171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.888843536377</t>
   </si>
   <si>
     <t xml:space="preserve">25.9810409545898</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0916728973389</t>
+    <t xml:space="preserve">26.0916767120361</t>
   </si>
   <si>
     <t xml:space="preserve">25.907283782959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8058662414551</t>
+    <t xml:space="preserve">25.8058681488037</t>
   </si>
   <si>
     <t xml:space="preserve">25.9533805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">25.676794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.658353805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0775146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4001998901367</t>
+    <t xml:space="preserve">25.6767921447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6583518981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0775108337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4002017974854</t>
   </si>
   <si>
     <t xml:space="preserve">25.2619075775146</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3264427185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8009243011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4186420440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6441860198975</t>
+    <t xml:space="preserve">25.3264446258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8009204864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4186401367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6441879272461</t>
   </si>
   <si>
     <t xml:space="preserve">24.8562393188477</t>
@@ -995,55 +995,55 @@
     <t xml:space="preserve">24.9576568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8931217193604</t>
+    <t xml:space="preserve">24.8931198120117</t>
   </si>
   <si>
     <t xml:space="preserve">23.187479019165</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9754257202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1229419708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2335777282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9938678741455</t>
+    <t xml:space="preserve">22.9754276275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1229400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2335796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9938659667969</t>
   </si>
   <si>
     <t xml:space="preserve">23.0123062133789</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7818126678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.671178817749</t>
+    <t xml:space="preserve">22.781810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6711769104004</t>
   </si>
   <si>
     <t xml:space="preserve">22.4960041046143</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7264976501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5052223205566</t>
+    <t xml:space="preserve">22.7264957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5052242279053</t>
   </si>
   <si>
     <t xml:space="preserve">22.3208293914795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5882015228271</t>
+    <t xml:space="preserve">22.5881996154785</t>
   </si>
   <si>
     <t xml:space="preserve">23.1137237548828</t>
   </si>
   <si>
-    <t xml:space="preserve">22.910888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3995323181152</t>
+    <t xml:space="preserve">22.9108905792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3995304107666</t>
   </si>
   <si>
     <t xml:space="preserve">23.7775402069092</t>
@@ -1052,19 +1052,19 @@
     <t xml:space="preserve">23.6208076477051</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1413841247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9846477508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8740119934082</t>
+    <t xml:space="preserve">23.1413822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9846496582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8740100860596</t>
   </si>
   <si>
     <t xml:space="preserve">22.7357139587402</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6896152496338</t>
+    <t xml:space="preserve">22.6896190643311</t>
   </si>
   <si>
     <t xml:space="preserve">23.3257751464844</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">23.9803733825684</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9711494445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0633506774902</t>
+    <t xml:space="preserve">23.9711513519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.063346862793</t>
   </si>
   <si>
     <t xml:space="preserve">24.2477416992188</t>
@@ -1088,10 +1088,10 @@
     <t xml:space="preserve">24.3860378265381</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1555442810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6165313720703</t>
+    <t xml:space="preserve">24.1555461883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6165294647217</t>
   </si>
   <si>
     <t xml:space="preserve">25.8611869812012</t>
@@ -1103,22 +1103,22 @@
     <t xml:space="preserve">25.2158088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1697063446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080024719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4463005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5384941101074</t>
+    <t xml:space="preserve">25.1697082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4462985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5384960174561</t>
   </si>
   <si>
     <t xml:space="preserve">25.1236114501953</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4321365356445</t>
+    <t xml:space="preserve">24.4321346282959</t>
   </si>
   <si>
     <t xml:space="preserve">23.6484622955322</t>
@@ -1130,13 +1130,13 @@
     <t xml:space="preserve">24.109447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3399391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2016429901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2938423156738</t>
+    <t xml:space="preserve">24.3399353027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2016448974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2938404083252</t>
   </si>
   <si>
     <t xml:space="preserve">24.7548236846924</t>
@@ -1148,49 +1148,49 @@
     <t xml:space="preserve">24.985315322876</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4924011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7228889465332</t>
+    <t xml:space="preserve">25.492395401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7228870391846</t>
   </si>
   <si>
     <t xml:space="preserve">24.5704307556152</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5845947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9994831085205</t>
+    <t xml:space="preserve">25.5845985412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9994812011719</t>
   </si>
   <si>
     <t xml:space="preserve">26.4143657684326</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5668258666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.751220703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0739059448242</t>
+    <t xml:space="preserve">27.5668239593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7512149810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0739078521729</t>
   </si>
   <si>
     <t xml:space="preserve">27.5207252502441</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7370529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5065612792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0314121246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5243320465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3682689666748</t>
+    <t xml:space="preserve">26.7370567321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5065650939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0314140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5243339538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3682651519775</t>
   </si>
   <si>
     <t xml:space="preserve">26.5987586975098</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">26.4604625701904</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2299747467041</t>
+    <t xml:space="preserve">26.2299728393555</t>
   </si>
   <si>
     <t xml:space="preserve">26.3221683502197</t>
@@ -1208,37 +1208,37 @@
     <t xml:space="preserve">27.1980381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2760715484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2902336120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3824329376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4746265411377</t>
+    <t xml:space="preserve">26.2760696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2902355194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3824310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4746284484863</t>
   </si>
   <si>
     <t xml:space="preserve">26.552661895752</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8292541503906</t>
+    <t xml:space="preserve">26.8292503356934</t>
   </si>
   <si>
     <t xml:space="preserve">27.1058387756348</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8753471374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8434143066406</t>
+    <t xml:space="preserve">26.8753490447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8434181213379</t>
   </si>
   <si>
     <t xml:space="preserve">28.7653846740723</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5809879302979</t>
+    <t xml:space="preserve">28.5809917449951</t>
   </si>
   <si>
     <t xml:space="preserve">27.9356117248535</t>
@@ -1253,10 +1253,10 @@
     <t xml:space="preserve">28.7192840576172</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1200065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0597438812256</t>
+    <t xml:space="preserve">28.1200046539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.059741973877</t>
   </si>
   <si>
     <t xml:space="preserve">26.9675464630127</t>
@@ -1268,67 +1268,67 @@
     <t xml:space="preserve">26.6909561157227</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7831516265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.045581817627</t>
+    <t xml:space="preserve">26.7831535339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0455799102783</t>
   </si>
   <si>
     <t xml:space="preserve">27.6590213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9214477539062</t>
+    <t xml:space="preserve">26.9214458465576</t>
   </si>
   <si>
     <t xml:space="preserve">26.1828804016113</t>
   </si>
   <si>
-    <t xml:space="preserve">26.088695526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4654312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2299728393555</t>
+    <t xml:space="preserve">26.0886974334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4654293060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2299709320068</t>
   </si>
   <si>
     <t xml:space="preserve">25.8061485290527</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7119617462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1468696594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3352355957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9114112854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.487585067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3934001922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9224872589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.263204574585</t>
+    <t xml:space="preserve">25.7119655609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1468677520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3352317810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9114093780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4875869750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.393404006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9224853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2632083892822</t>
   </si>
   <si>
     <t xml:space="preserve">23.0277481079102</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0748405456543</t>
+    <t xml:space="preserve">23.0748386383057</t>
   </si>
   <si>
     <t xml:space="preserve">22.7451992034912</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6039257049561</t>
+    <t xml:space="preserve">22.6039237976074</t>
   </si>
   <si>
     <t xml:space="preserve">22.5097427368164</t>
@@ -1337,19 +1337,19 @@
     <t xml:space="preserve">22.4155597686768</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1801013946533</t>
+    <t xml:space="preserve">22.1800994873047</t>
   </si>
   <si>
     <t xml:space="preserve">22.0388278961182</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8504619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4626483917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2271938323975</t>
+    <t xml:space="preserve">21.8504600524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4626541137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2271919250488</t>
   </si>
   <si>
     <t xml:space="preserve">23.4044799804688</t>
@@ -1358,19 +1358,19 @@
     <t xml:space="preserve">23.2161159515381</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8864727020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4986667633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5568370819092</t>
+    <t xml:space="preserve">22.886474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4986629486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5568332672119</t>
   </si>
   <si>
     <t xml:space="preserve">22.1330089569092</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6620941162109</t>
+    <t xml:space="preserve">21.6620979309082</t>
   </si>
   <si>
     <t xml:space="preserve">21.1911811828613</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">21.0028133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0969982147217</t>
+    <t xml:space="preserve">21.096996307373</t>
   </si>
   <si>
     <t xml:space="preserve">20.8615379333496</t>
@@ -1391,16 +1391,16 @@
     <t xml:space="preserve">21.4737281799316</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2742862701416</t>
+    <t xml:space="preserve">22.2742824554443</t>
   </si>
   <si>
     <t xml:space="preserve">21.7562789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9446430206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5679092407227</t>
+    <t xml:space="preserve">21.9446449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5679130554199</t>
   </si>
   <si>
     <t xml:space="preserve">21.5208206176758</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">21.2382717132568</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8393821716309</t>
+    <t xml:space="preserve">22.8393840789795</t>
   </si>
   <si>
     <t xml:space="preserve">22.7922916412354</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">23.5457534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6399402618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7341213226318</t>
+    <t xml:space="preserve">23.6399421691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7341232299805</t>
   </si>
   <si>
     <t xml:space="preserve">23.6870307922363</t>
@@ -1433,130 +1433,130 @@
     <t xml:space="preserve">23.781213760376</t>
   </si>
   <si>
-    <t xml:space="preserve">24.016674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2992191314697</t>
+    <t xml:space="preserve">24.0166721343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2992172241211</t>
   </si>
   <si>
     <t xml:space="preserve">24.1579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2521286010742</t>
+    <t xml:space="preserve">24.2521266937256</t>
   </si>
   <si>
     <t xml:space="preserve">24.7230434417725</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6288585662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.675952911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5817699432373</t>
+    <t xml:space="preserve">24.6288604736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6759510040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5817680358887</t>
   </si>
   <si>
     <t xml:space="preserve">24.770133972168</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9585018157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9003295898438</t>
+    <t xml:space="preserve">24.9584999084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.900333404541</t>
   </si>
   <si>
     <t xml:space="preserve">25.7590579986572</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9474201202393</t>
+    <t xml:space="preserve">25.9474220275879</t>
   </si>
   <si>
     <t xml:space="preserve">26.277063369751</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9363460540771</t>
+    <t xml:space="preserve">26.9363441467285</t>
   </si>
   <si>
     <t xml:space="preserve">26.983434677124</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8421630859375</t>
+    <t xml:space="preserve">26.8421592712402</t>
   </si>
   <si>
     <t xml:space="preserve">26.7479782104492</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2659873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4543495178223</t>
+    <t xml:space="preserve">27.265983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4543514251709</t>
   </si>
   <si>
     <t xml:space="preserve">27.501443862915</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3130760192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0776195526123</t>
+    <t xml:space="preserve">27.3130779266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0776214599609</t>
   </si>
   <si>
     <t xml:space="preserve">26.7008876800537</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6537933349609</t>
+    <t xml:space="preserve">26.6537971496582</t>
   </si>
   <si>
     <t xml:space="preserve">26.6067047119141</t>
   </si>
   <si>
-    <t xml:space="preserve">25.994514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1357879638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0416069030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6177825927734</t>
+    <t xml:space="preserve">25.9945125579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1357898712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0416030883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6177806854248</t>
   </si>
   <si>
     <t xml:space="preserve">25.4294166564941</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0055904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0997772216797</t>
+    <t xml:space="preserve">25.00559425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0997734069824</t>
   </si>
   <si>
     <t xml:space="preserve">24.8643169403076</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4404945373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5235996246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.371244430542</t>
+    <t xml:space="preserve">24.4404964447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5235977172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3712463378906</t>
   </si>
   <si>
     <t xml:space="preserve">26.3241558074951</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7950706481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.889253616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0305252075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1718006134033</t>
+    <t xml:space="preserve">26.7950687408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8892517089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0305290222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.171802520752</t>
   </si>
   <si>
     <t xml:space="preserve">27.5485343933105</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">28.1136302947998</t>
   </si>
   <si>
-    <t xml:space="preserve">28.396183013916</t>
+    <t xml:space="preserve">28.3961791992188</t>
   </si>
   <si>
     <t xml:space="preserve">28.7258224487305</t>
@@ -1580,34 +1580,34 @@
     <t xml:space="preserve">29.9502010345459</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7618350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3269348144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5042190551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6925926208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4460487365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4931449890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4820709228516</t>
+    <t xml:space="preserve">29.761833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3269329071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3740253448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5042247772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.692590713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4460525512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4931411743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4820594787598</t>
   </si>
   <si>
     <t xml:space="preserve">33.6704292297363</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2936973571777</t>
+    <t xml:space="preserve">33.293701171875</t>
   </si>
   <si>
     <t xml:space="preserve">33.576244354248</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">33.2466087341309</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8698806762695</t>
+    <t xml:space="preserve">32.869873046875</t>
   </si>
   <si>
     <t xml:space="preserve">33.1524238586426</t>
@@ -1628,46 +1628,46 @@
     <t xml:space="preserve">33.0582389831543</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5873222351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3047752380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9280414581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4571304321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3629417419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.892032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0803966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0333080291748</t>
+    <t xml:space="preserve">32.5873260498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3047790527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9280452728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4571266174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3629474639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8920288085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0804004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0333042144775</t>
   </si>
   <si>
     <t xml:space="preserve">30.6565742492676</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6094837188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2687606811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9862155914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4100379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8449382781982</t>
+    <t xml:space="preserve">30.6094818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2687664031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9862174987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4100360870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8449401855469</t>
   </si>
   <si>
     <t xml:space="preserve">31.1745796203613</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">31.8809509277344</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0222282409668</t>
+    <t xml:space="preserve">32.0222244262695</t>
   </si>
   <si>
     <t xml:space="preserve">31.7396793365479</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0000686645508</t>
+    <t xml:space="preserve">34.000072479248</t>
   </si>
   <si>
     <t xml:space="preserve">34.4709815979004</t>
@@ -1691,19 +1691,19 @@
     <t xml:space="preserve">35.78955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5901031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7784690856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.155200958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.673210144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0846710205078</t>
+    <t xml:space="preserve">36.5900993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7784652709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1552047729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6732063293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0846786499023</t>
   </si>
   <si>
     <t xml:space="preserve">38.2282104492188</t>
@@ -1712,13 +1712,13 @@
     <t xml:space="preserve">37.3669967651367</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7976036071777</t>
+    <t xml:space="preserve">37.797607421875</t>
   </si>
   <si>
     <t xml:space="preserve">38.1803665161133</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3717422485352</t>
+    <t xml:space="preserve">38.3717498779297</t>
   </si>
   <si>
     <t xml:space="preserve">37.9411430358887</t>
@@ -1727,13 +1727,13 @@
     <t xml:space="preserve">37.9889907836914</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8454475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3191566467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8501930236816</t>
+    <t xml:space="preserve">37.8454513549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3191604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8501968383789</t>
   </si>
   <si>
     <t xml:space="preserve">38.7545051574707</t>
@@ -1751,43 +1751,43 @@
     <t xml:space="preserve">38.4674377441406</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1325187683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8980445861816</t>
+    <t xml:space="preserve">38.1325149536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8980484008789</t>
   </si>
   <si>
     <t xml:space="preserve">38.7066612243652</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2760581970215</t>
+    <t xml:space="preserve">38.2760543823242</t>
   </si>
   <si>
     <t xml:space="preserve">38.5631256103516</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4195976257324</t>
+    <t xml:space="preserve">38.4195938110352</t>
   </si>
   <si>
     <t xml:space="preserve">39.3764953613281</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1372718811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.185115814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2807998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9027900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1946029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1036605834961</t>
+    <t xml:space="preserve">39.1372680664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1851081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2808036804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9027938842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1946067810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1036643981934</t>
   </si>
   <si>
     <t xml:space="preserve">42.5342712402344</t>
@@ -1799,10 +1799,10 @@
     <t xml:space="preserve">40.8118476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7161521911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.912281036377</t>
+    <t xml:space="preserve">40.7161560058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9122848510742</t>
   </si>
   <si>
     <t xml:space="preserve">43.0605621337891</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">43.4433250427246</t>
   </si>
   <si>
-    <t xml:space="preserve">44.017463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6347045898438</t>
+    <t xml:space="preserve">44.0174674987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6347007751465</t>
   </si>
   <si>
     <t xml:space="preserve">43.2041015625</t>
@@ -1832,19 +1832,19 @@
     <t xml:space="preserve">42.9170303344727</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9265251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4049758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2614326477051</t>
+    <t xml:space="preserve">44.9265174865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.404972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2614364624023</t>
   </si>
   <si>
     <t xml:space="preserve">45.5963554382324</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6536865234375</t>
+    <t xml:space="preserve">47.653694152832</t>
   </si>
   <si>
     <t xml:space="preserve">48.8976631164551</t>
@@ -1853,25 +1853,25 @@
     <t xml:space="preserve">48.6105918884277</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1847343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9933471679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7588729858398</t>
+    <t xml:space="preserve">49.1847381591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9933547973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7588768005371</t>
   </si>
   <si>
     <t xml:space="preserve">49.2804183959961</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6631813049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3761138916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5674896240234</t>
+    <t xml:space="preserve">49.6631851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3761100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5674934387207</t>
   </si>
   <si>
     <t xml:space="preserve">50.6200866699219</t>
@@ -1883,94 +1883,94 @@
     <t xml:space="preserve">52.7252655029297</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6295738220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.9597434997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8640556335449</t>
+    <t xml:space="preserve">52.6295776367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9597473144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8640518188477</t>
   </si>
   <si>
     <t xml:space="preserve">51.6726760864258</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4192123413086</t>
+    <t xml:space="preserve">48.4192085266113</t>
   </si>
   <si>
     <t xml:space="preserve">48.3235206604004</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0459480285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3856086730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.907154083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.854564666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4287071228027</t>
+    <t xml:space="preserve">50.0459403991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3856048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9071578979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8545608520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4287033081055</t>
   </si>
   <si>
     <t xml:space="preserve">52.5338859558105</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0649299621582</t>
+    <t xml:space="preserve">54.0649337768555</t>
   </si>
   <si>
     <t xml:space="preserve">53.2994079589844</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4381980895996</t>
+    <t xml:space="preserve">52.4381942749023</t>
   </si>
   <si>
     <t xml:space="preserve">47.3666191101074</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9838562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.361873626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7398872375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9743614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.586856842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7687492370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6493263244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.596736907959</t>
+    <t xml:space="preserve">46.9838600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3618774414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7398834228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.974365234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5868606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7687454223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6493225097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5967330932617</t>
   </si>
   <si>
     <t xml:space="preserve">30.0945510864258</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4820575714111</t>
+    <t xml:space="preserve">31.4820594787598</t>
   </si>
   <si>
     <t xml:space="preserve">29.1854934692383</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5299015045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0992984771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3816184997559</t>
+    <t xml:space="preserve">31.5299053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0992965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3816204071045</t>
   </si>
   <si>
     <t xml:space="preserve">34.9269027709961</t>
@@ -1979,19 +1979,19 @@
     <t xml:space="preserve">36.410099029541</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5010375976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3096656799316</t>
+    <t xml:space="preserve">35.5010452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3096618652344</t>
   </si>
   <si>
     <t xml:space="preserve">34.5441398620605</t>
   </si>
   <si>
-    <t xml:space="preserve">35.070442199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0799293518066</t>
+    <t xml:space="preserve">35.0704345703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0799331665039</t>
   </si>
   <si>
     <t xml:space="preserve">37.2234649658203</t>
@@ -2009,55 +2009,55 @@
     <t xml:space="preserve">39.998477935791</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7351417541504</t>
+    <t xml:space="preserve">44.7351379394531</t>
   </si>
   <si>
     <t xml:space="preserve">45.9791107177734</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4528198242188</t>
+    <t xml:space="preserve">45.4528160095215</t>
   </si>
   <si>
     <t xml:space="preserve">45.0700569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3571319580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1179008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4575576782227</t>
+    <t xml:space="preserve">45.3571281433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1179046630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4575614929199</t>
   </si>
   <si>
     <t xml:space="preserve">45.6441955566406</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8786811828613</t>
+    <t xml:space="preserve">44.8786773681641</t>
   </si>
   <si>
     <t xml:space="preserve">45.3092842102051</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1657485961914</t>
+    <t xml:space="preserve">45.1657447814941</t>
   </si>
   <si>
     <t xml:space="preserve">44.2088470458984</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1562538146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9217758178711</t>
+    <t xml:space="preserve">43.15625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9217720031738</t>
   </si>
   <si>
     <t xml:space="preserve">41.8644371032715</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5821151733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0222091674805</t>
+    <t xml:space="preserve">42.5821113586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0222129821777</t>
   </si>
   <si>
     <t xml:space="preserve">45.5485076904297</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">47.5101585388184</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7015380859375</t>
+    <t xml:space="preserve">47.7015342712402</t>
   </si>
   <si>
     <t xml:space="preserve">48.7062873840332</t>
@@ -2075,25 +2075,25 @@
     <t xml:space="preserve">47.9407577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5149040222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4813003540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1942253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7683715820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2899131774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1080284118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9692420959473</t>
+    <t xml:space="preserve">48.5149002075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4812965393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1942291259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7683639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2899169921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1080322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.96923828125</t>
   </si>
   <si>
     <t xml:space="preserve">53.4907913208008</t>
@@ -2102,136 +2102,136 @@
     <t xml:space="preserve">55.1175231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6916618347168</t>
+    <t xml:space="preserve">55.6916656494141</t>
   </si>
   <si>
     <t xml:space="preserve">55.5002822875977</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3520011901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6390724182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.830451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4045906066895</t>
+    <t xml:space="preserve">54.3519973754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6390686035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8304481506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4045944213867</t>
   </si>
   <si>
     <t xml:space="preserve">56.744255065918</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9356384277344</t>
+    <t xml:space="preserve">56.9356346130371</t>
   </si>
   <si>
     <t xml:space="preserve">57.1270141601562</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2658042907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9787330627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3183975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6580581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2227058410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7011566162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3614959716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.988224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.849437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.3373794555664</t>
+    <t xml:space="preserve">56.2658004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9787368774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3183937072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6580543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2227020263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7011604309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3614921569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9882278442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8494338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.3373756408691</t>
   </si>
   <si>
     <t xml:space="preserve">63.4425659179688</t>
   </si>
   <si>
-    <t xml:space="preserve">62.2942848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3468742370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7296257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6339416503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3037643432617</t>
+    <t xml:space="preserve">62.2942810058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.346866607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7296295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6339454650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3037719726562</t>
   </si>
   <si>
     <t xml:space="preserve">64.5908432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">65.9305038452148</t>
+    <t xml:space="preserve">65.9305114746094</t>
   </si>
   <si>
     <t xml:space="preserve">66.6960220336914</t>
   </si>
   <si>
-    <t xml:space="preserve">65.3563613891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.9830932617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.1744766235352</t>
+    <t xml:space="preserve">65.3563690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9831008911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.1744689941406</t>
   </si>
   <si>
     <t xml:space="preserve">66.5046463012695</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8443145751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.0451812744141</t>
+    <t xml:space="preserve">67.8443222045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.0451889038086</t>
   </si>
   <si>
     <t xml:space="preserve">69.1839752197266</t>
   </si>
   <si>
-    <t xml:space="preserve">71.2891540527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8106994628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6193313598633</t>
+    <t xml:space="preserve">71.2891464233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8107070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6193237304688</t>
   </si>
   <si>
     <t xml:space="preserve">71.7676086425781</t>
   </si>
   <si>
-    <t xml:space="preserve">72.0546798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0020751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.4710311889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.9925918579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9494857788086</t>
+    <t xml:space="preserve">72.0546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0020904541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.4710388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.9925994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9495010375977</t>
   </si>
   <si>
     <t xml:space="preserve">68.8012161254883</t>
@@ -2240,10 +2240,10 @@
     <t xml:space="preserve">69.6624221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">76.552116394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.7003860473633</t>
+    <t xml:space="preserve">76.5521087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.7003936767578</t>
   </si>
   <si>
     <t xml:space="preserve">75.8822860717773</t>
@@ -2255,43 +2255,43 @@
     <t xml:space="preserve">73.8727874755859</t>
   </si>
   <si>
-    <t xml:space="preserve">74.8296813964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.8917846679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.274543762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.7960891723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.4228210449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.7624740600586</t>
+    <t xml:space="preserve">74.8296890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.8917694091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.2745361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.7960968017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.4228134155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.7624816894531</t>
   </si>
   <si>
     <t xml:space="preserve">82.0064468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">81.5279998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.910758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.3892059326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4323043823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.1452407836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4754028320312</t>
+    <t xml:space="preserve">81.5279922485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9107666015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.3892135620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4323120117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1452484130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4753952026367</t>
   </si>
   <si>
     <t xml:space="preserve">81.7193832397461</t>
@@ -2303,16 +2303,16 @@
     <t xml:space="preserve">83.3461074829102</t>
   </si>
   <si>
-    <t xml:space="preserve">80.9538497924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.77197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2935180664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.0305633544922</t>
+    <t xml:space="preserve">80.953857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7719802856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2935104370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.0305709838867</t>
   </si>
   <si>
     <t xml:space="preserve">79.3271331787109</t>
@@ -2324,19 +2324,19 @@
     <t xml:space="preserve">82.1021423339844</t>
   </si>
   <si>
-    <t xml:space="preserve">76.7434844970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.5185165405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8055801391602</t>
+    <t xml:space="preserve">76.7434997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.5185012817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8055877685547</t>
   </si>
   <si>
     <t xml:space="preserve">82.4849014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3797149658203</t>
+    <t xml:space="preserve">80.3797225952148</t>
   </si>
   <si>
     <t xml:space="preserve">78.6572875976562</t>
@@ -2345,31 +2345,31 @@
     <t xml:space="preserve">78.4659118652344</t>
   </si>
   <si>
-    <t xml:space="preserve">84.6857757568359</t>
+    <t xml:space="preserve">84.6857681274414</t>
   </si>
   <si>
     <t xml:space="preserve">85.3556060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">83.0590438842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.9297561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.173713684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2694091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3220062255859</t>
+    <t xml:space="preserve">83.0590362548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.9297485351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.1737213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.269401550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3219985961914</t>
   </si>
   <si>
     <t xml:space="preserve">86.7909545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">90.9056396484375</t>
+    <t xml:space="preserve">90.905632019043</t>
   </si>
   <si>
     <t xml:space="preserve">91.3840866088867</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">97.2211837768555</t>
   </si>
   <si>
-    <t xml:space="preserve">100.474639892578</t>
+    <t xml:space="preserve">100.474647521973</t>
   </si>
   <si>
     <t xml:space="preserve">101.622932434082</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">101.240173339844</t>
   </si>
   <si>
-    <t xml:space="preserve">97.9866943359375</t>
+    <t xml:space="preserve">97.9867095947266</t>
   </si>
   <si>
     <t xml:space="preserve">98.5608367919922</t>
@@ -2408,31 +2408,31 @@
     <t xml:space="preserve">95.6901397705078</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8289184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.307373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2547836303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0298080444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5418548583984</t>
+    <t xml:space="preserve">94.8289337158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3073883056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2547912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.446159362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0298004150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.541862487793</t>
   </si>
   <si>
     <t xml:space="preserve">94.1591033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8720245361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0634155273438</t>
+    <t xml:space="preserve">93.8720169067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0634078979492</t>
   </si>
   <si>
     <t xml:space="preserve">93.3935699462891</t>
@@ -2441,25 +2441,25 @@
     <t xml:space="preserve">93.6806488037109</t>
   </si>
   <si>
-    <t xml:space="preserve">92.9151153564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.2978820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.723747253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3504791259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6039505004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.431549072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.876396179199</t>
+    <t xml:space="preserve">92.9151229858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.2978897094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7237548828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3504867553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6039428710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.431541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.876388549805</t>
   </si>
   <si>
     <t xml:space="preserve">104.493629455566</t>
@@ -2468,10 +2468,10 @@
     <t xml:space="preserve">106.598815917969</t>
   </si>
   <si>
-    <t xml:space="preserve">107.364334106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.660903930664</t>
+    <t xml:space="preserve">107.36434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.66089630127</t>
   </si>
   <si>
     <t xml:space="preserve">110.235046386719</t>
@@ -2480,13 +2480,13 @@
     <t xml:space="preserve">105.641914367676</t>
   </si>
   <si>
-    <t xml:space="preserve">106.21605682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.938484191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.555725097656</t>
+    <t xml:space="preserve">106.216064453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.9384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.555717468262</t>
   </si>
   <si>
     <t xml:space="preserve">109.469520568848</t>
@@ -2495,46 +2495,46 @@
     <t xml:space="preserve">107.747100830078</t>
   </si>
   <si>
-    <t xml:space="preserve">108.704002380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.197082519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5177459716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.7091293334961</t>
+    <t xml:space="preserve">108.703994750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.197074890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5177536010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.7091217041016</t>
   </si>
   <si>
     <t xml:space="preserve">103.345352172852</t>
   </si>
   <si>
-    <t xml:space="preserve">103.536743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.024673461914</t>
+    <t xml:space="preserve">103.536727905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.024681091309</t>
   </si>
   <si>
     <t xml:space="preserve">106.981582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">108.512619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.833297729492</t>
+    <t xml:space="preserve">108.51261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.833282470703</t>
   </si>
   <si>
     <t xml:space="preserve">101.048789978027</t>
   </si>
   <si>
-    <t xml:space="preserve">102.388450622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.15397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.962600708008</t>
+    <t xml:space="preserve">102.388458251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.153984069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.962593078613</t>
   </si>
   <si>
     <t xml:space="preserve">105.450531005859</t>
@@ -2543,25 +2543,25 @@
     <t xml:space="preserve">102.00569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">103.919486999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.407432556152</t>
+    <t xml:space="preserve">103.919494628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.407440185547</t>
   </si>
   <si>
     <t xml:space="preserve">109.086761474609</t>
   </si>
   <si>
-    <t xml:space="preserve">110.809181213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.679893493652</t>
+    <t xml:space="preserve">110.809188842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.679885864258</t>
   </si>
   <si>
     <t xml:space="preserve">110.043655395508</t>
   </si>
   <si>
-    <t xml:space="preserve">107.172950744629</t>
+    <t xml:space="preserve">107.172958374023</t>
   </si>
   <si>
     <t xml:space="preserve">111.000564575195</t>
@@ -2570,55 +2570,55 @@
     <t xml:space="preserve">112.914367675781</t>
   </si>
   <si>
-    <t xml:space="preserve">109.852279663086</t>
+    <t xml:space="preserve">109.85228729248</t>
   </si>
   <si>
     <t xml:space="preserve">110.426422119141</t>
   </si>
   <si>
-    <t xml:space="preserve">111.383323669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.340225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.445411682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.29712677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.722991943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.019554138184</t>
+    <t xml:space="preserve">111.383331298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.340232849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.445404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.297134399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.722984313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.019546508789</t>
   </si>
   <si>
     <t xml:space="preserve">115.593688964844</t>
   </si>
   <si>
-    <t xml:space="preserve">115.210929870605</t>
+    <t xml:space="preserve">115.2109375</t>
   </si>
   <si>
     <t xml:space="preserve">116.741973876953</t>
   </si>
   <si>
-    <t xml:space="preserve">116.167823791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.78507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.550590515137</t>
+    <t xml:space="preserve">116.167831420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.550598144531</t>
   </si>
   <si>
     <t xml:space="preserve">119.804054260254</t>
   </si>
   <si>
-    <t xml:space="preserve">120.186813354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.100608825684</t>
+    <t xml:space="preserve">120.186828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.100616455078</t>
   </si>
   <si>
     <t xml:space="preserve">122.86612701416</t>
@@ -2630,52 +2630,52 @@
     <t xml:space="preserve">131.478256225586</t>
   </si>
   <si>
-    <t xml:space="preserve">127.267883300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.459251403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.990325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.052398681641</t>
+    <t xml:space="preserve">127.267890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.459259033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.990295410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.05241394043</t>
   </si>
   <si>
     <t xml:space="preserve">134.157577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">133.774841308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.626541137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.435134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.923110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.6455078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.411056518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.305862426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.86100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.731735229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.262741088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.793792724609</t>
+    <t xml:space="preserve">133.774826049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.626525878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.435150146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.923095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.645523071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.411041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.305847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.861022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.731719970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.262756347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.793807983398</t>
   </si>
   <si>
     <t xml:space="preserve">138.176559448242</t>
@@ -2684,34 +2684,34 @@
     <t xml:space="preserve">137.028274536133</t>
   </si>
   <si>
-    <t xml:space="preserve">138.559326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.898971557617</t>
+    <t xml:space="preserve">138.559310913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.899002075195</t>
   </si>
   <si>
     <t xml:space="preserve">136.454147338867</t>
   </si>
   <si>
-    <t xml:space="preserve">138.750686645508</t>
+    <t xml:space="preserve">138.750701904297</t>
   </si>
   <si>
     <t xml:space="preserve">139.324844360352</t>
   </si>
   <si>
-    <t xml:space="preserve">137.98518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.497268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.492126464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.874862670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.109359741211</t>
+    <t xml:space="preserve">137.985198974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.497253417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.492111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.874877929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.109375</t>
   </si>
   <si>
     <t xml:space="preserve">142.195556640625</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">143.91796875</t>
   </si>
   <si>
-    <t xml:space="preserve">144.683486938477</t>
+    <t xml:space="preserve">144.683471679688</t>
   </si>
   <si>
     <t xml:space="preserve">145.25764465332</t>
@@ -2738,49 +2738,49 @@
     <t xml:space="preserve">146.788665771484</t>
   </si>
   <si>
-    <t xml:space="preserve">149.276626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.999053955078</t>
+    <t xml:space="preserve">149.276641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.999038696289</t>
   </si>
   <si>
     <t xml:space="preserve">150.424896240234</t>
   </si>
   <si>
-    <t xml:space="preserve">153.486968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.338684082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.400772094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.190414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.888748168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.037033081055</t>
+    <t xml:space="preserve">153.486999511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.338714599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.400787353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.1904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.888732910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.037002563477</t>
   </si>
   <si>
     <t xml:space="preserve">158.654266357422</t>
   </si>
   <si>
-    <t xml:space="preserve">159.61116027832</t>
+    <t xml:space="preserve">159.611175537109</t>
   </si>
   <si>
     <t xml:space="preserve">161.333587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">161.524948120117</t>
+    <t xml:space="preserve">161.524963378906</t>
   </si>
   <si>
     <t xml:space="preserve">163.438766479492</t>
   </si>
   <si>
-    <t xml:space="preserve">163.821517944336</t>
+    <t xml:space="preserve">163.821533203125</t>
   </si>
   <si>
     <t xml:space="preserve">168.606018066406</t>
@@ -2789,19 +2789,19 @@
     <t xml:space="preserve">173.773300170898</t>
   </si>
   <si>
-    <t xml:space="preserve">170.328460693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.161193847656</t>
+    <t xml:space="preserve">170.32844543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.161178588867</t>
   </si>
   <si>
     <t xml:space="preserve">168.03190612793</t>
   </si>
   <si>
-    <t xml:space="preserve">165.352569580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.759429931641</t>
+    <t xml:space="preserve">165.352554321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.75944519043</t>
   </si>
   <si>
     <t xml:space="preserve">162.099090576172</t>
@@ -2810,10 +2810,10 @@
     <t xml:space="preserve">171.668121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">167.074996948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.930511474609</t>
+    <t xml:space="preserve">167.074981689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.93049621582</t>
   </si>
   <si>
     <t xml:space="preserve">161.353576660156</t>
@@ -2825,22 +2825,22 @@
     <t xml:space="preserve">159.045761108398</t>
   </si>
   <si>
-    <t xml:space="preserve">152.122360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.583602905273</t>
+    <t xml:space="preserve">152.122375488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.583618164062</t>
   </si>
   <si>
     <t xml:space="preserve">147.314468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">150.391510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.199203491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.083740234375</t>
+    <t xml:space="preserve">150.391525268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.19921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.083709716797</t>
   </si>
   <si>
     <t xml:space="preserve">151.737747192383</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">149.622268676758</t>
   </si>
   <si>
-    <t xml:space="preserve">155.199432373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.545669555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.968704223633</t>
+    <t xml:space="preserve">155.199447631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.545654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.968719482422</t>
   </si>
   <si>
     <t xml:space="preserve">154.430191040039</t>
@@ -2867,13 +2867,13 @@
     <t xml:space="preserve">166.353805541992</t>
   </si>
   <si>
-    <t xml:space="preserve">170.200134277344</t>
+    <t xml:space="preserve">170.200119018555</t>
   </si>
   <si>
     <t xml:space="preserve">168.469284057617</t>
   </si>
   <si>
-    <t xml:space="preserve">164.430633544922</t>
+    <t xml:space="preserve">164.430618286133</t>
   </si>
   <si>
     <t xml:space="preserve">165.007583618164</t>
@@ -2882,13 +2882,13 @@
     <t xml:space="preserve">162.507461547852</t>
   </si>
   <si>
-    <t xml:space="preserve">163.469039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.584518432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.161254882812</t>
+    <t xml:space="preserve">163.469055175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.584533691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.161270141602</t>
   </si>
   <si>
     <t xml:space="preserve">163.084426879883</t>
@@ -2897,25 +2897,25 @@
     <t xml:space="preserve">161.738189697266</t>
   </si>
   <si>
-    <t xml:space="preserve">168.853927612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.508163452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.585006713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.392929077148</t>
+    <t xml:space="preserve">168.853912353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.508178710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.584976196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.392913818359</t>
   </si>
   <si>
     <t xml:space="preserve">180.777526855469</t>
   </si>
   <si>
-    <t xml:space="preserve">178.469741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.815963745117</t>
+    <t xml:space="preserve">178.469757080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.815948486328</t>
   </si>
   <si>
     <t xml:space="preserve">181.739120483398</t>
@@ -2924,31 +2924,31 @@
     <t xml:space="preserve">185.008499145508</t>
   </si>
   <si>
-    <t xml:space="preserve">183.085342407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.508407592773</t>
+    <t xml:space="preserve">183.085327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.508392333984</t>
   </si>
   <si>
     <t xml:space="preserve">168.276962280273</t>
   </si>
   <si>
-    <t xml:space="preserve">169.046249389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.584777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.507690429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.046447753906</t>
+    <t xml:space="preserve">169.046234130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.584762573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.507705688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.046463012695</t>
   </si>
   <si>
     <t xml:space="preserve">170.96940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">169.623184204102</t>
+    <t xml:space="preserve">169.623168945312</t>
   </si>
   <si>
     <t xml:space="preserve">169.238540649414</t>
@@ -2960,22 +2960,22 @@
     <t xml:space="preserve">172.700256347656</t>
   </si>
   <si>
-    <t xml:space="preserve">172.123291015625</t>
+    <t xml:space="preserve">172.123306274414</t>
   </si>
   <si>
     <t xml:space="preserve">171.93098449707</t>
   </si>
   <si>
-    <t xml:space="preserve">167.315383911133</t>
+    <t xml:space="preserve">167.315399169922</t>
   </si>
   <si>
     <t xml:space="preserve">163.85368347168</t>
   </si>
   <si>
-    <t xml:space="preserve">166.738433837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.238327026367</t>
+    <t xml:space="preserve">166.738418579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.238311767578</t>
   </si>
   <si>
     <t xml:space="preserve">166.546112060547</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">165.392211914062</t>
   </si>
   <si>
-    <t xml:space="preserve">151.160781860352</t>
+    <t xml:space="preserve">151.160797119141</t>
   </si>
   <si>
     <t xml:space="preserve">158.853454589844</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">158.468826293945</t>
   </si>
   <si>
-    <t xml:space="preserve">157.31494140625</t>
+    <t xml:space="preserve">157.314926147461</t>
   </si>
   <si>
     <t xml:space="preserve">159.815048217773</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">156.930282592773</t>
   </si>
   <si>
-    <t xml:space="preserve">156.161010742188</t>
+    <t xml:space="preserve">156.161026000977</t>
   </si>
   <si>
     <t xml:space="preserve">152.314682006836</t>
@@ -3014,16 +3014,16 @@
     <t xml:space="preserve">145.96826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">146.929840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.353088378906</t>
+    <t xml:space="preserve">146.929824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.353103637695</t>
   </si>
   <si>
     <t xml:space="preserve">153.468597412109</t>
   </si>
   <si>
-    <t xml:space="preserve">153.276260375977</t>
+    <t xml:space="preserve">153.276245117188</t>
   </si>
   <si>
     <t xml:space="preserve">157.122604370117</t>
@@ -3032,34 +3032,34 @@
     <t xml:space="preserve">151.930053710938</t>
   </si>
   <si>
-    <t xml:space="preserve">146.545181274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.968032836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.929351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.660217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.69841003418</t>
+    <t xml:space="preserve">146.545196533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.968017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.92936706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.660232543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.698425292969</t>
   </si>
   <si>
     <t xml:space="preserve">132.506088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">130.198272705078</t>
+    <t xml:space="preserve">130.198287963867</t>
   </si>
   <si>
     <t xml:space="preserve">134.813888549805</t>
   </si>
   <si>
-    <t xml:space="preserve">130.005966186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.775238037109</t>
+    <t xml:space="preserve">130.005981445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.77522277832</t>
   </si>
   <si>
     <t xml:space="preserve">128.852081298828</t>
@@ -3068,40 +3068,40 @@
     <t xml:space="preserve">129.621353149414</t>
   </si>
   <si>
-    <t xml:space="preserve">132.890716552734</t>
+    <t xml:space="preserve">132.890731811523</t>
   </si>
   <si>
     <t xml:space="preserve">137.506317138672</t>
   </si>
   <si>
-    <t xml:space="preserve">136.160125732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.467895507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.583160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.813430786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.659301757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.582702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.198066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.313995361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.852523803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.891189575195</t>
+    <t xml:space="preserve">136.160110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.467910766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.583145141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.813438415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.659309387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.582695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.198059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.314010620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.8525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.891174316406</t>
   </si>
   <si>
     <t xml:space="preserve">140.391067504883</t>
@@ -3113,16 +3113,16 @@
     <t xml:space="preserve">145.00666809082</t>
   </si>
   <si>
-    <t xml:space="preserve">145.775955200195</t>
+    <t xml:space="preserve">145.775939941406</t>
   </si>
   <si>
     <t xml:space="preserve">144.814361572266</t>
   </si>
   <si>
-    <t xml:space="preserve">148.27604675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.275817871094</t>
+    <t xml:space="preserve">148.276031494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.275802612305</t>
   </si>
   <si>
     <t xml:space="preserve">142.602722167969</t>
@@ -3131,19 +3131,19 @@
     <t xml:space="preserve">142.698852539062</t>
   </si>
   <si>
-    <t xml:space="preserve">143.083511352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.525650024414</t>
+    <t xml:space="preserve">143.08349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.525634765625</t>
   </si>
   <si>
     <t xml:space="preserve">141.160339355469</t>
   </si>
   <si>
-    <t xml:space="preserve">140.198760986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.910278320312</t>
+    <t xml:space="preserve">140.198745727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.910263061523</t>
   </si>
   <si>
     <t xml:space="preserve">139.429473876953</t>
@@ -3155,28 +3155,28 @@
     <t xml:space="preserve">140.006439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">138.564056396484</t>
+    <t xml:space="preserve">138.564071655273</t>
   </si>
   <si>
     <t xml:space="preserve">143.179641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">142.314224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.871398925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.525177001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.909820556641</t>
+    <t xml:space="preserve">142.314239501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.87141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.525161743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.90983581543</t>
   </si>
   <si>
     <t xml:space="preserve">133.371520996094</t>
   </si>
   <si>
-    <t xml:space="preserve">128.275115966797</t>
+    <t xml:space="preserve">128.275131225586</t>
   </si>
   <si>
     <t xml:space="preserve">130.294448852539</t>
@@ -3185,19 +3185,19 @@
     <t xml:space="preserve">124.236473083496</t>
   </si>
   <si>
-    <t xml:space="preserve">122.890258789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.563140869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.812744140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.562911987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.389930725098</t>
+    <t xml:space="preserve">122.890266418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.563148498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.81273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.56290435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.389915466309</t>
   </si>
   <si>
     <t xml:space="preserve">115.774551391602</t>
@@ -3206,28 +3206,28 @@
     <t xml:space="preserve">118.755462646484</t>
   </si>
   <si>
-    <t xml:space="preserve">118.082344055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.31330871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.293991088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.101676940918</t>
+    <t xml:space="preserve">118.08235168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.313301086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.293983459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.101669311523</t>
   </si>
   <si>
     <t xml:space="preserve">119.236251831055</t>
   </si>
   <si>
-    <t xml:space="preserve">120.486305236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.736129760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.832290649414</t>
+    <t xml:space="preserve">120.486312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.736137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.832298278809</t>
   </si>
   <si>
     <t xml:space="preserve">119.043937683105</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">121.736366271973</t>
   </si>
   <si>
-    <t xml:space="preserve">124.621124267578</t>
+    <t xml:space="preserve">124.621109008789</t>
   </si>
   <si>
     <t xml:space="preserve">123.274894714355</t>
@@ -3248,19 +3248,19 @@
     <t xml:space="preserve">124.044158935547</t>
   </si>
   <si>
-    <t xml:space="preserve">124.332633972168</t>
+    <t xml:space="preserve">124.332641601562</t>
   </si>
   <si>
     <t xml:space="preserve">127.986656188965</t>
   </si>
   <si>
-    <t xml:space="preserve">128.659759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.69815826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.178741455078</t>
+    <t xml:space="preserve">128.659774780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.698188781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.178749084473</t>
   </si>
   <si>
     <t xml:space="preserve">114.524490356445</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">112.889801025391</t>
   </si>
   <si>
-    <t xml:space="preserve">114.236022949219</t>
+    <t xml:space="preserve">114.236030578613</t>
   </si>
   <si>
     <t xml:space="preserve">111.062789916992</t>
@@ -3278,28 +3278,28 @@
     <t xml:space="preserve">112.216690063477</t>
   </si>
   <si>
-    <t xml:space="preserve">112.505172729492</t>
+    <t xml:space="preserve">112.505180358887</t>
   </si>
   <si>
     <t xml:space="preserve">113.947547912598</t>
   </si>
   <si>
-    <t xml:space="preserve">116.447654724121</t>
+    <t xml:space="preserve">116.447662353516</t>
   </si>
   <si>
     <t xml:space="preserve">115.197608947754</t>
   </si>
   <si>
-    <t xml:space="preserve">119.140083312988</t>
+    <t xml:space="preserve">119.140090942383</t>
   </si>
   <si>
     <t xml:space="preserve">119.909355163574</t>
   </si>
   <si>
-    <t xml:space="preserve">119.428558349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.890037536621</t>
+    <t xml:space="preserve">119.428565979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.890029907227</t>
   </si>
   <si>
     <t xml:space="preserve">115.293762207031</t>
@@ -3320,22 +3320,22 @@
     <t xml:space="preserve">122.986419677734</t>
   </si>
   <si>
-    <t xml:space="preserve">118.27466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.717041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.774780273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.659530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.948226928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.736831665039</t>
+    <t xml:space="preserve">118.274673461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.71703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.774787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.659538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.9482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.73681640625</t>
   </si>
   <si>
     <t xml:space="preserve">130.679077148438</t>
@@ -3344,10 +3344,10 @@
     <t xml:space="preserve">126.832740783691</t>
   </si>
   <si>
-    <t xml:space="preserve">127.794334411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.467437744141</t>
+    <t xml:space="preserve">127.794319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.467468261719</t>
   </si>
   <si>
     <t xml:space="preserve">132.602249145508</t>
@@ -3362,10 +3362,10 @@
     <t xml:space="preserve">125.967323303223</t>
   </si>
   <si>
-    <t xml:space="preserve">126.351959228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.563377380371</t>
+    <t xml:space="preserve">126.351943969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.563369750977</t>
   </si>
   <si>
     <t xml:space="preserve">127.313545227051</t>
@@ -3374,19 +3374,19 @@
     <t xml:space="preserve">128.371292114258</t>
   </si>
   <si>
-    <t xml:space="preserve">126.736595153809</t>
+    <t xml:space="preserve">126.736587524414</t>
   </si>
   <si>
     <t xml:space="preserve">121.447891235352</t>
   </si>
   <si>
-    <t xml:space="preserve">117.6015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.947776794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.19783782959</t>
+    <t xml:space="preserve">117.601554870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.947769165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.197822570801</t>
   </si>
   <si>
     <t xml:space="preserve">121.063255310059</t>
@@ -3395,13 +3395,13 @@
     <t xml:space="preserve">117.505393981934</t>
   </si>
   <si>
-    <t xml:space="preserve">115.870712280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.255340576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.312850952148</t>
+    <t xml:space="preserve">115.870704650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.255348205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.312858581543</t>
   </si>
   <si>
     <t xml:space="preserve">115.582237243652</t>
@@ -3410,10 +3410,10 @@
     <t xml:space="preserve">115.678398132324</t>
   </si>
   <si>
-    <t xml:space="preserve">118.178504943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.909133911133</t>
+    <t xml:space="preserve">118.178512573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.909126281738</t>
   </si>
   <si>
     <t xml:space="preserve">106.596168518066</t>
@@ -5283,6 +5283,9 @@
   </si>
   <si>
     <t xml:space="preserve">83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.6999969482422</t>
   </si>
 </sst>
 </file>
@@ -71531,7 +71534,7 @@
     </row>
     <row r="2536">
       <c r="A2536" s="1" t="n">
-        <v>46009.6912962963</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B2536" t="n">
         <v>82564</v>
@@ -71552,6 +71555,32 @@
         <v>1716</v>
       </c>
       <c r="H2536" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" s="1" t="n">
+        <v>46010.6912037037</v>
+      </c>
+      <c r="B2537" t="n">
+        <v>141822</v>
+      </c>
+      <c r="C2537" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="D2537" t="n">
+        <v>84.3499984741211</v>
+      </c>
+      <c r="E2537" t="n">
+        <v>84.9499969482422</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>88.6999969482422</v>
+      </c>
+      <c r="G2537" t="s">
+        <v>1757</v>
+      </c>
+      <c r="H2537" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5495901107788</t>
+    <t xml:space="preserve">13.5495891571045</t>
   </si>
   <si>
     <t xml:space="preserve">SES.MI</t>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">13.5321073532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2523746490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9464139938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1125078201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8589973449707</t>
+    <t xml:space="preserve">13.2523736953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9464159011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1125059127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8590002059937</t>
   </si>
   <si>
     <t xml:space="preserve">13.0513153076172</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9901218414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9376735687256</t>
+    <t xml:space="preserve">12.9901247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9376726150513</t>
   </si>
   <si>
     <t xml:space="preserve">13.1037645339966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0250911712646</t>
+    <t xml:space="preserve">13.025089263916</t>
   </si>
   <si>
     <t xml:space="preserve">12.8502559661865</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">12.5880060195923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7890644073486</t>
+    <t xml:space="preserve">12.7890653610229</t>
   </si>
   <si>
     <t xml:space="preserve">12.7191314697266</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">12.6841650009155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.605489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3257579803467</t>
+    <t xml:space="preserve">12.6054916381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3257570266724</t>
   </si>
   <si>
     <t xml:space="preserve">12.0460224151611</t>
@@ -104,25 +104,25 @@
     <t xml:space="preserve">12.1771488189697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1421813964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9270887374878</t>
+    <t xml:space="preserve">12.1421804428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9270896911621</t>
   </si>
   <si>
     <t xml:space="preserve">10.9795398712158</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3641719818115</t>
+    <t xml:space="preserve">11.3641729354858</t>
   </si>
   <si>
     <t xml:space="preserve">11.4515905380249</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0984725952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1072149276733</t>
+    <t xml:space="preserve">12.0984716415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1072158813477</t>
   </si>
   <si>
     <t xml:space="preserve">11.8886737823486</t>
@@ -131,49 +131,49 @@
     <t xml:space="preserve">11.9760894775391</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9323806762695</t>
+    <t xml:space="preserve">11.9323816299438</t>
   </si>
   <si>
     <t xml:space="preserve">12.0110559463501</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0809879302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8012552261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334400177002</t>
+    <t xml:space="preserve">12.0809888839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8012571334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334390640259</t>
   </si>
   <si>
     <t xml:space="preserve">11.8274803161621</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0635061264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5005893707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.675422668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7978086471558</t>
+    <t xml:space="preserve">12.0635070800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5005903244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6754236221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7978076934814</t>
   </si>
   <si>
     <t xml:space="preserve">13.1649570465088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1562156677246</t>
+    <t xml:space="preserve">13.1562147140503</t>
   </si>
   <si>
     <t xml:space="preserve">13.0687990188599</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1212482452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1911821365356</t>
+    <t xml:space="preserve">13.1212501525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1911811828613</t>
   </si>
   <si>
     <t xml:space="preserve">12.7540979385376</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">12.8939647674561</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9027051925659</t>
+    <t xml:space="preserve">12.9027070999146</t>
   </si>
   <si>
     <t xml:space="preserve">13.0600566864014</t>
@@ -194,28 +194,28 @@
     <t xml:space="preserve">12.9813804626465</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4534330368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7069406509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4709157943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4621744155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2086639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3223066329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0950231552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9988660812378</t>
+    <t xml:space="preserve">13.4534339904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7069416046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4709148406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4621734619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.208664894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3223056793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0950222015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9988641738892</t>
   </si>
   <si>
     <t xml:space="preserve">12.640456199646</t>
@@ -224,16 +224,16 @@
     <t xml:space="preserve">12.4481391906738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3782062530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0285387039185</t>
+    <t xml:space="preserve">12.3782072067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0285396575928</t>
   </si>
   <si>
     <t xml:space="preserve">12.1509227752686</t>
   </si>
   <si>
-    <t xml:space="preserve">12.439398765564</t>
+    <t xml:space="preserve">12.4393978118896</t>
   </si>
   <si>
     <t xml:space="preserve">12.5617818832397</t>
@@ -242,85 +242,85 @@
     <t xml:space="preserve">12.5268144607544</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6317138671875</t>
+    <t xml:space="preserve">12.6317167282104</t>
   </si>
   <si>
     <t xml:space="preserve">12.3694648742676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7715826034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4306573867798</t>
+    <t xml:space="preserve">12.7715816497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4306564331055</t>
   </si>
   <si>
     <t xml:space="preserve">12.2820482254028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1946306228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2470817565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4131727218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5093307495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3869476318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8187398910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8449640274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.255823135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5792665481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2208557128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1858901977539</t>
+    <t xml:space="preserve">12.1946325302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2470808029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4131736755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.509331703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3869485855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8187379837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8449659347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2558221817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5792655944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2208566665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1858892440796</t>
   </si>
   <si>
     <t xml:space="preserve">12.7803239822388</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7278728485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8764801025391</t>
+    <t xml:space="preserve">12.7278747558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8764810562134</t>
   </si>
   <si>
     <t xml:space="preserve">12.8065481185913</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7628383636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8677396774292</t>
+    <t xml:space="preserve">12.7628402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8677406311035</t>
   </si>
   <si>
     <t xml:space="preserve">12.8327732086182</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5355558395386</t>
+    <t xml:space="preserve">12.5355567932129</t>
   </si>
   <si>
     <t xml:space="preserve">13.1824398040771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0338315963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3048238754272</t>
+    <t xml:space="preserve">13.0338325500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3048248291016</t>
   </si>
   <si>
     <t xml:space="preserve">13.261116027832</t>
@@ -332,22 +332,22 @@
     <t xml:space="preserve">13.6020402908325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6894578933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7244234085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7514743804932</t>
+    <t xml:space="preserve">13.6894569396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7244253158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7514762878418</t>
   </si>
   <si>
     <t xml:space="preserve">13.5711288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8687028884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6252317428589</t>
+    <t xml:space="preserve">13.8687019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6252307891846</t>
   </si>
   <si>
     <t xml:space="preserve">13.6432685852051</t>
@@ -359,25 +359,25 @@
     <t xml:space="preserve">13.598180770874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6162157058716</t>
+    <t xml:space="preserve">13.6162137985229</t>
   </si>
   <si>
     <t xml:space="preserve">13.5260419845581</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5530939102173</t>
+    <t xml:space="preserve">13.553092956543</t>
   </si>
   <si>
     <t xml:space="preserve">13.3456945419312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5801458358765</t>
+    <t xml:space="preserve">13.5801467895508</t>
   </si>
   <si>
     <t xml:space="preserve">13.6973714828491</t>
   </si>
   <si>
-    <t xml:space="preserve">13.778528213501</t>
+    <t xml:space="preserve">13.7785272598267</t>
   </si>
   <si>
     <t xml:space="preserve">13.6703195571899</t>
@@ -386,31 +386,31 @@
     <t xml:space="preserve">13.7965621948242</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9769105911255</t>
+    <t xml:space="preserve">13.9769086837769</t>
   </si>
   <si>
     <t xml:space="preserve">14.0400314331055</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0129795074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9047708511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1031532287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2474298477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1572580337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3646564483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4187602996826</t>
+    <t xml:space="preserve">14.0129804611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9047718048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1031541824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2474317550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1572570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3646574020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4187622070312</t>
   </si>
   <si>
     <t xml:space="preserve">14.517951965332</t>
@@ -419,19 +419,19 @@
     <t xml:space="preserve">14.6081256866455</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6622295379639</t>
+    <t xml:space="preserve">14.6622304916382</t>
   </si>
   <si>
     <t xml:space="preserve">14.3917093276978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3105525970459</t>
+    <t xml:space="preserve">14.3105516433716</t>
   </si>
   <si>
     <t xml:space="preserve">14.3015336990356</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5450048446655</t>
+    <t xml:space="preserve">14.5450029373169</t>
   </si>
   <si>
     <t xml:space="preserve">14.6441946029663</t>
@@ -443,28 +443,28 @@
     <t xml:space="preserve">14.7163324356079</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6351757049561</t>
+    <t xml:space="preserve">14.6351776123047</t>
   </si>
   <si>
     <t xml:space="preserve">14.6261596679688</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6892833709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8245420455933</t>
+    <t xml:space="preserve">14.6892824172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8245429992676</t>
   </si>
   <si>
     <t xml:space="preserve">14.8065071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">14.74338722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5810747146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6982975006104</t>
+    <t xml:space="preserve">14.7433862686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.581072807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6982984542847</t>
   </si>
   <si>
     <t xml:space="preserve">14.5089340209961</t>
@@ -476,67 +476,67 @@
     <t xml:space="preserve">14.6532106399536</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9237327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0499773025513</t>
+    <t xml:space="preserve">14.9237308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.049976348877</t>
   </si>
   <si>
     <t xml:space="preserve">15.212290763855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3746032714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5549488067627</t>
+    <t xml:space="preserve">15.3746013641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5549468994141</t>
   </si>
   <si>
     <t xml:space="preserve">15.9246606826782</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7803812026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8705577850342</t>
+    <t xml:space="preserve">15.7803821563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8705549240112</t>
   </si>
   <si>
     <t xml:space="preserve">15.8344869613647</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7082443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517107009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7452392578125</t>
+    <t xml:space="preserve">15.7082433700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7452411651611</t>
   </si>
   <si>
     <t xml:space="preserve">16.8714828491211</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0879039764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1510238647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2231636047363</t>
+    <t xml:space="preserve">17.0879020690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1510219573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2231597900391</t>
   </si>
   <si>
     <t xml:space="preserve">16.9796905517578</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9075527191162</t>
+    <t xml:space="preserve">16.9075508117676</t>
   </si>
   <si>
     <t xml:space="preserve">17.3043174743652</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0337963104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2772636413574</t>
+    <t xml:space="preserve">17.0337944030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2772674560547</t>
   </si>
   <si>
     <t xml:space="preserve">17.4756469726562</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.1690559387207</t>
   </si>
   <si>
-    <t xml:space="preserve">17.583854675293</t>
+    <t xml:space="preserve">17.5838565826416</t>
   </si>
   <si>
     <t xml:space="preserve">17.5748386383057</t>
@@ -560,22 +560,22 @@
     <t xml:space="preserve">17.2411956787109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1870918273926</t>
+    <t xml:space="preserve">17.1870899200439</t>
   </si>
   <si>
     <t xml:space="preserve">16.8534469604492</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8444309234619</t>
+    <t xml:space="preserve">16.8444328308105</t>
   </si>
   <si>
     <t xml:space="preserve">16.9526386260986</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7272033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6911354064941</t>
+    <t xml:space="preserve">16.7272052764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6911392211914</t>
   </si>
   <si>
     <t xml:space="preserve">16.8624668121338</t>
@@ -584,34 +584,34 @@
     <t xml:space="preserve">17.0428123474121</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8173770904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.997730255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7722949981689</t>
+    <t xml:space="preserve">16.8173809051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9977283477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7722930908203</t>
   </si>
   <si>
     <t xml:space="preserve">17.006742477417</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1961097717285</t>
+    <t xml:space="preserve">17.1961040496826</t>
   </si>
   <si>
     <t xml:space="preserve">17.3584213256836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6199226379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7642021179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0076713562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9896354675293</t>
+    <t xml:space="preserve">17.6199245452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7642040252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0076694488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9896392822266</t>
   </si>
   <si>
     <t xml:space="preserve">17.9445495605469</t>
@@ -620,40 +620,40 @@
     <t xml:space="preserve">17.9535655975342</t>
   </si>
   <si>
-    <t xml:space="preserve">17.809289932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2601566314697</t>
+    <t xml:space="preserve">17.8092880249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2601547241211</t>
   </si>
   <si>
     <t xml:space="preserve">18.7561092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8462829589844</t>
+    <t xml:space="preserve">18.8462867736816</t>
   </si>
   <si>
     <t xml:space="preserve">18.9364566802979</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6208515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2971496582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3602752685547</t>
+    <t xml:space="preserve">18.620849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2971534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3602771759033</t>
   </si>
   <si>
     <t xml:space="preserve">19.3512573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">19.666862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6488304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5586566925049</t>
+    <t xml:space="preserve">19.6668643951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6488285064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5586585998535</t>
   </si>
   <si>
     <t xml:space="preserve">19.252067565918</t>
@@ -662,19 +662,19 @@
     <t xml:space="preserve">19.1709117889404</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1348419189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.197961807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9544944763184</t>
+    <t xml:space="preserve">19.1348400115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1979656219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9544906616211</t>
   </si>
   <si>
     <t xml:space="preserve">18.9094066619873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0897579193115</t>
+    <t xml:space="preserve">19.0897521972656</t>
   </si>
   <si>
     <t xml:space="preserve">18.5757656097412</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">18.1970348358154</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5306739807129</t>
+    <t xml:space="preserve">18.5306777954102</t>
   </si>
   <si>
     <t xml:space="preserve">18.8372688293457</t>
@@ -692,16 +692,16 @@
     <t xml:space="preserve">19.4594650268555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3873233795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0185413360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3612022399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8301010131836</t>
+    <t xml:space="preserve">19.3873271942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0185432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3612003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8301067352295</t>
   </si>
   <si>
     <t xml:space="preserve">21.2809715270996</t>
@@ -710,40 +710,40 @@
     <t xml:space="preserve">20.8751907348633</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9292945861816</t>
+    <t xml:space="preserve">20.929292678833</t>
   </si>
   <si>
     <t xml:space="preserve">21.1006240844727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0104503631592</t>
+    <t xml:space="preserve">21.0104522705078</t>
   </si>
   <si>
     <t xml:space="preserve">20.5685997009277</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7218933105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6046695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1898727416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792343139648</t>
+    <t xml:space="preserve">20.7218952178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6046714782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1898708343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792381286621</t>
   </si>
   <si>
     <t xml:space="preserve">20.6497554779053</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6416664123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3711471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3801593780518</t>
+    <t xml:space="preserve">21.6416683197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3711452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3801651000977</t>
   </si>
   <si>
     <t xml:space="preserve">22.0925350189209</t>
@@ -752,37 +752,37 @@
     <t xml:space="preserve">22.6245594024658</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7147331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8049049377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5984344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0763568878174</t>
+    <t xml:space="preserve">22.7147312164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8049087524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5984325408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0763549804688</t>
   </si>
   <si>
     <t xml:space="preserve">24.0583209991455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7156620025635</t>
+    <t xml:space="preserve">23.7156600952148</t>
   </si>
   <si>
     <t xml:space="preserve">23.9320774078369</t>
   </si>
   <si>
-    <t xml:space="preserve">23.859935760498</t>
+    <t xml:space="preserve">23.8599395751953</t>
   </si>
   <si>
     <t xml:space="preserve">23.8058338165283</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5082607269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.994270324707</t>
+    <t xml:space="preserve">23.508264541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9942722320557</t>
   </si>
   <si>
     <t xml:space="preserve">22.4802837371826</t>
@@ -791,55 +791,55 @@
     <t xml:space="preserve">22.5434017181396</t>
   </si>
   <si>
-    <t xml:space="preserve">22.705717086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4532299041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4622497558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0023632049561</t>
+    <t xml:space="preserve">22.7057189941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4532318115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4622478485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0023593902588</t>
   </si>
   <si>
     <t xml:space="preserve">22.1827068328857</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7237510681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3630561828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2097606658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4883708953857</t>
+    <t xml:space="preserve">22.7237529754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3630542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2097587585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4883689880371</t>
   </si>
   <si>
     <t xml:space="preserve">21.9212036132812</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8761196136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7047882080078</t>
+    <t xml:space="preserve">21.8761177062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7047863006592</t>
   </si>
   <si>
     <t xml:space="preserve">21.9392395019531</t>
   </si>
   <si>
-    <t xml:space="preserve">22.074499130249</t>
+    <t xml:space="preserve">22.0745010375977</t>
   </si>
   <si>
     <t xml:space="preserve">22.299934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8139247894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3179664611816</t>
+    <t xml:space="preserve">22.8139228820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3179683685303</t>
   </si>
   <si>
     <t xml:space="preserve">22.1917266845703</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">22.354040145874</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5253658294678</t>
+    <t xml:space="preserve">22.525369644165</t>
   </si>
   <si>
     <t xml:space="preserve">22.6065254211426</t>
@@ -860,46 +860,46 @@
     <t xml:space="preserve">22.2458305358887</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2277965545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1286029815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.083517074585</t>
+    <t xml:space="preserve">22.2277946472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.128604888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0835189819336</t>
   </si>
   <si>
     <t xml:space="preserve">22.2007446289062</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1376209259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1466369628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5965824127197</t>
+    <t xml:space="preserve">22.137622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1466388702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5965805053711</t>
   </si>
   <si>
     <t xml:space="preserve">21.3260593414307</t>
   </si>
   <si>
-    <t xml:space="preserve">21.560510635376</t>
+    <t xml:space="preserve">21.5605125427246</t>
   </si>
   <si>
     <t xml:space="preserve">22.0294132232666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6867523193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2368125915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3991260528564</t>
+    <t xml:space="preserve">21.6867542266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2368144989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3720741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3991241455078</t>
   </si>
   <si>
     <t xml:space="preserve">22.6155414581299</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">23.0123081207275</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5193881988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2704563140869</t>
+    <t xml:space="preserve">23.5193862915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2704582214355</t>
   </si>
   <si>
     <t xml:space="preserve">24.1739845275879</t>
@@ -923,49 +923,49 @@
     <t xml:space="preserve">24.7087249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7732639312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.243465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8150863647461</t>
+    <t xml:space="preserve">24.7732620239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2434673309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8150882720947</t>
   </si>
   <si>
     <t xml:space="preserve">25.7966461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">25.686014175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.667573928833</t>
+    <t xml:space="preserve">25.6860122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6675720214844</t>
   </si>
   <si>
     <t xml:space="preserve">26.0086975097656</t>
   </si>
   <si>
-    <t xml:space="preserve">25.888843536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9810390472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0916748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.907283782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8058700561523</t>
+    <t xml:space="preserve">25.8888454437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9810371398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0916767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9072818756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8058681488037</t>
   </si>
   <si>
     <t xml:space="preserve">25.9533805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6767902374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.658353805542</t>
+    <t xml:space="preserve">25.6767921447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6583518981934</t>
   </si>
   <si>
     <t xml:space="preserve">25.0775165557861</t>
@@ -980,28 +980,28 @@
     <t xml:space="preserve">25.3264446258545</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8009204864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4186401367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6441879272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8562393188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9576568603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8931198120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1874771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9754276275635</t>
+    <t xml:space="preserve">24.8009223937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4186420440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6441860198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.856237411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9576549530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8931217193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.187479019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9754257202148</t>
   </si>
   <si>
     <t xml:space="preserve">23.1229419708252</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">23.2335796356201</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9938678741455</t>
+    <t xml:space="preserve">22.9938659667969</t>
   </si>
   <si>
     <t xml:space="preserve">23.0123062133789</t>
   </si>
   <si>
-    <t xml:space="preserve">22.781810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6711769104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4960060119629</t>
+    <t xml:space="preserve">22.7818164825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.671178817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4960021972656</t>
   </si>
   <si>
     <t xml:space="preserve">22.7264957427979</t>
@@ -1034,79 +1034,79 @@
     <t xml:space="preserve">22.3208293914795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5882015228271</t>
+    <t xml:space="preserve">22.5881996154785</t>
   </si>
   <si>
     <t xml:space="preserve">23.1137237548828</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9108867645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3995304107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7775402069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6208076477051</t>
+    <t xml:space="preserve">22.9108905792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3995323181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7775382995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6208038330078</t>
   </si>
   <si>
     <t xml:space="preserve">23.1413803100586</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9846477508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8740081787109</t>
+    <t xml:space="preserve">22.9846496582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8740100860596</t>
   </si>
   <si>
     <t xml:space="preserve">22.7357158660889</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6896152496338</t>
+    <t xml:space="preserve">22.6896171569824</t>
   </si>
   <si>
     <t xml:space="preserve">23.3257751464844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7406597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9803733825684</t>
+    <t xml:space="preserve">23.7406616210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9803714752197</t>
   </si>
   <si>
     <t xml:space="preserve">23.9711513519287</t>
   </si>
   <si>
-    <t xml:space="preserve">24.063346862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2477436065674</t>
+    <t xml:space="preserve">24.0633487701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2477416992188</t>
   </si>
   <si>
     <t xml:space="preserve">24.3860397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1555480957031</t>
+    <t xml:space="preserve">24.1555442810059</t>
   </si>
   <si>
     <t xml:space="preserve">24.6165313720703</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8611831665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6306915283203</t>
+    <t xml:space="preserve">25.8611850738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6306934356689</t>
   </si>
   <si>
     <t xml:space="preserve">25.2158069610596</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1697101593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080062866211</t>
+    <t xml:space="preserve">25.1697082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080043792725</t>
   </si>
   <si>
     <t xml:space="preserve">25.4463005065918</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">25.5384998321533</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1236114501953</t>
+    <t xml:space="preserve">25.1236095428467</t>
   </si>
   <si>
     <t xml:space="preserve">24.4321346282959</t>
@@ -1127,40 +1127,40 @@
     <t xml:space="preserve">24.0172500610352</t>
   </si>
   <si>
-    <t xml:space="preserve">24.109447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.339937210083</t>
+    <t xml:space="preserve">24.1094493865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3399391174316</t>
   </si>
   <si>
     <t xml:space="preserve">24.2016429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2938404083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7548236846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6626262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9853172302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.492395401001</t>
+    <t xml:space="preserve">24.2938423156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7548217773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6626281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9853134155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4923992156982</t>
   </si>
   <si>
     <t xml:space="preserve">25.7228889465332</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5704288482666</t>
+    <t xml:space="preserve">24.5704307556152</t>
   </si>
   <si>
     <t xml:space="preserve">25.5845928192139</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9994812011719</t>
+    <t xml:space="preserve">25.9994831085205</t>
   </si>
   <si>
     <t xml:space="preserve">26.4143657684326</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">26.7370529174805</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5065612792969</t>
+    <t xml:space="preserve">26.5065593719482</t>
   </si>
   <si>
     <t xml:space="preserve">25.0314140319824</t>
@@ -1190,13 +1190,13 @@
     <t xml:space="preserve">24.5243320465088</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3682651519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5987586975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4604625701904</t>
+    <t xml:space="preserve">26.3682689666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5987606048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4604644775391</t>
   </si>
   <si>
     <t xml:space="preserve">26.2299747467041</t>
@@ -1205,40 +1205,40 @@
     <t xml:space="preserve">26.3221683502197</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1980361938477</t>
+    <t xml:space="preserve">27.1980400085449</t>
   </si>
   <si>
     <t xml:space="preserve">26.2760696411133</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2902317047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3824272155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4746265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5526580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8292503356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1058387756348</t>
+    <t xml:space="preserve">27.2902336120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3824329376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4746284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5526599884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.829252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1058406829834</t>
   </si>
   <si>
     <t xml:space="preserve">26.8753490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8434143066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.765380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5809898376465</t>
+    <t xml:space="preserve">27.843412399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7653827667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5809879302979</t>
   </si>
   <si>
     <t xml:space="preserve">27.9356117248535</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">28.8114814758301</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1661014556885</t>
+    <t xml:space="preserve">28.1661033630371</t>
   </si>
   <si>
     <t xml:space="preserve">28.7192840576172</t>
@@ -1256,16 +1256,16 @@
     <t xml:space="preserve">28.1200046539307</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0597438812256</t>
+    <t xml:space="preserve">27.059741973877</t>
   </si>
   <si>
     <t xml:space="preserve">26.9675464630127</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1519374847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6909580230713</t>
+    <t xml:space="preserve">27.1519393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6909561157227</t>
   </si>
   <si>
     <t xml:space="preserve">26.7831516265869</t>
@@ -1277,25 +1277,25 @@
     <t xml:space="preserve">27.6590213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9214458465576</t>
+    <t xml:space="preserve">26.9214477539062</t>
   </si>
   <si>
     <t xml:space="preserve">26.1828804016113</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0886974334717</t>
+    <t xml:space="preserve">26.0887012481689</t>
   </si>
   <si>
     <t xml:space="preserve">26.4654293060303</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2299728393555</t>
+    <t xml:space="preserve">26.2299709320068</t>
   </si>
   <si>
     <t xml:space="preserve">25.8061485290527</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7119655609131</t>
+    <t xml:space="preserve">25.7119636535645</t>
   </si>
   <si>
     <t xml:space="preserve">25.1468696594238</t>
@@ -1304,10 +1304,10 @@
     <t xml:space="preserve">25.3352336883545</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9114112854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4875831604004</t>
+    <t xml:space="preserve">24.911413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4875869750977</t>
   </si>
   <si>
     <t xml:space="preserve">24.3934001922607</t>
@@ -1316,31 +1316,31 @@
     <t xml:space="preserve">23.9224872589111</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2632083892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0277481079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0748424530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7451972961426</t>
+    <t xml:space="preserve">23.2632064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0277500152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0748386383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7451992034912</t>
   </si>
   <si>
     <t xml:space="preserve">22.6039257049561</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5097427368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4155597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.180103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0388259887695</t>
+    <t xml:space="preserve">22.5097408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4155578613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1801013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0388240814209</t>
   </si>
   <si>
     <t xml:space="preserve">21.8504638671875</t>
@@ -1352,16 +1352,16 @@
     <t xml:space="preserve">22.2271919250488</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4044799804688</t>
+    <t xml:space="preserve">23.4044818878174</t>
   </si>
   <si>
     <t xml:space="preserve">23.2161140441895</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8864765167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4986629486084</t>
+    <t xml:space="preserve">22.886474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.498664855957</t>
   </si>
   <si>
     <t xml:space="preserve">22.5568351745605</t>
@@ -1370,34 +1370,34 @@
     <t xml:space="preserve">22.1330089569092</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6620941162109</t>
+    <t xml:space="preserve">21.6620960235596</t>
   </si>
   <si>
     <t xml:space="preserve">21.1911792755127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0028133392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.096996307373</t>
+    <t xml:space="preserve">21.002815246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0969982147217</t>
   </si>
   <si>
     <t xml:space="preserve">20.8615379333496</t>
   </si>
   <si>
-    <t xml:space="preserve">21.379545211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.473726272583</t>
+    <t xml:space="preserve">21.3795471191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4737281799316</t>
   </si>
   <si>
     <t xml:space="preserve">22.274284362793</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7562770843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9446430206299</t>
+    <t xml:space="preserve">21.7562789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9446449279785</t>
   </si>
   <si>
     <t xml:space="preserve">21.5679111480713</t>
@@ -1412,34 +1412,34 @@
     <t xml:space="preserve">21.2382717132568</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8393802642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.792293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5457553863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6399383544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7341251373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6870288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.781213760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0166683197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2992191314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1579456329346</t>
+    <t xml:space="preserve">22.8393840789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7922916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5457534790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6399364471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7341232299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6870307922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7812118530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0166721343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2992210388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1579437255859</t>
   </si>
   <si>
     <t xml:space="preserve">24.2521305084229</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">24.7230434417725</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6288623809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6759510040283</t>
+    <t xml:space="preserve">24.6288604736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.675952911377</t>
   </si>
   <si>
     <t xml:space="preserve">24.5817680358887</t>
@@ -1460,25 +1460,25 @@
     <t xml:space="preserve">24.770133972168</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9585018157959</t>
+    <t xml:space="preserve">24.9584999084473</t>
   </si>
   <si>
     <t xml:space="preserve">25.9003295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">25.75905418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9474220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2770614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9363441467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9834365844727</t>
+    <t xml:space="preserve">25.7590560913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9474201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.277063369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9363460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.983434677124</t>
   </si>
   <si>
     <t xml:space="preserve">26.8421611785889</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">26.7479782104492</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2659854888916</t>
+    <t xml:space="preserve">27.2659873962402</t>
   </si>
   <si>
     <t xml:space="preserve">27.4543514251709</t>
@@ -1496,25 +1496,25 @@
     <t xml:space="preserve">27.501443862915</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3130741119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0776195526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7008876800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6537952423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6067028045654</t>
+    <t xml:space="preserve">27.3130760192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0776176452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7008857727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6537971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6067008972168</t>
   </si>
   <si>
     <t xml:space="preserve">25.994514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1357879638672</t>
+    <t xml:space="preserve">26.1357860565186</t>
   </si>
   <si>
     <t xml:space="preserve">26.0416049957275</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">25.6177845001221</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4294147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.00559425354</t>
+    <t xml:space="preserve">25.4294166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0055923461914</t>
   </si>
   <si>
     <t xml:space="preserve">25.0997772216797</t>
@@ -1535,16 +1535,16 @@
     <t xml:space="preserve">24.8643169403076</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4404983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5235996246338</t>
+    <t xml:space="preserve">24.4404964447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5235977172852</t>
   </si>
   <si>
     <t xml:space="preserve">26.3712463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3241577148438</t>
+    <t xml:space="preserve">26.3241558074951</t>
   </si>
   <si>
     <t xml:space="preserve">26.7950706481934</t>
@@ -1562,34 +1562,34 @@
     <t xml:space="preserve">27.5485343933105</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6898097991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1136302947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3961791992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7258224487305</t>
+    <t xml:space="preserve">27.6898078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1136322021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.396183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7258205413818</t>
   </si>
   <si>
     <t xml:space="preserve">28.9141864776611</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9501991271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.761833190918</t>
+    <t xml:space="preserve">29.9502010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7618350982666</t>
   </si>
   <si>
     <t xml:space="preserve">30.3269329071045</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5042190551758</t>
+    <t xml:space="preserve">30.3740253448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5042209625244</t>
   </si>
   <si>
     <t xml:space="preserve">31.6925868988037</t>
@@ -1601,31 +1601,31 @@
     <t xml:space="preserve">32.4931411743164</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4820709228516</t>
+    <t xml:space="preserve">33.4820671081543</t>
   </si>
   <si>
     <t xml:space="preserve">33.6704330444336</t>
   </si>
   <si>
-    <t xml:space="preserve">33.293701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.576244354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9058837890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2466049194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8698768615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1524238586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0582427978516</t>
+    <t xml:space="preserve">33.2936973571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5762481689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9058876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2466087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8698806762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1524200439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0582389831543</t>
   </si>
   <si>
     <t xml:space="preserve">32.5873222351074</t>
@@ -1634,31 +1634,31 @@
     <t xml:space="preserve">32.3047752380371</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9280471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4571323394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3629455566406</t>
+    <t xml:space="preserve">31.9280452728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4571285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3629417419434</t>
   </si>
   <si>
     <t xml:space="preserve">30.8920288085938</t>
   </si>
   <si>
-    <t xml:space="preserve">31.080394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0333061218262</t>
+    <t xml:space="preserve">31.0803966522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0333080291748</t>
   </si>
   <si>
     <t xml:space="preserve">30.6565742492676</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6094818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2687683105469</t>
+    <t xml:space="preserve">30.6094799041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2687664031982</t>
   </si>
   <si>
     <t xml:space="preserve">30.9862174987793</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">31.4100379943848</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8449382781982</t>
+    <t xml:space="preserve">30.8449401855469</t>
   </si>
   <si>
     <t xml:space="preserve">31.1745777130127</t>
@@ -1679,13 +1679,13 @@
     <t xml:space="preserve">32.0222244262695</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7396850585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0000686645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4709892272949</t>
+    <t xml:space="preserve">31.7396793365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.000072479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4709815979004</t>
   </si>
   <si>
     <t xml:space="preserve">35.7895469665527</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">36.7784690856934</t>
   </si>
   <si>
-    <t xml:space="preserve">37.155200958252</t>
+    <t xml:space="preserve">37.1552047729492</t>
   </si>
   <si>
     <t xml:space="preserve">37.6732063293457</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0846748352051</t>
+    <t xml:space="preserve">38.0846710205078</t>
   </si>
   <si>
     <t xml:space="preserve">38.2282104492188</t>
@@ -1718,19 +1718,19 @@
     <t xml:space="preserve">38.1803665161133</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3717422485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9411430358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9889831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8454513549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3191528320312</t>
+    <t xml:space="preserve">38.3717460632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9411392211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9889869689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8454551696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3191566467285</t>
   </si>
   <si>
     <t xml:space="preserve">38.8501968383789</t>
@@ -1739,16 +1739,16 @@
     <t xml:space="preserve">38.7545051574707</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3286476135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.041576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8023529052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4674377441406</t>
+    <t xml:space="preserve">39.3286437988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0415725708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8023567199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4674415588379</t>
   </si>
   <si>
     <t xml:space="preserve">38.1325187683105</t>
@@ -1769,10 +1769,10 @@
     <t xml:space="preserve">38.4195938110352</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3764953613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1372718811035</t>
+    <t xml:space="preserve">39.3764877319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1372680664062</t>
   </si>
   <si>
     <t xml:space="preserve">39.1851119995117</t>
@@ -1781,10 +1781,10 @@
     <t xml:space="preserve">39.2807998657227</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9027938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1946105957031</t>
+    <t xml:space="preserve">39.9027900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1946067810059</t>
   </si>
   <si>
     <t xml:space="preserve">42.1036605834961</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">43.0605621337891</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4911689758301</t>
+    <t xml:space="preserve">43.4911727905273</t>
   </si>
   <si>
     <t xml:space="preserve">44.2566909790039</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">44.7829856872559</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4433212280273</t>
+    <t xml:space="preserve">43.4433288574219</t>
   </si>
   <si>
     <t xml:space="preserve">44.017463684082</t>
@@ -1835,10 +1835,10 @@
     <t xml:space="preserve">44.9265213012695</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4049758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2614364624023</t>
+    <t xml:space="preserve">45.404972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2614326477051</t>
   </si>
   <si>
     <t xml:space="preserve">45.5963516235352</t>
@@ -1850,40 +1850,40 @@
     <t xml:space="preserve">48.8976593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">48.610595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1847343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.993350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7588691711426</t>
+    <t xml:space="preserve">48.6105880737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1847381591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9933471679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7588729858398</t>
   </si>
   <si>
     <t xml:space="preserve">49.2804222106934</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6631889343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3761100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5674934387207</t>
+    <t xml:space="preserve">49.6631851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3761177062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5674896240234</t>
   </si>
   <si>
     <t xml:space="preserve">50.6200904846191</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0028457641602</t>
+    <t xml:space="preserve">51.0028419494629</t>
   </si>
   <si>
     <t xml:space="preserve">52.7252655029297</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6295738220215</t>
+    <t xml:space="preserve">52.6295776367188</t>
   </si>
   <si>
     <t xml:space="preserve">51.9597434997559</t>
@@ -1913,16 +1913,16 @@
     <t xml:space="preserve">49.8545608520508</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4287033081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5338897705078</t>
+    <t xml:space="preserve">50.4287071228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5338935852051</t>
   </si>
   <si>
     <t xml:space="preserve">54.0649299621582</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2994079589844</t>
+    <t xml:space="preserve">53.2994041442871</t>
   </si>
   <si>
     <t xml:space="preserve">52.4381980895996</t>
@@ -1931,34 +1931,34 @@
     <t xml:space="preserve">47.3666191101074</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9838562011719</t>
+    <t xml:space="preserve">46.9838600158691</t>
   </si>
   <si>
     <t xml:space="preserve">46.361873626709</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7398910522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.974365234375</t>
+    <t xml:space="preserve">45.7398872375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9743614196777</t>
   </si>
   <si>
     <t xml:space="preserve">43.5868606567383</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7687492370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6493225097656</t>
+    <t xml:space="preserve">41.7687454223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6493263244629</t>
   </si>
   <si>
     <t xml:space="preserve">35.5967330932617</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0945472717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4820594787598</t>
+    <t xml:space="preserve">30.0945491790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4820575714111</t>
   </si>
   <si>
     <t xml:space="preserve">29.1854934692383</t>
@@ -1970,16 +1970,16 @@
     <t xml:space="preserve">31.0992965698242</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3816204071045</t>
+    <t xml:space="preserve">30.3816184997559</t>
   </si>
   <si>
     <t xml:space="preserve">34.9268989562988</t>
   </si>
   <si>
-    <t xml:space="preserve">36.410099029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5010375976562</t>
+    <t xml:space="preserve">36.4101028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5010414123535</t>
   </si>
   <si>
     <t xml:space="preserve">35.3096656799316</t>
@@ -1994,13 +1994,13 @@
     <t xml:space="preserve">37.0799293518066</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2234687805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1277732849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2329559326172</t>
+    <t xml:space="preserve">37.2234649658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1277694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2329521179199</t>
   </si>
   <si>
     <t xml:space="preserve">40.429084777832</t>
@@ -2012,10 +2012,10 @@
     <t xml:space="preserve">44.7351417541504</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9791145324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4528198242188</t>
+    <t xml:space="preserve">45.979118347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4528160095215</t>
   </si>
   <si>
     <t xml:space="preserve">45.0700569152832</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">45.3571319580078</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1179046630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4575653076172</t>
+    <t xml:space="preserve">45.1179008483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4575614929199</t>
   </si>
   <si>
     <t xml:space="preserve">45.6441955566406</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">44.8786773681641</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3092765808105</t>
+    <t xml:space="preserve">45.3092803955078</t>
   </si>
   <si>
     <t xml:space="preserve">45.1657447814941</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">41.8644371032715</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5821151733398</t>
+    <t xml:space="preserve">42.5821075439453</t>
   </si>
   <si>
     <t xml:space="preserve">45.0222129821777</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">45.5485038757324</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5101547241211</t>
+    <t xml:space="preserve">47.5101585388184</t>
   </si>
   <si>
     <t xml:space="preserve">47.701530456543</t>
@@ -2072,16 +2072,16 @@
     <t xml:space="preserve">48.7062835693359</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9407615661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5149040222168</t>
+    <t xml:space="preserve">47.9407577514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5149002075195</t>
   </si>
   <si>
     <t xml:space="preserve">51.4812965393066</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1942253112793</t>
+    <t xml:space="preserve">51.194221496582</t>
   </si>
   <si>
     <t xml:space="preserve">51.768367767334</t>
@@ -2093,58 +2093,58 @@
     <t xml:space="preserve">53.1080284118652</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9692459106445</t>
+    <t xml:space="preserve">53.9692420959473</t>
   </si>
   <si>
     <t xml:space="preserve">53.490795135498</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1175193786621</t>
+    <t xml:space="preserve">55.1175231933594</t>
   </si>
   <si>
     <t xml:space="preserve">55.6916618347168</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5002822875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3520011901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6390686035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8304481506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4045906066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.744255065918</t>
+    <t xml:space="preserve">55.5002784729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3519973754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6390724182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.830451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4045867919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7442512512207</t>
   </si>
   <si>
     <t xml:space="preserve">56.9356346130371</t>
   </si>
   <si>
-    <t xml:space="preserve">57.1270141601562</t>
+    <t xml:space="preserve">57.1270179748535</t>
   </si>
   <si>
     <t xml:space="preserve">56.2658042907715</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9787292480469</t>
+    <t xml:space="preserve">55.9787330627441</t>
   </si>
   <si>
     <t xml:space="preserve">57.3183937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">58.6580581665039</t>
+    <t xml:space="preserve">58.6580543518066</t>
   </si>
   <si>
     <t xml:space="preserve">57.2227058410645</t>
   </si>
   <si>
-    <t xml:space="preserve">57.7011528015137</t>
+    <t xml:space="preserve">57.7011489868164</t>
   </si>
   <si>
     <t xml:space="preserve">56.3614921569824</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">62.2942848205566</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3468704223633</t>
+    <t xml:space="preserve">63.3468742370605</t>
   </si>
   <si>
     <t xml:space="preserve">63.7296333312988</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">63.6339454650879</t>
   </si>
   <si>
-    <t xml:space="preserve">64.3037719726562</t>
+    <t xml:space="preserve">64.3037643432617</t>
   </si>
   <si>
     <t xml:space="preserve">64.5908432006836</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">65.9305114746094</t>
   </si>
   <si>
-    <t xml:space="preserve">66.6960296630859</t>
+    <t xml:space="preserve">66.6960220336914</t>
   </si>
   <si>
     <t xml:space="preserve">65.3563613891602</t>
@@ -2195,22 +2195,22 @@
     <t xml:space="preserve">67.1744766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5046539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8443145751953</t>
+    <t xml:space="preserve">66.5046463012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8443069458008</t>
   </si>
   <si>
     <t xml:space="preserve">70.0451812744141</t>
   </si>
   <si>
-    <t xml:space="preserve">69.1839752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.2891616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8106994628906</t>
+    <t xml:space="preserve">69.183967590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.2891540527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8107070922852</t>
   </si>
   <si>
     <t xml:space="preserve">70.6193313598633</t>
@@ -2219,25 +2219,25 @@
     <t xml:space="preserve">71.7676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">72.0546798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0020751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.4710464477539</t>
+    <t xml:space="preserve">72.0546722412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.002082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.4710388183594</t>
   </si>
   <si>
     <t xml:space="preserve">68.9925918579102</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9494934082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8012084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.6624298095703</t>
+    <t xml:space="preserve">69.9494857788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8012161254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.6624221801758</t>
   </si>
   <si>
     <t xml:space="preserve">76.5521087646484</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">77.7003936767578</t>
   </si>
   <si>
-    <t xml:space="preserve">75.8822860717773</t>
+    <t xml:space="preserve">75.8822784423828</t>
   </si>
   <si>
     <t xml:space="preserve">74.734001159668</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">74.8296890258789</t>
   </si>
   <si>
-    <t xml:space="preserve">77.8917770385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.274543762207</t>
+    <t xml:space="preserve">77.8917846679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.2745361328125</t>
   </si>
   <si>
     <t xml:space="preserve">77.7960891723633</t>
@@ -2270,19 +2270,19 @@
     <t xml:space="preserve">79.4228210449219</t>
   </si>
   <si>
-    <t xml:space="preserve">80.7624893188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0064392089844</t>
+    <t xml:space="preserve">80.7624816894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0064468383789</t>
   </si>
   <si>
     <t xml:space="preserve">81.5279998779297</t>
   </si>
   <si>
-    <t xml:space="preserve">81.910758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.3892211914062</t>
+    <t xml:space="preserve">81.9107666015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.3892135620117</t>
   </si>
   <si>
     <t xml:space="preserve">81.4323120117188</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">81.1452407836914</t>
   </si>
   <si>
-    <t xml:space="preserve">80.4754104614258</t>
+    <t xml:space="preserve">80.4754028320312</t>
   </si>
   <si>
     <t xml:space="preserve">81.7193832397461</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">80.953857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">82.77197265625</t>
+    <t xml:space="preserve">82.7719650268555</t>
   </si>
   <si>
     <t xml:space="preserve">82.2935180664062</t>
@@ -2321,28 +2321,28 @@
     <t xml:space="preserve">83.728874206543</t>
   </si>
   <si>
-    <t xml:space="preserve">82.1021423339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.7434844970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.5185089111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8055877685547</t>
+    <t xml:space="preserve">82.1021499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.7434921264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.5185165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8055801391602</t>
   </si>
   <si>
     <t xml:space="preserve">82.4848937988281</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3797149658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.6572952270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.4659118652344</t>
+    <t xml:space="preserve">80.3797073364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.6572875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.4659042358398</t>
   </si>
   <si>
     <t xml:space="preserve">84.6857757568359</t>
@@ -2351,10 +2351,10 @@
     <t xml:space="preserve">85.3556060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">83.0590515136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.9297637939453</t>
+    <t xml:space="preserve">83.0590362548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.9297561645508</t>
   </si>
   <si>
     <t xml:space="preserve">87.1737213134766</t>
@@ -2363,85 +2363,85 @@
     <t xml:space="preserve">87.2694091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">88.3219985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7909545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.9056396484375</t>
+    <t xml:space="preserve">88.3220062255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7909469604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.905632019043</t>
   </si>
   <si>
     <t xml:space="preserve">91.3840866088867</t>
   </si>
   <si>
-    <t xml:space="preserve">93.1065063476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.8815231323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.22119140625</t>
+    <t xml:space="preserve">93.1065139770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.8815155029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.2211761474609</t>
   </si>
   <si>
     <t xml:space="preserve">100.474647521973</t>
   </si>
   <si>
-    <t xml:space="preserve">101.622932434082</t>
+    <t xml:space="preserve">101.622924804688</t>
   </si>
   <si>
     <t xml:space="preserve">101.240180969238</t>
   </si>
   <si>
-    <t xml:space="preserve">97.986701965332</t>
+    <t xml:space="preserve">97.9866943359375</t>
   </si>
   <si>
     <t xml:space="preserve">98.5608444213867</t>
   </si>
   <si>
-    <t xml:space="preserve">99.900505065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2642822265625</t>
+    <t xml:space="preserve">99.9004974365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.264289855957</t>
   </si>
   <si>
     <t xml:space="preserve">95.6901397705078</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8289337158203</t>
+    <t xml:space="preserve">94.8289260864258</t>
   </si>
   <si>
     <t xml:space="preserve">95.307373046875</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2547988891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.446174621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0298080444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5418548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1590957641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8720245361328</t>
+    <t xml:space="preserve">94.2547912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0298004150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.541862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1591033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8720321655273</t>
   </si>
   <si>
     <t xml:space="preserve">94.0634155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">93.3935699462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6806564331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9151306152344</t>
+    <t xml:space="preserve">93.3935775756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6806488037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9151229858398</t>
   </si>
   <si>
     <t xml:space="preserve">93.2978897094727</t>
@@ -2456,37 +2456,37 @@
     <t xml:space="preserve">97.6039428710938</t>
   </si>
   <si>
-    <t xml:space="preserve">101.43155670166</t>
+    <t xml:space="preserve">101.431549072266</t>
   </si>
   <si>
     <t xml:space="preserve">104.876396179199</t>
   </si>
   <si>
-    <t xml:space="preserve">104.493637084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.598815917969</t>
+    <t xml:space="preserve">104.493629455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.598808288574</t>
   </si>
   <si>
     <t xml:space="preserve">107.364334106445</t>
   </si>
   <si>
-    <t xml:space="preserve">109.66089630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.235038757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.641914367676</t>
+    <t xml:space="preserve">109.660903930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.235046386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.64192199707</t>
   </si>
   <si>
     <t xml:space="preserve">106.21605682373</t>
   </si>
   <si>
-    <t xml:space="preserve">107.938491821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.555717468262</t>
+    <t xml:space="preserve">107.938484191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.555725097656</t>
   </si>
   <si>
     <t xml:space="preserve">109.469520568848</t>
@@ -2495,13 +2495,13 @@
     <t xml:space="preserve">107.747100830078</t>
   </si>
   <si>
-    <t xml:space="preserve">108.704002380371</t>
+    <t xml:space="preserve">108.703994750977</t>
   </si>
   <si>
     <t xml:space="preserve">102.197074890137</t>
   </si>
   <si>
-    <t xml:space="preserve">99.5177383422852</t>
+    <t xml:space="preserve">99.5177459716797</t>
   </si>
   <si>
     <t xml:space="preserve">99.7091217041016</t>
@@ -2513,25 +2513,25 @@
     <t xml:space="preserve">103.536735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">106.024681091309</t>
+    <t xml:space="preserve">106.024673461914</t>
   </si>
   <si>
     <t xml:space="preserve">106.981590270996</t>
   </si>
   <si>
-    <t xml:space="preserve">108.512619018555</t>
+    <t xml:space="preserve">108.51261138916</t>
   </si>
   <si>
     <t xml:space="preserve">105.833297729492</t>
   </si>
   <si>
-    <t xml:space="preserve">101.048782348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.388450622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.15397644043</t>
+    <t xml:space="preserve">101.048789978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.388442993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.153984069824</t>
   </si>
   <si>
     <t xml:space="preserve">102.962593078613</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">105.450531005859</t>
   </si>
   <si>
-    <t xml:space="preserve">102.00569152832</t>
+    <t xml:space="preserve">102.005683898926</t>
   </si>
   <si>
     <t xml:space="preserve">103.919486999512</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">109.086761474609</t>
   </si>
   <si>
-    <t xml:space="preserve">110.809181213379</t>
+    <t xml:space="preserve">110.809173583984</t>
   </si>
   <si>
     <t xml:space="preserve">113.679893493652</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">107.172958374023</t>
   </si>
   <si>
-    <t xml:space="preserve">111.000564575195</t>
+    <t xml:space="preserve">111.000556945801</t>
   </si>
   <si>
     <t xml:space="preserve">112.914367675781</t>
   </si>
   <si>
-    <t xml:space="preserve">109.852272033691</t>
+    <t xml:space="preserve">109.852279663086</t>
   </si>
   <si>
     <t xml:space="preserve">110.426422119141</t>
@@ -2579,55 +2579,55 @@
     <t xml:space="preserve">111.383323669434</t>
   </si>
   <si>
-    <t xml:space="preserve">112.340232849121</t>
+    <t xml:space="preserve">112.340225219727</t>
   </si>
   <si>
     <t xml:space="preserve">114.445411682129</t>
   </si>
   <si>
-    <t xml:space="preserve">113.29712677002</t>
+    <t xml:space="preserve">113.297119140625</t>
   </si>
   <si>
     <t xml:space="preserve">112.722984313965</t>
   </si>
   <si>
-    <t xml:space="preserve">115.019546508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.593688964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.210922241211</t>
+    <t xml:space="preserve">115.019554138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.593696594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.210929870605</t>
   </si>
   <si>
     <t xml:space="preserve">116.741973876953</t>
   </si>
   <si>
-    <t xml:space="preserve">116.167823791504</t>
+    <t xml:space="preserve">116.167831420898</t>
   </si>
   <si>
     <t xml:space="preserve">115.78507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">116.550598144531</t>
+    <t xml:space="preserve">116.550590515137</t>
   </si>
   <si>
     <t xml:space="preserve">119.804061889648</t>
   </si>
   <si>
-    <t xml:space="preserve">120.186820983887</t>
+    <t xml:space="preserve">120.186813354492</t>
   </si>
   <si>
     <t xml:space="preserve">122.100624084473</t>
   </si>
   <si>
-    <t xml:space="preserve">122.866134643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.63166809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.478271484375</t>
+    <t xml:space="preserve">122.86612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.631660461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.478256225586</t>
   </si>
   <si>
     <t xml:space="preserve">127.267890930176</t>
@@ -2636,43 +2636,43 @@
     <t xml:space="preserve">127.459266662598</t>
   </si>
   <si>
-    <t xml:space="preserve">128.990310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.052368164062</t>
+    <t xml:space="preserve">128.990325927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.052398681641</t>
   </si>
   <si>
     <t xml:space="preserve">134.157577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">133.774826049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.626541137695</t>
+    <t xml:space="preserve">133.774810791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.626556396484</t>
   </si>
   <si>
     <t xml:space="preserve">132.435150146484</t>
   </si>
   <si>
-    <t xml:space="preserve">134.923080444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.645523071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.411056518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.305847167969</t>
+    <t xml:space="preserve">134.923095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.645538330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.411041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.305862426758</t>
   </si>
   <si>
     <t xml:space="preserve">131.861022949219</t>
   </si>
   <si>
-    <t xml:space="preserve">134.731735229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.262741088867</t>
+    <t xml:space="preserve">134.731719970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.262756347656</t>
   </si>
   <si>
     <t xml:space="preserve">137.793792724609</t>
@@ -2684,19 +2684,19 @@
     <t xml:space="preserve">137.028289794922</t>
   </si>
   <si>
-    <t xml:space="preserve">138.559341430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.898986816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.454132080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.750701904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.324859619141</t>
+    <t xml:space="preserve">138.559326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.898971557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.454162597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.750686645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.324844360352</t>
   </si>
   <si>
     <t xml:space="preserve">137.98518371582</t>
@@ -2705,19 +2705,19 @@
     <t xml:space="preserve">135.497253417969</t>
   </si>
   <si>
-    <t xml:space="preserve">144.492126464844</t>
+    <t xml:space="preserve">144.492111206055</t>
   </si>
   <si>
     <t xml:space="preserve">144.874877929688</t>
   </si>
   <si>
-    <t xml:space="preserve">144.109359741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.195556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.726593017578</t>
+    <t xml:space="preserve">144.109344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.195541381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.726577758789</t>
   </si>
   <si>
     <t xml:space="preserve">143.91796875</t>
@@ -2726,19 +2726,19 @@
     <t xml:space="preserve">144.683486938477</t>
   </si>
   <si>
-    <t xml:space="preserve">145.257629394531</t>
+    <t xml:space="preserve">145.25764465332</t>
   </si>
   <si>
     <t xml:space="preserve">147.936950683594</t>
   </si>
   <si>
-    <t xml:space="preserve">145.640396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.788681030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.276611328125</t>
+    <t xml:space="preserve">145.640411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.788665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.276626586914</t>
   </si>
   <si>
     <t xml:space="preserve">150.999053955078</t>
@@ -2747,10 +2747,10 @@
     <t xml:space="preserve">150.424911499023</t>
   </si>
   <si>
-    <t xml:space="preserve">153.486968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.33869934082</t>
+    <t xml:space="preserve">153.48698425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.338684082031</t>
   </si>
   <si>
     <t xml:space="preserve">155.400787353516</t>
@@ -2759,49 +2759,49 @@
     <t xml:space="preserve">151.190414428711</t>
   </si>
   <si>
-    <t xml:space="preserve">157.888732910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.037017822266</t>
+    <t xml:space="preserve">157.888748168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.037033081055</t>
   </si>
   <si>
     <t xml:space="preserve">158.654251098633</t>
   </si>
   <si>
-    <t xml:space="preserve">159.611175537109</t>
+    <t xml:space="preserve">159.61116027832</t>
   </si>
   <si>
     <t xml:space="preserve">161.333572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">161.524978637695</t>
+    <t xml:space="preserve">161.524963378906</t>
   </si>
   <si>
     <t xml:space="preserve">163.438766479492</t>
   </si>
   <si>
-    <t xml:space="preserve">163.821517944336</t>
+    <t xml:space="preserve">163.821533203125</t>
   </si>
   <si>
     <t xml:space="preserve">168.606033325195</t>
   </si>
   <si>
-    <t xml:space="preserve">173.773284912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.328460693359</t>
+    <t xml:space="preserve">173.773315429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.328430175781</t>
   </si>
   <si>
     <t xml:space="preserve">165.161193847656</t>
   </si>
   <si>
-    <t xml:space="preserve">168.031890869141</t>
+    <t xml:space="preserve">168.03190612793</t>
   </si>
   <si>
     <t xml:space="preserve">165.352569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">160.759429931641</t>
+    <t xml:space="preserve">160.759414672852</t>
   </si>
   <si>
     <t xml:space="preserve">162.099090576172</t>
@@ -2810,16 +2810,16 @@
     <t xml:space="preserve">171.668106079102</t>
   </si>
   <si>
-    <t xml:space="preserve">167.074996948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.930511474609</t>
+    <t xml:space="preserve">167.074981689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.93049621582</t>
   </si>
   <si>
     <t xml:space="preserve">161.353576660156</t>
   </si>
   <si>
-    <t xml:space="preserve">160.584320068359</t>
+    <t xml:space="preserve">160.58430480957</t>
   </si>
   <si>
     <t xml:space="preserve">159.045761108398</t>
@@ -2828,10 +2828,10 @@
     <t xml:space="preserve">152.12239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">145.583602905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.314453125</t>
+    <t xml:space="preserve">145.583618164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.314468383789</t>
   </si>
   <si>
     <t xml:space="preserve">150.391525268555</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">150.19921875</t>
   </si>
   <si>
-    <t xml:space="preserve">148.083724975586</t>
+    <t xml:space="preserve">148.083709716797</t>
   </si>
   <si>
     <t xml:space="preserve">151.737747192383</t>
   </si>
   <si>
-    <t xml:space="preserve">149.622283935547</t>
+    <t xml:space="preserve">149.622268676758</t>
   </si>
   <si>
     <t xml:space="preserve">155.199432373047</t>
@@ -2855,16 +2855,16 @@
     <t xml:space="preserve">156.545669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">155.968704223633</t>
+    <t xml:space="preserve">155.968719482422</t>
   </si>
   <si>
     <t xml:space="preserve">154.43017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">160.776626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.353805541992</t>
+    <t xml:space="preserve">160.776611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.353790283203</t>
   </si>
   <si>
     <t xml:space="preserve">170.200134277344</t>
@@ -2879,16 +2879,16 @@
     <t xml:space="preserve">165.007598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">162.507476806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.469039916992</t>
+    <t xml:space="preserve">162.507461547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.469055175781</t>
   </si>
   <si>
     <t xml:space="preserve">165.584533691406</t>
   </si>
   <si>
-    <t xml:space="preserve">161.161254882812</t>
+    <t xml:space="preserve">161.161270141602</t>
   </si>
   <si>
     <t xml:space="preserve">163.084426879883</t>
@@ -2897,25 +2897,25 @@
     <t xml:space="preserve">161.738189697266</t>
   </si>
   <si>
-    <t xml:space="preserve">168.853912353516</t>
+    <t xml:space="preserve">168.853927612305</t>
   </si>
   <si>
     <t xml:space="preserve">177.508163452148</t>
   </si>
   <si>
-    <t xml:space="preserve">175.584991455078</t>
+    <t xml:space="preserve">175.584976196289</t>
   </si>
   <si>
     <t xml:space="preserve">180.392913818359</t>
   </si>
   <si>
-    <t xml:space="preserve">180.777542114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.469741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.815948486328</t>
+    <t xml:space="preserve">180.777526855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.469757080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.815963745117</t>
   </si>
   <si>
     <t xml:space="preserve">181.739120483398</t>
@@ -2924,13 +2924,13 @@
     <t xml:space="preserve">185.008499145508</t>
   </si>
   <si>
-    <t xml:space="preserve">183.085342407227</t>
+    <t xml:space="preserve">183.085327148438</t>
   </si>
   <si>
     <t xml:space="preserve">182.508392333984</t>
   </si>
   <si>
-    <t xml:space="preserve">168.276977539062</t>
+    <t xml:space="preserve">168.276962280273</t>
   </si>
   <si>
     <t xml:space="preserve">169.046234130859</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">174.046463012695</t>
   </si>
   <si>
-    <t xml:space="preserve">170.96940612793</t>
+    <t xml:space="preserve">170.969390869141</t>
   </si>
   <si>
     <t xml:space="preserve">169.623184204102</t>
@@ -2960,25 +2960,25 @@
     <t xml:space="preserve">172.700256347656</t>
   </si>
   <si>
-    <t xml:space="preserve">172.123291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.93098449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.315368652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.853668212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.738418579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.238342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.546112060547</t>
+    <t xml:space="preserve">172.123306274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.930969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.315383911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.85368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.738403320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.238327026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.546096801758</t>
   </si>
   <si>
     <t xml:space="preserve">167.700012207031</t>
@@ -2987,37 +2987,37 @@
     <t xml:space="preserve">165.392211914062</t>
   </si>
   <si>
-    <t xml:space="preserve">151.160781860352</t>
+    <t xml:space="preserve">151.160797119141</t>
   </si>
   <si>
     <t xml:space="preserve">158.853454589844</t>
   </si>
   <si>
-    <t xml:space="preserve">158.468826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.31494140625</t>
+    <t xml:space="preserve">158.468841552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.314926147461</t>
   </si>
   <si>
     <t xml:space="preserve">159.815048217773</t>
   </si>
   <si>
-    <t xml:space="preserve">156.930282592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.161010742188</t>
+    <t xml:space="preserve">156.930267333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.161026000977</t>
   </si>
   <si>
     <t xml:space="preserve">152.314682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">145.968246459961</t>
+    <t xml:space="preserve">145.96826171875</t>
   </si>
   <si>
     <t xml:space="preserve">146.929840087891</t>
   </si>
   <si>
-    <t xml:space="preserve">151.353088378906</t>
+    <t xml:space="preserve">151.353103637695</t>
   </si>
   <si>
     <t xml:space="preserve">153.468597412109</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">153.276260375977</t>
   </si>
   <si>
-    <t xml:space="preserve">157.122604370117</t>
+    <t xml:space="preserve">157.122589111328</t>
   </si>
   <si>
     <t xml:space="preserve">151.930053710938</t>
@@ -3035,19 +3035,19 @@
     <t xml:space="preserve">146.545196533203</t>
   </si>
   <si>
-    <t xml:space="preserve">140.968032836914</t>
+    <t xml:space="preserve">140.968017578125</t>
   </si>
   <si>
     <t xml:space="preserve">136.92936706543</t>
   </si>
   <si>
-    <t xml:space="preserve">138.660202026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.698394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.506088256836</t>
+    <t xml:space="preserve">138.660217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.69841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.506103515625</t>
   </si>
   <si>
     <t xml:space="preserve">130.198287963867</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">128.852066040039</t>
   </si>
   <si>
-    <t xml:space="preserve">129.621337890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.890716552734</t>
+    <t xml:space="preserve">129.621353149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.890731811523</t>
   </si>
   <si>
     <t xml:space="preserve">137.506332397461</t>
@@ -3080,25 +3080,25 @@
     <t xml:space="preserve">138.467895507812</t>
   </si>
   <si>
-    <t xml:space="preserve">135.583160400391</t>
+    <t xml:space="preserve">135.583145141602</t>
   </si>
   <si>
     <t xml:space="preserve">124.813430786133</t>
   </si>
   <si>
-    <t xml:space="preserve">118.659294128418</t>
+    <t xml:space="preserve">118.659301757812</t>
   </si>
   <si>
     <t xml:space="preserve">125.582695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">125.198059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.314010620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.8525390625</t>
+    <t xml:space="preserve">125.198066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.314025878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.852523803711</t>
   </si>
   <si>
     <t xml:space="preserve">142.891174316406</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">145.00666809082</t>
   </si>
   <si>
-    <t xml:space="preserve">145.775924682617</t>
+    <t xml:space="preserve">145.775939941406</t>
   </si>
   <si>
     <t xml:space="preserve">144.814346313477</t>
@@ -3125,19 +3125,19 @@
     <t xml:space="preserve">143.275817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">142.602691650391</t>
+    <t xml:space="preserve">142.60270690918</t>
   </si>
   <si>
     <t xml:space="preserve">142.698867797852</t>
   </si>
   <si>
-    <t xml:space="preserve">143.083511352539</t>
+    <t xml:space="preserve">143.08349609375</t>
   </si>
   <si>
     <t xml:space="preserve">139.525650024414</t>
   </si>
   <si>
-    <t xml:space="preserve">141.160339355469</t>
+    <t xml:space="preserve">141.160354614258</t>
   </si>
   <si>
     <t xml:space="preserve">140.198745727539</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">139.429473876953</t>
   </si>
   <si>
-    <t xml:space="preserve">139.237182617188</t>
+    <t xml:space="preserve">139.237167358398</t>
   </si>
   <si>
     <t xml:space="preserve">140.006439208984</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">143.179641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">142.314224243164</t>
+    <t xml:space="preserve">142.314239501953</t>
   </si>
   <si>
     <t xml:space="preserve">130.87141418457</t>
@@ -3170,28 +3170,28 @@
     <t xml:space="preserve">129.525192260742</t>
   </si>
   <si>
-    <t xml:space="preserve">129.909820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.371505737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.275115966797</t>
+    <t xml:space="preserve">129.90983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.371520996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.275146484375</t>
   </si>
   <si>
     <t xml:space="preserve">130.294448852539</t>
   </si>
   <si>
-    <t xml:space="preserve">124.236473083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.890266418457</t>
+    <t xml:space="preserve">124.236480712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.890258789062</t>
   </si>
   <si>
     <t xml:space="preserve">118.563148498535</t>
   </si>
   <si>
-    <t xml:space="preserve">109.81273651123</t>
+    <t xml:space="preserve">109.812744140625</t>
   </si>
   <si>
     <t xml:space="preserve">113.56290435791</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">122.313316345215</t>
   </si>
   <si>
-    <t xml:space="preserve">120.293991088867</t>
+    <t xml:space="preserve">120.293983459473</t>
   </si>
   <si>
     <t xml:space="preserve">120.101676940918</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">119.236251831055</t>
   </si>
   <si>
-    <t xml:space="preserve">120.486312866211</t>
+    <t xml:space="preserve">120.486320495605</t>
   </si>
   <si>
     <t xml:space="preserve">116.736137390137</t>
@@ -3233,19 +3233,19 @@
     <t xml:space="preserve">119.043930053711</t>
   </si>
   <si>
-    <t xml:space="preserve">121.736358642578</t>
+    <t xml:space="preserve">121.736366271973</t>
   </si>
   <si>
     <t xml:space="preserve">124.621116638184</t>
   </si>
   <si>
-    <t xml:space="preserve">123.27490234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.544052124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.044166564941</t>
+    <t xml:space="preserve">123.274894714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.544044494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.044158935547</t>
   </si>
   <si>
     <t xml:space="preserve">124.332641601562</t>
@@ -3254,10 +3254,10 @@
     <t xml:space="preserve">127.986656188965</t>
   </si>
   <si>
-    <t xml:space="preserve">128.659759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.698173522949</t>
+    <t xml:space="preserve">128.659774780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.698188781738</t>
   </si>
   <si>
     <t xml:space="preserve">123.178741455078</t>
@@ -3266,13 +3266,13 @@
     <t xml:space="preserve">114.524490356445</t>
   </si>
   <si>
-    <t xml:space="preserve">112.889808654785</t>
+    <t xml:space="preserve">112.889801025391</t>
   </si>
   <si>
     <t xml:space="preserve">114.236022949219</t>
   </si>
   <si>
-    <t xml:space="preserve">111.062797546387</t>
+    <t xml:space="preserve">111.062805175781</t>
   </si>
   <si>
     <t xml:space="preserve">112.216690063477</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">116.447654724121</t>
   </si>
   <si>
-    <t xml:space="preserve">115.197593688965</t>
+    <t xml:space="preserve">115.197601318359</t>
   </si>
   <si>
     <t xml:space="preserve">119.140090942383</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">119.909355163574</t>
   </si>
   <si>
-    <t xml:space="preserve">119.428573608398</t>
+    <t xml:space="preserve">119.428565979004</t>
   </si>
   <si>
     <t xml:space="preserve">117.890029907227</t>
@@ -3314,19 +3314,19 @@
     <t xml:space="preserve">123.082580566406</t>
   </si>
   <si>
-    <t xml:space="preserve">125.39037322998</t>
+    <t xml:space="preserve">125.390365600586</t>
   </si>
   <si>
     <t xml:space="preserve">122.986427307129</t>
   </si>
   <si>
-    <t xml:space="preserve">118.274658203125</t>
+    <t xml:space="preserve">118.27466583252</t>
   </si>
   <si>
     <t xml:space="preserve">119.717041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">120.774772644043</t>
+    <t xml:space="preserve">120.774780273438</t>
   </si>
   <si>
     <t xml:space="preserve">123.659538269043</t>
@@ -3341,19 +3341,19 @@
     <t xml:space="preserve">130.679077148438</t>
   </si>
   <si>
-    <t xml:space="preserve">126.832748413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.794334411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.46745300293</t>
+    <t xml:space="preserve">126.832740783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.794319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.467468261719</t>
   </si>
   <si>
     <t xml:space="preserve">132.602249145508</t>
   </si>
   <si>
-    <t xml:space="preserve">129.044403076172</t>
+    <t xml:space="preserve">129.044387817383</t>
   </si>
   <si>
     <t xml:space="preserve">131.159866333008</t>
@@ -3365,16 +3365,16 @@
     <t xml:space="preserve">126.351959228516</t>
   </si>
   <si>
-    <t xml:space="preserve">123.563362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.313537597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.371276855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.736587524414</t>
+    <t xml:space="preserve">123.563369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.313545227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.371292114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.736595153809</t>
   </si>
   <si>
     <t xml:space="preserve">121.447891235352</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">118.947769165039</t>
   </si>
   <si>
-    <t xml:space="preserve">120.19783782959</t>
+    <t xml:space="preserve">120.197830200195</t>
   </si>
   <si>
     <t xml:space="preserve">121.063262939453</t>
@@ -3395,13 +3395,13 @@
     <t xml:space="preserve">117.505401611328</t>
   </si>
   <si>
-    <t xml:space="preserve">115.870712280273</t>
+    <t xml:space="preserve">115.870704650879</t>
   </si>
   <si>
     <t xml:space="preserve">116.255348205566</t>
   </si>
   <si>
-    <t xml:space="preserve">112.312850952148</t>
+    <t xml:space="preserve">112.312858581543</t>
   </si>
   <si>
     <t xml:space="preserve">115.582237243652</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">114.909133911133</t>
   </si>
   <si>
-    <t xml:space="preserve">106.596160888672</t>
+    <t xml:space="preserve">106.596168518066</t>
   </si>
   <si>
     <t xml:space="preserve">105.336387634277</t>
@@ -3449,10 +3449,10 @@
     <t xml:space="preserve">109.212615966797</t>
   </si>
   <si>
-    <t xml:space="preserve">113.185745239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.441444396973</t>
+    <t xml:space="preserve">113.185752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.441452026367</t>
   </si>
   <si>
     <t xml:space="preserve">111.829071044922</t>
@@ -3461,19 +3461,19 @@
     <t xml:space="preserve">107.274505615234</t>
   </si>
   <si>
-    <t xml:space="preserve">104.851860046387</t>
+    <t xml:space="preserve">104.851867675781</t>
   </si>
   <si>
     <t xml:space="preserve">104.658058166504</t>
   </si>
   <si>
-    <t xml:space="preserve">101.847785949707</t>
+    <t xml:space="preserve">101.847793579102</t>
   </si>
   <si>
     <t xml:space="preserve">102.429222106934</t>
   </si>
   <si>
-    <t xml:space="preserve">103.49520111084</t>
+    <t xml:space="preserve">103.495193481445</t>
   </si>
   <si>
     <t xml:space="preserve">104.076622009277</t>
@@ -3494,25 +3494,25 @@
     <t xml:space="preserve">114.348617553711</t>
   </si>
   <si>
-    <t xml:space="preserve">109.794059753418</t>
+    <t xml:space="preserve">109.794052124023</t>
   </si>
   <si>
     <t xml:space="preserve">107.468315124512</t>
   </si>
   <si>
-    <t xml:space="preserve">106.305442810059</t>
+    <t xml:space="preserve">106.305450439453</t>
   </si>
   <si>
     <t xml:space="preserve">102.332321166992</t>
   </si>
   <si>
-    <t xml:space="preserve">100.87873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.979713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.340469360352</t>
+    <t xml:space="preserve">100.878730773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.979721069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.340476989746</t>
   </si>
   <si>
     <t xml:space="preserve">117.643409729004</t>
@@ -3524,16 +3524,16 @@
     <t xml:space="preserve">117.837219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">116.771263122559</t>
+    <t xml:space="preserve">116.771255493164</t>
   </si>
   <si>
     <t xml:space="preserve">114.445518493652</t>
   </si>
   <si>
-    <t xml:space="preserve">114.73624420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.026954650879</t>
+    <t xml:space="preserve">114.736236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.026947021484</t>
   </si>
   <si>
     <t xml:space="preserve">115.317672729492</t>
@@ -3542,10 +3542,10 @@
     <t xml:space="preserve">115.51148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">115.220764160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.965057373047</t>
+    <t xml:space="preserve">115.220771789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.965065002441</t>
   </si>
   <si>
     <t xml:space="preserve">113.476463317871</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">118.612464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">112.991943359375</t>
+    <t xml:space="preserve">112.99193572998</t>
   </si>
   <si>
     <t xml:space="preserve">111.053825378418</t>
@@ -3581,10 +3581,10 @@
     <t xml:space="preserve">108.243560791016</t>
   </si>
   <si>
-    <t xml:space="preserve">107.080696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.375495910645</t>
+    <t xml:space="preserve">107.080703735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.37548828125</t>
   </si>
   <si>
     <t xml:space="preserve">108.534278869629</t>
@@ -3593,16 +3593,16 @@
     <t xml:space="preserve">110.181671142578</t>
   </si>
   <si>
-    <t xml:space="preserve">109.890960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.24764251709</t>
+    <t xml:space="preserve">109.890953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.247634887695</t>
   </si>
   <si>
     <t xml:space="preserve">113.282661437988</t>
   </si>
   <si>
-    <t xml:space="preserve">112.410507202148</t>
+    <t xml:space="preserve">112.410499572754</t>
   </si>
   <si>
     <t xml:space="preserve">114.639335632324</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">117.255783081055</t>
   </si>
   <si>
-    <t xml:space="preserve">117.352691650391</t>
+    <t xml:space="preserve">117.352684020996</t>
   </si>
   <si>
     <t xml:space="preserve">118.031028747559</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">120.162956237793</t>
   </si>
   <si>
-    <t xml:space="preserve">121.907257080078</t>
+    <t xml:space="preserve">121.907249450684</t>
   </si>
   <si>
     <t xml:space="preserve">120.550575256348</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">122.779403686523</t>
   </si>
   <si>
-    <t xml:space="preserve">123.263931274414</t>
+    <t xml:space="preserve">123.263938903809</t>
   </si>
   <si>
     <t xml:space="preserve">121.810340881348</t>
@@ -3653,10 +3653,10 @@
     <t xml:space="preserve">123.748458862305</t>
   </si>
   <si>
-    <t xml:space="preserve">131.985427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.888534545898</t>
+    <t xml:space="preserve">131.985443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.888549804688</t>
   </si>
   <si>
     <t xml:space="preserve">132.179244995117</t>
@@ -3689,10 +3689,10 @@
     <t xml:space="preserve">124.136085510254</t>
   </si>
   <si>
-    <t xml:space="preserve">123.845367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.422729492188</t>
+    <t xml:space="preserve">123.845359802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.422737121582</t>
   </si>
   <si>
     <t xml:space="preserve">121.325820922852</t>
@@ -3704,19 +3704,19 @@
     <t xml:space="preserve">120.35676574707</t>
   </si>
   <si>
-    <t xml:space="preserve">118.321739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.8681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.802200317383</t>
+    <t xml:space="preserve">118.321746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.868156433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.802207946777</t>
   </si>
   <si>
     <t xml:space="preserve">113.864097595215</t>
   </si>
   <si>
-    <t xml:space="preserve">113.960990905762</t>
+    <t xml:space="preserve">113.960998535156</t>
   </si>
   <si>
     <t xml:space="preserve">113.088836669922</t>
@@ -3725,13 +3725,13 @@
     <t xml:space="preserve">110.472389221191</t>
   </si>
   <si>
-    <t xml:space="preserve">108.824996948242</t>
+    <t xml:space="preserve">108.825004577637</t>
   </si>
   <si>
     <t xml:space="preserve">115.414573669434</t>
   </si>
   <si>
-    <t xml:space="preserve">109.987869262695</t>
+    <t xml:space="preserve">109.987861633301</t>
   </si>
   <si>
     <t xml:space="preserve">111.538352966309</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">113.670280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">118.127944946289</t>
+    <t xml:space="preserve">118.127937316895</t>
   </si>
   <si>
     <t xml:space="preserve">114.154808044434</t>
@@ -3758,13 +3758,13 @@
     <t xml:space="preserve">119.678428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">116.383628845215</t>
+    <t xml:space="preserve">116.383636474609</t>
   </si>
   <si>
     <t xml:space="preserve">115.123863220215</t>
   </si>
   <si>
-    <t xml:space="preserve">112.119789123535</t>
+    <t xml:space="preserve">112.119781494141</t>
   </si>
   <si>
     <t xml:space="preserve">110.569290161133</t>
@@ -3788,13 +3788,13 @@
     <t xml:space="preserve">104.754959106445</t>
   </si>
   <si>
-    <t xml:space="preserve">105.724006652832</t>
+    <t xml:space="preserve">105.724014282227</t>
   </si>
   <si>
     <t xml:space="preserve">103.592094421387</t>
   </si>
   <si>
-    <t xml:space="preserve">106.88688659668</t>
+    <t xml:space="preserve">106.886894226074</t>
   </si>
   <si>
     <t xml:space="preserve">103.204475402832</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">100.588027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">100.297309875488</t>
+    <t xml:space="preserve">100.297302246094</t>
   </si>
   <si>
     <t xml:space="preserve">102.719940185547</t>
@@ -3812,13 +3812,13 @@
     <t xml:space="preserve">103.107566833496</t>
   </si>
   <si>
-    <t xml:space="preserve">104.561149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.371421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.855949401855</t>
+    <t xml:space="preserve">104.561157226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.37141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.855941772461</t>
   </si>
   <si>
     <t xml:space="preserve">109.018814086914</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">116.480545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">115.705291748047</t>
+    <t xml:space="preserve">115.705299377441</t>
   </si>
   <si>
     <t xml:space="preserve">113.37956237793</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">102.235420227051</t>
   </si>
   <si>
-    <t xml:space="preserve">102.623046875</t>
+    <t xml:space="preserve">102.623039245605</t>
   </si>
   <si>
     <t xml:space="preserve">104.173530578613</t>
@@ -3872,10 +3872,10 @@
     <t xml:space="preserve">100.975639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">100.200393676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.491111755371</t>
+    <t xml:space="preserve">100.200401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.491104125977</t>
   </si>
   <si>
     <t xml:space="preserve">100.006591796875</t>
@@ -3890,10 +3890,10 @@
     <t xml:space="preserve">101.653984069824</t>
   </si>
   <si>
-    <t xml:space="preserve">100.39421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3282470703125</t>
+    <t xml:space="preserve">100.394203186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.328254699707</t>
   </si>
   <si>
     <t xml:space="preserve">99.6189727783203</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">102.138511657715</t>
   </si>
   <si>
-    <t xml:space="preserve">101.75089263916</t>
+    <t xml:space="preserve">101.750885009766</t>
   </si>
   <si>
     <t xml:space="preserve">99.8127746582031</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">97.1963272094727</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6808547973633</t>
+    <t xml:space="preserve">97.6808624267578</t>
   </si>
   <si>
     <t xml:space="preserve">99.0078277587891</t>
@@ -71615,7 +71615,7 @@
     </row>
     <row r="2539">
       <c r="A2539" s="1" t="n">
-        <v>46014.6912731481</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B2539" t="n">
         <v>59779</v>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="1761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="1762">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5495901107788</t>
+    <t xml:space="preserve">13.5495910644531</t>
   </si>
   <si>
     <t xml:space="preserve">SES.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5321054458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2523756027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9464159011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1125078201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8589992523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0513162612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.990122795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9376745223999</t>
+    <t xml:space="preserve">13.5321083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2523736953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9464139938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1125059127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.858998298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0513153076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9901237487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9376735687256</t>
   </si>
   <si>
     <t xml:space="preserve">13.1037645339966</t>
@@ -74,31 +74,31 @@
     <t xml:space="preserve">13.025089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8502559661865</t>
+    <t xml:space="preserve">12.8502569198608</t>
   </si>
   <si>
     <t xml:space="preserve">12.2383394241333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5880060195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7890663146973</t>
+    <t xml:space="preserve">12.5880069732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7890653610229</t>
   </si>
   <si>
     <t xml:space="preserve">12.7191324234009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6841669082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6054887771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3257551193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0460224151611</t>
+    <t xml:space="preserve">12.6841640472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.605489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3257579803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0460233688354</t>
   </si>
   <si>
     <t xml:space="preserve">12.1771488189697</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">12.1421813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9270906448364</t>
+    <t xml:space="preserve">10.9270877838135</t>
   </si>
   <si>
     <t xml:space="preserve">10.9795389175415</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">11.4515895843506</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0984735488892</t>
+    <t xml:space="preserve">12.0984725952148</t>
   </si>
   <si>
     <t xml:space="preserve">12.1072149276733</t>
@@ -128,34 +128,34 @@
     <t xml:space="preserve">11.8886737823486</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760904312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9323816299438</t>
+    <t xml:space="preserve">11.9760894775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9323806762695</t>
   </si>
   <si>
     <t xml:space="preserve">12.0110559463501</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0809888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8012571334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334400177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8274803161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0635080337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5005893707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6754217147827</t>
+    <t xml:space="preserve">12.0809898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8012552261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334409713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8274812698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0635061264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5005903244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6754236221313</t>
   </si>
   <si>
     <t xml:space="preserve">12.7978076934814</t>
@@ -164,19 +164,19 @@
     <t xml:space="preserve">13.1649570465088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1562147140503</t>
+    <t xml:space="preserve">13.1562156677246</t>
   </si>
   <si>
     <t xml:space="preserve">13.0687980651855</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1212501525879</t>
+    <t xml:space="preserve">13.1212482452393</t>
   </si>
   <si>
     <t xml:space="preserve">13.1911821365356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7540979385376</t>
+    <t xml:space="preserve">12.7540988922119</t>
   </si>
   <si>
     <t xml:space="preserve">12.8939638137817</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">12.9027070999146</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0600576400757</t>
+    <t xml:space="preserve">13.0600566864014</t>
   </si>
   <si>
     <t xml:space="preserve">13.1999225616455</t>
@@ -194,25 +194,25 @@
     <t xml:space="preserve">12.9813814163208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4534320831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7069406509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4709157943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4621725082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.208664894104</t>
+    <t xml:space="preserve">13.4534330368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7069425582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4709148406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4621744155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2086639404297</t>
   </si>
   <si>
     <t xml:space="preserve">13.3223066329956</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0950222015381</t>
+    <t xml:space="preserve">13.095025062561</t>
   </si>
   <si>
     <t xml:space="preserve">12.9988660812378</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">12.640456199646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4481401443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3782072067261</t>
+    <t xml:space="preserve">12.4481391906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3782062530518</t>
   </si>
   <si>
     <t xml:space="preserve">12.0285396575928</t>
@@ -233,40 +233,40 @@
     <t xml:space="preserve">12.1509227752686</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4393968582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5617809295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5268154144287</t>
+    <t xml:space="preserve">12.4393978118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5617818832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5268135070801</t>
   </si>
   <si>
     <t xml:space="preserve">12.6317148208618</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3694629669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.771580696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4306564331055</t>
+    <t xml:space="preserve">12.3694648742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7715816497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4306573867798</t>
   </si>
   <si>
     <t xml:space="preserve">12.2820482254028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1946325302124</t>
+    <t xml:space="preserve">12.1946296691895</t>
   </si>
   <si>
     <t xml:space="preserve">12.2470817565918</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4131736755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.509331703186</t>
+    <t xml:space="preserve">12.4131727218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5093307495117</t>
   </si>
   <si>
     <t xml:space="preserve">12.3869485855103</t>
@@ -284,43 +284,43 @@
     <t xml:space="preserve">12.5792655944824</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2208557128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1858901977539</t>
+    <t xml:space="preserve">12.2208566665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1858892440796</t>
   </si>
   <si>
     <t xml:space="preserve">12.7803230285645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7278738021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8764810562134</t>
+    <t xml:space="preserve">12.7278718948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8764820098877</t>
   </si>
   <si>
     <t xml:space="preserve">12.8065481185913</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7628393173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8677396774292</t>
+    <t xml:space="preserve">12.7628402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8677406311035</t>
   </si>
   <si>
     <t xml:space="preserve">12.8327741622925</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5355558395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1824407577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0338315963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3048229217529</t>
+    <t xml:space="preserve">12.5355567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1824388504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0338306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3048248291016</t>
   </si>
   <si>
     <t xml:space="preserve">13.261116027832</t>
@@ -332,43 +332,43 @@
     <t xml:space="preserve">13.6020402908325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6894578933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7244234085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7514753341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5711278915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8687028884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6252326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6432676315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.661301612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5981817245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6162147521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5260429382324</t>
+    <t xml:space="preserve">13.6894569396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.724422454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7514762878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5711297988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8687019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6252317428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6432685852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6613025665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5981798171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6162137985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5260410308838</t>
   </si>
   <si>
     <t xml:space="preserve">13.5530948638916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3456954956055</t>
+    <t xml:space="preserve">13.3456945419312</t>
   </si>
   <si>
     <t xml:space="preserve">13.5801458358765</t>
@@ -377,19 +377,19 @@
     <t xml:space="preserve">13.6973714828491</t>
   </si>
   <si>
-    <t xml:space="preserve">13.778528213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6703214645386</t>
+    <t xml:space="preserve">13.7785272598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6703195571899</t>
   </si>
   <si>
     <t xml:space="preserve">13.7965631484985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9769096374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0400314331055</t>
+    <t xml:space="preserve">13.9769105911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0400323867798</t>
   </si>
   <si>
     <t xml:space="preserve">14.0129795074463</t>
@@ -398,40 +398,40 @@
     <t xml:space="preserve">13.9047718048096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1031522750854</t>
+    <t xml:space="preserve">14.1031532287598</t>
   </si>
   <si>
     <t xml:space="preserve">14.2474298477173</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1572570800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3646564483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4187612533569</t>
+    <t xml:space="preserve">14.1572561264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3646583557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4187593460083</t>
   </si>
   <si>
     <t xml:space="preserve">14.5179510116577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6081247329712</t>
+    <t xml:space="preserve">14.6081266403198</t>
   </si>
   <si>
     <t xml:space="preserve">14.6622295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3917074203491</t>
+    <t xml:space="preserve">14.3917083740234</t>
   </si>
   <si>
     <t xml:space="preserve">14.3105525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3015356063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5450019836426</t>
+    <t xml:space="preserve">14.30153465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5450038909912</t>
   </si>
   <si>
     <t xml:space="preserve">14.6441946029663</t>
@@ -443,28 +443,28 @@
     <t xml:space="preserve">14.7163333892822</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6351776123047</t>
+    <t xml:space="preserve">14.6351757049561</t>
   </si>
   <si>
     <t xml:space="preserve">14.6261606216431</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6892824172974</t>
+    <t xml:space="preserve">14.6892833709717</t>
   </si>
   <si>
     <t xml:space="preserve">14.8245420455933</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8065061569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7433853149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.581072807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6982975006104</t>
+    <t xml:space="preserve">14.8065071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7433862686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5810747146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6982984542847</t>
   </si>
   <si>
     <t xml:space="preserve">14.5089340209961</t>
@@ -473,40 +473,40 @@
     <t xml:space="preserve">14.6712484359741</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6532125473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.923731803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0499782562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2122898101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3746004104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5549459457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9246625900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7803831100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8705549240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344841003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7082424163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517097473145</t>
+    <t xml:space="preserve">14.6532115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9237327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0499773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2122917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3746013641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5549478530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9246606826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7803812026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8705568313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344869613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7082433700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517107009888</t>
   </si>
   <si>
     <t xml:space="preserve">16.7452411651611</t>
@@ -515,19 +515,19 @@
     <t xml:space="preserve">16.8714828491211</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0879001617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1510200500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2231597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9796905517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9075527191162</t>
+    <t xml:space="preserve">17.0879039764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1510219573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2231636047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9796924591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9075546264648</t>
   </si>
   <si>
     <t xml:space="preserve">17.3043155670166</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">17.0337944030762</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2772655487061</t>
+    <t xml:space="preserve">17.2772636413574</t>
   </si>
   <si>
     <t xml:space="preserve">17.4756469726562</t>
@@ -545,25 +545,25 @@
     <t xml:space="preserve">17.3223495483398</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1690578460693</t>
+    <t xml:space="preserve">17.1690559387207</t>
   </si>
   <si>
     <t xml:space="preserve">17.583854675293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.574836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5658206939697</t>
+    <t xml:space="preserve">17.5748386383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5658168792725</t>
   </si>
   <si>
     <t xml:space="preserve">17.2411956787109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1870899200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8534488677979</t>
+    <t xml:space="preserve">17.1870918273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8534469604492</t>
   </si>
   <si>
     <t xml:space="preserve">16.8444309234619</t>
@@ -572,40 +572,40 @@
     <t xml:space="preserve">16.9526386260986</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7272033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6911373138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8624649047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0428142547607</t>
+    <t xml:space="preserve">16.7272071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6911354064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8624687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0428123474121</t>
   </si>
   <si>
     <t xml:space="preserve">16.8173789978027</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9977264404297</t>
+    <t xml:space="preserve">16.9977283477783</t>
   </si>
   <si>
     <t xml:space="preserve">16.7722930908203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0067443847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1961059570312</t>
+    <t xml:space="preserve">17.006742477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1961078643799</t>
   </si>
   <si>
     <t xml:space="preserve">17.358419418335</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6199245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7642021179199</t>
+    <t xml:space="preserve">17.6199264526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7642002105713</t>
   </si>
   <si>
     <t xml:space="preserve">18.0076694488525</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">17.9896354675293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9445476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9535655975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8092880249023</t>
+    <t xml:space="preserve">17.9445495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9535675048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.809289932251</t>
   </si>
   <si>
     <t xml:space="preserve">18.2601566314697</t>
@@ -629,13 +629,13 @@
     <t xml:space="preserve">18.7561092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8462867736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9364604949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6208477020264</t>
+    <t xml:space="preserve">18.846284866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9364585876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.620849609375</t>
   </si>
   <si>
     <t xml:space="preserve">19.2971515655518</t>
@@ -647,106 +647,106 @@
     <t xml:space="preserve">19.3512573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6668643951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6488304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5586566925049</t>
+    <t xml:space="preserve">19.666862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.648832321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5586585998535</t>
   </si>
   <si>
     <t xml:space="preserve">19.2520656585693</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1709136962891</t>
+    <t xml:space="preserve">19.1709098815918</t>
   </si>
   <si>
     <t xml:space="preserve">19.1348400115967</t>
   </si>
   <si>
-    <t xml:space="preserve">19.197961807251</t>
+    <t xml:space="preserve">19.1979637145996</t>
   </si>
   <si>
     <t xml:space="preserve">18.9544925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9094047546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0897541046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5757656097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1970367431641</t>
+    <t xml:space="preserve">18.9094066619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0897560119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5757637023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1970329284668</t>
   </si>
   <si>
     <t xml:space="preserve">18.5306758880615</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8372707366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4594669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3873252868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0185432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3612003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8301067352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2809753417969</t>
+    <t xml:space="preserve">18.8372669219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4594650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3873271942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0185413360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3612022399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8301048278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.280969619751</t>
   </si>
   <si>
     <t xml:space="preserve">20.8751907348633</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9292945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1006278991699</t>
+    <t xml:space="preserve">20.929292678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1006240844727</t>
   </si>
   <si>
     <t xml:space="preserve">21.0104503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5685977935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7218933105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6046714782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1898727416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792362213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6497592926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6416683197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3711490631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3801593780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0925350189209</t>
+    <t xml:space="preserve">20.5685997009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7218952178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6046695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1898746490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792343139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6497573852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6416645050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3711471557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3801612854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0925312042236</t>
   </si>
   <si>
     <t xml:space="preserve">22.6245594024658</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">22.7147350311279</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8049068450928</t>
+    <t xml:space="preserve">22.8049049377441</t>
   </si>
   <si>
     <t xml:space="preserve">23.5984363555908</t>
@@ -764,52 +764,52 @@
     <t xml:space="preserve">24.0763549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0583190917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7156600952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9320774078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8599376678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8058319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5082588195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9942722320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4802799224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5434055328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.705717086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4532318115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4622478485107</t>
+    <t xml:space="preserve">24.0583209991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7156581878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9320755004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8599338531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8058338165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5082607269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9942684173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.480281829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5434017181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7057151794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4532299041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4622497558594</t>
   </si>
   <si>
     <t xml:space="preserve">22.0023612976074</t>
   </si>
   <si>
-    <t xml:space="preserve">22.182710647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7237510681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3630542755127</t>
+    <t xml:space="preserve">22.1827087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7237529754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3630561828613</t>
   </si>
   <si>
     <t xml:space="preserve">22.2097587585449</t>
@@ -818,16 +818,16 @@
     <t xml:space="preserve">21.4883728027344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9212036132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8761157989502</t>
+    <t xml:space="preserve">21.9212017059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8761196136475</t>
   </si>
   <si>
     <t xml:space="preserve">21.7047901153564</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9392414093018</t>
+    <t xml:space="preserve">21.9392395019531</t>
   </si>
   <si>
     <t xml:space="preserve">22.0745010375977</t>
@@ -836,28 +836,28 @@
     <t xml:space="preserve">22.299934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8139266967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3179683685303</t>
+    <t xml:space="preserve">22.8139228820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3179664611816</t>
   </si>
   <si>
     <t xml:space="preserve">22.1917266845703</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3540382385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.525369644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6065235137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6335773468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2458324432373</t>
+    <t xml:space="preserve">22.3540363311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5253677368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6065273284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6335754394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2458305358887</t>
   </si>
   <si>
     <t xml:space="preserve">22.2277965545654</t>
@@ -869,31 +869,31 @@
     <t xml:space="preserve">22.083517074585</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2007446289062</t>
+    <t xml:space="preserve">22.2007465362549</t>
   </si>
   <si>
     <t xml:space="preserve">22.1376209259033</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1466369628906</t>
+    <t xml:space="preserve">22.1466388702393</t>
   </si>
   <si>
     <t xml:space="preserve">21.5965805053711</t>
   </si>
   <si>
-    <t xml:space="preserve">21.326057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.560510635376</t>
+    <t xml:space="preserve">21.3260593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5605125427246</t>
   </si>
   <si>
     <t xml:space="preserve">22.0294132232666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6867542266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2368125915527</t>
+    <t xml:space="preserve">21.6867523193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2368144989014</t>
   </si>
   <si>
     <t xml:space="preserve">22.3720722198486</t>
@@ -902,70 +902,70 @@
     <t xml:space="preserve">22.3991260528564</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6155395507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6606292724609</t>
+    <t xml:space="preserve">22.6155414581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6606273651123</t>
   </si>
   <si>
     <t xml:space="preserve">23.0123062133789</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5193862915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2704563140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1739845275879</t>
+    <t xml:space="preserve">23.5193901062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2704582214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1739864349365</t>
   </si>
   <si>
     <t xml:space="preserve">24.7087268829346</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7732620239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.243465423584</t>
+    <t xml:space="preserve">24.7732639312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2434692382812</t>
   </si>
   <si>
     <t xml:space="preserve">25.8150863647461</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7966461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6860122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6675720214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0086975097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.888843536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9810428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0916728973389</t>
+    <t xml:space="preserve">25.7966480255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6860103607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.667573928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0087013244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8888416290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9810409545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0916748046875</t>
   </si>
   <si>
     <t xml:space="preserve">25.907283782959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8058681488037</t>
+    <t xml:space="preserve">25.8058700561523</t>
   </si>
   <si>
     <t xml:space="preserve">25.9533805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">25.676794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.658353805542</t>
+    <t xml:space="preserve">25.6767902374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6583499908447</t>
   </si>
   <si>
     <t xml:space="preserve">25.0775146484375</t>
@@ -977,28 +977,28 @@
     <t xml:space="preserve">25.2619075775146</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3264427185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8009223937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4186401367188</t>
+    <t xml:space="preserve">25.3264446258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8009204864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4186420440674</t>
   </si>
   <si>
     <t xml:space="preserve">24.6441898345947</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8562393188477</t>
+    <t xml:space="preserve">24.8562412261963</t>
   </si>
   <si>
     <t xml:space="preserve">24.9576568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8931217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1874809265137</t>
+    <t xml:space="preserve">24.8931179046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.187479019165</t>
   </si>
   <si>
     <t xml:space="preserve">22.9754276275635</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">23.2335796356201</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9938659667969</t>
+    <t xml:space="preserve">22.9938678741455</t>
   </si>
   <si>
     <t xml:space="preserve">23.0123043060303</t>
@@ -1025,25 +1025,25 @@
     <t xml:space="preserve">22.4960041046143</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7264976501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5052223205566</t>
+    <t xml:space="preserve">22.7264957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5052242279053</t>
   </si>
   <si>
     <t xml:space="preserve">22.3208293914795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5882015228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1137218475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9108905792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3995323181152</t>
+    <t xml:space="preserve">22.5881977081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1137237548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9108867645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3995304107666</t>
   </si>
   <si>
     <t xml:space="preserve">23.7775402069092</t>
@@ -1052,10 +1052,10 @@
     <t xml:space="preserve">23.6208076477051</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9846458435059</t>
+    <t xml:space="preserve">23.1413803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9846477508545</t>
   </si>
   <si>
     <t xml:space="preserve">22.8740100860596</t>
@@ -1067,34 +1067,34 @@
     <t xml:space="preserve">22.6896171569824</t>
   </si>
   <si>
-    <t xml:space="preserve">23.325777053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7406597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9803714752197</t>
+    <t xml:space="preserve">23.3257751464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7406578063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.980375289917</t>
   </si>
   <si>
     <t xml:space="preserve">23.9711513519287</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0633525848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2477416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3860397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1555442810059</t>
+    <t xml:space="preserve">24.0633449554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2477397918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3860378265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1555480957031</t>
   </si>
   <si>
     <t xml:space="preserve">24.6165294647217</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8611850738525</t>
+    <t xml:space="preserve">25.8611831665039</t>
   </si>
   <si>
     <t xml:space="preserve">25.6306934356689</t>
@@ -1103,28 +1103,28 @@
     <t xml:space="preserve">25.2158069610596</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1697101593018</t>
+    <t xml:space="preserve">25.1697063446045</t>
   </si>
   <si>
     <t xml:space="preserve">25.3080062866211</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4463024139404</t>
+    <t xml:space="preserve">25.4463005065918</t>
   </si>
   <si>
     <t xml:space="preserve">25.5384979248047</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1236114501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4321365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6484642028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0172481536865</t>
+    <t xml:space="preserve">25.1236095428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4321346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6484622955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0172500610352</t>
   </si>
   <si>
     <t xml:space="preserve">24.109447479248</t>
@@ -1136,49 +1136,49 @@
     <t xml:space="preserve">24.2016429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2938423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7548217773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6626300811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9853172302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4923973083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7228908538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5704307556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5845966339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9994792938232</t>
+    <t xml:space="preserve">24.2938404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7548236846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6626281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.985315322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.492395401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7228870391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5704288482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5845947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9994831085205</t>
   </si>
   <si>
     <t xml:space="preserve">26.4143657684326</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5668239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7512168884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0739097595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5207271575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7370510101318</t>
+    <t xml:space="preserve">27.5668258666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7512187957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0739059448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5207252502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7370567321777</t>
   </si>
   <si>
     <t xml:space="preserve">26.5065612792969</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">25.0314140319824</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5243358612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3682651519775</t>
+    <t xml:space="preserve">24.5243320465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3682670593262</t>
   </si>
   <si>
     <t xml:space="preserve">26.5987586975098</t>
@@ -1199,127 +1199,127 @@
     <t xml:space="preserve">26.4604644775391</t>
   </si>
   <si>
+    <t xml:space="preserve">26.2299747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3221664428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1980361938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2760696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2902355194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3824310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4746265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5526599884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8292503356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.105842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8753471374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.843412399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.765380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5809879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9356117248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8114814758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1661033630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7192859649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1200046539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0597438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9675445556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1519374847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6909561157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7831516265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0455760955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6590194702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9214477539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1828804016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0886974334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4654293060303</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.2299728393555</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3221702575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1980361938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2760715484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2902355194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3824310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4746265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5526599884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.829252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1058387756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8753509521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8434143066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7653846740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5809879302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9356098175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8114833831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1661052703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7192840576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1200046539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0597457885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9675445556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1519412994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6909561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7831535339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0455799102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6590232849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9214477539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1828784942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.088695526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4654312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2299709320068</t>
-  </si>
-  <si>
     <t xml:space="preserve">25.8061466217041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7119655609131</t>
+    <t xml:space="preserve">25.7119674682617</t>
   </si>
   <si>
     <t xml:space="preserve">25.1468677520752</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3352298736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.911413192749</t>
+    <t xml:space="preserve">25.3352336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9114112854004</t>
   </si>
   <si>
     <t xml:space="preserve">24.487585067749</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3934001922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9224853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2632064819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0277481079102</t>
+    <t xml:space="preserve">24.393404006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9224872589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2632083892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0277500152588</t>
   </si>
   <si>
     <t xml:space="preserve">23.0748405456543</t>
@@ -1328,31 +1328,31 @@
     <t xml:space="preserve">22.7451992034912</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6039276123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5097427368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4155597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1800994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0388278961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8504638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4626522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2271938323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4044799804688</t>
+    <t xml:space="preserve">22.6039257049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5097408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4155578613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1801013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0388259887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8504619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4626502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2271919250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4044818878174</t>
   </si>
   <si>
     <t xml:space="preserve">23.2161159515381</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">23.498664855957</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5568351745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1330108642578</t>
+    <t xml:space="preserve">22.5568332672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1330089569092</t>
   </si>
   <si>
     <t xml:space="preserve">21.6620960235596</t>
@@ -1379,28 +1379,28 @@
     <t xml:space="preserve">21.0028133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.096996307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8615398406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.379545211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.473726272583</t>
+    <t xml:space="preserve">21.0969982147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8615379333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3795471191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4737300872803</t>
   </si>
   <si>
     <t xml:space="preserve">22.274284362793</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7562808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9446430206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5679130554199</t>
+    <t xml:space="preserve">21.7562770843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9446449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5679111480713</t>
   </si>
   <si>
     <t xml:space="preserve">21.5208206176758</t>
@@ -1409,19 +1409,19 @@
     <t xml:space="preserve">21.3324527740479</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2382717132568</t>
+    <t xml:space="preserve">21.2382698059082</t>
   </si>
   <si>
     <t xml:space="preserve">22.8393821716309</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7922916412354</t>
+    <t xml:space="preserve">22.792293548584</t>
   </si>
   <si>
     <t xml:space="preserve">23.5457553863525</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6399383544922</t>
+    <t xml:space="preserve">23.6399364471436</t>
   </si>
   <si>
     <t xml:space="preserve">23.7341232299805</t>
@@ -1430,34 +1430,34 @@
     <t xml:space="preserve">23.6870288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7812118530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0166721343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2992210388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1579475402832</t>
+    <t xml:space="preserve">23.781213760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0166702270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2992191314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1579437255859</t>
   </si>
   <si>
     <t xml:space="preserve">24.2521286010742</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7230415344238</t>
+    <t xml:space="preserve">24.7230434417725</t>
   </si>
   <si>
     <t xml:space="preserve">24.6288604736328</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6759490966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5817699432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7701320648193</t>
+    <t xml:space="preserve">24.675952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5817680358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.770133972168</t>
   </si>
   <si>
     <t xml:space="preserve">24.9584999084473</t>
@@ -1466,58 +1466,58 @@
     <t xml:space="preserve">25.9003295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7590579986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9474201202393</t>
+    <t xml:space="preserve">25.75905418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9474220275879</t>
   </si>
   <si>
     <t xml:space="preserve">26.277063369751</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9363441467285</t>
+    <t xml:space="preserve">26.9363460540771</t>
   </si>
   <si>
     <t xml:space="preserve">26.983434677124</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8421630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7479801177979</t>
+    <t xml:space="preserve">26.8421611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7479782104492</t>
   </si>
   <si>
     <t xml:space="preserve">27.2659854888916</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4543514251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.501443862915</t>
+    <t xml:space="preserve">27.4543533325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5014419555664</t>
   </si>
   <si>
     <t xml:space="preserve">27.3130760192871</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0776176452637</t>
+    <t xml:space="preserve">27.0776195526123</t>
   </si>
   <si>
     <t xml:space="preserve">26.7008857727051</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6537933349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6067047119141</t>
+    <t xml:space="preserve">26.6537971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6067028045654</t>
   </si>
   <si>
     <t xml:space="preserve">25.994514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1357898712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0416049957275</t>
+    <t xml:space="preserve">26.1357879638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0416069030762</t>
   </si>
   <si>
     <t xml:space="preserve">25.6177825927734</t>
@@ -1526,25 +1526,25 @@
     <t xml:space="preserve">25.4294166564941</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0055923461914</t>
+    <t xml:space="preserve">25.00559425354</t>
   </si>
   <si>
     <t xml:space="preserve">25.0997753143311</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8643188476562</t>
+    <t xml:space="preserve">24.8643169403076</t>
   </si>
   <si>
     <t xml:space="preserve">24.4404964447021</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5235977172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3712463378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3241558074951</t>
+    <t xml:space="preserve">25.5235996246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.371244430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3241577148438</t>
   </si>
   <si>
     <t xml:space="preserve">26.7950706481934</t>
@@ -1553,52 +1553,52 @@
     <t xml:space="preserve">26.889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0305290222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.171802520752</t>
+    <t xml:space="preserve">27.0305252075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1718006134033</t>
   </si>
   <si>
     <t xml:space="preserve">27.5485343933105</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6898097991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1136341094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3961791992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7258243560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9141883850098</t>
+    <t xml:space="preserve">27.6898059844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1136322021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3961811065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7258224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9141864776611</t>
   </si>
   <si>
     <t xml:space="preserve">29.9502010345459</t>
   </si>
   <si>
-    <t xml:space="preserve">29.761833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3269329071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5042209625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6925849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4460525512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4931411743164</t>
+    <t xml:space="preserve">29.7618312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3269348144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3740253448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5042190551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6925868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4460487365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4931373596191</t>
   </si>
   <si>
     <t xml:space="preserve">33.4820671081543</t>
@@ -1613,16 +1613,16 @@
     <t xml:space="preserve">33.5762481689453</t>
   </si>
   <si>
-    <t xml:space="preserve">33.905891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2466087341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8698768615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1524200439453</t>
+    <t xml:space="preserve">33.9058876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2466049194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.869873046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1524276733398</t>
   </si>
   <si>
     <t xml:space="preserve">33.0582389831543</t>
@@ -1634,64 +1634,64 @@
     <t xml:space="preserve">32.3047790527344</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9280433654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4571304321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3629417419434</t>
+    <t xml:space="preserve">31.9280452728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4571285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3629474639893</t>
   </si>
   <si>
     <t xml:space="preserve">30.8920288085938</t>
   </si>
   <si>
-    <t xml:space="preserve">31.080394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0333042144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6565742492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6094837188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.268762588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.986213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4100379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8449382781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.17458152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8809471130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0222282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7396850585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0000686645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4709892272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.78955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5901031494141</t>
+    <t xml:space="preserve">31.0803928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0333080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6565761566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6094799041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2687644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9862155914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4100399017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8449401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1745777130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8809509277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0222244262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7396831512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.000072479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4709815979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7895469665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5901069641113</t>
   </si>
   <si>
     <t xml:space="preserve">36.7784690856934</t>
@@ -1715,13 +1715,13 @@
     <t xml:space="preserve">37.797607421875</t>
   </si>
   <si>
-    <t xml:space="preserve">38.180362701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3717460632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9411430358887</t>
+    <t xml:space="preserve">38.1803665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3717422485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9411392211914</t>
   </si>
   <si>
     <t xml:space="preserve">37.9889869689941</t>
@@ -1730,16 +1730,16 @@
     <t xml:space="preserve">37.8454513549805</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3191566467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8501968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.754508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3286437988281</t>
+    <t xml:space="preserve">37.3191528320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8501930236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7545051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3286476135254</t>
   </si>
   <si>
     <t xml:space="preserve">39.041576385498</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">38.1325187683105</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8980407714844</t>
+    <t xml:space="preserve">38.8980445861816</t>
   </si>
   <si>
     <t xml:space="preserve">38.7066612243652</t>
@@ -1772,13 +1772,13 @@
     <t xml:space="preserve">39.3764953613281</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1372718811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.185115814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2807998657227</t>
+    <t xml:space="preserve">39.1372680664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1851119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2808036804199</t>
   </si>
   <si>
     <t xml:space="preserve">39.9027900695801</t>
@@ -1787,40 +1787,40 @@
     <t xml:space="preserve">41.1946067810059</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1036605834961</t>
+    <t xml:space="preserve">42.1036643981934</t>
   </si>
   <si>
     <t xml:space="preserve">42.5342674255371</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6730499267578</t>
+    <t xml:space="preserve">41.6730575561523</t>
   </si>
   <si>
     <t xml:space="preserve">40.8118476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7161521911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9122848510742</t>
+    <t xml:space="preserve">40.7161598205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.912281036377</t>
   </si>
   <si>
     <t xml:space="preserve">43.0605621337891</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4911651611328</t>
+    <t xml:space="preserve">43.4911689758301</t>
   </si>
   <si>
     <t xml:space="preserve">44.2566909790039</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7829895019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4433212280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.017463684082</t>
+    <t xml:space="preserve">44.7829818725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4433250427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0174674987793</t>
   </si>
   <si>
     <t xml:space="preserve">43.6347045898438</t>
@@ -1829,37 +1829,37 @@
     <t xml:space="preserve">43.2041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9170303344727</t>
+    <t xml:space="preserve">42.9170265197754</t>
   </si>
   <si>
     <t xml:space="preserve">44.9265213012695</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4049758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2614326477051</t>
+    <t xml:space="preserve">45.404972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2614364624023</t>
   </si>
   <si>
     <t xml:space="preserve">45.5963554382324</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6536865234375</t>
+    <t xml:space="preserve">47.6536903381348</t>
   </si>
   <si>
     <t xml:space="preserve">48.8976631164551</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6105918884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1847343444824</t>
+    <t xml:space="preserve">48.610595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1847381591797</t>
   </si>
   <si>
     <t xml:space="preserve">48.993350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7588729858398</t>
+    <t xml:space="preserve">49.7588691711426</t>
   </si>
   <si>
     <t xml:space="preserve">49.2804260253906</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">49.3761138916016</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5674896240234</t>
+    <t xml:space="preserve">49.5674934387207</t>
   </si>
   <si>
     <t xml:space="preserve">50.6200866699219</t>
@@ -1880,25 +1880,25 @@
     <t xml:space="preserve">51.0028457641602</t>
   </si>
   <si>
-    <t xml:space="preserve">52.725269317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6295776367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.9597473144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8640556335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.672679901123</t>
+    <t xml:space="preserve">52.7252655029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6295738220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9597434997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8640594482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6726760864258</t>
   </si>
   <si>
     <t xml:space="preserve">48.4192085266113</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3235244750977</t>
+    <t xml:space="preserve">48.3235206604004</t>
   </si>
   <si>
     <t xml:space="preserve">50.0459442138672</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">51.3856048583984</t>
   </si>
   <si>
-    <t xml:space="preserve">50.907154083252</t>
+    <t xml:space="preserve">50.9071578979492</t>
   </si>
   <si>
     <t xml:space="preserve">49.8545608520508</t>
@@ -1916,40 +1916,40 @@
     <t xml:space="preserve">50.4287033081055</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5338897705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0649299621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2994079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4381980895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3666191101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9838562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.361873626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7398872375488</t>
+    <t xml:space="preserve">52.5338935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0649261474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2994117736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4381942749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3666152954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9838600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3618774414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7398834228516</t>
   </si>
   <si>
     <t xml:space="preserve">44.974365234375</t>
   </si>
   <si>
-    <t xml:space="preserve">43.586856842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7687454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6493263244629</t>
+    <t xml:space="preserve">43.5868606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7687492370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6493186950684</t>
   </si>
   <si>
     <t xml:space="preserve">35.5967330932617</t>
@@ -1958,31 +1958,31 @@
     <t xml:space="preserve">30.0945491790771</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4820575714111</t>
+    <t xml:space="preserve">31.4820594787598</t>
   </si>
   <si>
     <t xml:space="preserve">29.1854934692383</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5299034118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0993003845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3816204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9269027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.410099029541</t>
+    <t xml:space="preserve">31.5299053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0992946624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3816223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9268951416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4101028442383</t>
   </si>
   <si>
     <t xml:space="preserve">35.5010414123535</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3096618652344</t>
+    <t xml:space="preserve">35.3096656799316</t>
   </si>
   <si>
     <t xml:space="preserve">34.5441398620605</t>
@@ -2000,43 +2000,43 @@
     <t xml:space="preserve">37.1277732849121</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2329559326172</t>
+    <t xml:space="preserve">39.2329521179199</t>
   </si>
   <si>
     <t xml:space="preserve">40.429084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9984741210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7351455688477</t>
+    <t xml:space="preserve">39.998477935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7351417541504</t>
   </si>
   <si>
     <t xml:space="preserve">45.9791145324707</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4528198242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0700531005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3571281433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1179046630859</t>
+    <t xml:space="preserve">45.4528160095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0700569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3571319580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1179008483887</t>
   </si>
   <si>
     <t xml:space="preserve">46.4575653076172</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6441993713379</t>
+    <t xml:space="preserve">45.6441955566406</t>
   </si>
   <si>
     <t xml:space="preserve">44.8786773681641</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3092765808105</t>
+    <t xml:space="preserve">45.3092803955078</t>
   </si>
   <si>
     <t xml:space="preserve">45.1657447814941</t>
@@ -2045,19 +2045,19 @@
     <t xml:space="preserve">44.2088470458984</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1562538146973</t>
+    <t xml:space="preserve">43.15625</t>
   </si>
   <si>
     <t xml:space="preserve">43.9217758178711</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8644409179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5821113586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0222091674805</t>
+    <t xml:space="preserve">41.8644371032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5821151733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0222129821777</t>
   </si>
   <si>
     <t xml:space="preserve">45.5485038757324</t>
@@ -2066,40 +2066,40 @@
     <t xml:space="preserve">47.5101585388184</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7015342712402</t>
+    <t xml:space="preserve">47.701530456543</t>
   </si>
   <si>
     <t xml:space="preserve">48.7062835693359</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9407577514648</t>
+    <t xml:space="preserve">47.9407615661621</t>
   </si>
   <si>
     <t xml:space="preserve">48.5149002075195</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4812927246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1942291259766</t>
+    <t xml:space="preserve">51.4812965393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1942253112793</t>
   </si>
   <si>
     <t xml:space="preserve">51.768367767334</t>
   </si>
   <si>
-    <t xml:space="preserve">51.289909362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.108024597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.96923828125</t>
+    <t xml:space="preserve">51.2899131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1080284118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9692420959473</t>
   </si>
   <si>
     <t xml:space="preserve">53.490795135498</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1175231933594</t>
+    <t xml:space="preserve">55.1175193786621</t>
   </si>
   <si>
     <t xml:space="preserve">55.6916618347168</t>
@@ -2114,28 +2114,28 @@
     <t xml:space="preserve">54.6390686035156</t>
   </si>
   <si>
-    <t xml:space="preserve">54.830451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4045906066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7442512512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9356384277344</t>
+    <t xml:space="preserve">54.8304481506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4045944213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.744255065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9356307983398</t>
   </si>
   <si>
     <t xml:space="preserve">57.1270141601562</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2658081054688</t>
+    <t xml:space="preserve">56.2658004760742</t>
   </si>
   <si>
     <t xml:space="preserve">55.9787330627441</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3183975219727</t>
+    <t xml:space="preserve">57.3183898925781</t>
   </si>
   <si>
     <t xml:space="preserve">58.6580581665039</t>
@@ -2144,52 +2144,52 @@
     <t xml:space="preserve">57.2227020263672</t>
   </si>
   <si>
-    <t xml:space="preserve">57.7011489868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3614959716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9882278442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.849437713623</t>
+    <t xml:space="preserve">57.7011566162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3614921569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.988224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8494338989258</t>
   </si>
   <si>
     <t xml:space="preserve">61.3373794555664</t>
   </si>
   <si>
-    <t xml:space="preserve">63.4425735473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2942810058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3468704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7296333312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6339378356934</t>
+    <t xml:space="preserve">63.4425621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2942848205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.346866607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7296371459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6339454650879</t>
   </si>
   <si>
     <t xml:space="preserve">64.3037719726562</t>
   </si>
   <si>
-    <t xml:space="preserve">64.5908508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9304962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6960220336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3563690185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.9830932617188</t>
+    <t xml:space="preserve">64.5908432006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9305038452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6960296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3563613891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9831008911133</t>
   </si>
   <si>
     <t xml:space="preserve">67.1744766235352</t>
@@ -2201,82 +2201,82 @@
     <t xml:space="preserve">67.8443145751953</t>
   </si>
   <si>
-    <t xml:space="preserve">70.0451889038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1839828491211</t>
+    <t xml:space="preserve">70.0451812744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.183967590332</t>
   </si>
   <si>
     <t xml:space="preserve">71.2891540527344</t>
   </si>
   <si>
-    <t xml:space="preserve">70.8106994628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6193237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7676086425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.0546875</t>
+    <t xml:space="preserve">70.8107070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6193313598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7676010131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.0546722412109</t>
   </si>
   <si>
     <t xml:space="preserve">71.002082824707</t>
   </si>
   <si>
-    <t xml:space="preserve">69.4710311889648</t>
+    <t xml:space="preserve">69.4710388183594</t>
   </si>
   <si>
     <t xml:space="preserve">68.9925918579102</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9495010375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8012084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.6624298095703</t>
+    <t xml:space="preserve">69.9494934082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8012161254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.6624221801758</t>
   </si>
   <si>
     <t xml:space="preserve">76.5521087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7003936767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8822860717773</t>
+    <t xml:space="preserve">77.7003860473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8822784423828</t>
   </si>
   <si>
     <t xml:space="preserve">74.734001159668</t>
   </si>
   <si>
-    <t xml:space="preserve">73.8727874755859</t>
+    <t xml:space="preserve">73.8727798461914</t>
   </si>
   <si>
     <t xml:space="preserve">74.8296890258789</t>
   </si>
   <si>
-    <t xml:space="preserve">77.8917694091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.274543762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.7960815429688</t>
+    <t xml:space="preserve">77.8917770385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.2745361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.7960891723633</t>
   </si>
   <si>
     <t xml:space="preserve">79.4228210449219</t>
   </si>
   <si>
-    <t xml:space="preserve">80.7624740600586</t>
+    <t xml:space="preserve">80.7624893188477</t>
   </si>
   <si>
     <t xml:space="preserve">82.0064468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">81.5279922485352</t>
+    <t xml:space="preserve">81.5279998779297</t>
   </si>
   <si>
     <t xml:space="preserve">81.910758972168</t>
@@ -2285,79 +2285,79 @@
     <t xml:space="preserve">82.3892135620117</t>
   </si>
   <si>
-    <t xml:space="preserve">81.4323043823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.1452484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4754104614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7193832397461</t>
+    <t xml:space="preserve">81.4323196411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1452407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4754028320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7193756103516</t>
   </si>
   <si>
     <t xml:space="preserve">81.815071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">83.3460998535156</t>
+    <t xml:space="preserve">83.3461151123047</t>
   </si>
   <si>
     <t xml:space="preserve">80.953857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">82.77197265625</t>
+    <t xml:space="preserve">82.7719802856445</t>
   </si>
   <si>
     <t xml:space="preserve">82.2935180664062</t>
   </si>
   <si>
-    <t xml:space="preserve">77.0305709838867</t>
+    <t xml:space="preserve">77.0305633544922</t>
   </si>
   <si>
     <t xml:space="preserve">79.3271331787109</t>
   </si>
   <si>
-    <t xml:space="preserve">83.7288818359375</t>
+    <t xml:space="preserve">83.728874206543</t>
   </si>
   <si>
     <t xml:space="preserve">82.1021499633789</t>
   </si>
   <si>
-    <t xml:space="preserve">76.7434921264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.5185089111328</t>
+    <t xml:space="preserve">76.7434844970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.5185165405273</t>
   </si>
   <si>
     <t xml:space="preserve">79.8055801391602</t>
   </si>
   <si>
-    <t xml:space="preserve">82.4849014282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3797225952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.6572875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.4659118652344</t>
+    <t xml:space="preserve">82.4848937988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3797149658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.6572952270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.4659042358398</t>
   </si>
   <si>
     <t xml:space="preserve">84.6857757568359</t>
   </si>
   <si>
-    <t xml:space="preserve">85.355598449707</t>
+    <t xml:space="preserve">85.3556060791016</t>
   </si>
   <si>
     <t xml:space="preserve">83.0590438842773</t>
   </si>
   <si>
-    <t xml:space="preserve">85.9297485351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.173713684082</t>
+    <t xml:space="preserve">85.9297561645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.1737213134766</t>
   </si>
   <si>
     <t xml:space="preserve">87.2694091796875</t>
@@ -2366,28 +2366,28 @@
     <t xml:space="preserve">88.3219985961914</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7909622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.9056396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3840866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1065139770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.8815155029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.2211837768555</t>
+    <t xml:space="preserve">86.7909545898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.905632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3840942382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1065063476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.8815231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.22119140625</t>
   </si>
   <si>
     <t xml:space="preserve">100.474647521973</t>
   </si>
   <si>
-    <t xml:space="preserve">101.622924804688</t>
+    <t xml:space="preserve">101.622940063477</t>
   </si>
   <si>
     <t xml:space="preserve">101.240173339844</t>
@@ -2399,10 +2399,10 @@
     <t xml:space="preserve">98.5608520507812</t>
   </si>
   <si>
-    <t xml:space="preserve">99.9005126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2642822265625</t>
+    <t xml:space="preserve">99.900505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.264274597168</t>
   </si>
   <si>
     <t xml:space="preserve">95.6901397705078</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">94.8289337158203</t>
   </si>
   <si>
-    <t xml:space="preserve">95.307373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2547836303711</t>
+    <t xml:space="preserve">95.3073806762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2547912597656</t>
   </si>
   <si>
     <t xml:space="preserve">94.4461669921875</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">97.0298004150391</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5418548583984</t>
+    <t xml:space="preserve">94.541862487793</t>
   </si>
   <si>
     <t xml:space="preserve">94.1590957641602</t>
@@ -2432,10 +2432,10 @@
     <t xml:space="preserve">93.8720245361328</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0634155273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3935699462891</t>
+    <t xml:space="preserve">94.0634002685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3935775756836</t>
   </si>
   <si>
     <t xml:space="preserve">93.6806488037109</t>
@@ -2444,76 +2444,76 @@
     <t xml:space="preserve">92.9151306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">93.2978820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.723747253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3504867553711</t>
+    <t xml:space="preserve">93.2978897094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7237548828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3504791259766</t>
   </si>
   <si>
     <t xml:space="preserve">97.6039428710938</t>
   </si>
   <si>
-    <t xml:space="preserve">101.43155670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.876396179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.493629455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.598815917969</t>
+    <t xml:space="preserve">101.431541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.876388549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.493637084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.598823547363</t>
   </si>
   <si>
     <t xml:space="preserve">107.364334106445</t>
   </si>
   <si>
-    <t xml:space="preserve">109.660903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.235046386719</t>
+    <t xml:space="preserve">109.66089630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.235038757324</t>
   </si>
   <si>
     <t xml:space="preserve">105.641914367676</t>
   </si>
   <si>
-    <t xml:space="preserve">106.216049194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.9384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.555725097656</t>
+    <t xml:space="preserve">106.21605682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.938484191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.555717468262</t>
   </si>
   <si>
     <t xml:space="preserve">109.469520568848</t>
   </si>
   <si>
-    <t xml:space="preserve">107.747093200684</t>
+    <t xml:space="preserve">107.747100830078</t>
   </si>
   <si>
     <t xml:space="preserve">108.704002380371</t>
   </si>
   <si>
-    <t xml:space="preserve">102.197074890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5177459716797</t>
+    <t xml:space="preserve">102.197082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5177383422852</t>
   </si>
   <si>
     <t xml:space="preserve">99.7091217041016</t>
   </si>
   <si>
-    <t xml:space="preserve">103.345359802246</t>
+    <t xml:space="preserve">103.345352172852</t>
   </si>
   <si>
     <t xml:space="preserve">103.536735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">106.024681091309</t>
+    <t xml:space="preserve">106.024673461914</t>
   </si>
   <si>
     <t xml:space="preserve">106.981590270996</t>
@@ -2525,55 +2525,55 @@
     <t xml:space="preserve">105.833297729492</t>
   </si>
   <si>
-    <t xml:space="preserve">101.048789978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.388458251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.153984069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.962585449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.450538635254</t>
+    <t xml:space="preserve">101.048782348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.388450622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.15397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.962593078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.450531005859</t>
   </si>
   <si>
     <t xml:space="preserve">102.00569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">103.919494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.407424926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.086769104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.809181213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.679885864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.043655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.172950744629</t>
+    <t xml:space="preserve">103.919486999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.407440185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.086761474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.809188842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.679893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.043663024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.172958374023</t>
   </si>
   <si>
     <t xml:space="preserve">111.000564575195</t>
   </si>
   <si>
-    <t xml:space="preserve">112.914360046387</t>
+    <t xml:space="preserve">112.914367675781</t>
   </si>
   <si>
     <t xml:space="preserve">109.852272033691</t>
   </si>
   <si>
-    <t xml:space="preserve">110.42643737793</t>
+    <t xml:space="preserve">110.426414489746</t>
   </si>
   <si>
     <t xml:space="preserve">111.383323669434</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">113.29712677002</t>
   </si>
   <si>
-    <t xml:space="preserve">112.722991943359</t>
+    <t xml:space="preserve">112.722984313965</t>
   </si>
   <si>
     <t xml:space="preserve">115.019546508789</t>
@@ -2603,37 +2603,37 @@
     <t xml:space="preserve">116.741973876953</t>
   </si>
   <si>
-    <t xml:space="preserve">116.167839050293</t>
+    <t xml:space="preserve">116.167831420898</t>
   </si>
   <si>
     <t xml:space="preserve">115.78507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">116.550590515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.804054260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.186813354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.100616455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.866142272949</t>
+    <t xml:space="preserve">116.550598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.804061889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.186828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.100624084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.866134643555</t>
   </si>
   <si>
     <t xml:space="preserve">123.631660461426</t>
   </si>
   <si>
-    <t xml:space="preserve">131.478240966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.267875671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.459266662598</t>
+    <t xml:space="preserve">131.478256225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.267890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.459274291992</t>
   </si>
   <si>
     <t xml:space="preserve">128.990325927734</t>
@@ -2645,115 +2645,115 @@
     <t xml:space="preserve">134.157577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">133.774826049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.626556396484</t>
+    <t xml:space="preserve">133.774810791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.626541137695</t>
   </si>
   <si>
     <t xml:space="preserve">132.435150146484</t>
   </si>
   <si>
-    <t xml:space="preserve">134.923095703125</t>
+    <t xml:space="preserve">134.923080444336</t>
   </si>
   <si>
     <t xml:space="preserve">136.645523071289</t>
   </si>
   <si>
-    <t xml:space="preserve">137.411041259766</t>
+    <t xml:space="preserve">137.411056518555</t>
   </si>
   <si>
     <t xml:space="preserve">135.305847167969</t>
   </si>
   <si>
-    <t xml:space="preserve">131.860992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.731719970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.262756347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.793807983398</t>
+    <t xml:space="preserve">131.86100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.731735229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.262741088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.793792724609</t>
   </si>
   <si>
     <t xml:space="preserve">138.176559448242</t>
   </si>
   <si>
-    <t xml:space="preserve">137.028274536133</t>
+    <t xml:space="preserve">137.028259277344</t>
   </si>
   <si>
     <t xml:space="preserve">138.559326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">139.899002075195</t>
+    <t xml:space="preserve">139.898986816406</t>
   </si>
   <si>
     <t xml:space="preserve">136.454147338867</t>
   </si>
   <si>
-    <t xml:space="preserve">138.750686645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.324859619141</t>
+    <t xml:space="preserve">138.750701904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.324844360352</t>
   </si>
   <si>
     <t xml:space="preserve">137.98518371582</t>
   </si>
   <si>
-    <t xml:space="preserve">135.49723815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.492111206055</t>
+    <t xml:space="preserve">135.497253417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.492126464844</t>
   </si>
   <si>
     <t xml:space="preserve">144.874862670898</t>
   </si>
   <si>
-    <t xml:space="preserve">144.109375</t>
+    <t xml:space="preserve">144.109344482422</t>
   </si>
   <si>
     <t xml:space="preserve">142.195556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">143.726593017578</t>
+    <t xml:space="preserve">143.726577758789</t>
   </si>
   <si>
     <t xml:space="preserve">143.91796875</t>
   </si>
   <si>
-    <t xml:space="preserve">144.683486938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.25764465332</t>
+    <t xml:space="preserve">144.683502197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.257629394531</t>
   </si>
   <si>
     <t xml:space="preserve">147.936950683594</t>
   </si>
   <si>
-    <t xml:space="preserve">145.640396118164</t>
+    <t xml:space="preserve">145.640411376953</t>
   </si>
   <si>
     <t xml:space="preserve">146.788681030273</t>
   </si>
   <si>
-    <t xml:space="preserve">149.276626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.999053955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.424896240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.48698425293</t>
+    <t xml:space="preserve">149.276611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.999038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.424911499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.486968994141</t>
   </si>
   <si>
     <t xml:space="preserve">152.33869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">155.400787353516</t>
+    <t xml:space="preserve">155.400772094727</t>
   </si>
   <si>
     <t xml:space="preserve">151.1904296875</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">157.888732910156</t>
   </si>
   <si>
-    <t xml:space="preserve">159.037017822266</t>
+    <t xml:space="preserve">159.037033081055</t>
   </si>
   <si>
     <t xml:space="preserve">158.654266357422</t>
@@ -2771,28 +2771,28 @@
     <t xml:space="preserve">159.61116027832</t>
   </si>
   <si>
-    <t xml:space="preserve">161.333587646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.524948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.438766479492</t>
+    <t xml:space="preserve">161.333572387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.524978637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.438751220703</t>
   </si>
   <si>
     <t xml:space="preserve">163.821517944336</t>
   </si>
   <si>
-    <t xml:space="preserve">168.606018066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.773284912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.32844543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.161193847656</t>
+    <t xml:space="preserve">168.606033325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.773300170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.328460693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.161178588867</t>
   </si>
   <si>
     <t xml:space="preserve">168.03190612793</t>
@@ -2801,19 +2801,19 @@
     <t xml:space="preserve">165.352569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">160.75944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.099090576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.668121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.074981689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.930526733398</t>
+    <t xml:space="preserve">160.759429931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.099075317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.668106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.074996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.93049621582</t>
   </si>
   <si>
     <t xml:space="preserve">161.353576660156</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">152.12239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">145.583602905273</t>
+    <t xml:space="preserve">145.583618164062</t>
   </si>
   <si>
     <t xml:space="preserve">147.314468383789</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">150.19921875</t>
   </si>
   <si>
-    <t xml:space="preserve">148.083740234375</t>
+    <t xml:space="preserve">148.083709716797</t>
   </si>
   <si>
     <t xml:space="preserve">151.737747192383</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">149.622268676758</t>
   </si>
   <si>
-    <t xml:space="preserve">155.199447631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.545654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.968704223633</t>
+    <t xml:space="preserve">155.199432373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.545669555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.968719482422</t>
   </si>
   <si>
     <t xml:space="preserve">154.43017578125</t>
@@ -2864,10 +2864,10 @@
     <t xml:space="preserve">160.776611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">166.353805541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.200119018555</t>
+    <t xml:space="preserve">166.353790283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.200134277344</t>
   </si>
   <si>
     <t xml:space="preserve">168.469284057617</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">165.584533691406</t>
   </si>
   <si>
-    <t xml:space="preserve">161.161254882812</t>
+    <t xml:space="preserve">161.161270141602</t>
   </si>
   <si>
     <t xml:space="preserve">163.084426879883</t>
@@ -2903,25 +2903,25 @@
     <t xml:space="preserve">177.508163452148</t>
   </si>
   <si>
-    <t xml:space="preserve">175.585006713867</t>
+    <t xml:space="preserve">175.584976196289</t>
   </si>
   <si>
     <t xml:space="preserve">180.392913818359</t>
   </si>
   <si>
-    <t xml:space="preserve">180.777542114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.4697265625</t>
+    <t xml:space="preserve">180.777526855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.469757080078</t>
   </si>
   <si>
     <t xml:space="preserve">179.815963745117</t>
   </si>
   <si>
-    <t xml:space="preserve">181.739135742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.008514404297</t>
+    <t xml:space="preserve">181.739120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.008499145508</t>
   </si>
   <si>
     <t xml:space="preserve">183.085327148438</t>
@@ -2930,25 +2930,25 @@
     <t xml:space="preserve">182.508392333984</t>
   </si>
   <si>
-    <t xml:space="preserve">168.276977539062</t>
+    <t xml:space="preserve">168.276962280273</t>
   </si>
   <si>
     <t xml:space="preserve">169.046234130859</t>
   </si>
   <si>
-    <t xml:space="preserve">170.584762573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.507690429688</t>
+    <t xml:space="preserve">170.584747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.507705688477</t>
   </si>
   <si>
     <t xml:space="preserve">174.046463012695</t>
   </si>
   <si>
-    <t xml:space="preserve">170.96940612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.623168945312</t>
+    <t xml:space="preserve">170.969390869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.623184204102</t>
   </si>
   <si>
     <t xml:space="preserve">169.238540649414</t>
@@ -2957,28 +2957,28 @@
     <t xml:space="preserve">175.008041381836</t>
   </si>
   <si>
-    <t xml:space="preserve">172.700241088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.123291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.93098449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.315368652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.853668212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.738433837891</t>
+    <t xml:space="preserve">172.700256347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.123306274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.930969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.315383911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.85368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.738403320312</t>
   </si>
   <si>
     <t xml:space="preserve">164.238327026367</t>
   </si>
   <si>
-    <t xml:space="preserve">166.546112060547</t>
+    <t xml:space="preserve">166.546096801758</t>
   </si>
   <si>
     <t xml:space="preserve">167.700012207031</t>
@@ -2987,46 +2987,46 @@
     <t xml:space="preserve">165.392211914062</t>
   </si>
   <si>
-    <t xml:space="preserve">151.160781860352</t>
+    <t xml:space="preserve">151.160797119141</t>
   </si>
   <si>
     <t xml:space="preserve">158.853454589844</t>
   </si>
   <si>
-    <t xml:space="preserve">158.468826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.31494140625</t>
+    <t xml:space="preserve">158.468841552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.314926147461</t>
   </si>
   <si>
     <t xml:space="preserve">159.815048217773</t>
   </si>
   <si>
-    <t xml:space="preserve">156.930282592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.161010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.314697265625</t>
+    <t xml:space="preserve">156.930267333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.161026000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.314682006836</t>
   </si>
   <si>
     <t xml:space="preserve">145.96826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">146.929824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.353088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.46858215332</t>
+    <t xml:space="preserve">146.929840087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.353103637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.468597412109</t>
   </si>
   <si>
     <t xml:space="preserve">153.276260375977</t>
   </si>
   <si>
-    <t xml:space="preserve">157.122604370117</t>
+    <t xml:space="preserve">157.122589111328</t>
   </si>
   <si>
     <t xml:space="preserve">151.930053710938</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">146.545196533203</t>
   </si>
   <si>
-    <t xml:space="preserve">140.968032836914</t>
+    <t xml:space="preserve">140.968017578125</t>
   </si>
   <si>
     <t xml:space="preserve">136.92936706543</t>
@@ -3047,10 +3047,10 @@
     <t xml:space="preserve">132.69841003418</t>
   </si>
   <si>
-    <t xml:space="preserve">132.506088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.198272705078</t>
+    <t xml:space="preserve">132.506103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.198287963867</t>
   </si>
   <si>
     <t xml:space="preserve">134.813888549805</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">129.621353149414</t>
   </si>
   <si>
-    <t xml:space="preserve">132.890716552734</t>
+    <t xml:space="preserve">132.890731811523</t>
   </si>
   <si>
     <t xml:space="preserve">137.506332397461</t>
@@ -3077,46 +3077,46 @@
     <t xml:space="preserve">136.160110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">138.467910766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.583160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.813438415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.659294128418</t>
+    <t xml:space="preserve">138.467895507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.583145141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.813430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.659301757812</t>
   </si>
   <si>
     <t xml:space="preserve">125.582695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">125.198059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.313995361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.8525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.891189575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.391067504883</t>
+    <t xml:space="preserve">125.198066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.314025878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.852523803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.891174316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.391052246094</t>
   </si>
   <si>
     <t xml:space="preserve">145.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">145.006652832031</t>
+    <t xml:space="preserve">145.00666809082</t>
   </si>
   <si>
     <t xml:space="preserve">145.775939941406</t>
   </si>
   <si>
-    <t xml:space="preserve">144.814361572266</t>
+    <t xml:space="preserve">144.814346313477</t>
   </si>
   <si>
     <t xml:space="preserve">148.27604675293</t>
@@ -3125,13 +3125,13 @@
     <t xml:space="preserve">143.275817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">142.602722167969</t>
+    <t xml:space="preserve">142.60270690918</t>
   </si>
   <si>
     <t xml:space="preserve">142.698867797852</t>
   </si>
   <si>
-    <t xml:space="preserve">143.083511352539</t>
+    <t xml:space="preserve">143.08349609375</t>
   </si>
   <si>
     <t xml:space="preserve">139.525650024414</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">139.910278320312</t>
   </si>
   <si>
-    <t xml:space="preserve">139.429458618164</t>
+    <t xml:space="preserve">139.429473876953</t>
   </si>
   <si>
     <t xml:space="preserve">139.237167358398</t>
@@ -3167,22 +3167,22 @@
     <t xml:space="preserve">130.87141418457</t>
   </si>
   <si>
-    <t xml:space="preserve">129.525177001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.909820556641</t>
+    <t xml:space="preserve">129.525192260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.90983581543</t>
   </si>
   <si>
     <t xml:space="preserve">133.371520996094</t>
   </si>
   <si>
-    <t xml:space="preserve">128.275115966797</t>
+    <t xml:space="preserve">128.275146484375</t>
   </si>
   <si>
     <t xml:space="preserve">130.294448852539</t>
   </si>
   <si>
-    <t xml:space="preserve">124.236473083496</t>
+    <t xml:space="preserve">124.236480712891</t>
   </si>
   <si>
     <t xml:space="preserve">122.890258789062</t>
@@ -3191,13 +3191,13 @@
     <t xml:space="preserve">118.563148498535</t>
   </si>
   <si>
-    <t xml:space="preserve">109.81273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.562911987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.389923095703</t>
+    <t xml:space="preserve">109.812744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.56290435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.389915466309</t>
   </si>
   <si>
     <t xml:space="preserve">115.774551391602</t>
@@ -3215,25 +3215,25 @@
     <t xml:space="preserve">120.293983459473</t>
   </si>
   <si>
-    <t xml:space="preserve">120.101684570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.23624420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.486305236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.736145019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.83228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.043937683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.736358642578</t>
+    <t xml:space="preserve">120.101676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.236251831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.486320495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.736137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.832298278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.043930053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.736366271973</t>
   </si>
   <si>
     <t xml:space="preserve">124.621116638184</t>
@@ -3245,34 +3245,34 @@
     <t xml:space="preserve">121.544044494629</t>
   </si>
   <si>
-    <t xml:space="preserve">124.044166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.332633972168</t>
+    <t xml:space="preserve">124.044158935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.332641601562</t>
   </si>
   <si>
     <t xml:space="preserve">127.986656188965</t>
   </si>
   <si>
-    <t xml:space="preserve">128.659759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.698173522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.178749084473</t>
+    <t xml:space="preserve">128.659774780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.698188781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.178741455078</t>
   </si>
   <si>
     <t xml:space="preserve">114.524490356445</t>
   </si>
   <si>
-    <t xml:space="preserve">112.889808654785</t>
+    <t xml:space="preserve">112.889801025391</t>
   </si>
   <si>
     <t xml:space="preserve">114.236022949219</t>
   </si>
   <si>
-    <t xml:space="preserve">111.062797546387</t>
+    <t xml:space="preserve">111.062805175781</t>
   </si>
   <si>
     <t xml:space="preserve">112.216690063477</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">113.947547912598</t>
   </si>
   <si>
-    <t xml:space="preserve">116.447662353516</t>
+    <t xml:space="preserve">116.447654724121</t>
   </si>
   <si>
     <t xml:space="preserve">115.197601318359</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">123.082580566406</t>
   </si>
   <si>
-    <t xml:space="preserve">125.39037322998</t>
+    <t xml:space="preserve">125.390365600586</t>
   </si>
   <si>
     <t xml:space="preserve">122.986427307129</t>
@@ -3323,61 +3323,61 @@
     <t xml:space="preserve">118.27466583252</t>
   </si>
   <si>
-    <t xml:space="preserve">119.71703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.774772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.659530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.948226928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.736831665039</t>
+    <t xml:space="preserve">119.717041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.774780273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.659538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.9482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.73681640625</t>
   </si>
   <si>
     <t xml:space="preserve">130.679077148438</t>
   </si>
   <si>
-    <t xml:space="preserve">126.832733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.794334411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.467437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.602233886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.044403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.159881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.967330932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.351943969727</t>
+    <t xml:space="preserve">126.832740783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.794319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.467468261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.602249145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.044387817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.159866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.967323303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.351959228516</t>
   </si>
   <si>
     <t xml:space="preserve">123.563369750977</t>
   </si>
   <si>
-    <t xml:space="preserve">127.313537597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.371276855469</t>
+    <t xml:space="preserve">127.313545227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.371292114258</t>
   </si>
   <si>
     <t xml:space="preserve">126.736595153809</t>
   </si>
   <si>
-    <t xml:space="preserve">121.447883605957</t>
+    <t xml:space="preserve">121.447891235352</t>
   </si>
   <si>
     <t xml:space="preserve">117.6015625</t>
@@ -3386,10 +3386,10 @@
     <t xml:space="preserve">118.947769165039</t>
   </si>
   <si>
-    <t xml:space="preserve">120.19783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.063255310059</t>
+    <t xml:space="preserve">120.197830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.063262939453</t>
   </si>
   <si>
     <t xml:space="preserve">117.505401611328</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">116.255348205566</t>
   </si>
   <si>
-    <t xml:space="preserve">112.312850952148</t>
+    <t xml:space="preserve">112.312858581543</t>
   </si>
   <si>
     <t xml:space="preserve">115.582237243652</t>
@@ -3410,13 +3410,13 @@
     <t xml:space="preserve">115.678398132324</t>
   </si>
   <si>
-    <t xml:space="preserve">118.178504943848</t>
+    <t xml:space="preserve">118.178512573242</t>
   </si>
   <si>
     <t xml:space="preserve">114.909133911133</t>
   </si>
   <si>
-    <t xml:space="preserve">106.596160888672</t>
+    <t xml:space="preserve">106.596168518066</t>
   </si>
   <si>
     <t xml:space="preserve">105.336387634277</t>
@@ -3449,10 +3449,10 @@
     <t xml:space="preserve">109.212615966797</t>
   </si>
   <si>
-    <t xml:space="preserve">113.185745239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.441444396973</t>
+    <t xml:space="preserve">113.185752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.441452026367</t>
   </si>
   <si>
     <t xml:space="preserve">111.829071044922</t>
@@ -3461,19 +3461,19 @@
     <t xml:space="preserve">107.274505615234</t>
   </si>
   <si>
-    <t xml:space="preserve">104.851860046387</t>
+    <t xml:space="preserve">104.851867675781</t>
   </si>
   <si>
     <t xml:space="preserve">104.658058166504</t>
   </si>
   <si>
-    <t xml:space="preserve">101.847785949707</t>
+    <t xml:space="preserve">101.847793579102</t>
   </si>
   <si>
     <t xml:space="preserve">102.429222106934</t>
   </si>
   <si>
-    <t xml:space="preserve">103.49520111084</t>
+    <t xml:space="preserve">103.495193481445</t>
   </si>
   <si>
     <t xml:space="preserve">104.076622009277</t>
@@ -3494,25 +3494,25 @@
     <t xml:space="preserve">114.348617553711</t>
   </si>
   <si>
-    <t xml:space="preserve">109.794059753418</t>
+    <t xml:space="preserve">109.794052124023</t>
   </si>
   <si>
     <t xml:space="preserve">107.468315124512</t>
   </si>
   <si>
-    <t xml:space="preserve">106.305442810059</t>
+    <t xml:space="preserve">106.305450439453</t>
   </si>
   <si>
     <t xml:space="preserve">102.332321166992</t>
   </si>
   <si>
-    <t xml:space="preserve">100.87873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.979713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.340469360352</t>
+    <t xml:space="preserve">100.878730773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.979721069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.340476989746</t>
   </si>
   <si>
     <t xml:space="preserve">117.643409729004</t>
@@ -3524,16 +3524,16 @@
     <t xml:space="preserve">117.837219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">116.771263122559</t>
+    <t xml:space="preserve">116.771255493164</t>
   </si>
   <si>
     <t xml:space="preserve">114.445518493652</t>
   </si>
   <si>
-    <t xml:space="preserve">114.73624420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.026954650879</t>
+    <t xml:space="preserve">114.736236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.026947021484</t>
   </si>
   <si>
     <t xml:space="preserve">115.317672729492</t>
@@ -3542,10 +3542,10 @@
     <t xml:space="preserve">115.51148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">115.220764160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.965057373047</t>
+    <t xml:space="preserve">115.220771789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.965065002441</t>
   </si>
   <si>
     <t xml:space="preserve">113.476463317871</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">118.612464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">112.991943359375</t>
+    <t xml:space="preserve">112.99193572998</t>
   </si>
   <si>
     <t xml:space="preserve">111.053825378418</t>
@@ -3581,10 +3581,10 @@
     <t xml:space="preserve">108.243560791016</t>
   </si>
   <si>
-    <t xml:space="preserve">107.080696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.375495910645</t>
+    <t xml:space="preserve">107.080703735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.37548828125</t>
   </si>
   <si>
     <t xml:space="preserve">108.534278869629</t>
@@ -3593,16 +3593,16 @@
     <t xml:space="preserve">110.181671142578</t>
   </si>
   <si>
-    <t xml:space="preserve">109.890960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.24764251709</t>
+    <t xml:space="preserve">109.890953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.247634887695</t>
   </si>
   <si>
     <t xml:space="preserve">113.282661437988</t>
   </si>
   <si>
-    <t xml:space="preserve">112.410507202148</t>
+    <t xml:space="preserve">112.410499572754</t>
   </si>
   <si>
     <t xml:space="preserve">114.639335632324</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">117.255783081055</t>
   </si>
   <si>
-    <t xml:space="preserve">117.352691650391</t>
+    <t xml:space="preserve">117.352684020996</t>
   </si>
   <si>
     <t xml:space="preserve">118.031028747559</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">120.162956237793</t>
   </si>
   <si>
-    <t xml:space="preserve">121.907257080078</t>
+    <t xml:space="preserve">121.907249450684</t>
   </si>
   <si>
     <t xml:space="preserve">120.550575256348</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">122.779403686523</t>
   </si>
   <si>
-    <t xml:space="preserve">123.263931274414</t>
+    <t xml:space="preserve">123.263938903809</t>
   </si>
   <si>
     <t xml:space="preserve">121.810340881348</t>
@@ -3653,10 +3653,10 @@
     <t xml:space="preserve">123.748458862305</t>
   </si>
   <si>
-    <t xml:space="preserve">131.985427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.888534545898</t>
+    <t xml:space="preserve">131.985443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.888549804688</t>
   </si>
   <si>
     <t xml:space="preserve">132.179244995117</t>
@@ -3689,10 +3689,10 @@
     <t xml:space="preserve">124.136085510254</t>
   </si>
   <si>
-    <t xml:space="preserve">123.845367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.422729492188</t>
+    <t xml:space="preserve">123.845359802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.422737121582</t>
   </si>
   <si>
     <t xml:space="preserve">121.325820922852</t>
@@ -3704,19 +3704,19 @@
     <t xml:space="preserve">120.35676574707</t>
   </si>
   <si>
-    <t xml:space="preserve">118.321739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.8681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.802200317383</t>
+    <t xml:space="preserve">118.321746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.868156433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.802207946777</t>
   </si>
   <si>
     <t xml:space="preserve">113.864097595215</t>
   </si>
   <si>
-    <t xml:space="preserve">113.960990905762</t>
+    <t xml:space="preserve">113.960998535156</t>
   </si>
   <si>
     <t xml:space="preserve">113.088836669922</t>
@@ -3725,13 +3725,13 @@
     <t xml:space="preserve">110.472389221191</t>
   </si>
   <si>
-    <t xml:space="preserve">108.824996948242</t>
+    <t xml:space="preserve">108.825004577637</t>
   </si>
   <si>
     <t xml:space="preserve">115.414573669434</t>
   </si>
   <si>
-    <t xml:space="preserve">109.987869262695</t>
+    <t xml:space="preserve">109.987861633301</t>
   </si>
   <si>
     <t xml:space="preserve">111.538352966309</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">113.670280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">118.127944946289</t>
+    <t xml:space="preserve">118.127937316895</t>
   </si>
   <si>
     <t xml:space="preserve">114.154808044434</t>
@@ -3758,13 +3758,13 @@
     <t xml:space="preserve">119.678428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">116.383628845215</t>
+    <t xml:space="preserve">116.383636474609</t>
   </si>
   <si>
     <t xml:space="preserve">115.123863220215</t>
   </si>
   <si>
-    <t xml:space="preserve">112.119789123535</t>
+    <t xml:space="preserve">112.119781494141</t>
   </si>
   <si>
     <t xml:space="preserve">110.569290161133</t>
@@ -3788,13 +3788,13 @@
     <t xml:space="preserve">104.754959106445</t>
   </si>
   <si>
-    <t xml:space="preserve">105.724006652832</t>
+    <t xml:space="preserve">105.724014282227</t>
   </si>
   <si>
     <t xml:space="preserve">103.592094421387</t>
   </si>
   <si>
-    <t xml:space="preserve">106.88688659668</t>
+    <t xml:space="preserve">106.886894226074</t>
   </si>
   <si>
     <t xml:space="preserve">103.204475402832</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">100.588027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">100.297309875488</t>
+    <t xml:space="preserve">100.297302246094</t>
   </si>
   <si>
     <t xml:space="preserve">102.719940185547</t>
@@ -3812,13 +3812,13 @@
     <t xml:space="preserve">103.107566833496</t>
   </si>
   <si>
-    <t xml:space="preserve">104.561149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.371421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.855949401855</t>
+    <t xml:space="preserve">104.561157226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.37141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.855941772461</t>
   </si>
   <si>
     <t xml:space="preserve">109.018814086914</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">116.480545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">115.705291748047</t>
+    <t xml:space="preserve">115.705299377441</t>
   </si>
   <si>
     <t xml:space="preserve">113.37956237793</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">102.235420227051</t>
   </si>
   <si>
-    <t xml:space="preserve">102.623046875</t>
+    <t xml:space="preserve">102.623039245605</t>
   </si>
   <si>
     <t xml:space="preserve">104.173530578613</t>
@@ -3872,10 +3872,10 @@
     <t xml:space="preserve">100.975639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">100.200393676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.491111755371</t>
+    <t xml:space="preserve">100.200401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.491104125977</t>
   </si>
   <si>
     <t xml:space="preserve">100.006591796875</t>
@@ -3890,10 +3890,10 @@
     <t xml:space="preserve">101.653984069824</t>
   </si>
   <si>
-    <t xml:space="preserve">100.39421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3282470703125</t>
+    <t xml:space="preserve">100.394203186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.328254699707</t>
   </si>
   <si>
     <t xml:space="preserve">99.6189727783203</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">102.138511657715</t>
   </si>
   <si>
-    <t xml:space="preserve">101.75089263916</t>
+    <t xml:space="preserve">101.750885009766</t>
   </si>
   <si>
     <t xml:space="preserve">99.8127746582031</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">97.1963272094727</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6808547973633</t>
+    <t xml:space="preserve">97.6808624267578</t>
   </si>
   <si>
     <t xml:space="preserve">99.0078277587891</t>
@@ -5295,6 +5295,9 @@
   </si>
   <si>
     <t xml:space="preserve">89.8000030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.0999984741211</t>
   </si>
 </sst>
 </file>
@@ -71697,6 +71700,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2542">
+      <c r="A2542" s="1" t="n">
+        <v>46024.6911111111</v>
+      </c>
+      <c r="B2542" t="n">
+        <v>36799</v>
+      </c>
+      <c r="C2542" t="n">
+        <v>91.5999984741211</v>
+      </c>
+      <c r="D2542" t="n">
+        <v>89.8499984741211</v>
+      </c>
+      <c r="E2542" t="n">
+        <v>89.8499984741211</v>
+      </c>
+      <c r="F2542" t="n">
+        <v>90.0999984741211</v>
+      </c>
+      <c r="G2542" t="s">
+        <v>1761</v>
+      </c>
+      <c r="H2542" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5495910644531</t>
+    <t xml:space="preserve">13.5495901107788</t>
   </si>
   <si>
     <t xml:space="preserve">SES.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5321063995361</t>
+    <t xml:space="preserve">13.5321073532104</t>
   </si>
   <si>
     <t xml:space="preserve">13.2523736953735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9464139938354</t>
+    <t xml:space="preserve">12.9464159011841</t>
   </si>
   <si>
     <t xml:space="preserve">13.1125068664551</t>
@@ -59,16 +59,16 @@
     <t xml:space="preserve">12.858998298645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0513134002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9901237487793</t>
+    <t xml:space="preserve">13.0513143539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9901247024536</t>
   </si>
   <si>
     <t xml:space="preserve">12.9376735687256</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1037645339966</t>
+    <t xml:space="preserve">13.1037664413452</t>
   </si>
   <si>
     <t xml:space="preserve">13.025089263916</t>
@@ -77,28 +77,28 @@
     <t xml:space="preserve">12.8502559661865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.238338470459</t>
+    <t xml:space="preserve">12.2383394241333</t>
   </si>
   <si>
     <t xml:space="preserve">12.5880060195923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7890663146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7191333770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6841659545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6054906845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3257579803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0460224151611</t>
+    <t xml:space="preserve">12.7890653610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7191314697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6841650009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.605489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3257570266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0460233688354</t>
   </si>
   <si>
     <t xml:space="preserve">12.1771488189697</t>
@@ -116,22 +116,22 @@
     <t xml:space="preserve">11.3641729354858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4515886306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0984735488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1072149276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8886737823486</t>
+    <t xml:space="preserve">11.4515895843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0984745025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1072158813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8886728286743</t>
   </si>
   <si>
     <t xml:space="preserve">11.9760885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9323806762695</t>
+    <t xml:space="preserve">11.9323816299438</t>
   </si>
   <si>
     <t xml:space="preserve">12.0110569000244</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">11.8274803161621</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0635061264038</t>
+    <t xml:space="preserve">12.0635070800781</t>
   </si>
   <si>
     <t xml:space="preserve">12.5005903244019</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">12.7978057861328</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1649570465088</t>
+    <t xml:space="preserve">13.1649560928345</t>
   </si>
   <si>
     <t xml:space="preserve">13.1562147140503</t>
@@ -176,85 +176,85 @@
     <t xml:space="preserve">13.1911821365356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7540988922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8939657211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9027061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0600566864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1999235153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9813833236694</t>
+    <t xml:space="preserve">12.7540979385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8939647674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9027070999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0600576400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1999244689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9813823699951</t>
   </si>
   <si>
     <t xml:space="preserve">13.4534330368042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7069396972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4709148406982</t>
+    <t xml:space="preserve">13.7069425582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4709138870239</t>
   </si>
   <si>
     <t xml:space="preserve">13.4621734619141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.208664894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3223066329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0950241088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9988641738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.640456199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4481401443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3782062530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0285396575928</t>
+    <t xml:space="preserve">13.2086639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3223056793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0950231552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9988651275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6404571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4481391906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3782043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0285406112671</t>
   </si>
   <si>
     <t xml:space="preserve">12.1509227752686</t>
   </si>
   <si>
-    <t xml:space="preserve">12.439395904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5617818832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5268144607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6317148208618</t>
+    <t xml:space="preserve">12.439398765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5617809295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5268154144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6317157745361</t>
   </si>
   <si>
     <t xml:space="preserve">12.3694648742676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7715826034546</t>
+    <t xml:space="preserve">12.7715816497803</t>
   </si>
   <si>
     <t xml:space="preserve">12.4306564331055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2820482254028</t>
+    <t xml:space="preserve">12.2820491790771</t>
   </si>
   <si>
     <t xml:space="preserve">12.1946306228638</t>
@@ -263,22 +263,22 @@
     <t xml:space="preserve">12.2470817565918</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4131746292114</t>
+    <t xml:space="preserve">12.4131727218628</t>
   </si>
   <si>
     <t xml:space="preserve">12.509331703186</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3869495391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8187408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8449649810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.255823135376</t>
+    <t xml:space="preserve">12.3869476318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8187398910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8449640274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2558240890503</t>
   </si>
   <si>
     <t xml:space="preserve">12.5792655944824</t>
@@ -290,43 +290,43 @@
     <t xml:space="preserve">12.1858882904053</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7803239822388</t>
+    <t xml:space="preserve">12.7803230285645</t>
   </si>
   <si>
     <t xml:space="preserve">12.7278738021851</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8764820098877</t>
+    <t xml:space="preserve">12.8764810562134</t>
   </si>
   <si>
     <t xml:space="preserve">12.8065481185913</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7628393173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8677406311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327741622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5355567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1824398040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0338325500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3048238754272</t>
+    <t xml:space="preserve">12.7628402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8677396774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327722549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5355577468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1824417114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0338315963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3048248291016</t>
   </si>
   <si>
     <t xml:space="preserve">13.2611141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3747577667236</t>
+    <t xml:space="preserve">13.3747568130493</t>
   </si>
   <si>
     <t xml:space="preserve">13.6020412445068</t>
@@ -338,22 +338,22 @@
     <t xml:space="preserve">13.7244253158569</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7514772415161</t>
+    <t xml:space="preserve">13.7514753341675</t>
   </si>
   <si>
     <t xml:space="preserve">13.5711288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8687009811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6252336502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6432666778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6613035202026</t>
+    <t xml:space="preserve">13.8687019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6252307891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6432676315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.661301612854</t>
   </si>
   <si>
     <t xml:space="preserve">13.5981817245483</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">13.5260419845581</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5530939102173</t>
+    <t xml:space="preserve">13.553092956543</t>
   </si>
   <si>
     <t xml:space="preserve">13.3456945419312</t>
@@ -377,16 +377,16 @@
     <t xml:space="preserve">13.6973714828491</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7785263061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6703195571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7965631484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9769105911255</t>
+    <t xml:space="preserve">13.7785272598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6703205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7965621948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9769096374512</t>
   </si>
   <si>
     <t xml:space="preserve">14.0400314331055</t>
@@ -395,16 +395,16 @@
     <t xml:space="preserve">14.012978553772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9047718048096</t>
+    <t xml:space="preserve">13.9047708511353</t>
   </si>
   <si>
     <t xml:space="preserve">14.1031541824341</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2474308013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1572570800781</t>
+    <t xml:space="preserve">14.2474327087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1572580337524</t>
   </si>
   <si>
     <t xml:space="preserve">14.3646564483643</t>
@@ -413,124 +413,124 @@
     <t xml:space="preserve">14.4187602996826</t>
   </si>
   <si>
-    <t xml:space="preserve">14.517951965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6081256866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6622304916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3917093276978</t>
+    <t xml:space="preserve">14.5179510116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6081275939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6622285842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3917074203491</t>
   </si>
   <si>
     <t xml:space="preserve">14.3105525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.30153465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5450038909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6441926956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7343683242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7163333892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6351766586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6261577606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6892833709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8245429992676</t>
+    <t xml:space="preserve">14.3015336990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5450019836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6441946029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7343673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7163343429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6351757049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6261587142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6892824172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8245420455933</t>
   </si>
   <si>
     <t xml:space="preserve">14.80650806427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.74338722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.581072807312</t>
+    <t xml:space="preserve">14.7433862686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5810737609863</t>
   </si>
   <si>
     <t xml:space="preserve">14.6982975006104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5089330673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6712484359741</t>
+    <t xml:space="preserve">14.5089359283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6712455749512</t>
   </si>
   <si>
     <t xml:space="preserve">14.6532115936279</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9237308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0499744415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2122888565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3746023178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5549507141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9246587753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7803821563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8705577850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344860076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7082462310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517116546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7452373504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8714809417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0879020690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1510238647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2231597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9796924591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9075527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3043155670166</t>
+    <t xml:space="preserve">14.9237327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.049976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.212290763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3746013641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5549478530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9246616363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7803812026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8705558776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344850540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7082452774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517126083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7452430725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8714828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0879001617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1510200500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2231616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9796905517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9075508117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3043174743652</t>
   </si>
   <si>
     <t xml:space="preserve">17.0337944030762</t>
@@ -539,25 +539,25 @@
     <t xml:space="preserve">17.2772636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4756469726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3223476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1690578460693</t>
+    <t xml:space="preserve">17.475643157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3223495483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1690559387207</t>
   </si>
   <si>
     <t xml:space="preserve">17.583854675293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5748348236084</t>
+    <t xml:space="preserve">17.574836730957</t>
   </si>
   <si>
     <t xml:space="preserve">17.5658187866211</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2411956787109</t>
+    <t xml:space="preserve">17.2411975860596</t>
   </si>
   <si>
     <t xml:space="preserve">17.1870918273926</t>
@@ -572,94 +572,94 @@
     <t xml:space="preserve">16.9526386260986</t>
   </si>
   <si>
-    <t xml:space="preserve">16.727201461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6911373138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8624706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0428142547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8173770904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9977264404297</t>
+    <t xml:space="preserve">16.7272033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6911354064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8624649047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0428104400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8173789978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9977283477783</t>
   </si>
   <si>
     <t xml:space="preserve">16.7722930908203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0067462921143</t>
+    <t xml:space="preserve">17.0067443847656</t>
   </si>
   <si>
     <t xml:space="preserve">17.1961078643799</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3584213256836</t>
+    <t xml:space="preserve">17.358419418335</t>
   </si>
   <si>
     <t xml:space="preserve">17.6199264526367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7642021179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0076675415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9896373748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9445457458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9535675048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.809289932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2601566314697</t>
+    <t xml:space="preserve">17.7642040252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0076713562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9896354675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9445495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9535655975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8092880249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2601547241211</t>
   </si>
   <si>
     <t xml:space="preserve">18.7561130523682</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8462829589844</t>
+    <t xml:space="preserve">18.8462867736816</t>
   </si>
   <si>
     <t xml:space="preserve">18.9364585876465</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6208477020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2971534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3602752685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3512573242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6668663024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6488304138184</t>
+    <t xml:space="preserve">18.6208534240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2971515655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3602733612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3512554168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6668643951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.648832321167</t>
   </si>
   <si>
     <t xml:space="preserve">19.5586566925049</t>
   </si>
   <si>
-    <t xml:space="preserve">19.252067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1709117889404</t>
+    <t xml:space="preserve">19.2520656585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1709098815918</t>
   </si>
   <si>
     <t xml:space="preserve">19.134838104248</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">19.197961807251</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9544906616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9094047546387</t>
+    <t xml:space="preserve">18.9544925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9094066619873</t>
   </si>
   <si>
     <t xml:space="preserve">19.0897560119629</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">18.5757656097412</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1970367431641</t>
+    <t xml:space="preserve">18.1970348358154</t>
   </si>
   <si>
     <t xml:space="preserve">18.5306777954102</t>
@@ -689,49 +689,49 @@
     <t xml:space="preserve">18.8372669219971</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4594688415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3873233795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0185451507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3612022399902</t>
+    <t xml:space="preserve">19.4594669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3873252868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0185432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3612003326416</t>
   </si>
   <si>
     <t xml:space="preserve">20.8301048278809</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2809734344482</t>
+    <t xml:space="preserve">21.2809715270996</t>
   </si>
   <si>
     <t xml:space="preserve">20.8751907348633</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9292945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1006259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0104541778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5685997009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7218971252441</t>
+    <t xml:space="preserve">20.9292964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1006240844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0104522705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.568603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7218952178955</t>
   </si>
   <si>
     <t xml:space="preserve">20.6046714782715</t>
   </si>
   <si>
-    <t xml:space="preserve">20.189868927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792362213135</t>
+    <t xml:space="preserve">20.1898708343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792381286621</t>
   </si>
   <si>
     <t xml:space="preserve">20.6497573852539</t>
@@ -740,52 +740,52 @@
     <t xml:space="preserve">21.6416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3711471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.380163192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0925350189209</t>
+    <t xml:space="preserve">21.3711452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3801612854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0925369262695</t>
   </si>
   <si>
     <t xml:space="preserve">22.6245594024658</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7147331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8049068450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5984344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0763549804688</t>
+    <t xml:space="preserve">22.7147350311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8049049377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5984325408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.076358795166</t>
   </si>
   <si>
     <t xml:space="preserve">24.0583209991455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7156600952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9320774078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.859935760498</t>
+    <t xml:space="preserve">23.7156581878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9320755004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8599414825439</t>
   </si>
   <si>
     <t xml:space="preserve">23.8058319091797</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5082626342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.994270324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4802837371826</t>
+    <t xml:space="preserve">23.5082607269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9942722320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.480281829834</t>
   </si>
   <si>
     <t xml:space="preserve">22.5434036254883</t>
@@ -794,25 +794,25 @@
     <t xml:space="preserve">22.7057151794434</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4532299041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4622459411621</t>
+    <t xml:space="preserve">22.4532260894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4622440338135</t>
   </si>
   <si>
     <t xml:space="preserve">22.0023612976074</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1827087402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7237491607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3630542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2097625732422</t>
+    <t xml:space="preserve">22.182710647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7237510681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3630561828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2097587585449</t>
   </si>
   <si>
     <t xml:space="preserve">21.4883728027344</t>
@@ -821,31 +821,31 @@
     <t xml:space="preserve">21.9212055206299</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8761234283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7047882080078</t>
+    <t xml:space="preserve">21.8761196136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7047901153564</t>
   </si>
   <si>
     <t xml:space="preserve">21.9392414093018</t>
   </si>
   <si>
-    <t xml:space="preserve">22.074499130249</t>
+    <t xml:space="preserve">22.0745029449463</t>
   </si>
   <si>
     <t xml:space="preserve">22.299934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8139228820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3179683685303</t>
+    <t xml:space="preserve">22.8139247894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3179702758789</t>
   </si>
   <si>
     <t xml:space="preserve">22.1917266845703</t>
   </si>
   <si>
-    <t xml:space="preserve">22.354040145874</t>
+    <t xml:space="preserve">22.3540420532227</t>
   </si>
   <si>
     <t xml:space="preserve">22.5253677368164</t>
@@ -854,49 +854,49 @@
     <t xml:space="preserve">22.6065235137939</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6335773468018</t>
+    <t xml:space="preserve">22.6335754394531</t>
   </si>
   <si>
     <t xml:space="preserve">22.2458305358887</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2277984619141</t>
+    <t xml:space="preserve">22.2277965545654</t>
   </si>
   <si>
     <t xml:space="preserve">22.128604888916</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0835189819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2007446289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.137622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1466388702393</t>
+    <t xml:space="preserve">22.0835208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2007427215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1376190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1466369628906</t>
   </si>
   <si>
     <t xml:space="preserve">21.5965785980225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3260593414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5605087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0294151306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6867523193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.23681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3720741271973</t>
+    <t xml:space="preserve">21.326057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5605125427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.029411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6867561340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2368125915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3720722198486</t>
   </si>
   <si>
     <t xml:space="preserve">22.3991260528564</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">22.6155414581299</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6606292724609</t>
+    <t xml:space="preserve">22.6606273651123</t>
   </si>
   <si>
     <t xml:space="preserve">23.0123062133789</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">23.5193881988525</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2704582214355</t>
+    <t xml:space="preserve">23.2704563140869</t>
   </si>
   <si>
     <t xml:space="preserve">24.1739845275879</t>
@@ -926,16 +926,16 @@
     <t xml:space="preserve">24.7732639312744</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2434673309326</t>
+    <t xml:space="preserve">25.243465423584</t>
   </si>
   <si>
     <t xml:space="preserve">25.8150844573975</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7966499328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6860084533691</t>
+    <t xml:space="preserve">25.7966480255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.686014175415</t>
   </si>
   <si>
     <t xml:space="preserve">25.6675720214844</t>
@@ -944,28 +944,28 @@
     <t xml:space="preserve">26.0086994171143</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8888473510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9810447692871</t>
+    <t xml:space="preserve">25.8888416290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9810428619385</t>
   </si>
   <si>
     <t xml:space="preserve">26.0916767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9072856903076</t>
+    <t xml:space="preserve">25.907283782959</t>
   </si>
   <si>
     <t xml:space="preserve">25.8058681488037</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9533843994141</t>
+    <t xml:space="preserve">25.9533805847168</t>
   </si>
   <si>
     <t xml:space="preserve">25.6767921447754</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6583499908447</t>
+    <t xml:space="preserve">25.6583518981934</t>
   </si>
   <si>
     <t xml:space="preserve">25.0775127410889</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">25.4001998901367</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2619037628174</t>
+    <t xml:space="preserve">25.261905670166</t>
   </si>
   <si>
     <t xml:space="preserve">25.3264427185059</t>
@@ -983,31 +983,31 @@
     <t xml:space="preserve">24.8009243011475</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4186382293701</t>
+    <t xml:space="preserve">25.4186401367188</t>
   </si>
   <si>
     <t xml:space="preserve">24.6441879272461</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8562393188477</t>
+    <t xml:space="preserve">24.8562412261963</t>
   </si>
   <si>
     <t xml:space="preserve">24.9576549530029</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8931159973145</t>
+    <t xml:space="preserve">24.8931198120117</t>
   </si>
   <si>
     <t xml:space="preserve">23.187479019165</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9754276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1229419708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2335796356201</t>
+    <t xml:space="preserve">22.9754295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1229400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2335777282715</t>
   </si>
   <si>
     <t xml:space="preserve">22.9938659667969</t>
@@ -1016,10 +1016,10 @@
     <t xml:space="preserve">22.7818126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6711769104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4960060119629</t>
+    <t xml:space="preserve">22.671178817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4960021972656</t>
   </si>
   <si>
     <t xml:space="preserve">22.7264957427979</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">22.5882015228271</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1137218475342</t>
+    <t xml:space="preserve">23.1137237548828</t>
   </si>
   <si>
     <t xml:space="preserve">22.910888671875</t>
@@ -1043,19 +1043,19 @@
     <t xml:space="preserve">23.3995323181152</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7775402069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6208057403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1413841247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9846496582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8740100860596</t>
+    <t xml:space="preserve">23.7775421142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6208038330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1413822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9846477508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8740081787109</t>
   </si>
   <si>
     <t xml:space="preserve">22.7357158660889</t>
@@ -1067,61 +1067,61 @@
     <t xml:space="preserve">23.3257751464844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7406597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9803733825684</t>
+    <t xml:space="preserve">23.7406578063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9803714752197</t>
   </si>
   <si>
     <t xml:space="preserve">23.9711532592773</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0633506774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2477416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3860378265381</t>
+    <t xml:space="preserve">24.0633487701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2477397918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3860397338867</t>
   </si>
   <si>
     <t xml:space="preserve">24.1555442810059</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6165313720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8611850738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6306915283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2158107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1697101593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080043792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4463005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5384998321533</t>
+    <t xml:space="preserve">24.6165294647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8611831665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6306934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2158069610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1697082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4462985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5384979248047</t>
   </si>
   <si>
     <t xml:space="preserve">25.1236133575439</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4321365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6484622955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0172481536865</t>
+    <t xml:space="preserve">24.4321384429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6484642028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0172500610352</t>
   </si>
   <si>
     <t xml:space="preserve">24.109447479248</t>
@@ -1142,22 +1142,22 @@
     <t xml:space="preserve">24.6626281738281</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9853172302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4923992156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7228889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5704307556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5845966339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9994792938232</t>
+    <t xml:space="preserve">24.985315322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.492395401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7228908538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5704288482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5845985412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9994831085205</t>
   </si>
   <si>
     <t xml:space="preserve">26.4143657684326</t>
@@ -1166,28 +1166,28 @@
     <t xml:space="preserve">27.5668258666992</t>
   </si>
   <si>
-    <t xml:space="preserve">27.751220703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0739059448242</t>
+    <t xml:space="preserve">27.7512168884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0739078521729</t>
   </si>
   <si>
     <t xml:space="preserve">27.5207252502441</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7370529174805</t>
+    <t xml:space="preserve">26.7370548248291</t>
   </si>
   <si>
     <t xml:space="preserve">26.5065612792969</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0314159393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5243320465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3682651519775</t>
+    <t xml:space="preserve">25.0314121246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5243339538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3682670593262</t>
   </si>
   <si>
     <t xml:space="preserve">26.5987586975098</t>
@@ -1205,16 +1205,16 @@
     <t xml:space="preserve">27.1980400085449</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2760715484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2902355194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3824367523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4746284484863</t>
+    <t xml:space="preserve">26.2760677337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2902336120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3824329376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4746227264404</t>
   </si>
   <si>
     <t xml:space="preserve">26.5526599884033</t>
@@ -1223,34 +1223,34 @@
     <t xml:space="preserve">26.8292503356934</t>
   </si>
   <si>
-    <t xml:space="preserve">27.105842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8753490447998</t>
+    <t xml:space="preserve">27.1058406829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8753509521484</t>
   </si>
   <si>
     <t xml:space="preserve">27.8434181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7653846740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5809898376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9356136322021</t>
+    <t xml:space="preserve">28.7653827667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5809879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9356079101562</t>
   </si>
   <si>
     <t xml:space="preserve">28.8114795684814</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1661014556885</t>
+    <t xml:space="preserve">28.1661033630371</t>
   </si>
   <si>
     <t xml:space="preserve">28.7192821502686</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1200084686279</t>
+    <t xml:space="preserve">28.1200065612793</t>
   </si>
   <si>
     <t xml:space="preserve">27.059741973877</t>
@@ -1259,37 +1259,37 @@
     <t xml:space="preserve">26.9675464630127</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1519374847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6909561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7831497192383</t>
+    <t xml:space="preserve">27.1519393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6909580230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7831535339355</t>
   </si>
   <si>
     <t xml:space="preserve">26.0455799102783</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6590213775635</t>
+    <t xml:space="preserve">27.6590232849121</t>
   </si>
   <si>
     <t xml:space="preserve">26.9214496612549</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1828784942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0886974334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4654312133789</t>
+    <t xml:space="preserve">26.1828804016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0886993408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4654293060303</t>
   </si>
   <si>
     <t xml:space="preserve">25.8061466217041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7119655609131</t>
+    <t xml:space="preserve">25.7119636535645</t>
   </si>
   <si>
     <t xml:space="preserve">25.1468677520752</t>
@@ -1307,19 +1307,19 @@
     <t xml:space="preserve">24.3934020996094</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9224872589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2632083892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0277500152588</t>
+    <t xml:space="preserve">23.9224853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2632064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0277481079102</t>
   </si>
   <si>
     <t xml:space="preserve">23.0748405456543</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7451992034912</t>
+    <t xml:space="preserve">22.7452011108398</t>
   </si>
   <si>
     <t xml:space="preserve">22.6039257049561</t>
@@ -1337,37 +1337,37 @@
     <t xml:space="preserve">22.0388278961182</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8504619598389</t>
+    <t xml:space="preserve">21.8504600524902</t>
   </si>
   <si>
     <t xml:space="preserve">22.4626502990723</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2271957397461</t>
+    <t xml:space="preserve">22.2271919250488</t>
   </si>
   <si>
     <t xml:space="preserve">23.4044799804688</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2161159515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8864727020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.498664855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5568351745605</t>
+    <t xml:space="preserve">23.2161140441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.886474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4986629486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5568313598633</t>
   </si>
   <si>
     <t xml:space="preserve">22.1330089569092</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6620960235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1911773681641</t>
+    <t xml:space="preserve">21.6620979309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1911811828613</t>
   </si>
   <si>
     <t xml:space="preserve">21.0028133392334</t>
@@ -1385,13 +1385,13 @@
     <t xml:space="preserve">21.4737300872803</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2742862701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7562789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9446430206299</t>
+    <t xml:space="preserve">22.2742824554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7562770843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9446449279785</t>
   </si>
   <si>
     <t xml:space="preserve">21.5679130554199</t>
@@ -1406,16 +1406,16 @@
     <t xml:space="preserve">21.2382717132568</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8393821716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.792293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5457553863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6399383544922</t>
+    <t xml:space="preserve">22.8393859863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7922916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5457534790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6399402618408</t>
   </si>
   <si>
     <t xml:space="preserve">23.7341213226318</t>
@@ -1433,13 +1433,13 @@
     <t xml:space="preserve">24.2992191314697</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1579437255859</t>
+    <t xml:space="preserve">24.1579456329346</t>
   </si>
   <si>
     <t xml:space="preserve">24.2521266937256</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7230453491211</t>
+    <t xml:space="preserve">24.7230415344238</t>
   </si>
   <si>
     <t xml:space="preserve">24.6288604736328</t>
@@ -1451,19 +1451,19 @@
     <t xml:space="preserve">24.5817680358887</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7701358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9584999084473</t>
+    <t xml:space="preserve">24.7701320648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9585037231445</t>
   </si>
   <si>
     <t xml:space="preserve">25.9003314971924</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7590579986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9474220275879</t>
+    <t xml:space="preserve">25.7590560913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9474201202393</t>
   </si>
   <si>
     <t xml:space="preserve">26.277063369751</t>
@@ -1475,28 +1475,28 @@
     <t xml:space="preserve">26.9834365844727</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8421611785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7479763031006</t>
+    <t xml:space="preserve">26.8421592712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7479782104492</t>
   </si>
   <si>
     <t xml:space="preserve">27.2659873962402</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4543495178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5014419555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3130760192871</t>
+    <t xml:space="preserve">27.4543533325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.501443862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3130779266357</t>
   </si>
   <si>
     <t xml:space="preserve">27.0776176452637</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7008857727051</t>
+    <t xml:space="preserve">26.7008876800537</t>
   </si>
   <si>
     <t xml:space="preserve">26.6537952423096</t>
@@ -1505,40 +1505,40 @@
     <t xml:space="preserve">26.6067047119141</t>
   </si>
   <si>
-    <t xml:space="preserve">25.994514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1357879638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0416069030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6177806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4294147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0055904388428</t>
+    <t xml:space="preserve">25.9945125579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1357917785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0416030883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6177825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4294166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.00559425354</t>
   </si>
   <si>
     <t xml:space="preserve">25.0997734069824</t>
   </si>
   <si>
-    <t xml:space="preserve">24.864315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4404945373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5235996246338</t>
+    <t xml:space="preserve">24.8643169403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4404964447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5235977172852</t>
   </si>
   <si>
     <t xml:space="preserve">26.371244430542</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3241558074951</t>
+    <t xml:space="preserve">26.3241577148438</t>
   </si>
   <si>
     <t xml:space="preserve">26.7950706481934</t>
@@ -1547,10 +1547,10 @@
     <t xml:space="preserve">26.8892517089844</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0305309295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.171802520752</t>
+    <t xml:space="preserve">27.0305290222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1718006134033</t>
   </si>
   <si>
     <t xml:space="preserve">27.5485343933105</t>
@@ -1559,61 +1559,61 @@
     <t xml:space="preserve">27.6898078918457</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1136322021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3961811065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7258243560791</t>
+    <t xml:space="preserve">28.1136302947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.396183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7258224487305</t>
   </si>
   <si>
     <t xml:space="preserve">28.9141883850098</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9501991271973</t>
+    <t xml:space="preserve">29.9502010345459</t>
   </si>
   <si>
     <t xml:space="preserve">29.7618350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3269348144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3740253448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.504222869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6925888061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4460525512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4931449890137</t>
+    <t xml:space="preserve">30.3269329071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5042247772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.692590713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4460563659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4931411743164</t>
   </si>
   <si>
     <t xml:space="preserve">33.482063293457</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6704330444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2936935424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5762519836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9058876037598</t>
+    <t xml:space="preserve">33.6704292297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.293701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.576244354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.905891418457</t>
   </si>
   <si>
     <t xml:space="preserve">33.2466087341309</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8698768615723</t>
+    <t xml:space="preserve">32.869873046875</t>
   </si>
   <si>
     <t xml:space="preserve">33.1524276733398</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">32.5873222351074</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3047752380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9280471801758</t>
+    <t xml:space="preserve">32.3047790527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9280490875244</t>
   </si>
   <si>
     <t xml:space="preserve">31.4571304321289</t>
@@ -1640,127 +1640,127 @@
     <t xml:space="preserve">30.8920307159424</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0803966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0333118438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6565723419189</t>
+    <t xml:space="preserve">31.0803928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0333061218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6565742492676</t>
   </si>
   <si>
     <t xml:space="preserve">30.6094799041748</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2687644958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9862194061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4100379943848</t>
+    <t xml:space="preserve">31.2687683105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.986213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4100360870361</t>
   </si>
   <si>
     <t xml:space="preserve">30.8449401855469</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1745758056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8809547424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0222282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7396812438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0000762939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4709854125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7895469665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5901069641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7784690856934</t>
+    <t xml:space="preserve">31.1745796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8809490203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0222244262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7396793365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0000686645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4709815979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.78955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5901031494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7784652709961</t>
   </si>
   <si>
     <t xml:space="preserve">37.1552047729492</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6732063293457</t>
+    <t xml:space="preserve">37.6732025146484</t>
   </si>
   <si>
     <t xml:space="preserve">38.0846786499023</t>
   </si>
   <si>
-    <t xml:space="preserve">38.228214263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.367000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7976036071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1803703308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3717498779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9411430358887</t>
+    <t xml:space="preserve">38.2282104492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3669967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.797607421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1803665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3717460632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9411392211914</t>
   </si>
   <si>
     <t xml:space="preserve">37.9889869689941</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8454475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3191566467285</t>
+    <t xml:space="preserve">37.8454513549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3191604614258</t>
   </si>
   <si>
     <t xml:space="preserve">38.8501930236816</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7545051574707</t>
+    <t xml:space="preserve">38.754508972168</t>
   </si>
   <si>
     <t xml:space="preserve">39.3286476135254</t>
   </si>
   <si>
-    <t xml:space="preserve">39.041576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8023490905762</t>
+    <t xml:space="preserve">39.0415802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8023529052734</t>
   </si>
   <si>
     <t xml:space="preserve">38.4674377441406</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1325187683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8980407714844</t>
+    <t xml:space="preserve">38.1325149536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8980484008789</t>
   </si>
   <si>
     <t xml:space="preserve">38.7066612243652</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2760581970215</t>
+    <t xml:space="preserve">38.2760543823242</t>
   </si>
   <si>
     <t xml:space="preserve">38.5631256103516</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4195976257324</t>
+    <t xml:space="preserve">38.4195899963379</t>
   </si>
   <si>
     <t xml:space="preserve">39.3764953613281</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">39.1372680664062</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1851119995117</t>
+    <t xml:space="preserve">39.185115814209</t>
   </si>
   <si>
     <t xml:space="preserve">39.2808036804199</t>
@@ -1784,16 +1784,16 @@
     <t xml:space="preserve">42.1036643981934</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5342674255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6730575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8118438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7161521911621</t>
+    <t xml:space="preserve">42.5342712402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6730537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8118476867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7161560058594</t>
   </si>
   <si>
     <t xml:space="preserve">41.912281036377</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">43.0605621337891</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4911651611328</t>
+    <t xml:space="preserve">43.4911727905273</t>
   </si>
   <si>
     <t xml:space="preserve">44.2566909790039</t>
@@ -1814,34 +1814,34 @@
     <t xml:space="preserve">43.4433250427246</t>
   </si>
   <si>
-    <t xml:space="preserve">44.017463684082</t>
+    <t xml:space="preserve">44.0174674987793</t>
   </si>
   <si>
     <t xml:space="preserve">43.6347007751465</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2040977478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9170265197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9265213012695</t>
+    <t xml:space="preserve">43.2041053771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9170303344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9265174865723</t>
   </si>
   <si>
     <t xml:space="preserve">45.404972076416</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2614402770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5963516235352</t>
+    <t xml:space="preserve">45.2614364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5963592529297</t>
   </si>
   <si>
     <t xml:space="preserve">47.6536903381348</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8976593017578</t>
+    <t xml:space="preserve">48.8976631164551</t>
   </si>
   <si>
     <t xml:space="preserve">48.6105918884277</t>
@@ -1850,40 +1850,40 @@
     <t xml:space="preserve">49.1847343444824</t>
   </si>
   <si>
-    <t xml:space="preserve">48.993350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7588729858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2804183959961</t>
+    <t xml:space="preserve">48.9933547973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7588768005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2804222106934</t>
   </si>
   <si>
     <t xml:space="preserve">49.6631813049316</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3761100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5674896240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6200866699219</t>
+    <t xml:space="preserve">49.3761138916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5674934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6200828552246</t>
   </si>
   <si>
     <t xml:space="preserve">51.0028457641602</t>
   </si>
   <si>
-    <t xml:space="preserve">52.7252616882324</t>
+    <t xml:space="preserve">52.7252655029297</t>
   </si>
   <si>
     <t xml:space="preserve">52.6295738220215</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9597473144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8640594482422</t>
+    <t xml:space="preserve">51.9597434997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8640556335449</t>
   </si>
   <si>
     <t xml:space="preserve">51.6726760864258</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">48.4192123413086</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3235244750977</t>
+    <t xml:space="preserve">48.3235168457031</t>
   </si>
   <si>
     <t xml:space="preserve">50.0459442138672</t>
@@ -1901,28 +1901,28 @@
     <t xml:space="preserve">51.3856086730957</t>
   </si>
   <si>
-    <t xml:space="preserve">50.907154083252</t>
+    <t xml:space="preserve">50.9071578979492</t>
   </si>
   <si>
     <t xml:space="preserve">49.8545608520508</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4287071228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5338859558105</t>
+    <t xml:space="preserve">50.4287033081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5338897705078</t>
   </si>
   <si>
     <t xml:space="preserve">54.0649337768555</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2994079589844</t>
+    <t xml:space="preserve">53.2994117736816</t>
   </si>
   <si>
     <t xml:space="preserve">52.4381942749023</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3666191101074</t>
+    <t xml:space="preserve">47.3666229248047</t>
   </si>
   <si>
     <t xml:space="preserve">46.9838562011719</t>
@@ -1940,49 +1940,49 @@
     <t xml:space="preserve">43.586856842041</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7687492370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6493263244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5967330932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0945510864258</t>
+    <t xml:space="preserve">41.7687454223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6493225097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5967292785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0945491790771</t>
   </si>
   <si>
     <t xml:space="preserve">31.4820594787598</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1854934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5299015045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0992984771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3816184997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9269027709961</t>
+    <t xml:space="preserve">29.1854915618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5299053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0992946624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3816204071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9268989562988</t>
   </si>
   <si>
     <t xml:space="preserve">36.410099029541</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5010375976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3096656799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5441398620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0704383850098</t>
+    <t xml:space="preserve">35.5010452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3096618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5441360473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0704345703125</t>
   </si>
   <si>
     <t xml:space="preserve">37.0799293518066</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">37.1277732849121</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2329597473145</t>
+    <t xml:space="preserve">39.2329559326172</t>
   </si>
   <si>
     <t xml:space="preserve">40.429084777832</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">39.998477935791</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7351417541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9791069030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4528198242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0700607299805</t>
+    <t xml:space="preserve">44.7351379394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9791107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4528160095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0700569152832</t>
   </si>
   <si>
     <t xml:space="preserve">45.3571319580078</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1179084777832</t>
+    <t xml:space="preserve">45.1179046630859</t>
   </si>
   <si>
     <t xml:space="preserve">46.4575614929199</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6441955566406</t>
+    <t xml:space="preserve">45.6441917419434</t>
   </si>
   <si>
     <t xml:space="preserve">44.8786773681641</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">45.3092842102051</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1657485961914</t>
+    <t xml:space="preserve">45.1657447814941</t>
   </si>
   <si>
     <t xml:space="preserve">44.2088470458984</t>
@@ -2042,34 +2042,34 @@
     <t xml:space="preserve">43.15625</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9217720031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8644371032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5821113586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.022216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5485038757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5101585388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7015342712402</t>
+    <t xml:space="preserve">43.9217758178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8644409179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5821075439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0222091674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5485076904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5101547241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7015380859375</t>
   </si>
   <si>
     <t xml:space="preserve">48.7062873840332</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9407577514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5149078369141</t>
+    <t xml:space="preserve">47.9407615661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5149002075195</t>
   </si>
   <si>
     <t xml:space="preserve">51.4813003540039</t>
@@ -2078,49 +2078,49 @@
     <t xml:space="preserve">51.1942291259766</t>
   </si>
   <si>
-    <t xml:space="preserve">51.768367767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2899169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1080284118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9692420959473</t>
+    <t xml:space="preserve">51.7683639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2899131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1080360412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.96923828125</t>
   </si>
   <si>
     <t xml:space="preserve">53.4907913208008</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1175231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6916580200195</t>
+    <t xml:space="preserve">55.1175193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6916656494141</t>
   </si>
   <si>
     <t xml:space="preserve">55.5002822875977</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3520011901855</t>
+    <t xml:space="preserve">54.3519973754883</t>
   </si>
   <si>
     <t xml:space="preserve">54.6390686035156</t>
   </si>
   <si>
-    <t xml:space="preserve">54.830451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4045944213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7442512512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9356346130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1270179748535</t>
+    <t xml:space="preserve">54.8304481506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.404598236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.744255065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9356307983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1270141601562</t>
   </si>
   <si>
     <t xml:space="preserve">56.2658004760742</t>
@@ -2129,13 +2129,13 @@
     <t xml:space="preserve">55.9787330627441</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3183975219727</t>
+    <t xml:space="preserve">57.3183937072754</t>
   </si>
   <si>
     <t xml:space="preserve">58.6580543518066</t>
   </si>
   <si>
-    <t xml:space="preserve">57.2227058410645</t>
+    <t xml:space="preserve">57.2227020263672</t>
   </si>
   <si>
     <t xml:space="preserve">57.7011566162109</t>
@@ -2147,19 +2147,19 @@
     <t xml:space="preserve">57.988224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">58.849437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.3373756408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.442569732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2942810058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.346866607666</t>
+    <t xml:space="preserve">58.8494338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.3373794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4425659179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2942848205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3468742370605</t>
   </si>
   <si>
     <t xml:space="preserve">63.7296295166016</t>
@@ -2174,31 +2174,31 @@
     <t xml:space="preserve">64.5908432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">65.9305038452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6960296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3563690185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.9831008911133</t>
+    <t xml:space="preserve">65.9305114746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6960220336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3563766479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9830932617188</t>
   </si>
   <si>
     <t xml:space="preserve">67.1744766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5046539306641</t>
+    <t xml:space="preserve">66.504638671875</t>
   </si>
   <si>
     <t xml:space="preserve">67.8443145751953</t>
   </si>
   <si>
-    <t xml:space="preserve">70.0451812744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1839752197266</t>
+    <t xml:space="preserve">70.0451889038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1839828491211</t>
   </si>
   <si>
     <t xml:space="preserve">71.2891540527344</t>
@@ -2207,46 +2207,46 @@
     <t xml:space="preserve">70.8107070922852</t>
   </si>
   <si>
-    <t xml:space="preserve">70.6193313598633</t>
+    <t xml:space="preserve">70.6193237304688</t>
   </si>
   <si>
     <t xml:space="preserve">71.7676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">72.0546798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0020751953125</t>
+    <t xml:space="preserve">72.0546722412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0020904541016</t>
   </si>
   <si>
     <t xml:space="preserve">69.4710464477539</t>
   </si>
   <si>
-    <t xml:space="preserve">68.9925918579102</t>
+    <t xml:space="preserve">68.9925994873047</t>
   </si>
   <si>
     <t xml:space="preserve">69.9494934082031</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8012161254883</t>
+    <t xml:space="preserve">68.8012084960938</t>
   </si>
   <si>
     <t xml:space="preserve">69.6624221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">76.552116394043</t>
+    <t xml:space="preserve">76.5521087646484</t>
   </si>
   <si>
     <t xml:space="preserve">77.7003860473633</t>
   </si>
   <si>
-    <t xml:space="preserve">75.8822860717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.734001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.8727874755859</t>
+    <t xml:space="preserve">75.8822784423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.7339935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.8727798461914</t>
   </si>
   <si>
     <t xml:space="preserve">74.8296890258789</t>
@@ -2258,19 +2258,19 @@
     <t xml:space="preserve">78.2745361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7960815429688</t>
+    <t xml:space="preserve">77.7960968017578</t>
   </si>
   <si>
     <t xml:space="preserve">79.4228210449219</t>
   </si>
   <si>
-    <t xml:space="preserve">80.7624816894531</t>
+    <t xml:space="preserve">80.7624893188477</t>
   </si>
   <si>
     <t xml:space="preserve">82.0064468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">81.5279998779297</t>
+    <t xml:space="preserve">81.5279922485352</t>
   </si>
   <si>
     <t xml:space="preserve">81.910758972168</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">82.3892135620117</t>
   </si>
   <si>
-    <t xml:space="preserve">81.4323043823242</t>
+    <t xml:space="preserve">81.4323120117188</t>
   </si>
   <si>
     <t xml:space="preserve">81.1452407836914</t>
@@ -2288,64 +2288,64 @@
     <t xml:space="preserve">80.4754028320312</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7193756103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8150634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.3461151123047</t>
+    <t xml:space="preserve">81.7193832397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8150787353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.3461074829102</t>
   </si>
   <si>
     <t xml:space="preserve">80.9538497924805</t>
   </si>
   <si>
-    <t xml:space="preserve">82.7719802856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2935180664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.0305633544922</t>
+    <t xml:space="preserve">82.77197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2935256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.0305709838867</t>
   </si>
   <si>
     <t xml:space="preserve">79.3271331787109</t>
   </si>
   <si>
-    <t xml:space="preserve">83.728874206543</t>
+    <t xml:space="preserve">83.7288818359375</t>
   </si>
   <si>
     <t xml:space="preserve">82.1021423339844</t>
   </si>
   <si>
-    <t xml:space="preserve">76.7434997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.5185089111328</t>
+    <t xml:space="preserve">76.7434921264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.5185012817383</t>
   </si>
   <si>
     <t xml:space="preserve">79.8055801391602</t>
   </si>
   <si>
-    <t xml:space="preserve">82.4849014282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3797149658203</t>
+    <t xml:space="preserve">82.4848937988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3797225952148</t>
   </si>
   <si>
     <t xml:space="preserve">78.6572952270508</t>
   </si>
   <si>
-    <t xml:space="preserve">78.4659194946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6857757568359</t>
+    <t xml:space="preserve">78.4659118652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6857681274414</t>
   </si>
   <si>
     <t xml:space="preserve">85.3556060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">83.0590438842773</t>
+    <t xml:space="preserve">83.0590362548828</t>
   </si>
   <si>
     <t xml:space="preserve">85.9297485351562</t>
@@ -2357,22 +2357,22 @@
     <t xml:space="preserve">87.269401550293</t>
   </si>
   <si>
-    <t xml:space="preserve">88.3220062255859</t>
+    <t xml:space="preserve">88.3219985961914</t>
   </si>
   <si>
     <t xml:space="preserve">86.7909545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">90.9056396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3840866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1065063476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.8815155029297</t>
+    <t xml:space="preserve">90.905632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3840789794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1065139770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.8815231323242</t>
   </si>
   <si>
     <t xml:space="preserve">97.2211837768555</t>
@@ -2381,25 +2381,25 @@
     <t xml:space="preserve">100.474647521973</t>
   </si>
   <si>
-    <t xml:space="preserve">101.622924804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.240173339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.986701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5608367919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.9004974365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.264289855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.6901473999023</t>
+    <t xml:space="preserve">101.622932434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.240165710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.9867095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5608444213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.900505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2642822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.6901397705078</t>
   </si>
   <si>
     <t xml:space="preserve">94.8289337158203</t>
@@ -2408,43 +2408,43 @@
     <t xml:space="preserve">95.3073806762695</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2547912597656</t>
+    <t xml:space="preserve">94.2547836303711</t>
   </si>
   <si>
     <t xml:space="preserve">94.4461669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">97.0298156738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.541862487793</t>
+    <t xml:space="preserve">97.0298004150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5418548583984</t>
   </si>
   <si>
     <t xml:space="preserve">94.1591033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8720169067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0634155273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3935699462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6806488037109</t>
+    <t xml:space="preserve">93.8720245361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0634078979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3935775756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6806411743164</t>
   </si>
   <si>
     <t xml:space="preserve">92.9151229858398</t>
   </si>
   <si>
-    <t xml:space="preserve">93.2978820800781</t>
+    <t xml:space="preserve">93.2978897094727</t>
   </si>
   <si>
     <t xml:space="preserve">92.723747253418</t>
   </si>
   <si>
-    <t xml:space="preserve">94.3504867553711</t>
+    <t xml:space="preserve">94.3504791259766</t>
   </si>
   <si>
     <t xml:space="preserve">97.6039428710938</t>
@@ -2456,31 +2456,31 @@
     <t xml:space="preserve">104.876388549805</t>
   </si>
   <si>
-    <t xml:space="preserve">104.493621826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.598815917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.364334106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.660903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.235046386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.641914367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.21605682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.938484191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.555717468262</t>
+    <t xml:space="preserve">104.493629455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.598823547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.364326477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.66089630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.235038757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.64192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.21607208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.9384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.555725097656</t>
   </si>
   <si>
     <t xml:space="preserve">109.469528198242</t>
@@ -2489,13 +2489,13 @@
     <t xml:space="preserve">107.747100830078</t>
   </si>
   <si>
-    <t xml:space="preserve">108.704002380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.197082519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5177459716797</t>
+    <t xml:space="preserve">108.703994750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.197074890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5177536010742</t>
   </si>
   <si>
     <t xml:space="preserve">99.7091217041016</t>
@@ -2504,10 +2504,10 @@
     <t xml:space="preserve">103.345352172852</t>
   </si>
   <si>
-    <t xml:space="preserve">103.536735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.024681091309</t>
+    <t xml:space="preserve">103.536727905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.024673461914</t>
   </si>
   <si>
     <t xml:space="preserve">106.981582641602</t>
@@ -2531,31 +2531,31 @@
     <t xml:space="preserve">102.962600708008</t>
   </si>
   <si>
-    <t xml:space="preserve">105.450523376465</t>
+    <t xml:space="preserve">105.450531005859</t>
   </si>
   <si>
     <t xml:space="preserve">102.00569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">103.919494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.407440185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.086769104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.809188842773</t>
+    <t xml:space="preserve">103.919486999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.407432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.086753845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.809196472168</t>
   </si>
   <si>
     <t xml:space="preserve">113.679893493652</t>
   </si>
   <si>
-    <t xml:space="preserve">110.043663024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.172950744629</t>
+    <t xml:space="preserve">110.043647766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.172966003418</t>
   </si>
   <si>
     <t xml:space="preserve">111.000564575195</t>
@@ -2567,34 +2567,34 @@
     <t xml:space="preserve">109.85228729248</t>
   </si>
   <si>
-    <t xml:space="preserve">110.426429748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.383316040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.340225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.445411682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.29712677002</t>
+    <t xml:space="preserve">110.426422119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.383331298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.340232849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.445404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.297119140625</t>
   </si>
   <si>
     <t xml:space="preserve">112.722984313965</t>
   </si>
   <si>
-    <t xml:space="preserve">115.019554138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.593688964844</t>
+    <t xml:space="preserve">115.019546508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.593696594238</t>
   </si>
   <si>
     <t xml:space="preserve">115.210929870605</t>
   </si>
   <si>
-    <t xml:space="preserve">116.741973876953</t>
+    <t xml:space="preserve">116.741966247559</t>
   </si>
   <si>
     <t xml:space="preserve">116.167831420898</t>
@@ -2603,13 +2603,13 @@
     <t xml:space="preserve">115.78507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">116.550590515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.804061889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.186820983887</t>
+    <t xml:space="preserve">116.550598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.804054260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.186828613281</t>
   </si>
   <si>
     <t xml:space="preserve">122.100616455078</t>
@@ -2618,10 +2618,10 @@
     <t xml:space="preserve">122.866134643555</t>
   </si>
   <si>
-    <t xml:space="preserve">123.631660461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.478240966797</t>
+    <t xml:space="preserve">123.631652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.478256225586</t>
   </si>
   <si>
     <t xml:space="preserve">127.267890930176</t>
@@ -2636,19 +2636,19 @@
     <t xml:space="preserve">132.052398681641</t>
   </si>
   <si>
-    <t xml:space="preserve">134.157577514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.774826049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.626541137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.435134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.923110961914</t>
+    <t xml:space="preserve">134.157562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.774810791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.626556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.435165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.923095703125</t>
   </si>
   <si>
     <t xml:space="preserve">136.645523071289</t>
@@ -2660,19 +2660,19 @@
     <t xml:space="preserve">135.305847167969</t>
   </si>
   <si>
-    <t xml:space="preserve">131.86100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.731735229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.262771606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.793792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.176559448242</t>
+    <t xml:space="preserve">131.861022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.731719970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.262756347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.793807983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.176544189453</t>
   </si>
   <si>
     <t xml:space="preserve">137.028274536133</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">139.898986816406</t>
   </si>
   <si>
-    <t xml:space="preserve">136.454132080078</t>
+    <t xml:space="preserve">136.454147338867</t>
   </si>
   <si>
     <t xml:space="preserve">138.750701904297</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">139.324844360352</t>
   </si>
   <si>
-    <t xml:space="preserve">137.98518371582</t>
+    <t xml:space="preserve">137.985198974609</t>
   </si>
   <si>
     <t xml:space="preserve">135.497253417969</t>
@@ -2702,19 +2702,19 @@
     <t xml:space="preserve">144.492111206055</t>
   </si>
   <si>
-    <t xml:space="preserve">144.874877929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.109359741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.195541381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.726577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.917953491211</t>
+    <t xml:space="preserve">144.874893188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.109344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.195556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.726593017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.917984008789</t>
   </si>
   <si>
     <t xml:space="preserve">144.683486938477</t>
@@ -2732,16 +2732,16 @@
     <t xml:space="preserve">146.788681030273</t>
   </si>
   <si>
-    <t xml:space="preserve">149.276626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.999053955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.424896240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.486999511719</t>
+    <t xml:space="preserve">149.276641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.999038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.424911499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.48698425293</t>
   </si>
   <si>
     <t xml:space="preserve">152.338714599609</t>
@@ -2750,13 +2750,13 @@
     <t xml:space="preserve">155.400772094727</t>
   </si>
   <si>
-    <t xml:space="preserve">151.190414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.888732910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.037017822266</t>
+    <t xml:space="preserve">151.1904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.888717651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.037002563477</t>
   </si>
   <si>
     <t xml:space="preserve">158.654266357422</t>
@@ -2765,13 +2765,13 @@
     <t xml:space="preserve">159.61116027832</t>
   </si>
   <si>
-    <t xml:space="preserve">161.333587646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.524963378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.438751220703</t>
+    <t xml:space="preserve">161.333572387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.524978637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.438766479492</t>
   </si>
   <si>
     <t xml:space="preserve">163.821517944336</t>
@@ -2783,43 +2783,43 @@
     <t xml:space="preserve">173.773300170898</t>
   </si>
   <si>
-    <t xml:space="preserve">170.32844543457</t>
+    <t xml:space="preserve">170.328430175781</t>
   </si>
   <si>
     <t xml:space="preserve">165.161193847656</t>
   </si>
   <si>
-    <t xml:space="preserve">168.031890869141</t>
+    <t xml:space="preserve">168.031921386719</t>
   </si>
   <si>
     <t xml:space="preserve">165.352569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">160.759429931641</t>
+    <t xml:space="preserve">160.75944519043</t>
   </si>
   <si>
     <t xml:space="preserve">162.099090576172</t>
   </si>
   <si>
-    <t xml:space="preserve">171.668106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.074996948242</t>
+    <t xml:space="preserve">171.668121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.074981689453</t>
   </si>
   <si>
     <t xml:space="preserve">161.93049621582</t>
   </si>
   <si>
-    <t xml:space="preserve">161.353576660156</t>
+    <t xml:space="preserve">161.353561401367</t>
   </si>
   <si>
     <t xml:space="preserve">160.58430480957</t>
   </si>
   <si>
-    <t xml:space="preserve">159.045761108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.122360229492</t>
+    <t xml:space="preserve">159.045776367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.12239074707</t>
   </si>
   <si>
     <t xml:space="preserve">145.583618164062</t>
@@ -2828,16 +2828,16 @@
     <t xml:space="preserve">147.314468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">150.391510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.199203491211</t>
+    <t xml:space="preserve">150.391525268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.19921875</t>
   </si>
   <si>
     <t xml:space="preserve">148.083724975586</t>
   </si>
   <si>
-    <t xml:space="preserve">151.737747192383</t>
+    <t xml:space="preserve">151.737731933594</t>
   </si>
   <si>
     <t xml:space="preserve">149.622268676758</t>
@@ -2852,31 +2852,31 @@
     <t xml:space="preserve">155.968704223633</t>
   </si>
   <si>
-    <t xml:space="preserve">154.430191040039</t>
+    <t xml:space="preserve">154.43017578125</t>
   </si>
   <si>
     <t xml:space="preserve">160.776611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">166.353805541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.200134277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.469268798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.430618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.007583618164</t>
+    <t xml:space="preserve">166.353790283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.200119018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.469284057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.430633544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.007598876953</t>
   </si>
   <si>
     <t xml:space="preserve">162.507461547852</t>
   </si>
   <si>
-    <t xml:space="preserve">163.469039916992</t>
+    <t xml:space="preserve">163.46907043457</t>
   </si>
   <si>
     <t xml:space="preserve">165.584533691406</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">161.738189697266</t>
   </si>
   <si>
-    <t xml:space="preserve">168.853912353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.508178710938</t>
+    <t xml:space="preserve">168.853927612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.508163452148</t>
   </si>
   <si>
     <t xml:space="preserve">175.584991455078</t>
@@ -2915,10 +2915,10 @@
     <t xml:space="preserve">181.739120483398</t>
   </si>
   <si>
-    <t xml:space="preserve">185.008499145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.085342407227</t>
+    <t xml:space="preserve">185.008514404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.085327148438</t>
   </si>
   <si>
     <t xml:space="preserve">182.508392333984</t>
@@ -2927,13 +2927,13 @@
     <t xml:space="preserve">168.276962280273</t>
   </si>
   <si>
-    <t xml:space="preserve">169.046249389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.584777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.507690429688</t>
+    <t xml:space="preserve">169.046234130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.584747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.507705688477</t>
   </si>
   <si>
     <t xml:space="preserve">174.046463012695</t>
@@ -2945,16 +2945,16 @@
     <t xml:space="preserve">169.623184204102</t>
   </si>
   <si>
-    <t xml:space="preserve">169.238555908203</t>
+    <t xml:space="preserve">169.238540649414</t>
   </si>
   <si>
     <t xml:space="preserve">175.008041381836</t>
   </si>
   <si>
-    <t xml:space="preserve">172.700256347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.123291015625</t>
+    <t xml:space="preserve">172.700241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.123306274414</t>
   </si>
   <si>
     <t xml:space="preserve">171.93098449707</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">163.85368347168</t>
   </si>
   <si>
-    <t xml:space="preserve">166.738433837891</t>
+    <t xml:space="preserve">166.738403320312</t>
   </si>
   <si>
     <t xml:space="preserve">164.238311767578</t>
@@ -2981,16 +2981,16 @@
     <t xml:space="preserve">165.392211914062</t>
   </si>
   <si>
-    <t xml:space="preserve">151.160781860352</t>
+    <t xml:space="preserve">151.160797119141</t>
   </si>
   <si>
     <t xml:space="preserve">158.853454589844</t>
   </si>
   <si>
-    <t xml:space="preserve">158.468826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.31494140625</t>
+    <t xml:space="preserve">158.468841552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.314926147461</t>
   </si>
   <si>
     <t xml:space="preserve">159.815032958984</t>
@@ -2999,25 +2999,25 @@
     <t xml:space="preserve">156.930282592773</t>
   </si>
   <si>
-    <t xml:space="preserve">156.161010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.314666748047</t>
+    <t xml:space="preserve">156.161026000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.314682006836</t>
   </si>
   <si>
     <t xml:space="preserve">145.96826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">146.929840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.353088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.468612670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.276260375977</t>
+    <t xml:space="preserve">146.929824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.353103637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.468597412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.276245117188</t>
   </si>
   <si>
     <t xml:space="preserve">157.122604370117</t>
@@ -3035,13 +3035,13 @@
     <t xml:space="preserve">136.92936706543</t>
   </si>
   <si>
-    <t xml:space="preserve">138.660217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.69841003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.506088256836</t>
+    <t xml:space="preserve">138.660232543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.698425292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.506103515625</t>
   </si>
   <si>
     <t xml:space="preserve">130.198287963867</t>
@@ -3053,10 +3053,10 @@
     <t xml:space="preserve">130.005981445312</t>
   </si>
   <si>
-    <t xml:space="preserve">130.775238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.852066040039</t>
+    <t xml:space="preserve">130.77522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.852081298828</t>
   </si>
   <si>
     <t xml:space="preserve">129.621353149414</t>
@@ -3065,19 +3065,19 @@
     <t xml:space="preserve">132.890716552734</t>
   </si>
   <si>
-    <t xml:space="preserve">137.506317138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.160125732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.467895507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.583160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.813438415527</t>
+    <t xml:space="preserve">137.506332397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.160110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.467910766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.583145141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.813430786133</t>
   </si>
   <si>
     <t xml:space="preserve">118.659301757812</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">125.582702636719</t>
   </si>
   <si>
-    <t xml:space="preserve">125.198059082031</t>
+    <t xml:space="preserve">125.198066711426</t>
   </si>
   <si>
     <t xml:space="preserve">137.314010620117</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">142.891189575195</t>
   </si>
   <si>
-    <t xml:space="preserve">140.391067504883</t>
+    <t xml:space="preserve">140.391052246094</t>
   </si>
   <si>
     <t xml:space="preserve">145.391296386719</t>
@@ -3107,37 +3107,37 @@
     <t xml:space="preserve">145.00666809082</t>
   </si>
   <si>
-    <t xml:space="preserve">145.775955200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.814361572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.27604675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.275817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.602722167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.698852539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.083511352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.525650024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.160339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.198745727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.910263061523</t>
+    <t xml:space="preserve">145.775924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.814346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.276031494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.275802612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.60270690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.698867797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.08349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.525634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.160354614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.198760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.910278320312</t>
   </si>
   <si>
     <t xml:space="preserve">139.429473876953</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">142.314239501953</t>
   </si>
   <si>
-    <t xml:space="preserve">130.871398925781</t>
+    <t xml:space="preserve">130.87141418457</t>
   </si>
   <si>
     <t xml:space="preserve">129.525177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">129.909820556641</t>
+    <t xml:space="preserve">129.90983581543</t>
   </si>
   <si>
     <t xml:space="preserve">133.371520996094</t>
@@ -3188,10 +3188,10 @@
     <t xml:space="preserve">109.81273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">113.562911987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.389923095703</t>
+    <t xml:space="preserve">113.56290435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.389915466309</t>
   </si>
   <si>
     <t xml:space="preserve">115.774551391602</t>
@@ -3200,13 +3200,13 @@
     <t xml:space="preserve">118.755462646484</t>
   </si>
   <si>
-    <t xml:space="preserve">118.082344055176</t>
+    <t xml:space="preserve">118.08235168457</t>
   </si>
   <si>
     <t xml:space="preserve">122.31330871582</t>
   </si>
   <si>
-    <t xml:space="preserve">120.293991088867</t>
+    <t xml:space="preserve">120.293983459473</t>
   </si>
   <si>
     <t xml:space="preserve">120.101669311523</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">120.486312866211</t>
   </si>
   <si>
-    <t xml:space="preserve">116.736129760742</t>
+    <t xml:space="preserve">116.736145019531</t>
   </si>
   <si>
     <t xml:space="preserve">116.832298278809</t>
@@ -3233,28 +3233,28 @@
     <t xml:space="preserve">124.621116638184</t>
   </si>
   <si>
-    <t xml:space="preserve">123.274887084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.544044494629</t>
+    <t xml:space="preserve">123.274894714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.544052124023</t>
   </si>
   <si>
     <t xml:space="preserve">124.044158935547</t>
   </si>
   <si>
-    <t xml:space="preserve">124.332641601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.986656188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.659759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.698173522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.178741455078</t>
+    <t xml:space="preserve">124.332633972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.986640930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.659774780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.698188781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.178749084473</t>
   </si>
   <si>
     <t xml:space="preserve">114.52449798584</t>
@@ -3263,16 +3263,16 @@
     <t xml:space="preserve">112.889801025391</t>
   </si>
   <si>
-    <t xml:space="preserve">114.236022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.062789916992</t>
+    <t xml:space="preserve">114.236030578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.062797546387</t>
   </si>
   <si>
     <t xml:space="preserve">112.216690063477</t>
   </si>
   <si>
-    <t xml:space="preserve">112.505180358887</t>
+    <t xml:space="preserve">112.505172729492</t>
   </si>
   <si>
     <t xml:space="preserve">113.947547912598</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">116.447662353516</t>
   </si>
   <si>
-    <t xml:space="preserve">115.197608947754</t>
+    <t xml:space="preserve">115.197601318359</t>
   </si>
   <si>
     <t xml:space="preserve">119.140090942383</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">119.428565979004</t>
   </si>
   <si>
-    <t xml:space="preserve">117.890029907227</t>
+    <t xml:space="preserve">117.890022277832</t>
   </si>
   <si>
     <t xml:space="preserve">115.293762207031</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">113.178276062012</t>
   </si>
   <si>
-    <t xml:space="preserve">119.332405090332</t>
+    <t xml:space="preserve">119.332412719727</t>
   </si>
   <si>
     <t xml:space="preserve">123.082580566406</t>
@@ -3314,61 +3314,61 @@
     <t xml:space="preserve">122.986419677734</t>
   </si>
   <si>
-    <t xml:space="preserve">118.27466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.717041015625</t>
+    <t xml:space="preserve">118.274673461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.71703338623</t>
   </si>
   <si>
     <t xml:space="preserve">120.774787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">123.659530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.948226928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.736831665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.679077148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.832740783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.794319152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.467437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.602233886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.044372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.159866333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.967338562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.351959228516</t>
+    <t xml:space="preserve">123.659538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.948257446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.736801147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.679061889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.83275604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.794334411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.46745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.602249145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.044387817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.159881591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.967323303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.351943969727</t>
   </si>
   <si>
     <t xml:space="preserve">123.563369750977</t>
   </si>
   <si>
-    <t xml:space="preserve">127.313529968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.371276855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.736595153809</t>
+    <t xml:space="preserve">127.313545227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.371307373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.736587524414</t>
   </si>
   <si>
     <t xml:space="preserve">121.447891235352</t>
@@ -3386,28 +3386,28 @@
     <t xml:space="preserve">121.063255310059</t>
   </si>
   <si>
-    <t xml:space="preserve">117.505393981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.870712280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.255332946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.312850952148</t>
+    <t xml:space="preserve">117.505401611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.870704650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.255348205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.312858581543</t>
   </si>
   <si>
     <t xml:space="preserve">115.582237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">115.678398132324</t>
+    <t xml:space="preserve">115.67839050293</t>
   </si>
   <si>
     <t xml:space="preserve">118.178504943848</t>
   </si>
   <si>
-    <t xml:space="preserve">114.909133911133</t>
+    <t xml:space="preserve">114.909126281738</t>
   </si>
   <si>
     <t xml:space="preserve">106.596168518066</t>
@@ -3431,13 +3431,13 @@
     <t xml:space="preserve">102.816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">106.014739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.041603088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.437377929688</t>
+    <t xml:space="preserve">106.01473236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.041610717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.437370300293</t>
   </si>
   <si>
     <t xml:space="preserve">109.212615966797</t>
@@ -3452,16 +3452,16 @@
     <t xml:space="preserve">111.829071044922</t>
   </si>
   <si>
-    <t xml:space="preserve">107.27449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.851860046387</t>
+    <t xml:space="preserve">107.274505615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.851867675781</t>
   </si>
   <si>
     <t xml:space="preserve">104.658050537109</t>
   </si>
   <si>
-    <t xml:space="preserve">101.847785949707</t>
+    <t xml:space="preserve">101.847793579102</t>
   </si>
   <si>
     <t xml:space="preserve">102.429222106934</t>
@@ -3470,10 +3470,10 @@
     <t xml:space="preserve">103.495193481445</t>
   </si>
   <si>
-    <t xml:space="preserve">104.076622009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.402359008789</t>
+    <t xml:space="preserve">104.076629638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.402366638184</t>
   </si>
   <si>
     <t xml:space="preserve">106.693069458008</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">102.332321166992</t>
   </si>
   <si>
-    <t xml:space="preserve">100.87873840332</t>
+    <t xml:space="preserve">100.878730773926</t>
   </si>
   <si>
     <t xml:space="preserve">103.979721069336</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">108.340476989746</t>
   </si>
   <si>
-    <t xml:space="preserve">117.643409729004</t>
+    <t xml:space="preserve">117.643417358398</t>
   </si>
   <si>
     <t xml:space="preserve">118.515556335449</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">114.445518493652</t>
   </si>
   <si>
-    <t xml:space="preserve">114.73624420166</t>
+    <t xml:space="preserve">114.736236572266</t>
   </si>
   <si>
     <t xml:space="preserve">115.026947021484</t>
@@ -3542,10 +3542,10 @@
     <t xml:space="preserve">116.965065002441</t>
   </si>
   <si>
-    <t xml:space="preserve">113.476470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.25171661377</t>
+    <t xml:space="preserve">113.476463317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.251708984375</t>
   </si>
   <si>
     <t xml:space="preserve">114.833145141602</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">117.449592590332</t>
   </si>
   <si>
-    <t xml:space="preserve">118.61247253418</t>
+    <t xml:space="preserve">118.612464904785</t>
   </si>
   <si>
     <t xml:space="preserve">112.99193572998</t>
@@ -3563,19 +3563,19 @@
     <t xml:space="preserve">111.053825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">112.701225280762</t>
+    <t xml:space="preserve">112.701232910156</t>
   </si>
   <si>
     <t xml:space="preserve">112.604316711426</t>
   </si>
   <si>
-    <t xml:space="preserve">115.996017456055</t>
+    <t xml:space="preserve">115.99600982666</t>
   </si>
   <si>
     <t xml:space="preserve">112.216697692871</t>
   </si>
   <si>
-    <t xml:space="preserve">108.24356842041</t>
+    <t xml:space="preserve">108.243560791016</t>
   </si>
   <si>
     <t xml:space="preserve">107.080696105957</t>
@@ -3587,22 +3587,22 @@
     <t xml:space="preserve">108.534278869629</t>
   </si>
   <si>
-    <t xml:space="preserve">110.181671142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.890953063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.24764251709</t>
+    <t xml:space="preserve">110.181678771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.890960693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.247634887695</t>
   </si>
   <si>
     <t xml:space="preserve">113.282661437988</t>
   </si>
   <si>
-    <t xml:space="preserve">112.410499572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.639335632324</t>
+    <t xml:space="preserve">112.410507202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.639343261719</t>
   </si>
   <si>
     <t xml:space="preserve">117.934120178223</t>
@@ -3617,10 +3617,10 @@
     <t xml:space="preserve">118.031028747559</t>
   </si>
   <si>
-    <t xml:space="preserve">121.13200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.10107421875</t>
+    <t xml:space="preserve">121.132011413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.101066589355</t>
   </si>
   <si>
     <t xml:space="preserve">122.876312255859</t>
@@ -3635,19 +3635,19 @@
     <t xml:space="preserve">120.550575256348</t>
   </si>
   <si>
-    <t xml:space="preserve">122.779403686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.26392364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.810348510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.74437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.74845123291</t>
+    <t xml:space="preserve">122.779411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.263931274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.810340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.744384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.748458862305</t>
   </si>
   <si>
     <t xml:space="preserve">131.985443115234</t>
@@ -3656,10 +3656,10 @@
     <t xml:space="preserve">131.888549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">132.179244995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.531829833984</t>
+    <t xml:space="preserve">132.179260253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.531845092773</t>
   </si>
   <si>
     <t xml:space="preserve">128.593734741211</t>
@@ -3668,10 +3668,10 @@
     <t xml:space="preserve">127.043251037598</t>
   </si>
   <si>
-    <t xml:space="preserve">124.814430236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.686569213867</t>
+    <t xml:space="preserve">124.814422607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.686561584473</t>
   </si>
   <si>
     <t xml:space="preserve">126.849433898926</t>
@@ -3692,10 +3692,10 @@
     <t xml:space="preserve">121.422729492188</t>
   </si>
   <si>
-    <t xml:space="preserve">121.325820922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.259857177734</t>
+    <t xml:space="preserve">121.325813293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.259864807129</t>
   </si>
   <si>
     <t xml:space="preserve">120.35676574707</t>
@@ -3704,13 +3704,13 @@
     <t xml:space="preserve">118.321746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">116.8681640625</t>
+    <t xml:space="preserve">116.868156433105</t>
   </si>
   <si>
     <t xml:space="preserve">115.802200317383</t>
   </si>
   <si>
-    <t xml:space="preserve">113.864097595215</t>
+    <t xml:space="preserve">113.86408996582</t>
   </si>
   <si>
     <t xml:space="preserve">113.960998535156</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">113.088836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">110.472396850586</t>
+    <t xml:space="preserve">110.472389221191</t>
   </si>
   <si>
     <t xml:space="preserve">108.825004577637</t>
   </si>
   <si>
-    <t xml:space="preserve">115.414573669434</t>
+    <t xml:space="preserve">115.414581298828</t>
   </si>
   <si>
     <t xml:space="preserve">109.987861633301</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">113.670280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">118.1279296875</t>
+    <t xml:space="preserve">118.127937316895</t>
   </si>
   <si>
     <t xml:space="preserve">114.154808044434</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">119.193901062012</t>
   </si>
   <si>
-    <t xml:space="preserve">119.09700012207</t>
+    <t xml:space="preserve">119.096992492676</t>
   </si>
   <si>
     <t xml:space="preserve">119.678428649902</t>
@@ -3767,16 +3767,16 @@
     <t xml:space="preserve">110.569297790527</t>
   </si>
   <si>
-    <t xml:space="preserve">110.956924438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.921905517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.952850341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.565223693848</t>
+    <t xml:space="preserve">110.956916809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.921913146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.952842712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.565231323242</t>
   </si>
   <si>
     <t xml:space="preserve">105.045684814453</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">104.754959106445</t>
   </si>
   <si>
-    <t xml:space="preserve">105.724021911621</t>
+    <t xml:space="preserve">105.724014282227</t>
   </si>
   <si>
     <t xml:space="preserve">103.592094421387</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">103.107566833496</t>
   </si>
   <si>
-    <t xml:space="preserve">104.561149597168</t>
+    <t xml:space="preserve">104.561157226562</t>
   </si>
   <si>
     <t xml:space="preserve">107.37141418457</t>
@@ -3827,10 +3827,10 @@
     <t xml:space="preserve">116.480545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">115.705291748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.379570007324</t>
+    <t xml:space="preserve">115.705299377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.37956237793</t>
   </si>
   <si>
     <t xml:space="preserve">112.798126220703</t>
@@ -3848,13 +3848,13 @@
     <t xml:space="preserve">109.115715026855</t>
   </si>
   <si>
-    <t xml:space="preserve">110.278579711914</t>
+    <t xml:space="preserve">110.278587341309</t>
   </si>
   <si>
     <t xml:space="preserve">109.697143554688</t>
   </si>
   <si>
-    <t xml:space="preserve">102.235420227051</t>
+    <t xml:space="preserve">102.235412597656</t>
   </si>
   <si>
     <t xml:space="preserve">102.623046875</t>
@@ -3878,22 +3878,22 @@
     <t xml:space="preserve">100.006591796875</t>
   </si>
   <si>
-    <t xml:space="preserve">99.4251480102539</t>
+    <t xml:space="preserve">99.4251556396484</t>
   </si>
   <si>
     <t xml:space="preserve">101.26636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">101.653984069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.39421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.328239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6189727783203</t>
+    <t xml:space="preserve">101.65397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.394203186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3282470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6189651489258</t>
   </si>
   <si>
     <t xml:space="preserve">99.2313385009766</t>
@@ -5300,7 +5300,7 @@
     <t xml:space="preserve">92.1999969482422</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4000015258789</t>
+    <t xml:space="preserve">93.9499969482422</t>
   </si>
 </sst>
 </file>
@@ -71757,10 +71757,10 @@
     </row>
     <row r="2544">
       <c r="A2544" s="1" t="n">
-        <v>46028.686875</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B2544" t="n">
-        <v>29922</v>
+        <v>33626</v>
       </c>
       <c r="C2544" t="n">
         <v>93.3000030517578</v>
@@ -71772,12 +71772,38 @@
         <v>91.9499969482422</v>
       </c>
       <c r="F2544" t="n">
-        <v>92.4000015258789</v>
+        <v>92.1500015258789</v>
       </c>
       <c r="G2544" t="s">
+        <v>1708</v>
+      </c>
+      <c r="H2544" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" s="1" t="n">
+        <v>46029.6937731481</v>
+      </c>
+      <c r="B2545" t="n">
+        <v>64169</v>
+      </c>
+      <c r="C2545" t="n">
+        <v>94.3000030517578</v>
+      </c>
+      <c r="D2545" t="n">
+        <v>92</v>
+      </c>
+      <c r="E2545" t="n">
+        <v>92</v>
+      </c>
+      <c r="F2545" t="n">
+        <v>93.9499969482422</v>
+      </c>
+      <c r="G2545" t="s">
         <v>1762</v>
       </c>
-      <c r="H2544" t="s">
+      <c r="H2545" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="1766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="1767">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -53,52 +53,52 @@
     <t xml:space="preserve">12.9464159011841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1125059127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8589992523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0513143539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.990122795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9376745223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1037654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.025089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8502559661865</t>
+    <t xml:space="preserve">13.1125068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8589973449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0513153076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9901218414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9376735687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1037645339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0250902175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8502569198608</t>
   </si>
   <si>
     <t xml:space="preserve">12.2383403778076</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5880079269409</t>
+    <t xml:space="preserve">12.5880060195923</t>
   </si>
   <si>
     <t xml:space="preserve">12.7890653610229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7191314697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6841659545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6054906845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3257570266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0460233688354</t>
+    <t xml:space="preserve">12.7191305160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6841650009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6054916381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.325756072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0460224151611</t>
   </si>
   <si>
     <t xml:space="preserve">12.1771478652954</t>
@@ -107,73 +107,73 @@
     <t xml:space="preserve">12.1421823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9270906448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9795398712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3641729354858</t>
+    <t xml:space="preserve">10.9270887374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9795389175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3641719818115</t>
   </si>
   <si>
     <t xml:space="preserve">11.4515895843506</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0984745025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1072158813477</t>
+    <t xml:space="preserve">12.0984725952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1072149276733</t>
   </si>
   <si>
     <t xml:space="preserve">11.8886737823486</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760904312134</t>
+    <t xml:space="preserve">11.9760894775391</t>
   </si>
   <si>
     <t xml:space="preserve">11.9323806762695</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0110559463501</t>
+    <t xml:space="preserve">12.0110578536987</t>
   </si>
   <si>
     <t xml:space="preserve">12.0809888839722</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8012561798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334390640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8274803161621</t>
+    <t xml:space="preserve">11.8012552261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334400177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8274822235107</t>
   </si>
   <si>
     <t xml:space="preserve">12.0635070800781</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5005893707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.675422668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7978057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1649570465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1562166213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0687980651855</t>
+    <t xml:space="preserve">12.5005903244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6754236221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7978076934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1649560928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1562156677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0687999725342</t>
   </si>
   <si>
     <t xml:space="preserve">13.1212491989136</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1911821365356</t>
+    <t xml:space="preserve">13.1911811828613</t>
   </si>
   <si>
     <t xml:space="preserve">12.7540979385376</t>
@@ -182,55 +182,55 @@
     <t xml:space="preserve">12.8939647674561</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9027061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0600566864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1999225616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9813833236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4534330368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7069396972656</t>
+    <t xml:space="preserve">12.9027080535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0600557327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1999244689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9813814163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4534320831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7069406509399</t>
   </si>
   <si>
     <t xml:space="preserve">13.4709148406982</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4621734619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2086658477783</t>
+    <t xml:space="preserve">13.4621715545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.208664894104</t>
   </si>
   <si>
     <t xml:space="preserve">13.3223075866699</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0950222015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9988660812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.640456199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4481401443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3782062530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0285406112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1509237289429</t>
+    <t xml:space="preserve">13.0950231552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9988651275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6404552459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4481372833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3782072067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0285396575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1509227752686</t>
   </si>
   <si>
     <t xml:space="preserve">12.4393978118896</t>
@@ -239,13 +239,13 @@
     <t xml:space="preserve">12.5617818832397</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5268135070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6317138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3694658279419</t>
+    <t xml:space="preserve">12.5268154144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6317148208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3694639205933</t>
   </si>
   <si>
     <t xml:space="preserve">12.7715816497803</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">12.2820491790771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1946315765381</t>
+    <t xml:space="preserve">12.1946325302124</t>
   </si>
   <si>
     <t xml:space="preserve">12.2470817565918</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">12.4131727218628</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5093307495117</t>
+    <t xml:space="preserve">12.509331703186</t>
   </si>
   <si>
     <t xml:space="preserve">12.3869485855103</t>
@@ -275,28 +275,28 @@
     <t xml:space="preserve">11.8187408447266</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8449640274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.255823135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5792655944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2208557128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1858892440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7803220748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7278728485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8764810562134</t>
+    <t xml:space="preserve">11.8449649810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2558250427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5792665481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2208566665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1858901977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7803239822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7278738021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8764820098877</t>
   </si>
   <si>
     <t xml:space="preserve">12.806547164917</t>
@@ -314,196 +314,196 @@
     <t xml:space="preserve">12.5355577468872</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1824388504028</t>
+    <t xml:space="preserve">13.1824378967285</t>
   </si>
   <si>
     <t xml:space="preserve">13.0338325500488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3048238754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.261116027832</t>
+    <t xml:space="preserve">13.3048229217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2611141204834</t>
   </si>
   <si>
     <t xml:space="preserve">13.3747577667236</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6020412445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6894559860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7244243621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7514772415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5711307525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8687009811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6252336502075</t>
+    <t xml:space="preserve">13.6020402908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6894588470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7244234085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7514753341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5711297988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8687028884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6252317428589</t>
   </si>
   <si>
     <t xml:space="preserve">13.6432685852051</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6613035202026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.598180770874</t>
+    <t xml:space="preserve">13.6613025665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5981798171997</t>
   </si>
   <si>
     <t xml:space="preserve">13.6162157058716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5260410308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5530939102173</t>
+    <t xml:space="preserve">13.5260419845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5530948638916</t>
   </si>
   <si>
     <t xml:space="preserve">13.3456954956055</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5801467895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6973724365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7785263061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6703186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7965631484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9769105911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0400314331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0129804611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9047698974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1031532287598</t>
+    <t xml:space="preserve">13.5801448822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6973705291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7785272598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6703205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7965621948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9769096374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0400323867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0129776000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9047718048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1031541824341</t>
   </si>
   <si>
     <t xml:space="preserve">14.2474298477173</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1572580337524</t>
+    <t xml:space="preserve">14.1572570800781</t>
   </si>
   <si>
     <t xml:space="preserve">14.3646564483643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4187602996826</t>
+    <t xml:space="preserve">14.4187612533569</t>
   </si>
   <si>
     <t xml:space="preserve">14.517951965332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6081247329712</t>
+    <t xml:space="preserve">14.6081256866455</t>
   </si>
   <si>
     <t xml:space="preserve">14.6622295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3917102813721</t>
+    <t xml:space="preserve">14.3917083740234</t>
   </si>
   <si>
     <t xml:space="preserve">14.3105516433716</t>
   </si>
   <si>
-    <t xml:space="preserve">14.30153465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5450029373169</t>
+    <t xml:space="preserve">14.3015356063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5450038909912</t>
   </si>
   <si>
     <t xml:space="preserve">14.644193649292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7343673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7163333892822</t>
+    <t xml:space="preserve">14.7343683242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7163324356079</t>
   </si>
   <si>
     <t xml:space="preserve">14.6351766586304</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6261587142944</t>
+    <t xml:space="preserve">14.6261577606201</t>
   </si>
   <si>
     <t xml:space="preserve">14.6892824172974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8245420455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8065090179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7433862686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5810747146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6982975006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5089340209961</t>
+    <t xml:space="preserve">14.8245429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8065061569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.74338722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.581072807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6982984542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5089330673218</t>
   </si>
   <si>
     <t xml:space="preserve">14.6712465286255</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6532125473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.923731803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.049976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.212290763855</t>
+    <t xml:space="preserve">14.6532135009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9237308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0499773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2122898101807</t>
   </si>
   <si>
     <t xml:space="preserve">15.3746004104614</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5549468994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9246587753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7803821563721</t>
+    <t xml:space="preserve">15.554949760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9246597290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7803802490234</t>
   </si>
   <si>
     <t xml:space="preserve">15.8705577850342</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8344879150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7082462310791</t>
+    <t xml:space="preserve">15.8344869613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7082452774048</t>
   </si>
   <si>
     <t xml:space="preserve">15.9517126083374</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">16.8714828491211</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0879001617432</t>
+    <t xml:space="preserve">17.0879020690918</t>
   </si>
   <si>
     <t xml:space="preserve">17.1510219573975</t>
@@ -524,40 +524,40 @@
     <t xml:space="preserve">17.2231616973877</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9796886444092</t>
+    <t xml:space="preserve">16.9796924591064</t>
   </si>
   <si>
     <t xml:space="preserve">16.9075527191162</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3043174743652</t>
+    <t xml:space="preserve">17.3043155670166</t>
   </si>
   <si>
     <t xml:space="preserve">17.0337963104248</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2772655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4756469726562</t>
+    <t xml:space="preserve">17.2772636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4756450653076</t>
   </si>
   <si>
     <t xml:space="preserve">17.3223495483398</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1690578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5838527679443</t>
+    <t xml:space="preserve">17.1690559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.583854675293</t>
   </si>
   <si>
     <t xml:space="preserve">17.5748348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5658206939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2411937713623</t>
+    <t xml:space="preserve">17.5658187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2411956787109</t>
   </si>
   <si>
     <t xml:space="preserve">17.1870918273926</t>
@@ -566,46 +566,46 @@
     <t xml:space="preserve">16.8534469604492</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8444309234619</t>
+    <t xml:space="preserve">16.8444328308105</t>
   </si>
   <si>
     <t xml:space="preserve">16.9526386260986</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7272033691406</t>
+    <t xml:space="preserve">16.7272052764893</t>
   </si>
   <si>
     <t xml:space="preserve">16.6911354064941</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8624668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0428123474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8173751831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9977264404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7722949981689</t>
+    <t xml:space="preserve">16.8624687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0428104400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8173789978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9977283477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7722930908203</t>
   </si>
   <si>
     <t xml:space="preserve">17.006742477417</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1961040496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3584213256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6199245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7641983032227</t>
+    <t xml:space="preserve">17.1961059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.358419418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6199264526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7642021179199</t>
   </si>
   <si>
     <t xml:space="preserve">18.0076694488525</t>
@@ -617,19 +617,19 @@
     <t xml:space="preserve">17.9445476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9535636901855</t>
+    <t xml:space="preserve">17.9535675048828</t>
   </si>
   <si>
     <t xml:space="preserve">17.809289932251</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2601566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7561092376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8462829589844</t>
+    <t xml:space="preserve">18.2601547241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7561111450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8462867736816</t>
   </si>
   <si>
     <t xml:space="preserve">18.9364585876465</t>
@@ -641,19 +641,19 @@
     <t xml:space="preserve">19.2971515655518</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3602733612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3512535095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.666862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6488304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5586585998535</t>
+    <t xml:space="preserve">19.3602752685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3512554168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6668643951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6488285064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5586566925049</t>
   </si>
   <si>
     <t xml:space="preserve">19.252067565918</t>
@@ -662,19 +662,19 @@
     <t xml:space="preserve">19.1709098815918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.134838104248</t>
+    <t xml:space="preserve">19.1348419189453</t>
   </si>
   <si>
     <t xml:space="preserve">19.1979637145996</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9544944763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9094047546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0897541046143</t>
+    <t xml:space="preserve">18.9544925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9094085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0897521972656</t>
   </si>
   <si>
     <t xml:space="preserve">18.5757637023926</t>
@@ -683,46 +683,46 @@
     <t xml:space="preserve">18.1970348358154</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5306758880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8372688293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4594650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3873252868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0185432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3612041473389</t>
+    <t xml:space="preserve">18.5306797027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8372669219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4594669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3873271942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0185394287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3612022399902</t>
   </si>
   <si>
     <t xml:space="preserve">20.8301048278809</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2809715270996</t>
+    <t xml:space="preserve">21.280969619751</t>
   </si>
   <si>
     <t xml:space="preserve">20.8751907348633</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9292964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1006259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0104522705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5686016082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7218952178955</t>
+    <t xml:space="preserve">20.9292945861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.100622177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0104503631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5685997009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7218971252441</t>
   </si>
   <si>
     <t xml:space="preserve">20.6046714782715</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">20.1898727416992</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3792362213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6497535705566</t>
+    <t xml:space="preserve">20.3792381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6497554779053</t>
   </si>
   <si>
     <t xml:space="preserve">21.6416683197021</t>
@@ -743,13 +743,13 @@
     <t xml:space="preserve">21.3711471557617</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3801593780518</t>
+    <t xml:space="preserve">21.3801612854004</t>
   </si>
   <si>
     <t xml:space="preserve">22.0925350189209</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6245594024658</t>
+    <t xml:space="preserve">22.6245574951172</t>
   </si>
   <si>
     <t xml:space="preserve">22.7147350311279</t>
@@ -758,28 +758,28 @@
     <t xml:space="preserve">22.8049068450928</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5984344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0763549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0583209991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7156581878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9320793151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8599395751953</t>
+    <t xml:space="preserve">23.5984306335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0763568878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0583229064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7156600952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9320774078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8599376678467</t>
   </si>
   <si>
     <t xml:space="preserve">23.8058319091797</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5082626342773</t>
+    <t xml:space="preserve">23.5082607269287</t>
   </si>
   <si>
     <t xml:space="preserve">22.994270324707</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">22.480281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5434055328369</t>
+    <t xml:space="preserve">22.5434036254883</t>
   </si>
   <si>
     <t xml:space="preserve">22.705717086792</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">22.4532299041748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4622478485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0023612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1827068328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7237529754639</t>
+    <t xml:space="preserve">22.4622459411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0023593902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.182710647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7237510681152</t>
   </si>
   <si>
     <t xml:space="preserve">22.3630542755127</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">21.4883728027344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9212036132812</t>
+    <t xml:space="preserve">21.9212055206299</t>
   </si>
   <si>
     <t xml:space="preserve">21.8761177062988</t>
@@ -827,43 +827,43 @@
     <t xml:space="preserve">21.7047901153564</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9392414093018</t>
+    <t xml:space="preserve">21.9392395019531</t>
   </si>
   <si>
     <t xml:space="preserve">22.0745010375977</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2999324798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8139228820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3179683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1917285919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3540420532227</t>
+    <t xml:space="preserve">22.299934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8139247894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3179702758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1917266845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3540382385254</t>
   </si>
   <si>
     <t xml:space="preserve">22.525369644165</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6065273284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6335792541504</t>
+    <t xml:space="preserve">22.6065254211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6335773468018</t>
   </si>
   <si>
     <t xml:space="preserve">22.2458305358887</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2277984619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1286029815674</t>
+    <t xml:space="preserve">22.2277965545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1286067962646</t>
   </si>
   <si>
     <t xml:space="preserve">22.0835189819336</t>
@@ -872,55 +872,55 @@
     <t xml:space="preserve">22.2007446289062</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1376190185547</t>
+    <t xml:space="preserve">22.1376209259033</t>
   </si>
   <si>
     <t xml:space="preserve">22.1466369628906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5965824127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3260612487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.560510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0294151306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6867542266846</t>
+    <t xml:space="preserve">21.5965805053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3260593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5605125427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0294132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6867523193359</t>
   </si>
   <si>
     <t xml:space="preserve">22.2368125915527</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3720741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3991260528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6155433654785</t>
+    <t xml:space="preserve">22.3720722198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3991241455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6155414581299</t>
   </si>
   <si>
     <t xml:space="preserve">22.6606254577637</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0123081207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5193881988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2704582214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1739826202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7087268829346</t>
+    <t xml:space="preserve">23.0123062133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5193901062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2704563140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1739845275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7087249755859</t>
   </si>
   <si>
     <t xml:space="preserve">24.773265838623</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">25.243465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8150863647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7966461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6860103607178</t>
+    <t xml:space="preserve">25.8150882720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7966480255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6860122680664</t>
   </si>
   <si>
     <t xml:space="preserve">25.6675720214844</t>
@@ -947,40 +947,40 @@
     <t xml:space="preserve">25.888843536377</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9810428619385</t>
+    <t xml:space="preserve">25.9810409545898</t>
   </si>
   <si>
     <t xml:space="preserve">26.0916748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9072818756104</t>
+    <t xml:space="preserve">25.907283782959</t>
   </si>
   <si>
     <t xml:space="preserve">25.8058662414551</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9533805847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6767921447754</t>
+    <t xml:space="preserve">25.9533824920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6767902374268</t>
   </si>
   <si>
     <t xml:space="preserve">25.6583518981934</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0775146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4001998901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2619037628174</t>
+    <t xml:space="preserve">25.0775127410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4002017974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.261905670166</t>
   </si>
   <si>
     <t xml:space="preserve">25.3264427185059</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8009243011475</t>
+    <t xml:space="preserve">24.8009204864502</t>
   </si>
   <si>
     <t xml:space="preserve">25.4186401367188</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">24.6441879272461</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8562393188477</t>
+    <t xml:space="preserve">24.8562412261963</t>
   </si>
   <si>
     <t xml:space="preserve">24.9576549530029</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8931179046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.187479019165</t>
+    <t xml:space="preserve">24.8931198120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1874809265137</t>
   </si>
   <si>
     <t xml:space="preserve">22.9754257202148</t>
@@ -1007,19 +1007,19 @@
     <t xml:space="preserve">23.1229419708252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2335796356201</t>
+    <t xml:space="preserve">23.2335777282715</t>
   </si>
   <si>
     <t xml:space="preserve">22.9938678741455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0123062133789</t>
+    <t xml:space="preserve">23.0123043060303</t>
   </si>
   <si>
     <t xml:space="preserve">22.7818126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6711807250977</t>
+    <t xml:space="preserve">22.671178817749</t>
   </si>
   <si>
     <t xml:space="preserve">22.4960021972656</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">22.7264976501465</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5052223205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3208293914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5881996154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1137199401855</t>
+    <t xml:space="preserve">22.5052242279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3208274841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5882015228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1137218475342</t>
   </si>
   <si>
     <t xml:space="preserve">22.910888671875</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">23.3995304107666</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7775363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6208076477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1413841247559</t>
+    <t xml:space="preserve">23.7775402069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6208038330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1413822174072</t>
   </si>
   <si>
     <t xml:space="preserve">22.9846477508545</t>
@@ -1067,79 +1067,79 @@
     <t xml:space="preserve">22.6896152496338</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3257732391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7406597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9803714752197</t>
+    <t xml:space="preserve">23.325777053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7406616210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9803733825684</t>
   </si>
   <si>
     <t xml:space="preserve">23.9711513519287</t>
   </si>
   <si>
-    <t xml:space="preserve">24.063346862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2477416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3860378265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1555500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6165313720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8611869812012</t>
+    <t xml:space="preserve">24.0633506774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2477397918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3860397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1555461883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6165294647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8611850738525</t>
   </si>
   <si>
     <t xml:space="preserve">25.6306953430176</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2158107757568</t>
+    <t xml:space="preserve">25.2158069610596</t>
   </si>
   <si>
     <t xml:space="preserve">25.1697101593018</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3080024719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4463005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5384998321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1236114501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4321365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6484622955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0172481536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1094493865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3399410247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2016429901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2938423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.754825592041</t>
+    <t xml:space="preserve">25.3080062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4462985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5384960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1236095428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4321346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6484642028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0172538757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1094436645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.339937210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2016448974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2938404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7548274993896</t>
   </si>
   <si>
     <t xml:space="preserve">24.6626262664795</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">24.985315322876</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4923973083496</t>
+    <t xml:space="preserve">25.4923992156982</t>
   </si>
   <si>
     <t xml:space="preserve">25.7228889465332</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5704307556152</t>
+    <t xml:space="preserve">24.5704288482666</t>
   </si>
   <si>
     <t xml:space="preserve">25.5845947265625</t>
@@ -1169,19 +1169,19 @@
     <t xml:space="preserve">27.5668239593506</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7512168884277</t>
+    <t xml:space="preserve">27.7512187957764</t>
   </si>
   <si>
     <t xml:space="preserve">28.0739059448242</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5207290649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7370510101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5065631866455</t>
+    <t xml:space="preserve">27.5207271575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7370529174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5065650939941</t>
   </si>
   <si>
     <t xml:space="preserve">25.0314140319824</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">24.5243339538574</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3682651519775</t>
+    <t xml:space="preserve">26.3682670593262</t>
   </si>
   <si>
     <t xml:space="preserve">26.5987606048584</t>
@@ -1199,16 +1199,16 @@
     <t xml:space="preserve">26.4604663848877</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2299728393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3221664428711</t>
+    <t xml:space="preserve">26.2299709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3221683502197</t>
   </si>
   <si>
     <t xml:space="preserve">27.1980381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2760696411133</t>
+    <t xml:space="preserve">26.2760715484619</t>
   </si>
   <si>
     <t xml:space="preserve">27.2902355194092</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">26.5526599884033</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8292484283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1058406829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8753509521484</t>
+    <t xml:space="preserve">26.829252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1058387756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8753490447998</t>
   </si>
   <si>
     <t xml:space="preserve">27.8434143066406</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">28.7653827667236</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5809898376465</t>
+    <t xml:space="preserve">28.5809879302979</t>
   </si>
   <si>
     <t xml:space="preserve">27.9356117248535</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">28.8114795684814</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1661014556885</t>
+    <t xml:space="preserve">28.1661033630371</t>
   </si>
   <si>
     <t xml:space="preserve">28.7192840576172</t>
@@ -1259,49 +1259,49 @@
     <t xml:space="preserve">27.0597438812256</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9675483703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1519412994385</t>
+    <t xml:space="preserve">26.9675445556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1519432067871</t>
   </si>
   <si>
     <t xml:space="preserve">26.6909561157227</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7831516265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0455799102783</t>
+    <t xml:space="preserve">26.7831554412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0455780029297</t>
   </si>
   <si>
     <t xml:space="preserve">27.6590213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9214496612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1828804016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0886993408203</t>
+    <t xml:space="preserve">26.9214515686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1828784942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0886974334717</t>
   </si>
   <si>
     <t xml:space="preserve">26.4654293060303</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2299709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8061447143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7119655609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1468677520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3352336883545</t>
+    <t xml:space="preserve">26.2299690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8061485290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7119636535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1468658447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3352317810059</t>
   </si>
   <si>
     <t xml:space="preserve">24.9114112854004</t>
@@ -1313,88 +1313,88 @@
     <t xml:space="preserve">24.3934020996094</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9224872589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2632083892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0277481079102</t>
+    <t xml:space="preserve">23.9224891662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2632064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0277500152588</t>
   </si>
   <si>
     <t xml:space="preserve">23.0748405456543</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7451992034912</t>
+    <t xml:space="preserve">22.7451972961426</t>
   </si>
   <si>
     <t xml:space="preserve">22.6039237976074</t>
   </si>
   <si>
-    <t xml:space="preserve">22.509744644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4155597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.180103302002</t>
+    <t xml:space="preserve">22.5097427368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4155578613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1801013946533</t>
   </si>
   <si>
     <t xml:space="preserve">22.0388259887695</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8504657745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4626502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2271938323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4044780731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2161159515381</t>
+    <t xml:space="preserve">21.8504619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4626522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2271919250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4044799804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2161140441895</t>
   </si>
   <si>
     <t xml:space="preserve">22.886474609375</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4986629486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5568332672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1330089569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6620941162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1911792755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0028114318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.096996307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8615379333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3795471191406</t>
+    <t xml:space="preserve">23.4986667633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5568351745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1330108642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6620922088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.19118309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.002815246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0970001220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8615398406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.379545211792</t>
   </si>
   <si>
     <t xml:space="preserve">21.4737281799316</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2742862701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7562808990479</t>
+    <t xml:space="preserve">22.2742824554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7562770843506</t>
   </si>
   <si>
     <t xml:space="preserve">21.9446449279785</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">21.5679111480713</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5208206176758</t>
+    <t xml:space="preserve">21.5208187103271</t>
   </si>
   <si>
     <t xml:space="preserve">21.3324546813965</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">21.2382698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8393821716309</t>
+    <t xml:space="preserve">22.8393840789795</t>
   </si>
   <si>
     <t xml:space="preserve">22.792293548584</t>
@@ -1421,58 +1421,58 @@
     <t xml:space="preserve">23.5457572937012</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6399402618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7341213226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6870288848877</t>
+    <t xml:space="preserve">23.6399383544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7341232299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6870307922363</t>
   </si>
   <si>
     <t xml:space="preserve">23.781213760376</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0166702270508</t>
+    <t xml:space="preserve">24.0166721343994</t>
   </si>
   <si>
     <t xml:space="preserve">24.2992191314697</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1579456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2521305084229</t>
+    <t xml:space="preserve">24.1579437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2521286010742</t>
   </si>
   <si>
     <t xml:space="preserve">24.7230434417725</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6288623809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.675952911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5817680358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7701320648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9584999084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9003295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7590599060059</t>
+    <t xml:space="preserve">24.6288585662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6759510040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5817718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.770133972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9585018157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9003314971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7590579986572</t>
   </si>
   <si>
     <t xml:space="preserve">25.9474220275879</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2770614624023</t>
+    <t xml:space="preserve">26.277063369751</t>
   </si>
   <si>
     <t xml:space="preserve">26.9363441467285</t>
@@ -1493,76 +1493,76 @@
     <t xml:space="preserve">27.4543514251709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.501443862915</t>
+    <t xml:space="preserve">27.5014457702637</t>
   </si>
   <si>
     <t xml:space="preserve">27.3130760192871</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0776195526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7008857727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6537952423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6067047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.994514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1357879638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0416030883789</t>
+    <t xml:space="preserve">27.0776176452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7008876800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6537971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6067028045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9945125579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1357898712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0416049957275</t>
   </si>
   <si>
     <t xml:space="preserve">25.6177825927734</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4294128417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0055904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0997753143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8643169403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4404945373535</t>
+    <t xml:space="preserve">25.4294166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0055885314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0997734069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.864315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4404964447021</t>
   </si>
   <si>
     <t xml:space="preserve">25.5235977172852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3712463378906</t>
+    <t xml:space="preserve">26.3712482452393</t>
   </si>
   <si>
     <t xml:space="preserve">26.3241558074951</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7950706481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8892498016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0305309295654</t>
+    <t xml:space="preserve">26.795072555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8892517089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0305290222168</t>
   </si>
   <si>
     <t xml:space="preserve">27.171802520752</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5485363006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6898097991943</t>
+    <t xml:space="preserve">27.5485343933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6898078918457</t>
   </si>
   <si>
     <t xml:space="preserve">28.1136322021484</t>
@@ -1574,73 +1574,73 @@
     <t xml:space="preserve">28.7258224487305</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9141864776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9502010345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.761833190918</t>
+    <t xml:space="preserve">28.9141883850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9501991271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7618350982666</t>
   </si>
   <si>
     <t xml:space="preserve">30.3269348144531</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5042190551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6925926208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4460487365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4931411743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.482063293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6704330444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2936973571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.576244354248</t>
+    <t xml:space="preserve">30.3740253448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5042247772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6925868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.446044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4931449890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4820671081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6704292297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.293701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5762519836426</t>
   </si>
   <si>
     <t xml:space="preserve">33.9058876037598</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2466049194336</t>
+    <t xml:space="preserve">33.2466087341309</t>
   </si>
   <si>
     <t xml:space="preserve">32.8698768615723</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1524238586426</t>
+    <t xml:space="preserve">33.1524200439453</t>
   </si>
   <si>
     <t xml:space="preserve">33.0582389831543</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5873184204102</t>
+    <t xml:space="preserve">32.5873260498047</t>
   </si>
   <si>
     <t xml:space="preserve">32.3047790527344</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9280471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4571342468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3629455566406</t>
+    <t xml:space="preserve">31.9280452728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4571304321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.362943649292</t>
   </si>
   <si>
     <t xml:space="preserve">30.8920307159424</t>
@@ -1649,19 +1649,19 @@
     <t xml:space="preserve">31.0803985595703</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0333080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6565742492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6094818115234</t>
+    <t xml:space="preserve">31.0333042144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6565723419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6094856262207</t>
   </si>
   <si>
     <t xml:space="preserve">31.2687644958496</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9862194061279</t>
+    <t xml:space="preserve">30.9862155914307</t>
   </si>
   <si>
     <t xml:space="preserve">31.4100341796875</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">31.8809547424316</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0222244262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7396812438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0000686645508</t>
+    <t xml:space="preserve">32.0222282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7396755218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.000072479248</t>
   </si>
   <si>
     <t xml:space="preserve">34.4709892272949</t>
@@ -1691,31 +1691,31 @@
     <t xml:space="preserve">35.78955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5901031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7784729003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1552047729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6732063293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0846786499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.228214263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.367000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7976036071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1803703308105</t>
+    <t xml:space="preserve">36.5900993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7784690856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.155200958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6732025146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0846748352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2282066345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3669967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.797607421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1803665161133</t>
   </si>
   <si>
     <t xml:space="preserve">38.3717460632324</t>
@@ -1727,13 +1727,13 @@
     <t xml:space="preserve">37.9889869689941</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8454475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3191604614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8501968383789</t>
+    <t xml:space="preserve">37.8454513549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3191566467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8502006530762</t>
   </si>
   <si>
     <t xml:space="preserve">38.7545051574707</t>
@@ -1745,13 +1745,13 @@
     <t xml:space="preserve">39.041576385498</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8023529052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4674377441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1325187683105</t>
+    <t xml:space="preserve">38.8023490905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4674339294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1325225830078</t>
   </si>
   <si>
     <t xml:space="preserve">38.8980445861816</t>
@@ -1766,46 +1766,46 @@
     <t xml:space="preserve">38.5631256103516</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4195976257324</t>
+    <t xml:space="preserve">38.4195938110352</t>
   </si>
   <si>
     <t xml:space="preserve">39.3764915466309</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1372680664062</t>
+    <t xml:space="preserve">39.1372718811035</t>
   </si>
   <si>
     <t xml:space="preserve">39.185115814209</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2808036804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9027938842773</t>
+    <t xml:space="preserve">39.2807998657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9027900695801</t>
   </si>
   <si>
     <t xml:space="preserve">41.1946067810059</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1036643981934</t>
+    <t xml:space="preserve">42.1036605834961</t>
   </si>
   <si>
     <t xml:space="preserve">42.5342674255371</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6730537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8118438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7161483764648</t>
+    <t xml:space="preserve">41.6730575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8118476867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7161560058594</t>
   </si>
   <si>
     <t xml:space="preserve">41.912281036377</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0605621337891</t>
+    <t xml:space="preserve">43.0605659484863</t>
   </si>
   <si>
     <t xml:space="preserve">43.4911689758301</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">44.017463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6347007751465</t>
+    <t xml:space="preserve">43.634708404541</t>
   </si>
   <si>
     <t xml:space="preserve">43.2041015625</t>
@@ -1838,13 +1838,13 @@
     <t xml:space="preserve">45.404972076416</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2614402770996</t>
+    <t xml:space="preserve">45.2614326477051</t>
   </si>
   <si>
     <t xml:space="preserve">45.5963516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6536865234375</t>
+    <t xml:space="preserve">47.6536903381348</t>
   </si>
   <si>
     <t xml:space="preserve">48.8976593017578</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">48.6105918884277</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1847381591797</t>
+    <t xml:space="preserve">49.1847343444824</t>
   </si>
   <si>
     <t xml:space="preserve">48.993350982666</t>
@@ -1865,19 +1865,19 @@
     <t xml:space="preserve">49.2804260253906</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6631851196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3761100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5674934387207</t>
+    <t xml:space="preserve">49.6631813049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3761138916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5674896240234</t>
   </si>
   <si>
     <t xml:space="preserve">50.6200866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0028457641602</t>
+    <t xml:space="preserve">51.0028419494629</t>
   </si>
   <si>
     <t xml:space="preserve">52.7252655029297</t>
@@ -1886,40 +1886,40 @@
     <t xml:space="preserve">52.6295776367188</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9597473144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8640556335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6726722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4192085266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3235206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0459442138672</t>
+    <t xml:space="preserve">51.9597434997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8640594482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6726760864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4192047119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3235244750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0459403991699</t>
   </si>
   <si>
     <t xml:space="preserve">51.3856086730957</t>
   </si>
   <si>
-    <t xml:space="preserve">50.907154083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8545608520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4287071228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5338859558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0649337768555</t>
+    <t xml:space="preserve">50.9071578979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.854564666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5338935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0649261474609</t>
   </si>
   <si>
     <t xml:space="preserve">53.2994079589844</t>
@@ -1934,13 +1934,13 @@
     <t xml:space="preserve">46.9838562011719</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3618774414062</t>
+    <t xml:space="preserve">46.361873626709</t>
   </si>
   <si>
     <t xml:space="preserve">45.7398872375488</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9743614196777</t>
+    <t xml:space="preserve">44.974365234375</t>
   </si>
   <si>
     <t xml:space="preserve">43.5868606567383</t>
@@ -1949,37 +1949,37 @@
     <t xml:space="preserve">41.7687454223633</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6493263244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5967330932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0945491790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4820613861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1854953765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5299034118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0992965698242</t>
+    <t xml:space="preserve">36.6493225097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.596736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0945510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4820556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1854934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5299053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0992984771729</t>
   </si>
   <si>
     <t xml:space="preserve">30.3816204071045</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9269027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.410099029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5010414123535</t>
+    <t xml:space="preserve">34.9268989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4100952148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5010375976562</t>
   </si>
   <si>
     <t xml:space="preserve">35.3096656799316</t>
@@ -1988,34 +1988,34 @@
     <t xml:space="preserve">34.5441398620605</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0704345703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0799331665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2234687805176</t>
+    <t xml:space="preserve">35.0704383850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0799293518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2234649658203</t>
   </si>
   <si>
     <t xml:space="preserve">37.1277732849121</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2329597473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.429084777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.998477935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7351379394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9791069030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4528198242188</t>
+    <t xml:space="preserve">39.2329559326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4290809631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9984817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7351417541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9791145324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4528160095215</t>
   </si>
   <si>
     <t xml:space="preserve">45.0700569152832</t>
@@ -2024,58 +2024,58 @@
     <t xml:space="preserve">45.3571281433105</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1179046630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4575614929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6441955566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8786735534668</t>
+    <t xml:space="preserve">45.1179008483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4575653076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6441993713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8786773681641</t>
   </si>
   <si>
     <t xml:space="preserve">45.3092803955078</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1657485961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2088470458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1562538146973</t>
+    <t xml:space="preserve">45.1657447814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2088432312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.15625</t>
   </si>
   <si>
     <t xml:space="preserve">43.9217758178711</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8644371032715</t>
+    <t xml:space="preserve">41.8644332885742</t>
   </si>
   <si>
     <t xml:space="preserve">42.5821151733398</t>
   </si>
   <si>
-    <t xml:space="preserve">45.022216796875</t>
+    <t xml:space="preserve">45.0222053527832</t>
   </si>
   <si>
     <t xml:space="preserve">45.5485038757324</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5101585388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7015342712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7062835693359</t>
+    <t xml:space="preserve">47.5101547241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.701530456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7062797546387</t>
   </si>
   <si>
     <t xml:space="preserve">47.9407577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5149040222168</t>
+    <t xml:space="preserve">48.5149002075195</t>
   </si>
   <si>
     <t xml:space="preserve">51.4812965393066</t>
@@ -2084,34 +2084,34 @@
     <t xml:space="preserve">51.1942253112793</t>
   </si>
   <si>
-    <t xml:space="preserve">51.768367767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2899169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1080322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9692420959473</t>
+    <t xml:space="preserve">51.7683601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2899131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1080284118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9692459106445</t>
   </si>
   <si>
     <t xml:space="preserve">53.4907913208008</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1175231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6916618347168</t>
+    <t xml:space="preserve">55.1175270080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6916656494141</t>
   </si>
   <si>
     <t xml:space="preserve">55.5002784729004</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3520011901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6390647888184</t>
+    <t xml:space="preserve">54.3519973754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6390724182129</t>
   </si>
   <si>
     <t xml:space="preserve">54.8304481506348</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">55.4045944213867</t>
   </si>
   <si>
-    <t xml:space="preserve">56.7442512512207</t>
+    <t xml:space="preserve">56.7442474365234</t>
   </si>
   <si>
     <t xml:space="preserve">56.9356346130371</t>
@@ -2129,37 +2129,37 @@
     <t xml:space="preserve">57.1270179748535</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2658042907715</t>
+    <t xml:space="preserve">56.2658004760742</t>
   </si>
   <si>
     <t xml:space="preserve">55.9787330627441</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3183975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6580543518066</t>
+    <t xml:space="preserve">57.3183937072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6580581665039</t>
   </si>
   <si>
     <t xml:space="preserve">57.2227058410645</t>
   </si>
   <si>
-    <t xml:space="preserve">57.7011528015137</t>
+    <t xml:space="preserve">57.7011566162109</t>
   </si>
   <si>
     <t xml:space="preserve">56.3614959716797</t>
   </si>
   <si>
-    <t xml:space="preserve">57.9882278442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8494338989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.3373756408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4425735473633</t>
+    <t xml:space="preserve">57.988224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8494300842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.3373794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4425582885742</t>
   </si>
   <si>
     <t xml:space="preserve">62.2942810058594</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">63.3468627929688</t>
   </si>
   <si>
-    <t xml:space="preserve">63.7296257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6339454650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3037796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5908432006836</t>
+    <t xml:space="preserve">63.7296295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6339492797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3037719726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5908508300781</t>
   </si>
   <si>
     <t xml:space="preserve">65.9305038452148</t>
   </si>
   <si>
-    <t xml:space="preserve">66.6960220336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3563690185547</t>
+    <t xml:space="preserve">66.6960296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3563613891602</t>
   </si>
   <si>
     <t xml:space="preserve">66.9831008911133</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">67.1744766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5046539306641</t>
+    <t xml:space="preserve">66.5046463012695</t>
   </si>
   <si>
     <t xml:space="preserve">67.8443145751953</t>
@@ -2204,13 +2204,13 @@
     <t xml:space="preserve">70.0451812744141</t>
   </si>
   <si>
-    <t xml:space="preserve">69.1839752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.2891616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8107070922852</t>
+    <t xml:space="preserve">69.1839828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.2891540527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8106994628906</t>
   </si>
   <si>
     <t xml:space="preserve">70.6193313598633</t>
@@ -2219,10 +2219,10 @@
     <t xml:space="preserve">71.7676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">72.0546798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.002082824707</t>
+    <t xml:space="preserve">72.0546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0020751953125</t>
   </si>
   <si>
     <t xml:space="preserve">69.4710388183594</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">68.9925918579102</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9494934082031</t>
+    <t xml:space="preserve">69.9494857788086</t>
   </si>
   <si>
     <t xml:space="preserve">68.8012161254883</t>
@@ -2243,25 +2243,25 @@
     <t xml:space="preserve">76.5521087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7003936767578</t>
+    <t xml:space="preserve">77.7004013061523</t>
   </si>
   <si>
     <t xml:space="preserve">75.8822860717773</t>
   </si>
   <si>
-    <t xml:space="preserve">74.734001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.8727798461914</t>
+    <t xml:space="preserve">74.7339935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.8727874755859</t>
   </si>
   <si>
     <t xml:space="preserve">74.8296890258789</t>
   </si>
   <si>
-    <t xml:space="preserve">77.8917694091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.2745361328125</t>
+    <t xml:space="preserve">77.8917770385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.274543762207</t>
   </si>
   <si>
     <t xml:space="preserve">77.7960891723633</t>
@@ -2276,34 +2276,34 @@
     <t xml:space="preserve">82.0064468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">81.5279998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.910758972168</t>
+    <t xml:space="preserve">81.5279922485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9107666015625</t>
   </si>
   <si>
     <t xml:space="preserve">82.3892135620117</t>
   </si>
   <si>
-    <t xml:space="preserve">81.4322967529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.1452484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4754104614258</t>
+    <t xml:space="preserve">81.4323120117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1452407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4754180908203</t>
   </si>
   <si>
     <t xml:space="preserve">81.7193832397461</t>
   </si>
   <si>
-    <t xml:space="preserve">81.815071105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.3461074829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.9538497924805</t>
+    <t xml:space="preserve">81.8150634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.3461151123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.953857421875</t>
   </si>
   <si>
     <t xml:space="preserve">82.77197265625</t>
@@ -2312,43 +2312,43 @@
     <t xml:space="preserve">82.2935180664062</t>
   </si>
   <si>
-    <t xml:space="preserve">77.0305633544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3271331787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.728874206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.1021347045898</t>
+    <t xml:space="preserve">77.0305557250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3271255493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7288665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.1021423339844</t>
   </si>
   <si>
     <t xml:space="preserve">76.7434921264648</t>
   </si>
   <si>
-    <t xml:space="preserve">79.5185089111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8055877685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4849090576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3797225952148</t>
+    <t xml:space="preserve">79.5184936523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8055801391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4849014282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3797149658203</t>
   </si>
   <si>
     <t xml:space="preserve">78.6572952270508</t>
   </si>
   <si>
-    <t xml:space="preserve">78.4659194946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6857833862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3556060791016</t>
+    <t xml:space="preserve">78.4659118652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6857757568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.355598449707</t>
   </si>
   <si>
     <t xml:space="preserve">83.0590438842773</t>
@@ -2360,22 +2360,22 @@
     <t xml:space="preserve">87.1737213134766</t>
   </si>
   <si>
-    <t xml:space="preserve">87.269401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3220138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7909545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.9056396484375</t>
+    <t xml:space="preserve">87.269416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3219985961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7909622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.905632019043</t>
   </si>
   <si>
     <t xml:space="preserve">91.3840866088867</t>
   </si>
   <si>
-    <t xml:space="preserve">93.1065063476562</t>
+    <t xml:space="preserve">93.1064987182617</t>
   </si>
   <si>
     <t xml:space="preserve">95.8815155029297</t>
@@ -2411,43 +2411,43 @@
     <t xml:space="preserve">94.8289260864258</t>
   </si>
   <si>
-    <t xml:space="preserve">95.307373046875</t>
+    <t xml:space="preserve">95.3073806762695</t>
   </si>
   <si>
     <t xml:space="preserve">94.2547912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">94.446174621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0298080444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.541862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1590957641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8720169067383</t>
+    <t xml:space="preserve">94.446159362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0298004150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5418548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1591110229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8720321655273</t>
   </si>
   <si>
     <t xml:space="preserve">94.0634155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">93.3935699462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6806564331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9151229858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.2978820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7237548828125</t>
+    <t xml:space="preserve">93.3935775756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6806488037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9151306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.2978897094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.723747253418</t>
   </si>
   <si>
     <t xml:space="preserve">94.3504867553711</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">104.876396179199</t>
   </si>
   <si>
-    <t xml:space="preserve">104.493629455566</t>
+    <t xml:space="preserve">104.493621826172</t>
   </si>
   <si>
     <t xml:space="preserve">106.598815917969</t>
@@ -2474,16 +2474,16 @@
     <t xml:space="preserve">109.66089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">110.235046386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.641914367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.216064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.938484191895</t>
+    <t xml:space="preserve">110.235054016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.64192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.21605682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.938491821289</t>
   </si>
   <si>
     <t xml:space="preserve">107.555717468262</t>
@@ -2492,10 +2492,10 @@
     <t xml:space="preserve">109.469520568848</t>
   </si>
   <si>
-    <t xml:space="preserve">107.747093200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.704002380371</t>
+    <t xml:space="preserve">107.747100830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.703994750977</t>
   </si>
   <si>
     <t xml:space="preserve">102.197074890137</t>
@@ -2504,13 +2504,13 @@
     <t xml:space="preserve">99.5177459716797</t>
   </si>
   <si>
-    <t xml:space="preserve">99.7091217041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.345344543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.536735534668</t>
+    <t xml:space="preserve">99.7091293334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.345352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.536720275879</t>
   </si>
   <si>
     <t xml:space="preserve">106.024681091309</t>
@@ -2519,19 +2519,19 @@
     <t xml:space="preserve">106.981582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">108.51261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.833282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.048789978027</t>
+    <t xml:space="preserve">108.512619018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.833290100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.048782348633</t>
   </si>
   <si>
     <t xml:space="preserve">102.388450622559</t>
   </si>
   <si>
-    <t xml:space="preserve">103.153968811035</t>
+    <t xml:space="preserve">103.15397644043</t>
   </si>
   <si>
     <t xml:space="preserve">102.962593078613</t>
@@ -2540,16 +2540,16 @@
     <t xml:space="preserve">105.450531005859</t>
   </si>
   <si>
-    <t xml:space="preserve">102.00569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.919494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.407440185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.086769104004</t>
+    <t xml:space="preserve">102.005683898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.919486999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.407424926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.086761474609</t>
   </si>
   <si>
     <t xml:space="preserve">110.809188842773</t>
@@ -2558,34 +2558,34 @@
     <t xml:space="preserve">113.679885864258</t>
   </si>
   <si>
-    <t xml:space="preserve">110.043670654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.172950744629</t>
+    <t xml:space="preserve">110.043663024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.172966003418</t>
   </si>
   <si>
     <t xml:space="preserve">111.000556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">112.914367675781</t>
+    <t xml:space="preserve">112.914360046387</t>
   </si>
   <si>
     <t xml:space="preserve">109.85228729248</t>
   </si>
   <si>
-    <t xml:space="preserve">110.426429748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.383323669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.340225219727</t>
+    <t xml:space="preserve">110.426414489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.383331298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.340232849121</t>
   </si>
   <si>
     <t xml:space="preserve">114.445411682129</t>
   </si>
   <si>
-    <t xml:space="preserve">113.29712677002</t>
+    <t xml:space="preserve">113.297134399414</t>
   </si>
   <si>
     <t xml:space="preserve">112.722991943359</t>
@@ -2600,25 +2600,25 @@
     <t xml:space="preserve">115.210929870605</t>
   </si>
   <si>
-    <t xml:space="preserve">116.741981506348</t>
+    <t xml:space="preserve">116.741973876953</t>
   </si>
   <si>
     <t xml:space="preserve">116.167831420898</t>
   </si>
   <si>
-    <t xml:space="preserve">115.78507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.550590515137</t>
+    <t xml:space="preserve">115.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.550598144531</t>
   </si>
   <si>
     <t xml:space="preserve">119.804054260254</t>
   </si>
   <si>
-    <t xml:space="preserve">120.186820983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.100624084473</t>
+    <t xml:space="preserve">120.186813354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.100616455078</t>
   </si>
   <si>
     <t xml:space="preserve">122.866134643555</t>
@@ -2630,28 +2630,28 @@
     <t xml:space="preserve">131.478240966797</t>
   </si>
   <si>
-    <t xml:space="preserve">127.267890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.459251403809</t>
+    <t xml:space="preserve">127.26789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.459259033203</t>
   </si>
   <si>
     <t xml:space="preserve">128.990310668945</t>
   </si>
   <si>
-    <t xml:space="preserve">132.052383422852</t>
+    <t xml:space="preserve">132.052398681641</t>
   </si>
   <si>
     <t xml:space="preserve">134.157577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">133.774826049805</t>
+    <t xml:space="preserve">133.774841308594</t>
   </si>
   <si>
     <t xml:space="preserve">132.626541137695</t>
   </si>
   <si>
-    <t xml:space="preserve">132.435134887695</t>
+    <t xml:space="preserve">132.435150146484</t>
   </si>
   <si>
     <t xml:space="preserve">134.923095703125</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">136.645538330078</t>
   </si>
   <si>
-    <t xml:space="preserve">137.411041259766</t>
+    <t xml:space="preserve">137.411056518555</t>
   </si>
   <si>
     <t xml:space="preserve">135.305847167969</t>
@@ -2675,22 +2675,22 @@
     <t xml:space="preserve">136.262756347656</t>
   </si>
   <si>
-    <t xml:space="preserve">137.793792724609</t>
+    <t xml:space="preserve">137.793807983398</t>
   </si>
   <si>
     <t xml:space="preserve">138.176559448242</t>
   </si>
   <si>
-    <t xml:space="preserve">137.028289794922</t>
+    <t xml:space="preserve">137.028259277344</t>
   </si>
   <si>
     <t xml:space="preserve">138.559341430664</t>
   </si>
   <si>
-    <t xml:space="preserve">139.898986816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.454132080078</t>
+    <t xml:space="preserve">139.898971557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.454147338867</t>
   </si>
   <si>
     <t xml:space="preserve">138.750701904297</t>
@@ -2702,25 +2702,25 @@
     <t xml:space="preserve">137.98518371582</t>
   </si>
   <si>
-    <t xml:space="preserve">135.49723815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.492111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.874877929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.109359741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.195541381836</t>
+    <t xml:space="preserve">135.497253417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.492095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.874847412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.195571899414</t>
   </si>
   <si>
     <t xml:space="preserve">143.726577758789</t>
   </si>
   <si>
-    <t xml:space="preserve">143.91796875</t>
+    <t xml:space="preserve">143.917938232422</t>
   </si>
   <si>
     <t xml:space="preserve">144.683486938477</t>
@@ -2732,16 +2732,16 @@
     <t xml:space="preserve">147.936965942383</t>
   </si>
   <si>
-    <t xml:space="preserve">145.640396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.788665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.276641845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.999053955078</t>
+    <t xml:space="preserve">145.640380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.788681030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.276626586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.999038696289</t>
   </si>
   <si>
     <t xml:space="preserve">150.424896240234</t>
@@ -2750,25 +2750,25 @@
     <t xml:space="preserve">153.48698425293</t>
   </si>
   <si>
-    <t xml:space="preserve">152.338714599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.400787353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.190414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.888732910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.037017822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.654266357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.611175537109</t>
+    <t xml:space="preserve">152.33869934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.400802612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.1904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.888717651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.036987304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.654251098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.61116027832</t>
   </si>
   <si>
     <t xml:space="preserve">161.333587646484</t>
@@ -2780,10 +2780,10 @@
     <t xml:space="preserve">163.438766479492</t>
   </si>
   <si>
-    <t xml:space="preserve">163.821517944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.606018066406</t>
+    <t xml:space="preserve">163.821533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.606033325195</t>
   </si>
   <si>
     <t xml:space="preserve">173.773300170898</t>
@@ -2792,19 +2792,19 @@
     <t xml:space="preserve">170.328460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">165.161193847656</t>
+    <t xml:space="preserve">165.161209106445</t>
   </si>
   <si>
     <t xml:space="preserve">168.031890869141</t>
   </si>
   <si>
-    <t xml:space="preserve">165.352554321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.75944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.099105834961</t>
+    <t xml:space="preserve">165.352569580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.759429931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.099090576172</t>
   </si>
   <si>
     <t xml:space="preserve">171.668106079102</t>
@@ -2816,13 +2816,13 @@
     <t xml:space="preserve">161.930511474609</t>
   </si>
   <si>
-    <t xml:space="preserve">161.353591918945</t>
+    <t xml:space="preserve">161.353576660156</t>
   </si>
   <si>
     <t xml:space="preserve">160.58430480957</t>
   </si>
   <si>
-    <t xml:space="preserve">159.045761108398</t>
+    <t xml:space="preserve">159.045776367188</t>
   </si>
   <si>
     <t xml:space="preserve">152.122375488281</t>
@@ -2831,16 +2831,16 @@
     <t xml:space="preserve">145.583618164062</t>
   </si>
   <si>
-    <t xml:space="preserve">147.314468383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.391525268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.19921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.083724975586</t>
+    <t xml:space="preserve">147.314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.391540527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.199203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.083755493164</t>
   </si>
   <si>
     <t xml:space="preserve">151.737747192383</t>
@@ -2855,28 +2855,28 @@
     <t xml:space="preserve">156.545654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">155.968704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.430191040039</t>
+    <t xml:space="preserve">155.968688964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.43017578125</t>
   </si>
   <si>
     <t xml:space="preserve">160.776611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">166.353805541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.200119018555</t>
+    <t xml:space="preserve">166.353820800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.200134277344</t>
   </si>
   <si>
     <t xml:space="preserve">168.469268798828</t>
   </si>
   <si>
-    <t xml:space="preserve">164.430618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.007583618164</t>
+    <t xml:space="preserve">164.430648803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.007598876953</t>
   </si>
   <si>
     <t xml:space="preserve">162.507461547852</t>
@@ -2885,10 +2885,10 @@
     <t xml:space="preserve">163.469055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">165.584548950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.161270141602</t>
+    <t xml:space="preserve">165.584518432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.161239624023</t>
   </si>
   <si>
     <t xml:space="preserve">163.084426879883</t>
@@ -2897,34 +2897,34 @@
     <t xml:space="preserve">161.738189697266</t>
   </si>
   <si>
-    <t xml:space="preserve">168.853897094727</t>
+    <t xml:space="preserve">168.853927612305</t>
   </si>
   <si>
     <t xml:space="preserve">177.508178710938</t>
   </si>
   <si>
-    <t xml:space="preserve">175.584991455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.392913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.777542114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.469757080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.815948486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.739120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.008514404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.085327148438</t>
+    <t xml:space="preserve">175.585006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.392929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.777526855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.469741821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.815963745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.739135742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.008499145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.085311889648</t>
   </si>
   <si>
     <t xml:space="preserve">182.508392333984</t>
@@ -2933,64 +2933,64 @@
     <t xml:space="preserve">168.276962280273</t>
   </si>
   <si>
-    <t xml:space="preserve">169.046249389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.584762573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.507705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.046478271484</t>
+    <t xml:space="preserve">169.046234130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.584747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.507690429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.046463012695</t>
   </si>
   <si>
     <t xml:space="preserve">170.96940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">169.623184204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.238555908203</t>
+    <t xml:space="preserve">169.623168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.238540649414</t>
   </si>
   <si>
     <t xml:space="preserve">175.008041381836</t>
   </si>
   <si>
-    <t xml:space="preserve">172.700241088867</t>
+    <t xml:space="preserve">172.700256347656</t>
   </si>
   <si>
     <t xml:space="preserve">172.123291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">171.93098449707</t>
+    <t xml:space="preserve">171.930969238281</t>
   </si>
   <si>
     <t xml:space="preserve">167.315383911133</t>
   </si>
   <si>
-    <t xml:space="preserve">163.853668212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.738418579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.238311767578</t>
+    <t xml:space="preserve">163.85368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.738433837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.238327026367</t>
   </si>
   <si>
     <t xml:space="preserve">166.546112060547</t>
   </si>
   <si>
-    <t xml:space="preserve">167.700012207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.392227172852</t>
+    <t xml:space="preserve">167.699996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.392211914062</t>
   </si>
   <si>
     <t xml:space="preserve">151.160781860352</t>
   </si>
   <si>
-    <t xml:space="preserve">158.853454589844</t>
+    <t xml:space="preserve">158.853439331055</t>
   </si>
   <si>
     <t xml:space="preserve">158.468826293945</t>
@@ -2999,13 +2999,13 @@
     <t xml:space="preserve">157.314926147461</t>
   </si>
   <si>
-    <t xml:space="preserve">159.815032958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.930282592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.161010742188</t>
+    <t xml:space="preserve">159.815048217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.930297851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.161026000977</t>
   </si>
   <si>
     <t xml:space="preserve">152.314682006836</t>
@@ -3017,28 +3017,28 @@
     <t xml:space="preserve">146.929824829102</t>
   </si>
   <si>
-    <t xml:space="preserve">151.353088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.468597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.276260375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.122619628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.930053710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.545211791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.968017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.92936706543</t>
+    <t xml:space="preserve">151.353103637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.46858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.276275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.122604370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.930068969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.545181274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.968032836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.929351806641</t>
   </si>
   <si>
     <t xml:space="preserve">138.660217285156</t>
@@ -3053,10 +3053,10 @@
     <t xml:space="preserve">130.198287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">134.813888549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.005981445312</t>
+    <t xml:space="preserve">134.813873291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.005966186523</t>
   </si>
   <si>
     <t xml:space="preserve">130.775238037109</t>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve">128.852066040039</t>
   </si>
   <si>
-    <t xml:space="preserve">129.621337890625</t>
+    <t xml:space="preserve">129.621353149414</t>
   </si>
   <si>
     <t xml:space="preserve">132.890716552734</t>
   </si>
   <si>
-    <t xml:space="preserve">137.506332397461</t>
+    <t xml:space="preserve">137.506301879883</t>
   </si>
   <si>
     <t xml:space="preserve">136.160110473633</t>
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">138.467895507812</t>
   </si>
   <si>
-    <t xml:space="preserve">135.583160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.813438415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.659301757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.582702636719</t>
+    <t xml:space="preserve">135.583145141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.813430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.659309387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.582695007324</t>
   </si>
   <si>
     <t xml:space="preserve">125.198059082031</t>
@@ -3110,10 +3110,10 @@
     <t xml:space="preserve">145.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">145.006652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.775939941406</t>
+    <t xml:space="preserve">145.00666809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.775924682617</t>
   </si>
   <si>
     <t xml:space="preserve">144.814346313477</t>
@@ -3122,13 +3122,13 @@
     <t xml:space="preserve">148.27604675293</t>
   </si>
   <si>
-    <t xml:space="preserve">143.275817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.60270690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.698852539062</t>
+    <t xml:space="preserve">143.275833129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.602722167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.698867797852</t>
   </si>
   <si>
     <t xml:space="preserve">143.083511352539</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">141.160339355469</t>
   </si>
   <si>
-    <t xml:space="preserve">140.198745727539</t>
+    <t xml:space="preserve">140.198760986328</t>
   </si>
   <si>
     <t xml:space="preserve">139.910278320312</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">139.429473876953</t>
   </si>
   <si>
-    <t xml:space="preserve">139.237167358398</t>
+    <t xml:space="preserve">139.237152099609</t>
   </si>
   <si>
     <t xml:space="preserve">140.006439208984</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">143.179641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">142.314239501953</t>
+    <t xml:space="preserve">142.314224243164</t>
   </si>
   <si>
     <t xml:space="preserve">130.87141418457</t>
@@ -3173,37 +3173,37 @@
     <t xml:space="preserve">129.909820556641</t>
   </si>
   <si>
-    <t xml:space="preserve">133.371520996094</t>
+    <t xml:space="preserve">133.371505737305</t>
   </si>
   <si>
     <t xml:space="preserve">128.275115966797</t>
   </si>
   <si>
-    <t xml:space="preserve">130.294448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.236473083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.890266418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.563148498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.812728881836</t>
+    <t xml:space="preserve">130.294464111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.236480712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.890258789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.563140869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.81273651123</t>
   </si>
   <si>
     <t xml:space="preserve">113.562911987305</t>
   </si>
   <si>
-    <t xml:space="preserve">115.389915466309</t>
+    <t xml:space="preserve">115.389923095703</t>
   </si>
   <si>
     <t xml:space="preserve">115.774551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">118.755462646484</t>
+    <t xml:space="preserve">118.75545501709</t>
   </si>
   <si>
     <t xml:space="preserve">118.08235168457</t>
@@ -3212,22 +3212,22 @@
     <t xml:space="preserve">122.313316345215</t>
   </si>
   <si>
-    <t xml:space="preserve">120.293991088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.101676940918</t>
+    <t xml:space="preserve">120.293983459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.101684570312</t>
   </si>
   <si>
     <t xml:space="preserve">119.236251831055</t>
   </si>
   <si>
-    <t xml:space="preserve">120.486312866211</t>
+    <t xml:space="preserve">120.486305236816</t>
   </si>
   <si>
     <t xml:space="preserve">116.736137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">116.832298278809</t>
+    <t xml:space="preserve">116.832290649414</t>
   </si>
   <si>
     <t xml:space="preserve">119.043937683105</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">121.736358642578</t>
   </si>
   <si>
-    <t xml:space="preserve">124.621109008789</t>
+    <t xml:space="preserve">124.621116638184</t>
   </si>
   <si>
     <t xml:space="preserve">123.274894714355</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">124.044158935547</t>
   </si>
   <si>
-    <t xml:space="preserve">124.332649230957</t>
+    <t xml:space="preserve">124.332626342773</t>
   </si>
   <si>
     <t xml:space="preserve">127.986656188965</t>
@@ -3263,25 +3263,25 @@
     <t xml:space="preserve">123.178741455078</t>
   </si>
   <si>
-    <t xml:space="preserve">114.52449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.889801025391</t>
+    <t xml:space="preserve">114.524490356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.889808654785</t>
   </si>
   <si>
     <t xml:space="preserve">114.236022949219</t>
   </si>
   <si>
-    <t xml:space="preserve">111.062797546387</t>
+    <t xml:space="preserve">111.062789916992</t>
   </si>
   <si>
     <t xml:space="preserve">112.216690063477</t>
   </si>
   <si>
-    <t xml:space="preserve">112.505180358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.947540283203</t>
+    <t xml:space="preserve">112.505165100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.947547912598</t>
   </si>
   <si>
     <t xml:space="preserve">116.447662353516</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">115.197601318359</t>
   </si>
   <si>
-    <t xml:space="preserve">119.140098571777</t>
+    <t xml:space="preserve">119.140090942383</t>
   </si>
   <si>
     <t xml:space="preserve">119.909355163574</t>
@@ -3299,34 +3299,34 @@
     <t xml:space="preserve">119.428565979004</t>
   </si>
   <si>
-    <t xml:space="preserve">117.890029907227</t>
+    <t xml:space="preserve">117.890037536621</t>
   </si>
   <si>
     <t xml:space="preserve">115.293762207031</t>
   </si>
   <si>
-    <t xml:space="preserve">113.178276062012</t>
+    <t xml:space="preserve">113.178283691406</t>
   </si>
   <si>
     <t xml:space="preserve">119.332397460938</t>
   </si>
   <si>
-    <t xml:space="preserve">123.082580566406</t>
+    <t xml:space="preserve">123.082588195801</t>
   </si>
   <si>
     <t xml:space="preserve">125.39037322998</t>
   </si>
   <si>
-    <t xml:space="preserve">122.986427307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.274658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.71703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.774780273438</t>
+    <t xml:space="preserve">122.986419677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.27466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.717041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.774772644043</t>
   </si>
   <si>
     <t xml:space="preserve">123.659530639648</t>
@@ -3341,52 +3341,52 @@
     <t xml:space="preserve">130.679077148438</t>
   </si>
   <si>
-    <t xml:space="preserve">126.832748413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.794319152832</t>
+    <t xml:space="preserve">126.832733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.794334411621</t>
   </si>
   <si>
     <t xml:space="preserve">128.46745300293</t>
   </si>
   <si>
-    <t xml:space="preserve">132.602233886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.044387817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.159881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.967330932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.351951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.563362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.313537597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.371276855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.736602783203</t>
+    <t xml:space="preserve">132.602249145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.044403076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.159866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.967323303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.35196685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.563377380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.313552856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.371292114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.736610412598</t>
   </si>
   <si>
     <t xml:space="preserve">121.447883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">117.601554870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.947769165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.197830200195</t>
+    <t xml:space="preserve">117.6015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.947776794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.19783782959</t>
   </si>
   <si>
     <t xml:space="preserve">121.063255310059</t>
@@ -3398,7 +3398,7 @@
     <t xml:space="preserve">115.870704650879</t>
   </si>
   <si>
-    <t xml:space="preserve">116.255340576172</t>
+    <t xml:space="preserve">116.255348205566</t>
   </si>
   <si>
     <t xml:space="preserve">112.312850952148</t>
@@ -3407,13 +3407,13 @@
     <t xml:space="preserve">115.582237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">115.678398132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.178512573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.909133911133</t>
+    <t xml:space="preserve">115.67839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.178504943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.909118652344</t>
   </si>
   <si>
     <t xml:space="preserve">106.596168518066</t>
@@ -3434,40 +3434,40 @@
     <t xml:space="preserve">105.917831420898</t>
   </si>
   <si>
-    <t xml:space="preserve">102.816841125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.014739990234</t>
+    <t xml:space="preserve">102.816848754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.01473236084</t>
   </si>
   <si>
     <t xml:space="preserve">102.041610717773</t>
   </si>
   <si>
-    <t xml:space="preserve">108.437377929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.212623596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.185752868652</t>
+    <t xml:space="preserve">108.437370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.212615966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.185760498047</t>
   </si>
   <si>
     <t xml:space="preserve">111.441444396973</t>
   </si>
   <si>
-    <t xml:space="preserve">111.829078674316</t>
+    <t xml:space="preserve">111.829071044922</t>
   </si>
   <si>
     <t xml:space="preserve">107.274505615234</t>
   </si>
   <si>
-    <t xml:space="preserve">104.851860046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.658058166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.847793579102</t>
+    <t xml:space="preserve">104.851867675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.658050537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.847801208496</t>
   </si>
   <si>
     <t xml:space="preserve">102.429222106934</t>
@@ -3476,16 +3476,16 @@
     <t xml:space="preserve">103.495193481445</t>
   </si>
   <si>
-    <t xml:space="preserve">104.076622009277</t>
+    <t xml:space="preserve">104.076629638672</t>
   </si>
   <si>
     <t xml:space="preserve">106.402359008789</t>
   </si>
   <si>
-    <t xml:space="preserve">106.693077087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.860015869141</t>
+    <t xml:space="preserve">106.693069458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.860023498535</t>
   </si>
   <si>
     <t xml:space="preserve">116.189826965332</t>
@@ -3494,31 +3494,31 @@
     <t xml:space="preserve">114.348617553711</t>
   </si>
   <si>
-    <t xml:space="preserve">109.794059753418</t>
+    <t xml:space="preserve">109.794052124023</t>
   </si>
   <si>
     <t xml:space="preserve">107.468315124512</t>
   </si>
   <si>
-    <t xml:space="preserve">106.305442810059</t>
+    <t xml:space="preserve">106.305450439453</t>
   </si>
   <si>
     <t xml:space="preserve">102.332321166992</t>
   </si>
   <si>
-    <t xml:space="preserve">100.87873840332</t>
+    <t xml:space="preserve">100.878730773926</t>
   </si>
   <si>
     <t xml:space="preserve">103.979721069336</t>
   </si>
   <si>
-    <t xml:space="preserve">108.340469360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.643409729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.515563964844</t>
+    <t xml:space="preserve">108.340476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.643417358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.515556335449</t>
   </si>
   <si>
     <t xml:space="preserve">117.837219238281</t>
@@ -3530,10 +3530,10 @@
     <t xml:space="preserve">114.445526123047</t>
   </si>
   <si>
-    <t xml:space="preserve">114.73624420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.026954650879</t>
+    <t xml:space="preserve">114.736236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.026947021484</t>
   </si>
   <si>
     <t xml:space="preserve">115.317672729492</t>
@@ -3542,16 +3542,16 @@
     <t xml:space="preserve">115.511474609375</t>
   </si>
   <si>
-    <t xml:space="preserve">115.220771789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.965065002441</t>
+    <t xml:space="preserve">115.220764160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.965072631836</t>
   </si>
   <si>
     <t xml:space="preserve">113.476463317871</t>
   </si>
   <si>
-    <t xml:space="preserve">114.25171661377</t>
+    <t xml:space="preserve">114.251708984375</t>
   </si>
   <si>
     <t xml:space="preserve">114.833145141602</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">118.612464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">112.991943359375</t>
+    <t xml:space="preserve">112.99193572998</t>
   </si>
   <si>
     <t xml:space="preserve">111.053825378418</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">107.080696105957</t>
   </si>
   <si>
-    <t xml:space="preserve">110.375495910645</t>
+    <t xml:space="preserve">110.37548828125</t>
   </si>
   <si>
     <t xml:space="preserve">108.534278869629</t>
@@ -3599,22 +3599,22 @@
     <t xml:space="preserve">109.890960693359</t>
   </si>
   <si>
-    <t xml:space="preserve">111.247650146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.282653808594</t>
+    <t xml:space="preserve">111.247634887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.282661437988</t>
   </si>
   <si>
     <t xml:space="preserve">112.410507202148</t>
   </si>
   <si>
-    <t xml:space="preserve">114.63932800293</t>
+    <t xml:space="preserve">114.639343261719</t>
   </si>
   <si>
     <t xml:space="preserve">117.934120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">117.25577545166</t>
+    <t xml:space="preserve">117.255783081055</t>
   </si>
   <si>
     <t xml:space="preserve">117.352691650391</t>
@@ -3644,28 +3644,28 @@
     <t xml:space="preserve">122.779403686523</t>
   </si>
   <si>
-    <t xml:space="preserve">123.26392364502</t>
+    <t xml:space="preserve">123.263931274414</t>
   </si>
   <si>
     <t xml:space="preserve">121.810340881348</t>
   </si>
   <si>
-    <t xml:space="preserve">120.744384765625</t>
+    <t xml:space="preserve">120.74439239502</t>
   </si>
   <si>
     <t xml:space="preserve">123.748458862305</t>
   </si>
   <si>
-    <t xml:space="preserve">131.985427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.888534545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.179244995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.531845092773</t>
+    <t xml:space="preserve">131.985443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.888549804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.179260253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.531860351562</t>
   </si>
   <si>
     <t xml:space="preserve">128.593734741211</t>
@@ -3674,31 +3674,31 @@
     <t xml:space="preserve">127.043251037598</t>
   </si>
   <si>
-    <t xml:space="preserve">124.814430236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.686576843262</t>
+    <t xml:space="preserve">124.814422607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.686561584473</t>
   </si>
   <si>
     <t xml:space="preserve">126.849433898926</t>
   </si>
   <si>
-    <t xml:space="preserve">127.333961486816</t>
+    <t xml:space="preserve">127.333953857422</t>
   </si>
   <si>
     <t xml:space="preserve">126.946342468262</t>
   </si>
   <si>
-    <t xml:space="preserve">124.136085510254</t>
+    <t xml:space="preserve">124.136093139648</t>
   </si>
   <si>
     <t xml:space="preserve">123.845367431641</t>
   </si>
   <si>
-    <t xml:space="preserve">121.422729492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.325820922852</t>
+    <t xml:space="preserve">121.422737121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.325813293457</t>
   </si>
   <si>
     <t xml:space="preserve">120.259857177734</t>
@@ -3710,28 +3710,28 @@
     <t xml:space="preserve">118.321746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">116.8681640625</t>
+    <t xml:space="preserve">116.868156433105</t>
   </si>
   <si>
     <t xml:space="preserve">115.802200317383</t>
   </si>
   <si>
-    <t xml:space="preserve">113.864097595215</t>
+    <t xml:space="preserve">113.86408996582</t>
   </si>
   <si>
     <t xml:space="preserve">113.960990905762</t>
   </si>
   <si>
-    <t xml:space="preserve">113.088844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.472396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.824996948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.414573669434</t>
+    <t xml:space="preserve">113.088836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.472389221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.825004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.414581298828</t>
   </si>
   <si>
     <t xml:space="preserve">109.987861633301</t>
@@ -3752,16 +3752,16 @@
     <t xml:space="preserve">116.286727905273</t>
   </si>
   <si>
-    <t xml:space="preserve">119.193893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.09700012207</t>
+    <t xml:space="preserve">119.193901062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.096992492676</t>
   </si>
   <si>
     <t xml:space="preserve">119.678428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">116.383628845215</t>
+    <t xml:space="preserve">116.383636474609</t>
   </si>
   <si>
     <t xml:space="preserve">115.123870849609</t>
@@ -3773,19 +3773,19 @@
     <t xml:space="preserve">110.569297790527</t>
   </si>
   <si>
-    <t xml:space="preserve">110.956924438477</t>
+    <t xml:space="preserve">110.956916809082</t>
   </si>
   <si>
     <t xml:space="preserve">108.921905517578</t>
   </si>
   <si>
-    <t xml:space="preserve">107.952850341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.565223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.045677185059</t>
+    <t xml:space="preserve">107.952842712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.565231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.045684814453</t>
   </si>
   <si>
     <t xml:space="preserve">104.754959106445</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">103.592094421387</t>
   </si>
   <si>
-    <t xml:space="preserve">106.88688659668</t>
+    <t xml:space="preserve">106.886894226074</t>
   </si>
   <si>
     <t xml:space="preserve">103.204475402832</t>
@@ -3812,10 +3812,10 @@
     <t xml:space="preserve">102.719947814941</t>
   </si>
   <si>
-    <t xml:space="preserve">103.107566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.561149597168</t>
+    <t xml:space="preserve">103.107574462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.561157226562</t>
   </si>
   <si>
     <t xml:space="preserve">107.37141418457</t>
@@ -3830,10 +3830,10 @@
     <t xml:space="preserve">110.084770202637</t>
   </si>
   <si>
-    <t xml:space="preserve">116.480545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.705299377441</t>
+    <t xml:space="preserve">116.480537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.705307006836</t>
   </si>
   <si>
     <t xml:space="preserve">113.37956237793</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">111.150726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">110.763107299805</t>
+    <t xml:space="preserve">110.763114929199</t>
   </si>
   <si>
     <t xml:space="preserve">109.503341674805</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">109.115715026855</t>
   </si>
   <si>
-    <t xml:space="preserve">110.278579711914</t>
+    <t xml:space="preserve">110.278587341309</t>
   </si>
   <si>
     <t xml:space="preserve">109.697143554688</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">102.235412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">102.623046875</t>
+    <t xml:space="preserve">102.623039245605</t>
   </si>
   <si>
     <t xml:space="preserve">104.173522949219</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">100.975639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">100.200393676758</t>
+    <t xml:space="preserve">100.200401306152</t>
   </si>
   <si>
     <t xml:space="preserve">100.491111755371</t>
@@ -3890,25 +3890,25 @@
     <t xml:space="preserve">101.26636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">101.653984069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.39421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3282470703125</t>
+    <t xml:space="preserve">101.65397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.394203186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.328254699707</t>
   </si>
   <si>
     <t xml:space="preserve">99.6189651489258</t>
   </si>
   <si>
-    <t xml:space="preserve">99.2313461303711</t>
+    <t xml:space="preserve">99.2313385009766</t>
   </si>
   <si>
     <t xml:space="preserve">102.138511657715</t>
   </si>
   <si>
-    <t xml:space="preserve">101.75089263916</t>
+    <t xml:space="preserve">101.750885009766</t>
   </si>
   <si>
     <t xml:space="preserve">99.8127746582031</t>
@@ -3923,22 +3923,22 @@
     <t xml:space="preserve">97.1963272094727</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6808471679688</t>
+    <t xml:space="preserve">97.6808547973633</t>
   </si>
   <si>
     <t xml:space="preserve">99.0078277587891</t>
   </si>
   <si>
-    <t xml:space="preserve">98.6164932250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.573173522949</t>
+    <t xml:space="preserve">98.6165008544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.573181152344</t>
   </si>
   <si>
     <t xml:space="preserve">97.051155090332</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0672302246094</t>
+    <t xml:space="preserve">94.0672225952148</t>
   </si>
   <si>
     <t xml:space="preserve">95.8771438598633</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">95.7793197631836</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5780487060547</t>
+    <t xml:space="preserve">93.5780563354492</t>
   </si>
   <si>
     <t xml:space="preserve">92.5997161865234</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">90.0071182250977</t>
   </si>
   <si>
-    <t xml:space="preserve">90.4962844848633</t>
+    <t xml:space="preserve">90.4962921142578</t>
   </si>
   <si>
     <t xml:space="preserve">90.8386993408203</t>
@@ -3995,13 +3995,13 @@
     <t xml:space="preserve">92.3062133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">92.942138671875</t>
+    <t xml:space="preserve">92.9421310424805</t>
   </si>
   <si>
     <t xml:space="preserve">91.2789611816406</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6213760375977</t>
+    <t xml:space="preserve">91.6213836669922</t>
   </si>
   <si>
     <t xml:space="preserve">90.6430435180664</t>
@@ -4052,28 +4052,28 @@
     <t xml:space="preserve">103.508193969727</t>
   </si>
   <si>
-    <t xml:space="preserve">103.703857421875</t>
+    <t xml:space="preserve">103.70384979248</t>
   </si>
   <si>
     <t xml:space="preserve">106.051864624023</t>
   </si>
   <si>
-    <t xml:space="preserve">104.975700378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.171356201172</t>
+    <t xml:space="preserve">104.975692749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.171363830566</t>
   </si>
   <si>
     <t xml:space="preserve">102.627685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">101.747184753418</t>
+    <t xml:space="preserve">101.747177124023</t>
   </si>
   <si>
     <t xml:space="preserve">103.997360229492</t>
   </si>
   <si>
-    <t xml:space="preserve">102.529846191406</t>
+    <t xml:space="preserve">102.529853820801</t>
   </si>
   <si>
     <t xml:space="preserve">100.377502441406</t>
@@ -4085,10 +4085,10 @@
     <t xml:space="preserve">104.193023681641</t>
   </si>
   <si>
-    <t xml:space="preserve">106.541030883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.617210388184</t>
+    <t xml:space="preserve">106.541038513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.617202758789</t>
   </si>
   <si>
     <t xml:space="preserve">106.834533691406</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">105.85619354248</t>
   </si>
   <si>
-    <t xml:space="preserve">111.530563354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.367736816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.291572570801</t>
+    <t xml:space="preserve">111.530555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.367744445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.291564941406</t>
   </si>
   <si>
     <t xml:space="preserve">117.694091796875</t>
@@ -4112,22 +4112,22 @@
     <t xml:space="preserve">118.672431945801</t>
   </si>
   <si>
-    <t xml:space="preserve">118.378921508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.259429931641</t>
+    <t xml:space="preserve">118.378929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.259437561035</t>
   </si>
   <si>
     <t xml:space="preserve">120.335601806641</t>
   </si>
   <si>
-    <t xml:space="preserve">118.085426330566</t>
+    <t xml:space="preserve">118.085418701172</t>
   </si>
   <si>
     <t xml:space="preserve">115.346084594727</t>
   </si>
   <si>
-    <t xml:space="preserve">115.737411499023</t>
+    <t xml:space="preserve">115.737419128418</t>
   </si>
   <si>
     <t xml:space="preserve">113.682907104492</t>
@@ -4142,19 +4142,19 @@
     <t xml:space="preserve">111.921897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">111.824058532715</t>
+    <t xml:space="preserve">111.824066162109</t>
   </si>
   <si>
     <t xml:space="preserve">114.074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">113.976402282715</t>
+    <t xml:space="preserve">113.976409912109</t>
   </si>
   <si>
     <t xml:space="preserve">112.802406311035</t>
   </si>
   <si>
-    <t xml:space="preserve">112.31324005127</t>
+    <t xml:space="preserve">112.313232421875</t>
   </si>
   <si>
     <t xml:space="preserve">114.856910705566</t>
@@ -4175,10 +4175,10 @@
     <t xml:space="preserve">122.585784912109</t>
   </si>
   <si>
-    <t xml:space="preserve">122.781448364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.368453979492</t>
+    <t xml:space="preserve">122.781455993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.368446350098</t>
   </si>
   <si>
     <t xml:space="preserve">120.433433532715</t>
@@ -4193,13 +4193,13 @@
     <t xml:space="preserve">122.194450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">121.803108215332</t>
+    <t xml:space="preserve">121.803115844727</t>
   </si>
   <si>
     <t xml:space="preserve">120.042098999023</t>
   </si>
   <si>
-    <t xml:space="preserve">119.455101013184</t>
+    <t xml:space="preserve">119.455093383789</t>
   </si>
   <si>
     <t xml:space="preserve">118.574592590332</t>
@@ -4235,31 +4235,31 @@
     <t xml:space="preserve">112.019729614258</t>
   </si>
   <si>
-    <t xml:space="preserve">112.900238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.095893859863</t>
+    <t xml:space="preserve">112.900230407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.095901489258</t>
   </si>
   <si>
     <t xml:space="preserve">110.943557739258</t>
   </si>
   <si>
-    <t xml:space="preserve">111.334892272949</t>
+    <t xml:space="preserve">111.334899902344</t>
   </si>
   <si>
     <t xml:space="preserve">110.747886657715</t>
   </si>
   <si>
-    <t xml:space="preserve">110.063049316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.671722412109</t>
+    <t xml:space="preserve">110.063056945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.671714782715</t>
   </si>
   <si>
     <t xml:space="preserve">102.725517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">100.181838989258</t>
+    <t xml:space="preserve">100.181831359863</t>
   </si>
   <si>
     <t xml:space="preserve">96.8554840087891</t>
@@ -4292,10 +4292,10 @@
     <t xml:space="preserve">98.322998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">96.8065643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2195587158203</t>
+    <t xml:space="preserve">96.8065719604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2195663452148</t>
   </si>
   <si>
     <t xml:space="preserve">94.9966430664062</t>
@@ -4313,7 +4313,7 @@
     <t xml:space="preserve">95.7303924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">97.9316558837891</t>
+    <t xml:space="preserve">97.9316635131836</t>
   </si>
   <si>
     <t xml:space="preserve">95.8282318115234</t>
@@ -4346,7 +4346,7 @@
     <t xml:space="preserve">106.638870239258</t>
   </si>
   <si>
-    <t xml:space="preserve">107.128036499023</t>
+    <t xml:space="preserve">107.128044128418</t>
   </si>
   <si>
     <t xml:space="preserve">105.954032897949</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">104.682189941406</t>
   </si>
   <si>
-    <t xml:space="preserve">103.899513244629</t>
+    <t xml:space="preserve">103.899520874023</t>
   </si>
   <si>
     <t xml:space="preserve">104.78002166748</t>
@@ -4367,10 +4367,10 @@
     <t xml:space="preserve">105.660530090332</t>
   </si>
   <si>
-    <t xml:space="preserve">106.345367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.443199157715</t>
+    <t xml:space="preserve">106.345359802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.443206787109</t>
   </si>
   <si>
     <t xml:space="preserve">103.801681518555</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">112.704566955566</t>
   </si>
   <si>
-    <t xml:space="preserve">114.172073364258</t>
+    <t xml:space="preserve">114.172065734863</t>
   </si>
   <si>
     <t xml:space="preserve">117.107086181641</t>
@@ -4394,10 +4394,10 @@
     <t xml:space="preserve">115.150405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">116.813591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.204925537109</t>
+    <t xml:space="preserve">116.813583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.204917907715</t>
   </si>
   <si>
     <t xml:space="preserve">116.128746032715</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">96.5619812011719</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2628860473633</t>
+    <t xml:space="preserve">94.2628936767578</t>
   </si>
   <si>
     <t xml:space="preserve">91.3767929077148</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">95.3390579223633</t>
   </si>
   <si>
-    <t xml:space="preserve">94.3118133544922</t>
+    <t xml:space="preserve">94.3118057250977</t>
   </si>
   <si>
     <t xml:space="preserve">93.4802169799805</t>
@@ -4454,28 +4454,28 @@
     <t xml:space="preserve">94.7031478881836</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8498840332031</t>
+    <t xml:space="preserve">94.8498916625977</t>
   </si>
   <si>
     <t xml:space="preserve">94.2139739990234</t>
   </si>
   <si>
-    <t xml:space="preserve">91.8659591674805</t>
+    <t xml:space="preserve">91.865966796875</t>
   </si>
   <si>
     <t xml:space="preserve">90.6919479370117</t>
   </si>
   <si>
-    <t xml:space="preserve">89.2244415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7080230712891</t>
+    <t xml:space="preserve">89.2244491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7080307006836</t>
   </si>
   <si>
     <t xml:space="preserve">85.751350402832</t>
   </si>
   <si>
-    <t xml:space="preserve">84.5284194946289</t>
+    <t xml:space="preserve">84.5284271240234</t>
   </si>
   <si>
     <t xml:space="preserve">84.3327560424805</t>
@@ -4484,13 +4484,13 @@
     <t xml:space="preserve">86.2894287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2517013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.441780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0287857055664</t>
+    <t xml:space="preserve">90.251708984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4417724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0287780761719</t>
   </si>
   <si>
     <t xml:space="preserve">88.4906921386719</t>
@@ -5310,6 +5310,9 @@
   </si>
   <si>
     <t xml:space="preserve">91.5500030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9000015258789</t>
   </si>
 </sst>
 </file>
@@ -71818,7 +71821,7 @@
     </row>
     <row r="2546">
       <c r="A2546" s="1" t="n">
-        <v>46030.6912847222</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B2546" t="n">
         <v>39102</v>
@@ -71827,7 +71830,7 @@
         <v>94.25</v>
       </c>
       <c r="D2546" t="n">
-        <v>91.9000015258789</v>
+        <v>91.5500030517578</v>
       </c>
       <c r="E2546" t="n">
         <v>93.5</v>
@@ -71839,6 +71842,32 @@
         <v>1765</v>
       </c>
       <c r="H2546" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" s="1" t="n">
+        <v>46031.6910300926</v>
+      </c>
+      <c r="B2547" t="n">
+        <v>24230</v>
+      </c>
+      <c r="C2547" t="n">
+        <v>94</v>
+      </c>
+      <c r="D2547" t="n">
+        <v>91.6500015258789</v>
+      </c>
+      <c r="E2547" t="n">
+        <v>92</v>
+      </c>
+      <c r="F2547" t="n">
+        <v>93.9000015258789</v>
+      </c>
+      <c r="G2547" t="s">
+        <v>1766</v>
+      </c>
+      <c r="H2547" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="1768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="1769">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5495891571045</t>
+    <t xml:space="preserve">13.5495910644531</t>
   </si>
   <si>
     <t xml:space="preserve">SES.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5321054458618</t>
+    <t xml:space="preserve">13.5321073532104</t>
   </si>
   <si>
     <t xml:space="preserve">13.2523736953735</t>
@@ -53,34 +53,34 @@
     <t xml:space="preserve">12.9464149475098</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1125059127808</t>
+    <t xml:space="preserve">13.1125078201294</t>
   </si>
   <si>
     <t xml:space="preserve">12.858998298645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0513153076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.990122795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9376726150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1037664413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.025089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8502569198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2383394241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5880060195923</t>
+    <t xml:space="preserve">13.0513143539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9901237487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9376735687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1037645339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0250911712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8502559661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2383413314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5880069732666</t>
   </si>
   <si>
     <t xml:space="preserve">12.7890653610229</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">12.7191314697266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6841659545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.605489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3257570266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0460233688354</t>
+    <t xml:space="preserve">12.6841650009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6054887771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.325756072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0460224151611</t>
   </si>
   <si>
     <t xml:space="preserve">12.1771488189697</t>
@@ -107,16 +107,16 @@
     <t xml:space="preserve">12.1421823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9270896911621</t>
+    <t xml:space="preserve">10.9270906448364</t>
   </si>
   <si>
     <t xml:space="preserve">10.9795389175415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3641719818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4515905380249</t>
+    <t xml:space="preserve">11.3641738891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4515895843506</t>
   </si>
   <si>
     <t xml:space="preserve">12.0984725952148</t>
@@ -128,28 +128,28 @@
     <t xml:space="preserve">11.888671875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760904312134</t>
+    <t xml:space="preserve">11.9760885238647</t>
   </si>
   <si>
     <t xml:space="preserve">11.9323806762695</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0110569000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0809888839722</t>
+    <t xml:space="preserve">12.0110559463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0809907913208</t>
   </si>
   <si>
     <t xml:space="preserve">11.8012561798096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1334400177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8274812698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0635070800781</t>
+    <t xml:space="preserve">12.1334390640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8274793624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0635061264038</t>
   </si>
   <si>
     <t xml:space="preserve">12.5005893707275</t>
@@ -158,55 +158,55 @@
     <t xml:space="preserve">12.6754245758057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7978057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1649570465088</t>
+    <t xml:space="preserve">12.7978067398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1649560928345</t>
   </si>
   <si>
     <t xml:space="preserve">13.1562147140503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0687999725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1212491989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1911811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7540988922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8939647674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9027070999146</t>
+    <t xml:space="preserve">13.0687990188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1212482452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.19118309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7540979385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8939657211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9027080535889</t>
   </si>
   <si>
     <t xml:space="preserve">13.0600576400757</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1999235153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9813814163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4534339904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7069396972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4709148406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4621744155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2086658477783</t>
+    <t xml:space="preserve">13.1999244689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9813823699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4534330368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7069406509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4709157943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4621734619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2086639404297</t>
   </si>
   <si>
     <t xml:space="preserve">13.3223066329956</t>
@@ -215,16 +215,16 @@
     <t xml:space="preserve">13.0950222015381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9988660812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6404581069946</t>
+    <t xml:space="preserve">12.9988651275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.640456199646</t>
   </si>
   <si>
     <t xml:space="preserve">12.4481391906738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3782072067261</t>
+    <t xml:space="preserve">12.3782052993774</t>
   </si>
   <si>
     <t xml:space="preserve">12.0285396575928</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">12.5617818832397</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5268144607544</t>
+    <t xml:space="preserve">12.5268154144287</t>
   </si>
   <si>
     <t xml:space="preserve">12.6317148208618</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">12.3694648742676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7715826034546</t>
+    <t xml:space="preserve">12.7715816497803</t>
   </si>
   <si>
     <t xml:space="preserve">12.4306564331055</t>
@@ -266,31 +266,31 @@
     <t xml:space="preserve">12.4131727218628</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5093336105347</t>
+    <t xml:space="preserve">12.509331703186</t>
   </si>
   <si>
     <t xml:space="preserve">12.3869485855103</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8187389373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8449659347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.255823135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5792665481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2208547592163</t>
+    <t xml:space="preserve">11.8187398910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8449649810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2558221817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5792655944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2208557128906</t>
   </si>
   <si>
     <t xml:space="preserve">12.1858901977539</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7803239822388</t>
+    <t xml:space="preserve">12.7803230285645</t>
   </si>
   <si>
     <t xml:space="preserve">12.7278738021851</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">12.8764810562134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.806547164917</t>
+    <t xml:space="preserve">12.8065481185913</t>
   </si>
   <si>
     <t xml:space="preserve">12.7628402709961</t>
@@ -308,22 +308,22 @@
     <t xml:space="preserve">12.8677406311035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8327732086182</t>
+    <t xml:space="preserve">12.8327741622925</t>
   </si>
   <si>
     <t xml:space="preserve">12.5355567932129</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1824388504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0338335037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3048248291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.261116027832</t>
+    <t xml:space="preserve">13.1824417114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0338315963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3048257827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2611169815063</t>
   </si>
   <si>
     <t xml:space="preserve">13.3747577667236</t>
@@ -338,37 +338,37 @@
     <t xml:space="preserve">13.7244243621826</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7514762878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5711278915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8687019348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6252326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6432676315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6613025665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5981798171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6162166595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5260410308838</t>
+    <t xml:space="preserve">13.7514753341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5711288452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8687009811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6252317428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6432685852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.661301612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5981817245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6162176132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5260429382324</t>
   </si>
   <si>
     <t xml:space="preserve">13.5530948638916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3456945419312</t>
+    <t xml:space="preserve">13.3456954956055</t>
   </si>
   <si>
     <t xml:space="preserve">13.5801467895508</t>
@@ -383,16 +383,16 @@
     <t xml:space="preserve">13.6703195571899</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7965612411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9769086837769</t>
+    <t xml:space="preserve">13.7965621948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9769105911255</t>
   </si>
   <si>
     <t xml:space="preserve">14.0400323867798</t>
   </si>
   <si>
-    <t xml:space="preserve">14.012978553772</t>
+    <t xml:space="preserve">14.0129795074463</t>
   </si>
   <si>
     <t xml:space="preserve">13.9047708511353</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">14.2474317550659</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1572561264038</t>
+    <t xml:space="preserve">14.1572570800781</t>
   </si>
   <si>
     <t xml:space="preserve">14.3646564483643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4187593460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5179529190063</t>
+    <t xml:space="preserve">14.4187622070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5179500579834</t>
   </si>
   <si>
     <t xml:space="preserve">14.6081247329712</t>
@@ -422,49 +422,49 @@
     <t xml:space="preserve">14.6622304916382</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3917083740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3105525970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3015365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5450029373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6441946029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7343683242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7163324356079</t>
+    <t xml:space="preserve">14.3917093276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3105516433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.30153465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5450038909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6441926956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7343692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7163333892822</t>
   </si>
   <si>
     <t xml:space="preserve">14.6351776123047</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6261606216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6892824172974</t>
+    <t xml:space="preserve">14.6261596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.689281463623</t>
   </si>
   <si>
     <t xml:space="preserve">14.8245420455933</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8065090179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.74338722229</t>
+    <t xml:space="preserve">14.8065071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7433853149414</t>
   </si>
   <si>
     <t xml:space="preserve">14.581072807312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.698299407959</t>
+    <t xml:space="preserve">14.6982975006104</t>
   </si>
   <si>
     <t xml:space="preserve">14.5089340209961</t>
@@ -473,40 +473,40 @@
     <t xml:space="preserve">14.6712484359741</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6532125473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.923731803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0499753952026</t>
+    <t xml:space="preserve">14.6532115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9237327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0499773025513</t>
   </si>
   <si>
     <t xml:space="preserve">15.2122898101807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3746013641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5549449920654</t>
+    <t xml:space="preserve">15.3746004104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5549478530884</t>
   </si>
   <si>
     <t xml:space="preserve">15.9246606826782</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7803831100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8705558776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344869613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7082443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517116546631</t>
+    <t xml:space="preserve">15.7803802490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8705549240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344860076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7082433700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517135620117</t>
   </si>
   <si>
     <t xml:space="preserve">16.7452392578125</t>
@@ -521,55 +521,55 @@
     <t xml:space="preserve">17.1510219573975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2231616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9796905517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9075508117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3043155670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0337982177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2772617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4756450653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3223495483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.169059753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5838565826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.574836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5658206939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2411975860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1870899200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8534469604492</t>
+    <t xml:space="preserve">17.2231578826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9796924591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9075527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3043174743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0337944030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2772655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.475643157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3223533630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1690559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5838527679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5748405456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5658168792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2411956787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1870880126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8534507751465</t>
   </si>
   <si>
     <t xml:space="preserve">16.8444309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9526386260986</t>
+    <t xml:space="preserve">16.9526405334473</t>
   </si>
   <si>
     <t xml:space="preserve">16.7272052764893</t>
@@ -581,55 +581,55 @@
     <t xml:space="preserve">16.8624668121338</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0428123474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8173789978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9977245330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7722911834717</t>
+    <t xml:space="preserve">17.0428142547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8173809051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9977264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7722930908203</t>
   </si>
   <si>
     <t xml:space="preserve">17.006742477417</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1961078643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3584175109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6199245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7642002105713</t>
+    <t xml:space="preserve">17.1961059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.358419418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6199264526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7642021179199</t>
   </si>
   <si>
     <t xml:space="preserve">18.0076694488525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9896373748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9445514678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9535694122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8092880249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2601585388184</t>
+    <t xml:space="preserve">17.9896354675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9445495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9535675048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.809289932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2601566314697</t>
   </si>
   <si>
     <t xml:space="preserve">18.7561092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8462829589844</t>
+    <t xml:space="preserve">18.8462867736816</t>
   </si>
   <si>
     <t xml:space="preserve">18.9364604949951</t>
@@ -641,28 +641,28 @@
     <t xml:space="preserve">19.2971515655518</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3602771759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3512554168701</t>
+    <t xml:space="preserve">19.3602752685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3512573242188</t>
   </si>
   <si>
     <t xml:space="preserve">19.666862487793</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6488285064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5586605072021</t>
+    <t xml:space="preserve">19.6488265991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5586566925049</t>
   </si>
   <si>
     <t xml:space="preserve">19.2520656585693</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1709117889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1348419189453</t>
+    <t xml:space="preserve">19.1709079742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1348400115967</t>
   </si>
   <si>
     <t xml:space="preserve">19.1979637145996</t>
@@ -671,16 +671,16 @@
     <t xml:space="preserve">18.9544925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9094066619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0897521972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5757656097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1970329284668</t>
+    <t xml:space="preserve">18.9094085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0897541046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5757637023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1970348358154</t>
   </si>
   <si>
     <t xml:space="preserve">18.5306739807129</t>
@@ -689,37 +689,37 @@
     <t xml:space="preserve">18.8372669219971</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4594631195068</t>
+    <t xml:space="preserve">19.4594650268555</t>
   </si>
   <si>
     <t xml:space="preserve">19.3873271942139</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0185413360596</t>
+    <t xml:space="preserve">20.0185432434082</t>
   </si>
   <si>
     <t xml:space="preserve">20.3612003326416</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8301048278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.280969619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8751907348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.929292678833</t>
+    <t xml:space="preserve">20.8301067352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2809715270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8751926422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9292945861816</t>
   </si>
   <si>
     <t xml:space="preserve">21.1006259918213</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0104522705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5685997009277</t>
+    <t xml:space="preserve">21.0104503631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5686016082764</t>
   </si>
   <si>
     <t xml:space="preserve">20.7218952178955</t>
@@ -728,22 +728,22 @@
     <t xml:space="preserve">20.6046714782715</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1898708343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792381286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6497554779053</t>
+    <t xml:space="preserve">20.1898727416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792362213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6497573852539</t>
   </si>
   <si>
     <t xml:space="preserve">21.6416645050049</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3711452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3801651000977</t>
+    <t xml:space="preserve">21.3711471557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.380163192749</t>
   </si>
   <si>
     <t xml:space="preserve">22.0925350189209</t>
@@ -758,52 +758,52 @@
     <t xml:space="preserve">22.8049087524414</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5984325408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0763530731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0583190917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7156581878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9320793151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8599376678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8058300018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5082626342773</t>
+    <t xml:space="preserve">23.5984344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0763568878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0583209991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7156600952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9320774078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8599395751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8058319091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5082607269287</t>
   </si>
   <si>
     <t xml:space="preserve">22.9942722320557</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4802799224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5434017181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.705717086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4532279968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4622459411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0023574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1827087402344</t>
+    <t xml:space="preserve">22.480281829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5434055328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7057151794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4532299041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4622440338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0023612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.182710647583</t>
   </si>
   <si>
     <t xml:space="preserve">22.7237529754639</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">22.3630561828613</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2097587585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.488374710083</t>
+    <t xml:space="preserve">22.2097606658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4883728027344</t>
   </si>
   <si>
     <t xml:space="preserve">21.9212055206299</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8761196136475</t>
+    <t xml:space="preserve">21.8761215209961</t>
   </si>
   <si>
     <t xml:space="preserve">21.7047863006592</t>
@@ -833,31 +833,31 @@
     <t xml:space="preserve">22.074499130249</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2999362945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8139209747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3179702758789</t>
+    <t xml:space="preserve">22.299934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8139228820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3179683685303</t>
   </si>
   <si>
     <t xml:space="preserve">22.1917247772217</t>
   </si>
   <si>
-    <t xml:space="preserve">22.354040145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5253677368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6065254211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6335792541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2458324432373</t>
+    <t xml:space="preserve">22.3540382385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.525369644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6065235137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.633581161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2458343505859</t>
   </si>
   <si>
     <t xml:space="preserve">22.2277965545654</t>
@@ -869,19 +869,19 @@
     <t xml:space="preserve">22.0835189819336</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2007465362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1376209259033</t>
+    <t xml:space="preserve">22.2007446289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.137622833252</t>
   </si>
   <si>
     <t xml:space="preserve">22.1466369628906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5965805053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3260593414307</t>
+    <t xml:space="preserve">21.5965824127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3260612487793</t>
   </si>
   <si>
     <t xml:space="preserve">21.5605087280273</t>
@@ -890,28 +890,28 @@
     <t xml:space="preserve">22.0294151306152</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6867504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2368144989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3720741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3991241455078</t>
+    <t xml:space="preserve">21.6867523193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2368125915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3991222381592</t>
   </si>
   <si>
     <t xml:space="preserve">22.6155414581299</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6606311798096</t>
+    <t xml:space="preserve">22.6606292724609</t>
   </si>
   <si>
     <t xml:space="preserve">23.0123081207275</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5193881988525</t>
+    <t xml:space="preserve">23.5193901062012</t>
   </si>
   <si>
     <t xml:space="preserve">23.2704582214355</t>
@@ -920,16 +920,16 @@
     <t xml:space="preserve">24.1739845275879</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7087268829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7732677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2434673309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8150844573975</t>
+    <t xml:space="preserve">24.7087287902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.773265838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.243465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8150882720947</t>
   </si>
   <si>
     <t xml:space="preserve">25.7966461181641</t>
@@ -938,28 +938,28 @@
     <t xml:space="preserve">25.6860122680664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6675720214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0086994171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8888473510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9810390472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0916767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.907283782959</t>
+    <t xml:space="preserve">25.6675701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0086975097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8888454437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9810428619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0916728973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9072818756104</t>
   </si>
   <si>
     <t xml:space="preserve">25.8058681488037</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9533824920654</t>
+    <t xml:space="preserve">25.9533786773682</t>
   </si>
   <si>
     <t xml:space="preserve">25.676794052124</t>
@@ -968,70 +968,70 @@
     <t xml:space="preserve">25.6583518981934</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0775146484375</t>
+    <t xml:space="preserve">25.0775127410889</t>
   </si>
   <si>
     <t xml:space="preserve">25.4001998901367</t>
   </si>
   <si>
-    <t xml:space="preserve">25.261905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3264408111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8009243011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4186420440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6441898345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8562393188477</t>
+    <t xml:space="preserve">25.2619075775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3264446258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8009204864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4186401367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6441860198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.856237411499</t>
   </si>
   <si>
     <t xml:space="preserve">24.9576568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8931198120117</t>
+    <t xml:space="preserve">24.8931217193604</t>
   </si>
   <si>
     <t xml:space="preserve">23.187479019165</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9754276275635</t>
+    <t xml:space="preserve">22.9754295349121</t>
   </si>
   <si>
     <t xml:space="preserve">23.1229419708252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2335796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9938678741455</t>
+    <t xml:space="preserve">23.2335777282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9938659667969</t>
   </si>
   <si>
     <t xml:space="preserve">23.0123062133789</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7818145751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.671178817749</t>
+    <t xml:space="preserve">22.781810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6711807250977</t>
   </si>
   <si>
     <t xml:space="preserve">22.4960041046143</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7264957427979</t>
+    <t xml:space="preserve">22.7264976501465</t>
   </si>
   <si>
     <t xml:space="preserve">22.5052242279053</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3208293914795</t>
+    <t xml:space="preserve">22.3208312988281</t>
   </si>
   <si>
     <t xml:space="preserve">22.5881996154785</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">23.1137237548828</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9108905792236</t>
+    <t xml:space="preserve">22.910888671875</t>
   </si>
   <si>
     <t xml:space="preserve">23.3995304107666</t>
@@ -1052,16 +1052,16 @@
     <t xml:space="preserve">23.6208076477051</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1413860321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9846477508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8740100860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7357158660889</t>
+    <t xml:space="preserve">23.1413841247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9846496582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8740081787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7357139587402</t>
   </si>
   <si>
     <t xml:space="preserve">22.6896171569824</t>
@@ -1070,58 +1070,58 @@
     <t xml:space="preserve">23.3257751464844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7406578063965</t>
+    <t xml:space="preserve">23.7406597137451</t>
   </si>
   <si>
     <t xml:space="preserve">23.9803733825684</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9711513519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.063346862793</t>
+    <t xml:space="preserve">23.9711532592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0633487701416</t>
   </si>
   <si>
     <t xml:space="preserve">24.2477416992188</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3860397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1555442810059</t>
+    <t xml:space="preserve">24.3860359191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1555461883545</t>
   </si>
   <si>
     <t xml:space="preserve">24.6165313720703</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8611850738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6306953430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2158088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1697063446045</t>
+    <t xml:space="preserve">25.8611869812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6306934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2158107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1697082519531</t>
   </si>
   <si>
     <t xml:space="preserve">25.3080043792725</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4463024139404</t>
+    <t xml:space="preserve">25.4463005065918</t>
   </si>
   <si>
     <t xml:space="preserve">25.5384960174561</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1236114501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4321384429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6484642028809</t>
+    <t xml:space="preserve">25.123607635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4321327209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6484603881836</t>
   </si>
   <si>
     <t xml:space="preserve">24.0172500610352</t>
@@ -1133,10 +1133,10 @@
     <t xml:space="preserve">24.339937210083</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2016448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2938423156738</t>
+    <t xml:space="preserve">24.2016429901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2938404083252</t>
   </si>
   <si>
     <t xml:space="preserve">24.7548236846924</t>
@@ -1145,10 +1145,10 @@
     <t xml:space="preserve">24.6626281738281</t>
   </si>
   <si>
-    <t xml:space="preserve">24.985315322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4924011230469</t>
+    <t xml:space="preserve">24.9853172302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4923992156982</t>
   </si>
   <si>
     <t xml:space="preserve">25.7228889465332</t>
@@ -1163,61 +1163,61 @@
     <t xml:space="preserve">25.9994831085205</t>
   </si>
   <si>
-    <t xml:space="preserve">26.414363861084</t>
+    <t xml:space="preserve">26.4143657684326</t>
   </si>
   <si>
     <t xml:space="preserve">27.5668258666992</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7512168884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0739078521729</t>
+    <t xml:space="preserve">27.7512187957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0739059448242</t>
   </si>
   <si>
     <t xml:space="preserve">27.5207290649414</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7370548248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5065612792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0314140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5243320465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3682670593262</t>
+    <t xml:space="preserve">26.7370567321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5065631866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0314121246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5243339538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3682689666748</t>
   </si>
   <si>
     <t xml:space="preserve">26.5987606048584</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4604625701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2299709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3221664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1980381011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2760734558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2902336120605</t>
+    <t xml:space="preserve">26.4604644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2299747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3221645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1980400085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2760696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2902355194092</t>
   </si>
   <si>
     <t xml:space="preserve">27.3824329376221</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4746246337891</t>
+    <t xml:space="preserve">27.4746265411377</t>
   </si>
   <si>
     <t xml:space="preserve">26.5526599884033</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">26.8292503356934</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1058387756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8753490447998</t>
+    <t xml:space="preserve">27.1058406829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8753471374512</t>
   </si>
   <si>
     <t xml:space="preserve">27.8434143066406</t>
@@ -1238,46 +1238,46 @@
     <t xml:space="preserve">28.7653827667236</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5809898376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9356136322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8114833831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1661071777344</t>
+    <t xml:space="preserve">28.5809917449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9356117248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8114814758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1661014556885</t>
   </si>
   <si>
     <t xml:space="preserve">28.7192821502686</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1200046539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0597438812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9675464630127</t>
+    <t xml:space="preserve">28.1200065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.059741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9675445556641</t>
   </si>
   <si>
     <t xml:space="preserve">27.1519412994385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6909580230713</t>
+    <t xml:space="preserve">26.6909561157227</t>
   </si>
   <si>
     <t xml:space="preserve">26.7831535339355</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0455780029297</t>
+    <t xml:space="preserve">26.0455799102783</t>
   </si>
   <si>
     <t xml:space="preserve">27.6590213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9214496612549</t>
+    <t xml:space="preserve">26.9214458465576</t>
   </si>
   <si>
     <t xml:space="preserve">26.1828804016113</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">26.0886974334717</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4654331207275</t>
+    <t xml:space="preserve">26.4654293060303</t>
   </si>
   <si>
     <t xml:space="preserve">25.8061485290527</t>
@@ -1304,37 +1304,37 @@
     <t xml:space="preserve">24.9114112854004</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4875869750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3934001922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9224853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2632083892822</t>
+    <t xml:space="preserve">24.4875888824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3934020996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9224872589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2632064819336</t>
   </si>
   <si>
     <t xml:space="preserve">23.0277500152588</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0748405456543</t>
+    <t xml:space="preserve">23.0748386383057</t>
   </si>
   <si>
     <t xml:space="preserve">22.7451992034912</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6039257049561</t>
+    <t xml:space="preserve">22.6039237976074</t>
   </si>
   <si>
     <t xml:space="preserve">22.5097427368164</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4155578613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.180103302002</t>
+    <t xml:space="preserve">22.4155597686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1800975799561</t>
   </si>
   <si>
     <t xml:space="preserve">22.0388259887695</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">22.2271938323975</t>
   </si>
   <si>
-    <t xml:space="preserve">23.404483795166</t>
+    <t xml:space="preserve">23.4044799804688</t>
   </si>
   <si>
     <t xml:space="preserve">23.2161159515381</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">22.8864727020264</t>
   </si>
   <si>
-    <t xml:space="preserve">23.498664855957</t>
+    <t xml:space="preserve">23.4986629486084</t>
   </si>
   <si>
     <t xml:space="preserve">22.5568332672119</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">21.1911811828613</t>
   </si>
   <si>
-    <t xml:space="preserve">21.002815246582</t>
+    <t xml:space="preserve">21.0028133392334</t>
   </si>
   <si>
     <t xml:space="preserve">21.096996307373</t>
@@ -1385,22 +1385,22 @@
     <t xml:space="preserve">21.379545211792</t>
   </si>
   <si>
-    <t xml:space="preserve">21.473726272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.274284362793</t>
+    <t xml:space="preserve">21.4737281799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2742862701416</t>
   </si>
   <si>
     <t xml:space="preserve">21.7562770843506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9446411132812</t>
+    <t xml:space="preserve">21.9446430206299</t>
   </si>
   <si>
     <t xml:space="preserve">21.5679130554199</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5208206176758</t>
+    <t xml:space="preserve">21.5208187103271</t>
   </si>
   <si>
     <t xml:space="preserve">21.3324527740479</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">21.2382717132568</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8393840789795</t>
+    <t xml:space="preserve">22.8393821716309</t>
   </si>
   <si>
     <t xml:space="preserve">22.792293548584</t>
@@ -1421,19 +1421,19 @@
     <t xml:space="preserve">23.6399402618408</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7341213226318</t>
+    <t xml:space="preserve">23.7341232299805</t>
   </si>
   <si>
     <t xml:space="preserve">23.6870307922363</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7812099456787</t>
+    <t xml:space="preserve">23.7812118530273</t>
   </si>
   <si>
     <t xml:space="preserve">24.0166721343994</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2992210388184</t>
+    <t xml:space="preserve">24.2992191314697</t>
   </si>
   <si>
     <t xml:space="preserve">24.1579437255859</t>
@@ -1451,28 +1451,28 @@
     <t xml:space="preserve">24.675952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">24.58176612854</t>
+    <t xml:space="preserve">24.5817680358887</t>
   </si>
   <si>
     <t xml:space="preserve">24.770133972168</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9585018157959</t>
+    <t xml:space="preserve">24.9584999084473</t>
   </si>
   <si>
     <t xml:space="preserve">25.9003314971924</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7590560913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9474220275879</t>
+    <t xml:space="preserve">25.7590599060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9474201202393</t>
   </si>
   <si>
     <t xml:space="preserve">26.277063369751</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9363460540771</t>
+    <t xml:space="preserve">26.9363441467285</t>
   </si>
   <si>
     <t xml:space="preserve">26.983434677124</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">26.8421611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7479782104492</t>
+    <t xml:space="preserve">26.7479763031006</t>
   </si>
   <si>
     <t xml:space="preserve">27.2659854888916</t>
@@ -1493,70 +1493,70 @@
     <t xml:space="preserve">27.501443862915</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3130760192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0776195526123</t>
+    <t xml:space="preserve">27.3130779266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0776214599609</t>
   </si>
   <si>
     <t xml:space="preserve">26.7008876800537</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6537952423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6067047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9945163726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1357898712158</t>
+    <t xml:space="preserve">26.6537971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6067028045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.994514465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1357879638672</t>
   </si>
   <si>
     <t xml:space="preserve">26.0416049957275</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6177825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4294147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0055904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0997753143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8643169403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4404945373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5236015319824</t>
+    <t xml:space="preserve">25.6177806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4294166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0055923461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0997772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.864315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4404964447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5235996246338</t>
   </si>
   <si>
     <t xml:space="preserve">26.3712463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3241577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7950687408447</t>
+    <t xml:space="preserve">26.3241539001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7950706481934</t>
   </si>
   <si>
     <t xml:space="preserve">26.8892517089844</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0305252075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1718006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5485343933105</t>
+    <t xml:space="preserve">27.0305271148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.171802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5485324859619</t>
   </si>
   <si>
     <t xml:space="preserve">27.6898078918457</t>
@@ -1565,28 +1565,28 @@
     <t xml:space="preserve">28.1136322021484</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3961791992188</t>
+    <t xml:space="preserve">28.3961811065674</t>
   </si>
   <si>
     <t xml:space="preserve">28.7258205413818</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9141883850098</t>
+    <t xml:space="preserve">28.9141902923584</t>
   </si>
   <si>
     <t xml:space="preserve">29.9502010345459</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7618370056152</t>
+    <t xml:space="preserve">29.7618350982666</t>
   </si>
   <si>
     <t xml:space="preserve">30.3269329071045</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5042247772217</t>
+    <t xml:space="preserve">30.3740253448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5042266845703</t>
   </si>
   <si>
     <t xml:space="preserve">31.6925888061523</t>
@@ -1601,25 +1601,25 @@
     <t xml:space="preserve">33.482063293457</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6704330444336</t>
+    <t xml:space="preserve">33.6704292297363</t>
   </si>
   <si>
     <t xml:space="preserve">33.2936973571777</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5762519836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.905891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2466049194336</t>
+    <t xml:space="preserve">33.5762481689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9058876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2466125488281</t>
   </si>
   <si>
     <t xml:space="preserve">32.8698768615723</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1524238586426</t>
+    <t xml:space="preserve">33.1524200439453</t>
   </si>
   <si>
     <t xml:space="preserve">33.0582389831543</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">32.5873260498047</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3047714233398</t>
+    <t xml:space="preserve">32.3047752380371</t>
   </si>
   <si>
     <t xml:space="preserve">31.9280452728271</t>
@@ -1640,31 +1640,31 @@
     <t xml:space="preserve">31.3629455566406</t>
   </si>
   <si>
-    <t xml:space="preserve">30.892032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0803966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0333042144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6565742492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6094837188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2687664031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9862155914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4100360870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8449382781982</t>
+    <t xml:space="preserve">30.8920288085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0804004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0333080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6565761566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6094818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.268762588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9862174987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4100341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8449401855469</t>
   </si>
   <si>
     <t xml:space="preserve">31.17458152771</t>
@@ -1679,25 +1679,25 @@
     <t xml:space="preserve">31.7396812438965</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0000686645508</t>
+    <t xml:space="preserve">34.000072479248</t>
   </si>
   <si>
     <t xml:space="preserve">34.4709815979004</t>
   </si>
   <si>
-    <t xml:space="preserve">35.78955078125</t>
+    <t xml:space="preserve">35.7895469665527</t>
   </si>
   <si>
     <t xml:space="preserve">36.5901031494141</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7784729003906</t>
+    <t xml:space="preserve">36.7784690856934</t>
   </si>
   <si>
     <t xml:space="preserve">37.155200958252</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6732063293457</t>
+    <t xml:space="preserve">37.673210144043</t>
   </si>
   <si>
     <t xml:space="preserve">38.0846748352051</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">38.1803665161133</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3717460632324</t>
+    <t xml:space="preserve">38.3717498779297</t>
   </si>
   <si>
     <t xml:space="preserve">37.9411430358887</t>
@@ -1724,13 +1724,13 @@
     <t xml:space="preserve">37.9889869689941</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8454551696777</t>
+    <t xml:space="preserve">37.8454513549805</t>
   </si>
   <si>
     <t xml:space="preserve">37.3191604614258</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8501968383789</t>
+    <t xml:space="preserve">38.8501930236816</t>
   </si>
   <si>
     <t xml:space="preserve">38.7545051574707</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">38.8023529052734</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4674415588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1325149536133</t>
+    <t xml:space="preserve">38.4674377441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1325187683105</t>
   </si>
   <si>
     <t xml:space="preserve">38.8980445861816</t>
@@ -1757,34 +1757,34 @@
     <t xml:space="preserve">38.7066612243652</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2760543823242</t>
+    <t xml:space="preserve">38.2760581970215</t>
   </si>
   <si>
     <t xml:space="preserve">38.5631256103516</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4195938110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3764877319336</t>
+    <t xml:space="preserve">38.4195976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3764915466309</t>
   </si>
   <si>
     <t xml:space="preserve">39.1372680664062</t>
   </si>
   <si>
-    <t xml:space="preserve">39.185115814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2807998657227</t>
+    <t xml:space="preserve">39.1851119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2808036804199</t>
   </si>
   <si>
     <t xml:space="preserve">39.9027862548828</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1946067810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1036605834961</t>
+    <t xml:space="preserve">41.1946105957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1036643981934</t>
   </si>
   <si>
     <t xml:space="preserve">42.5342712402344</t>
@@ -1796,10 +1796,10 @@
     <t xml:space="preserve">40.8118476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7161560058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.912281036377</t>
+    <t xml:space="preserve">40.7161521911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9122772216797</t>
   </si>
   <si>
     <t xml:space="preserve">43.0605659484863</t>
@@ -1811,31 +1811,31 @@
     <t xml:space="preserve">44.2566909790039</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7829856872559</t>
+    <t xml:space="preserve">44.7829818725586</t>
   </si>
   <si>
     <t xml:space="preserve">43.4433250427246</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0174674987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6347007751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2041053771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9170303344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9265251159668</t>
+    <t xml:space="preserve">44.017463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6347045898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9170265197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9265213012695</t>
   </si>
   <si>
     <t xml:space="preserve">45.404972076416</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2614326477051</t>
+    <t xml:space="preserve">45.2614364624023</t>
   </si>
   <si>
     <t xml:space="preserve">45.5963516235352</t>
@@ -1850,25 +1850,25 @@
     <t xml:space="preserve">48.6105880737305</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1847343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9933471679688</t>
+    <t xml:space="preserve">49.1847381591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9933547973633</t>
   </si>
   <si>
     <t xml:space="preserve">49.7588768005371</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2804222106934</t>
+    <t xml:space="preserve">49.2804183959961</t>
   </si>
   <si>
     <t xml:space="preserve">49.6631813049316</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3761177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5674896240234</t>
+    <t xml:space="preserve">49.3761138916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5674934387207</t>
   </si>
   <si>
     <t xml:space="preserve">50.6200866699219</t>
@@ -1883,25 +1883,25 @@
     <t xml:space="preserve">52.6295776367188</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9597434997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8640594482422</t>
+    <t xml:space="preserve">51.9597473144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8640556335449</t>
   </si>
   <si>
     <t xml:space="preserve">51.6726722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4192123413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3235168457031</t>
+    <t xml:space="preserve">48.4192085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3235206604004</t>
   </si>
   <si>
     <t xml:space="preserve">50.0459480285645</t>
   </si>
   <si>
-    <t xml:space="preserve">51.385612487793</t>
+    <t xml:space="preserve">51.3856048583984</t>
   </si>
   <si>
     <t xml:space="preserve">50.907154083252</t>
@@ -1913,34 +1913,34 @@
     <t xml:space="preserve">50.4287071228027</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5338935852051</t>
+    <t xml:space="preserve">52.5338859558105</t>
   </si>
   <si>
     <t xml:space="preserve">54.0649299621582</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2994041442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4381980895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3666229248047</t>
+    <t xml:space="preserve">53.2994079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4381942749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3666191101074</t>
   </si>
   <si>
     <t xml:space="preserve">46.9838562011719</t>
   </si>
   <si>
-    <t xml:space="preserve">46.361873626709</t>
+    <t xml:space="preserve">46.3618774414062</t>
   </si>
   <si>
     <t xml:space="preserve">45.7398872375488</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9743614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.586856842041</t>
+    <t xml:space="preserve">44.974365234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5868606567383</t>
   </si>
   <si>
     <t xml:space="preserve">41.7687454223633</t>
@@ -1949,19 +1949,19 @@
     <t xml:space="preserve">36.6493263244629</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5967330932617</t>
+    <t xml:space="preserve">35.596736907959</t>
   </si>
   <si>
     <t xml:space="preserve">30.0945510864258</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4820575714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1854915618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.529899597168</t>
+    <t xml:space="preserve">31.4820613861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1854934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5299034118652</t>
   </si>
   <si>
     <t xml:space="preserve">31.0992984771729</t>
@@ -1970,19 +1970,19 @@
     <t xml:space="preserve">30.3816184997559</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9268989562988</t>
+    <t xml:space="preserve">34.9269027709961</t>
   </si>
   <si>
     <t xml:space="preserve">36.410099029541</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5010414123535</t>
+    <t xml:space="preserve">35.5010375976562</t>
   </si>
   <si>
     <t xml:space="preserve">35.3096656799316</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5441398620605</t>
+    <t xml:space="preserve">34.5441436767578</t>
   </si>
   <si>
     <t xml:space="preserve">35.0704383850098</t>
@@ -1994,10 +1994,10 @@
     <t xml:space="preserve">37.2234649658203</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1277694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2329521179199</t>
+    <t xml:space="preserve">37.1277732849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2329597473145</t>
   </si>
   <si>
     <t xml:space="preserve">40.429084777832</t>
@@ -2009,13 +2009,13 @@
     <t xml:space="preserve">44.7351379394531</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9791145324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4528160095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0700607299805</t>
+    <t xml:space="preserve">45.9791107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4528198242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0700569152832</t>
   </si>
   <si>
     <t xml:space="preserve">45.3571319580078</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">45.1179008483887</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4575576782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6441955566406</t>
+    <t xml:space="preserve">46.4575614929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6441917419434</t>
   </si>
   <si>
     <t xml:space="preserve">44.8786773681641</t>
@@ -2039,13 +2039,13 @@
     <t xml:space="preserve">45.1657485961914</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2088432312012</t>
+    <t xml:space="preserve">44.2088470458984</t>
   </si>
   <si>
     <t xml:space="preserve">43.1562538146973</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9217758178711</t>
+    <t xml:space="preserve">43.9217681884766</t>
   </si>
   <si>
     <t xml:space="preserve">41.8644371032715</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">48.7062835693359</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9407539367676</t>
+    <t xml:space="preserve">47.9407577514648</t>
   </si>
   <si>
     <t xml:space="preserve">48.5149040222168</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">51.4812965393066</t>
   </si>
   <si>
-    <t xml:space="preserve">51.194221496582</t>
+    <t xml:space="preserve">51.1942253112793</t>
   </si>
   <si>
     <t xml:space="preserve">51.768367767334</t>
@@ -2087,19 +2087,19 @@
     <t xml:space="preserve">51.2899169921875</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1080322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.96923828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.490795135498</t>
+    <t xml:space="preserve">53.1080284118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9692420959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4907913208008</t>
   </si>
   <si>
     <t xml:space="preserve">55.1175231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6916618347168</t>
+    <t xml:space="preserve">55.6916580200195</t>
   </si>
   <si>
     <t xml:space="preserve">55.5002822875977</t>
@@ -2108,16 +2108,16 @@
     <t xml:space="preserve">54.3519973754883</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6390686035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.830451965332</t>
+    <t xml:space="preserve">54.6390647888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8304481506348</t>
   </si>
   <si>
     <t xml:space="preserve">55.4045906066895</t>
   </si>
   <si>
-    <t xml:space="preserve">56.744255065918</t>
+    <t xml:space="preserve">56.7442474365234</t>
   </si>
   <si>
     <t xml:space="preserve">56.9356346130371</t>
@@ -2126,22 +2126,22 @@
     <t xml:space="preserve">57.1270179748535</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2658042907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9787330627441</t>
+    <t xml:space="preserve">56.2658004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9787368774414</t>
   </si>
   <si>
     <t xml:space="preserve">57.3183937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">58.6580505371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2227058410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7011489868164</t>
+    <t xml:space="preserve">58.6580543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2227020263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7011566162109</t>
   </si>
   <si>
     <t xml:space="preserve">56.3614921569824</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">57.988224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">58.8494415283203</t>
+    <t xml:space="preserve">58.8494338989258</t>
   </si>
   <si>
     <t xml:space="preserve">61.3373794555664</t>
@@ -2159,31 +2159,31 @@
     <t xml:space="preserve">63.4425659179688</t>
   </si>
   <si>
-    <t xml:space="preserve">62.2942848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3468742370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7296333312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6339454650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3037643432617</t>
+    <t xml:space="preserve">62.2942810058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3468704223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7296257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6339416503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3037796020508</t>
   </si>
   <si>
     <t xml:space="preserve">64.5908432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">65.9305114746094</t>
+    <t xml:space="preserve">65.9305038452148</t>
   </si>
   <si>
     <t xml:space="preserve">66.6960220336914</t>
   </si>
   <si>
-    <t xml:space="preserve">65.3563613891602</t>
+    <t xml:space="preserve">65.3563690185547</t>
   </si>
   <si>
     <t xml:space="preserve">66.9831008911133</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">69.1839752197266</t>
   </si>
   <si>
-    <t xml:space="preserve">71.2891464233398</t>
+    <t xml:space="preserve">71.2891540527344</t>
   </si>
   <si>
     <t xml:space="preserve">70.8107070922852</t>
@@ -2213,34 +2213,34 @@
     <t xml:space="preserve">70.6193313598633</t>
   </si>
   <si>
-    <t xml:space="preserve">71.7676010131836</t>
+    <t xml:space="preserve">71.7676086425781</t>
   </si>
   <si>
     <t xml:space="preserve">72.0546722412109</t>
   </si>
   <si>
-    <t xml:space="preserve">71.002082824707</t>
+    <t xml:space="preserve">71.0020751953125</t>
   </si>
   <si>
     <t xml:space="preserve">69.4710464477539</t>
   </si>
   <si>
-    <t xml:space="preserve">68.9925994873047</t>
+    <t xml:space="preserve">68.9925918579102</t>
   </si>
   <si>
     <t xml:space="preserve">69.9494857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8012084960938</t>
+    <t xml:space="preserve">68.8012161254883</t>
   </si>
   <si>
     <t xml:space="preserve">69.6624221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">76.5521087646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.7003936767578</t>
+    <t xml:space="preserve">76.552116394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.7003860473633</t>
   </si>
   <si>
     <t xml:space="preserve">75.8822860717773</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">77.7960891723633</t>
   </si>
   <si>
-    <t xml:space="preserve">79.4228286743164</t>
+    <t xml:space="preserve">79.4228134155273</t>
   </si>
   <si>
     <t xml:space="preserve">80.7624816894531</t>
@@ -2273,16 +2273,16 @@
     <t xml:space="preserve">82.0064468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">81.5279998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9107666015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.3892135620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4323120117188</t>
+    <t xml:space="preserve">81.5279922485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.910758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.3892211914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4323043823242</t>
   </si>
   <si>
     <t xml:space="preserve">81.1452407836914</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">81.7193756103516</t>
   </si>
   <si>
-    <t xml:space="preserve">81.815071105957</t>
+    <t xml:space="preserve">81.8150634765625</t>
   </si>
   <si>
     <t xml:space="preserve">83.3461151123047</t>
@@ -2303,13 +2303,13 @@
     <t xml:space="preserve">80.953857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">82.7719650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2935180664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.0305709838867</t>
+    <t xml:space="preserve">82.77197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2935256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.0305633544922</t>
   </si>
   <si>
     <t xml:space="preserve">79.3271255493164</t>
@@ -2318,10 +2318,10 @@
     <t xml:space="preserve">83.728874206543</t>
   </si>
   <si>
-    <t xml:space="preserve">82.1021499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.7434921264648</t>
+    <t xml:space="preserve">82.1021423339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.7434997558594</t>
   </si>
   <si>
     <t xml:space="preserve">79.5185089111328</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">79.8055725097656</t>
   </si>
   <si>
-    <t xml:space="preserve">82.4848861694336</t>
+    <t xml:space="preserve">82.4849014282227</t>
   </si>
   <si>
     <t xml:space="preserve">80.3797149658203</t>
@@ -2339,49 +2339,49 @@
     <t xml:space="preserve">78.6572952270508</t>
   </si>
   <si>
-    <t xml:space="preserve">78.4659042358398</t>
+    <t xml:space="preserve">78.4659194946289</t>
   </si>
   <si>
     <t xml:space="preserve">84.6857681274414</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3556137084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0590362548828</t>
+    <t xml:space="preserve">85.3556060791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0590438842773</t>
   </si>
   <si>
     <t xml:space="preserve">85.9297485351562</t>
   </si>
   <si>
-    <t xml:space="preserve">87.173713684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.269401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3220062255859</t>
+    <t xml:space="preserve">87.1737213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2694091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3220138549805</t>
   </si>
   <si>
     <t xml:space="preserve">86.7909469604492</t>
   </si>
   <si>
-    <t xml:space="preserve">90.905632019043</t>
+    <t xml:space="preserve">90.9056396484375</t>
   </si>
   <si>
     <t xml:space="preserve">91.3840866088867</t>
   </si>
   <si>
-    <t xml:space="preserve">93.1065139770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.8815078735352</t>
+    <t xml:space="preserve">93.1065216064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.8815155029297</t>
   </si>
   <si>
     <t xml:space="preserve">97.2211761474609</t>
   </si>
   <si>
-    <t xml:space="preserve">100.474647521973</t>
+    <t xml:space="preserve">100.474655151367</t>
   </si>
   <si>
     <t xml:space="preserve">101.622924804688</t>
@@ -2390,10 +2390,10 @@
     <t xml:space="preserve">101.240173339844</t>
   </si>
   <si>
-    <t xml:space="preserve">97.9866943359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5608444213867</t>
+    <t xml:space="preserve">97.9867095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5608367919922</t>
   </si>
   <si>
     <t xml:space="preserve">99.9004974365234</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">95.6901397705078</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8289260864258</t>
+    <t xml:space="preserve">94.8289337158203</t>
   </si>
   <si>
     <t xml:space="preserve">95.307373046875</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">94.2547836303711</t>
   </si>
   <si>
-    <t xml:space="preserve">94.446174621582</t>
+    <t xml:space="preserve">94.4461669921875</t>
   </si>
   <si>
     <t xml:space="preserve">97.0298080444336</t>
@@ -2423,52 +2423,52 @@
     <t xml:space="preserve">94.541862487793</t>
   </si>
   <si>
-    <t xml:space="preserve">94.1591033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8720321655273</t>
+    <t xml:space="preserve">94.1591110229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8720245361328</t>
   </si>
   <si>
     <t xml:space="preserve">94.0634155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">93.3935775756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6806411743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9151153564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.2978897094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.723747253418</t>
+    <t xml:space="preserve">93.3935699462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6806488037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9151229858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.2978820800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7237548828125</t>
   </si>
   <si>
     <t xml:space="preserve">94.3504791259766</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6039505004883</t>
+    <t xml:space="preserve">97.6039428710938</t>
   </si>
   <si>
     <t xml:space="preserve">101.43155670166</t>
   </si>
   <si>
-    <t xml:space="preserve">104.876396179199</t>
+    <t xml:space="preserve">104.876388549805</t>
   </si>
   <si>
     <t xml:space="preserve">104.493629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">106.598808288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.364326477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.660903930664</t>
+    <t xml:space="preserve">106.598815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.364334106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.66089630127</t>
   </si>
   <si>
     <t xml:space="preserve">110.235046386719</t>
@@ -2477,16 +2477,16 @@
     <t xml:space="preserve">105.64192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">106.216064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.9384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.555732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.469528198242</t>
+    <t xml:space="preserve">106.21605682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.938484191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.555717468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.469520568848</t>
   </si>
   <si>
     <t xml:space="preserve">107.747100830078</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">108.703994750977</t>
   </si>
   <si>
-    <t xml:space="preserve">102.197074890137</t>
+    <t xml:space="preserve">102.197082519531</t>
   </si>
   <si>
     <t xml:space="preserve">99.5177536010742</t>
@@ -2510,10 +2510,10 @@
     <t xml:space="preserve">103.536735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">106.024673461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.981590270996</t>
+    <t xml:space="preserve">106.024681091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.981582641602</t>
   </si>
   <si>
     <t xml:space="preserve">108.512619018555</t>
@@ -2522,13 +2522,13 @@
     <t xml:space="preserve">105.833290100098</t>
   </si>
   <si>
-    <t xml:space="preserve">101.048789978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.388442993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.15397644043</t>
+    <t xml:space="preserve">101.048782348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.388450622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.153968811035</t>
   </si>
   <si>
     <t xml:space="preserve">102.962593078613</t>
@@ -2540,49 +2540,49 @@
     <t xml:space="preserve">102.005683898926</t>
   </si>
   <si>
-    <t xml:space="preserve">103.919486999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.407432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.086761474609</t>
+    <t xml:space="preserve">103.919494628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.407440185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.086769104004</t>
   </si>
   <si>
     <t xml:space="preserve">110.809181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">113.679901123047</t>
+    <t xml:space="preserve">113.679893493652</t>
   </si>
   <si>
     <t xml:space="preserve">110.043663024902</t>
   </si>
   <si>
-    <t xml:space="preserve">107.172958374023</t>
+    <t xml:space="preserve">107.172950744629</t>
   </si>
   <si>
     <t xml:space="preserve">111.000564575195</t>
   </si>
   <si>
-    <t xml:space="preserve">112.914367675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.852279663086</t>
+    <t xml:space="preserve">112.914375305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.852294921875</t>
   </si>
   <si>
     <t xml:space="preserve">110.426422119141</t>
   </si>
   <si>
-    <t xml:space="preserve">111.383323669434</t>
+    <t xml:space="preserve">111.383316040039</t>
   </si>
   <si>
     <t xml:space="preserve">112.340225219727</t>
   </si>
   <si>
-    <t xml:space="preserve">114.445411682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.297119140625</t>
+    <t xml:space="preserve">114.445404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.297134399414</t>
   </si>
   <si>
     <t xml:space="preserve">112.722984313965</t>
@@ -2591,28 +2591,28 @@
     <t xml:space="preserve">115.019554138184</t>
   </si>
   <si>
-    <t xml:space="preserve">115.593704223633</t>
+    <t xml:space="preserve">115.593688964844</t>
   </si>
   <si>
     <t xml:space="preserve">115.210929870605</t>
   </si>
   <si>
-    <t xml:space="preserve">116.741966247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.167839050293</t>
+    <t xml:space="preserve">116.741973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.167831420898</t>
   </si>
   <si>
     <t xml:space="preserve">115.78507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">116.550590515137</t>
+    <t xml:space="preserve">116.550598144531</t>
   </si>
   <si>
     <t xml:space="preserve">119.804054260254</t>
   </si>
   <si>
-    <t xml:space="preserve">120.186820983887</t>
+    <t xml:space="preserve">120.186813354492</t>
   </si>
   <si>
     <t xml:space="preserve">122.100616455078</t>
@@ -2624,58 +2624,58 @@
     <t xml:space="preserve">123.631652832031</t>
   </si>
   <si>
-    <t xml:space="preserve">131.478256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.267890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.459266662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.990325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.05241394043</t>
+    <t xml:space="preserve">131.478240966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.267883300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.459251403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.990310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.052398681641</t>
   </si>
   <si>
     <t xml:space="preserve">134.157577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">133.774810791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.626541137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.435150146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.923095703125</t>
+    <t xml:space="preserve">133.774826049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.626556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.435134887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.923110961914</t>
   </si>
   <si>
     <t xml:space="preserve">136.645523071289</t>
   </si>
   <si>
-    <t xml:space="preserve">137.411056518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.305862426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.861022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.731719970703</t>
+    <t xml:space="preserve">137.411041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.30583190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.86100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.731735229492</t>
   </si>
   <si>
     <t xml:space="preserve">136.262756347656</t>
   </si>
   <si>
-    <t xml:space="preserve">137.793807983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.176559448242</t>
+    <t xml:space="preserve">137.793792724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.176574707031</t>
   </si>
   <si>
     <t xml:space="preserve">137.028289794922</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">139.898971557617</t>
   </si>
   <si>
-    <t xml:space="preserve">136.454162597656</t>
+    <t xml:space="preserve">136.454147338867</t>
   </si>
   <si>
     <t xml:space="preserve">138.750686645508</t>
@@ -2696,13 +2696,13 @@
     <t xml:space="preserve">139.324844360352</t>
   </si>
   <si>
-    <t xml:space="preserve">137.985198974609</t>
+    <t xml:space="preserve">137.98518371582</t>
   </si>
   <si>
     <t xml:space="preserve">135.497253417969</t>
   </si>
   <si>
-    <t xml:space="preserve">144.492111206055</t>
+    <t xml:space="preserve">144.492126464844</t>
   </si>
   <si>
     <t xml:space="preserve">144.874877929688</t>
@@ -2711,13 +2711,13 @@
     <t xml:space="preserve">144.109344482422</t>
   </si>
   <si>
-    <t xml:space="preserve">142.195556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.726577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.917984008789</t>
+    <t xml:space="preserve">142.195541381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.726593017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.917953491211</t>
   </si>
   <si>
     <t xml:space="preserve">144.683486938477</t>
@@ -2738,19 +2738,19 @@
     <t xml:space="preserve">149.276641845703</t>
   </si>
   <si>
-    <t xml:space="preserve">150.999038696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.424911499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.48698425293</t>
+    <t xml:space="preserve">150.999053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.424896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.486999511719</t>
   </si>
   <si>
     <t xml:space="preserve">152.33869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">155.400787353516</t>
+    <t xml:space="preserve">155.400772094727</t>
   </si>
   <si>
     <t xml:space="preserve">151.190414428711</t>
@@ -2777,10 +2777,10 @@
     <t xml:space="preserve">163.438751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">163.821533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.606018066406</t>
+    <t xml:space="preserve">163.821517944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.606033325195</t>
   </si>
   <si>
     <t xml:space="preserve">173.773300170898</t>
@@ -2789,13 +2789,13 @@
     <t xml:space="preserve">170.32844543457</t>
   </si>
   <si>
-    <t xml:space="preserve">165.161193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.03190612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.352584838867</t>
+    <t xml:space="preserve">165.161178588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.031875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.352569580078</t>
   </si>
   <si>
     <t xml:space="preserve">160.759429931641</t>
@@ -2804,25 +2804,25 @@
     <t xml:space="preserve">162.099105834961</t>
   </si>
   <si>
-    <t xml:space="preserve">171.668121337891</t>
+    <t xml:space="preserve">171.668106079102</t>
   </si>
   <si>
     <t xml:space="preserve">167.074981689453</t>
   </si>
   <si>
-    <t xml:space="preserve">161.93049621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.353561401367</t>
+    <t xml:space="preserve">161.930511474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.353591918945</t>
   </si>
   <si>
     <t xml:space="preserve">160.58430480957</t>
   </si>
   <si>
-    <t xml:space="preserve">159.045776367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.12239074707</t>
+    <t xml:space="preserve">159.045761108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.122375488281</t>
   </si>
   <si>
     <t xml:space="preserve">145.583618164062</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">148.083724975586</t>
   </si>
   <si>
-    <t xml:space="preserve">151.737731933594</t>
+    <t xml:space="preserve">151.737747192383</t>
   </si>
   <si>
     <t xml:space="preserve">149.622268676758</t>
@@ -2855,34 +2855,34 @@
     <t xml:space="preserve">155.968704223633</t>
   </si>
   <si>
-    <t xml:space="preserve">154.43017578125</t>
+    <t xml:space="preserve">154.430191040039</t>
   </si>
   <si>
     <t xml:space="preserve">160.776611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">166.353790283203</t>
+    <t xml:space="preserve">166.353805541992</t>
   </si>
   <si>
     <t xml:space="preserve">170.200119018555</t>
   </si>
   <si>
-    <t xml:space="preserve">168.469284057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.430633544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.007598876953</t>
+    <t xml:space="preserve">168.469268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.430618286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.007583618164</t>
   </si>
   <si>
     <t xml:space="preserve">162.507461547852</t>
   </si>
   <si>
-    <t xml:space="preserve">163.46907043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.584533691406</t>
+    <t xml:space="preserve">163.469055175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.584548950195</t>
   </si>
   <si>
     <t xml:space="preserve">161.161270141602</t>
@@ -2894,10 +2894,10 @@
     <t xml:space="preserve">161.738189697266</t>
   </si>
   <si>
-    <t xml:space="preserve">168.853927612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.508163452148</t>
+    <t xml:space="preserve">168.853897094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.508178710938</t>
   </si>
   <si>
     <t xml:space="preserve">175.584991455078</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">180.392913818359</t>
   </si>
   <si>
-    <t xml:space="preserve">180.777526855469</t>
+    <t xml:space="preserve">180.777542114258</t>
   </si>
   <si>
     <t xml:space="preserve">178.469757080078</t>
@@ -2930,16 +2930,16 @@
     <t xml:space="preserve">168.276962280273</t>
   </si>
   <si>
-    <t xml:space="preserve">169.046234130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.584747314453</t>
+    <t xml:space="preserve">169.046249389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.584762573242</t>
   </si>
   <si>
     <t xml:space="preserve">167.507705688477</t>
   </si>
   <si>
-    <t xml:space="preserve">174.046463012695</t>
+    <t xml:space="preserve">174.046478271484</t>
   </si>
   <si>
     <t xml:space="preserve">170.96940612793</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">169.623184204102</t>
   </si>
   <si>
-    <t xml:space="preserve">169.238540649414</t>
+    <t xml:space="preserve">169.238555908203</t>
   </si>
   <si>
     <t xml:space="preserve">175.008041381836</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">172.700241088867</t>
   </si>
   <si>
-    <t xml:space="preserve">172.123306274414</t>
+    <t xml:space="preserve">172.123291015625</t>
   </si>
   <si>
     <t xml:space="preserve">171.93098449707</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">167.315383911133</t>
   </si>
   <si>
-    <t xml:space="preserve">163.85368347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.738403320312</t>
+    <t xml:space="preserve">163.853668212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.738418579102</t>
   </si>
   <si>
     <t xml:space="preserve">164.238311767578</t>
@@ -2981,16 +2981,16 @@
     <t xml:space="preserve">167.700012207031</t>
   </si>
   <si>
-    <t xml:space="preserve">165.392211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.160797119141</t>
+    <t xml:space="preserve">165.392227172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.160781860352</t>
   </si>
   <si>
     <t xml:space="preserve">158.853454589844</t>
   </si>
   <si>
-    <t xml:space="preserve">158.468841552734</t>
+    <t xml:space="preserve">158.468826293945</t>
   </si>
   <si>
     <t xml:space="preserve">157.314926147461</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">156.930282592773</t>
   </si>
   <si>
-    <t xml:space="preserve">156.161026000977</t>
+    <t xml:space="preserve">156.161010742188</t>
   </si>
   <si>
     <t xml:space="preserve">152.314682006836</t>
@@ -3014,22 +3014,22 @@
     <t xml:space="preserve">146.929824829102</t>
   </si>
   <si>
-    <t xml:space="preserve">151.353103637695</t>
+    <t xml:space="preserve">151.353088378906</t>
   </si>
   <si>
     <t xml:space="preserve">153.468597412109</t>
   </si>
   <si>
-    <t xml:space="preserve">153.276245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.122604370117</t>
+    <t xml:space="preserve">153.276260375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.122619628906</t>
   </si>
   <si>
     <t xml:space="preserve">151.930053710938</t>
   </si>
   <si>
-    <t xml:space="preserve">146.545196533203</t>
+    <t xml:space="preserve">146.545211791992</t>
   </si>
   <si>
     <t xml:space="preserve">140.968017578125</t>
@@ -3038,13 +3038,13 @@
     <t xml:space="preserve">136.92936706543</t>
   </si>
   <si>
-    <t xml:space="preserve">138.660232543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.698425292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.506103515625</t>
+    <t xml:space="preserve">138.660217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.69841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.506088256836</t>
   </si>
   <si>
     <t xml:space="preserve">130.198287963867</t>
@@ -3056,13 +3056,13 @@
     <t xml:space="preserve">130.005981445312</t>
   </si>
   <si>
-    <t xml:space="preserve">130.77522277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.852081298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.621353149414</t>
+    <t xml:space="preserve">130.775238037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.852066040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.621337890625</t>
   </si>
   <si>
     <t xml:space="preserve">132.890716552734</t>
@@ -3074,13 +3074,13 @@
     <t xml:space="preserve">136.160110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">138.467910766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.583145141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.813430786133</t>
+    <t xml:space="preserve">138.467895507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.583160400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.813438415527</t>
   </si>
   <si>
     <t xml:space="preserve">118.659301757812</t>
@@ -3089,55 +3089,55 @@
     <t xml:space="preserve">125.582702636719</t>
   </si>
   <si>
-    <t xml:space="preserve">125.198066711426</t>
+    <t xml:space="preserve">125.198059082031</t>
   </si>
   <si>
     <t xml:space="preserve">137.314010620117</t>
   </si>
   <si>
-    <t xml:space="preserve">138.852523803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.891189575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.391052246094</t>
+    <t xml:space="preserve">138.8525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.891174316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.391067504883</t>
   </si>
   <si>
     <t xml:space="preserve">145.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">145.00666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.775924682617</t>
+    <t xml:space="preserve">145.006652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.775939941406</t>
   </si>
   <si>
     <t xml:space="preserve">144.814346313477</t>
   </si>
   <si>
-    <t xml:space="preserve">148.276031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.275802612305</t>
+    <t xml:space="preserve">148.27604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.275817871094</t>
   </si>
   <si>
     <t xml:space="preserve">142.60270690918</t>
   </si>
   <si>
-    <t xml:space="preserve">142.698867797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.08349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.525634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.160354614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.198760986328</t>
+    <t xml:space="preserve">142.698852539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.083511352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.525650024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.160339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.198745727539</t>
   </si>
   <si>
     <t xml:space="preserve">139.910278320312</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">129.525177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">129.90983581543</t>
+    <t xml:space="preserve">129.909820556641</t>
   </si>
   <si>
     <t xml:space="preserve">133.371520996094</t>
@@ -3188,10 +3188,10 @@
     <t xml:space="preserve">118.563148498535</t>
   </si>
   <si>
-    <t xml:space="preserve">109.81273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.56290435791</t>
+    <t xml:space="preserve">109.812728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.562911987305</t>
   </si>
   <si>
     <t xml:space="preserve">115.389915466309</t>
@@ -3206,13 +3206,13 @@
     <t xml:space="preserve">118.08235168457</t>
   </si>
   <si>
-    <t xml:space="preserve">122.31330871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.293983459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.101669311523</t>
+    <t xml:space="preserve">122.313316345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.293991088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.101676940918</t>
   </si>
   <si>
     <t xml:space="preserve">119.236251831055</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">120.486312866211</t>
   </si>
   <si>
-    <t xml:space="preserve">116.736145019531</t>
+    <t xml:space="preserve">116.736137390137</t>
   </si>
   <si>
     <t xml:space="preserve">116.832298278809</t>
@@ -3230,34 +3230,34 @@
     <t xml:space="preserve">119.043937683105</t>
   </si>
   <si>
-    <t xml:space="preserve">121.736366271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.621116638184</t>
+    <t xml:space="preserve">121.736358642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.621109008789</t>
   </si>
   <si>
     <t xml:space="preserve">123.274894714355</t>
   </si>
   <si>
-    <t xml:space="preserve">121.544052124023</t>
+    <t xml:space="preserve">121.544044494629</t>
   </si>
   <si>
     <t xml:space="preserve">124.044158935547</t>
   </si>
   <si>
-    <t xml:space="preserve">124.332633972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.986640930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.659774780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.698188781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.178749084473</t>
+    <t xml:space="preserve">124.332649230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.986656188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.659759521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.698173522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.178741455078</t>
   </si>
   <si>
     <t xml:space="preserve">114.52449798584</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">112.889801025391</t>
   </si>
   <si>
-    <t xml:space="preserve">114.236030578613</t>
+    <t xml:space="preserve">114.236022949219</t>
   </si>
   <si>
     <t xml:space="preserve">111.062797546387</t>
@@ -3275,10 +3275,10 @@
     <t xml:space="preserve">112.216690063477</t>
   </si>
   <si>
-    <t xml:space="preserve">112.505172729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.947547912598</t>
+    <t xml:space="preserve">112.505180358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.947540283203</t>
   </si>
   <si>
     <t xml:space="preserve">116.447662353516</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">115.197601318359</t>
   </si>
   <si>
-    <t xml:space="preserve">119.140090942383</t>
+    <t xml:space="preserve">119.140098571777</t>
   </si>
   <si>
     <t xml:space="preserve">119.909355163574</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">119.428565979004</t>
   </si>
   <si>
-    <t xml:space="preserve">117.890022277832</t>
+    <t xml:space="preserve">117.890029907227</t>
   </si>
   <si>
     <t xml:space="preserve">115.293762207031</t>
@@ -3305,49 +3305,49 @@
     <t xml:space="preserve">113.178276062012</t>
   </si>
   <si>
-    <t xml:space="preserve">119.332412719727</t>
+    <t xml:space="preserve">119.332397460938</t>
   </si>
   <si>
     <t xml:space="preserve">123.082580566406</t>
   </si>
   <si>
-    <t xml:space="preserve">125.390365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.986419677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.274673461914</t>
+    <t xml:space="preserve">125.39037322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.986427307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.274658203125</t>
   </si>
   <si>
     <t xml:space="preserve">119.71703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">120.774787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.659538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.948257446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.736801147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.679061889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.83275604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.794334411621</t>
+    <t xml:space="preserve">120.774780273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.659530639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.9482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.73681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.679077148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.832748413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.794319152832</t>
   </si>
   <si>
     <t xml:space="preserve">128.46745300293</t>
   </si>
   <si>
-    <t xml:space="preserve">132.602249145508</t>
+    <t xml:space="preserve">132.602233886719</t>
   </si>
   <si>
     <t xml:space="preserve">129.044387817383</t>
@@ -3356,25 +3356,25 @@
     <t xml:space="preserve">131.159881591797</t>
   </si>
   <si>
-    <t xml:space="preserve">125.967323303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.351943969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.563369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.313545227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.371307373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.736587524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.447891235352</t>
+    <t xml:space="preserve">125.967330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.351951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.563362121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.313537597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.371276855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.736602783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.447883605957</t>
   </si>
   <si>
     <t xml:space="preserve">117.601554870605</t>
@@ -3389,28 +3389,28 @@
     <t xml:space="preserve">121.063255310059</t>
   </si>
   <si>
-    <t xml:space="preserve">117.505401611328</t>
+    <t xml:space="preserve">117.505393981934</t>
   </si>
   <si>
     <t xml:space="preserve">115.870704650879</t>
   </si>
   <si>
-    <t xml:space="preserve">116.255348205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.312858581543</t>
+    <t xml:space="preserve">116.255340576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.312850952148</t>
   </si>
   <si>
     <t xml:space="preserve">115.582237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">115.67839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.178504943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.909126281738</t>
+    <t xml:space="preserve">115.678398132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.178512573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.909133911133</t>
   </si>
   <si>
     <t xml:space="preserve">106.596168518066</t>
@@ -3431,37 +3431,37 @@
     <t xml:space="preserve">105.917831420898</t>
   </si>
   <si>
-    <t xml:space="preserve">102.816848754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.01473236084</t>
+    <t xml:space="preserve">102.816841125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.014739990234</t>
   </si>
   <si>
     <t xml:space="preserve">102.041610717773</t>
   </si>
   <si>
-    <t xml:space="preserve">108.437370300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.212615966797</t>
+    <t xml:space="preserve">108.437377929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.212623596191</t>
   </si>
   <si>
     <t xml:space="preserve">113.185752868652</t>
   </si>
   <si>
-    <t xml:space="preserve">111.441452026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.829071044922</t>
+    <t xml:space="preserve">111.441444396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.829078674316</t>
   </si>
   <si>
     <t xml:space="preserve">107.274505615234</t>
   </si>
   <si>
-    <t xml:space="preserve">104.851867675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.658050537109</t>
+    <t xml:space="preserve">104.851860046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.658058166504</t>
   </si>
   <si>
     <t xml:space="preserve">101.847793579102</t>
@@ -3473,16 +3473,16 @@
     <t xml:space="preserve">103.495193481445</t>
   </si>
   <si>
-    <t xml:space="preserve">104.076629638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.402366638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.693069458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.860023498535</t>
+    <t xml:space="preserve">104.076622009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.402359008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.693077087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.860015869141</t>
   </si>
   <si>
     <t xml:space="preserve">116.189826965332</t>
@@ -3491,31 +3491,31 @@
     <t xml:space="preserve">114.348617553711</t>
   </si>
   <si>
-    <t xml:space="preserve">109.794052124023</t>
+    <t xml:space="preserve">109.794059753418</t>
   </si>
   <si>
     <t xml:space="preserve">107.468315124512</t>
   </si>
   <si>
-    <t xml:space="preserve">106.305450439453</t>
+    <t xml:space="preserve">106.305442810059</t>
   </si>
   <si>
     <t xml:space="preserve">102.332321166992</t>
   </si>
   <si>
-    <t xml:space="preserve">100.878730773926</t>
+    <t xml:space="preserve">100.87873840332</t>
   </si>
   <si>
     <t xml:space="preserve">103.979721069336</t>
   </si>
   <si>
-    <t xml:space="preserve">108.340476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.643417358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.515556335449</t>
+    <t xml:space="preserve">108.340469360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.643409729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.515563964844</t>
   </si>
   <si>
     <t xml:space="preserve">117.837219238281</t>
@@ -3524,13 +3524,13 @@
     <t xml:space="preserve">116.771255493164</t>
   </si>
   <si>
-    <t xml:space="preserve">114.445518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.736236572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.026947021484</t>
+    <t xml:space="preserve">114.445526123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.73624420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.026954650879</t>
   </si>
   <si>
     <t xml:space="preserve">115.317672729492</t>
@@ -3548,7 +3548,7 @@
     <t xml:space="preserve">113.476463317871</t>
   </si>
   <si>
-    <t xml:space="preserve">114.251708984375</t>
+    <t xml:space="preserve">114.25171661377</t>
   </si>
   <si>
     <t xml:space="preserve">114.833145141602</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">118.612464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">112.99193572998</t>
+    <t xml:space="preserve">112.991943359375</t>
   </si>
   <si>
     <t xml:space="preserve">111.053825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">112.701232910156</t>
+    <t xml:space="preserve">112.701225280762</t>
   </si>
   <si>
     <t xml:space="preserve">112.604316711426</t>
@@ -3584,34 +3584,34 @@
     <t xml:space="preserve">107.080696105957</t>
   </si>
   <si>
-    <t xml:space="preserve">110.37548828125</t>
+    <t xml:space="preserve">110.375495910645</t>
   </si>
   <si>
     <t xml:space="preserve">108.534278869629</t>
   </si>
   <si>
-    <t xml:space="preserve">110.181678771973</t>
+    <t xml:space="preserve">110.181671142578</t>
   </si>
   <si>
     <t xml:space="preserve">109.890960693359</t>
   </si>
   <si>
-    <t xml:space="preserve">111.247634887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.282661437988</t>
+    <t xml:space="preserve">111.247650146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.282653808594</t>
   </si>
   <si>
     <t xml:space="preserve">112.410507202148</t>
   </si>
   <si>
-    <t xml:space="preserve">114.639343261719</t>
+    <t xml:space="preserve">114.63932800293</t>
   </si>
   <si>
     <t xml:space="preserve">117.934120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">117.255783081055</t>
+    <t xml:space="preserve">117.25577545166</t>
   </si>
   <si>
     <t xml:space="preserve">117.352691650391</t>
@@ -3638,10 +3638,10 @@
     <t xml:space="preserve">120.550575256348</t>
   </si>
   <si>
-    <t xml:space="preserve">122.779411315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.263931274414</t>
+    <t xml:space="preserve">122.779403686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.26392364502</t>
   </si>
   <si>
     <t xml:space="preserve">121.810340881348</t>
@@ -3653,13 +3653,13 @@
     <t xml:space="preserve">123.748458862305</t>
   </si>
   <si>
-    <t xml:space="preserve">131.985443115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.888549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.179260253906</t>
+    <t xml:space="preserve">131.985427856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.888534545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.179244995117</t>
   </si>
   <si>
     <t xml:space="preserve">130.531845092773</t>
@@ -3671,22 +3671,22 @@
     <t xml:space="preserve">127.043251037598</t>
   </si>
   <si>
-    <t xml:space="preserve">124.814422607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.686561584473</t>
+    <t xml:space="preserve">124.814430236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.686576843262</t>
   </si>
   <si>
     <t xml:space="preserve">126.849433898926</t>
   </si>
   <si>
-    <t xml:space="preserve">127.333953857422</t>
+    <t xml:space="preserve">127.333961486816</t>
   </si>
   <si>
     <t xml:space="preserve">126.946342468262</t>
   </si>
   <si>
-    <t xml:space="preserve">124.136093139648</t>
+    <t xml:space="preserve">124.136085510254</t>
   </si>
   <si>
     <t xml:space="preserve">123.845367431641</t>
@@ -3695,10 +3695,10 @@
     <t xml:space="preserve">121.422729492188</t>
   </si>
   <si>
-    <t xml:space="preserve">121.325813293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.259864807129</t>
+    <t xml:space="preserve">121.325820922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.259857177734</t>
   </si>
   <si>
     <t xml:space="preserve">120.35676574707</t>
@@ -3707,28 +3707,28 @@
     <t xml:space="preserve">118.321746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">116.868156433105</t>
+    <t xml:space="preserve">116.8681640625</t>
   </si>
   <si>
     <t xml:space="preserve">115.802200317383</t>
   </si>
   <si>
-    <t xml:space="preserve">113.86408996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.960998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.088836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.472389221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.825004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.414581298828</t>
+    <t xml:space="preserve">113.864097595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.960990905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.088844299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.472396850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.824996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.414573669434</t>
   </si>
   <si>
     <t xml:space="preserve">109.987861633301</t>
@@ -3749,16 +3749,16 @@
     <t xml:space="preserve">116.286727905273</t>
   </si>
   <si>
-    <t xml:space="preserve">119.193901062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.096992492676</t>
+    <t xml:space="preserve">119.193893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.09700012207</t>
   </si>
   <si>
     <t xml:space="preserve">119.678428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">116.383636474609</t>
+    <t xml:space="preserve">116.383628845215</t>
   </si>
   <si>
     <t xml:space="preserve">115.123870849609</t>
@@ -3770,19 +3770,19 @@
     <t xml:space="preserve">110.569297790527</t>
   </si>
   <si>
-    <t xml:space="preserve">110.956916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.921913146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.952842712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.565231323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.045684814453</t>
+    <t xml:space="preserve">110.956924438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.921905517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.952850341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.565223693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.045677185059</t>
   </si>
   <si>
     <t xml:space="preserve">104.754959106445</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">103.204475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">100.588020324707</t>
+    <t xml:space="preserve">100.588027954102</t>
   </si>
   <si>
     <t xml:space="preserve">100.297302246094</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">103.107566833496</t>
   </si>
   <si>
-    <t xml:space="preserve">104.561157226562</t>
+    <t xml:space="preserve">104.561149597168</t>
   </si>
   <si>
     <t xml:space="preserve">107.37141418457</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">111.150726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">110.763114929199</t>
+    <t xml:space="preserve">110.763107299805</t>
   </si>
   <si>
     <t xml:space="preserve">109.503341674805</t>
@@ -3851,7 +3851,7 @@
     <t xml:space="preserve">109.115715026855</t>
   </si>
   <si>
-    <t xml:space="preserve">110.278587341309</t>
+    <t xml:space="preserve">110.278579711914</t>
   </si>
   <si>
     <t xml:space="preserve">109.697143554688</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">100.975639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">100.200401306152</t>
+    <t xml:space="preserve">100.200393676758</t>
   </si>
   <si>
     <t xml:space="preserve">100.491111755371</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">101.26636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">101.65397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.394203186035</t>
+    <t xml:space="preserve">101.653984069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.39421081543</t>
   </si>
   <si>
     <t xml:space="preserve">99.3282470703125</t>
@@ -3899,13 +3899,13 @@
     <t xml:space="preserve">99.6189651489258</t>
   </si>
   <si>
-    <t xml:space="preserve">99.2313385009766</t>
+    <t xml:space="preserve">99.2313461303711</t>
   </si>
   <si>
     <t xml:space="preserve">102.138511657715</t>
   </si>
   <si>
-    <t xml:space="preserve">101.750885009766</t>
+    <t xml:space="preserve">101.75089263916</t>
   </si>
   <si>
     <t xml:space="preserve">99.8127746582031</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">97.1963272094727</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6808547973633</t>
+    <t xml:space="preserve">97.6808471679688</t>
   </si>
   <si>
     <t xml:space="preserve">99.0078277587891</t>
@@ -5316,6 +5316,9 @@
   </si>
   <si>
     <t xml:space="preserve">92.6500015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.5</t>
   </si>
 </sst>
 </file>
@@ -71902,7 +71905,7 @@
     </row>
     <row r="2549">
       <c r="A2549" s="1" t="n">
-        <v>46035.6911574074</v>
+        <v>46035.3333333333</v>
       </c>
       <c r="B2549" t="n">
         <v>35171</v>
@@ -71923,6 +71926,32 @@
         <v>1767</v>
       </c>
       <c r="H2549" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" s="1" t="n">
+        <v>46036.6912037037</v>
+      </c>
+      <c r="B2550" t="n">
+        <v>81632</v>
+      </c>
+      <c r="C2550" t="n">
+        <v>96.5500030517578</v>
+      </c>
+      <c r="D2550" t="n">
+        <v>92.8499984741211</v>
+      </c>
+      <c r="E2550" t="n">
+        <v>93.0999984741211</v>
+      </c>
+      <c r="F2550" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="G2550" t="s">
+        <v>1768</v>
+      </c>
+      <c r="H2550" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="1769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="1770">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5495910644531</t>
+    <t xml:space="preserve">13.5495901107788</t>
   </si>
   <si>
     <t xml:space="preserve">SES.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5321073532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2523736953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9464149475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1125078201294</t>
+    <t xml:space="preserve">13.5321063995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2523746490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9464168548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1125068664551</t>
   </si>
   <si>
     <t xml:space="preserve">12.858998298645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0513143539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9901237487793</t>
+    <t xml:space="preserve">13.0513153076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9901247024536</t>
   </si>
   <si>
     <t xml:space="preserve">12.9376735687256</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1037645339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0250911712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8502559661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2383413314819</t>
+    <t xml:space="preserve">13.1037654876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0250902175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8502569198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2383403778076</t>
   </si>
   <si>
     <t xml:space="preserve">12.5880069732666</t>
@@ -86,19 +86,19 @@
     <t xml:space="preserve">12.7890653610229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7191314697266</t>
+    <t xml:space="preserve">12.7191324234009</t>
   </si>
   <si>
     <t xml:space="preserve">12.6841650009155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6054887771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.325756072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0460224151611</t>
+    <t xml:space="preserve">12.605489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3257579803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0460214614868</t>
   </si>
   <si>
     <t xml:space="preserve">12.1771488189697</t>
@@ -107,154 +107,154 @@
     <t xml:space="preserve">12.1421823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9270906448364</t>
+    <t xml:space="preserve">10.9270896911621</t>
   </si>
   <si>
     <t xml:space="preserve">10.9795389175415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3641738891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4515895843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0984725952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.107213973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.888671875</t>
+    <t xml:space="preserve">11.3641719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4515886306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0984735488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1072149276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8886728286743</t>
   </si>
   <si>
     <t xml:space="preserve">11.9760885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9323806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0110559463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0809907913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8012561798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334390640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8274793624878</t>
+    <t xml:space="preserve">11.9323816299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0110569000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0809898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8012571334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334400177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8274803161621</t>
   </si>
   <si>
     <t xml:space="preserve">12.0635061264038</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5005893707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6754245758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7978067398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1649560928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1562147140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0687990188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1212482452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.19118309021</t>
+    <t xml:space="preserve">12.5005903244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6754236221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7978076934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1649570465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1562156677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0687980651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1212501525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1911811828613</t>
   </si>
   <si>
     <t xml:space="preserve">12.7540979385376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8939657211304</t>
+    <t xml:space="preserve">12.8939647674561</t>
   </si>
   <si>
     <t xml:space="preserve">12.9027080535889</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0600576400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1999244689941</t>
+    <t xml:space="preserve">13.0600566864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1999235153198</t>
   </si>
   <si>
     <t xml:space="preserve">12.9813823699951</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4534330368042</t>
+    <t xml:space="preserve">13.4534320831299</t>
   </si>
   <si>
     <t xml:space="preserve">13.7069406509399</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4709157943726</t>
+    <t xml:space="preserve">13.4709148406982</t>
   </si>
   <si>
     <t xml:space="preserve">13.4621734619141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2086639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3223066329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0950222015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9988651275635</t>
+    <t xml:space="preserve">13.208664894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3223075866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0950241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9988641738892</t>
   </si>
   <si>
     <t xml:space="preserve">12.640456199646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4481391906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3782052993774</t>
+    <t xml:space="preserve">12.4481401443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3782072067261</t>
   </si>
   <si>
     <t xml:space="preserve">12.0285396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1509227752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4393978118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5617818832397</t>
+    <t xml:space="preserve">12.1509237289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4393968582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5617809295654</t>
   </si>
   <si>
     <t xml:space="preserve">12.5268154144287</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6317148208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3694648742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7715816497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4306564331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2820472717285</t>
+    <t xml:space="preserve">12.6317157745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3694639205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.771580696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4306554794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2820501327515</t>
   </si>
   <si>
     <t xml:space="preserve">12.1946315765381</t>
@@ -263,109 +263,109 @@
     <t xml:space="preserve">12.2470817565918</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4131727218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.509331703186</t>
+    <t xml:space="preserve">12.4131746292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5093307495117</t>
   </si>
   <si>
     <t xml:space="preserve">12.3869485855103</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8187398910522</t>
+    <t xml:space="preserve">11.8187408447266</t>
   </si>
   <si>
     <t xml:space="preserve">11.8449649810791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2558221817017</t>
+    <t xml:space="preserve">12.2558240890503</t>
   </si>
   <si>
     <t xml:space="preserve">12.5792655944824</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2208557128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1858901977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7803230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7278738021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8764810562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8065481185913</t>
+    <t xml:space="preserve">12.2208566665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1858882904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7803239822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7278718948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8764820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.806547164917</t>
   </si>
   <si>
     <t xml:space="preserve">12.7628402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8677406311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327741622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5355567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1824417114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0338315963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3048257827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2611169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3747577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6020402908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6894569396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7244243621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7514753341675</t>
+    <t xml:space="preserve">12.8677396774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327732086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5355558395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1824398040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0338306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3048238754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2611150741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3747568130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6020421981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6894578933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7244234085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7514762878418</t>
   </si>
   <si>
     <t xml:space="preserve">13.5711288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8687009811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6252317428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6432685852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.661301612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5981817245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6162176132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5260429382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5530948638916</t>
+    <t xml:space="preserve">13.8687028884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6252326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6432666778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6613025665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.598180770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6162166595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5260419845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5530939102173</t>
   </si>
   <si>
     <t xml:space="preserve">13.3456954956055</t>
@@ -377,85 +377,85 @@
     <t xml:space="preserve">13.6973714828491</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7785272598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6703195571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7965621948242</t>
+    <t xml:space="preserve">13.7785263061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6703205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7965631484985</t>
   </si>
   <si>
     <t xml:space="preserve">13.9769105911255</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0400323867798</t>
+    <t xml:space="preserve">14.0400314331055</t>
   </si>
   <si>
     <t xml:space="preserve">14.0129795074463</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9047708511353</t>
+    <t xml:space="preserve">13.9047718048096</t>
   </si>
   <si>
     <t xml:space="preserve">14.1031532287598</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2474317550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1572570800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3646564483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4187622070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5179500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6081247329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6622304916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3917093276978</t>
+    <t xml:space="preserve">14.2474308013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1572561264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3646574020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4187602996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5179510116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6081266403198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6622285842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3917074203491</t>
   </si>
   <si>
     <t xml:space="preserve">14.3105516433716</t>
   </si>
   <si>
-    <t xml:space="preserve">14.30153465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5450038909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6441926956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7343692779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7163333892822</t>
+    <t xml:space="preserve">14.3015356063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5450019836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.644193649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7343683242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7163343429565</t>
   </si>
   <si>
     <t xml:space="preserve">14.6351776123047</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6261596679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.689281463623</t>
+    <t xml:space="preserve">14.6261577606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6892824172974</t>
   </si>
   <si>
     <t xml:space="preserve">14.8245420455933</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8065071105957</t>
+    <t xml:space="preserve">14.8065061569214</t>
   </si>
   <si>
     <t xml:space="preserve">14.7433853149414</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">14.581072807312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6982975006104</t>
+    <t xml:space="preserve">14.698296546936</t>
   </si>
   <si>
     <t xml:space="preserve">14.5089340209961</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">14.6712484359741</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6532115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9237327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0499773025513</t>
+    <t xml:space="preserve">14.6532125473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.923731803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.049976348877</t>
   </si>
   <si>
     <t xml:space="preserve">15.2122898101807</t>
@@ -488,79 +488,79 @@
     <t xml:space="preserve">15.3746004104614</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5549478530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9246606826782</t>
+    <t xml:space="preserve">15.5549468994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9246625900269</t>
   </si>
   <si>
     <t xml:space="preserve">15.7803802490234</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8705549240112</t>
+    <t xml:space="preserve">15.8705558776855</t>
   </si>
   <si>
     <t xml:space="preserve">15.8344860076904</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7082433700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517135620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7452392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8714828491211</t>
+    <t xml:space="preserve">15.7082414627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517116546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7452354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8714790344238</t>
   </si>
   <si>
     <t xml:space="preserve">17.0879001617432</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1510219573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2231578826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9796924591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9075527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3043174743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0337944030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2772655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.475643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3223533630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1690559387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5838527679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5748405456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5658168792725</t>
+    <t xml:space="preserve">17.1510238647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2231597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9796943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9075508117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3043155670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0337924957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2772636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4756450653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3223514556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1690578460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.583854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5748348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5658206939697</t>
   </si>
   <si>
     <t xml:space="preserve">17.2411956787109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1870880126953</t>
+    <t xml:space="preserve">17.1870918273926</t>
   </si>
   <si>
     <t xml:space="preserve">16.8534507751465</t>
@@ -569,109 +569,109 @@
     <t xml:space="preserve">16.8444309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9526405334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7272052764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6911373138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8624668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0428142547607</t>
+    <t xml:space="preserve">16.95263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7272033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6911392211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8624649047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0428123474121</t>
   </si>
   <si>
     <t xml:space="preserve">16.8173809051514</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9977264404297</t>
+    <t xml:space="preserve">16.9977245330811</t>
   </si>
   <si>
     <t xml:space="preserve">16.7722930908203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.006742477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1961059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.358419418335</t>
+    <t xml:space="preserve">17.0067462921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1961078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3584213256836</t>
   </si>
   <si>
     <t xml:space="preserve">17.6199264526367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7642021179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0076694488525</t>
+    <t xml:space="preserve">17.7642002105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0076675415039</t>
   </si>
   <si>
     <t xml:space="preserve">17.9896354675293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9445495605469</t>
+    <t xml:space="preserve">17.9445457458496</t>
   </si>
   <si>
     <t xml:space="preserve">17.9535675048828</t>
   </si>
   <si>
-    <t xml:space="preserve">17.809289932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2601566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7561092376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8462867736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9364604949951</t>
+    <t xml:space="preserve">17.8092880249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2601585388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7561111450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.846284866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9364585876465</t>
   </si>
   <si>
     <t xml:space="preserve">18.620849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2971515655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3602752685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3512573242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.666862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6488265991211</t>
+    <t xml:space="preserve">19.2971534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3602733612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3512554168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6668663024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6488304138184</t>
   </si>
   <si>
     <t xml:space="preserve">19.5586566925049</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2520656585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1709079742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1348400115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1979637145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9544925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9094085693359</t>
+    <t xml:space="preserve">19.2520694732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1709098815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.134838104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.197961807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9544944763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9094047546387</t>
   </si>
   <si>
     <t xml:space="preserve">19.0897541046143</t>
@@ -680,34 +680,34 @@
     <t xml:space="preserve">18.5757637023926</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1970348358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5306739807129</t>
+    <t xml:space="preserve">18.1970367431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5306777954102</t>
   </si>
   <si>
     <t xml:space="preserve">18.8372669219971</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4594650268555</t>
+    <t xml:space="preserve">19.4594669342041</t>
   </si>
   <si>
     <t xml:space="preserve">19.3873271942139</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0185432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3612003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8301067352295</t>
+    <t xml:space="preserve">20.0185451507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3612022399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8301048278809</t>
   </si>
   <si>
     <t xml:space="preserve">21.2809715270996</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8751926422119</t>
+    <t xml:space="preserve">20.8751907348633</t>
   </si>
   <si>
     <t xml:space="preserve">20.9292945861816</t>
@@ -716,19 +716,19 @@
     <t xml:space="preserve">21.1006259918213</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0104503631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5686016082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7218952178955</t>
+    <t xml:space="preserve">21.0104541778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5685977935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7218971252441</t>
   </si>
   <si>
     <t xml:space="preserve">20.6046714782715</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1898727416992</t>
+    <t xml:space="preserve">20.1898708343506</t>
   </si>
   <si>
     <t xml:space="preserve">20.3792362213135</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">20.6497573852539</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6416645050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3711471557617</t>
+    <t xml:space="preserve">21.6416683197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3711452484131</t>
   </si>
   <si>
     <t xml:space="preserve">21.380163192749</t>
@@ -749,157 +749,157 @@
     <t xml:space="preserve">22.0925350189209</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6245574951172</t>
+    <t xml:space="preserve">22.6245632171631</t>
   </si>
   <si>
     <t xml:space="preserve">22.7147331237793</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8049087524414</t>
+    <t xml:space="preserve">22.8049068450928</t>
   </si>
   <si>
     <t xml:space="preserve">23.5984344482422</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0763568878174</t>
+    <t xml:space="preserve">24.0763549804688</t>
   </si>
   <si>
     <t xml:space="preserve">24.0583209991455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7156600952148</t>
+    <t xml:space="preserve">23.7156620025635</t>
   </si>
   <si>
     <t xml:space="preserve">23.9320774078369</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8599395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8058319091797</t>
+    <t xml:space="preserve">23.8599376678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8058338165283</t>
   </si>
   <si>
     <t xml:space="preserve">23.5082607269287</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9942722320557</t>
+    <t xml:space="preserve">22.994270324707</t>
   </si>
   <si>
     <t xml:space="preserve">22.480281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5434055328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7057151794434</t>
+    <t xml:space="preserve">22.5434036254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.705717086792</t>
   </si>
   <si>
     <t xml:space="preserve">22.4532299041748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4622440338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0023612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.182710647583</t>
+    <t xml:space="preserve">22.4622459411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0023593902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1827087402344</t>
   </si>
   <si>
     <t xml:space="preserve">22.7237529754639</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3630561828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2097606658936</t>
+    <t xml:space="preserve">22.3630523681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2097625732422</t>
   </si>
   <si>
     <t xml:space="preserve">21.4883728027344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9212055206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8761215209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7047863006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9392414093018</t>
+    <t xml:space="preserve">21.9212036132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8761177062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7047882080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9392395019531</t>
   </si>
   <si>
     <t xml:space="preserve">22.074499130249</t>
   </si>
   <si>
-    <t xml:space="preserve">22.299934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8139228820801</t>
+    <t xml:space="preserve">22.2999324798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8139247894287</t>
   </si>
   <si>
     <t xml:space="preserve">22.3179683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1917247772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3540382385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.525369644165</t>
+    <t xml:space="preserve">22.1917266845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3540420532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5253658294678</t>
   </si>
   <si>
     <t xml:space="preserve">22.6065235137939</t>
   </si>
   <si>
-    <t xml:space="preserve">22.633581161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2458343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2277965545654</t>
+    <t xml:space="preserve">22.6335754394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2458305358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2277946472168</t>
   </si>
   <si>
     <t xml:space="preserve">22.1286067962646</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0835189819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2007446289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.137622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1466369628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5965824127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3260612487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5605087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0294151306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6867523193359</t>
+    <t xml:space="preserve">22.0835208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2007427215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1376190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1466388702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5965785980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3260593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.560510635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0294132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6867542266846</t>
   </si>
   <si>
     <t xml:space="preserve">22.2368125915527</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3991222381592</t>
+    <t xml:space="preserve">22.3720760345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3991260528564</t>
   </si>
   <si>
     <t xml:space="preserve">22.6155414581299</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">23.0123081207275</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5193901062012</t>
+    <t xml:space="preserve">23.5193881988525</t>
   </si>
   <si>
     <t xml:space="preserve">23.2704582214355</t>
@@ -920,19 +920,19 @@
     <t xml:space="preserve">24.1739845275879</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7087287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.773265838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.243465423584</t>
+    <t xml:space="preserve">24.7087249755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7732639312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2434673309326</t>
   </si>
   <si>
     <t xml:space="preserve">25.8150882720947</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7966461181641</t>
+    <t xml:space="preserve">25.7966480255127</t>
   </si>
   <si>
     <t xml:space="preserve">25.6860122680664</t>
@@ -941,28 +941,28 @@
     <t xml:space="preserve">25.6675701141357</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0086975097656</t>
+    <t xml:space="preserve">26.0086994171143</t>
   </si>
   <si>
     <t xml:space="preserve">25.8888454437256</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9810428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0916728973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9072818756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8058681488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9533786773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.676794052124</t>
+    <t xml:space="preserve">25.9810447692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0916748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9072856903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8058662414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9533824920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6767921447754</t>
   </si>
   <si>
     <t xml:space="preserve">25.6583518981934</t>
@@ -974,25 +974,25 @@
     <t xml:space="preserve">25.4001998901367</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2619075775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3264446258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8009204864502</t>
+    <t xml:space="preserve">25.2619037628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3264408111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8009223937988</t>
   </si>
   <si>
     <t xml:space="preserve">25.4186401367188</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6441860198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.856237411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9576568603516</t>
+    <t xml:space="preserve">24.6441898345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8562393188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9576549530029</t>
   </si>
   <si>
     <t xml:space="preserve">24.8931217193604</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">23.187479019165</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9754295349121</t>
+    <t xml:space="preserve">22.9754276275635</t>
   </si>
   <si>
     <t xml:space="preserve">23.1229419708252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2335777282715</t>
+    <t xml:space="preserve">23.2335815429688</t>
   </si>
   <si>
     <t xml:space="preserve">22.9938659667969</t>
@@ -1016,49 +1016,49 @@
     <t xml:space="preserve">23.0123062133789</t>
   </si>
   <si>
-    <t xml:space="preserve">22.781810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6711807250977</t>
+    <t xml:space="preserve">22.7818145751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.671178817749</t>
   </si>
   <si>
     <t xml:space="preserve">22.4960041046143</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7264976501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5052242279053</t>
+    <t xml:space="preserve">22.7264938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5052223205566</t>
   </si>
   <si>
     <t xml:space="preserve">22.3208312988281</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5881996154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1137237548828</t>
+    <t xml:space="preserve">22.5882015228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1137199401855</t>
   </si>
   <si>
     <t xml:space="preserve">22.910888671875</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3995304107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7775382995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6208076477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1413841247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9846496582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8740081787109</t>
+    <t xml:space="preserve">23.3995323181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7775402069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6208057403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1413822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9846458435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8740139007568</t>
   </si>
   <si>
     <t xml:space="preserve">22.7357139587402</t>
@@ -1070,52 +1070,52 @@
     <t xml:space="preserve">23.3257751464844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7406597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9803733825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9711532592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0633487701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2477416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3860359191895</t>
+    <t xml:space="preserve">23.7406578063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.980375289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9711513519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0633506774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2477436065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">24.1555461883545</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6165313720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8611869812012</t>
+    <t xml:space="preserve">24.6165294647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8611850738525</t>
   </si>
   <si>
     <t xml:space="preserve">25.6306934356689</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2158107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1697082519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080043792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4463005065918</t>
+    <t xml:space="preserve">25.2158069610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1697101593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080024719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4462985992432</t>
   </si>
   <si>
     <t xml:space="preserve">25.5384960174561</t>
   </si>
   <si>
-    <t xml:space="preserve">25.123607635498</t>
+    <t xml:space="preserve">25.1236133575439</t>
   </si>
   <si>
     <t xml:space="preserve">24.4321327209473</t>
@@ -1124,16 +1124,16 @@
     <t xml:space="preserve">23.6484603881836</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0172500610352</t>
+    <t xml:space="preserve">24.0172481536865</t>
   </si>
   <si>
     <t xml:space="preserve">24.109447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">24.339937210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2016429901123</t>
+    <t xml:space="preserve">24.3399391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2016410827637</t>
   </si>
   <si>
     <t xml:space="preserve">24.2938404083252</t>
@@ -1142,19 +1142,19 @@
     <t xml:space="preserve">24.7548236846924</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6626281738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9853172302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4923992156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7228889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5704288482666</t>
+    <t xml:space="preserve">24.6626262664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.985315322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4923973083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7228908538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5704307556152</t>
   </si>
   <si>
     <t xml:space="preserve">25.5845947265625</t>
@@ -1169,85 +1169,85 @@
     <t xml:space="preserve">27.5668258666992</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7512187957764</t>
+    <t xml:space="preserve">27.751220703125</t>
   </si>
   <si>
     <t xml:space="preserve">28.0739059448242</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5207290649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7370567321777</t>
+    <t xml:space="preserve">27.5207271575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7370548248291</t>
   </si>
   <si>
     <t xml:space="preserve">26.5065631866455</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0314121246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5243339538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3682689666748</t>
+    <t xml:space="preserve">25.0314140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5243320465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3682670593262</t>
   </si>
   <si>
     <t xml:space="preserve">26.5987606048584</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4604644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2299747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3221645355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1980400085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2760696411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2902355194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3824329376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4746265411377</t>
+    <t xml:space="preserve">26.4604663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2299728393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3221683502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1980381011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2760715484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2902374267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3824348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.474630355835</t>
   </si>
   <si>
     <t xml:space="preserve">26.5526599884033</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8292503356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1058406829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8753471374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8434143066406</t>
+    <t xml:space="preserve">26.829252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.105842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8753509521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8434162139893</t>
   </si>
   <si>
     <t xml:space="preserve">28.7653827667236</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5809917449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9356117248535</t>
+    <t xml:space="preserve">28.5809898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9356136322021</t>
   </si>
   <si>
     <t xml:space="preserve">28.8114814758301</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1661014556885</t>
+    <t xml:space="preserve">28.1661033630371</t>
   </si>
   <si>
     <t xml:space="preserve">28.7192821502686</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">28.1200065612793</t>
   </si>
   <si>
-    <t xml:space="preserve">27.059741973877</t>
+    <t xml:space="preserve">27.0597438812256</t>
   </si>
   <si>
     <t xml:space="preserve">26.9675445556641</t>
@@ -1265,49 +1265,49 @@
     <t xml:space="preserve">27.1519412994385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6909561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7831535339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0455799102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6590213775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9214458465576</t>
+    <t xml:space="preserve">26.6909580230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7831516265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.045581817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6590232849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9214515686035</t>
   </si>
   <si>
     <t xml:space="preserve">26.1828804016113</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0886974334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4654293060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8061485290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7119636535645</t>
+    <t xml:space="preserve">26.088695526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4654312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8061466217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7119655609131</t>
   </si>
   <si>
     <t xml:space="preserve">25.1468677520752</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3352336883545</t>
+    <t xml:space="preserve">25.3352317810059</t>
   </si>
   <si>
     <t xml:space="preserve">24.9114112854004</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4875888824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3934020996094</t>
+    <t xml:space="preserve">24.487585067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3934001922607</t>
   </si>
   <si>
     <t xml:space="preserve">23.9224872589111</t>
@@ -1316,31 +1316,31 @@
     <t xml:space="preserve">23.2632064819336</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0277500152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0748386383057</t>
+    <t xml:space="preserve">23.0277481079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0748405456543</t>
   </si>
   <si>
     <t xml:space="preserve">22.7451992034912</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6039237976074</t>
+    <t xml:space="preserve">22.6039257049561</t>
   </si>
   <si>
     <t xml:space="preserve">22.5097427368164</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4155597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1800975799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0388259887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8504638671875</t>
+    <t xml:space="preserve">22.4155559539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1801013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0388278961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8504600524902</t>
   </si>
   <si>
     <t xml:space="preserve">22.4626502990723</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">22.2271938323975</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4044799804688</t>
+    <t xml:space="preserve">23.4044818878174</t>
   </si>
   <si>
     <t xml:space="preserve">23.2161159515381</t>
@@ -1358,19 +1358,19 @@
     <t xml:space="preserve">22.8864727020264</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4986629486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5568332672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1330089569092</t>
+    <t xml:space="preserve">23.498664855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5568351745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1330108642578</t>
   </si>
   <si>
     <t xml:space="preserve">21.6620960235596</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1911811828613</t>
+    <t xml:space="preserve">21.1911792755127</t>
   </si>
   <si>
     <t xml:space="preserve">21.0028133392334</t>
@@ -1379,28 +1379,28 @@
     <t xml:space="preserve">21.096996307373</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8615379333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.379545211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4737281799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2742862701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7562770843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9446430206299</t>
+    <t xml:space="preserve">20.8615398406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3795471191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4737300872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.274284362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7562789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9446411132812</t>
   </si>
   <si>
     <t xml:space="preserve">21.5679130554199</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5208187103271</t>
+    <t xml:space="preserve">21.520824432373</t>
   </si>
   <si>
     <t xml:space="preserve">21.3324527740479</t>
@@ -1412,13 +1412,13 @@
     <t xml:space="preserve">22.8393821716309</t>
   </si>
   <si>
-    <t xml:space="preserve">22.792293548584</t>
+    <t xml:space="preserve">22.7922916412354</t>
   </si>
   <si>
     <t xml:space="preserve">23.5457553863525</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6399402618408</t>
+    <t xml:space="preserve">23.6399383544922</t>
   </si>
   <si>
     <t xml:space="preserve">23.7341232299805</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">23.6870307922363</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7812118530273</t>
+    <t xml:space="preserve">23.781213760376</t>
   </si>
   <si>
     <t xml:space="preserve">24.0166721343994</t>
@@ -1436,40 +1436,40 @@
     <t xml:space="preserve">24.2992191314697</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1579437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2521286010742</t>
+    <t xml:space="preserve">24.1579456329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2521266937256</t>
   </si>
   <si>
     <t xml:space="preserve">24.7230434417725</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6288604736328</t>
+    <t xml:space="preserve">24.6288623809814</t>
   </si>
   <si>
     <t xml:space="preserve">24.675952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5817680358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.770133972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9584999084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9003314971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7590599060059</t>
+    <t xml:space="preserve">24.5817718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7701358795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9584980010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9003295898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7590560913086</t>
   </si>
   <si>
     <t xml:space="preserve">25.9474201202393</t>
   </si>
   <si>
-    <t xml:space="preserve">26.277063369751</t>
+    <t xml:space="preserve">26.2770652770996</t>
   </si>
   <si>
     <t xml:space="preserve">26.9363441467285</t>
@@ -1481,97 +1481,97 @@
     <t xml:space="preserve">26.8421611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7479763031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2659854888916</t>
+    <t xml:space="preserve">26.7479782104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2659873962402</t>
   </si>
   <si>
     <t xml:space="preserve">27.4543495178223</t>
   </si>
   <si>
-    <t xml:space="preserve">27.501443862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3130779266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0776214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7008876800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6537971496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6067028045654</t>
+    <t xml:space="preserve">27.5014419555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3130760192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0776195526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7008857727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6537952423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6067047119141</t>
   </si>
   <si>
     <t xml:space="preserve">25.994514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1357879638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0416049957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6177806854248</t>
+    <t xml:space="preserve">26.1357898712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0416069030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6177825927734</t>
   </si>
   <si>
     <t xml:space="preserve">25.4294166564941</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0055923461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0997772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.864315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4404964447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5235996246338</t>
+    <t xml:space="preserve">25.0055885314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0997753143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8643169403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4404945373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5235977172852</t>
   </si>
   <si>
     <t xml:space="preserve">26.3712463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3241539001465</t>
+    <t xml:space="preserve">26.3241577148438</t>
   </si>
   <si>
     <t xml:space="preserve">26.7950706481934</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8892517089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0305271148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.171802520752</t>
+    <t xml:space="preserve">26.889253616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0305290222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1718044281006</t>
   </si>
   <si>
     <t xml:space="preserve">27.5485324859619</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6898078918457</t>
+    <t xml:space="preserve">27.6898097991943</t>
   </si>
   <si>
     <t xml:space="preserve">28.1136322021484</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3961811065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7258205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9141902923584</t>
+    <t xml:space="preserve">28.3961791992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7258224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9141883850098</t>
   </si>
   <si>
     <t xml:space="preserve">29.9502010345459</t>
@@ -1580,13 +1580,13 @@
     <t xml:space="preserve">29.7618350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3269329071045</t>
+    <t xml:space="preserve">30.3269348144531</t>
   </si>
   <si>
     <t xml:space="preserve">30.3740253448486</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5042266845703</t>
+    <t xml:space="preserve">31.504222869873</t>
   </si>
   <si>
     <t xml:space="preserve">31.6925888061523</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">32.4460525512695</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4931488037109</t>
+    <t xml:space="preserve">32.4931373596191</t>
   </si>
   <si>
     <t xml:space="preserve">33.482063293457</t>
@@ -1610,79 +1610,79 @@
     <t xml:space="preserve">33.5762481689453</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9058876037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2466125488281</t>
+    <t xml:space="preserve">33.905891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2466087341309</t>
   </si>
   <si>
     <t xml:space="preserve">32.8698768615723</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1524200439453</t>
+    <t xml:space="preserve">33.1524238586426</t>
   </si>
   <si>
     <t xml:space="preserve">33.0582389831543</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5873260498047</t>
+    <t xml:space="preserve">32.5873222351074</t>
   </si>
   <si>
     <t xml:space="preserve">32.3047752380371</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9280452728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4571323394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3629455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8920288085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0804004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0333080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6565761566162</t>
+    <t xml:space="preserve">31.9280471801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4571285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3629398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8920307159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0803966522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0333061218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6565723419189</t>
   </si>
   <si>
     <t xml:space="preserve">30.6094818115234</t>
   </si>
   <si>
-    <t xml:space="preserve">31.268762588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9862174987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4100341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8449401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.17458152771</t>
+    <t xml:space="preserve">31.2687606811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9862155914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4100360870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8449382781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1745796203613</t>
   </si>
   <si>
     <t xml:space="preserve">31.8809509277344</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0222244262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7396812438965</t>
+    <t xml:space="preserve">32.0222282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7396850585938</t>
   </si>
   <si>
     <t xml:space="preserve">34.000072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4709815979004</t>
+    <t xml:space="preserve">34.4709854125977</t>
   </si>
   <si>
     <t xml:space="preserve">35.7895469665527</t>
@@ -1691,25 +1691,25 @@
     <t xml:space="preserve">36.5901031494141</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7784690856934</t>
+    <t xml:space="preserve">36.7784729003906</t>
   </si>
   <si>
     <t xml:space="preserve">37.155200958252</t>
   </si>
   <si>
-    <t xml:space="preserve">37.673210144043</t>
+    <t xml:space="preserve">37.6732063293457</t>
   </si>
   <si>
     <t xml:space="preserve">38.0846748352051</t>
   </si>
   <si>
-    <t xml:space="preserve">38.228214263916</t>
+    <t xml:space="preserve">38.2282104492188</t>
   </si>
   <si>
     <t xml:space="preserve">37.367000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7976036071777</t>
+    <t xml:space="preserve">37.797607421875</t>
   </si>
   <si>
     <t xml:space="preserve">38.1803665161133</t>
@@ -1721,28 +1721,28 @@
     <t xml:space="preserve">37.9411430358887</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9889869689941</t>
+    <t xml:space="preserve">37.9889907836914</t>
   </si>
   <si>
     <t xml:space="preserve">37.8454513549805</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3191604614258</t>
+    <t xml:space="preserve">37.3191566467285</t>
   </si>
   <si>
     <t xml:space="preserve">38.8501930236816</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7545051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3286476135254</t>
+    <t xml:space="preserve">38.754508972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3286437988281</t>
   </si>
   <si>
     <t xml:space="preserve">39.041576385498</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8023529052734</t>
+    <t xml:space="preserve">38.8023452758789</t>
   </si>
   <si>
     <t xml:space="preserve">38.4674377441406</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">38.1325187683105</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8980445861816</t>
+    <t xml:space="preserve">38.8980407714844</t>
   </si>
   <si>
     <t xml:space="preserve">38.7066612243652</t>
@@ -1760,64 +1760,64 @@
     <t xml:space="preserve">38.2760581970215</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5631256103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4195976257324</t>
+    <t xml:space="preserve">38.5631294250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4195938110352</t>
   </si>
   <si>
     <t xml:space="preserve">39.3764915466309</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1372680664062</t>
+    <t xml:space="preserve">39.137264251709</t>
   </si>
   <si>
     <t xml:space="preserve">39.1851119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2808036804199</t>
+    <t xml:space="preserve">39.2807998657227</t>
   </si>
   <si>
     <t xml:space="preserve">39.9027862548828</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1946105957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1036643981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5342712402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6730575561523</t>
+    <t xml:space="preserve">41.1946029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1036605834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5342674255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6730537414551</t>
   </si>
   <si>
     <t xml:space="preserve">40.8118476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7161521911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9122772216797</t>
+    <t xml:space="preserve">40.7161560058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.912281036377</t>
   </si>
   <si>
     <t xml:space="preserve">43.0605659484863</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4911689758301</t>
+    <t xml:space="preserve">43.4911651611328</t>
   </si>
   <si>
     <t xml:space="preserve">44.2566909790039</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7829818725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4433250427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.017463684082</t>
+    <t xml:space="preserve">44.7829856872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4433288574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0174674987793</t>
   </si>
   <si>
     <t xml:space="preserve">43.6347045898438</t>
@@ -1829,82 +1829,82 @@
     <t xml:space="preserve">42.9170265197754</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9265213012695</t>
+    <t xml:space="preserve">44.9265251159668</t>
   </si>
   <si>
     <t xml:space="preserve">45.404972076416</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2614364624023</t>
+    <t xml:space="preserve">45.2614402770996</t>
   </si>
   <si>
     <t xml:space="preserve">45.5963516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6536865234375</t>
+    <t xml:space="preserve">47.653694152832</t>
   </si>
   <si>
     <t xml:space="preserve">48.8976593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6105880737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1847381591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9933547973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7588768005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2804183959961</t>
+    <t xml:space="preserve">48.6105918884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1847343444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9933471679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7588729858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2804222106934</t>
   </si>
   <si>
     <t xml:space="preserve">49.6631813049316</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3761138916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5674934387207</t>
+    <t xml:space="preserve">49.3761100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5674896240234</t>
   </si>
   <si>
     <t xml:space="preserve">50.6200866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0028419494629</t>
+    <t xml:space="preserve">51.0028457641602</t>
   </si>
   <si>
     <t xml:space="preserve">52.7252655029297</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6295776367188</t>
+    <t xml:space="preserve">52.6295738220215</t>
   </si>
   <si>
     <t xml:space="preserve">51.9597473144531</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8640556335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6726722717285</t>
+    <t xml:space="preserve">51.8640594482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6726760864258</t>
   </si>
   <si>
     <t xml:space="preserve">48.4192085266113</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3235206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0459480285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3856048583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.907154083252</t>
+    <t xml:space="preserve">48.3235244750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0459442138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3856086730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9071578979492</t>
   </si>
   <si>
     <t xml:space="preserve">49.8545608520508</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">50.4287071228027</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5338859558105</t>
+    <t xml:space="preserve">52.5338897705078</t>
   </si>
   <si>
     <t xml:space="preserve">54.0649299621582</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">46.9838562011719</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3618774414062</t>
+    <t xml:space="preserve">46.361873626709</t>
   </si>
   <si>
     <t xml:space="preserve">45.7398872375488</t>
@@ -1940,40 +1940,40 @@
     <t xml:space="preserve">44.974365234375</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5868606567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7687454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6493263244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.596736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0945510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4820613861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1854934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5299034118652</t>
+    <t xml:space="preserve">43.586856842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7687530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6493225097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5967330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0945491790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4820575714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1854915618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5299015045166</t>
   </si>
   <si>
     <t xml:space="preserve">31.0992984771729</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3816184997559</t>
+    <t xml:space="preserve">30.3816204071045</t>
   </si>
   <si>
     <t xml:space="preserve">34.9269027709961</t>
   </si>
   <si>
-    <t xml:space="preserve">36.410099029541</t>
+    <t xml:space="preserve">36.4100952148438</t>
   </si>
   <si>
     <t xml:space="preserve">35.5010375976562</t>
@@ -1985,19 +1985,19 @@
     <t xml:space="preserve">34.5441436767578</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0704383850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0799293518066</t>
+    <t xml:space="preserve">35.070442199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0799331665039</t>
   </si>
   <si>
     <t xml:space="preserve">37.2234649658203</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1277732849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2329597473145</t>
+    <t xml:space="preserve">37.1277694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2329559326172</t>
   </si>
   <si>
     <t xml:space="preserve">40.429084777832</t>
@@ -2006,10 +2006,10 @@
     <t xml:space="preserve">39.998477935791</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7351379394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9791107177734</t>
+    <t xml:space="preserve">44.7351455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9791145324707</t>
   </si>
   <si>
     <t xml:space="preserve">45.4528198242188</t>
@@ -2021,16 +2021,16 @@
     <t xml:space="preserve">45.3571319580078</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1179008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4575614929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6441917419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8786773681641</t>
+    <t xml:space="preserve">45.1179046630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4575653076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6441955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8786811828613</t>
   </si>
   <si>
     <t xml:space="preserve">45.3092803955078</t>
@@ -2039,13 +2039,13 @@
     <t xml:space="preserve">45.1657485961914</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2088470458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1562538146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9217681884766</t>
+    <t xml:space="preserve">44.2088432312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.15625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9217758178711</t>
   </si>
   <si>
     <t xml:space="preserve">41.8644371032715</t>
@@ -2057,16 +2057,16 @@
     <t xml:space="preserve">45.0222129821777</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5485038757324</t>
+    <t xml:space="preserve">45.5485000610352</t>
   </si>
   <si>
     <t xml:space="preserve">47.5101585388184</t>
   </si>
   <si>
-    <t xml:space="preserve">47.701530456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7062835693359</t>
+    <t xml:space="preserve">47.7015342712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7062873840332</t>
   </si>
   <si>
     <t xml:space="preserve">47.9407577514648</t>
@@ -2078,16 +2078,16 @@
     <t xml:space="preserve">51.4812965393066</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1942253112793</t>
+    <t xml:space="preserve">51.1942291259766</t>
   </si>
   <si>
     <t xml:space="preserve">51.768367767334</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2899169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1080284118652</t>
+    <t xml:space="preserve">51.289909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.108024597168</t>
   </si>
   <si>
     <t xml:space="preserve">53.9692420959473</t>
@@ -2099,79 +2099,79 @@
     <t xml:space="preserve">55.1175231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6916580200195</t>
+    <t xml:space="preserve">55.6916618347168</t>
   </si>
   <si>
     <t xml:space="preserve">55.5002822875977</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3519973754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6390647888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8304481506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4045906066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7442474365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9356346130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1270179748535</t>
+    <t xml:space="preserve">54.3520011901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6390724182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.830451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4045944213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7442512512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9356307983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1270141601562</t>
   </si>
   <si>
     <t xml:space="preserve">56.2658004760742</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9787368774414</t>
+    <t xml:space="preserve">55.9787292480469</t>
   </si>
   <si>
     <t xml:space="preserve">57.3183937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">58.6580543518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2227020263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7011566162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3614921569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.988224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8494338989258</t>
+    <t xml:space="preserve">58.6580581665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2227058410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7011528015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3614959716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9882278442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.849437713623</t>
   </si>
   <si>
     <t xml:space="preserve">61.3373794555664</t>
   </si>
   <si>
-    <t xml:space="preserve">63.4425659179688</t>
+    <t xml:space="preserve">63.442569732666</t>
   </si>
   <si>
     <t xml:space="preserve">62.2942810058594</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3468704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7296257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6339416503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3037796020508</t>
+    <t xml:space="preserve">63.3468818664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7296295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6339454650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3037719726562</t>
   </si>
   <si>
     <t xml:space="preserve">64.5908432006836</t>
@@ -2180,43 +2180,43 @@
     <t xml:space="preserve">65.9305038452148</t>
   </si>
   <si>
-    <t xml:space="preserve">66.6960220336914</t>
+    <t xml:space="preserve">66.6960296630859</t>
   </si>
   <si>
     <t xml:space="preserve">65.3563690185547</t>
   </si>
   <si>
-    <t xml:space="preserve">66.9831008911133</t>
+    <t xml:space="preserve">66.9830932617188</t>
   </si>
   <si>
     <t xml:space="preserve">67.1744766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5046539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8443069458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.0451736450195</t>
+    <t xml:space="preserve">66.5046463012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8443145751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.0451889038086</t>
   </si>
   <si>
     <t xml:space="preserve">69.1839752197266</t>
   </si>
   <si>
-    <t xml:space="preserve">71.2891540527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8107070922852</t>
+    <t xml:space="preserve">71.2891616821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8106994628906</t>
   </si>
   <si>
     <t xml:space="preserve">70.6193313598633</t>
   </si>
   <si>
-    <t xml:space="preserve">71.7676086425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.0546722412109</t>
+    <t xml:space="preserve">71.7676010131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.0546798706055</t>
   </si>
   <si>
     <t xml:space="preserve">71.0020751953125</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">68.9925918579102</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9494857788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8012161254883</t>
+    <t xml:space="preserve">69.9494934082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8012237548828</t>
   </si>
   <si>
     <t xml:space="preserve">69.6624221801758</t>
@@ -2252,19 +2252,19 @@
     <t xml:space="preserve">73.8727874755859</t>
   </si>
   <si>
-    <t xml:space="preserve">74.8296890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.8917770385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.2745361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.7960891723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.4228134155273</t>
+    <t xml:space="preserve">74.8296966552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.8917694091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.274528503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.7960815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.4228210449219</t>
   </si>
   <si>
     <t xml:space="preserve">80.7624816894531</t>
@@ -2273,52 +2273,52 @@
     <t xml:space="preserve">82.0064468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">81.5279922485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.910758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.3892211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4323043823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.1452407836914</t>
+    <t xml:space="preserve">81.5279998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9107513427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.3892059326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4323120117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1452484130859</t>
   </si>
   <si>
     <t xml:space="preserve">80.4754028320312</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7193756103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8150634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.3461151123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.953857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.77197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2935256958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.0305633544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3271255493164</t>
+    <t xml:space="preserve">81.7193832397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8150787353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.3461074829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.9538497924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7719802856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2935180664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.0305709838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3271331787109</t>
   </si>
   <si>
     <t xml:space="preserve">83.728874206543</t>
   </si>
   <si>
-    <t xml:space="preserve">82.1021423339844</t>
+    <t xml:space="preserve">82.1021499633789</t>
   </si>
   <si>
     <t xml:space="preserve">76.7434997558594</t>
@@ -2333,19 +2333,19 @@
     <t xml:space="preserve">82.4849014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3797149658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.6572952270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.4659194946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6857681274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3556060791016</t>
+    <t xml:space="preserve">80.3797225952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.6572875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.4659118652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6857757568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.355598449707</t>
   </si>
   <si>
     <t xml:space="preserve">83.0590438842773</t>
@@ -2354,34 +2354,34 @@
     <t xml:space="preserve">85.9297485351562</t>
   </si>
   <si>
-    <t xml:space="preserve">87.1737213134766</t>
+    <t xml:space="preserve">87.173713684082</t>
   </si>
   <si>
     <t xml:space="preserve">87.2694091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">88.3220138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7909469604492</t>
+    <t xml:space="preserve">88.3220062255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7909545898438</t>
   </si>
   <si>
     <t xml:space="preserve">90.9056396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3840866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1065216064453</t>
+    <t xml:space="preserve">91.3840789794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1065139770508</t>
   </si>
   <si>
     <t xml:space="preserve">95.8815155029297</t>
   </si>
   <si>
-    <t xml:space="preserve">97.2211761474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.474655151367</t>
+    <t xml:space="preserve">97.2211837768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.474639892578</t>
   </si>
   <si>
     <t xml:space="preserve">101.622924804688</t>
@@ -2390,13 +2390,13 @@
     <t xml:space="preserve">101.240173339844</t>
   </si>
   <si>
-    <t xml:space="preserve">97.9867095947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5608367919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.9004974365234</t>
+    <t xml:space="preserve">97.9866943359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5608444213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.9005126953125</t>
   </si>
   <si>
     <t xml:space="preserve">96.264289855957</t>
@@ -2408,13 +2408,13 @@
     <t xml:space="preserve">94.8289337158203</t>
   </si>
   <si>
-    <t xml:space="preserve">95.307373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2547836303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4461669921875</t>
+    <t xml:space="preserve">95.3073883056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2547912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.446159362793</t>
   </si>
   <si>
     <t xml:space="preserve">97.0298080444336</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">94.541862487793</t>
   </si>
   <si>
-    <t xml:space="preserve">94.1591110229492</t>
+    <t xml:space="preserve">94.1591033935547</t>
   </si>
   <si>
     <t xml:space="preserve">93.8720245361328</t>
@@ -2432,43 +2432,43 @@
     <t xml:space="preserve">94.0634155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">93.3935699462891</t>
+    <t xml:space="preserve">93.3935775756836</t>
   </si>
   <si>
     <t xml:space="preserve">93.6806488037109</t>
   </si>
   <si>
-    <t xml:space="preserve">92.9151229858398</t>
+    <t xml:space="preserve">92.9151306152344</t>
   </si>
   <si>
     <t xml:space="preserve">93.2978820800781</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7237548828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3504791259766</t>
+    <t xml:space="preserve">92.723747253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3504867553711</t>
   </si>
   <si>
     <t xml:space="preserve">97.6039428710938</t>
   </si>
   <si>
-    <t xml:space="preserve">101.43155670166</t>
+    <t xml:space="preserve">101.431549072266</t>
   </si>
   <si>
     <t xml:space="preserve">104.876388549805</t>
   </si>
   <si>
-    <t xml:space="preserve">104.493629455566</t>
+    <t xml:space="preserve">104.493621826172</t>
   </si>
   <si>
     <t xml:space="preserve">106.598815917969</t>
   </si>
   <si>
-    <t xml:space="preserve">107.364334106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.66089630127</t>
+    <t xml:space="preserve">107.364326477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.660903930664</t>
   </si>
   <si>
     <t xml:space="preserve">110.235046386719</t>
@@ -2477,13 +2477,13 @@
     <t xml:space="preserve">105.64192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">106.21605682373</t>
+    <t xml:space="preserve">106.216049194336</t>
   </si>
   <si>
     <t xml:space="preserve">107.938484191895</t>
   </si>
   <si>
-    <t xml:space="preserve">107.555717468262</t>
+    <t xml:space="preserve">107.555725097656</t>
   </si>
   <si>
     <t xml:space="preserve">109.469520568848</t>
@@ -2492,25 +2492,25 @@
     <t xml:space="preserve">107.747100830078</t>
   </si>
   <si>
-    <t xml:space="preserve">108.703994750977</t>
+    <t xml:space="preserve">108.704002380371</t>
   </si>
   <si>
     <t xml:space="preserve">102.197082519531</t>
   </si>
   <si>
-    <t xml:space="preserve">99.5177536010742</t>
+    <t xml:space="preserve">99.5177459716797</t>
   </si>
   <si>
     <t xml:space="preserve">99.7091217041016</t>
   </si>
   <si>
-    <t xml:space="preserve">103.345344543457</t>
+    <t xml:space="preserve">103.345352172852</t>
   </si>
   <si>
     <t xml:space="preserve">103.536735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">106.024681091309</t>
+    <t xml:space="preserve">106.024673461914</t>
   </si>
   <si>
     <t xml:space="preserve">106.981582641602</t>
@@ -2519,16 +2519,16 @@
     <t xml:space="preserve">108.512619018555</t>
   </si>
   <si>
-    <t xml:space="preserve">105.833290100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.048782348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.388450622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.153968811035</t>
+    <t xml:space="preserve">105.833297729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.048797607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.388458251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.15397644043</t>
   </si>
   <si>
     <t xml:space="preserve">102.962593078613</t>
@@ -2537,19 +2537,19 @@
     <t xml:space="preserve">105.450531005859</t>
   </si>
   <si>
-    <t xml:space="preserve">102.005683898926</t>
+    <t xml:space="preserve">102.00569152832</t>
   </si>
   <si>
     <t xml:space="preserve">103.919494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">106.407440185547</t>
+    <t xml:space="preserve">106.407432556152</t>
   </si>
   <si>
     <t xml:space="preserve">109.086769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">110.809181213379</t>
+    <t xml:space="preserve">110.809188842773</t>
   </si>
   <si>
     <t xml:space="preserve">113.679893493652</t>
@@ -2564,49 +2564,49 @@
     <t xml:space="preserve">111.000564575195</t>
   </si>
   <si>
-    <t xml:space="preserve">112.914375305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.852294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.426422119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.383316040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.340225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.445404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.297134399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.722984313965</t>
+    <t xml:space="preserve">112.914360046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.852279663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.42643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.383323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.340232849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.445411682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.29712677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.722991943359</t>
   </si>
   <si>
     <t xml:space="preserve">115.019554138184</t>
   </si>
   <si>
-    <t xml:space="preserve">115.593688964844</t>
+    <t xml:space="preserve">115.593696594238</t>
   </si>
   <si>
     <t xml:space="preserve">115.210929870605</t>
   </si>
   <si>
-    <t xml:space="preserve">116.741973876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.167831420898</t>
+    <t xml:space="preserve">116.741966247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.167839050293</t>
   </si>
   <si>
     <t xml:space="preserve">115.78507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">116.550598144531</t>
+    <t xml:space="preserve">116.550590515137</t>
   </si>
   <si>
     <t xml:space="preserve">119.804054260254</t>
@@ -2618,55 +2618,55 @@
     <t xml:space="preserve">122.100616455078</t>
   </si>
   <si>
-    <t xml:space="preserve">122.866134643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.631652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.478240966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.267883300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.459251403809</t>
+    <t xml:space="preserve">122.866142272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.631660461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.478256225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.267890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.459259033203</t>
   </si>
   <si>
     <t xml:space="preserve">128.990310668945</t>
   </si>
   <si>
-    <t xml:space="preserve">132.052398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.157577514648</t>
+    <t xml:space="preserve">132.052383422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.157562255859</t>
   </si>
   <si>
     <t xml:space="preserve">133.774826049805</t>
   </si>
   <si>
-    <t xml:space="preserve">132.626556396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.435134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.923110961914</t>
+    <t xml:space="preserve">132.626525878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.435150146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.923095703125</t>
   </si>
   <si>
     <t xml:space="preserve">136.645523071289</t>
   </si>
   <si>
-    <t xml:space="preserve">137.411041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.30583190918</t>
+    <t xml:space="preserve">137.411056518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.305862426758</t>
   </si>
   <si>
     <t xml:space="preserve">131.86100769043</t>
   </si>
   <si>
-    <t xml:space="preserve">134.731735229492</t>
+    <t xml:space="preserve">134.731719970703</t>
   </si>
   <si>
     <t xml:space="preserve">136.262756347656</t>
@@ -2678,19 +2678,19 @@
     <t xml:space="preserve">138.176574707031</t>
   </si>
   <si>
-    <t xml:space="preserve">137.028289794922</t>
+    <t xml:space="preserve">137.028274536133</t>
   </si>
   <si>
     <t xml:space="preserve">138.559326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">139.898971557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.454147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.750686645508</t>
+    <t xml:space="preserve">139.898986816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.454132080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.750701904297</t>
   </si>
   <si>
     <t xml:space="preserve">139.324844360352</t>
@@ -2699,25 +2699,25 @@
     <t xml:space="preserve">137.98518371582</t>
   </si>
   <si>
-    <t xml:space="preserve">135.497253417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.492126464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.874877929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.109344482422</t>
+    <t xml:space="preserve">135.49723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.492111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.874862670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.109359741211</t>
   </si>
   <si>
     <t xml:space="preserve">142.195541381836</t>
   </si>
   <si>
-    <t xml:space="preserve">143.726593017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.917953491211</t>
+    <t xml:space="preserve">143.726577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.91796875</t>
   </si>
   <si>
     <t xml:space="preserve">144.683486938477</t>
@@ -2726,16 +2726,16 @@
     <t xml:space="preserve">145.25764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">147.936965942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.640396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.788665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.276641845703</t>
+    <t xml:space="preserve">147.936950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.640380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.788681030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.276626586914</t>
   </si>
   <si>
     <t xml:space="preserve">150.999053955078</t>
@@ -2753,16 +2753,16 @@
     <t xml:space="preserve">155.400772094727</t>
   </si>
   <si>
-    <t xml:space="preserve">151.190414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.888748168945</t>
+    <t xml:space="preserve">151.1904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.888732910156</t>
   </si>
   <si>
     <t xml:space="preserve">159.037017822266</t>
   </si>
   <si>
-    <t xml:space="preserve">158.654251098633</t>
+    <t xml:space="preserve">158.654266357422</t>
   </si>
   <si>
     <t xml:space="preserve">159.611145019531</t>
@@ -2774,46 +2774,46 @@
     <t xml:space="preserve">161.524963378906</t>
   </si>
   <si>
-    <t xml:space="preserve">163.438751220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.821517944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.606033325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.773300170898</t>
+    <t xml:space="preserve">163.438766479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.821502685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.606002807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.773315429688</t>
   </si>
   <si>
     <t xml:space="preserve">170.32844543457</t>
   </si>
   <si>
-    <t xml:space="preserve">165.161178588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.031875610352</t>
+    <t xml:space="preserve">165.161209106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.031921386719</t>
   </si>
   <si>
     <t xml:space="preserve">165.352569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">160.759429931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.099105834961</t>
+    <t xml:space="preserve">160.75944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.099090576172</t>
   </si>
   <si>
     <t xml:space="preserve">171.668106079102</t>
   </si>
   <si>
-    <t xml:space="preserve">167.074981689453</t>
+    <t xml:space="preserve">167.075012207031</t>
   </si>
   <si>
     <t xml:space="preserve">161.930511474609</t>
   </si>
   <si>
-    <t xml:space="preserve">161.353591918945</t>
+    <t xml:space="preserve">161.353576660156</t>
   </si>
   <si>
     <t xml:space="preserve">160.58430480957</t>
@@ -2825,19 +2825,19 @@
     <t xml:space="preserve">152.122375488281</t>
   </si>
   <si>
-    <t xml:space="preserve">145.583618164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.314468383789</t>
+    <t xml:space="preserve">145.583602905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.314453125</t>
   </si>
   <si>
     <t xml:space="preserve">150.391525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">150.19921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.083724975586</t>
+    <t xml:space="preserve">150.199203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.083740234375</t>
   </si>
   <si>
     <t xml:space="preserve">151.737747192383</t>
@@ -2852,10 +2852,10 @@
     <t xml:space="preserve">156.545654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">155.968704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.430191040039</t>
+    <t xml:space="preserve">155.968688964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.43017578125</t>
   </si>
   <si>
     <t xml:space="preserve">160.776611328125</t>
@@ -2864,16 +2864,16 @@
     <t xml:space="preserve">166.353805541992</t>
   </si>
   <si>
-    <t xml:space="preserve">170.200119018555</t>
+    <t xml:space="preserve">170.200134277344</t>
   </si>
   <si>
     <t xml:space="preserve">168.469268798828</t>
   </si>
   <si>
-    <t xml:space="preserve">164.430618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.007583618164</t>
+    <t xml:space="preserve">164.430648803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.007598876953</t>
   </si>
   <si>
     <t xml:space="preserve">162.507461547852</t>
@@ -2882,43 +2882,43 @@
     <t xml:space="preserve">163.469055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">165.584548950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.161270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.084426879883</t>
+    <t xml:space="preserve">165.584518432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.161254882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.084442138672</t>
   </si>
   <si>
     <t xml:space="preserve">161.738189697266</t>
   </si>
   <si>
-    <t xml:space="preserve">168.853897094727</t>
+    <t xml:space="preserve">168.853942871094</t>
   </si>
   <si>
     <t xml:space="preserve">177.508178710938</t>
   </si>
   <si>
-    <t xml:space="preserve">175.584991455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.392913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.777542114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.469757080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.815948486328</t>
+    <t xml:space="preserve">175.585006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.392929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.777526855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.469741821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.815963745117</t>
   </si>
   <si>
     <t xml:space="preserve">181.739120483398</t>
   </si>
   <si>
-    <t xml:space="preserve">185.008514404297</t>
+    <t xml:space="preserve">185.008499145508</t>
   </si>
   <si>
     <t xml:space="preserve">183.085327148438</t>
@@ -2930,16 +2930,16 @@
     <t xml:space="preserve">168.276962280273</t>
   </si>
   <si>
-    <t xml:space="preserve">169.046249389648</t>
+    <t xml:space="preserve">169.046234130859</t>
   </si>
   <si>
     <t xml:space="preserve">170.584762573242</t>
   </si>
   <si>
-    <t xml:space="preserve">167.507705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.046478271484</t>
+    <t xml:space="preserve">167.507675170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.046447753906</t>
   </si>
   <si>
     <t xml:space="preserve">170.96940612793</t>
@@ -2948,31 +2948,31 @@
     <t xml:space="preserve">169.623184204102</t>
   </si>
   <si>
-    <t xml:space="preserve">169.238555908203</t>
+    <t xml:space="preserve">169.238540649414</t>
   </si>
   <si>
     <t xml:space="preserve">175.008041381836</t>
   </si>
   <si>
-    <t xml:space="preserve">172.700241088867</t>
+    <t xml:space="preserve">172.700256347656</t>
   </si>
   <si>
     <t xml:space="preserve">172.123291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">171.93098449707</t>
+    <t xml:space="preserve">171.930969238281</t>
   </si>
   <si>
     <t xml:space="preserve">167.315383911133</t>
   </si>
   <si>
-    <t xml:space="preserve">163.853668212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.738418579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.238311767578</t>
+    <t xml:space="preserve">163.85368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.73844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.238327026367</t>
   </si>
   <si>
     <t xml:space="preserve">166.546112060547</t>
@@ -2981,13 +2981,13 @@
     <t xml:space="preserve">167.700012207031</t>
   </si>
   <si>
-    <t xml:space="preserve">165.392227172852</t>
+    <t xml:space="preserve">165.392211914062</t>
   </si>
   <si>
     <t xml:space="preserve">151.160781860352</t>
   </si>
   <si>
-    <t xml:space="preserve">158.853454589844</t>
+    <t xml:space="preserve">158.853439331055</t>
   </si>
   <si>
     <t xml:space="preserve">158.468826293945</t>
@@ -3011,10 +3011,10 @@
     <t xml:space="preserve">145.96826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">146.929824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.353088378906</t>
+    <t xml:space="preserve">146.929840087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.353103637695</t>
   </si>
   <si>
     <t xml:space="preserve">153.468597412109</t>
@@ -3023,25 +3023,25 @@
     <t xml:space="preserve">153.276260375977</t>
   </si>
   <si>
-    <t xml:space="preserve">157.122619628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.930053710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.545211791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.968017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.92936706543</t>
+    <t xml:space="preserve">157.122604370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.930068969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.545181274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.968032836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.929351806641</t>
   </si>
   <si>
     <t xml:space="preserve">138.660217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">132.69841003418</t>
+    <t xml:space="preserve">132.698394775391</t>
   </si>
   <si>
     <t xml:space="preserve">132.506088256836</t>
@@ -3050,10 +3050,10 @@
     <t xml:space="preserve">130.198287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">134.813888549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.005981445312</t>
+    <t xml:space="preserve">134.813873291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.005966186523</t>
   </si>
   <si>
     <t xml:space="preserve">130.775238037109</t>
@@ -3062,13 +3062,13 @@
     <t xml:space="preserve">128.852066040039</t>
   </si>
   <si>
-    <t xml:space="preserve">129.621337890625</t>
+    <t xml:space="preserve">129.621353149414</t>
   </si>
   <si>
     <t xml:space="preserve">132.890716552734</t>
   </si>
   <si>
-    <t xml:space="preserve">137.506332397461</t>
+    <t xml:space="preserve">137.506317138672</t>
   </si>
   <si>
     <t xml:space="preserve">136.160110473633</t>
@@ -3077,19 +3077,19 @@
     <t xml:space="preserve">138.467895507812</t>
   </si>
   <si>
-    <t xml:space="preserve">135.583160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.813438415527</t>
+    <t xml:space="preserve">135.583145141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.813430786133</t>
   </si>
   <si>
     <t xml:space="preserve">118.659301757812</t>
   </si>
   <si>
-    <t xml:space="preserve">125.582702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.198059082031</t>
+    <t xml:space="preserve">125.582695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.198066711426</t>
   </si>
   <si>
     <t xml:space="preserve">137.314010620117</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">138.8525390625</t>
   </si>
   <si>
-    <t xml:space="preserve">142.891174316406</t>
+    <t xml:space="preserve">142.891189575195</t>
   </si>
   <si>
     <t xml:space="preserve">140.391067504883</t>
@@ -3107,22 +3107,22 @@
     <t xml:space="preserve">145.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">145.006652832031</t>
+    <t xml:space="preserve">145.00666809082</t>
   </si>
   <si>
     <t xml:space="preserve">145.775939941406</t>
   </si>
   <si>
-    <t xml:space="preserve">144.814346313477</t>
+    <t xml:space="preserve">144.814361572266</t>
   </si>
   <si>
     <t xml:space="preserve">148.27604675293</t>
   </si>
   <si>
-    <t xml:space="preserve">143.275817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.60270690918</t>
+    <t xml:space="preserve">143.275833129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.602722167969</t>
   </si>
   <si>
     <t xml:space="preserve">142.698852539062</t>
@@ -3131,13 +3131,13 @@
     <t xml:space="preserve">143.083511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">139.525650024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.160339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.198745727539</t>
+    <t xml:space="preserve">139.525665283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.160354614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.198760986328</t>
   </si>
   <si>
     <t xml:space="preserve">139.910278320312</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">143.179641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">142.314239501953</t>
+    <t xml:space="preserve">142.314224243164</t>
   </si>
   <si>
     <t xml:space="preserve">130.87141418457</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">129.909820556641</t>
   </si>
   <si>
-    <t xml:space="preserve">133.371520996094</t>
+    <t xml:space="preserve">133.371505737305</t>
   </si>
   <si>
     <t xml:space="preserve">128.275115966797</t>
@@ -3182,19 +3182,19 @@
     <t xml:space="preserve">124.236473083496</t>
   </si>
   <si>
-    <t xml:space="preserve">122.890266418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.563148498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.812728881836</t>
+    <t xml:space="preserve">122.890258789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.563140869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.812744140625</t>
   </si>
   <si>
     <t xml:space="preserve">113.562911987305</t>
   </si>
   <si>
-    <t xml:space="preserve">115.389915466309</t>
+    <t xml:space="preserve">115.389923095703</t>
   </si>
   <si>
     <t xml:space="preserve">115.774551391602</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">118.755462646484</t>
   </si>
   <si>
-    <t xml:space="preserve">118.08235168457</t>
+    <t xml:space="preserve">118.082344055176</t>
   </si>
   <si>
     <t xml:space="preserve">122.313316345215</t>
   </si>
   <si>
-    <t xml:space="preserve">120.293991088867</t>
+    <t xml:space="preserve">120.293983459473</t>
   </si>
   <si>
     <t xml:space="preserve">120.101676940918</t>
@@ -3218,13 +3218,13 @@
     <t xml:space="preserve">119.236251831055</t>
   </si>
   <si>
-    <t xml:space="preserve">120.486312866211</t>
+    <t xml:space="preserve">120.486305236816</t>
   </si>
   <si>
     <t xml:space="preserve">116.736137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">116.832298278809</t>
+    <t xml:space="preserve">116.832290649414</t>
   </si>
   <si>
     <t xml:space="preserve">119.043937683105</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">121.736358642578</t>
   </si>
   <si>
-    <t xml:space="preserve">124.621109008789</t>
+    <t xml:space="preserve">124.621116638184</t>
   </si>
   <si>
     <t xml:space="preserve">123.274894714355</t>
@@ -3242,16 +3242,16 @@
     <t xml:space="preserve">121.544044494629</t>
   </si>
   <si>
-    <t xml:space="preserve">124.044158935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.332649230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.986656188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.659759521484</t>
+    <t xml:space="preserve">124.044166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.332626342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.986671447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.659774780273</t>
   </si>
   <si>
     <t xml:space="preserve">127.698173522949</t>
@@ -3260,25 +3260,25 @@
     <t xml:space="preserve">123.178741455078</t>
   </si>
   <si>
-    <t xml:space="preserve">114.52449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.889801025391</t>
+    <t xml:space="preserve">114.524490356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.889808654785</t>
   </si>
   <si>
     <t xml:space="preserve">114.236022949219</t>
   </si>
   <si>
-    <t xml:space="preserve">111.062797546387</t>
+    <t xml:space="preserve">111.062789916992</t>
   </si>
   <si>
     <t xml:space="preserve">112.216690063477</t>
   </si>
   <si>
-    <t xml:space="preserve">112.505180358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.947540283203</t>
+    <t xml:space="preserve">112.505172729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.947547912598</t>
   </si>
   <si>
     <t xml:space="preserve">116.447662353516</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">115.197601318359</t>
   </si>
   <si>
-    <t xml:space="preserve">119.140098571777</t>
+    <t xml:space="preserve">119.140083312988</t>
   </si>
   <si>
     <t xml:space="preserve">119.909355163574</t>
@@ -3296,31 +3296,31 @@
     <t xml:space="preserve">119.428565979004</t>
   </si>
   <si>
-    <t xml:space="preserve">117.890029907227</t>
+    <t xml:space="preserve">117.890037536621</t>
   </si>
   <si>
     <t xml:space="preserve">115.293762207031</t>
   </si>
   <si>
-    <t xml:space="preserve">113.178276062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.332397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.082580566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.39037322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.986427307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.274658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.71703338623</t>
+    <t xml:space="preserve">113.178283691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.332405090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.082588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.390365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.986419677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.27466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.71704864502</t>
   </si>
   <si>
     <t xml:space="preserve">120.774780273438</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">123.659530639648</t>
   </si>
   <si>
-    <t xml:space="preserve">128.9482421875</t>
+    <t xml:space="preserve">128.948226928711</t>
   </si>
   <si>
     <t xml:space="preserve">131.73681640625</t>
@@ -3338,13 +3338,13 @@
     <t xml:space="preserve">130.679077148438</t>
   </si>
   <si>
-    <t xml:space="preserve">126.832748413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.794319152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.46745300293</t>
+    <t xml:space="preserve">126.832740783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.794334411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.467437744141</t>
   </si>
   <si>
     <t xml:space="preserve">132.602233886719</t>
@@ -3353,43 +3353,43 @@
     <t xml:space="preserve">129.044387817383</t>
   </si>
   <si>
-    <t xml:space="preserve">131.159881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.967330932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.351951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.563362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.313537597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.371276855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.736602783203</t>
+    <t xml:space="preserve">131.159866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.967323303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.351959228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.563377380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.313552856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.371292114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.736595153809</t>
   </si>
   <si>
     <t xml:space="preserve">121.447883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">117.601554870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.947769165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.197830200195</t>
+    <t xml:space="preserve">117.6015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.947776794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.197845458984</t>
   </si>
   <si>
     <t xml:space="preserve">121.063255310059</t>
   </si>
   <si>
-    <t xml:space="preserve">117.505393981934</t>
+    <t xml:space="preserve">117.505401611328</t>
   </si>
   <si>
     <t xml:space="preserve">115.870704650879</t>
@@ -3404,13 +3404,13 @@
     <t xml:space="preserve">115.582237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">115.678398132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.178512573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.909133911133</t>
+    <t xml:space="preserve">115.67839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.178504943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.909126281738</t>
   </si>
   <si>
     <t xml:space="preserve">106.596168518066</t>
@@ -3431,37 +3431,37 @@
     <t xml:space="preserve">105.917831420898</t>
   </si>
   <si>
-    <t xml:space="preserve">102.816841125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.014739990234</t>
+    <t xml:space="preserve">102.816848754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.01473236084</t>
   </si>
   <si>
     <t xml:space="preserve">102.041610717773</t>
   </si>
   <si>
-    <t xml:space="preserve">108.437377929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.212623596191</t>
+    <t xml:space="preserve">108.437370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.212615966797</t>
   </si>
   <si>
     <t xml:space="preserve">113.185752868652</t>
   </si>
   <si>
-    <t xml:space="preserve">111.441444396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.829078674316</t>
+    <t xml:space="preserve">111.441452026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.829071044922</t>
   </si>
   <si>
     <t xml:space="preserve">107.274505615234</t>
   </si>
   <si>
-    <t xml:space="preserve">104.851860046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.658058166504</t>
+    <t xml:space="preserve">104.851867675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.658050537109</t>
   </si>
   <si>
     <t xml:space="preserve">101.847793579102</t>
@@ -3473,16 +3473,16 @@
     <t xml:space="preserve">103.495193481445</t>
   </si>
   <si>
-    <t xml:space="preserve">104.076622009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.402359008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.693077087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.860015869141</t>
+    <t xml:space="preserve">104.076629638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.402366638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.693069458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.860023498535</t>
   </si>
   <si>
     <t xml:space="preserve">116.189826965332</t>
@@ -3491,31 +3491,31 @@
     <t xml:space="preserve">114.348617553711</t>
   </si>
   <si>
-    <t xml:space="preserve">109.794059753418</t>
+    <t xml:space="preserve">109.794052124023</t>
   </si>
   <si>
     <t xml:space="preserve">107.468315124512</t>
   </si>
   <si>
-    <t xml:space="preserve">106.305442810059</t>
+    <t xml:space="preserve">106.305450439453</t>
   </si>
   <si>
     <t xml:space="preserve">102.332321166992</t>
   </si>
   <si>
-    <t xml:space="preserve">100.87873840332</t>
+    <t xml:space="preserve">100.878730773926</t>
   </si>
   <si>
     <t xml:space="preserve">103.979721069336</t>
   </si>
   <si>
-    <t xml:space="preserve">108.340469360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.643409729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.515563964844</t>
+    <t xml:space="preserve">108.340476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.643417358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.515556335449</t>
   </si>
   <si>
     <t xml:space="preserve">117.837219238281</t>
@@ -3524,13 +3524,13 @@
     <t xml:space="preserve">116.771255493164</t>
   </si>
   <si>
-    <t xml:space="preserve">114.445526123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.73624420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.026954650879</t>
+    <t xml:space="preserve">114.445518493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.736236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.026947021484</t>
   </si>
   <si>
     <t xml:space="preserve">115.317672729492</t>
@@ -3548,7 +3548,7 @@
     <t xml:space="preserve">113.476463317871</t>
   </si>
   <si>
-    <t xml:space="preserve">114.25171661377</t>
+    <t xml:space="preserve">114.251708984375</t>
   </si>
   <si>
     <t xml:space="preserve">114.833145141602</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">118.612464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">112.991943359375</t>
+    <t xml:space="preserve">112.99193572998</t>
   </si>
   <si>
     <t xml:space="preserve">111.053825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">112.701225280762</t>
+    <t xml:space="preserve">112.701232910156</t>
   </si>
   <si>
     <t xml:space="preserve">112.604316711426</t>
@@ -3584,34 +3584,34 @@
     <t xml:space="preserve">107.080696105957</t>
   </si>
   <si>
-    <t xml:space="preserve">110.375495910645</t>
+    <t xml:space="preserve">110.37548828125</t>
   </si>
   <si>
     <t xml:space="preserve">108.534278869629</t>
   </si>
   <si>
-    <t xml:space="preserve">110.181671142578</t>
+    <t xml:space="preserve">110.181678771973</t>
   </si>
   <si>
     <t xml:space="preserve">109.890960693359</t>
   </si>
   <si>
-    <t xml:space="preserve">111.247650146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.282653808594</t>
+    <t xml:space="preserve">111.247634887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.282661437988</t>
   </si>
   <si>
     <t xml:space="preserve">112.410507202148</t>
   </si>
   <si>
-    <t xml:space="preserve">114.63932800293</t>
+    <t xml:space="preserve">114.639343261719</t>
   </si>
   <si>
     <t xml:space="preserve">117.934120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">117.25577545166</t>
+    <t xml:space="preserve">117.255783081055</t>
   </si>
   <si>
     <t xml:space="preserve">117.352691650391</t>
@@ -3638,10 +3638,10 @@
     <t xml:space="preserve">120.550575256348</t>
   </si>
   <si>
-    <t xml:space="preserve">122.779403686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.26392364502</t>
+    <t xml:space="preserve">122.779411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.263931274414</t>
   </si>
   <si>
     <t xml:space="preserve">121.810340881348</t>
@@ -3653,13 +3653,13 @@
     <t xml:space="preserve">123.748458862305</t>
   </si>
   <si>
-    <t xml:space="preserve">131.985427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.888534545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.179244995117</t>
+    <t xml:space="preserve">131.985443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.888549804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.179260253906</t>
   </si>
   <si>
     <t xml:space="preserve">130.531845092773</t>
@@ -3671,22 +3671,22 @@
     <t xml:space="preserve">127.043251037598</t>
   </si>
   <si>
-    <t xml:space="preserve">124.814430236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.686576843262</t>
+    <t xml:space="preserve">124.814422607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.686561584473</t>
   </si>
   <si>
     <t xml:space="preserve">126.849433898926</t>
   </si>
   <si>
-    <t xml:space="preserve">127.333961486816</t>
+    <t xml:space="preserve">127.333953857422</t>
   </si>
   <si>
     <t xml:space="preserve">126.946342468262</t>
   </si>
   <si>
-    <t xml:space="preserve">124.136085510254</t>
+    <t xml:space="preserve">124.136093139648</t>
   </si>
   <si>
     <t xml:space="preserve">123.845367431641</t>
@@ -3695,10 +3695,10 @@
     <t xml:space="preserve">121.422729492188</t>
   </si>
   <si>
-    <t xml:space="preserve">121.325820922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.259857177734</t>
+    <t xml:space="preserve">121.325813293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.259864807129</t>
   </si>
   <si>
     <t xml:space="preserve">120.35676574707</t>
@@ -3707,28 +3707,28 @@
     <t xml:space="preserve">118.321746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">116.8681640625</t>
+    <t xml:space="preserve">116.868156433105</t>
   </si>
   <si>
     <t xml:space="preserve">115.802200317383</t>
   </si>
   <si>
-    <t xml:space="preserve">113.864097595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.960990905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.088844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.472396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.824996948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.414573669434</t>
+    <t xml:space="preserve">113.86408996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.960998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.088836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.472389221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.825004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.414581298828</t>
   </si>
   <si>
     <t xml:space="preserve">109.987861633301</t>
@@ -3749,16 +3749,16 @@
     <t xml:space="preserve">116.286727905273</t>
   </si>
   <si>
-    <t xml:space="preserve">119.193893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.09700012207</t>
+    <t xml:space="preserve">119.193901062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.096992492676</t>
   </si>
   <si>
     <t xml:space="preserve">119.678428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">116.383628845215</t>
+    <t xml:space="preserve">116.383636474609</t>
   </si>
   <si>
     <t xml:space="preserve">115.123870849609</t>
@@ -3770,19 +3770,19 @@
     <t xml:space="preserve">110.569297790527</t>
   </si>
   <si>
-    <t xml:space="preserve">110.956924438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.921905517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.952850341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.565223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.045677185059</t>
+    <t xml:space="preserve">110.956916809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.921913146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.952842712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.565231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.045684814453</t>
   </si>
   <si>
     <t xml:space="preserve">104.754959106445</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">103.204475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">100.588027954102</t>
+    <t xml:space="preserve">100.588020324707</t>
   </si>
   <si>
     <t xml:space="preserve">100.297302246094</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">103.107566833496</t>
   </si>
   <si>
-    <t xml:space="preserve">104.561149597168</t>
+    <t xml:space="preserve">104.561157226562</t>
   </si>
   <si>
     <t xml:space="preserve">107.37141418457</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">111.150726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">110.763107299805</t>
+    <t xml:space="preserve">110.763114929199</t>
   </si>
   <si>
     <t xml:space="preserve">109.503341674805</t>
@@ -3851,7 +3851,7 @@
     <t xml:space="preserve">109.115715026855</t>
   </si>
   <si>
-    <t xml:space="preserve">110.278579711914</t>
+    <t xml:space="preserve">110.278587341309</t>
   </si>
   <si>
     <t xml:space="preserve">109.697143554688</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">100.975639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">100.200393676758</t>
+    <t xml:space="preserve">100.200401306152</t>
   </si>
   <si>
     <t xml:space="preserve">100.491111755371</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">101.26636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">101.653984069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.39421081543</t>
+    <t xml:space="preserve">101.65397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.394203186035</t>
   </si>
   <si>
     <t xml:space="preserve">99.3282470703125</t>
@@ -3899,13 +3899,13 @@
     <t xml:space="preserve">99.6189651489258</t>
   </si>
   <si>
-    <t xml:space="preserve">99.2313461303711</t>
+    <t xml:space="preserve">99.2313385009766</t>
   </si>
   <si>
     <t xml:space="preserve">102.138511657715</t>
   </si>
   <si>
-    <t xml:space="preserve">101.75089263916</t>
+    <t xml:space="preserve">101.750885009766</t>
   </si>
   <si>
     <t xml:space="preserve">99.8127746582031</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">97.1963272094727</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6808471679688</t>
+    <t xml:space="preserve">97.6808547973633</t>
   </si>
   <si>
     <t xml:space="preserve">99.0078277587891</t>
@@ -5319,6 +5319,9 @@
   </si>
   <si>
     <t xml:space="preserve">96.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8499984741211</t>
   </si>
 </sst>
 </file>
@@ -71931,7 +71934,7 @@
     </row>
     <row r="2550">
       <c r="A2550" s="1" t="n">
-        <v>46036.6912037037</v>
+        <v>46036.3333333333</v>
       </c>
       <c r="B2550" t="n">
         <v>81632</v>
@@ -71952,6 +71955,32 @@
         <v>1768</v>
       </c>
       <c r="H2550" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2551">
+      <c r="A2551" s="1" t="n">
+        <v>46037.6911458333</v>
+      </c>
+      <c r="B2551" t="n">
+        <v>46727</v>
+      </c>
+      <c r="C2551" t="n">
+        <v>96.8499984741211</v>
+      </c>
+      <c r="D2551" t="n">
+        <v>94.0999984741211</v>
+      </c>
+      <c r="E2551" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="F2551" t="n">
+        <v>93.8499984741211</v>
+      </c>
+      <c r="G2551" t="s">
+        <v>1769</v>
+      </c>
+      <c r="H2551" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="1770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="1771">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,28 +44,28 @@
     <t xml:space="preserve">SES.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5321063995361</t>
+    <t xml:space="preserve">13.5321083068848</t>
   </si>
   <si>
     <t xml:space="preserve">13.2523746490479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9464168548584</t>
+    <t xml:space="preserve">12.9464149475098</t>
   </si>
   <si>
     <t xml:space="preserve">13.1125068664551</t>
   </si>
   <si>
-    <t xml:space="preserve">12.858998298645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0513153076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9901247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9376735687256</t>
+    <t xml:space="preserve">12.8589992523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0513143539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.990122795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9376726150513</t>
   </si>
   <si>
     <t xml:space="preserve">13.1037654876709</t>
@@ -74,31 +74,31 @@
     <t xml:space="preserve">13.0250902175903</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8502569198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2383403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5880069732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7890653610229</t>
+    <t xml:space="preserve">12.8502578735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2383394241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5880060195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7890663146973</t>
   </si>
   <si>
     <t xml:space="preserve">12.7191324234009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6841650009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.605489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3257579803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0460214614868</t>
+    <t xml:space="preserve">12.6841640472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6054906845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3257570266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0460224151611</t>
   </si>
   <si>
     <t xml:space="preserve">12.1771488189697</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">12.1421823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9270896911621</t>
+    <t xml:space="preserve">10.9270877838135</t>
   </si>
   <si>
     <t xml:space="preserve">10.9795389175415</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">11.4515886306763</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0984735488892</t>
+    <t xml:space="preserve">12.0984725952148</t>
   </si>
   <si>
     <t xml:space="preserve">12.1072149276733</t>
@@ -128,19 +128,19 @@
     <t xml:space="preserve">11.8886728286743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760885238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9323816299438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0110569000244</t>
+    <t xml:space="preserve">11.9760894775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9323806762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0110559463501</t>
   </si>
   <si>
     <t xml:space="preserve">12.0809898376465</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8012571334839</t>
+    <t xml:space="preserve">11.8012561798096</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334400177002</t>
@@ -149,34 +149,34 @@
     <t xml:space="preserve">11.8274803161621</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0635061264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5005903244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6754236221313</t>
+    <t xml:space="preserve">12.0635080337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5005912780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.675422668457</t>
   </si>
   <si>
     <t xml:space="preserve">12.7978076934814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1649570465088</t>
+    <t xml:space="preserve">13.1649551391602</t>
   </si>
   <si>
     <t xml:space="preserve">13.1562156677246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0687980651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1212501525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1911811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7540979385376</t>
+    <t xml:space="preserve">13.0687990188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1212491989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1911821365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7540969848633</t>
   </si>
   <si>
     <t xml:space="preserve">12.8939647674561</t>
@@ -197,13 +197,13 @@
     <t xml:space="preserve">13.4534320831299</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7069406509399</t>
+    <t xml:space="preserve">13.7069416046143</t>
   </si>
   <si>
     <t xml:space="preserve">13.4709148406982</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4621734619141</t>
+    <t xml:space="preserve">13.4621725082397</t>
   </si>
   <si>
     <t xml:space="preserve">13.208664894104</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">13.3223075866699</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0950241088867</t>
+    <t xml:space="preserve">13.0950231552124</t>
   </si>
   <si>
     <t xml:space="preserve">12.9988641738892</t>
@@ -224,10 +224,10 @@
     <t xml:space="preserve">12.4481401443481</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3782072067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0285396575928</t>
+    <t xml:space="preserve">12.3782081604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0285387039185</t>
   </si>
   <si>
     <t xml:space="preserve">12.1509237289429</t>
@@ -239,13 +239,13 @@
     <t xml:space="preserve">12.5617809295654</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5268154144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6317157745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3694639205933</t>
+    <t xml:space="preserve">12.5268144607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6317138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3694658279419</t>
   </si>
   <si>
     <t xml:space="preserve">12.771580696106</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">12.4306554794312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2820501327515</t>
+    <t xml:space="preserve">12.2820491790771</t>
   </si>
   <si>
     <t xml:space="preserve">12.1946315765381</t>
@@ -263,16 +263,16 @@
     <t xml:space="preserve">12.2470817565918</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4131746292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5093307495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3869485855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8187408447266</t>
+    <t xml:space="preserve">12.4131736755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.509331703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3869504928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8187398910522</t>
   </si>
   <si>
     <t xml:space="preserve">11.8449649810791</t>
@@ -284,31 +284,31 @@
     <t xml:space="preserve">12.5792655944824</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2208566665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1858882904053</t>
+    <t xml:space="preserve">12.2208557128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1858901977539</t>
   </si>
   <si>
     <t xml:space="preserve">12.7803239822388</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7278718948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8764820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.806547164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7628402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8677396774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8327732086182</t>
+    <t xml:space="preserve">12.7278728485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8764810562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8065490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7628383636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8677406311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8327741622925</t>
   </si>
   <si>
     <t xml:space="preserve">12.5355558395386</t>
@@ -317,52 +317,52 @@
     <t xml:space="preserve">13.1824398040771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0338306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3048238754272</t>
+    <t xml:space="preserve">13.0338315963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3048248291016</t>
   </si>
   <si>
     <t xml:space="preserve">13.2611150741577</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3747568130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6020421981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6894578933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7244234085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7514762878418</t>
+    <t xml:space="preserve">13.3747577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6020412445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6894559860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7244243621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7514753341675</t>
   </si>
   <si>
     <t xml:space="preserve">13.5711288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8687028884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6252326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6432666778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6613025665283</t>
+    <t xml:space="preserve">13.8687009811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6252336502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6432676315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.661301612854</t>
   </si>
   <si>
     <t xml:space="preserve">13.598180770874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6162166595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5260419845581</t>
+    <t xml:space="preserve">13.6162157058716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5260429382324</t>
   </si>
   <si>
     <t xml:space="preserve">13.5530939102173</t>
@@ -371,19 +371,19 @@
     <t xml:space="preserve">13.3456954956055</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5801467895508</t>
+    <t xml:space="preserve">13.5801448822021</t>
   </si>
   <si>
     <t xml:space="preserve">13.6973714828491</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7785263061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6703205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7965631484985</t>
+    <t xml:space="preserve">13.7785272598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6703195571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7965621948242</t>
   </si>
   <si>
     <t xml:space="preserve">13.9769105911255</t>
@@ -395,25 +395,25 @@
     <t xml:space="preserve">14.0129795074463</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9047718048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1031532287598</t>
+    <t xml:space="preserve">13.9047708511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1031541824341</t>
   </si>
   <si>
     <t xml:space="preserve">14.2474308013916</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1572561264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3646574020386</t>
+    <t xml:space="preserve">14.1572570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3646554946899</t>
   </si>
   <si>
     <t xml:space="preserve">14.4187602996826</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5179510116577</t>
+    <t xml:space="preserve">14.517951965332</t>
   </si>
   <si>
     <t xml:space="preserve">14.6081266403198</t>
@@ -422,64 +422,64 @@
     <t xml:space="preserve">14.6622285842896</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3917074203491</t>
+    <t xml:space="preserve">14.3917093276978</t>
   </si>
   <si>
     <t xml:space="preserve">14.3105516433716</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3015356063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5450019836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.644193649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7343683242798</t>
+    <t xml:space="preserve">14.30153465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5450029373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6441955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7343702316284</t>
   </si>
   <si>
     <t xml:space="preserve">14.7163343429565</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6351776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6261577606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6892824172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8245420455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8065061569214</t>
+    <t xml:space="preserve">14.635178565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6261587142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.689284324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8245410919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.80650806427</t>
   </si>
   <si>
     <t xml:space="preserve">14.7433853149414</t>
   </si>
   <si>
-    <t xml:space="preserve">14.581072807312</t>
+    <t xml:space="preserve">14.5810718536377</t>
   </si>
   <si>
     <t xml:space="preserve">14.698296546936</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5089340209961</t>
+    <t xml:space="preserve">14.5089330673218</t>
   </si>
   <si>
     <t xml:space="preserve">14.6712484359741</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6532125473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.923731803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.049976348877</t>
+    <t xml:space="preserve">14.6532135009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9237337112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0499782562256</t>
   </si>
   <si>
     <t xml:space="preserve">15.2122898101807</t>
@@ -488,10 +488,10 @@
     <t xml:space="preserve">15.3746004104614</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5549468994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9246625900269</t>
+    <t xml:space="preserve">15.5549488067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9246587753296</t>
   </si>
   <si>
     <t xml:space="preserve">15.7803802490234</t>
@@ -500,37 +500,37 @@
     <t xml:space="preserve">15.8705558776855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8344860076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7082414627075</t>
+    <t xml:space="preserve">15.8344879150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7082433700562</t>
   </si>
   <si>
     <t xml:space="preserve">15.9517116546631</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7452354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8714790344238</t>
+    <t xml:space="preserve">16.7452392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8714809417725</t>
   </si>
   <si>
     <t xml:space="preserve">17.0879001617432</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1510238647461</t>
+    <t xml:space="preserve">17.1510219573975</t>
   </si>
   <si>
     <t xml:space="preserve">17.2231597900391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9796943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9075508117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3043155670166</t>
+    <t xml:space="preserve">16.9796924591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9075527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.304313659668</t>
   </si>
   <si>
     <t xml:space="preserve">17.0337924957275</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">17.4756450653076</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3223514556885</t>
+    <t xml:space="preserve">17.3223495483398</t>
   </si>
   <si>
     <t xml:space="preserve">17.1690578460693</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">17.583854675293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5748348236084</t>
+    <t xml:space="preserve">17.574836730957</t>
   </si>
   <si>
     <t xml:space="preserve">17.5658206939697</t>
@@ -563,46 +563,46 @@
     <t xml:space="preserve">17.1870918273926</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8534507751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8444309234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.95263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7272033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6911392211914</t>
+    <t xml:space="preserve">16.8534488677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8444290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9526386260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7272071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6911373138428</t>
   </si>
   <si>
     <t xml:space="preserve">16.8624649047852</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0428123474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8173809051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9977245330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7722930908203</t>
+    <t xml:space="preserve">17.0428142547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8173789978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9977264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7722949981689</t>
   </si>
   <si>
     <t xml:space="preserve">17.0067462921143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1961078643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3584213256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6199264526367</t>
+    <t xml:space="preserve">17.1961059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3584232330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6199245452881</t>
   </si>
   <si>
     <t xml:space="preserve">17.7642002105713</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">18.0076675415039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9896354675293</t>
+    <t xml:space="preserve">17.9896373748779</t>
   </si>
   <si>
     <t xml:space="preserve">17.9445457458496</t>
@@ -620,22 +620,22 @@
     <t xml:space="preserve">17.9535675048828</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8092880249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2601585388184</t>
+    <t xml:space="preserve">17.809289932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2601566314697</t>
   </si>
   <si>
     <t xml:space="preserve">18.7561111450195</t>
   </si>
   <si>
-    <t xml:space="preserve">18.846284866333</t>
+    <t xml:space="preserve">18.8462829589844</t>
   </si>
   <si>
     <t xml:space="preserve">18.9364585876465</t>
   </si>
   <si>
-    <t xml:space="preserve">18.620849609375</t>
+    <t xml:space="preserve">18.6208515167236</t>
   </si>
   <si>
     <t xml:space="preserve">19.2971534729004</t>
@@ -647,34 +647,34 @@
     <t xml:space="preserve">19.3512554168701</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6668663024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6488304138184</t>
+    <t xml:space="preserve">19.6668643951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6488361358643</t>
   </si>
   <si>
     <t xml:space="preserve">19.5586566925049</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2520694732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1709098815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.134838104248</t>
+    <t xml:space="preserve">19.252067565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1709117889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1348400115967</t>
   </si>
   <si>
     <t xml:space="preserve">19.197961807251</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9544944763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9094047546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0897541046143</t>
+    <t xml:space="preserve">18.9544925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9094066619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0897521972656</t>
   </si>
   <si>
     <t xml:space="preserve">18.5757637023926</t>
@@ -695,19 +695,19 @@
     <t xml:space="preserve">19.3873271942139</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0185451507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3612022399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8301048278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2809715270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8751907348633</t>
+    <t xml:space="preserve">20.0185432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3612003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8301067352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2809734344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8751926422119</t>
   </si>
   <si>
     <t xml:space="preserve">20.9292945861816</t>
@@ -716,13 +716,13 @@
     <t xml:space="preserve">21.1006259918213</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0104541778564</t>
+    <t xml:space="preserve">21.0104503631592</t>
   </si>
   <si>
     <t xml:space="preserve">20.5685977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7218971252441</t>
+    <t xml:space="preserve">20.7218990325928</t>
   </si>
   <si>
     <t xml:space="preserve">20.6046714782715</t>
@@ -731,34 +731,34 @@
     <t xml:space="preserve">20.1898708343506</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3792362213135</t>
+    <t xml:space="preserve">20.3792343139648</t>
   </si>
   <si>
     <t xml:space="preserve">20.6497573852539</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6416683197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3711452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.380163192749</t>
+    <t xml:space="preserve">21.6416645050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3711471557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3801651000977</t>
   </si>
   <si>
     <t xml:space="preserve">22.0925350189209</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6245632171631</t>
+    <t xml:space="preserve">22.6245613098145</t>
   </si>
   <si>
     <t xml:space="preserve">22.7147331237793</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8049068450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5984344482422</t>
+    <t xml:space="preserve">22.8049087524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5984382629395</t>
   </si>
   <si>
     <t xml:space="preserve">24.0763549804688</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">23.8599376678467</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8058338165283</t>
+    <t xml:space="preserve">23.805835723877</t>
   </si>
   <si>
     <t xml:space="preserve">23.5082607269287</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">22.994270324707</t>
   </si>
   <si>
-    <t xml:space="preserve">22.480281829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5434036254883</t>
+    <t xml:space="preserve">22.4802856445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5434017181396</t>
   </si>
   <si>
     <t xml:space="preserve">22.705717086792</t>
@@ -797,28 +797,28 @@
     <t xml:space="preserve">22.4532299041748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4622459411621</t>
+    <t xml:space="preserve">22.4622478485107</t>
   </si>
   <si>
     <t xml:space="preserve">22.0023593902588</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1827087402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7237529754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3630523681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2097625732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4883728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9212036132812</t>
+    <t xml:space="preserve">22.182710647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7237548828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3630561828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2097606658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4883708953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9212017059326</t>
   </si>
   <si>
     <t xml:space="preserve">21.8761177062988</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">22.074499130249</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2999324798584</t>
+    <t xml:space="preserve">22.299934387207</t>
   </si>
   <si>
     <t xml:space="preserve">22.8139247894287</t>
@@ -845,58 +845,58 @@
     <t xml:space="preserve">22.1917266845703</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3540420532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5253658294678</t>
+    <t xml:space="preserve">22.354040145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5253677368164</t>
   </si>
   <si>
     <t xml:space="preserve">22.6065235137939</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6335754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2458305358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2277946472168</t>
+    <t xml:space="preserve">22.6335773468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2458324432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2277984619141</t>
   </si>
   <si>
     <t xml:space="preserve">22.1286067962646</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0835208892822</t>
+    <t xml:space="preserve">22.083517074585</t>
   </si>
   <si>
     <t xml:space="preserve">22.2007427215576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1376190185547</t>
+    <t xml:space="preserve">22.137622833252</t>
   </si>
   <si>
     <t xml:space="preserve">22.1466388702393</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5965785980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3260593414307</t>
+    <t xml:space="preserve">21.5965805053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.326057434082</t>
   </si>
   <si>
     <t xml:space="preserve">21.560510635376</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0294132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6867542266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2368125915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3720760345459</t>
+    <t xml:space="preserve">22.0294151306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6867523193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2368144989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3720741271973</t>
   </si>
   <si>
     <t xml:space="preserve">22.3991260528564</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">22.6606292724609</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0123081207275</t>
+    <t xml:space="preserve">23.0123062133789</t>
   </si>
   <si>
     <t xml:space="preserve">23.5193881988525</t>
@@ -917,10 +917,10 @@
     <t xml:space="preserve">23.2704582214355</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1739845275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7087249755859</t>
+    <t xml:space="preserve">24.1739864349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7087230682373</t>
   </si>
   <si>
     <t xml:space="preserve">24.7732639312744</t>
@@ -929,46 +929,46 @@
     <t xml:space="preserve">25.2434673309326</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8150882720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7966480255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6860122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6675701141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0086994171143</t>
+    <t xml:space="preserve">25.8150844573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7966461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6860103607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6675720214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0087013244629</t>
   </si>
   <si>
     <t xml:space="preserve">25.8888454437256</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9810447692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0916748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9072856903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8058662414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9533824920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6767921447754</t>
+    <t xml:space="preserve">25.9810409545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0916767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.907283782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8058681488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9533805847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.676794052124</t>
   </si>
   <si>
     <t xml:space="preserve">25.6583518981934</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0775127410889</t>
+    <t xml:space="preserve">25.0775165557861</t>
   </si>
   <si>
     <t xml:space="preserve">25.4001998901367</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">25.2619037628174</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3264408111572</t>
+    <t xml:space="preserve">25.3264427185059</t>
   </si>
   <si>
     <t xml:space="preserve">24.8009223937988</t>
@@ -986,91 +986,91 @@
     <t xml:space="preserve">25.4186401367188</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6441898345947</t>
+    <t xml:space="preserve">24.6441879272461</t>
   </si>
   <si>
     <t xml:space="preserve">24.8562393188477</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9576549530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8931217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.187479019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9754276275635</t>
+    <t xml:space="preserve">24.9576568603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8931198120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1874809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9754257202148</t>
   </si>
   <si>
     <t xml:space="preserve">23.1229419708252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2335815429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9938659667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0123062133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7818145751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.671178817749</t>
+    <t xml:space="preserve">23.2335796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9938678741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0123043060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.781810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6711769104004</t>
   </si>
   <si>
     <t xml:space="preserve">22.4960041046143</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7264938354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5052223205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3208312988281</t>
+    <t xml:space="preserve">22.7264957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5052242279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3208332061768</t>
   </si>
   <si>
     <t xml:space="preserve">22.5882015228271</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1137199401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.910888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3995323181152</t>
+    <t xml:space="preserve">23.1137218475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9108924865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3995304107666</t>
   </si>
   <si>
     <t xml:space="preserve">23.7775402069092</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6208057403564</t>
+    <t xml:space="preserve">23.6208038330078</t>
   </si>
   <si>
     <t xml:space="preserve">23.1413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9846458435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8740139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7357139587402</t>
+    <t xml:space="preserve">22.9846477508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8740119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7357158660889</t>
   </si>
   <si>
     <t xml:space="preserve">22.6896171569824</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3257751464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7406578063965</t>
+    <t xml:space="preserve">23.3257732391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7406597137451</t>
   </si>
   <si>
     <t xml:space="preserve">23.980375289917</t>
@@ -1079,100 +1079,100 @@
     <t xml:space="preserve">23.9711513519287</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0633506774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2477436065674</t>
+    <t xml:space="preserve">24.0633525848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2477416992188</t>
   </si>
   <si>
     <t xml:space="preserve">24.3860378265381</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1555461883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6165294647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8611850738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6306934356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2158069610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1697101593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080024719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4462985992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5384960174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1236133575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4321327209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6484603881836</t>
+    <t xml:space="preserve">24.1555423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6165313720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8611831665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6306915283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2158107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1697082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4463024139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5384941101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1236114501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4321365356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6484622955322</t>
   </si>
   <si>
     <t xml:space="preserve">24.0172481536865</t>
   </si>
   <si>
-    <t xml:space="preserve">24.109447479248</t>
+    <t xml:space="preserve">24.1094455718994</t>
   </si>
   <si>
     <t xml:space="preserve">24.3399391174316</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2016410827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2938404083252</t>
+    <t xml:space="preserve">24.2016429901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2938423156738</t>
   </si>
   <si>
     <t xml:space="preserve">24.7548236846924</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6626262664795</t>
+    <t xml:space="preserve">24.6626300811768</t>
   </si>
   <si>
     <t xml:space="preserve">24.985315322876</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4923973083496</t>
+    <t xml:space="preserve">25.4923992156982</t>
   </si>
   <si>
     <t xml:space="preserve">25.7228908538818</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5704307556152</t>
+    <t xml:space="preserve">24.5704326629639</t>
   </si>
   <si>
     <t xml:space="preserve">25.5845947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9994831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4143657684326</t>
+    <t xml:space="preserve">25.9994812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.414363861084</t>
   </si>
   <si>
     <t xml:space="preserve">27.5668258666992</t>
   </si>
   <si>
-    <t xml:space="preserve">27.751220703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0739059448242</t>
+    <t xml:space="preserve">27.7512187957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0739078521729</t>
   </si>
   <si>
     <t xml:space="preserve">27.5207271575928</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">26.5065631866455</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0314140319824</t>
+    <t xml:space="preserve">25.0314121246338</t>
   </si>
   <si>
     <t xml:space="preserve">24.5243320465088</t>
@@ -1196,40 +1196,40 @@
     <t xml:space="preserve">26.5987606048584</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4604663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2299728393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3221683502197</t>
+    <t xml:space="preserve">26.4604644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2299747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3221702575684</t>
   </si>
   <si>
     <t xml:space="preserve">27.1980381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2760715484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2902374267578</t>
+    <t xml:space="preserve">26.2760696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2902355194092</t>
   </si>
   <si>
     <t xml:space="preserve">27.3824348449707</t>
   </si>
   <si>
-    <t xml:space="preserve">27.474630355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5526599884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.829252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.105842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8753509521484</t>
+    <t xml:space="preserve">27.4746265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.552661895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8292503356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1058406829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8753490447998</t>
   </si>
   <si>
     <t xml:space="preserve">27.8434162139893</t>
@@ -1241,25 +1241,25 @@
     <t xml:space="preserve">28.5809898376465</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9356136322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8114814758301</t>
+    <t xml:space="preserve">27.9356117248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8114795684814</t>
   </si>
   <si>
     <t xml:space="preserve">28.1661033630371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7192821502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1200065612793</t>
+    <t xml:space="preserve">28.7192840576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1200046539307</t>
   </si>
   <si>
     <t xml:space="preserve">27.0597438812256</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9675445556641</t>
+    <t xml:space="preserve">26.9675464630127</t>
   </si>
   <si>
     <t xml:space="preserve">27.1519412994385</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">26.6909580230713</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7831516265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.045581817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6590232849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9214515686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1828804016113</t>
+    <t xml:space="preserve">26.7831535339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0455780029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6590213775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9214477539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1828784942627</t>
   </si>
   <si>
     <t xml:space="preserve">26.088695526123</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">26.4654312133789</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8061466217041</t>
+    <t xml:space="preserve">25.8061447143555</t>
   </si>
   <si>
     <t xml:space="preserve">25.7119655609131</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">25.1468677520752</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3352317810059</t>
+    <t xml:space="preserve">25.3352336883545</t>
   </si>
   <si>
     <t xml:space="preserve">24.9114112854004</t>
@@ -1331,10 +1331,10 @@
     <t xml:space="preserve">22.5097427368164</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4155559539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1801013946533</t>
+    <t xml:space="preserve">22.4155578613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1800994873047</t>
   </si>
   <si>
     <t xml:space="preserve">22.0388278961182</t>
@@ -1346,19 +1346,19 @@
     <t xml:space="preserve">22.4626502990723</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2271938323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4044818878174</t>
+    <t xml:space="preserve">22.2271919250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.404483795166</t>
   </si>
   <si>
     <t xml:space="preserve">23.2161159515381</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8864727020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.498664855957</t>
+    <t xml:space="preserve">22.886474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4986629486084</t>
   </si>
   <si>
     <t xml:space="preserve">22.5568351745605</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">21.1911792755127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0028133392334</t>
+    <t xml:space="preserve">21.0028114318848</t>
   </si>
   <si>
     <t xml:space="preserve">21.096996307373</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">20.8615398406982</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3795471191406</t>
+    <t xml:space="preserve">21.379545211792</t>
   </si>
   <si>
     <t xml:space="preserve">21.4737300872803</t>
@@ -1391,28 +1391,28 @@
     <t xml:space="preserve">22.274284362793</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7562789916992</t>
+    <t xml:space="preserve">21.7562808990479</t>
   </si>
   <si>
     <t xml:space="preserve">21.9446411132812</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5679130554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.520824432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3324527740479</t>
+    <t xml:space="preserve">21.5679111480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5208225250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3324546813965</t>
   </si>
   <si>
     <t xml:space="preserve">21.2382717132568</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8393821716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7922916412354</t>
+    <t xml:space="preserve">22.8393840789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7922897338867</t>
   </si>
   <si>
     <t xml:space="preserve">23.5457553863525</t>
@@ -1421,13 +1421,13 @@
     <t xml:space="preserve">23.6399383544922</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7341232299805</t>
+    <t xml:space="preserve">23.7341213226318</t>
   </si>
   <si>
     <t xml:space="preserve">23.6870307922363</t>
   </si>
   <si>
-    <t xml:space="preserve">23.781213760376</t>
+    <t xml:space="preserve">23.7812156677246</t>
   </si>
   <si>
     <t xml:space="preserve">24.0166721343994</t>
@@ -1436,40 +1436,40 @@
     <t xml:space="preserve">24.2992191314697</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1579456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2521266937256</t>
+    <t xml:space="preserve">24.1579437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2521286010742</t>
   </si>
   <si>
     <t xml:space="preserve">24.7230434417725</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6288623809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.675952911377</t>
+    <t xml:space="preserve">24.6288604736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6759490966797</t>
   </si>
   <si>
     <t xml:space="preserve">24.5817718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7701358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9584980010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9003295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7590560913086</t>
+    <t xml:space="preserve">24.770133972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9584999084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9003314971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7590579986572</t>
   </si>
   <si>
     <t xml:space="preserve">25.9474201202393</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2770652770996</t>
+    <t xml:space="preserve">26.277063369751</t>
   </si>
   <si>
     <t xml:space="preserve">26.9363441467285</t>
@@ -1490,10 +1490,10 @@
     <t xml:space="preserve">27.4543495178223</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5014419555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3130760192871</t>
+    <t xml:space="preserve">27.5014400482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3130779266357</t>
   </si>
   <si>
     <t xml:space="preserve">27.0776195526123</t>
@@ -1502,22 +1502,22 @@
     <t xml:space="preserve">26.7008857727051</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6537952423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6067047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.994514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1357898712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0416069030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6177825927734</t>
+    <t xml:space="preserve">26.6537933349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6067028045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9945163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1357879638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0416049957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6177845001221</t>
   </si>
   <si>
     <t xml:space="preserve">25.4294166564941</t>
@@ -1529,19 +1529,19 @@
     <t xml:space="preserve">25.0997753143311</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8643169403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4404945373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5235977172852</t>
+    <t xml:space="preserve">24.8643188476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4404926300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5235996246338</t>
   </si>
   <si>
     <t xml:space="preserve">26.3712463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3241577148438</t>
+    <t xml:space="preserve">26.3241558074951</t>
   </si>
   <si>
     <t xml:space="preserve">26.7950706481934</t>
@@ -1556,49 +1556,49 @@
     <t xml:space="preserve">27.1718044281006</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5485324859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6898097991943</t>
+    <t xml:space="preserve">27.5485343933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6898078918457</t>
   </si>
   <si>
     <t xml:space="preserve">28.1136322021484</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3961791992188</t>
+    <t xml:space="preserve">28.3961811065674</t>
   </si>
   <si>
     <t xml:space="preserve">28.7258224487305</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9141883850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9502010345459</t>
+    <t xml:space="preserve">28.9141864776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9501991271973</t>
   </si>
   <si>
     <t xml:space="preserve">29.7618350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3269348144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3740253448486</t>
+    <t xml:space="preserve">30.3269329071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3740272521973</t>
   </si>
   <si>
     <t xml:space="preserve">31.504222869873</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6925888061523</t>
+    <t xml:space="preserve">31.6925849914551</t>
   </si>
   <si>
     <t xml:space="preserve">32.4460525512695</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4931373596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.482063293457</t>
+    <t xml:space="preserve">32.4931411743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4820671081543</t>
   </si>
   <si>
     <t xml:space="preserve">33.6704292297363</t>
@@ -1607,67 +1607,67 @@
     <t xml:space="preserve">33.2936973571777</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5762481689453</t>
+    <t xml:space="preserve">33.5762519836426</t>
   </si>
   <si>
     <t xml:space="preserve">33.905891418457</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2466087341309</t>
+    <t xml:space="preserve">33.2466049194336</t>
   </si>
   <si>
     <t xml:space="preserve">32.8698768615723</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1524238586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0582389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5873222351074</t>
+    <t xml:space="preserve">33.1524276733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.058235168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5873184204102</t>
   </si>
   <si>
     <t xml:space="preserve">32.3047752380371</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9280471801758</t>
+    <t xml:space="preserve">31.9280433654785</t>
   </si>
   <si>
     <t xml:space="preserve">31.4571285247803</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3629398345947</t>
+    <t xml:space="preserve">31.3629455566406</t>
   </si>
   <si>
     <t xml:space="preserve">30.8920307159424</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0803966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0333061218262</t>
+    <t xml:space="preserve">31.0804004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0333080291748</t>
   </si>
   <si>
     <t xml:space="preserve">30.6565723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6094818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2687606811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9862155914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4100360870361</t>
+    <t xml:space="preserve">30.6094856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.268762588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.986213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4100341796875</t>
   </si>
   <si>
     <t xml:space="preserve">30.8449382781982</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1745796203613</t>
+    <t xml:space="preserve">31.17458152771</t>
   </si>
   <si>
     <t xml:space="preserve">31.8809509277344</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">32.0222282409668</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7396850585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.000072479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4709854125977</t>
+    <t xml:space="preserve">31.7396812438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0000686645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4709815979004</t>
   </si>
   <si>
     <t xml:space="preserve">35.7895469665527</t>
@@ -1691,16 +1691,16 @@
     <t xml:space="preserve">36.5901031494141</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7784729003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.155200958252</t>
+    <t xml:space="preserve">36.7784690856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1552047729492</t>
   </si>
   <si>
     <t xml:space="preserve">37.6732063293457</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0846748352051</t>
+    <t xml:space="preserve">38.0846710205078</t>
   </si>
   <si>
     <t xml:space="preserve">38.2282104492188</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">37.367000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">37.797607421875</t>
+    <t xml:space="preserve">37.7976036071777</t>
   </si>
   <si>
     <t xml:space="preserve">38.1803665161133</t>
@@ -1721,10 +1721,10 @@
     <t xml:space="preserve">37.9411430358887</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9889907836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8454513549805</t>
+    <t xml:space="preserve">37.9889869689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8454475402832</t>
   </si>
   <si>
     <t xml:space="preserve">37.3191566467285</t>
@@ -1733,16 +1733,16 @@
     <t xml:space="preserve">38.8501930236816</t>
   </si>
   <si>
-    <t xml:space="preserve">38.754508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3286437988281</t>
+    <t xml:space="preserve">38.7545051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3286476135254</t>
   </si>
   <si>
     <t xml:space="preserve">39.041576385498</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8023452758789</t>
+    <t xml:space="preserve">38.8023490905762</t>
   </si>
   <si>
     <t xml:space="preserve">38.4674377441406</t>
@@ -1751,25 +1751,25 @@
     <t xml:space="preserve">38.1325187683105</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8980407714844</t>
+    <t xml:space="preserve">38.8980445861816</t>
   </si>
   <si>
     <t xml:space="preserve">38.7066612243652</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2760581970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5631294250488</t>
+    <t xml:space="preserve">38.2760543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5631256103516</t>
   </si>
   <si>
     <t xml:space="preserve">38.4195938110352</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3764915466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.137264251709</t>
+    <t xml:space="preserve">39.3764953613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1372680664062</t>
   </si>
   <si>
     <t xml:space="preserve">39.1851119995117</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">39.9027862548828</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1946029663086</t>
+    <t xml:space="preserve">41.1946067810059</t>
   </si>
   <si>
     <t xml:space="preserve">42.1036605834961</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">42.5342674255371</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6730537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8118476867676</t>
+    <t xml:space="preserve">41.6730575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8118438720703</t>
   </si>
   <si>
     <t xml:space="preserve">40.7161560058594</t>
@@ -1802,19 +1802,19 @@
     <t xml:space="preserve">41.912281036377</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0605659484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4911651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2566909790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7829856872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4433288574219</t>
+    <t xml:space="preserve">43.0605621337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4911689758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2566947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7829895019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4433250427246</t>
   </si>
   <si>
     <t xml:space="preserve">44.0174674987793</t>
@@ -1823,25 +1823,25 @@
     <t xml:space="preserve">43.6347045898438</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2041015625</t>
+    <t xml:space="preserve">43.2040977478027</t>
   </si>
   <si>
     <t xml:space="preserve">42.9170265197754</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9265251159668</t>
+    <t xml:space="preserve">44.9265213012695</t>
   </si>
   <si>
     <t xml:space="preserve">45.404972076416</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2614402770996</t>
+    <t xml:space="preserve">45.2614364624023</t>
   </si>
   <si>
     <t xml:space="preserve">45.5963516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">47.653694152832</t>
+    <t xml:space="preserve">47.6536903381348</t>
   </si>
   <si>
     <t xml:space="preserve">48.8976593017578</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">49.1847343444824</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9933471679688</t>
+    <t xml:space="preserve">48.993350982666</t>
   </si>
   <si>
     <t xml:space="preserve">49.7588729858398</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">49.6631813049316</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3761100769043</t>
+    <t xml:space="preserve">49.3761138916016</t>
   </si>
   <si>
     <t xml:space="preserve">49.5674896240234</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">52.7252655029297</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6295738220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.9597473144531</t>
+    <t xml:space="preserve">52.6295776367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9597434997559</t>
   </si>
   <si>
     <t xml:space="preserve">51.8640594482422</t>
@@ -1901,10 +1901,10 @@
     <t xml:space="preserve">50.0459442138672</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3856086730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9071578979492</t>
+    <t xml:space="preserve">51.3856048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.907154083252</t>
   </si>
   <si>
     <t xml:space="preserve">49.8545608520508</t>
@@ -1913,13 +1913,13 @@
     <t xml:space="preserve">50.4287071228027</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5338897705078</t>
+    <t xml:space="preserve">52.5338935852051</t>
   </si>
   <si>
     <t xml:space="preserve">54.0649299621582</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2994079589844</t>
+    <t xml:space="preserve">53.2994117736816</t>
   </si>
   <si>
     <t xml:space="preserve">52.4381942749023</t>
@@ -1940,10 +1940,10 @@
     <t xml:space="preserve">44.974365234375</t>
   </si>
   <si>
-    <t xml:space="preserve">43.586856842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7687530517578</t>
+    <t xml:space="preserve">43.5868606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7687492370605</t>
   </si>
   <si>
     <t xml:space="preserve">36.6493225097656</t>
@@ -1952,43 +1952,43 @@
     <t xml:space="preserve">35.5967330932617</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0945491790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4820575714111</t>
+    <t xml:space="preserve">30.0945510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4820556640625</t>
   </si>
   <si>
     <t xml:space="preserve">29.1854915618896</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5299015045166</t>
+    <t xml:space="preserve">31.5299034118652</t>
   </si>
   <si>
     <t xml:space="preserve">31.0992984771729</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3816204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9269027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4100952148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5010375976562</t>
+    <t xml:space="preserve">30.3816184997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9268989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.410099029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5010414123535</t>
   </si>
   <si>
     <t xml:space="preserve">35.3096656799316</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5441436767578</t>
+    <t xml:space="preserve">34.5441398620605</t>
   </si>
   <si>
     <t xml:space="preserve">35.070442199707</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0799331665039</t>
+    <t xml:space="preserve">37.0799293518066</t>
   </si>
   <si>
     <t xml:space="preserve">37.2234649658203</t>
@@ -2003,22 +2003,22 @@
     <t xml:space="preserve">40.429084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">39.998477935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7351455688477</t>
+    <t xml:space="preserve">39.9984817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7351417541504</t>
   </si>
   <si>
     <t xml:space="preserve">45.9791145324707</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4528198242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0700569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3571319580078</t>
+    <t xml:space="preserve">45.452823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0700531005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3571281433105</t>
   </si>
   <si>
     <t xml:space="preserve">45.1179046630859</t>
@@ -2030,34 +2030,34 @@
     <t xml:space="preserve">45.6441955566406</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8786811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3092803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1657485961914</t>
+    <t xml:space="preserve">44.8786773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3092842102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1657447814941</t>
   </si>
   <si>
     <t xml:space="preserve">44.2088432312012</t>
   </si>
   <si>
-    <t xml:space="preserve">43.15625</t>
+    <t xml:space="preserve">43.1562538146973</t>
   </si>
   <si>
     <t xml:space="preserve">43.9217758178711</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8644371032715</t>
+    <t xml:space="preserve">41.8644332885742</t>
   </si>
   <si>
     <t xml:space="preserve">42.5821113586426</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0222129821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5485000610352</t>
+    <t xml:space="preserve">45.0222091674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5485038757324</t>
   </si>
   <si>
     <t xml:space="preserve">47.5101585388184</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">47.7015342712402</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7062873840332</t>
+    <t xml:space="preserve">48.7062835693359</t>
   </si>
   <si>
     <t xml:space="preserve">47.9407577514648</t>
@@ -2087,31 +2087,31 @@
     <t xml:space="preserve">51.289909362793</t>
   </si>
   <si>
-    <t xml:space="preserve">53.108024597168</t>
+    <t xml:space="preserve">53.1080284118652</t>
   </si>
   <si>
     <t xml:space="preserve">53.9692420959473</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4907913208008</t>
+    <t xml:space="preserve">53.490795135498</t>
   </si>
   <si>
     <t xml:space="preserve">55.1175231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6916618347168</t>
+    <t xml:space="preserve">55.6916656494141</t>
   </si>
   <si>
     <t xml:space="preserve">55.5002822875977</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3520011901855</t>
+    <t xml:space="preserve">54.3519973754883</t>
   </si>
   <si>
     <t xml:space="preserve">54.6390724182129</t>
   </si>
   <si>
-    <t xml:space="preserve">54.830451965332</t>
+    <t xml:space="preserve">54.8304481506348</t>
   </si>
   <si>
     <t xml:space="preserve">55.4045944213867</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">55.9787292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3183937072754</t>
+    <t xml:space="preserve">57.3183975219727</t>
   </si>
   <si>
     <t xml:space="preserve">58.6580581665039</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">56.3614959716797</t>
   </si>
   <si>
-    <t xml:space="preserve">57.9882278442383</t>
+    <t xml:space="preserve">57.988224029541</t>
   </si>
   <si>
     <t xml:space="preserve">58.849437713623</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">62.2942810058594</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3468818664551</t>
+    <t xml:space="preserve">63.346866607666</t>
   </si>
   <si>
     <t xml:space="preserve">63.7296295166016</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">64.3037719726562</t>
   </si>
   <si>
-    <t xml:space="preserve">64.5908432006836</t>
+    <t xml:space="preserve">64.5908508300781</t>
   </si>
   <si>
     <t xml:space="preserve">65.9305038452148</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">66.9830932617188</t>
   </si>
   <si>
-    <t xml:space="preserve">67.1744766235352</t>
+    <t xml:space="preserve">67.1744689941406</t>
   </si>
   <si>
     <t xml:space="preserve">66.5046463012695</t>
@@ -2198,16 +2198,16 @@
     <t xml:space="preserve">67.8443145751953</t>
   </si>
   <si>
-    <t xml:space="preserve">70.0451889038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1839752197266</t>
+    <t xml:space="preserve">70.0451812744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1839828491211</t>
   </si>
   <si>
     <t xml:space="preserve">71.2891616821289</t>
   </si>
   <si>
-    <t xml:space="preserve">70.8106994628906</t>
+    <t xml:space="preserve">70.8107070922852</t>
   </si>
   <si>
     <t xml:space="preserve">70.6193313598633</t>
@@ -2219,25 +2219,25 @@
     <t xml:space="preserve">72.0546798706055</t>
   </si>
   <si>
-    <t xml:space="preserve">71.0020751953125</t>
+    <t xml:space="preserve">71.002082824707</t>
   </si>
   <si>
     <t xml:space="preserve">69.4710464477539</t>
   </si>
   <si>
-    <t xml:space="preserve">68.9925918579102</t>
+    <t xml:space="preserve">68.9925842285156</t>
   </si>
   <si>
     <t xml:space="preserve">69.9494934082031</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8012237548828</t>
+    <t xml:space="preserve">68.8012161254883</t>
   </si>
   <si>
     <t xml:space="preserve">69.6624221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">76.552116394043</t>
+    <t xml:space="preserve">76.5521087646484</t>
   </si>
   <si>
     <t xml:space="preserve">77.7003860473633</t>
@@ -2255,70 +2255,70 @@
     <t xml:space="preserve">74.8296966552734</t>
   </si>
   <si>
-    <t xml:space="preserve">77.8917694091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.274528503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.7960815429688</t>
+    <t xml:space="preserve">77.8917770385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.2745361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.7960891723633</t>
   </si>
   <si>
     <t xml:space="preserve">79.4228210449219</t>
   </si>
   <si>
-    <t xml:space="preserve">80.7624816894531</t>
+    <t xml:space="preserve">80.7624740600586</t>
   </si>
   <si>
     <t xml:space="preserve">82.0064468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">81.5279998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9107513427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.3892059326172</t>
+    <t xml:space="preserve">81.5280075073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.910758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.3892135620117</t>
   </si>
   <si>
     <t xml:space="preserve">81.4323120117188</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1452484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4754028320312</t>
+    <t xml:space="preserve">81.1452407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4754104614258</t>
   </si>
   <si>
     <t xml:space="preserve">81.7193832397461</t>
   </si>
   <si>
-    <t xml:space="preserve">81.8150787353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.3461074829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.9538497924805</t>
+    <t xml:space="preserve">81.815071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.3461151123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.953857421875</t>
   </si>
   <si>
     <t xml:space="preserve">82.7719802856445</t>
   </si>
   <si>
-    <t xml:space="preserve">82.2935180664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.0305709838867</t>
+    <t xml:space="preserve">82.2935104370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.0305633544922</t>
   </si>
   <si>
     <t xml:space="preserve">79.3271331787109</t>
   </si>
   <si>
-    <t xml:space="preserve">83.728874206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.1021499633789</t>
+    <t xml:space="preserve">83.7288665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.1021423339844</t>
   </si>
   <si>
     <t xml:space="preserve">76.7434997558594</t>
@@ -2333,16 +2333,16 @@
     <t xml:space="preserve">82.4849014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3797225952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.6572875976562</t>
+    <t xml:space="preserve">80.3797149658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.6572952270508</t>
   </si>
   <si>
     <t xml:space="preserve">78.4659118652344</t>
   </si>
   <si>
-    <t xml:space="preserve">84.6857757568359</t>
+    <t xml:space="preserve">84.6857681274414</t>
   </si>
   <si>
     <t xml:space="preserve">85.355598449707</t>
@@ -2354,25 +2354,25 @@
     <t xml:space="preserve">85.9297485351562</t>
   </si>
   <si>
-    <t xml:space="preserve">87.173713684082</t>
+    <t xml:space="preserve">87.1737213134766</t>
   </si>
   <si>
     <t xml:space="preserve">87.2694091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">88.3220062255859</t>
+    <t xml:space="preserve">88.3219985961914</t>
   </si>
   <si>
     <t xml:space="preserve">86.7909545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">90.9056396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3840789794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1065139770508</t>
+    <t xml:space="preserve">90.905647277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3840866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1065063476562</t>
   </si>
   <si>
     <t xml:space="preserve">95.8815155029297</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">97.2211837768555</t>
   </si>
   <si>
-    <t xml:space="preserve">100.474639892578</t>
+    <t xml:space="preserve">100.474647521973</t>
   </si>
   <si>
     <t xml:space="preserve">101.622924804688</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">101.240173339844</t>
   </si>
   <si>
-    <t xml:space="preserve">97.9866943359375</t>
+    <t xml:space="preserve">97.986701965332</t>
   </si>
   <si>
     <t xml:space="preserve">98.5608444213867</t>
@@ -2399,16 +2399,16 @@
     <t xml:space="preserve">99.9005126953125</t>
   </si>
   <si>
-    <t xml:space="preserve">96.264289855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.6901397705078</t>
+    <t xml:space="preserve">96.2642822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.6901473999023</t>
   </si>
   <si>
     <t xml:space="preserve">94.8289337158203</t>
   </si>
   <si>
-    <t xml:space="preserve">95.3073883056641</t>
+    <t xml:space="preserve">95.3073806762695</t>
   </si>
   <si>
     <t xml:space="preserve">94.2547912597656</t>
@@ -2420,19 +2420,19 @@
     <t xml:space="preserve">97.0298080444336</t>
   </si>
   <si>
-    <t xml:space="preserve">94.541862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1591033935547</t>
+    <t xml:space="preserve">94.5418548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1591110229492</t>
   </si>
   <si>
     <t xml:space="preserve">93.8720245361328</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0634155273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3935775756836</t>
+    <t xml:space="preserve">94.0634078979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3935699462891</t>
   </si>
   <si>
     <t xml:space="preserve">93.6806488037109</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">92.9151306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">93.2978820800781</t>
+    <t xml:space="preserve">93.2978897094727</t>
   </si>
   <si>
     <t xml:space="preserve">92.723747253418</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">94.3504867553711</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6039428710938</t>
+    <t xml:space="preserve">97.6039505004883</t>
   </si>
   <si>
     <t xml:space="preserve">101.431549072266</t>
@@ -2459,16 +2459,16 @@
     <t xml:space="preserve">104.876388549805</t>
   </si>
   <si>
-    <t xml:space="preserve">104.493621826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.598815917969</t>
+    <t xml:space="preserve">104.493629455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.598823547363</t>
   </si>
   <si>
     <t xml:space="preserve">107.364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">109.660903930664</t>
+    <t xml:space="preserve">109.66089630127</t>
   </si>
   <si>
     <t xml:space="preserve">110.235046386719</t>
@@ -2477,13 +2477,13 @@
     <t xml:space="preserve">105.64192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">106.216049194336</t>
+    <t xml:space="preserve">106.21605682373</t>
   </si>
   <si>
     <t xml:space="preserve">107.938484191895</t>
   </si>
   <si>
-    <t xml:space="preserve">107.555725097656</t>
+    <t xml:space="preserve">107.555717468262</t>
   </si>
   <si>
     <t xml:space="preserve">109.469520568848</t>
@@ -2492,7 +2492,7 @@
     <t xml:space="preserve">107.747100830078</t>
   </si>
   <si>
-    <t xml:space="preserve">108.704002380371</t>
+    <t xml:space="preserve">108.703994750977</t>
   </si>
   <si>
     <t xml:space="preserve">102.197082519531</t>
@@ -2513,16 +2513,16 @@
     <t xml:space="preserve">106.024673461914</t>
   </si>
   <si>
-    <t xml:space="preserve">106.981582641602</t>
+    <t xml:space="preserve">106.981590270996</t>
   </si>
   <si>
     <t xml:space="preserve">108.512619018555</t>
   </si>
   <si>
-    <t xml:space="preserve">105.833297729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.048797607422</t>
+    <t xml:space="preserve">105.833290100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.048789978027</t>
   </si>
   <si>
     <t xml:space="preserve">102.388458251953</t>
@@ -2540,13 +2540,13 @@
     <t xml:space="preserve">102.00569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">103.919494628906</t>
+    <t xml:space="preserve">103.919486999512</t>
   </si>
   <si>
     <t xml:space="preserve">106.407432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">109.086769104004</t>
+    <t xml:space="preserve">109.086761474609</t>
   </si>
   <si>
     <t xml:space="preserve">110.809188842773</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">111.000564575195</t>
   </si>
   <si>
-    <t xml:space="preserve">112.914360046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.852279663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.42643737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.383323669434</t>
+    <t xml:space="preserve">112.914367675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.85228729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.426429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.383331298828</t>
   </si>
   <si>
     <t xml:space="preserve">112.340232849121</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">114.445411682129</t>
   </si>
   <si>
-    <t xml:space="preserve">113.29712677002</t>
+    <t xml:space="preserve">113.297119140625</t>
   </si>
   <si>
     <t xml:space="preserve">112.722991943359</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">115.593696594238</t>
   </si>
   <si>
-    <t xml:space="preserve">115.210929870605</t>
+    <t xml:space="preserve">115.210922241211</t>
   </si>
   <si>
     <t xml:space="preserve">116.741966247559</t>
@@ -2612,19 +2612,19 @@
     <t xml:space="preserve">119.804054260254</t>
   </si>
   <si>
-    <t xml:space="preserve">120.186813354492</t>
+    <t xml:space="preserve">120.186820983887</t>
   </si>
   <si>
     <t xml:space="preserve">122.100616455078</t>
   </si>
   <si>
-    <t xml:space="preserve">122.866142272949</t>
+    <t xml:space="preserve">122.866134643555</t>
   </si>
   <si>
     <t xml:space="preserve">123.631660461426</t>
   </si>
   <si>
-    <t xml:space="preserve">131.478256225586</t>
+    <t xml:space="preserve">131.478240966797</t>
   </si>
   <si>
     <t xml:space="preserve">127.267890930176</t>
@@ -2633,49 +2633,49 @@
     <t xml:space="preserve">127.459259033203</t>
   </si>
   <si>
-    <t xml:space="preserve">128.990310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.052383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.157562255859</t>
+    <t xml:space="preserve">128.990325927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.052398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.157577514648</t>
   </si>
   <si>
     <t xml:space="preserve">133.774826049805</t>
   </si>
   <si>
-    <t xml:space="preserve">132.626525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.435150146484</t>
+    <t xml:space="preserve">132.626541137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.435134887695</t>
   </si>
   <si>
     <t xml:space="preserve">134.923095703125</t>
   </si>
   <si>
-    <t xml:space="preserve">136.645523071289</t>
+    <t xml:space="preserve">136.6455078125</t>
   </si>
   <si>
     <t xml:space="preserve">137.411056518555</t>
   </si>
   <si>
-    <t xml:space="preserve">135.305862426758</t>
+    <t xml:space="preserve">135.305847167969</t>
   </si>
   <si>
     <t xml:space="preserve">131.86100769043</t>
   </si>
   <si>
-    <t xml:space="preserve">134.731719970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.262756347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.793792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.176574707031</t>
+    <t xml:space="preserve">134.731735229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.262741088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.793807983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.176559448242</t>
   </si>
   <si>
     <t xml:space="preserve">137.028274536133</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">139.898986816406</t>
   </si>
   <si>
-    <t xml:space="preserve">136.454132080078</t>
+    <t xml:space="preserve">136.454147338867</t>
   </si>
   <si>
     <t xml:space="preserve">138.750701904297</t>
@@ -2696,13 +2696,13 @@
     <t xml:space="preserve">139.324844360352</t>
   </si>
   <si>
-    <t xml:space="preserve">137.98518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.49723815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.492111206055</t>
+    <t xml:space="preserve">137.985168457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.497253417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.492095947266</t>
   </si>
   <si>
     <t xml:space="preserve">144.874862670898</t>
@@ -2711,13 +2711,13 @@
     <t xml:space="preserve">144.109359741211</t>
   </si>
   <si>
-    <t xml:space="preserve">142.195541381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.726577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.91796875</t>
+    <t xml:space="preserve">142.195556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.726593017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.917953491211</t>
   </si>
   <si>
     <t xml:space="preserve">144.683486938477</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">145.25764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">147.936950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.640380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.788681030273</t>
+    <t xml:space="preserve">147.936965942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.640396118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.788696289062</t>
   </si>
   <si>
     <t xml:space="preserve">149.276626586914</t>
@@ -2747,16 +2747,16 @@
     <t xml:space="preserve">153.486999511719</t>
   </si>
   <si>
-    <t xml:space="preserve">152.33869934082</t>
+    <t xml:space="preserve">152.338684082031</t>
   </si>
   <si>
     <t xml:space="preserve">155.400772094727</t>
   </si>
   <si>
-    <t xml:space="preserve">151.1904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.888732910156</t>
+    <t xml:space="preserve">151.190414428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.888717651367</t>
   </si>
   <si>
     <t xml:space="preserve">159.037017822266</t>
@@ -2768,37 +2768,37 @@
     <t xml:space="preserve">159.611145019531</t>
   </si>
   <si>
-    <t xml:space="preserve">161.333587646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.524963378906</t>
+    <t xml:space="preserve">161.333602905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.524948120117</t>
   </si>
   <si>
     <t xml:space="preserve">163.438766479492</t>
   </si>
   <si>
-    <t xml:space="preserve">163.821502685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.606002807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.773315429688</t>
+    <t xml:space="preserve">163.821517944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.606018066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">170.32844543457</t>
   </si>
   <si>
-    <t xml:space="preserve">165.161209106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.031921386719</t>
+    <t xml:space="preserve">165.161193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.031890869141</t>
   </si>
   <si>
     <t xml:space="preserve">165.352569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">160.75944519043</t>
+    <t xml:space="preserve">160.759429931641</t>
   </si>
   <si>
     <t xml:space="preserve">162.099090576172</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">171.668106079102</t>
   </si>
   <si>
-    <t xml:space="preserve">167.075012207031</t>
+    <t xml:space="preserve">167.074996948242</t>
   </si>
   <si>
     <t xml:space="preserve">161.930511474609</t>
@@ -5322,6 +5322,9 @@
   </si>
   <si>
     <t xml:space="preserve">93.8499984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4499969482422</t>
   </si>
 </sst>
 </file>
@@ -71960,7 +71963,7 @@
     </row>
     <row r="2551">
       <c r="A2551" s="1" t="n">
-        <v>46037.6911458333</v>
+        <v>46037.3333333333</v>
       </c>
       <c r="B2551" t="n">
         <v>46727</v>
@@ -71969,7 +71972,7 @@
         <v>96.8499984741211</v>
       </c>
       <c r="D2551" t="n">
-        <v>94.0999984741211</v>
+        <v>93.8499984741211</v>
       </c>
       <c r="E2551" t="n">
         <v>96.5</v>
@@ -71981,6 +71984,32 @@
         <v>1769</v>
       </c>
       <c r="H2551" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2552">
+      <c r="A2552" s="1" t="n">
+        <v>46038.6912384259</v>
+      </c>
+      <c r="B2552" t="n">
+        <v>48015</v>
+      </c>
+      <c r="C2552" t="n">
+        <v>94.1500015258789</v>
+      </c>
+      <c r="D2552" t="n">
+        <v>91.8499984741211</v>
+      </c>
+      <c r="E2552" t="n">
+        <v>93.5500030517578</v>
+      </c>
+      <c r="F2552" t="n">
+        <v>92.4499969482422</v>
+      </c>
+      <c r="G2552" t="s">
+        <v>1770</v>
+      </c>
+      <c r="H2552" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="1771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="1772">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5495901107788</t>
+    <t xml:space="preserve">13.5495920181274</t>
   </si>
   <si>
     <t xml:space="preserve">SES.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5321083068848</t>
+    <t xml:space="preserve">13.5321073532104</t>
   </si>
   <si>
     <t xml:space="preserve">13.2523746490479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9464149475098</t>
+    <t xml:space="preserve">12.9464159011841</t>
   </si>
   <si>
     <t xml:space="preserve">13.1125068664551</t>
@@ -59,43 +59,43 @@
     <t xml:space="preserve">12.8589992523193</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0513143539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.990122795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9376726150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1037654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0250902175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8502578735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2383394241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5880060195923</t>
+    <t xml:space="preserve">13.0513162612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9901237487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9376745223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1037645339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0250911712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8502550125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2383403778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5880079269409</t>
   </si>
   <si>
     <t xml:space="preserve">12.7890663146973</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7191324234009</t>
+    <t xml:space="preserve">12.7191314697266</t>
   </si>
   <si>
     <t xml:space="preserve">12.6841640472412</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6054906845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3257570266724</t>
+    <t xml:space="preserve">12.6054916381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.325756072998</t>
   </si>
   <si>
     <t xml:space="preserve">12.0460224151611</t>
@@ -104,40 +104,40 @@
     <t xml:space="preserve">12.1771488189697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1421823501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9270877838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9795389175415</t>
+    <t xml:space="preserve">12.1421813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9270896911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9795398712158</t>
   </si>
   <si>
     <t xml:space="preserve">11.3641719818115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4515886306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0984725952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1072149276733</t>
+    <t xml:space="preserve">11.4515905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0984735488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1072158813477</t>
   </si>
   <si>
     <t xml:space="preserve">11.8886728286743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760894775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9323806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0110559463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0809898376465</t>
+    <t xml:space="preserve">11.9760904312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9323816299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0110569000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0809888839722</t>
   </si>
   <si>
     <t xml:space="preserve">11.8012561798096</t>
@@ -146,25 +146,25 @@
     <t xml:space="preserve">12.1334400177002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8274803161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0635080337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5005912780762</t>
+    <t xml:space="preserve">11.8274822235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0635061264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5005903244019</t>
   </si>
   <si>
     <t xml:space="preserve">12.675422668457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7978076934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1649551391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1562156677246</t>
+    <t xml:space="preserve">12.7978057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1649570465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1562166213989</t>
   </si>
   <si>
     <t xml:space="preserve">13.0687990188599</t>
@@ -176,37 +176,37 @@
     <t xml:space="preserve">13.1911821365356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7540969848633</t>
+    <t xml:space="preserve">12.7540988922119</t>
   </si>
   <si>
     <t xml:space="preserve">12.8939647674561</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9027080535889</t>
+    <t xml:space="preserve">12.9027070999146</t>
   </si>
   <si>
     <t xml:space="preserve">13.0600566864014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1999235153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9813823699951</t>
+    <t xml:space="preserve">13.1999225616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9813804626465</t>
   </si>
   <si>
     <t xml:space="preserve">13.4534320831299</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7069416046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4709148406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4621725082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.208664894104</t>
+    <t xml:space="preserve">13.7069406509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4709157943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4621715545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2086639404297</t>
   </si>
   <si>
     <t xml:space="preserve">13.3223075866699</t>
@@ -215,94 +215,94 @@
     <t xml:space="preserve">13.0950231552124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9988641738892</t>
+    <t xml:space="preserve">12.9988632202148</t>
   </si>
   <si>
     <t xml:space="preserve">12.640456199646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4481401443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3782081604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0285387039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1509237289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4393968582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5617809295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5268144607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6317138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3694658279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.771580696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4306554794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2820491790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1946315765381</t>
+    <t xml:space="preserve">12.4481382369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3782072067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0285406112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1509227752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4393978118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5617818832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5268154144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6317148208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3694639205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7715835571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4306564331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2820482254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1946306228638</t>
   </si>
   <si>
     <t xml:space="preserve">12.2470817565918</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4131736755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.509331703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3869504928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8187398910522</t>
+    <t xml:space="preserve">12.4131727218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5093326568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3869485855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8187389373779</t>
   </si>
   <si>
     <t xml:space="preserve">11.8449649810791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2558240890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5792655944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2208557128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1858901977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7803239822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7278728485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8764810562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8065490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7628383636475</t>
+    <t xml:space="preserve">12.255823135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5792646408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2208547592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1858892440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7803230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7278747558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8764820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8065481185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7628412246704</t>
   </si>
   <si>
     <t xml:space="preserve">12.8677406311035</t>
@@ -311,85 +311,85 @@
     <t xml:space="preserve">12.8327741622925</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5355558395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1824398040771</t>
+    <t xml:space="preserve">12.5355567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1824388504028</t>
   </si>
   <si>
     <t xml:space="preserve">13.0338315963745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3048248291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2611150741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3747577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6020412445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6894559860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7244243621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7514753341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5711288452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8687009811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6252336502075</t>
+    <t xml:space="preserve">13.3048229217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2611141204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.374755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6020402908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6894569396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7244234085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7514762878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5711307525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8687019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6252317428589</t>
   </si>
   <si>
     <t xml:space="preserve">13.6432676315308</t>
   </si>
   <si>
-    <t xml:space="preserve">13.661301612854</t>
+    <t xml:space="preserve">13.6613025665283</t>
   </si>
   <si>
     <t xml:space="preserve">13.598180770874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6162157058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5260429382324</t>
+    <t xml:space="preserve">13.6162147521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5260419845581</t>
   </si>
   <si>
     <t xml:space="preserve">13.5530939102173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3456954956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801448822021</t>
+    <t xml:space="preserve">13.3456964492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801458358765</t>
   </si>
   <si>
     <t xml:space="preserve">13.6973714828491</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7785272598267</t>
+    <t xml:space="preserve">13.778528213501</t>
   </si>
   <si>
     <t xml:space="preserve">13.6703195571899</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7965621948242</t>
+    <t xml:space="preserve">13.7965631484985</t>
   </si>
   <si>
     <t xml:space="preserve">13.9769105911255</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0400314331055</t>
+    <t xml:space="preserve">14.0400323867798</t>
   </si>
   <si>
     <t xml:space="preserve">14.0129795074463</t>
@@ -398,19 +398,19 @@
     <t xml:space="preserve">13.9047708511353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1031541824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2474308013916</t>
+    <t xml:space="preserve">14.1031532287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2474317550659</t>
   </si>
   <si>
     <t xml:space="preserve">14.1572570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3646554946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4187602996826</t>
+    <t xml:space="preserve">14.3646564483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4187593460083</t>
   </si>
   <si>
     <t xml:space="preserve">14.517951965332</t>
@@ -428,22 +428,22 @@
     <t xml:space="preserve">14.3105516433716</t>
   </si>
   <si>
-    <t xml:space="preserve">14.30153465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5450029373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6441955566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7343702316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7163343429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.635178565979</t>
+    <t xml:space="preserve">14.3015356063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5450019836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6441946029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7343683242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7163333892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6351776123047</t>
   </si>
   <si>
     <t xml:space="preserve">14.6261587142944</t>
@@ -452,208 +452,208 @@
     <t xml:space="preserve">14.689284324646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8245410919189</t>
+    <t xml:space="preserve">14.8245439529419</t>
   </si>
   <si>
     <t xml:space="preserve">14.80650806427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7433853149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5810718536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.698296546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5089330673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6712484359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6532135009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9237337112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0499782562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2122898101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3746004104614</t>
+    <t xml:space="preserve">14.7433862686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.581072807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6982975006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5089340209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6712465286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6532125473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9237308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.049976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2122917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3745994567871</t>
   </si>
   <si>
     <t xml:space="preserve">15.5549488067627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9246587753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7803802490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8705558776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344879150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7082433700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517116546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7452392578125</t>
+    <t xml:space="preserve">15.9246606826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7803831100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8705549240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344860076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7082462310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7452411651611</t>
   </si>
   <si>
     <t xml:space="preserve">16.8714809417725</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0879001617432</t>
+    <t xml:space="preserve">17.0878982543945</t>
   </si>
   <si>
     <t xml:space="preserve">17.1510219573975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2231597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9796924591064</t>
+    <t xml:space="preserve">17.2231616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9796905517578</t>
   </si>
   <si>
     <t xml:space="preserve">16.9075527191162</t>
   </si>
   <si>
-    <t xml:space="preserve">17.304313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0337924957275</t>
+    <t xml:space="preserve">17.3043174743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0337963104248</t>
   </si>
   <si>
     <t xml:space="preserve">17.2772636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4756450653076</t>
+    <t xml:space="preserve">17.475643157959</t>
   </si>
   <si>
     <t xml:space="preserve">17.3223495483398</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1690578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.583854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.574836730957</t>
+    <t xml:space="preserve">17.1690616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5838565826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5748348236084</t>
   </si>
   <si>
     <t xml:space="preserve">17.5658206939697</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2411956787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1870918273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8534488677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8444290161133</t>
+    <t xml:space="preserve">17.2411975860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1870899200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8534507751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8444328308105</t>
   </si>
   <si>
     <t xml:space="preserve">16.9526386260986</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7272071838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6911373138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8624649047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0428142547607</t>
+    <t xml:space="preserve">16.7272033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6911354064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8624668121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0428123474121</t>
   </si>
   <si>
     <t xml:space="preserve">16.8173789978027</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9977264404297</t>
+    <t xml:space="preserve">16.9977283477783</t>
   </si>
   <si>
     <t xml:space="preserve">16.7722949981689</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0067462921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1961059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3584232330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6199245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7642002105713</t>
+    <t xml:space="preserve">17.006742477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1961078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.358419418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6199264526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7642021179199</t>
   </si>
   <si>
     <t xml:space="preserve">18.0076675415039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9896373748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9445457458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9535675048828</t>
+    <t xml:space="preserve">17.9896354675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9445495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9535694122314</t>
   </si>
   <si>
     <t xml:space="preserve">17.809289932251</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2601566314697</t>
+    <t xml:space="preserve">18.2601547241211</t>
   </si>
   <si>
     <t xml:space="preserve">18.7561111450195</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8462829589844</t>
+    <t xml:space="preserve">18.846284866333</t>
   </si>
   <si>
     <t xml:space="preserve">18.9364585876465</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6208515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2971534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3602733612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3512554168701</t>
+    <t xml:space="preserve">18.6208477020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2971515655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3602752685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3512573242188</t>
   </si>
   <si>
     <t xml:space="preserve">19.6668643951416</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6488361358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5586566925049</t>
+    <t xml:space="preserve">19.6488304138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5586585998535</t>
   </si>
   <si>
     <t xml:space="preserve">19.252067565918</t>
@@ -665,28 +665,28 @@
     <t xml:space="preserve">19.1348400115967</t>
   </si>
   <si>
-    <t xml:space="preserve">19.197961807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9544925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9094066619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0897521972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5757637023926</t>
+    <t xml:space="preserve">19.1979637145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.954496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9094047546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0897541046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5757656097412</t>
   </si>
   <si>
     <t xml:space="preserve">18.1970367431641</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5306777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8372669219971</t>
+    <t xml:space="preserve">18.5306758880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8372707366943</t>
   </si>
   <si>
     <t xml:space="preserve">19.4594669342041</t>
@@ -695,34 +695,34 @@
     <t xml:space="preserve">19.3873271942139</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0185432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3612003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8301067352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2809734344482</t>
+    <t xml:space="preserve">20.0185413360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3612022399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8301029205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2809753417969</t>
   </si>
   <si>
     <t xml:space="preserve">20.8751926422119</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9292945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1006259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0104503631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5685977935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7218990325928</t>
+    <t xml:space="preserve">20.9292964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.100622177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0104522705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5685997009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7218952178955</t>
   </si>
   <si>
     <t xml:space="preserve">20.6046714782715</t>
@@ -731,85 +731,85 @@
     <t xml:space="preserve">20.1898708343506</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3792343139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6497573852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6416645050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3711471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3801651000977</t>
+    <t xml:space="preserve">20.3792381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6497554779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6416683197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3711452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.380163192749</t>
   </si>
   <si>
     <t xml:space="preserve">22.0925350189209</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6245613098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7147331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8049087524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5984382629395</t>
+    <t xml:space="preserve">22.6245574951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7147350311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8049068450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5984344482422</t>
   </si>
   <si>
     <t xml:space="preserve">24.0763549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0583209991455</t>
+    <t xml:space="preserve">24.0583190917969</t>
   </si>
   <si>
     <t xml:space="preserve">23.7156620025635</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9320774078369</t>
+    <t xml:space="preserve">23.9320793151855</t>
   </si>
   <si>
     <t xml:space="preserve">23.8599376678467</t>
   </si>
   <si>
-    <t xml:space="preserve">23.805835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5082607269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.994270324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4802856445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5434017181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.705717086792</t>
+    <t xml:space="preserve">23.8058319091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5082588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9942722320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4802799224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5434055328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7057151794434</t>
   </si>
   <si>
     <t xml:space="preserve">22.4532299041748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4622478485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0023593902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.182710647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7237548828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3630561828613</t>
+    <t xml:space="preserve">22.4622497558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0023632049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1827125549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7237491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3630542755127</t>
   </si>
   <si>
     <t xml:space="preserve">22.2097606658936</t>
@@ -818,34 +818,34 @@
     <t xml:space="preserve">21.4883708953857</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9212017059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8761177062988</t>
+    <t xml:space="preserve">21.9212074279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8761157989502</t>
   </si>
   <si>
     <t xml:space="preserve">21.7047882080078</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9392395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.074499130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.299934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8139247894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3179683685303</t>
+    <t xml:space="preserve">21.9392414093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0745010375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2999362945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8139228820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3179702758789</t>
   </si>
   <si>
     <t xml:space="preserve">22.1917266845703</t>
   </si>
   <si>
-    <t xml:space="preserve">22.354040145874</t>
+    <t xml:space="preserve">22.3540382385254</t>
   </si>
   <si>
     <t xml:space="preserve">22.5253677368164</t>
@@ -857,22 +857,22 @@
     <t xml:space="preserve">22.6335773468018</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2458324432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2277984619141</t>
+    <t xml:space="preserve">22.2458305358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2277946472168</t>
   </si>
   <si>
     <t xml:space="preserve">22.1286067962646</t>
   </si>
   <si>
-    <t xml:space="preserve">22.083517074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2007427215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.137622833252</t>
+    <t xml:space="preserve">22.0835151672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2007465362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1376190185547</t>
   </si>
   <si>
     <t xml:space="preserve">22.1466388702393</t>
@@ -881,10 +881,10 @@
     <t xml:space="preserve">21.5965805053711</t>
   </si>
   <si>
-    <t xml:space="preserve">21.326057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.560510635376</t>
+    <t xml:space="preserve">21.3260555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5605125427246</t>
   </si>
   <si>
     <t xml:space="preserve">22.0294151306152</t>
@@ -893,34 +893,34 @@
     <t xml:space="preserve">21.6867523193359</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2368144989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3720741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3991260528564</t>
+    <t xml:space="preserve">22.2368125915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3720722198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3991241455078</t>
   </si>
   <si>
     <t xml:space="preserve">22.6155414581299</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6606292724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0123062133789</t>
+    <t xml:space="preserve">22.6606273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0123043060303</t>
   </si>
   <si>
     <t xml:space="preserve">23.5193881988525</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2704582214355</t>
+    <t xml:space="preserve">23.2704563140869</t>
   </si>
   <si>
     <t xml:space="preserve">24.1739864349365</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7087230682373</t>
+    <t xml:space="preserve">24.7087249755859</t>
   </si>
   <si>
     <t xml:space="preserve">24.7732639312744</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">25.2434673309326</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8150844573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7966461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6860103607178</t>
+    <t xml:space="preserve">25.8150882720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7966480255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6860122680664</t>
   </si>
   <si>
     <t xml:space="preserve">25.6675720214844</t>
@@ -947,10 +947,10 @@
     <t xml:space="preserve">25.8888454437256</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9810409545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0916767120361</t>
+    <t xml:space="preserve">25.9810390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0916748046875</t>
   </si>
   <si>
     <t xml:space="preserve">25.907283782959</t>
@@ -959,22 +959,22 @@
     <t xml:space="preserve">25.8058681488037</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9533805847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.676794052124</t>
+    <t xml:space="preserve">25.9533824920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6767921447754</t>
   </si>
   <si>
     <t xml:space="preserve">25.6583518981934</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0775165557861</t>
+    <t xml:space="preserve">25.0775108337402</t>
   </si>
   <si>
     <t xml:space="preserve">25.4001998901367</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2619037628174</t>
+    <t xml:space="preserve">25.2619075775146</t>
   </si>
   <si>
     <t xml:space="preserve">25.3264427185059</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">25.4186401367188</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6441879272461</t>
+    <t xml:space="preserve">24.6441898345947</t>
   </si>
   <si>
     <t xml:space="preserve">24.8562393188477</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9576568603516</t>
+    <t xml:space="preserve">24.9576549530029</t>
   </si>
   <si>
     <t xml:space="preserve">24.8931198120117</t>
@@ -1007,22 +1007,19 @@
     <t xml:space="preserve">23.1229419708252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2335796356201</t>
+    <t xml:space="preserve">23.2335777282715</t>
   </si>
   <si>
     <t xml:space="preserve">22.9938678741455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0123043060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.781810760498</t>
+    <t xml:space="preserve">22.7818145751953</t>
   </si>
   <si>
     <t xml:space="preserve">22.6711769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4960041046143</t>
+    <t xml:space="preserve">22.4960060119629</t>
   </si>
   <si>
     <t xml:space="preserve">22.7264957427979</t>
@@ -1031,7 +1028,7 @@
     <t xml:space="preserve">22.5052242279053</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3208332061768</t>
+    <t xml:space="preserve">22.3208293914795</t>
   </si>
   <si>
     <t xml:space="preserve">22.5882015228271</t>
@@ -1040,25 +1037,25 @@
     <t xml:space="preserve">23.1137218475342</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9108924865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3995304107666</t>
+    <t xml:space="preserve">22.910888671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3995342254639</t>
   </si>
   <si>
     <t xml:space="preserve">23.7775402069092</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6208038330078</t>
+    <t xml:space="preserve">23.6208057403564</t>
   </si>
   <si>
     <t xml:space="preserve">23.1413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9846477508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8740119934082</t>
+    <t xml:space="preserve">22.9846458435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8740100860596</t>
   </si>
   <si>
     <t xml:space="preserve">22.7357158660889</t>
@@ -1073,25 +1070,25 @@
     <t xml:space="preserve">23.7406597137451</t>
   </si>
   <si>
-    <t xml:space="preserve">23.980375289917</t>
+    <t xml:space="preserve">23.9803733825684</t>
   </si>
   <si>
     <t xml:space="preserve">23.9711513519287</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0633525848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2477416992188</t>
+    <t xml:space="preserve">24.0633506774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2477436065674</t>
   </si>
   <si>
     <t xml:space="preserve">24.3860378265381</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1555423736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6165313720703</t>
+    <t xml:space="preserve">24.1555442810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6165294647217</t>
   </si>
   <si>
     <t xml:space="preserve">25.8611831665039</t>
@@ -1103,19 +1100,19 @@
     <t xml:space="preserve">25.2158107757568</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1697082519531</t>
+    <t xml:space="preserve">25.1697063446045</t>
   </si>
   <si>
     <t xml:space="preserve">25.3080062866211</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4463024139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5384941101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1236114501953</t>
+    <t xml:space="preserve">25.4463005065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5384960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1236133575439</t>
   </si>
   <si>
     <t xml:space="preserve">24.4321365356445</t>
@@ -1124,28 +1121,28 @@
     <t xml:space="preserve">23.6484622955322</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0172481536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1094455718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3399391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2016429901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2938423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7548236846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6626300811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.985315322876</t>
+    <t xml:space="preserve">24.0172500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1094436645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.339937210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2016448974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2938404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7548274993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6626281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9853172302246</t>
   </si>
   <si>
     <t xml:space="preserve">25.4923992156982</t>
@@ -1154,22 +1151,22 @@
     <t xml:space="preserve">25.7228908538818</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5704326629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5845947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9994812011719</t>
+    <t xml:space="preserve">24.5704307556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5845966339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9994792938232</t>
   </si>
   <si>
     <t xml:space="preserve">26.414363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5668258666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7512187957764</t>
+    <t xml:space="preserve">27.5668277740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7512226104736</t>
   </si>
   <si>
     <t xml:space="preserve">28.0739078521729</t>
@@ -1178,31 +1175,31 @@
     <t xml:space="preserve">27.5207271575928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7370548248291</t>
+    <t xml:space="preserve">26.7370529174805</t>
   </si>
   <si>
     <t xml:space="preserve">26.5065631866455</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0314121246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5243320465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3682670593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5987606048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4604644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2299747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3221702575684</t>
+    <t xml:space="preserve">25.0314159393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5243358612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3682689666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5987586975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4604625701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2299728393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3221683502197</t>
   </si>
   <si>
     <t xml:space="preserve">27.1980381011963</t>
@@ -1211,10 +1208,10 @@
     <t xml:space="preserve">26.2760696411133</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2902355194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3824348449707</t>
+    <t xml:space="preserve">27.2902374267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3824310302734</t>
   </si>
   <si>
     <t xml:space="preserve">27.4746265411377</t>
@@ -1223,7 +1220,7 @@
     <t xml:space="preserve">26.552661895752</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8292503356934</t>
+    <t xml:space="preserve">26.829252243042</t>
   </si>
   <si>
     <t xml:space="preserve">27.1058406829834</t>
@@ -1232,7 +1229,7 @@
     <t xml:space="preserve">26.8753490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8434162139893</t>
+    <t xml:space="preserve">27.843412399292</t>
   </si>
   <si>
     <t xml:space="preserve">28.7653827667236</t>
@@ -1244,34 +1241,34 @@
     <t xml:space="preserve">27.9356117248535</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8114795684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1661033630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7192840576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1200046539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0597438812256</t>
+    <t xml:space="preserve">28.8114814758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1661014556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7192821502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1200065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0597457885742</t>
   </si>
   <si>
     <t xml:space="preserve">26.9675464630127</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1519412994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6909580230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7831535339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0455780029297</t>
+    <t xml:space="preserve">27.1519393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6909561157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7831516265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0455799102783</t>
   </si>
   <si>
     <t xml:space="preserve">27.6590213775635</t>
@@ -1283,19 +1280,22 @@
     <t xml:space="preserve">26.1828784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">26.088695526123</t>
+    <t xml:space="preserve">26.0886974334717</t>
   </si>
   <si>
     <t xml:space="preserve">26.4654312133789</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8061447143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7119655609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1468677520752</t>
+    <t xml:space="preserve">26.2299709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8061485290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7119636535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1468658447266</t>
   </si>
   <si>
     <t xml:space="preserve">25.3352336883545</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">23.2632064819336</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0277481079102</t>
+    <t xml:space="preserve">23.0277500152588</t>
   </si>
   <si>
     <t xml:space="preserve">23.0748405456543</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">22.7451992034912</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6039257049561</t>
+    <t xml:space="preserve">22.6039237976074</t>
   </si>
   <si>
     <t xml:space="preserve">22.5097427368164</t>
@@ -1334,31 +1334,31 @@
     <t xml:space="preserve">22.4155578613281</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1800994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0388278961182</t>
+    <t xml:space="preserve">22.1801013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0388240814209</t>
   </si>
   <si>
     <t xml:space="preserve">21.8504600524902</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4626502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2271919250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.404483795166</t>
+    <t xml:space="preserve">22.4626541137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2271957397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4044799804688</t>
   </si>
   <si>
     <t xml:space="preserve">23.2161159515381</t>
   </si>
   <si>
-    <t xml:space="preserve">22.886474609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4986629486084</t>
+    <t xml:space="preserve">22.8864727020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.498664855957</t>
   </si>
   <si>
     <t xml:space="preserve">22.5568351745605</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">21.6620960235596</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1911792755127</t>
+    <t xml:space="preserve">21.1911811828613</t>
   </si>
   <si>
     <t xml:space="preserve">21.0028114318848</t>
@@ -1388,25 +1388,25 @@
     <t xml:space="preserve">21.4737300872803</t>
   </si>
   <si>
-    <t xml:space="preserve">22.274284362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7562808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9446411132812</t>
+    <t xml:space="preserve">22.2742824554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7562789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9446449279785</t>
   </si>
   <si>
     <t xml:space="preserve">21.5679111480713</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5208225250244</t>
+    <t xml:space="preserve">21.5208206176758</t>
   </si>
   <si>
     <t xml:space="preserve">21.3324546813965</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2382717132568</t>
+    <t xml:space="preserve">21.2382678985596</t>
   </si>
   <si>
     <t xml:space="preserve">22.8393840789795</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">22.7922897338867</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5457553863525</t>
+    <t xml:space="preserve">23.5457572937012</t>
   </si>
   <si>
     <t xml:space="preserve">23.6399383544922</t>
@@ -1442,25 +1442,25 @@
     <t xml:space="preserve">24.2521286010742</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7230434417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6288604736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6759490966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5817718505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.770133972168</t>
+    <t xml:space="preserve">24.7230453491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6288585662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6759510040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5817699432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7701358795166</t>
   </si>
   <si>
     <t xml:space="preserve">24.9584999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9003314971924</t>
+    <t xml:space="preserve">25.9003295898438</t>
   </si>
   <si>
     <t xml:space="preserve">25.7590579986572</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">25.9474201202393</t>
   </si>
   <si>
-    <t xml:space="preserve">26.277063369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9363441467285</t>
+    <t xml:space="preserve">26.2770652770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9363460540771</t>
   </si>
   <si>
     <t xml:space="preserve">26.983434677124</t>
@@ -1484,13 +1484,13 @@
     <t xml:space="preserve">26.7479782104492</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2659873962402</t>
+    <t xml:space="preserve">27.2659854888916</t>
   </si>
   <si>
     <t xml:space="preserve">27.4543495178223</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5014400482178</t>
+    <t xml:space="preserve">27.5014419555664</t>
   </si>
   <si>
     <t xml:space="preserve">27.3130779266357</t>
@@ -1505,19 +1505,19 @@
     <t xml:space="preserve">26.6537933349609</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6067028045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9945163726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1357879638672</t>
+    <t xml:space="preserve">26.6067047119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.994514465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1357898712158</t>
   </si>
   <si>
     <t xml:space="preserve">26.0416049957275</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6177845001221</t>
+    <t xml:space="preserve">25.6177806854248</t>
   </si>
   <si>
     <t xml:space="preserve">25.4294166564941</t>
@@ -1526,19 +1526,19 @@
     <t xml:space="preserve">25.0055885314941</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0997753143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8643188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4404926300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5235996246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3712463378906</t>
+    <t xml:space="preserve">25.0997734069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8643169403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4404945373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5236015319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3712482452393</t>
   </si>
   <si>
     <t xml:space="preserve">26.3241558074951</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">26.7950706481934</t>
   </si>
   <si>
-    <t xml:space="preserve">26.889253616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0305290222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1718044281006</t>
+    <t xml:space="preserve">26.8892517089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0305271148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.171802520752</t>
   </si>
   <si>
     <t xml:space="preserve">27.5485343933105</t>
@@ -1580,31 +1580,31 @@
     <t xml:space="preserve">29.7618350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3269329071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3740272521973</t>
+    <t xml:space="preserve">30.3269348144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3740253448486</t>
   </si>
   <si>
     <t xml:space="preserve">31.504222869873</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6925849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4460525512695</t>
+    <t xml:space="preserve">31.6925888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4460487365723</t>
   </si>
   <si>
     <t xml:space="preserve">32.4931411743164</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4820671081543</t>
+    <t xml:space="preserve">33.482063293457</t>
   </si>
   <si>
     <t xml:space="preserve">33.6704292297363</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2936973571777</t>
+    <t xml:space="preserve">33.293701171875</t>
   </si>
   <si>
     <t xml:space="preserve">33.5762519836426</t>
@@ -1613,22 +1613,22 @@
     <t xml:space="preserve">33.905891418457</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2466049194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8698768615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1524276733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.058235168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5873184204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3047752380371</t>
+    <t xml:space="preserve">33.2466087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.869873046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1524238586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0582389831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5873260498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3047790527344</t>
   </si>
   <si>
     <t xml:space="preserve">31.9280433654785</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">31.3629455566406</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8920307159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0804004669189</t>
+    <t xml:space="preserve">30.8920288085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0804023742676</t>
   </si>
   <si>
     <t xml:space="preserve">31.0333080291748</t>
@@ -1652,55 +1652,55 @@
     <t xml:space="preserve">30.6565723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6094856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.268762588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.986213684082</t>
+    <t xml:space="preserve">30.6094837188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2687644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9862155914307</t>
   </si>
   <si>
     <t xml:space="preserve">31.4100341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8449382781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.17458152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8809509277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0222282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7396812438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0000686645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4709815979004</t>
+    <t xml:space="preserve">30.8449420928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1745777130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8809547424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0222320556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7396774291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.000072479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4709854125977</t>
   </si>
   <si>
     <t xml:space="preserve">35.7895469665527</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5901031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7784690856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1552047729492</t>
+    <t xml:space="preserve">36.5900993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7784729003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.155200958252</t>
   </si>
   <si>
     <t xml:space="preserve">37.6732063293457</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0846710205078</t>
+    <t xml:space="preserve">38.0846748352051</t>
   </si>
   <si>
     <t xml:space="preserve">38.2282104492188</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">37.367000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7976036071777</t>
+    <t xml:space="preserve">37.797607421875</t>
   </si>
   <si>
     <t xml:space="preserve">38.1803665161133</t>
@@ -1721,7 +1721,7 @@
     <t xml:space="preserve">37.9411430358887</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9889869689941</t>
+    <t xml:space="preserve">37.9889831542969</t>
   </si>
   <si>
     <t xml:space="preserve">37.8454475402832</t>
@@ -1730,13 +1730,13 @@
     <t xml:space="preserve">37.3191566467285</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8501930236816</t>
+    <t xml:space="preserve">38.8501968383789</t>
   </si>
   <si>
     <t xml:space="preserve">38.7545051574707</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3286476135254</t>
+    <t xml:space="preserve">39.3286514282227</t>
   </si>
   <si>
     <t xml:space="preserve">39.041576385498</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">38.8023490905762</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4674377441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1325187683105</t>
+    <t xml:space="preserve">38.4674339294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1325225830078</t>
   </si>
   <si>
     <t xml:space="preserve">38.8980445861816</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">39.2807998657227</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9027862548828</t>
+    <t xml:space="preserve">39.9027900695801</t>
   </si>
   <si>
     <t xml:space="preserve">41.1946067810059</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">42.1036605834961</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5342674255371</t>
+    <t xml:space="preserve">42.5342636108398</t>
   </si>
   <si>
     <t xml:space="preserve">41.6730575561523</t>
@@ -1802,16 +1802,16 @@
     <t xml:space="preserve">41.912281036377</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0605621337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4911689758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2566947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7829895019531</t>
+    <t xml:space="preserve">43.0605659484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4911651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2566909790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7829856872559</t>
   </si>
   <si>
     <t xml:space="preserve">43.4433250427246</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">45.404972076416</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2614364624023</t>
+    <t xml:space="preserve">45.2614326477051</t>
   </si>
   <si>
     <t xml:space="preserve">45.5963516235352</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">47.6536903381348</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8976593017578</t>
+    <t xml:space="preserve">48.8976554870605</t>
   </si>
   <si>
     <t xml:space="preserve">48.6105918884277</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">50.6200866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0028457641602</t>
+    <t xml:space="preserve">51.0028419494629</t>
   </si>
   <si>
     <t xml:space="preserve">52.7252655029297</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">51.9597434997559</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8640594482422</t>
+    <t xml:space="preserve">51.8640632629395</t>
   </si>
   <si>
     <t xml:space="preserve">51.6726760864258</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">48.3235244750977</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0459442138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3856048583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.907154083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8545608520508</t>
+    <t xml:space="preserve">50.0459403991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3856086730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9071578979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.854564666748</t>
   </si>
 